--- a/AAPL.xlsx
+++ b/AAPL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3D3E39-7C56-394A-A3C5-C6C506FED9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2B82F2-0826-D343-9076-E9AEA96BA099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="14" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="4" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -1194,7 +1194,7 @@
     <numFmt numFmtId="168" formatCode="#,##0.0_);\(#,##0.0\)"/>
     <numFmt numFmtId="169" formatCode="0.00_);\(0.00\)"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1367,12 +1367,6 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="18">
@@ -1956,9 +1950,18 @@
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="24" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="24" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="18" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="18" fillId="11" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="38" fontId="11" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1966,6 +1969,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1986,18 +1992,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="18" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="18" fillId="11" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="38" fontId="11" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="11" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2544,7 +2538,7 @@
         <v>74</v>
       </c>
       <c r="C3" s="35">
-        <f ca="1">[1]Sheet1!$C$17</f>
+        <f>[1]Sheet1!$C$17</f>
         <v>271.06</v>
       </c>
     </row>
@@ -2570,7 +2564,7 @@
         <v>110</v>
       </c>
       <c r="C11" s="93">
-        <f ca="1">$C$3/'Statement Q'!$N$19</f>
+        <f>$C$3/'Statement Q'!$N$19</f>
         <v>34.336752252137515</v>
       </c>
     </row>
@@ -2579,7 +2573,7 @@
         <v>190</v>
       </c>
       <c r="C12" s="93">
-        <f ca="1">$C$3/Statements!W18</f>
+        <f>$C$3/Statements!W18</f>
         <v>34.336752252137515</v>
       </c>
     </row>
@@ -2588,7 +2582,7 @@
         <v>111</v>
       </c>
       <c r="C13" s="98">
-        <f ca="1">$C$3/('Statement Q'!$N$5/'Statement Q'!$N$17)</f>
+        <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$17)</f>
         <v>9.2835671472876413</v>
       </c>
     </row>
@@ -2597,7 +2591,7 @@
         <v>149</v>
       </c>
       <c r="C15" s="20">
-        <f ca="1">C3*'Statement Q'!N100</f>
+        <f>C3*'Statement Q'!N100</f>
         <v>3979431.86</v>
       </c>
     </row>
@@ -2624,7 +2618,7 @@
         <v>151</v>
       </c>
       <c r="C18" s="20">
-        <f ca="1">C15+C17-C16</f>
+        <f>C15+C17-C16</f>
         <v>4003033.86</v>
       </c>
     </row>
@@ -2845,60 +2839,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="181" t="s">
+      <c r="C2" s="196" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="181"/>
-      <c r="E2" s="181"/>
-      <c r="F2" s="181"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="188" t="s">
+      <c r="D2" s="196"/>
+      <c r="E2" s="196"/>
+      <c r="F2" s="196"/>
+      <c r="G2" s="199"/>
+      <c r="H2" s="200" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="181"/>
-      <c r="J2" s="181"/>
-      <c r="K2" s="181"/>
-      <c r="L2" s="181"/>
-      <c r="S2" s="190"/>
-      <c r="T2" s="190"/>
-      <c r="U2" s="190"/>
-      <c r="V2" s="190"/>
-      <c r="W2" s="190"/>
-      <c r="X2" s="190"/>
-      <c r="Y2" s="190"/>
-      <c r="Z2" s="190"/>
-      <c r="AA2" s="190"/>
-      <c r="AB2" s="190"/>
-      <c r="AC2" s="190"/>
+      <c r="I2" s="196"/>
+      <c r="J2" s="196"/>
+      <c r="K2" s="196"/>
+      <c r="L2" s="196"/>
+      <c r="S2" s="202"/>
+      <c r="T2" s="202"/>
+      <c r="U2" s="202"/>
+      <c r="V2" s="202"/>
+      <c r="W2" s="202"/>
+      <c r="X2" s="202"/>
+      <c r="Y2" s="202"/>
+      <c r="Z2" s="202"/>
+      <c r="AA2" s="202"/>
+      <c r="AB2" s="202"/>
+      <c r="AC2" s="202"/>
       <c r="AE2" s="122"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="201" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="189"/>
-      <c r="K4" s="189"/>
-      <c r="L4" s="189"/>
-      <c r="S4" s="190"/>
-      <c r="T4" s="190"/>
-      <c r="U4" s="190"/>
-      <c r="V4" s="190"/>
-      <c r="W4" s="190"/>
-      <c r="X4" s="190"/>
-      <c r="Y4" s="190"/>
-      <c r="Z4" s="190"/>
-      <c r="AA4" s="190"/>
-      <c r="AB4" s="190"/>
-      <c r="AC4" s="190"/>
+      <c r="D4" s="201"/>
+      <c r="E4" s="201"/>
+      <c r="F4" s="201"/>
+      <c r="G4" s="201"/>
+      <c r="H4" s="201"/>
+      <c r="I4" s="201"/>
+      <c r="J4" s="201"/>
+      <c r="K4" s="201"/>
+      <c r="L4" s="201"/>
+      <c r="S4" s="202"/>
+      <c r="T4" s="202"/>
+      <c r="U4" s="202"/>
+      <c r="V4" s="202"/>
+      <c r="W4" s="202"/>
+      <c r="X4" s="202"/>
+      <c r="Y4" s="202"/>
+      <c r="Z4" s="202"/>
+      <c r="AA4" s="202"/>
+      <c r="AB4" s="202"/>
+      <c r="AC4" s="202"/>
       <c r="AE4" s="123"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -3328,43 +3322,43 @@
         <v>109</v>
       </c>
       <c r="C12" s="109">
-        <f>C8-C11</f>
+        <f t="shared" ref="C12:L12" si="1">C8-C11</f>
         <v>108949</v>
       </c>
       <c r="D12" s="109">
-        <f>D8-D11</f>
+        <f t="shared" si="1"/>
         <v>119437</v>
       </c>
       <c r="E12" s="109">
-        <f>E8-E11</f>
+        <f t="shared" si="1"/>
         <v>114301</v>
       </c>
       <c r="F12" s="109">
-        <f>F8-F11</f>
+        <f t="shared" si="1"/>
         <v>123216</v>
       </c>
       <c r="G12" s="136">
-        <f>G8-G11</f>
+        <f t="shared" si="1"/>
         <v>133050</v>
       </c>
       <c r="H12" s="109">
-        <f>H8-H11</f>
+        <f t="shared" si="1"/>
         <v>137256.83886000002</v>
       </c>
       <c r="I12" s="109">
-        <f>I8-I11</f>
+        <f t="shared" si="1"/>
         <v>143416.11125069999</v>
       </c>
       <c r="J12" s="109">
-        <f>J8-J11</f>
+        <f t="shared" si="1"/>
         <v>149546.31281875688</v>
       </c>
       <c r="K12" s="109">
-        <f>K8-K11</f>
+        <f t="shared" si="1"/>
         <v>154128.43771134</v>
       </c>
       <c r="L12" s="109">
-        <f>L8-L11</f>
+        <f t="shared" si="1"/>
         <v>165252.65618158632</v>
       </c>
       <c r="N12" s="115"/>
@@ -3383,58 +3377,58 @@
       <c r="AE12" s="104"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C15" s="189" t="s">
+      <c r="C15" s="201" t="s">
         <v>142</v>
       </c>
-      <c r="D15" s="189"/>
-      <c r="E15" s="189"/>
-      <c r="F15" s="189"/>
-      <c r="G15" s="189"/>
-      <c r="H15" s="189"/>
-      <c r="I15" s="189"/>
-      <c r="J15" s="189"/>
-      <c r="K15" s="189"/>
-      <c r="L15" s="189"/>
+      <c r="D15" s="201"/>
+      <c r="E15" s="201"/>
+      <c r="F15" s="201"/>
+      <c r="G15" s="201"/>
+      <c r="H15" s="201"/>
+      <c r="I15" s="201"/>
+      <c r="J15" s="201"/>
+      <c r="K15" s="201"/>
+      <c r="L15" s="201"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C16" s="62">
-        <f>C5</f>
+        <f t="shared" ref="C16:L16" si="2">C5</f>
         <v>2021</v>
       </c>
       <c r="D16" s="62">
-        <f>D5</f>
+        <f t="shared" si="2"/>
         <v>2022</v>
       </c>
       <c r="E16" s="62">
-        <f>E5</f>
+        <f t="shared" si="2"/>
         <v>2023</v>
       </c>
       <c r="F16" s="62">
-        <f>F5</f>
+        <f t="shared" si="2"/>
         <v>2024</v>
       </c>
       <c r="G16" s="62">
-        <f>G5</f>
+        <f t="shared" si="2"/>
         <v>2025</v>
       </c>
       <c r="H16" s="62">
-        <f>H5</f>
+        <f t="shared" si="2"/>
         <v>2026</v>
       </c>
       <c r="I16" s="62">
-        <f>I5</f>
+        <f t="shared" si="2"/>
         <v>2027</v>
       </c>
       <c r="J16" s="62">
-        <f>J5</f>
+        <f t="shared" si="2"/>
         <v>2028</v>
       </c>
       <c r="K16" s="62">
-        <f>K5</f>
+        <f t="shared" si="2"/>
         <v>2029</v>
       </c>
       <c r="L16" s="62">
-        <f>L5</f>
+        <f t="shared" si="2"/>
         <v>2030</v>
       </c>
     </row>
@@ -3479,61 +3473,61 @@
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C20" s="189" t="s">
+      <c r="C20" s="201" t="s">
         <v>314</v>
       </c>
-      <c r="D20" s="189"/>
-      <c r="E20" s="189"/>
-      <c r="F20" s="189"/>
-      <c r="G20" s="189"/>
-      <c r="H20" s="189"/>
-      <c r="I20" s="189"/>
-      <c r="J20" s="189"/>
-      <c r="K20" s="189"/>
-      <c r="L20" s="189"/>
+      <c r="D20" s="201"/>
+      <c r="E20" s="201"/>
+      <c r="F20" s="201"/>
+      <c r="G20" s="201"/>
+      <c r="H20" s="201"/>
+      <c r="I20" s="201"/>
+      <c r="J20" s="201"/>
+      <c r="K20" s="201"/>
+      <c r="L20" s="201"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
         <v>133</v>
       </c>
       <c r="C21" s="62">
-        <f>C5</f>
+        <f t="shared" ref="C21:L21" si="3">C5</f>
         <v>2021</v>
       </c>
       <c r="D21" s="62">
-        <f>D5</f>
+        <f t="shared" si="3"/>
         <v>2022</v>
       </c>
       <c r="E21" s="62">
-        <f>E5</f>
+        <f t="shared" si="3"/>
         <v>2023</v>
       </c>
       <c r="F21" s="62">
-        <f>F5</f>
+        <f t="shared" si="3"/>
         <v>2024</v>
       </c>
       <c r="G21" s="62">
-        <f>G5</f>
+        <f t="shared" si="3"/>
         <v>2025</v>
       </c>
       <c r="H21" s="62">
-        <f>H5</f>
+        <f t="shared" si="3"/>
         <v>2026</v>
       </c>
       <c r="I21" s="62">
-        <f>I5</f>
+        <f t="shared" si="3"/>
         <v>2027</v>
       </c>
       <c r="J21" s="62">
-        <f>J5</f>
+        <f t="shared" si="3"/>
         <v>2028</v>
       </c>
       <c r="K21" s="62">
-        <f>K5</f>
+        <f t="shared" si="3"/>
         <v>2029</v>
       </c>
       <c r="L21" s="62">
-        <f>L5</f>
+        <f t="shared" si="3"/>
         <v>2030</v>
       </c>
     </row>
@@ -3682,61 +3676,61 @@
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="189" t="s">
+      <c r="C27" s="201" t="s">
         <v>145</v>
       </c>
-      <c r="D27" s="189"/>
-      <c r="E27" s="189"/>
-      <c r="F27" s="189"/>
-      <c r="G27" s="189"/>
-      <c r="H27" s="189"/>
-      <c r="I27" s="189"/>
-      <c r="J27" s="189"/>
-      <c r="K27" s="189"/>
-      <c r="L27" s="189"/>
+      <c r="D27" s="201"/>
+      <c r="E27" s="201"/>
+      <c r="F27" s="201"/>
+      <c r="G27" s="201"/>
+      <c r="H27" s="201"/>
+      <c r="I27" s="201"/>
+      <c r="J27" s="201"/>
+      <c r="K27" s="201"/>
+      <c r="L27" s="201"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
         <v>133</v>
       </c>
       <c r="C28" s="62">
-        <f>C5</f>
+        <f t="shared" ref="C28:L28" si="4">C5</f>
         <v>2021</v>
       </c>
       <c r="D28" s="62">
-        <f>D5</f>
+        <f t="shared" si="4"/>
         <v>2022</v>
       </c>
       <c r="E28" s="62">
-        <f>E5</f>
+        <f t="shared" si="4"/>
         <v>2023</v>
       </c>
       <c r="F28" s="62">
-        <f>F5</f>
+        <f t="shared" si="4"/>
         <v>2024</v>
       </c>
       <c r="G28" s="62">
-        <f>G5</f>
+        <f t="shared" si="4"/>
         <v>2025</v>
       </c>
       <c r="H28" s="62">
-        <f>H5</f>
+        <f t="shared" si="4"/>
         <v>2026</v>
       </c>
       <c r="I28" s="62">
-        <f>I5</f>
+        <f t="shared" si="4"/>
         <v>2027</v>
       </c>
       <c r="J28" s="62">
-        <f>J5</f>
+        <f t="shared" si="4"/>
         <v>2028</v>
       </c>
       <c r="K28" s="62">
-        <f>K5</f>
+        <f t="shared" si="4"/>
         <v>2029</v>
       </c>
       <c r="L28" s="62">
-        <f>L5</f>
+        <f t="shared" si="4"/>
         <v>2030</v>
       </c>
     </row>
@@ -3749,39 +3743,39 @@
         <v>94456.319832977737</v>
       </c>
       <c r="D29" s="133">
-        <f t="shared" ref="D29:L29" si="1">D12*(1-D17)</f>
+        <f t="shared" ref="D29:L29" si="5">D12*(1-D17)</f>
         <v>100082.87709797402</v>
       </c>
       <c r="E29" s="133">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>97476.836665611598</v>
       </c>
       <c r="F29" s="133">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>93531.80528809168</v>
       </c>
       <c r="G29" s="140">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>112280.89189250277</v>
       </c>
       <c r="H29" s="133">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>108432.90269940002</v>
       </c>
       <c r="I29" s="133">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>113298.72788805299</v>
       </c>
       <c r="J29" s="133">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>118141.58712681795</v>
       </c>
       <c r="K29" s="133">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>121761.4657919586</v>
       </c>
       <c r="L29" s="133">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>130549.59838345321</v>
       </c>
     </row>
@@ -3794,45 +3788,44 @@
         <v>89744.319832977737</v>
       </c>
       <c r="D30" s="109">
-        <f t="shared" ref="D30:L30" si="2">D29+D22-D23+D24</f>
+        <f t="shared" ref="D30:L30" si="6">D29+D22-D23+D24</f>
         <v>101678.87709797402</v>
       </c>
       <c r="E30" s="109">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>91459.836665611598</v>
       </c>
       <c r="F30" s="109">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>99180.80528809168</v>
       </c>
       <c r="G30" s="136">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>86263.891892502768</v>
       </c>
       <c r="H30" s="109">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>99403.682848427416</v>
       </c>
       <c r="I30" s="109">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>103992.52677256019</v>
       </c>
       <c r="J30" s="109">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>108201.66099470138</v>
       </c>
       <c r="K30" s="109">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>111727.01960804759</v>
       </c>
       <c r="L30" s="109">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>119949.25929680829</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C15:L15"/>
     <mergeCell ref="C20:L20"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="C2:G2"/>
@@ -3841,6 +3834,7 @@
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C15:L15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3900,10 +3894,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="181" t="s">
+      <c r="B4" s="196" t="s">
         <v>160</v>
       </c>
-      <c r="C4" s="181"/>
+      <c r="C4" s="196"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -3919,7 +3913,7 @@
         <v>74</v>
       </c>
       <c r="C6" s="145">
-        <f ca="1">Overview!C3</f>
+        <f>Overview!C3</f>
         <v>271.06</v>
       </c>
     </row>
@@ -3928,7 +3922,7 @@
         <v>147</v>
       </c>
       <c r="C7" s="147">
-        <f ca="1">C5*C6</f>
+        <f>C5*C6</f>
         <v>3979431.86</v>
       </c>
     </row>
@@ -3946,7 +3940,7 @@
         <v>162</v>
       </c>
       <c r="C9" s="170">
-        <f ca="1">[1]Sheet1!$C$10/1000</f>
+        <f>[1]Sheet1!$C$10/1000</f>
         <v>4.3099999999999999E-2</v>
       </c>
     </row>
@@ -3955,7 +3949,7 @@
         <v>163</v>
       </c>
       <c r="C10" s="145">
-        <f ca="1">[1]Sheet1!$F$17</f>
+        <f>[1]Sheet1!$F$17</f>
         <v>1.0716000000000001</v>
       </c>
     </row>
@@ -3985,17 +3979,17 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="181" t="s">
+      <c r="B15" s="196" t="s">
         <v>166</v>
       </c>
-      <c r="C15" s="181"/>
+      <c r="C15" s="196"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
         <v>157</v>
       </c>
       <c r="C16" s="148">
-        <f ca="1">C8/(C8+C7)</f>
+        <f>C8/(C8+C7)</f>
         <v>2.2238406677978117E-2</v>
       </c>
     </row>
@@ -4004,7 +3998,7 @@
         <v>158</v>
       </c>
       <c r="C17" s="148">
-        <f ca="1">C7/(C8+C7)</f>
+        <f>C7/(C8+C7)</f>
         <v>0.97776159332202184</v>
       </c>
     </row>
@@ -4022,7 +4016,7 @@
         <v>159</v>
       </c>
       <c r="C19" s="148">
-        <f ca="1">C9+C10*C11</f>
+        <f>C9+C10*C11</f>
         <v>0.102038</v>
       </c>
     </row>
@@ -4031,7 +4025,7 @@
         <v>156</v>
       </c>
       <c r="C20" s="148">
-        <f ca="1">(C17*C19)+(C16*C18)</f>
+        <f>(C17*C19)+(C16*C18)</f>
         <v>0.10055941281679459</v>
       </c>
     </row>
@@ -4079,60 +4073,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="181" t="s">
+      <c r="C3" s="196" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="181"/>
-      <c r="E3" s="181"/>
-      <c r="F3" s="181"/>
-      <c r="G3" s="187"/>
-      <c r="H3" s="188" t="s">
+      <c r="D3" s="196"/>
+      <c r="E3" s="196"/>
+      <c r="F3" s="196"/>
+      <c r="G3" s="199"/>
+      <c r="H3" s="200" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="181"/>
-      <c r="J3" s="181"/>
-      <c r="K3" s="181"/>
-      <c r="L3" s="181"/>
-      <c r="P3" s="190"/>
-      <c r="Q3" s="190"/>
-      <c r="R3" s="190"/>
-      <c r="S3" s="190"/>
-      <c r="T3" s="190"/>
-      <c r="U3" s="190"/>
-      <c r="V3" s="190"/>
-      <c r="W3" s="190"/>
-      <c r="X3" s="190"/>
-      <c r="Y3" s="190"/>
-      <c r="Z3" s="190"/>
+      <c r="I3" s="196"/>
+      <c r="J3" s="196"/>
+      <c r="K3" s="196"/>
+      <c r="L3" s="196"/>
+      <c r="P3" s="202"/>
+      <c r="Q3" s="202"/>
+      <c r="R3" s="202"/>
+      <c r="S3" s="202"/>
+      <c r="T3" s="202"/>
+      <c r="U3" s="202"/>
+      <c r="V3" s="202"/>
+      <c r="W3" s="202"/>
+      <c r="X3" s="202"/>
+      <c r="Y3" s="202"/>
+      <c r="Z3" s="202"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="189" t="s">
+      <c r="C5" s="201" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="189"/>
-      <c r="E5" s="189"/>
-      <c r="F5" s="189"/>
-      <c r="G5" s="189"/>
-      <c r="H5" s="189"/>
-      <c r="I5" s="189"/>
-      <c r="J5" s="189"/>
-      <c r="K5" s="189"/>
-      <c r="L5" s="189"/>
-      <c r="P5" s="190"/>
-      <c r="Q5" s="190"/>
-      <c r="R5" s="190"/>
-      <c r="S5" s="190"/>
-      <c r="T5" s="190"/>
-      <c r="U5" s="190"/>
-      <c r="V5" s="190"/>
-      <c r="W5" s="190"/>
-      <c r="X5" s="190"/>
-      <c r="Y5" s="190"/>
-      <c r="Z5" s="190"/>
+      <c r="D5" s="201"/>
+      <c r="E5" s="201"/>
+      <c r="F5" s="201"/>
+      <c r="G5" s="201"/>
+      <c r="H5" s="201"/>
+      <c r="I5" s="201"/>
+      <c r="J5" s="201"/>
+      <c r="K5" s="201"/>
+      <c r="L5" s="201"/>
+      <c r="P5" s="202"/>
+      <c r="Q5" s="202"/>
+      <c r="R5" s="202"/>
+      <c r="S5" s="202"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="202"/>
+      <c r="V5" s="202"/>
+      <c r="W5" s="202"/>
+      <c r="X5" s="202"/>
+      <c r="Y5" s="202"/>
+      <c r="Z5" s="202"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -4284,7 +4278,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="133">
-        <f ca="1">L7*(1+C14)/(C15-C14)</f>
+        <f>L7*(1+C14)/(C15-C14)</f>
         <v>1518733.0717142213</v>
       </c>
       <c r="N8" s="91"/>
@@ -4338,23 +4332,23 @@
       <c r="F10" s="130"/>
       <c r="G10" s="150"/>
       <c r="H10" s="133">
-        <f ca="1">H7/(1+$C$15)^H9</f>
+        <f>H7/(1+$C$15)^H9</f>
         <v>90321.050995340236</v>
       </c>
       <c r="I10" s="133">
-        <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
+        <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
         <v>85856.888535362625</v>
       </c>
       <c r="J10" s="133">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>81169.608254759558</v>
       </c>
       <c r="K10" s="133">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>76156.020760377622</v>
       </c>
       <c r="L10" s="133">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>74289.957120385516</v>
       </c>
       <c r="N10" s="91"/>
@@ -4373,15 +4367,15 @@
       <c r="J11" s="130"/>
       <c r="K11" s="130"/>
       <c r="L11" s="133">
-        <f ca="1">L8/(1+C15)^L9</f>
+        <f>L8/(1+C15)^L9</f>
         <v>940619.52059059578</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="181" t="s">
+      <c r="B13" s="196" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="181"/>
+      <c r="C13" s="196"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -4396,22 +4390,22 @@
         <v>156</v>
       </c>
       <c r="C15" s="149">
-        <f ca="1">WACC!C20</f>
+        <f>WACC!C20</f>
         <v>0.10055941281679459</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="181" t="s">
+      <c r="B18" s="196" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="181"/>
+      <c r="C18" s="196"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>179</v>
       </c>
       <c r="C19" s="104">
-        <f ca="1">SUM(H10:L10)</f>
+        <f>SUM(H10:L10)</f>
         <v>407793.52566622559</v>
       </c>
     </row>
@@ -4420,7 +4414,7 @@
         <v>173</v>
       </c>
       <c r="C20" s="104">
-        <f ca="1">L11</f>
+        <f>L11</f>
         <v>940619.52059059578</v>
       </c>
     </row>
@@ -4429,7 +4423,7 @@
         <v>176</v>
       </c>
       <c r="C21" s="109">
-        <f ca="1">C19+C20</f>
+        <f>C19+C20</f>
         <v>1348413.0462568214</v>
       </c>
     </row>
@@ -4456,7 +4450,7 @@
         <v>177</v>
       </c>
       <c r="C24" s="109">
-        <f ca="1">C21+C22-C23</f>
+        <f>C21+C22-C23</f>
         <v>1324811.0462568214</v>
       </c>
     </row>
@@ -4474,7 +4468,7 @@
         <v>178</v>
       </c>
       <c r="C26" s="152">
-        <f ca="1">C24/C25</f>
+        <f>C24/C25</f>
         <v>88.797281829606987</v>
       </c>
     </row>
@@ -4518,37 +4512,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="181" t="s">
+      <c r="C2" s="196" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="181"/>
-      <c r="E2" s="181"/>
-      <c r="F2" s="181"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="188" t="s">
+      <c r="D2" s="196"/>
+      <c r="E2" s="196"/>
+      <c r="F2" s="196"/>
+      <c r="G2" s="199"/>
+      <c r="H2" s="200" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="181"/>
-      <c r="J2" s="181"/>
-      <c r="K2" s="181"/>
-      <c r="L2" s="181"/>
+      <c r="I2" s="196"/>
+      <c r="J2" s="196"/>
+      <c r="K2" s="196"/>
+      <c r="L2" s="196"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="201" t="s">
         <v>318</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="189"/>
-      <c r="K4" s="189"/>
-      <c r="L4" s="189"/>
+      <c r="D4" s="201"/>
+      <c r="E4" s="201"/>
+      <c r="F4" s="201"/>
+      <c r="G4" s="201"/>
+      <c r="H4" s="201"/>
+      <c r="I4" s="201"/>
+      <c r="J4" s="201"/>
+      <c r="K4" s="201"/>
+      <c r="L4" s="201"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -4737,18 +4731,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="189" t="s">
+      <c r="C10" s="201" t="s">
         <v>116</v>
       </c>
-      <c r="D10" s="189"/>
-      <c r="E10" s="189"/>
-      <c r="F10" s="189"/>
-      <c r="G10" s="189"/>
-      <c r="H10" s="189"/>
-      <c r="I10" s="189"/>
-      <c r="J10" s="189"/>
-      <c r="K10" s="189"/>
-      <c r="L10" s="189"/>
+      <c r="D10" s="201"/>
+      <c r="E10" s="201"/>
+      <c r="F10" s="201"/>
+      <c r="G10" s="201"/>
+      <c r="H10" s="201"/>
+      <c r="I10" s="201"/>
+      <c r="J10" s="201"/>
+      <c r="K10" s="201"/>
+      <c r="L10" s="201"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -4930,18 +4924,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="189" t="s">
+      <c r="C16" s="201" t="s">
         <v>217</v>
       </c>
-      <c r="D16" s="189"/>
-      <c r="E16" s="189"/>
-      <c r="F16" s="189"/>
-      <c r="G16" s="189"/>
-      <c r="H16" s="189"/>
-      <c r="I16" s="189"/>
-      <c r="J16" s="189"/>
-      <c r="K16" s="189"/>
-      <c r="L16" s="189"/>
+      <c r="D16" s="201"/>
+      <c r="E16" s="201"/>
+      <c r="F16" s="201"/>
+      <c r="G16" s="201"/>
+      <c r="H16" s="201"/>
+      <c r="I16" s="201"/>
+      <c r="J16" s="201"/>
+      <c r="K16" s="201"/>
+      <c r="L16" s="201"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -5007,7 +5001,7 @@
         <f>'Statement Y'!K19</f>
         <v>15408</v>
       </c>
-      <c r="G18" s="194">
+      <c r="G18" s="184">
         <f>'Statement Y'!L19</f>
         <v>15005</v>
       </c>
@@ -5050,7 +5044,7 @@
         <f t="shared" si="5"/>
         <v>-2.5611838360842354E-2</v>
       </c>
-      <c r="G19" s="195">
+      <c r="G19" s="185">
         <f t="shared" si="5"/>
         <v>-2.6155244029075764E-2</v>
       </c>
@@ -5075,18 +5069,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="189" t="s">
+      <c r="C21" s="201" t="s">
         <v>319</v>
       </c>
-      <c r="D21" s="189"/>
-      <c r="E21" s="189"/>
-      <c r="F21" s="189"/>
-      <c r="G21" s="189"/>
-      <c r="H21" s="189"/>
-      <c r="I21" s="189"/>
-      <c r="J21" s="189"/>
-      <c r="K21" s="189"/>
-      <c r="L21" s="189"/>
+      <c r="D21" s="201"/>
+      <c r="E21" s="201"/>
+      <c r="F21" s="201"/>
+      <c r="G21" s="201"/>
+      <c r="H21" s="201"/>
+      <c r="I21" s="201"/>
+      <c r="J21" s="201"/>
+      <c r="K21" s="201"/>
+      <c r="L21" s="201"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -5136,23 +5130,23 @@
       <c r="B23" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="196">
+      <c r="C23" s="186">
         <f>'Statement Y'!H165</f>
         <v>146.91999999999999</v>
       </c>
-      <c r="D23" s="196">
+      <c r="D23" s="186">
         <f>'Statement Y'!I165</f>
         <v>150.43</v>
       </c>
-      <c r="E23" s="196">
+      <c r="E23" s="186">
         <f>'Statement Y'!J165</f>
         <v>171.21</v>
       </c>
-      <c r="F23" s="196">
+      <c r="F23" s="186">
         <f>'Statement Y'!K165</f>
         <v>227.79</v>
       </c>
-      <c r="G23" s="197">
+      <c r="G23" s="187">
         <f>'Statement Y'!L165</f>
         <v>255.46</v>
       </c>
@@ -5170,18 +5164,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="189" t="s">
+      <c r="C26" s="201" t="s">
         <v>320</v>
       </c>
-      <c r="D26" s="189"/>
-      <c r="E26" s="189"/>
-      <c r="F26" s="189"/>
-      <c r="G26" s="189"/>
-      <c r="H26" s="189"/>
-      <c r="I26" s="189"/>
-      <c r="J26" s="189"/>
-      <c r="K26" s="189"/>
-      <c r="L26" s="189"/>
+      <c r="D26" s="201"/>
+      <c r="E26" s="201"/>
+      <c r="F26" s="201"/>
+      <c r="G26" s="201"/>
+      <c r="H26" s="201"/>
+      <c r="I26" s="201"/>
+      <c r="J26" s="201"/>
+      <c r="K26" s="201"/>
+      <c r="L26" s="201"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -5231,23 +5225,23 @@
       <c r="B28" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C28" s="198">
+      <c r="C28" s="188">
         <f>C23/(C6/C18)</f>
         <v>6.7733478761238537</v>
       </c>
-      <c r="D28" s="198">
+      <c r="D28" s="188">
         <f t="shared" ref="D28:G28" si="8">D23/(D6/D18)</f>
         <v>6.2281151224361446</v>
       </c>
-      <c r="E28" s="198">
+      <c r="E28" s="188">
         <f t="shared" si="8"/>
         <v>7.0635264359419239</v>
       </c>
-      <c r="F28" s="198">
+      <c r="F28" s="188">
         <f t="shared" si="8"/>
         <v>8.9756372703210712</v>
       </c>
-      <c r="G28" s="199">
+      <c r="G28" s="189">
         <f t="shared" si="8"/>
         <v>9.2108037514327386</v>
       </c>
@@ -5278,7 +5272,7 @@
         <f t="shared" si="9"/>
         <v>3509788.32</v>
       </c>
-      <c r="G29" s="200">
+      <c r="G29" s="190">
         <f t="shared" si="9"/>
         <v>3833177.3000000003</v>
       </c>
@@ -5297,19 +5291,19 @@
         <f>Statements!H35+Statements!H36+Statements!H38</f>
         <v>124719</v>
       </c>
-      <c r="D30" s="201">
+      <c r="D30" s="191">
         <f>Statements!I35+Statements!I36+Statements!I38</f>
         <v>120069</v>
       </c>
-      <c r="E30" s="201">
+      <c r="E30" s="191">
         <f>Statements!J35+Statements!J36+Statements!J38</f>
         <v>111088</v>
       </c>
-      <c r="F30" s="201">
+      <c r="F30" s="191">
         <f>Statements!K35+Statements!K36+Statements!K38</f>
         <v>106629</v>
       </c>
-      <c r="G30" s="202">
+      <c r="G30" s="192">
         <f>Statements!L35+Statements!L36+Statements!L38</f>
         <v>98657</v>
       </c>
@@ -5324,23 +5318,23 @@
       <c r="B31" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C31" s="201">
+      <c r="C31" s="191">
         <f>Statements!H21</f>
         <v>62639</v>
       </c>
-      <c r="D31" s="201">
+      <c r="D31" s="191">
         <f>Statements!I21</f>
         <v>48304</v>
       </c>
-      <c r="E31" s="201">
+      <c r="E31" s="191">
         <f>Statements!J21</f>
         <v>61555</v>
       </c>
-      <c r="F31" s="201">
+      <c r="F31" s="191">
         <f>Statements!K21</f>
         <v>65171</v>
       </c>
-      <c r="G31" s="202">
+      <c r="G31" s="192">
         <f>Statements!L21</f>
         <v>54697</v>
       </c>
@@ -5371,7 +5365,7 @@
         <f t="shared" si="10"/>
         <v>3551246.32</v>
       </c>
-      <c r="G32" s="200">
+      <c r="G32" s="190">
         <f t="shared" si="10"/>
         <v>3877137.3000000003</v>
       </c>
@@ -5386,23 +5380,23 @@
       <c r="B33" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="C33" s="198">
+      <c r="C33" s="188">
         <f>C32/C7</f>
         <v>23.31261232319709</v>
       </c>
-      <c r="D33" s="198">
+      <c r="D33" s="188">
         <f t="shared" ref="D33:G33" si="11">D32/D7</f>
         <v>21.163334477590698</v>
       </c>
-      <c r="E33" s="198">
+      <c r="E33" s="188">
         <f t="shared" si="11"/>
         <v>24.119445411676189</v>
       </c>
-      <c r="F33" s="198">
+      <c r="F33" s="188">
         <f t="shared" si="11"/>
         <v>28.821308271653031</v>
       </c>
-      <c r="G33" s="199">
+      <c r="G33" s="189">
         <f t="shared" si="11"/>
         <v>29.140453213077791</v>
       </c>
@@ -5417,23 +5411,23 @@
       <c r="B34" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="C34" s="198">
+      <c r="C34" s="188">
         <f>C32/C8</f>
         <v>28.30135438907951</v>
       </c>
-      <c r="D34" s="198">
+      <c r="D34" s="188">
         <f t="shared" ref="D34:G34" si="12">D32/D8</f>
         <v>24.859491490690008</v>
       </c>
-      <c r="E34" s="198">
+      <c r="E34" s="188">
         <f t="shared" si="12"/>
         <v>30.143031416942936</v>
       </c>
-      <c r="F34" s="198">
+      <c r="F34" s="188">
         <f t="shared" si="12"/>
         <v>35.805782274953827</v>
       </c>
-      <c r="G34" s="199">
+      <c r="G34" s="189">
         <f t="shared" si="12"/>
         <v>44.945077423952441</v>
       </c>
@@ -5451,10 +5445,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="181" t="s">
+      <c r="B37" s="196" t="s">
         <v>324</v>
       </c>
-      <c r="C37" s="181"/>
+      <c r="C37" s="196"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -5471,7 +5465,7 @@
         <v>156</v>
       </c>
       <c r="C39" s="138">
-        <f ca="1">WACC!C20</f>
+        <f>WACC!C20</f>
         <v>0.10055941281679459</v>
       </c>
     </row>
@@ -5515,15 +5509,15 @@
         <v>327</v>
       </c>
       <c r="C44" s="152">
-        <f ca="1">C43/(1+C48)^5</f>
+        <f>C43/(1+C48)^5</f>
         <v>174.91540155566045</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="181" t="s">
+      <c r="B46" s="196" t="s">
         <v>193</v>
       </c>
-      <c r="C46" s="181"/>
+      <c r="C46" s="196"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -5539,7 +5533,7 @@
         <v>156</v>
       </c>
       <c r="C48" s="138">
-        <f ca="1">WACC!C20</f>
+        <f>WACC!C20</f>
         <v>0.10055941281679459</v>
       </c>
     </row>
@@ -5574,15 +5568,15 @@
         <v>327</v>
       </c>
       <c r="C52" s="152">
-        <f ca="1">C51/(1+C48)^5</f>
+        <f>C51/(1+C48)^5</f>
         <v>145.62787316121953</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="181" t="s">
+      <c r="B54" s="196" t="s">
         <v>328</v>
       </c>
-      <c r="C54" s="181"/>
+      <c r="C54" s="196"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -5598,7 +5592,7 @@
         <v>156</v>
       </c>
       <c r="C56" s="138">
-        <f ca="1">[2]WACC!C20</f>
+        <f>[2]WACC!C20</f>
         <v>8.92125E-2</v>
       </c>
     </row>
@@ -5642,7 +5636,7 @@
         <v>327</v>
       </c>
       <c r="C61" s="152">
-        <f ca="1">C60/(1+C56)^5</f>
+        <f>C60/(1+C56)^5</f>
         <v>162.53320471955453</v>
       </c>
     </row>
@@ -5692,10 +5686,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="181" t="s">
+      <c r="B4" s="196" t="s">
         <v>201</v>
       </c>
-      <c r="C4" s="181"/>
+      <c r="C4" s="196"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -5703,7 +5697,7 @@
         <v>198</v>
       </c>
       <c r="C5" s="167">
-        <f ca="1">DCF!C26</f>
+        <f>DCF!C26</f>
         <v>88.797281829606987</v>
       </c>
     </row>
@@ -5712,7 +5706,7 @@
         <v>331</v>
       </c>
       <c r="C6" s="167">
-        <f ca="1">Multiples!C44</f>
+        <f>Multiples!C44</f>
         <v>174.91540155566045</v>
       </c>
     </row>
@@ -5721,7 +5715,7 @@
         <v>199</v>
       </c>
       <c r="C7" s="167">
-        <f ca="1">Multiples!C52</f>
+        <f>Multiples!C52</f>
         <v>145.62787316121953</v>
       </c>
     </row>
@@ -5730,7 +5724,7 @@
         <v>332</v>
       </c>
       <c r="C8" s="167">
-        <f ca="1">Multiples!C61</f>
+        <f>Multiples!C61</f>
         <v>162.53320471955453</v>
       </c>
     </row>
@@ -5739,7 +5733,7 @@
         <v>197</v>
       </c>
       <c r="C9" s="152">
-        <f ca="1">AVERAGE(C5:C8)</f>
+        <f>AVERAGE(C5:C8)</f>
         <v>142.96844031651037</v>
       </c>
     </row>
@@ -12129,11 +12123,11 @@
         <v>75</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="182" t="s">
+      <c r="P4" s="193" t="s">
         <v>76</v>
       </c>
-      <c r="Q4" s="183"/>
-      <c r="R4" s="184"/>
+      <c r="Q4" s="194"/>
+      <c r="R4" s="195"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -21668,69 +21662,69 @@
       </c>
       <c r="C83" s="163"/>
       <c r="D83" s="159">
-        <f t="shared" ref="D83:L83" si="26">(D10-C10)/C10</f>
-        <v>0.10738891868476422</v>
+        <f>(D17-C17)/C17</f>
+        <v>-4.5090909090909091E-2</v>
       </c>
       <c r="E83" s="159">
-        <f t="shared" si="26"/>
-        <v>0.15270844199389016</v>
+        <f t="shared" ref="E83:L83" si="26">(E17-D17)/D17</f>
+        <v>-4.7981721249047982E-2</v>
       </c>
       <c r="F83" s="159">
         <f t="shared" si="26"/>
-        <v>0.11379722698038201</v>
+        <v>-7.0199999999999999E-2</v>
       </c>
       <c r="G83" s="159">
         <f t="shared" si="26"/>
-        <v>0.12204747257849226</v>
+        <v>-5.7431705743170573E-2</v>
       </c>
       <c r="H83" s="159">
         <f t="shared" si="26"/>
-        <v>0.13496948381090307</v>
+        <v>-3.7825193975353721E-2</v>
       </c>
       <c r="I83" s="159">
         <f t="shared" si="26"/>
-        <v>0.16993642764372138</v>
+        <v>-3.1959679810257928E-2</v>
       </c>
       <c r="J83" s="159">
         <f t="shared" si="26"/>
-        <v>6.8205278021228943E-2</v>
+        <v>-3.1422271223814774E-2</v>
       </c>
       <c r="K83" s="159">
         <f t="shared" si="26"/>
-        <v>4.7769249001768557E-2</v>
+        <v>-2.5611838360842343E-2</v>
       </c>
       <c r="L83" s="159">
         <f t="shared" si="26"/>
-        <v>8.1507647867471764E-2</v>
+        <v>-2.6155244029075805E-2</v>
       </c>
       <c r="N83" s="163"/>
       <c r="O83" s="159">
-        <f t="shared" ref="O83:U83" si="27">(O10-N10)/N10</f>
-        <v>-3.1313061025676709E-3</v>
+        <f>(O17-N17)/N17</f>
+        <v>-7.5654704170708053E-3</v>
       </c>
       <c r="P83" s="159">
-        <f t="shared" si="27"/>
-        <v>-2.6525198938992041E-3</v>
+        <f t="shared" ref="P83:U83" si="27">(P17-O17)/O17</f>
+        <v>-6.9064373208235601E-3</v>
       </c>
       <c r="Q83" s="159">
         <f t="shared" si="27"/>
-        <v>8.0837066069428892E-2</v>
+        <v>-5.9703450990683639E-3</v>
       </c>
       <c r="R83" s="159">
         <f t="shared" si="27"/>
-        <v>-1.0684452502752056E-2</v>
+        <v>-6.2702131872483663E-3</v>
       </c>
       <c r="S83" s="159">
         <f t="shared" si="27"/>
-        <v>1.5577955229742113E-2</v>
+        <v>-7.1732199787460146E-3</v>
       </c>
       <c r="T83" s="159">
         <f t="shared" si="27"/>
-        <v>2.5650940964166022E-2</v>
+        <v>-5.6194808670056197E-3</v>
       </c>
       <c r="U83" s="159">
         <f t="shared" si="27"/>
-        <v>0.15489506095262034</v>
+        <v>-3.6329386437029061E-3</v>
       </c>
       <c r="W83" s="163"/>
     </row>
@@ -22082,7 +22076,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="W17 C72:H72 W72 D83:H83 O83:U83 I72:L72 I83:L83" formula="1"/>
+    <ignoredError sqref="W17 C72:H72 W72 I72:L72 D83:L83 O83:U83" formula="1"/>
     <ignoredError sqref="N54:U54" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
@@ -22141,36 +22135,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="181" t="s">
+      <c r="C2" s="196" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="181"/>
-      <c r="E2" s="181"/>
-      <c r="F2" s="181"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="188" t="s">
+      <c r="D2" s="196"/>
+      <c r="E2" s="196"/>
+      <c r="F2" s="196"/>
+      <c r="G2" s="199"/>
+      <c r="H2" s="200" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="181"/>
-      <c r="J2" s="181"/>
-      <c r="K2" s="181"/>
-      <c r="L2" s="181"/>
+      <c r="I2" s="196"/>
+      <c r="J2" s="196"/>
+      <c r="K2" s="196"/>
+      <c r="L2" s="196"/>
       <c r="O2" s="90"/>
-      <c r="S2" s="181" t="s">
+      <c r="S2" s="196" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="181"/>
-      <c r="U2" s="181"/>
-      <c r="V2" s="181"/>
-      <c r="W2" s="181"/>
-      <c r="X2" s="181"/>
-      <c r="Y2" s="181"/>
-      <c r="Z2" s="181"/>
-      <c r="AA2" s="181" t="s">
+      <c r="T2" s="196"/>
+      <c r="U2" s="196"/>
+      <c r="V2" s="196"/>
+      <c r="W2" s="196"/>
+      <c r="X2" s="196"/>
+      <c r="Y2" s="196"/>
+      <c r="Z2" s="196"/>
+      <c r="AA2" s="196" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="181"/>
-      <c r="AC2" s="181"/>
+      <c r="AB2" s="196"/>
+      <c r="AC2" s="196"/>
       <c r="AE2" s="117" t="s">
         <v>75</v>
       </c>
@@ -22181,32 +22175,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="201" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="189"/>
-      <c r="K4" s="189"/>
-      <c r="L4" s="189"/>
+      <c r="D4" s="201"/>
+      <c r="E4" s="201"/>
+      <c r="F4" s="201"/>
+      <c r="G4" s="201"/>
+      <c r="H4" s="201"/>
+      <c r="I4" s="201"/>
+      <c r="J4" s="201"/>
+      <c r="K4" s="201"/>
+      <c r="L4" s="201"/>
       <c r="O4" s="90"/>
-      <c r="S4" s="185" t="s">
+      <c r="S4" s="197" t="s">
         <v>114</v>
       </c>
-      <c r="T4" s="186"/>
-      <c r="U4" s="186"/>
-      <c r="V4" s="186"/>
-      <c r="W4" s="186"/>
-      <c r="X4" s="186"/>
-      <c r="Y4" s="186"/>
-      <c r="Z4" s="186"/>
-      <c r="AA4" s="186"/>
-      <c r="AB4" s="186"/>
-      <c r="AC4" s="186"/>
+      <c r="T4" s="198"/>
+      <c r="U4" s="198"/>
+      <c r="V4" s="198"/>
+      <c r="W4" s="198"/>
+      <c r="X4" s="198"/>
+      <c r="Y4" s="198"/>
+      <c r="Z4" s="198"/>
+      <c r="AA4" s="198"/>
+      <c r="AB4" s="198"/>
+      <c r="AC4" s="198"/>
       <c r="AE4" s="119" t="s">
         <v>121</v>
       </c>
@@ -22882,33 +22876,33 @@
       <c r="Q12" s="91"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="189" t="s">
+      <c r="C13" s="201" t="s">
         <v>116</v>
       </c>
-      <c r="D13" s="189"/>
-      <c r="E13" s="189"/>
-      <c r="F13" s="189"/>
-      <c r="G13" s="189"/>
-      <c r="H13" s="189"/>
-      <c r="I13" s="189"/>
-      <c r="J13" s="189"/>
-      <c r="K13" s="189"/>
-      <c r="L13" s="189"/>
+      <c r="D13" s="201"/>
+      <c r="E13" s="201"/>
+      <c r="F13" s="201"/>
+      <c r="G13" s="201"/>
+      <c r="H13" s="201"/>
+      <c r="I13" s="201"/>
+      <c r="J13" s="201"/>
+      <c r="K13" s="201"/>
+      <c r="L13" s="201"/>
       <c r="O13" s="90"/>
       <c r="Q13" s="91"/>
-      <c r="S13" s="185" t="s">
+      <c r="S13" s="197" t="s">
         <v>116</v>
       </c>
-      <c r="T13" s="186"/>
-      <c r="U13" s="186"/>
-      <c r="V13" s="186"/>
-      <c r="W13" s="186"/>
-      <c r="X13" s="186"/>
-      <c r="Y13" s="186"/>
-      <c r="Z13" s="186"/>
-      <c r="AA13" s="186"/>
-      <c r="AB13" s="186"/>
-      <c r="AC13" s="186"/>
+      <c r="T13" s="198"/>
+      <c r="U13" s="198"/>
+      <c r="V13" s="198"/>
+      <c r="W13" s="198"/>
+      <c r="X13" s="198"/>
+      <c r="Y13" s="198"/>
+      <c r="Z13" s="198"/>
+      <c r="AA13" s="198"/>
+      <c r="AB13" s="198"/>
+      <c r="AC13" s="198"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
@@ -23490,35 +23484,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="181" t="s">
+      <c r="C2" s="196" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="181"/>
-      <c r="E2" s="181"/>
-      <c r="F2" s="181"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="188" t="s">
+      <c r="D2" s="196"/>
+      <c r="E2" s="196"/>
+      <c r="F2" s="196"/>
+      <c r="G2" s="199"/>
+      <c r="H2" s="200" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="181"/>
-      <c r="J2" s="181"/>
-      <c r="K2" s="181"/>
-      <c r="L2" s="181"/>
-      <c r="P2" s="181" t="s">
+      <c r="I2" s="196"/>
+      <c r="J2" s="196"/>
+      <c r="K2" s="196"/>
+      <c r="L2" s="196"/>
+      <c r="P2" s="196" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="181"/>
-      <c r="R2" s="181"/>
-      <c r="S2" s="181"/>
-      <c r="T2" s="181"/>
-      <c r="U2" s="181"/>
-      <c r="V2" s="181"/>
-      <c r="W2" s="181"/>
-      <c r="X2" s="181" t="s">
+      <c r="Q2" s="196"/>
+      <c r="R2" s="196"/>
+      <c r="S2" s="196"/>
+      <c r="T2" s="196"/>
+      <c r="U2" s="196"/>
+      <c r="V2" s="196"/>
+      <c r="W2" s="196"/>
+      <c r="X2" s="196" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="181"/>
-      <c r="Z2" s="181"/>
+      <c r="Y2" s="196"/>
+      <c r="Z2" s="196"/>
       <c r="AB2" s="117" t="s">
         <v>75</v>
       </c>
@@ -23527,31 +23521,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="201" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="189"/>
-      <c r="K4" s="189"/>
-      <c r="L4" s="189"/>
-      <c r="P4" s="186" t="s">
+      <c r="D4" s="201"/>
+      <c r="E4" s="201"/>
+      <c r="F4" s="201"/>
+      <c r="G4" s="201"/>
+      <c r="H4" s="201"/>
+      <c r="I4" s="201"/>
+      <c r="J4" s="201"/>
+      <c r="K4" s="201"/>
+      <c r="L4" s="201"/>
+      <c r="P4" s="198" t="s">
         <v>114</v>
       </c>
-      <c r="Q4" s="186"/>
-      <c r="R4" s="186"/>
-      <c r="S4" s="186"/>
-      <c r="T4" s="186"/>
-      <c r="U4" s="186"/>
-      <c r="V4" s="186"/>
-      <c r="W4" s="186"/>
-      <c r="X4" s="186"/>
-      <c r="Y4" s="186"/>
-      <c r="Z4" s="186"/>
+      <c r="Q4" s="198"/>
+      <c r="R4" s="198"/>
+      <c r="S4" s="198"/>
+      <c r="T4" s="198"/>
+      <c r="U4" s="198"/>
+      <c r="V4" s="198"/>
+      <c r="W4" s="198"/>
+      <c r="X4" s="198"/>
+      <c r="Y4" s="198"/>
+      <c r="Z4" s="198"/>
       <c r="AB4" s="119" t="s">
         <v>121</v>
       </c>
@@ -23752,32 +23746,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="189" t="s">
+      <c r="C9" s="201" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="189"/>
-      <c r="E9" s="189"/>
-      <c r="F9" s="189"/>
-      <c r="G9" s="189"/>
-      <c r="H9" s="189"/>
-      <c r="I9" s="189"/>
-      <c r="J9" s="189"/>
-      <c r="K9" s="189"/>
-      <c r="L9" s="189"/>
+      <c r="D9" s="201"/>
+      <c r="E9" s="201"/>
+      <c r="F9" s="201"/>
+      <c r="G9" s="201"/>
+      <c r="H9" s="201"/>
+      <c r="I9" s="201"/>
+      <c r="J9" s="201"/>
+      <c r="K9" s="201"/>
+      <c r="L9" s="201"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="186" t="s">
+      <c r="P9" s="198" t="s">
         <v>128</v>
       </c>
-      <c r="Q9" s="186"/>
-      <c r="R9" s="186"/>
-      <c r="S9" s="186"/>
-      <c r="T9" s="186"/>
-      <c r="U9" s="186"/>
-      <c r="V9" s="186"/>
-      <c r="W9" s="186"/>
-      <c r="X9" s="186"/>
-      <c r="Y9" s="186"/>
-      <c r="Z9" s="186"/>
+      <c r="Q9" s="198"/>
+      <c r="R9" s="198"/>
+      <c r="S9" s="198"/>
+      <c r="T9" s="198"/>
+      <c r="U9" s="198"/>
+      <c r="V9" s="198"/>
+      <c r="W9" s="198"/>
+      <c r="X9" s="198"/>
+      <c r="Y9" s="198"/>
+      <c r="Z9" s="198"/>
       <c r="AB9" s="119" t="str">
         <f>AB4</f>
         <v>Q1-Q2-Q3</v>
@@ -24247,31 +24241,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="189" t="s">
+      <c r="C17" s="201" t="s">
         <v>126</v>
       </c>
-      <c r="D17" s="189"/>
-      <c r="E17" s="189"/>
-      <c r="F17" s="189"/>
-      <c r="G17" s="189"/>
-      <c r="H17" s="189"/>
-      <c r="I17" s="189"/>
-      <c r="J17" s="189"/>
-      <c r="K17" s="189"/>
-      <c r="L17" s="189"/>
-      <c r="P17" s="186" t="s">
+      <c r="D17" s="201"/>
+      <c r="E17" s="201"/>
+      <c r="F17" s="201"/>
+      <c r="G17" s="201"/>
+      <c r="H17" s="201"/>
+      <c r="I17" s="201"/>
+      <c r="J17" s="201"/>
+      <c r="K17" s="201"/>
+      <c r="L17" s="201"/>
+      <c r="P17" s="198" t="s">
         <v>126</v>
       </c>
-      <c r="Q17" s="186"/>
-      <c r="R17" s="186"/>
-      <c r="S17" s="186"/>
-      <c r="T17" s="186"/>
-      <c r="U17" s="186"/>
-      <c r="V17" s="186"/>
-      <c r="W17" s="186"/>
-      <c r="X17" s="186"/>
-      <c r="Y17" s="186"/>
-      <c r="Z17" s="186"/>
+      <c r="Q17" s="198"/>
+      <c r="R17" s="198"/>
+      <c r="S17" s="198"/>
+      <c r="T17" s="198"/>
+      <c r="U17" s="198"/>
+      <c r="V17" s="198"/>
+      <c r="W17" s="198"/>
+      <c r="X17" s="198"/>
+      <c r="Y17" s="198"/>
+      <c r="Z17" s="198"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="7" t="s">
@@ -24661,60 +24655,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="181" t="s">
+      <c r="C3" s="196" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="181"/>
-      <c r="E3" s="181"/>
-      <c r="F3" s="181"/>
-      <c r="G3" s="187"/>
-      <c r="H3" s="188" t="s">
+      <c r="D3" s="196"/>
+      <c r="E3" s="196"/>
+      <c r="F3" s="196"/>
+      <c r="G3" s="199"/>
+      <c r="H3" s="200" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="181"/>
-      <c r="J3" s="181"/>
-      <c r="K3" s="181"/>
-      <c r="L3" s="181"/>
-      <c r="P3" s="190"/>
-      <c r="Q3" s="190"/>
-      <c r="R3" s="190"/>
-      <c r="S3" s="190"/>
-      <c r="T3" s="190"/>
-      <c r="U3" s="190"/>
-      <c r="V3" s="190"/>
-      <c r="W3" s="190"/>
-      <c r="X3" s="190"/>
-      <c r="Y3" s="190"/>
-      <c r="Z3" s="190"/>
+      <c r="I3" s="196"/>
+      <c r="J3" s="196"/>
+      <c r="K3" s="196"/>
+      <c r="L3" s="196"/>
+      <c r="P3" s="202"/>
+      <c r="Q3" s="202"/>
+      <c r="R3" s="202"/>
+      <c r="S3" s="202"/>
+      <c r="T3" s="202"/>
+      <c r="U3" s="202"/>
+      <c r="V3" s="202"/>
+      <c r="W3" s="202"/>
+      <c r="X3" s="202"/>
+      <c r="Y3" s="202"/>
+      <c r="Z3" s="202"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="189" t="s">
+      <c r="C5" s="201" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="189"/>
-      <c r="E5" s="189"/>
-      <c r="F5" s="189"/>
-      <c r="G5" s="189"/>
-      <c r="H5" s="189"/>
-      <c r="I5" s="189"/>
-      <c r="J5" s="189"/>
-      <c r="K5" s="189"/>
-      <c r="L5" s="189"/>
-      <c r="P5" s="190"/>
-      <c r="Q5" s="190"/>
-      <c r="R5" s="190"/>
-      <c r="S5" s="190"/>
-      <c r="T5" s="190"/>
-      <c r="U5" s="190"/>
-      <c r="V5" s="190"/>
-      <c r="W5" s="190"/>
-      <c r="X5" s="190"/>
-      <c r="Y5" s="190"/>
-      <c r="Z5" s="190"/>
+      <c r="D5" s="201"/>
+      <c r="E5" s="201"/>
+      <c r="F5" s="201"/>
+      <c r="G5" s="201"/>
+      <c r="H5" s="201"/>
+      <c r="I5" s="201"/>
+      <c r="J5" s="201"/>
+      <c r="K5" s="201"/>
+      <c r="L5" s="201"/>
+      <c r="P5" s="202"/>
+      <c r="Q5" s="202"/>
+      <c r="R5" s="202"/>
+      <c r="S5" s="202"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="202"/>
+      <c r="V5" s="202"/>
+      <c r="W5" s="202"/>
+      <c r="X5" s="202"/>
+      <c r="Y5" s="202"/>
+      <c r="Z5" s="202"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -24900,30 +24894,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="189" t="s">
+      <c r="C11" s="201" t="s">
         <v>134</v>
       </c>
-      <c r="D11" s="189"/>
-      <c r="E11" s="189"/>
-      <c r="F11" s="189"/>
-      <c r="G11" s="189"/>
-      <c r="H11" s="189"/>
-      <c r="I11" s="189"/>
-      <c r="J11" s="189"/>
-      <c r="K11" s="189"/>
-      <c r="L11" s="189"/>
+      <c r="D11" s="201"/>
+      <c r="E11" s="201"/>
+      <c r="F11" s="201"/>
+      <c r="G11" s="201"/>
+      <c r="H11" s="201"/>
+      <c r="I11" s="201"/>
+      <c r="J11" s="201"/>
+      <c r="K11" s="201"/>
+      <c r="L11" s="201"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="190"/>
-      <c r="Q11" s="190"/>
-      <c r="R11" s="190"/>
-      <c r="S11" s="190"/>
-      <c r="T11" s="190"/>
-      <c r="U11" s="190"/>
-      <c r="V11" s="190"/>
-      <c r="W11" s="190"/>
-      <c r="X11" s="190"/>
-      <c r="Y11" s="190"/>
-      <c r="Z11" s="190"/>
+      <c r="P11" s="202"/>
+      <c r="Q11" s="202"/>
+      <c r="R11" s="202"/>
+      <c r="S11" s="202"/>
+      <c r="T11" s="202"/>
+      <c r="U11" s="202"/>
+      <c r="V11" s="202"/>
+      <c r="W11" s="202"/>
+      <c r="X11" s="202"/>
+      <c r="Y11" s="202"/>
+      <c r="Z11" s="202"/>
       <c r="AB11" s="123"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -24931,43 +24925,43 @@
         <v>133</v>
       </c>
       <c r="C12" s="62">
-        <f>C6</f>
+        <f t="shared" ref="C12:L12" si="0">C6</f>
         <v>2021</v>
       </c>
       <c r="D12" s="62">
-        <f>D6</f>
+        <f t="shared" si="0"/>
         <v>2022</v>
       </c>
       <c r="E12" s="62">
-        <f>E6</f>
+        <f t="shared" si="0"/>
         <v>2023</v>
       </c>
       <c r="F12" s="62">
-        <f>F6</f>
+        <f t="shared" si="0"/>
         <v>2024</v>
       </c>
       <c r="G12" s="62">
-        <f>G6</f>
+        <f t="shared" si="0"/>
         <v>2025</v>
       </c>
       <c r="H12" s="62">
-        <f>H6</f>
+        <f t="shared" si="0"/>
         <v>2026</v>
       </c>
       <c r="I12" s="62">
-        <f>I6</f>
+        <f t="shared" si="0"/>
         <v>2027</v>
       </c>
       <c r="J12" s="62">
-        <f>J6</f>
+        <f t="shared" si="0"/>
         <v>2028</v>
       </c>
       <c r="K12" s="62">
-        <f>K6</f>
+        <f t="shared" si="0"/>
         <v>2029</v>
       </c>
       <c r="L12" s="62">
-        <f>L6</f>
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="N12" s="91"/>
@@ -25073,19 +25067,19 @@
         <v>6283.3024898630147</v>
       </c>
       <c r="I14" s="34">
-        <f t="shared" ref="I14:L14" si="0">I21*I8/365</f>
+        <f t="shared" ref="I14:L14" si="1">I21*I8/365</f>
         <v>7180.7529258955483</v>
       </c>
       <c r="J14" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7454.2284737055506</v>
       </c>
       <c r="K14" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8499.8802591141139</v>
       </c>
       <c r="L14" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8826.4242271483818</v>
       </c>
       <c r="N14" s="91"/>
@@ -25165,61 +25159,61 @@
       <c r="D16" s="20"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="189" t="s">
+      <c r="C18" s="201" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="189"/>
-      <c r="E18" s="189"/>
-      <c r="F18" s="189"/>
-      <c r="G18" s="189"/>
-      <c r="H18" s="189"/>
-      <c r="I18" s="189"/>
-      <c r="J18" s="189"/>
-      <c r="K18" s="189"/>
-      <c r="L18" s="189"/>
+      <c r="D18" s="201"/>
+      <c r="E18" s="201"/>
+      <c r="F18" s="201"/>
+      <c r="G18" s="201"/>
+      <c r="H18" s="201"/>
+      <c r="I18" s="201"/>
+      <c r="J18" s="201"/>
+      <c r="K18" s="201"/>
+      <c r="L18" s="201"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
         <v>138</v>
       </c>
       <c r="C19" s="62">
-        <f>C6</f>
+        <f t="shared" ref="C19:L19" si="2">C6</f>
         <v>2021</v>
       </c>
       <c r="D19" s="62">
-        <f>D6</f>
+        <f t="shared" si="2"/>
         <v>2022</v>
       </c>
       <c r="E19" s="62">
-        <f>E6</f>
+        <f t="shared" si="2"/>
         <v>2023</v>
       </c>
       <c r="F19" s="62">
-        <f>F6</f>
+        <f t="shared" si="2"/>
         <v>2024</v>
       </c>
       <c r="G19" s="62">
-        <f>G6</f>
+        <f t="shared" si="2"/>
         <v>2025</v>
       </c>
       <c r="H19" s="62">
-        <f>H6</f>
+        <f t="shared" si="2"/>
         <v>2026</v>
       </c>
       <c r="I19" s="62">
-        <f>I6</f>
+        <f t="shared" si="2"/>
         <v>2027</v>
       </c>
       <c r="J19" s="62">
-        <f>J6</f>
+        <f t="shared" si="2"/>
         <v>2028</v>
       </c>
       <c r="K19" s="62">
-        <f>K6</f>
+        <f t="shared" si="2"/>
         <v>2029</v>
       </c>
       <c r="L19" s="62">
-        <f>L6</f>
+        <f t="shared" si="2"/>
         <v>2030</v>
       </c>
     </row>
@@ -25272,19 +25266,19 @@
         <v>11.27659274770989</v>
       </c>
       <c r="D21" s="129">
-        <f t="shared" ref="D21:G21" si="1">D14/D8*365</f>
+        <f t="shared" ref="D21:G21" si="3">D14/D8*365</f>
         <v>8.0756980666171607</v>
       </c>
       <c r="E21" s="129">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10.791292490321617</v>
       </c>
       <c r="F21" s="129">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12.642570548414087</v>
       </c>
       <c r="G21" s="135">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9.4454652425778427</v>
       </c>
       <c r="H21" s="97">
@@ -25352,103 +25346,103 @@
         <v>-56.355166632892498</v>
       </c>
       <c r="D23" s="129">
-        <f t="shared" ref="D23:L23" si="2">D20+D21-D22</f>
+        <f t="shared" ref="D23:L23" si="4">D20+D21-D22</f>
         <v>-70.521753872831582</v>
       </c>
       <c r="E23" s="129">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-67.829884635581323</v>
       </c>
       <c r="F23" s="129">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-75.830335046699929</v>
       </c>
       <c r="G23" s="135">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-71.06806888722123</v>
       </c>
       <c r="H23" s="129">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-72</v>
       </c>
       <c r="I23" s="129">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-74</v>
       </c>
       <c r="J23" s="129">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-76</v>
       </c>
       <c r="K23" s="129">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-77</v>
       </c>
       <c r="L23" s="129">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-77</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="190"/>
-      <c r="C25" s="190"/>
+      <c r="B25" s="202"/>
+      <c r="C25" s="202"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="122"/>
-      <c r="C26" s="189" t="s">
+      <c r="C26" s="201" t="s">
         <v>302</v>
       </c>
-      <c r="D26" s="189"/>
-      <c r="E26" s="189"/>
-      <c r="F26" s="189"/>
-      <c r="G26" s="189"/>
-      <c r="H26" s="189"/>
-      <c r="I26" s="189"/>
-      <c r="J26" s="189"/>
-      <c r="K26" s="189"/>
-      <c r="L26" s="189"/>
+      <c r="D26" s="201"/>
+      <c r="E26" s="201"/>
+      <c r="F26" s="201"/>
+      <c r="G26" s="201"/>
+      <c r="H26" s="201"/>
+      <c r="I26" s="201"/>
+      <c r="J26" s="201"/>
+      <c r="K26" s="201"/>
+      <c r="L26" s="201"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
         <v>133</v>
       </c>
       <c r="C27" s="62">
-        <f>C6</f>
+        <f t="shared" ref="C27:L27" si="5">C6</f>
         <v>2021</v>
       </c>
       <c r="D27" s="62">
-        <f>D6</f>
+        <f t="shared" si="5"/>
         <v>2022</v>
       </c>
       <c r="E27" s="62">
-        <f>E6</f>
+        <f t="shared" si="5"/>
         <v>2023</v>
       </c>
       <c r="F27" s="62">
-        <f>F6</f>
+        <f t="shared" si="5"/>
         <v>2024</v>
       </c>
       <c r="G27" s="62">
-        <f>G6</f>
+        <f t="shared" si="5"/>
         <v>2025</v>
       </c>
       <c r="H27" s="62">
-        <f>H6</f>
+        <f t="shared" si="5"/>
         <v>2026</v>
       </c>
       <c r="I27" s="62">
-        <f>I6</f>
+        <f t="shared" si="5"/>
         <v>2027</v>
       </c>
       <c r="J27" s="62">
-        <f>J6</f>
+        <f t="shared" si="5"/>
         <v>2028</v>
       </c>
       <c r="K27" s="62">
-        <f>K6</f>
+        <f t="shared" si="5"/>
         <v>2029</v>
       </c>
       <c r="L27" s="62">
-        <f>L6</f>
+        <f t="shared" si="5"/>
         <v>2030</v>
       </c>
     </row>
@@ -25481,19 +25475,19 @@
         <v>-4253.7182054794539</v>
       </c>
       <c r="I28" s="34">
-        <f t="shared" ref="I28:L28" si="3">-(I13-H13)</f>
+        <f t="shared" ref="I28:L28" si="6">-(I13-H13)</f>
         <v>-5706.0985972602793</v>
       </c>
       <c r="J28" s="34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-6192.6587459147268</v>
       </c>
       <c r="K28" s="34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-5367.7378584184626</v>
       </c>
       <c r="L28" s="34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-2972.8659168230661</v>
       </c>
     </row>
@@ -25526,19 +25520,19 @@
         <v>-565.30248986301467</v>
       </c>
       <c r="I29" s="34">
-        <f t="shared" ref="I29:L29" si="4">-(I14-H14)</f>
+        <f t="shared" ref="I29:L29" si="7">-(I14-H14)</f>
         <v>-897.45043603253362</v>
       </c>
       <c r="J29" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-273.47554781000235</v>
       </c>
       <c r="K29" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-1045.6517854085632</v>
       </c>
       <c r="L29" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-326.54396803426789</v>
       </c>
     </row>
@@ -25571,19 +25565,19 @@
         <v>4911.299629369867</v>
       </c>
       <c r="I30" s="20">
-        <f t="shared" ref="I30:L30" si="5">I15-H15</f>
+        <f t="shared" ref="I30:L30" si="8">I15-H15</f>
         <v>6828.1654376250081</v>
       </c>
       <c r="J30" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>6495.9623495252745</v>
       </c>
       <c r="K30" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>6819.9021435874311</v>
       </c>
       <c r="L30" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3646.4076430493442</v>
       </c>
     </row>
@@ -25597,61 +25591,61 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="122"/>
-      <c r="C33" s="189" t="s">
+      <c r="C33" s="201" t="s">
         <v>305</v>
       </c>
-      <c r="D33" s="189"/>
-      <c r="E33" s="189"/>
-      <c r="F33" s="189"/>
-      <c r="G33" s="189"/>
-      <c r="H33" s="189"/>
-      <c r="I33" s="189"/>
-      <c r="J33" s="189"/>
-      <c r="K33" s="189"/>
-      <c r="L33" s="189"/>
+      <c r="D33" s="201"/>
+      <c r="E33" s="201"/>
+      <c r="F33" s="201"/>
+      <c r="G33" s="201"/>
+      <c r="H33" s="201"/>
+      <c r="I33" s="201"/>
+      <c r="J33" s="201"/>
+      <c r="K33" s="201"/>
+      <c r="L33" s="201"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
         <v>133</v>
       </c>
       <c r="C34" s="62">
-        <f>C6</f>
+        <f t="shared" ref="C34:L34" si="9">C6</f>
         <v>2021</v>
       </c>
       <c r="D34" s="62">
-        <f>D6</f>
+        <f t="shared" si="9"/>
         <v>2022</v>
       </c>
       <c r="E34" s="62">
-        <f>E6</f>
+        <f t="shared" si="9"/>
         <v>2023</v>
       </c>
       <c r="F34" s="62">
-        <f>F6</f>
+        <f t="shared" si="9"/>
         <v>2024</v>
       </c>
       <c r="G34" s="62">
-        <f>G6</f>
+        <f t="shared" si="9"/>
         <v>2025</v>
       </c>
       <c r="H34" s="62">
-        <f>H6</f>
+        <f t="shared" si="9"/>
         <v>2026</v>
       </c>
       <c r="I34" s="62">
-        <f>I6</f>
+        <f t="shared" si="9"/>
         <v>2027</v>
       </c>
       <c r="J34" s="62">
-        <f>J6</f>
+        <f t="shared" si="9"/>
         <v>2028</v>
       </c>
       <c r="K34" s="62">
-        <f>K6</f>
+        <f t="shared" si="9"/>
         <v>2029</v>
       </c>
       <c r="L34" s="62">
-        <f>L6</f>
+        <f t="shared" si="9"/>
         <v>2030</v>
       </c>
     </row>
@@ -25684,19 +25678,19 @@
         <v>-8594.8627659726008</v>
       </c>
       <c r="I35" s="34">
-        <f t="shared" ref="I35:L35" si="6">I36+I28+I29+I30</f>
+        <f t="shared" ref="I35:L35" si="10">I36+I28+I29+I30</f>
         <v>-8852.3526621678047</v>
       </c>
       <c r="J35" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-9465.1759326919564</v>
       </c>
       <c r="K35" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-9537.2576751647575</v>
       </c>
       <c r="L35" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-10079.037332128893</v>
       </c>
     </row>
@@ -25709,19 +25703,19 @@
         <v>-4470</v>
       </c>
       <c r="D36" s="141">
-        <f t="shared" ref="D36:G36" si="7">D35-D28-D29-D30</f>
+        <f t="shared" ref="D36:G36" si="11">D35-D28-D29-D30</f>
         <v>-7909</v>
       </c>
       <c r="E36" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>-1382</v>
       </c>
       <c r="F36" s="141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2465</v>
       </c>
       <c r="G36" s="142">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>-20620</v>
       </c>
       <c r="H36" s="20">
@@ -25746,26 +25740,26 @@
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B37" s="191" t="s">
+      <c r="B37" s="181" t="s">
         <v>107</v>
       </c>
-      <c r="C37" s="192">
+      <c r="C37" s="182">
         <f>C36/C7</f>
         <v>-1.2219224366281501E-2</v>
       </c>
-      <c r="D37" s="192">
+      <c r="D37" s="182">
         <f>D36/D7</f>
         <v>-2.0056906940415085E-2</v>
       </c>
-      <c r="E37" s="192">
+      <c r="E37" s="182">
         <f>E36/E7</f>
         <v>-3.6056720195155041E-3</v>
       </c>
-      <c r="F37" s="192">
+      <c r="F37" s="182">
         <f>F36/F7</f>
         <v>6.3037835487871931E-3</v>
       </c>
-      <c r="G37" s="193">
+      <c r="G37" s="183">
         <f>G36/G7</f>
         <v>-4.9548131612524964E-2</v>
       </c>
@@ -25792,61 +25786,61 @@
       <c r="C39" s="131"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="189" t="s">
+      <c r="C40" s="201" t="s">
         <v>308</v>
       </c>
-      <c r="D40" s="189"/>
-      <c r="E40" s="189"/>
-      <c r="F40" s="189"/>
-      <c r="G40" s="189"/>
-      <c r="H40" s="189"/>
-      <c r="I40" s="189"/>
-      <c r="J40" s="189"/>
-      <c r="K40" s="189"/>
-      <c r="L40" s="189"/>
+      <c r="D40" s="201"/>
+      <c r="E40" s="201"/>
+      <c r="F40" s="201"/>
+      <c r="G40" s="201"/>
+      <c r="H40" s="201"/>
+      <c r="I40" s="201"/>
+      <c r="J40" s="201"/>
+      <c r="K40" s="201"/>
+      <c r="L40" s="201"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
         <v>133</v>
       </c>
       <c r="C41" s="62">
-        <f>C6</f>
+        <f t="shared" ref="C41:L41" si="12">C6</f>
         <v>2021</v>
       </c>
       <c r="D41" s="62">
-        <f>D6</f>
+        <f t="shared" si="12"/>
         <v>2022</v>
       </c>
       <c r="E41" s="62">
-        <f>E6</f>
+        <f t="shared" si="12"/>
         <v>2023</v>
       </c>
       <c r="F41" s="62">
-        <f>F6</f>
+        <f t="shared" si="12"/>
         <v>2024</v>
       </c>
       <c r="G41" s="62">
-        <f>G6</f>
+        <f t="shared" si="12"/>
         <v>2025</v>
       </c>
       <c r="H41" s="62">
-        <f>H6</f>
+        <f t="shared" si="12"/>
         <v>2026</v>
       </c>
       <c r="I41" s="62">
-        <f>I6</f>
+        <f t="shared" si="12"/>
         <v>2027</v>
       </c>
       <c r="J41" s="62">
-        <f>J6</f>
+        <f t="shared" si="12"/>
         <v>2028</v>
       </c>
       <c r="K41" s="62">
-        <f>K6</f>
+        <f t="shared" si="12"/>
         <v>2029</v>
       </c>
       <c r="L41" s="62">
-        <f>L6</f>
+        <f t="shared" si="12"/>
         <v>2030</v>
       </c>
     </row>
@@ -25896,26 +25890,26 @@
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B43" s="191" t="s">
+      <c r="B43" s="181" t="s">
         <v>309</v>
       </c>
-      <c r="C43" s="192">
+      <c r="C43" s="182">
         <f>C42/C7</f>
         <v>3.084602410494865E-2</v>
       </c>
-      <c r="D43" s="192">
+      <c r="D43" s="182">
         <f>D42/D7</f>
         <v>2.8159298857803657E-2</v>
       </c>
-      <c r="E43" s="192">
+      <c r="E43" s="182">
         <f>E42/E7</f>
         <v>3.0053354553400212E-2</v>
       </c>
-      <c r="F43" s="192">
+      <c r="F43" s="182">
         <f>F42/F7</f>
         <v>2.9268479803598143E-2</v>
       </c>
-      <c r="G43" s="193">
+      <c r="G43" s="183">
         <f>G42/G7</f>
         <v>2.8109313462818475E-2</v>
       </c>
@@ -25936,47 +25930,47 @@
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B44" s="191" t="s">
+      <c r="B44" s="181" t="s">
         <v>310</v>
       </c>
-      <c r="C44" s="192">
+      <c r="C44" s="182">
         <f>C42/C45</f>
         <v>1.0179521876409563</v>
       </c>
-      <c r="D44" s="192">
-        <f t="shared" ref="D44:L44" si="8">D42/D45</f>
+      <c r="D44" s="182">
+        <f t="shared" ref="D44:L44" si="13">D42/D45</f>
         <v>1.0369816959282778</v>
       </c>
-      <c r="E44" s="192">
-        <f t="shared" si="8"/>
+      <c r="E44" s="182">
+        <f t="shared" si="13"/>
         <v>1.0510995528789122</v>
       </c>
-      <c r="F44" s="192">
-        <f t="shared" si="8"/>
+      <c r="F44" s="182">
+        <f t="shared" si="13"/>
         <v>1.2114957129247381</v>
       </c>
-      <c r="G44" s="193">
-        <f t="shared" si="8"/>
+      <c r="G44" s="183">
+        <f t="shared" si="13"/>
         <v>0.92001572945340149</v>
       </c>
-      <c r="H44" s="192">
-        <f t="shared" si="8"/>
+      <c r="H44" s="182">
+        <f t="shared" si="13"/>
         <v>0.96666666666666667</v>
       </c>
-      <c r="I44" s="192">
-        <f t="shared" si="8"/>
+      <c r="I44" s="182">
+        <f t="shared" si="13"/>
         <v>0.96666666666666667</v>
       </c>
-      <c r="J44" s="192">
-        <f t="shared" si="8"/>
+      <c r="J44" s="182">
+        <f t="shared" si="13"/>
         <v>0.96666666666666679</v>
       </c>
-      <c r="K44" s="192">
-        <f t="shared" si="8"/>
+      <c r="K44" s="182">
+        <f t="shared" si="13"/>
         <v>0.96666666666666679</v>
       </c>
-      <c r="L44" s="192">
-        <f t="shared" si="8"/>
+      <c r="L44" s="182">
+        <f t="shared" si="13"/>
         <v>0.96666666666666679</v>
       </c>
     </row>
@@ -26026,26 +26020,26 @@
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B46" s="191" t="s">
+      <c r="B46" s="181" t="s">
         <v>309</v>
       </c>
-      <c r="C46" s="192">
+      <c r="C46" s="182">
         <f>C45/C7</f>
         <v>3.0302036264033657E-2</v>
       </c>
-      <c r="D46" s="192">
+      <c r="D46" s="182">
         <f>D45/D7</f>
         <v>2.7155058732831552E-2</v>
       </c>
-      <c r="E46" s="192">
+      <c r="E46" s="182">
         <f>E45/E7</f>
         <v>2.859230076835775E-2</v>
       </c>
-      <c r="F46" s="192">
+      <c r="F46" s="182">
         <f>F45/F7</f>
         <v>2.415896275269477E-2</v>
       </c>
-      <c r="G46" s="193">
+      <c r="G46" s="183">
         <f>G45/G7</f>
         <v>3.0553079216937677E-2</v>
       </c>

--- a/AAPL.xlsx
+++ b/AAPL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2B82F2-0826-D343-9076-E9AEA96BA099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12E9FBC-E5AA-CA44-8942-81CF0F55297D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="4" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="15" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -28,9 +28,9 @@
     <sheet name="DCF" sheetId="22" r:id="rId13"/>
     <sheet name="Multiples" sheetId="28" r:id="rId14"/>
     <sheet name="AVG target price" sheetId="29" r:id="rId15"/>
+    <sheet name="Reverse DCF" sheetId="30" r:id="rId16"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId16"/>
     <externalReference r:id="rId17"/>
   </externalReferences>
   <calcPr calcId="191029" iterate="1"/>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="349">
   <si>
     <t>Date</t>
   </si>
@@ -1179,6 +1179,54 @@
   </si>
   <si>
     <t>EV/UFCF price</t>
+  </si>
+  <si>
+    <t>Reverse DCF</t>
+  </si>
+  <si>
+    <t>Growth adjustment</t>
+  </si>
+  <si>
+    <t>Current Price</t>
+  </si>
+  <si>
+    <t>Calculated Price</t>
+  </si>
+  <si>
+    <t>UFCF Growth</t>
+  </si>
+  <si>
+    <t>Modify until Calculated Price is very close to Current Price</t>
+  </si>
+  <si>
+    <t>Enterprise Value</t>
+  </si>
+  <si>
+    <t>Compare Metrics and growth rates</t>
+  </si>
+  <si>
+    <t>UFCF to EBIT margin</t>
+  </si>
+  <si>
+    <t>UFCF to Revenue margin</t>
+  </si>
+  <si>
+    <t>UFCF growth</t>
+  </si>
+  <si>
+    <t>EBIT growth</t>
+  </si>
+  <si>
+    <t>Revenue growth</t>
+  </si>
+  <si>
+    <t>Current price</t>
+  </si>
+  <si>
+    <t>Upside/Downside</t>
+  </si>
+  <si>
+    <t>EBIT margin</t>
   </si>
 </sst>
 </file>
@@ -1473,7 +1521,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1715,12 +1763,100 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="203">
+  <cellXfs count="221">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1962,6 +2098,45 @@
     <xf numFmtId="3" fontId="0" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="11" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="8" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="8" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="3" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="0" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="2" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="1" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="38" fontId="0" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1971,25 +2146,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2015,6 +2175,71 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>128348</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>20266</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>716064</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>216170</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Right Arrow 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2678D1F3-B427-B85A-A2D1-38A53E324AEA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="3749199" y="6295957"/>
+          <a:ext cx="587716" cy="195904"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -2023,73 +2248,30 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
+      <sheetName val="1. List_AutomaticData"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="4">
+          <cell r="C4">
+            <v>106.24</v>
+          </cell>
+        </row>
         <row r="10">
           <cell r="C10">
-            <v>43.1</v>
+            <v>43.36</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>271.06</v>
+            <v>270.70999999999998</v>
           </cell>
           <cell r="F17">
-            <v>1.0716000000000001</v>
+            <v>1.06</v>
           </cell>
         </row>
       </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Overview"/>
-      <sheetName val="Financials -&gt;"/>
-      <sheetName val="Statement Y"/>
-      <sheetName val="Statement Q"/>
-      <sheetName val="Statements"/>
-      <sheetName val="Forecast -&gt;"/>
-      <sheetName val="Revenue"/>
-      <sheetName val="COGS &amp; OpEx"/>
-      <sheetName val="WC &amp; Investments"/>
-      <sheetName val="FCF &amp; Other"/>
-      <sheetName val="Valuation -&gt;"/>
-      <sheetName val="WACC"/>
-      <sheetName val="DCF"/>
-      <sheetName val="Multiples"/>
-      <sheetName val="AVG target price"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11">
-        <row r="20">
-          <cell r="C20">
-            <v>8.92125E-2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2539,7 +2721,7 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$17</f>
-        <v>271.06</v>
+        <v>270.70999999999998</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2565,7 +2747,7 @@
       </c>
       <c r="C11" s="93">
         <f>$C$3/'Statement Q'!$N$19</f>
-        <v>34.336752252137515</v>
+        <v>34.292415709349022</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2574,7 +2756,7 @@
       </c>
       <c r="C12" s="93">
         <f>$C$3/Statements!W18</f>
-        <v>34.336752252137515</v>
+        <v>34.292415709349022</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2583,7 +2765,7 @@
       </c>
       <c r="C13" s="98">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$17)</f>
-        <v>9.2835671472876413</v>
+        <v>9.2715799544094928</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -2592,7 +2774,7 @@
       </c>
       <c r="C15" s="20">
         <f>C3*'Statement Q'!N100</f>
-        <v>3979431.86</v>
+        <v>3974293.51</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -2600,8 +2782,8 @@
         <v>150</v>
       </c>
       <c r="C16" s="20">
-        <f>Statements!W21</f>
-        <v>66907</v>
+        <f>Statements!W21+Statements!W27</f>
+        <v>144795</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -2619,7 +2801,7 @@
       </c>
       <c r="C18" s="20">
         <f>C15+C17-C16</f>
-        <v>4003033.86</v>
+        <v>3920007.51</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -2628,7 +2810,7 @@
       </c>
       <c r="C19" s="93">
         <f>C16/'Statement Q'!J100</f>
-        <v>4.5573870989714598</v>
+        <v>9.8627477692255301</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -2784,8 +2966,8 @@
         <v>150</v>
       </c>
       <c r="C47" s="20">
-        <f>Statements!W21</f>
-        <v>66907</v>
+        <f>Statements!W21+Statements!W27</f>
+        <v>144795</v>
       </c>
       <c r="D47" s="20"/>
     </row>
@@ -2795,7 +2977,7 @@
       </c>
       <c r="C48" s="159">
         <f>C44/(C45+C46-C47)</f>
-        <v>1.0649149286638468</v>
+        <v>3.5113546987136846</v>
       </c>
       <c r="D48" s="159"/>
     </row>
@@ -2839,60 +3021,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="196" t="s">
+      <c r="C2" s="208" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="196"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="199"/>
-      <c r="H2" s="200" t="s">
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="209"/>
+      <c r="H2" s="210" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="196"/>
-      <c r="J2" s="196"/>
-      <c r="K2" s="196"/>
-      <c r="L2" s="196"/>
-      <c r="S2" s="202"/>
-      <c r="T2" s="202"/>
-      <c r="U2" s="202"/>
-      <c r="V2" s="202"/>
-      <c r="W2" s="202"/>
-      <c r="X2" s="202"/>
-      <c r="Y2" s="202"/>
-      <c r="Z2" s="202"/>
-      <c r="AA2" s="202"/>
-      <c r="AB2" s="202"/>
-      <c r="AC2" s="202"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
+      <c r="S2" s="211"/>
+      <c r="T2" s="211"/>
+      <c r="U2" s="211"/>
+      <c r="V2" s="211"/>
+      <c r="W2" s="211"/>
+      <c r="X2" s="211"/>
+      <c r="Y2" s="211"/>
+      <c r="Z2" s="211"/>
+      <c r="AA2" s="211"/>
+      <c r="AB2" s="211"/>
+      <c r="AC2" s="211"/>
       <c r="AE2" s="122"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="201" t="s">
+      <c r="C4" s="212" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="201"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="201"/>
-      <c r="G4" s="201"/>
-      <c r="H4" s="201"/>
-      <c r="I4" s="201"/>
-      <c r="J4" s="201"/>
-      <c r="K4" s="201"/>
-      <c r="L4" s="201"/>
-      <c r="S4" s="202"/>
-      <c r="T4" s="202"/>
-      <c r="U4" s="202"/>
-      <c r="V4" s="202"/>
-      <c r="W4" s="202"/>
-      <c r="X4" s="202"/>
-      <c r="Y4" s="202"/>
-      <c r="Z4" s="202"/>
-      <c r="AA4" s="202"/>
-      <c r="AB4" s="202"/>
-      <c r="AC4" s="202"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="212"/>
+      <c r="H4" s="212"/>
+      <c r="I4" s="212"/>
+      <c r="J4" s="212"/>
+      <c r="K4" s="212"/>
+      <c r="L4" s="212"/>
+      <c r="S4" s="211"/>
+      <c r="T4" s="211"/>
+      <c r="U4" s="211"/>
+      <c r="V4" s="211"/>
+      <c r="W4" s="211"/>
+      <c r="X4" s="211"/>
+      <c r="Y4" s="211"/>
+      <c r="Z4" s="211"/>
+      <c r="AA4" s="211"/>
+      <c r="AB4" s="211"/>
+      <c r="AC4" s="211"/>
       <c r="AE4" s="123"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -2979,23 +3161,23 @@
       </c>
       <c r="H6" s="107">
         <f>Revenue!H11</f>
-        <v>434357.08500000002</v>
+        <v>447340.815</v>
       </c>
       <c r="I6" s="107">
         <f>Revenue!I11</f>
-        <v>453848.45332500001</v>
+        <v>475336.03063499997</v>
       </c>
       <c r="J6" s="107">
         <f>Revenue!J11</f>
-        <v>474750.19942462503</v>
+        <v>506344.383478845</v>
       </c>
       <c r="K6" s="107">
         <f>Revenue!K11</f>
-        <v>497188.50874625816</v>
+        <v>542553.17067444802</v>
       </c>
       <c r="L6" s="107">
         <f>Revenue!L11</f>
-        <v>521301.75451604521</v>
+        <v>583800.43145643547</v>
       </c>
       <c r="N6" s="115" t="s">
         <v>154</v>
@@ -3040,23 +3222,23 @@
       </c>
       <c r="H7" s="132">
         <f>'COGS &amp; OpEx'!H11</f>
-        <v>229340.54088000002</v>
+        <v>236195.95032</v>
       </c>
       <c r="I7" s="132">
         <f>'COGS &amp; OpEx'!I11</f>
-        <v>238270.43799562502</v>
+        <v>249551.41608337499</v>
       </c>
       <c r="J7" s="132">
         <f>'COGS &amp; OpEx'!J11</f>
-        <v>247344.85390022965</v>
+        <v>263805.42379247828</v>
       </c>
       <c r="K7" s="132">
         <f>'COGS &amp; OpEx'!K11</f>
-        <v>258538.02454805427</v>
+        <v>282127.64875071298</v>
       </c>
       <c r="L7" s="132">
         <f>'COGS &amp; OpEx'!L11</f>
-        <v>268470.40357576328</v>
+        <v>300657.22220006428</v>
       </c>
       <c r="N7" s="115" t="s">
         <v>148</v>
@@ -3101,23 +3283,23 @@
       </c>
       <c r="H8" s="109">
         <f t="shared" si="0"/>
-        <v>205016.54412000001</v>
+        <v>211144.86468</v>
       </c>
       <c r="I8" s="109">
         <f t="shared" si="0"/>
-        <v>215578.01532937499</v>
+        <v>225784.61455162498</v>
       </c>
       <c r="J8" s="109">
         <f t="shared" si="0"/>
-        <v>227405.34552439538</v>
+        <v>242538.95968636672</v>
       </c>
       <c r="K8" s="109">
         <f t="shared" si="0"/>
-        <v>238650.48419820389</v>
+        <v>260425.52192373504</v>
       </c>
       <c r="L8" s="109">
         <f t="shared" si="0"/>
-        <v>252831.35094028193</v>
+        <v>283143.20925637119</v>
       </c>
       <c r="N8" s="115"/>
       <c r="Q8" s="115"/>
@@ -3160,23 +3342,23 @@
       </c>
       <c r="H9" s="132">
         <f>'COGS &amp; OpEx'!H12</f>
-        <v>38223.423479999998</v>
+        <v>39365.991719999998</v>
       </c>
       <c r="I9" s="132">
         <f>'COGS &amp; OpEx'!I12</f>
-        <v>41754.057705899999</v>
+        <v>43730.914818419995</v>
       </c>
       <c r="J9" s="132">
         <f>'COGS &amp; OpEx'!J12</f>
-        <v>45101.268945339376</v>
+        <v>48102.716430490276</v>
       </c>
       <c r="K9" s="132">
         <f>'COGS &amp; OpEx'!K12</f>
-        <v>49718.850874625816</v>
+        <v>54255.317067444805</v>
       </c>
       <c r="L9" s="132">
         <f>'COGS &amp; OpEx'!L12</f>
-        <v>52130.175451604526</v>
+        <v>58380.043145643547</v>
       </c>
       <c r="N9" s="115" t="s">
         <v>148</v>
@@ -3221,23 +3403,23 @@
       </c>
       <c r="H10" s="132">
         <f>'COGS &amp; OpEx'!H13</f>
-        <v>29536.281780000005</v>
+        <v>30419.175420000003</v>
       </c>
       <c r="I10" s="132">
         <f>'COGS &amp; OpEx'!I13</f>
-        <v>30407.846372775002</v>
+        <v>31847.514052545001</v>
       </c>
       <c r="J10" s="132">
         <f>'COGS &amp; OpEx'!J13</f>
-        <v>32757.763760299131</v>
+        <v>34937.762460040307</v>
       </c>
       <c r="K10" s="132">
         <f>'COGS &amp; OpEx'!K13</f>
-        <v>34803.195612238072</v>
+        <v>37978.721947211365</v>
       </c>
       <c r="L10" s="132">
         <f>'COGS &amp; OpEx'!L13</f>
-        <v>35448.519307091075</v>
+        <v>39698.429339037611</v>
       </c>
       <c r="N10" s="115" t="s">
         <v>148</v>
@@ -3282,23 +3464,23 @@
       </c>
       <c r="H11" s="132">
         <f>'COGS &amp; OpEx'!H14</f>
-        <v>67759.705260000002</v>
+        <v>69785.167140000005</v>
       </c>
       <c r="I11" s="132">
         <f>'COGS &amp; OpEx'!I14</f>
-        <v>72161.904078674997</v>
+        <v>75578.428870964999</v>
       </c>
       <c r="J11" s="132">
         <f>'COGS &amp; OpEx'!J14</f>
-        <v>77859.032705638499</v>
+        <v>83040.47889053059</v>
       </c>
       <c r="K11" s="132">
         <f>'COGS &amp; OpEx'!K14</f>
-        <v>84522.046486863896</v>
+        <v>92234.039014656169</v>
       </c>
       <c r="L11" s="132">
         <f>'COGS &amp; OpEx'!L14</f>
-        <v>87578.694758695608</v>
+        <v>98078.472484681159</v>
       </c>
       <c r="N11" s="143" t="s">
         <v>148</v>
@@ -3343,23 +3525,23 @@
       </c>
       <c r="H12" s="109">
         <f t="shared" si="1"/>
-        <v>137256.83886000002</v>
+        <v>141359.69753999999</v>
       </c>
       <c r="I12" s="109">
         <f t="shared" si="1"/>
-        <v>143416.11125069999</v>
+        <v>150206.18568065998</v>
       </c>
       <c r="J12" s="109">
         <f t="shared" si="1"/>
-        <v>149546.31281875688</v>
+        <v>159498.48079583613</v>
       </c>
       <c r="K12" s="109">
         <f t="shared" si="1"/>
-        <v>154128.43771134</v>
+        <v>168191.48290907888</v>
       </c>
       <c r="L12" s="109">
         <f t="shared" si="1"/>
-        <v>165252.65618158632</v>
+        <v>185064.73677169002</v>
       </c>
       <c r="N12" s="115"/>
       <c r="Q12" s="115"/>
@@ -3377,18 +3559,18 @@
       <c r="AE12" s="104"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C15" s="201" t="s">
+      <c r="C15" s="212" t="s">
         <v>142</v>
       </c>
-      <c r="D15" s="201"/>
-      <c r="E15" s="201"/>
-      <c r="F15" s="201"/>
-      <c r="G15" s="201"/>
-      <c r="H15" s="201"/>
-      <c r="I15" s="201"/>
-      <c r="J15" s="201"/>
-      <c r="K15" s="201"/>
-      <c r="L15" s="201"/>
+      <c r="D15" s="212"/>
+      <c r="E15" s="212"/>
+      <c r="F15" s="212"/>
+      <c r="G15" s="212"/>
+      <c r="H15" s="212"/>
+      <c r="I15" s="212"/>
+      <c r="J15" s="212"/>
+      <c r="K15" s="212"/>
+      <c r="L15" s="212"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C16" s="62">
@@ -3473,18 +3655,18 @@
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C20" s="201" t="s">
+      <c r="C20" s="212" t="s">
         <v>314</v>
       </c>
-      <c r="D20" s="201"/>
-      <c r="E20" s="201"/>
-      <c r="F20" s="201"/>
-      <c r="G20" s="201"/>
-      <c r="H20" s="201"/>
-      <c r="I20" s="201"/>
-      <c r="J20" s="201"/>
-      <c r="K20" s="201"/>
-      <c r="L20" s="201"/>
+      <c r="D20" s="212"/>
+      <c r="E20" s="212"/>
+      <c r="F20" s="212"/>
+      <c r="G20" s="212"/>
+      <c r="H20" s="212"/>
+      <c r="I20" s="212"/>
+      <c r="J20" s="212"/>
+      <c r="K20" s="212"/>
+      <c r="L20" s="212"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
@@ -3557,23 +3739,23 @@
       </c>
       <c r="H22" s="103">
         <f>'WC &amp; Investments'!H42</f>
-        <v>12596.355465000001</v>
+        <v>12972.883635</v>
       </c>
       <c r="I22" s="103">
         <f>'WC &amp; Investments'!I42</f>
-        <v>13161.605146425001</v>
+        <v>13784.744888415</v>
       </c>
       <c r="J22" s="103">
         <f>'WC &amp; Investments'!J42</f>
-        <v>13767.755783314127</v>
+        <v>14683.987120886506</v>
       </c>
       <c r="K22" s="103">
         <f>'WC &amp; Investments'!K42</f>
-        <v>14418.466753641487</v>
+        <v>15734.041949558994</v>
       </c>
       <c r="L22" s="103">
         <f>'WC &amp; Investments'!L42</f>
-        <v>15117.750880965312</v>
+        <v>16930.212512236631</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>315</v>
@@ -3605,23 +3787,23 @@
       </c>
       <c r="H23" s="103">
         <f>'WC &amp; Investments'!H45</f>
-        <v>13030.71255</v>
+        <v>13420.22445</v>
       </c>
       <c r="I23" s="103">
         <f>'WC &amp; Investments'!I45</f>
-        <v>13615.453599750001</v>
+        <v>14260.080919049999</v>
       </c>
       <c r="J23" s="103">
         <f>'WC &amp; Investments'!J45</f>
-        <v>14242.50598273875</v>
+        <v>15190.331504365349</v>
       </c>
       <c r="K23" s="103">
         <f>'WC &amp; Investments'!K45</f>
-        <v>14915.655262387743</v>
+        <v>16276.59512023344</v>
       </c>
       <c r="L23" s="103">
         <f>'WC &amp; Investments'!L45</f>
-        <v>15639.052635481356</v>
+        <v>17514.012943693062</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>315</v>
@@ -3653,41 +3835,41 @@
       </c>
       <c r="H24" s="103">
         <f>'WC &amp; Investments'!H35</f>
-        <v>-8594.8627659726008</v>
+        <v>-8123.4644373150641</v>
       </c>
       <c r="I24" s="103">
         <f>'WC &amp; Investments'!I35</f>
-        <v>-8852.3526621678047</v>
+        <v>-8844.606151810287</v>
       </c>
       <c r="J24" s="103">
         <f>'WC &amp; Investments'!J35</f>
-        <v>-9465.1759326919564</v>
+        <v>-9621.0883994129763</v>
       </c>
       <c r="K24" s="103">
         <f>'WC &amp; Investments'!K35</f>
-        <v>-9537.2576751647575</v>
+        <v>-9797.2455353458463</v>
       </c>
       <c r="L24" s="103">
         <f>'WC &amp; Investments'!L35</f>
-        <v>-10079.037332128893</v>
+        <v>-10567.840887672719</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="201" t="s">
+      <c r="C27" s="212" t="s">
         <v>145</v>
       </c>
-      <c r="D27" s="201"/>
-      <c r="E27" s="201"/>
-      <c r="F27" s="201"/>
-      <c r="G27" s="201"/>
-      <c r="H27" s="201"/>
-      <c r="I27" s="201"/>
-      <c r="J27" s="201"/>
-      <c r="K27" s="201"/>
-      <c r="L27" s="201"/>
+      <c r="D27" s="212"/>
+      <c r="E27" s="212"/>
+      <c r="F27" s="212"/>
+      <c r="G27" s="212"/>
+      <c r="H27" s="212"/>
+      <c r="I27" s="212"/>
+      <c r="J27" s="212"/>
+      <c r="K27" s="212"/>
+      <c r="L27" s="212"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
@@ -3760,23 +3942,23 @@
       </c>
       <c r="H29" s="133">
         <f t="shared" si="5"/>
-        <v>108432.90269940002</v>
+        <v>111674.1610566</v>
       </c>
       <c r="I29" s="133">
         <f t="shared" si="5"/>
-        <v>113298.72788805299</v>
+        <v>118662.88668772139</v>
       </c>
       <c r="J29" s="133">
         <f t="shared" si="5"/>
-        <v>118141.58712681795</v>
+        <v>126003.79982871056</v>
       </c>
       <c r="K29" s="133">
         <f t="shared" si="5"/>
-        <v>121761.4657919586</v>
+        <v>132871.27149817231</v>
       </c>
       <c r="L29" s="133">
         <f t="shared" si="5"/>
-        <v>130549.59838345321</v>
+        <v>146201.14204963512</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.2">
@@ -3805,28 +3987,27 @@
       </c>
       <c r="H30" s="109">
         <f t="shared" si="6"/>
-        <v>99403.682848427416</v>
+        <v>103103.35580428495</v>
       </c>
       <c r="I30" s="109">
         <f t="shared" si="6"/>
-        <v>103992.52677256019</v>
+        <v>109342.9445052761</v>
       </c>
       <c r="J30" s="109">
         <f t="shared" si="6"/>
-        <v>108201.66099470138</v>
+        <v>115876.36704581874</v>
       </c>
       <c r="K30" s="109">
         <f t="shared" si="6"/>
-        <v>111727.01960804759</v>
+        <v>122531.47279215204</v>
       </c>
       <c r="L30" s="109">
         <f t="shared" si="6"/>
-        <v>119949.25929680829</v>
+        <v>135049.50073050597</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C20:L20"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
@@ -3835,6 +4016,7 @@
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C15:L15"/>
+    <mergeCell ref="C20:L20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3894,10 +4076,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="196" t="s">
+      <c r="B4" s="208" t="s">
         <v>160</v>
       </c>
-      <c r="C4" s="196"/>
+      <c r="C4" s="208"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -3914,7 +4096,7 @@
       </c>
       <c r="C6" s="145">
         <f>Overview!C3</f>
-        <v>271.06</v>
+        <v>270.70999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3923,7 +4105,7 @@
       </c>
       <c r="C7" s="147">
         <f>C5*C6</f>
-        <v>3979431.86</v>
+        <v>3974293.51</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3941,7 +4123,7 @@
       </c>
       <c r="C9" s="170">
         <f>[1]Sheet1!$C$10/1000</f>
-        <v>4.3099999999999999E-2</v>
+        <v>4.3360000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3950,7 +4132,7 @@
       </c>
       <c r="C10" s="145">
         <f>[1]Sheet1!$F$17</f>
-        <v>1.0716000000000001</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3958,7 +4140,7 @@
         <v>164</v>
       </c>
       <c r="C11" s="146">
-        <v>5.5E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3979,10 +4161,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="196" t="s">
+      <c r="B15" s="208" t="s">
         <v>166</v>
       </c>
-      <c r="C15" s="196"/>
+      <c r="C15" s="208"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -3990,7 +4172,7 @@
       </c>
       <c r="C16" s="148">
         <f>C8/(C8+C7)</f>
-        <v>2.2238406677978117E-2</v>
+        <v>2.2266518429206541E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3999,7 +4181,7 @@
       </c>
       <c r="C17" s="148">
         <f>C7/(C8+C7)</f>
-        <v>0.97776159332202184</v>
+        <v>0.97773348157079343</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4017,7 +4199,7 @@
       </c>
       <c r="C19" s="148">
         <f>C9+C10*C11</f>
-        <v>0.102038</v>
+        <v>9.6360000000000001E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4026,7 +4208,7 @@
       </c>
       <c r="C20" s="148">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>0.10055941281679459</v>
+        <v>9.5005973014319955E-2</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4073,60 +4255,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="196" t="s">
+      <c r="C3" s="208" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="196"/>
-      <c r="E3" s="196"/>
-      <c r="F3" s="196"/>
-      <c r="G3" s="199"/>
-      <c r="H3" s="200" t="s">
+      <c r="D3" s="208"/>
+      <c r="E3" s="208"/>
+      <c r="F3" s="208"/>
+      <c r="G3" s="209"/>
+      <c r="H3" s="210" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="196"/>
-      <c r="J3" s="196"/>
-      <c r="K3" s="196"/>
-      <c r="L3" s="196"/>
-      <c r="P3" s="202"/>
-      <c r="Q3" s="202"/>
-      <c r="R3" s="202"/>
-      <c r="S3" s="202"/>
-      <c r="T3" s="202"/>
-      <c r="U3" s="202"/>
-      <c r="V3" s="202"/>
-      <c r="W3" s="202"/>
-      <c r="X3" s="202"/>
-      <c r="Y3" s="202"/>
-      <c r="Z3" s="202"/>
+      <c r="I3" s="208"/>
+      <c r="J3" s="208"/>
+      <c r="K3" s="208"/>
+      <c r="L3" s="208"/>
+      <c r="P3" s="211"/>
+      <c r="Q3" s="211"/>
+      <c r="R3" s="211"/>
+      <c r="S3" s="211"/>
+      <c r="T3" s="211"/>
+      <c r="U3" s="211"/>
+      <c r="V3" s="211"/>
+      <c r="W3" s="211"/>
+      <c r="X3" s="211"/>
+      <c r="Y3" s="211"/>
+      <c r="Z3" s="211"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="201" t="s">
+      <c r="C5" s="212" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="201"/>
-      <c r="E5" s="201"/>
-      <c r="F5" s="201"/>
-      <c r="G5" s="201"/>
-      <c r="H5" s="201"/>
-      <c r="I5" s="201"/>
-      <c r="J5" s="201"/>
-      <c r="K5" s="201"/>
-      <c r="L5" s="201"/>
-      <c r="P5" s="202"/>
-      <c r="Q5" s="202"/>
-      <c r="R5" s="202"/>
-      <c r="S5" s="202"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="202"/>
-      <c r="W5" s="202"/>
-      <c r="X5" s="202"/>
-      <c r="Y5" s="202"/>
-      <c r="Z5" s="202"/>
+      <c r="D5" s="212"/>
+      <c r="E5" s="212"/>
+      <c r="F5" s="212"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="212"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="212"/>
+      <c r="K5" s="212"/>
+      <c r="L5" s="212"/>
+      <c r="P5" s="211"/>
+      <c r="Q5" s="211"/>
+      <c r="R5" s="211"/>
+      <c r="S5" s="211"/>
+      <c r="T5" s="211"/>
+      <c r="U5" s="211"/>
+      <c r="V5" s="211"/>
+      <c r="W5" s="211"/>
+      <c r="X5" s="211"/>
+      <c r="Y5" s="211"/>
+      <c r="Z5" s="211"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -4213,23 +4395,23 @@
       </c>
       <c r="H7" s="132">
         <f>'FCF &amp; Other'!H30</f>
-        <v>99403.682848427416</v>
+        <v>103103.35580428495</v>
       </c>
       <c r="I7" s="132">
         <f>'FCF &amp; Other'!I30</f>
-        <v>103992.52677256019</v>
+        <v>109342.9445052761</v>
       </c>
       <c r="J7" s="132">
         <f>'FCF &amp; Other'!J30</f>
-        <v>108201.66099470138</v>
+        <v>115876.36704581874</v>
       </c>
       <c r="K7" s="132">
         <f>'FCF &amp; Other'!K30</f>
-        <v>111727.01960804759</v>
+        <v>122531.47279215204</v>
       </c>
       <c r="L7" s="132">
         <f>'FCF &amp; Other'!L30</f>
-        <v>119949.25929680829</v>
+        <v>135049.50073050597</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="7"/>
@@ -4279,7 +4461,7 @@
       </c>
       <c r="L8" s="133">
         <f>L7*(1+C14)/(C15-C14)</f>
-        <v>1518733.0717142213</v>
+        <v>1977341.8222535548</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="7"/>
@@ -4333,23 +4515,23 @@
       <c r="G10" s="150"/>
       <c r="H10" s="133">
         <f>H7/(1+$C$15)^H9</f>
-        <v>90321.050995340236</v>
+        <v>94157.802190305141</v>
       </c>
       <c r="I10" s="133">
         <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>85856.888535362625</v>
+        <v>91192.220033433419</v>
       </c>
       <c r="J10" s="133">
         <f t="shared" si="0"/>
-        <v>81169.608254759558</v>
+        <v>88256.236972329716</v>
       </c>
       <c r="K10" s="133">
         <f t="shared" si="0"/>
-        <v>76156.020760377622</v>
+        <v>85227.88299488007</v>
       </c>
       <c r="L10" s="133">
         <f t="shared" si="0"/>
-        <v>74289.957120385516</v>
+        <v>85784.83932202826</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -4368,21 +4550,21 @@
       <c r="K11" s="130"/>
       <c r="L11" s="133">
         <f>L8/(1+C15)^L9</f>
-        <v>940619.52059059578</v>
+        <v>1256027.9718859517</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="196" t="s">
+      <c r="B13" s="208" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="196"/>
+      <c r="C13" s="208"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
         <v>170</v>
       </c>
       <c r="C14" s="139">
-        <v>0.02</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
@@ -4391,14 +4573,14 @@
       </c>
       <c r="C15" s="149">
         <f>WACC!C20</f>
-        <v>0.10055941281679459</v>
+        <v>9.5005973014319955E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="196" t="s">
+      <c r="B18" s="208" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="196"/>
+      <c r="C18" s="208"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -4406,7 +4588,7 @@
       </c>
       <c r="C19" s="104">
         <f>SUM(H10:L10)</f>
-        <v>407793.52566622559</v>
+        <v>444618.98151297664</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -4415,7 +4597,7 @@
       </c>
       <c r="C20" s="104">
         <f>L11</f>
-        <v>940619.52059059578</v>
+        <v>1256027.9718859517</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -4424,7 +4606,7 @@
       </c>
       <c r="C21" s="109">
         <f>C19+C20</f>
-        <v>1348413.0462568214</v>
+        <v>1700646.9533989283</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -4432,8 +4614,8 @@
         <v>174</v>
       </c>
       <c r="C22" s="20">
-        <f>Statements!W21</f>
-        <v>66907</v>
+        <f>Statements!W21+Statements!W27</f>
+        <v>144795</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
@@ -4451,7 +4633,7 @@
       </c>
       <c r="C24" s="109">
         <f>C21+C22-C23</f>
-        <v>1324811.0462568214</v>
+        <v>1754932.9533989283</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -4459,8 +4641,8 @@
         <v>4</v>
       </c>
       <c r="C25" s="104">
-        <f>'Statement Q'!N17</f>
-        <v>14919.5</v>
+        <f>'Statement Q'!N100</f>
+        <v>14681</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
@@ -4469,7 +4651,7 @@
       </c>
       <c r="C26" s="152">
         <f>C24/C25</f>
-        <v>88.797281829606987</v>
+        <v>119.5376986171874</v>
       </c>
     </row>
   </sheetData>
@@ -4512,37 +4694,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="196" t="s">
+      <c r="C2" s="208" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="196"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="199"/>
-      <c r="H2" s="200" t="s">
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="209"/>
+      <c r="H2" s="210" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="196"/>
-      <c r="J2" s="196"/>
-      <c r="K2" s="196"/>
-      <c r="L2" s="196"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="201" t="s">
+      <c r="C4" s="212" t="s">
         <v>318</v>
       </c>
-      <c r="D4" s="201"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="201"/>
-      <c r="G4" s="201"/>
-      <c r="H4" s="201"/>
-      <c r="I4" s="201"/>
-      <c r="J4" s="201"/>
-      <c r="K4" s="201"/>
-      <c r="L4" s="201"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="212"/>
+      <c r="H4" s="212"/>
+      <c r="I4" s="212"/>
+      <c r="J4" s="212"/>
+      <c r="K4" s="212"/>
+      <c r="L4" s="212"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -4615,23 +4797,23 @@
       </c>
       <c r="H6" s="107">
         <f>Revenue!H11</f>
-        <v>434357.08500000002</v>
+        <v>447340.815</v>
       </c>
       <c r="I6" s="107">
         <f>Revenue!I11</f>
-        <v>453848.45332500001</v>
+        <v>475336.03063499997</v>
       </c>
       <c r="J6" s="107">
         <f>Revenue!J11</f>
-        <v>474750.19942462503</v>
+        <v>506344.383478845</v>
       </c>
       <c r="K6" s="107">
         <f>Revenue!K11</f>
-        <v>497188.50874625816</v>
+        <v>542553.17067444802</v>
       </c>
       <c r="L6" s="107">
         <f>Revenue!L11</f>
-        <v>521301.75451604521</v>
+        <v>583800.43145643547</v>
       </c>
       <c r="N6" s="91"/>
     </row>
@@ -4661,23 +4843,23 @@
       </c>
       <c r="H7" s="107">
         <f>'FCF &amp; Other'!H12</f>
-        <v>137256.83886000002</v>
+        <v>141359.69753999999</v>
       </c>
       <c r="I7" s="107">
         <f>'FCF &amp; Other'!I12</f>
-        <v>143416.11125069999</v>
+        <v>150206.18568065998</v>
       </c>
       <c r="J7" s="107">
         <f>'FCF &amp; Other'!J12</f>
-        <v>149546.31281875688</v>
+        <v>159498.48079583613</v>
       </c>
       <c r="K7" s="107">
         <f>'FCF &amp; Other'!K12</f>
-        <v>154128.43771134</v>
+        <v>168191.48290907888</v>
       </c>
       <c r="L7" s="107">
         <f>'FCF &amp; Other'!L12</f>
-        <v>165252.65618158632</v>
+        <v>185064.73677169002</v>
       </c>
       <c r="N7" s="91"/>
     </row>
@@ -4707,23 +4889,23 @@
       </c>
       <c r="H8" s="107">
         <f>'FCF &amp; Other'!H30</f>
-        <v>99403.682848427416</v>
+        <v>103103.35580428495</v>
       </c>
       <c r="I8" s="107">
         <f>'FCF &amp; Other'!I30</f>
-        <v>103992.52677256019</v>
+        <v>109342.9445052761</v>
       </c>
       <c r="J8" s="107">
         <f>'FCF &amp; Other'!J30</f>
-        <v>108201.66099470138</v>
+        <v>115876.36704581874</v>
       </c>
       <c r="K8" s="107">
         <f>'FCF &amp; Other'!K30</f>
-        <v>111727.01960804759</v>
+        <v>122531.47279215204</v>
       </c>
       <c r="L8" s="107">
         <f>'FCF &amp; Other'!L30</f>
-        <v>119949.25929680829</v>
+        <v>135049.50073050597</v>
       </c>
       <c r="N8" s="91"/>
     </row>
@@ -4731,18 +4913,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="201" t="s">
+      <c r="C10" s="212" t="s">
         <v>116</v>
       </c>
-      <c r="D10" s="201"/>
-      <c r="E10" s="201"/>
-      <c r="F10" s="201"/>
-      <c r="G10" s="201"/>
-      <c r="H10" s="201"/>
-      <c r="I10" s="201"/>
-      <c r="J10" s="201"/>
-      <c r="K10" s="201"/>
-      <c r="L10" s="201"/>
+      <c r="D10" s="212"/>
+      <c r="E10" s="212"/>
+      <c r="F10" s="212"/>
+      <c r="G10" s="212"/>
+      <c r="H10" s="212"/>
+      <c r="I10" s="212"/>
+      <c r="J10" s="212"/>
+      <c r="K10" s="212"/>
+      <c r="L10" s="212"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -4814,23 +4996,23 @@
       </c>
       <c r="H12" s="111">
         <f t="shared" si="1"/>
-        <v>4.3723667042322611E-2</v>
+        <v>7.4922481924063047E-2</v>
       </c>
       <c r="I12" s="111">
         <f t="shared" si="1"/>
-        <v>4.4874065597433475E-2</v>
+        <v>6.25814025822794E-2</v>
       </c>
       <c r="J12" s="111">
         <f t="shared" si="1"/>
-        <v>4.6054461454024864E-2</v>
+        <v>6.5234593730294471E-2</v>
       </c>
       <c r="K12" s="111">
         <f t="shared" si="1"/>
-        <v>4.726340157166297E-2</v>
+        <v>7.1510198151760115E-2</v>
       </c>
       <c r="L12" s="111">
         <f t="shared" si="1"/>
-        <v>4.8499201702373478E-2</v>
+        <v>7.602436592659291E-2</v>
       </c>
       <c r="N12" s="91"/>
     </row>
@@ -4857,23 +5039,23 @@
       </c>
       <c r="H13" s="111">
         <f t="shared" si="1"/>
-        <v>3.1618480721533393E-2</v>
+        <v>6.2455449379932311E-2</v>
       </c>
       <c r="I13" s="111">
         <f t="shared" si="1"/>
-        <v>4.4874065597433309E-2</v>
+        <v>6.2581402582279386E-2</v>
       </c>
       <c r="J13" s="111">
         <f t="shared" si="1"/>
-        <v>4.2744162525372942E-2</v>
+        <v>6.1863598180514845E-2</v>
       </c>
       <c r="K13" s="111">
         <f t="shared" si="1"/>
-        <v>3.0640172975287178E-2</v>
+        <v>5.4502099768399107E-2</v>
       </c>
       <c r="L13" s="111">
         <f t="shared" si="1"/>
-        <v>7.2174990127911121E-2</v>
+        <v>0.10032169031848358</v>
       </c>
       <c r="N13" s="91"/>
     </row>
@@ -4900,23 +5082,23 @@
       </c>
       <c r="H14" s="111">
         <f t="shared" si="1"/>
-        <v>0.15232086876278106</v>
+        <v>0.1952087199215006</v>
       </c>
       <c r="I14" s="111">
         <f t="shared" si="1"/>
-        <v>4.6163721430019115E-2</v>
+        <v>6.0517804220023626E-2</v>
       </c>
       <c r="J14" s="111">
         <f t="shared" si="1"/>
-        <v>4.0475352919800645E-2</v>
+        <v>5.9751660887707163E-2</v>
       </c>
       <c r="K14" s="111">
         <f t="shared" si="1"/>
-        <v>3.2581372420140989E-2</v>
+        <v>5.7432813230171423E-2</v>
       </c>
       <c r="L14" s="111">
         <f t="shared" si="1"/>
-        <v>7.3592222522406409E-2</v>
+        <v>0.10216173570024772</v>
       </c>
       <c r="N14" s="91"/>
     </row>
@@ -4924,18 +5106,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="201" t="s">
+      <c r="C16" s="212" t="s">
         <v>217</v>
       </c>
-      <c r="D16" s="201"/>
-      <c r="E16" s="201"/>
-      <c r="F16" s="201"/>
-      <c r="G16" s="201"/>
-      <c r="H16" s="201"/>
-      <c r="I16" s="201"/>
-      <c r="J16" s="201"/>
-      <c r="K16" s="201"/>
-      <c r="L16" s="201"/>
+      <c r="D16" s="212"/>
+      <c r="E16" s="212"/>
+      <c r="F16" s="212"/>
+      <c r="G16" s="212"/>
+      <c r="H16" s="212"/>
+      <c r="I16" s="212"/>
+      <c r="J16" s="212"/>
+      <c r="K16" s="212"/>
+      <c r="L16" s="212"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -5069,18 +5251,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="201" t="s">
+      <c r="C21" s="212" t="s">
         <v>319</v>
       </c>
-      <c r="D21" s="201"/>
-      <c r="E21" s="201"/>
-      <c r="F21" s="201"/>
-      <c r="G21" s="201"/>
-      <c r="H21" s="201"/>
-      <c r="I21" s="201"/>
-      <c r="J21" s="201"/>
-      <c r="K21" s="201"/>
-      <c r="L21" s="201"/>
+      <c r="D21" s="212"/>
+      <c r="E21" s="212"/>
+      <c r="F21" s="212"/>
+      <c r="G21" s="212"/>
+      <c r="H21" s="212"/>
+      <c r="I21" s="212"/>
+      <c r="J21" s="212"/>
+      <c r="K21" s="212"/>
+      <c r="L21" s="212"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -5164,18 +5346,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="201" t="s">
+      <c r="C26" s="212" t="s">
         <v>320</v>
       </c>
-      <c r="D26" s="201"/>
-      <c r="E26" s="201"/>
-      <c r="F26" s="201"/>
-      <c r="G26" s="201"/>
-      <c r="H26" s="201"/>
-      <c r="I26" s="201"/>
-      <c r="J26" s="201"/>
-      <c r="K26" s="201"/>
-      <c r="L26" s="201"/>
+      <c r="D26" s="212"/>
+      <c r="E26" s="212"/>
+      <c r="F26" s="212"/>
+      <c r="G26" s="212"/>
+      <c r="H26" s="212"/>
+      <c r="I26" s="212"/>
+      <c r="J26" s="212"/>
+      <c r="K26" s="212"/>
+      <c r="L26" s="212"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -5445,10 +5627,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="196" t="s">
+      <c r="B37" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="C37" s="196"/>
+      <c r="C37" s="208"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -5457,7 +5639,7 @@
       </c>
       <c r="C38" s="104">
         <f>L7</f>
-        <v>165252.65618158632</v>
+        <v>185064.73677169002</v>
       </c>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
@@ -5466,7 +5648,7 @@
       </c>
       <c r="C39" s="138">
         <f>WACC!C20</f>
-        <v>0.10055941281679459</v>
+        <v>9.5005973014319955E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -5474,7 +5656,7 @@
         <v>326</v>
       </c>
       <c r="C40" s="118">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
@@ -5492,7 +5674,7 @@
       </c>
       <c r="C42" s="20">
         <f>(C38*C40)-G30+G31</f>
-        <v>3756851.0921764853</v>
+        <v>4582658.4192922506</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -5501,7 +5683,7 @@
       </c>
       <c r="C43" s="20">
         <f>C42/C41</f>
-        <v>282.42004262037705</v>
+        <v>344.49983625551374</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -5510,14 +5692,14 @@
       </c>
       <c r="C44" s="152">
         <f>C43/(1+C48)^5</f>
-        <v>174.91540155566045</v>
+        <v>218.82985823559341</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="196" t="s">
+      <c r="B46" s="208" t="s">
         <v>193</v>
       </c>
-      <c r="C46" s="196"/>
+      <c r="C46" s="208"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -5525,7 +5707,7 @@
       </c>
       <c r="C47" s="104">
         <f>L6</f>
-        <v>521301.75451604521</v>
+        <v>583800.43145643547</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
@@ -5534,7 +5716,7 @@
       </c>
       <c r="C48" s="138">
         <f>WACC!C20</f>
-        <v>0.10055941281679459</v>
+        <v>9.5005973014319955E-2</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -5542,7 +5724,7 @@
         <v>195</v>
       </c>
       <c r="C49" s="118">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
@@ -5560,7 +5742,7 @@
       </c>
       <c r="C51" s="20">
         <f>(C47*C49)/C50</f>
-        <v>235.13212546820196</v>
+        <v>307.20903512505498</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -5569,14 +5751,14 @@
       </c>
       <c r="C52" s="152">
         <f>C51/(1+C48)^5</f>
-        <v>145.62787316121953</v>
+        <v>195.14235575789263</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="196" t="s">
+      <c r="B54" s="208" t="s">
         <v>328</v>
       </c>
-      <c r="C54" s="196"/>
+      <c r="C54" s="208"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -5584,7 +5766,7 @@
       </c>
       <c r="C55" s="104">
         <f>L8</f>
-        <v>119949.25929680829</v>
+        <v>135049.50073050597</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
@@ -5592,8 +5774,8 @@
         <v>156</v>
       </c>
       <c r="C56" s="138">
-        <f>[2]WACC!C20</f>
-        <v>8.92125E-2</v>
+        <f>WACC!C20</f>
+        <v>9.5005973014319955E-2</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -5601,7 +5783,7 @@
         <v>330</v>
       </c>
       <c r="C57" s="118">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
@@ -5619,7 +5801,7 @@
       </c>
       <c r="C59" s="20">
         <f>(C55*C57)-G30+G31</f>
-        <v>3314619.2603106322</v>
+        <v>4007525.0219151792</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -5628,7 +5810,7 @@
       </c>
       <c r="C60" s="20">
         <f>C59/C58</f>
-        <v>249.1754104166329</v>
+        <v>301.26437266796614</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
@@ -5637,7 +5819,7 @@
       </c>
       <c r="C61" s="152">
         <f>C60/(1+C56)^5</f>
-        <v>162.53320471955453</v>
+        <v>191.36624469530753</v>
       </c>
     </row>
   </sheetData>
@@ -5659,7 +5841,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4129066-37B2-D945-8B9C-64190B26E6C8}">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="99" customWidth="1"/>
@@ -5686,10 +5868,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="196" t="s">
+      <c r="B4" s="208" t="s">
         <v>201</v>
       </c>
-      <c r="C4" s="196"/>
+      <c r="C4" s="208"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -5698,7 +5880,7 @@
       </c>
       <c r="C5" s="167">
         <f>DCF!C26</f>
-        <v>88.797281829606987</v>
+        <v>119.5376986171874</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -5707,7 +5889,7 @@
       </c>
       <c r="C6" s="167">
         <f>Multiples!C44</f>
-        <v>174.91540155566045</v>
+        <v>218.82985823559341</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -5716,7 +5898,7 @@
       </c>
       <c r="C7" s="167">
         <f>Multiples!C52</f>
-        <v>145.62787316121953</v>
+        <v>195.14235575789263</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -5725,7 +5907,7 @@
       </c>
       <c r="C8" s="167">
         <f>Multiples!C61</f>
-        <v>162.53320471955453</v>
+        <v>191.36624469530753</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -5734,7 +5916,25 @@
       </c>
       <c r="C9" s="152">
         <f>AVERAGE(C5:C8)</f>
-        <v>142.96844031651037</v>
+        <v>181.21903932649522</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C10" s="35">
+        <f>Overview!C3</f>
+        <v>270.70999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C11" s="89">
+        <f>(C9-C10)/C10</f>
+        <v>-0.33057870294228053</v>
       </c>
     </row>
   </sheetData>
@@ -5742,6 +5942,969 @@
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93080341-CAE4-D241-B95E-0D35628EE8CB}">
+  <dimension ref="A1:AB49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2" style="99" customWidth="1"/>
+    <col min="2" max="2" width="32" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="1"/>
+    <col min="4" max="4" width="10.83203125" style="1" customWidth="1"/>
+    <col min="5" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="10.83203125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="10.83203125" style="1"/>
+    <col min="13" max="13" width="28" style="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5" style="1" customWidth="1"/>
+    <col min="15" max="15" width="24.6640625" style="1" customWidth="1"/>
+    <col min="16" max="26" width="10.83203125" style="1"/>
+    <col min="27" max="27" width="2" style="1" customWidth="1"/>
+    <col min="28" max="28" width="12.33203125" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" s="99" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="100"/>
+      <c r="B1" s="101" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" s="99" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A3" s="100"/>
+      <c r="C3" s="208" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="208"/>
+      <c r="E3" s="208"/>
+      <c r="F3" s="208"/>
+      <c r="G3" s="209"/>
+      <c r="H3" s="210" t="s">
+        <v>106</v>
+      </c>
+      <c r="I3" s="208"/>
+      <c r="J3" s="208"/>
+      <c r="K3" s="208"/>
+      <c r="L3" s="208"/>
+      <c r="P3" s="211"/>
+      <c r="Q3" s="211"/>
+      <c r="R3" s="211"/>
+      <c r="S3" s="211"/>
+      <c r="T3" s="211"/>
+      <c r="U3" s="211"/>
+      <c r="V3" s="211"/>
+      <c r="W3" s="211"/>
+      <c r="X3" s="211"/>
+      <c r="Y3" s="211"/>
+      <c r="Z3" s="211"/>
+      <c r="AB3" s="122"/>
+    </row>
+    <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="105"/>
+      <c r="B5" s="92"/>
+      <c r="C5" s="212" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="212"/>
+      <c r="E5" s="212"/>
+      <c r="F5" s="212"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="212"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="212"/>
+      <c r="K5" s="212"/>
+      <c r="L5" s="212"/>
+      <c r="P5" s="211"/>
+      <c r="Q5" s="211"/>
+      <c r="R5" s="211"/>
+      <c r="S5" s="211"/>
+      <c r="T5" s="211"/>
+      <c r="U5" s="211"/>
+      <c r="V5" s="211"/>
+      <c r="W5" s="211"/>
+      <c r="X5" s="211"/>
+      <c r="Y5" s="211"/>
+      <c r="Z5" s="211"/>
+      <c r="AB5" s="123"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B6" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="62">
+        <f>Revenue!C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D6" s="62">
+        <f>Revenue!D5</f>
+        <v>2022</v>
+      </c>
+      <c r="E6" s="62">
+        <f>Revenue!E5</f>
+        <v>2023</v>
+      </c>
+      <c r="F6" s="62">
+        <f>Revenue!F5</f>
+        <v>2024</v>
+      </c>
+      <c r="G6" s="62">
+        <f>Revenue!G5</f>
+        <v>2025</v>
+      </c>
+      <c r="H6" s="62">
+        <f>Revenue!H5</f>
+        <v>2026</v>
+      </c>
+      <c r="I6" s="62">
+        <f>Revenue!I5</f>
+        <v>2027</v>
+      </c>
+      <c r="J6" s="62">
+        <f>Revenue!J5</f>
+        <v>2028</v>
+      </c>
+      <c r="K6" s="62">
+        <f>Revenue!K5</f>
+        <v>2029</v>
+      </c>
+      <c r="L6" s="62">
+        <f>Revenue!L5</f>
+        <v>2030</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="124"/>
+      <c r="Q6" s="124"/>
+      <c r="R6" s="124"/>
+      <c r="S6" s="124"/>
+      <c r="T6" s="124"/>
+      <c r="U6" s="124"/>
+      <c r="V6" s="124"/>
+      <c r="W6" s="124"/>
+      <c r="X6" s="124"/>
+      <c r="Y6" s="124"/>
+      <c r="Z6" s="124"/>
+      <c r="AB6" s="123"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B7" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" s="132">
+        <f>'FCF &amp; Other'!C30</f>
+        <v>89744.319832977737</v>
+      </c>
+      <c r="D7" s="132">
+        <f>'FCF &amp; Other'!D30</f>
+        <v>101678.87709797402</v>
+      </c>
+      <c r="E7" s="132">
+        <f>'FCF &amp; Other'!E30</f>
+        <v>91459.836665611598</v>
+      </c>
+      <c r="F7" s="132">
+        <f>'FCF &amp; Other'!F30</f>
+        <v>99180.80528809168</v>
+      </c>
+      <c r="G7" s="134">
+        <f>'FCF &amp; Other'!G30</f>
+        <v>86263.891892502768</v>
+      </c>
+      <c r="H7" s="133">
+        <f>G7*(1+$C$17)</f>
+        <v>113005.69837917863</v>
+      </c>
+      <c r="I7" s="133">
+        <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
+        <v>148037.46487672403</v>
+      </c>
+      <c r="J7" s="133">
+        <f t="shared" si="0"/>
+        <v>193929.0789885085</v>
+      </c>
+      <c r="K7" s="133">
+        <f t="shared" si="0"/>
+        <v>254047.09347494613</v>
+      </c>
+      <c r="L7" s="133">
+        <f t="shared" si="0"/>
+        <v>332801.69245217944</v>
+      </c>
+      <c r="N7" s="91"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="107"/>
+      <c r="Q7" s="107"/>
+      <c r="R7" s="107"/>
+      <c r="S7" s="107"/>
+      <c r="T7" s="107"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="107"/>
+      <c r="W7" s="107"/>
+      <c r="X7" s="109"/>
+      <c r="Y7" s="109"/>
+      <c r="Z7" s="109"/>
+      <c r="AB7" s="109"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B8" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="130"/>
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="130"/>
+      <c r="G8" s="150"/>
+      <c r="H8" s="130"/>
+      <c r="I8" s="130"/>
+      <c r="J8" s="130"/>
+      <c r="K8" s="130"/>
+      <c r="L8" s="133">
+        <f>L7*(1+C20)/(C21-C20)</f>
+        <v>4872751.8535269313</v>
+      </c>
+      <c r="N8" s="91"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="107"/>
+      <c r="Q8" s="107"/>
+      <c r="R8" s="107"/>
+      <c r="S8" s="107"/>
+      <c r="T8" s="107"/>
+      <c r="U8" s="107"/>
+      <c r="V8" s="107"/>
+      <c r="W8" s="107"/>
+      <c r="X8" s="109"/>
+      <c r="Y8" s="109"/>
+      <c r="Z8" s="109"/>
+      <c r="AB8" s="109"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" s="130"/>
+      <c r="D9" s="130"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="130"/>
+      <c r="G9" s="150"/>
+      <c r="H9" s="36">
+        <v>1</v>
+      </c>
+      <c r="I9" s="36">
+        <v>2</v>
+      </c>
+      <c r="J9" s="36">
+        <v>3</v>
+      </c>
+      <c r="K9" s="36">
+        <v>4</v>
+      </c>
+      <c r="L9" s="36">
+        <v>5</v>
+      </c>
+      <c r="N9" s="91"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C10" s="130"/>
+      <c r="D10" s="130"/>
+      <c r="E10" s="130"/>
+      <c r="F10" s="130"/>
+      <c r="G10" s="150"/>
+      <c r="H10" s="133">
+        <f>H7/(1+$C$21)^H9</f>
+        <v>103200.98808967939</v>
+      </c>
+      <c r="I10" s="133">
+        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
+        <v>123463.52232702571</v>
+      </c>
+      <c r="J10" s="133">
+        <f t="shared" si="1"/>
+        <v>147704.41279253969</v>
+      </c>
+      <c r="K10" s="133">
+        <f t="shared" si="1"/>
+        <v>176704.77196172933</v>
+      </c>
+      <c r="L10" s="133">
+        <f t="shared" si="1"/>
+        <v>211399.07632890897</v>
+      </c>
+      <c r="N10" s="91"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" s="130"/>
+      <c r="D11" s="130"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="150"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="130"/>
+      <c r="J11" s="130"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="133">
+        <f>L8/(1+C21)^L9</f>
+        <v>3095222.3632804621</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B14" s="213" t="s">
+        <v>334</v>
+      </c>
+      <c r="C14" s="214"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B15" s="193" t="s">
+        <v>335</v>
+      </c>
+      <c r="C15" s="194">
+        <f>Overview!C3</f>
+        <v>270.70999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B16" s="193" t="s">
+        <v>336</v>
+      </c>
+      <c r="C16" s="194">
+        <f>C36</f>
+        <v>266.46557692121416</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="195" t="s">
+        <v>337</v>
+      </c>
+      <c r="C17" s="196">
+        <v>0.31</v>
+      </c>
+      <c r="E17" s="215" t="s">
+        <v>338</v>
+      </c>
+      <c r="F17" s="215"/>
+      <c r="G17" s="215"/>
+      <c r="H17" s="215"/>
+      <c r="I17" s="215"/>
+    </row>
+    <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B19" s="213" t="s">
+        <v>181</v>
+      </c>
+      <c r="C19" s="214"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B20" s="197" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="198">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B21" s="197" t="s">
+        <v>156</v>
+      </c>
+      <c r="C21" s="199">
+        <f>WACC!C20</f>
+        <v>9.5005973014319955E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B22" s="197" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="200">
+        <f>'Statement Q'!N100</f>
+        <v>14681</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B23" s="197" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="200">
+        <f>C15*C22</f>
+        <v>3974293.51</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B24" s="197" t="s">
+        <v>150</v>
+      </c>
+      <c r="C24" s="200">
+        <f>Statements!W21+Statements!W27</f>
+        <v>144795</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B25" s="197" t="s">
+        <v>146</v>
+      </c>
+      <c r="C25" s="200">
+        <f>Statements!W35+Statements!W36+Statements!W38</f>
+        <v>90509</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="195" t="s">
+        <v>339</v>
+      </c>
+      <c r="C26" s="201">
+        <f>C23+C25-C24</f>
+        <v>3920007.51</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B28" s="213" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" s="214"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B29" s="197" t="s">
+        <v>179</v>
+      </c>
+      <c r="C29" s="200">
+        <f>SUM(H10:L10)</f>
+        <v>762472.77149988315</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B30" s="197" t="s">
+        <v>173</v>
+      </c>
+      <c r="C30" s="200">
+        <f>L11</f>
+        <v>3095222.3632804621</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B31" s="202" t="s">
+        <v>176</v>
+      </c>
+      <c r="C31" s="203">
+        <f>C29+C30</f>
+        <v>3857695.1347803455</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B32" s="197" t="s">
+        <v>174</v>
+      </c>
+      <c r="C32" s="204">
+        <f>Statements!W21+Statements!W27</f>
+        <v>144795</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B33" s="197" t="s">
+        <v>175</v>
+      </c>
+      <c r="C33" s="204">
+        <f>Statements!W35+Statements!W36+Statements!W38</f>
+        <v>90509</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B34" s="202" t="s">
+        <v>177</v>
+      </c>
+      <c r="C34" s="203">
+        <f>C31+C32-C33</f>
+        <v>3911981.1347803455</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B35" s="197" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="200">
+        <f>C22</f>
+        <v>14681</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="205" t="s">
+        <v>178</v>
+      </c>
+      <c r="C36" s="206">
+        <f>C34/C35</f>
+        <v>266.46557692121416</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C39" s="212" t="s">
+        <v>340</v>
+      </c>
+      <c r="D39" s="212"/>
+      <c r="E39" s="212"/>
+      <c r="F39" s="212"/>
+      <c r="G39" s="212"/>
+      <c r="H39" s="212"/>
+      <c r="I39" s="212"/>
+      <c r="J39" s="212"/>
+      <c r="K39" s="212"/>
+      <c r="L39" s="212"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C40" s="62">
+        <f>C6</f>
+        <v>2021</v>
+      </c>
+      <c r="D40" s="62">
+        <f t="shared" ref="D40:L40" si="2">D6</f>
+        <v>2022</v>
+      </c>
+      <c r="E40" s="62">
+        <f t="shared" si="2"/>
+        <v>2023</v>
+      </c>
+      <c r="F40" s="62">
+        <f t="shared" si="2"/>
+        <v>2024</v>
+      </c>
+      <c r="G40" s="62">
+        <f t="shared" si="2"/>
+        <v>2025</v>
+      </c>
+      <c r="H40" s="62">
+        <f t="shared" si="2"/>
+        <v>2026</v>
+      </c>
+      <c r="I40" s="62">
+        <f t="shared" si="2"/>
+        <v>2027</v>
+      </c>
+      <c r="J40" s="62">
+        <f t="shared" si="2"/>
+        <v>2028</v>
+      </c>
+      <c r="K40" s="62">
+        <f t="shared" si="2"/>
+        <v>2029</v>
+      </c>
+      <c r="L40" s="62">
+        <f t="shared" si="2"/>
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B41" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" s="132">
+        <f>C7</f>
+        <v>89744.319832977737</v>
+      </c>
+      <c r="D41" s="132">
+        <f t="shared" ref="D41:L41" si="3">D7</f>
+        <v>101678.87709797402</v>
+      </c>
+      <c r="E41" s="132">
+        <f t="shared" si="3"/>
+        <v>91459.836665611598</v>
+      </c>
+      <c r="F41" s="132">
+        <f t="shared" si="3"/>
+        <v>99180.80528809168</v>
+      </c>
+      <c r="G41" s="134">
+        <f t="shared" si="3"/>
+        <v>86263.891892502768</v>
+      </c>
+      <c r="H41" s="174">
+        <f t="shared" si="3"/>
+        <v>113005.69837917863</v>
+      </c>
+      <c r="I41" s="174">
+        <f t="shared" si="3"/>
+        <v>148037.46487672403</v>
+      </c>
+      <c r="J41" s="174">
+        <f t="shared" si="3"/>
+        <v>193929.0789885085</v>
+      </c>
+      <c r="K41" s="174">
+        <f t="shared" si="3"/>
+        <v>254047.09347494613</v>
+      </c>
+      <c r="L41" s="174">
+        <f t="shared" si="3"/>
+        <v>332801.69245217944</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B42" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42" s="132">
+        <f>'FCF &amp; Other'!C12</f>
+        <v>108949</v>
+      </c>
+      <c r="D42" s="132">
+        <f>'FCF &amp; Other'!D12</f>
+        <v>119437</v>
+      </c>
+      <c r="E42" s="132">
+        <f>'FCF &amp; Other'!E12</f>
+        <v>114301</v>
+      </c>
+      <c r="F42" s="132">
+        <f>'FCF &amp; Other'!F12</f>
+        <v>123216</v>
+      </c>
+      <c r="G42" s="134">
+        <f>'FCF &amp; Other'!G12</f>
+        <v>133050</v>
+      </c>
+      <c r="H42" s="174">
+        <f>H41/H43</f>
+        <v>141257.12297397328</v>
+      </c>
+      <c r="I42" s="174">
+        <f t="shared" ref="I42:L42" si="4">I41/I43</f>
+        <v>185046.83109590501</v>
+      </c>
+      <c r="J42" s="174">
+        <f t="shared" si="4"/>
+        <v>242411.34873563561</v>
+      </c>
+      <c r="K42" s="174">
+        <f t="shared" si="4"/>
+        <v>317558.86684368266</v>
+      </c>
+      <c r="L42" s="174">
+        <f t="shared" si="4"/>
+        <v>416002.11556522426</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B43" s="181" t="s">
+        <v>341</v>
+      </c>
+      <c r="C43" s="111">
+        <f>C41/C42</f>
+        <v>0.82372779771248694</v>
+      </c>
+      <c r="D43" s="111">
+        <f t="shared" ref="D43:G43" si="5">D41/D42</f>
+        <v>0.85131807645850133</v>
+      </c>
+      <c r="E43" s="111">
+        <f t="shared" si="5"/>
+        <v>0.8001665485482331</v>
+      </c>
+      <c r="F43" s="111">
+        <f t="shared" si="5"/>
+        <v>0.80493446701801452</v>
+      </c>
+      <c r="G43" s="112">
+        <f t="shared" si="5"/>
+        <v>0.64835694770764951</v>
+      </c>
+      <c r="H43" s="173">
+        <v>0.8</v>
+      </c>
+      <c r="I43" s="173">
+        <v>0.8</v>
+      </c>
+      <c r="J43" s="173">
+        <v>0.8</v>
+      </c>
+      <c r="K43" s="173">
+        <v>0.8</v>
+      </c>
+      <c r="L43" s="173">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="132">
+        <f>'FCF &amp; Other'!C6</f>
+        <v>365817</v>
+      </c>
+      <c r="D44" s="132">
+        <f>'FCF &amp; Other'!D6</f>
+        <v>394328</v>
+      </c>
+      <c r="E44" s="132">
+        <f>'FCF &amp; Other'!E6</f>
+        <v>383285</v>
+      </c>
+      <c r="F44" s="132">
+        <f>'FCF &amp; Other'!F6</f>
+        <v>391035</v>
+      </c>
+      <c r="G44" s="134">
+        <f>'FCF &amp; Other'!G6</f>
+        <v>416161</v>
+      </c>
+      <c r="H44" s="174">
+        <f>H41/H45</f>
+        <v>491329.12338773318</v>
+      </c>
+      <c r="I44" s="174">
+        <f t="shared" ref="I44:L44" si="6">I41/I45</f>
+        <v>643641.15163793054</v>
+      </c>
+      <c r="J44" s="174">
+        <f t="shared" si="6"/>
+        <v>843169.90864568902</v>
+      </c>
+      <c r="K44" s="174">
+        <f t="shared" si="6"/>
+        <v>1104552.5803258526</v>
+      </c>
+      <c r="L44" s="174">
+        <f t="shared" si="6"/>
+        <v>1446963.880226867</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B45" s="181" t="s">
+        <v>342</v>
+      </c>
+      <c r="C45" s="111">
+        <f>C41/C44</f>
+        <v>0.24532572251420173</v>
+      </c>
+      <c r="D45" s="111">
+        <f t="shared" ref="D45:G45" si="7">D41/D44</f>
+        <v>0.25785355617144617</v>
+      </c>
+      <c r="E45" s="111">
+        <f t="shared" si="7"/>
+        <v>0.23862096524938778</v>
+      </c>
+      <c r="F45" s="111">
+        <f t="shared" si="7"/>
+        <v>0.25363664451543133</v>
+      </c>
+      <c r="G45" s="112">
+        <f t="shared" si="7"/>
+        <v>0.20728490149846518</v>
+      </c>
+      <c r="H45" s="173">
+        <v>0.23</v>
+      </c>
+      <c r="I45" s="173">
+        <v>0.23</v>
+      </c>
+      <c r="J45" s="173">
+        <v>0.23</v>
+      </c>
+      <c r="K45" s="173">
+        <v>0.23</v>
+      </c>
+      <c r="L45" s="173">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B46" s="181" t="s">
+        <v>343</v>
+      </c>
+      <c r="C46" s="130"/>
+      <c r="D46" s="111">
+        <f>D41/C41-1</f>
+        <v>0.13298398480491658</v>
+      </c>
+      <c r="E46" s="111">
+        <f t="shared" ref="E46:L46" si="8">E41/D41-1</f>
+        <v>-0.1005030811120754</v>
+      </c>
+      <c r="F46" s="111">
+        <f t="shared" si="8"/>
+        <v>8.4419226011838377E-2</v>
+      </c>
+      <c r="G46" s="112">
+        <f t="shared" si="8"/>
+        <v>-0.13023602054922823</v>
+      </c>
+      <c r="H46" s="207">
+        <f t="shared" si="8"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="I46" s="207">
+        <f t="shared" si="8"/>
+        <v>0.31000000000000028</v>
+      </c>
+      <c r="J46" s="207">
+        <f t="shared" si="8"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="K46" s="207">
+        <f t="shared" si="8"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="L46" s="207">
+        <f t="shared" si="8"/>
+        <v>0.31000000000000005</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B47" s="181" t="s">
+        <v>344</v>
+      </c>
+      <c r="C47" s="130"/>
+      <c r="D47" s="111">
+        <f>D42/C42-1</f>
+        <v>9.6265225013538513E-2</v>
+      </c>
+      <c r="E47" s="111">
+        <f t="shared" ref="E47:L47" si="9">E42/D42-1</f>
+        <v>-4.3001749876503959E-2</v>
+      </c>
+      <c r="F47" s="111">
+        <f t="shared" si="9"/>
+        <v>7.7995818059334532E-2</v>
+      </c>
+      <c r="G47" s="112">
+        <f t="shared" si="9"/>
+        <v>7.9811063498246959E-2</v>
+      </c>
+      <c r="H47" s="207">
+        <f t="shared" si="9"/>
+        <v>6.1684501871276165E-2</v>
+      </c>
+      <c r="I47" s="207">
+        <f t="shared" si="9"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="J47" s="207">
+        <f t="shared" si="9"/>
+        <v>0.31000000000000028</v>
+      </c>
+      <c r="K47" s="207">
+        <f t="shared" si="9"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="L47" s="207">
+        <f t="shared" si="9"/>
+        <v>0.30999999999999983</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B48" s="181" t="s">
+        <v>345</v>
+      </c>
+      <c r="C48" s="130"/>
+      <c r="D48" s="111">
+        <f>D44/C44-1</f>
+        <v>7.7937876041846099E-2</v>
+      </c>
+      <c r="E48" s="111">
+        <f t="shared" ref="E48:L48" si="10">E44/D44-1</f>
+        <v>-2.800460530319937E-2</v>
+      </c>
+      <c r="F48" s="111">
+        <f t="shared" si="10"/>
+        <v>2.021994077514111E-2</v>
+      </c>
+      <c r="G48" s="112">
+        <f t="shared" si="10"/>
+        <v>6.425511782832749E-2</v>
+      </c>
+      <c r="H48" s="207">
+        <f t="shared" si="10"/>
+        <v>0.1806226998390843</v>
+      </c>
+      <c r="I48" s="207">
+        <f t="shared" si="10"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="J48" s="207">
+        <f t="shared" si="10"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="K48" s="207">
+        <f t="shared" si="10"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="L48" s="207">
+        <f t="shared" si="10"/>
+        <v>0.31000000000000005</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B49" s="181" t="s">
+        <v>348</v>
+      </c>
+      <c r="C49" s="111">
+        <f>C42/C44</f>
+        <v>0.29782377527561593</v>
+      </c>
+      <c r="D49" s="111">
+        <f t="shared" ref="D49:L49" si="11">D42/D44</f>
+        <v>0.30288744395528594</v>
+      </c>
+      <c r="E49" s="111">
+        <f t="shared" si="11"/>
+        <v>0.29821412265024722</v>
+      </c>
+      <c r="F49" s="111">
+        <f t="shared" si="11"/>
+        <v>0.31510222870075566</v>
+      </c>
+      <c r="G49" s="112">
+        <f t="shared" si="11"/>
+        <v>0.31970799762591884</v>
+      </c>
+      <c r="H49" s="207">
+        <f t="shared" si="11"/>
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="I49" s="207">
+        <f t="shared" si="11"/>
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="J49" s="207">
+        <f t="shared" si="11"/>
+        <v>0.28750000000000003</v>
+      </c>
+      <c r="K49" s="207">
+        <f t="shared" si="11"/>
+        <v>0.28750000000000003</v>
+      </c>
+      <c r="L49" s="207">
+        <f t="shared" si="11"/>
+        <v>0.28749999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12123,11 +13286,11 @@
         <v>75</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="193" t="s">
+      <c r="P4" s="216" t="s">
         <v>76</v>
       </c>
-      <c r="Q4" s="194"/>
-      <c r="R4" s="195"/>
+      <c r="Q4" s="217"/>
+      <c r="R4" s="218"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -22135,36 +23298,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="196" t="s">
+      <c r="C2" s="208" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="196"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="199"/>
-      <c r="H2" s="200" t="s">
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="209"/>
+      <c r="H2" s="210" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="196"/>
-      <c r="J2" s="196"/>
-      <c r="K2" s="196"/>
-      <c r="L2" s="196"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
       <c r="O2" s="90"/>
-      <c r="S2" s="196" t="s">
+      <c r="S2" s="208" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="196"/>
-      <c r="U2" s="196"/>
-      <c r="V2" s="196"/>
-      <c r="W2" s="196"/>
-      <c r="X2" s="196"/>
-      <c r="Y2" s="196"/>
-      <c r="Z2" s="196"/>
-      <c r="AA2" s="196" t="s">
+      <c r="T2" s="208"/>
+      <c r="U2" s="208"/>
+      <c r="V2" s="208"/>
+      <c r="W2" s="208"/>
+      <c r="X2" s="208"/>
+      <c r="Y2" s="208"/>
+      <c r="Z2" s="208"/>
+      <c r="AA2" s="208" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="196"/>
-      <c r="AC2" s="196"/>
+      <c r="AB2" s="208"/>
+      <c r="AC2" s="208"/>
       <c r="AE2" s="117" t="s">
         <v>75</v>
       </c>
@@ -22175,32 +23338,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="201" t="s">
+      <c r="C4" s="212" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="201"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="201"/>
-      <c r="G4" s="201"/>
-      <c r="H4" s="201"/>
-      <c r="I4" s="201"/>
-      <c r="J4" s="201"/>
-      <c r="K4" s="201"/>
-      <c r="L4" s="201"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="212"/>
+      <c r="H4" s="212"/>
+      <c r="I4" s="212"/>
+      <c r="J4" s="212"/>
+      <c r="K4" s="212"/>
+      <c r="L4" s="212"/>
       <c r="O4" s="90"/>
-      <c r="S4" s="197" t="s">
+      <c r="S4" s="219" t="s">
         <v>114</v>
       </c>
-      <c r="T4" s="198"/>
-      <c r="U4" s="198"/>
-      <c r="V4" s="198"/>
-      <c r="W4" s="198"/>
-      <c r="X4" s="198"/>
-      <c r="Y4" s="198"/>
-      <c r="Z4" s="198"/>
-      <c r="AA4" s="198"/>
-      <c r="AB4" s="198"/>
-      <c r="AC4" s="198"/>
+      <c r="T4" s="220"/>
+      <c r="U4" s="220"/>
+      <c r="V4" s="220"/>
+      <c r="W4" s="220"/>
+      <c r="X4" s="220"/>
+      <c r="Y4" s="220"/>
+      <c r="Z4" s="220"/>
+      <c r="AA4" s="220"/>
+      <c r="AB4" s="220"/>
+      <c r="AC4" s="220"/>
       <c r="AE4" s="119" t="s">
         <v>121</v>
       </c>
@@ -22325,23 +23488,23 @@
       </c>
       <c r="H6" s="104">
         <f>G6*(1+H15)</f>
-        <v>215873.58000000002</v>
+        <v>219017.37</v>
       </c>
       <c r="I6" s="104">
         <f t="shared" ref="I6:L6" si="1">H6*(1+I15)</f>
-        <v>222349.78740000003</v>
+        <v>228435.11690999998</v>
       </c>
       <c r="J6" s="104">
         <f t="shared" si="1"/>
-        <v>229020.28102200004</v>
+        <v>238029.39182021999</v>
       </c>
       <c r="K6" s="104">
         <f t="shared" si="1"/>
-        <v>235890.88945266005</v>
+        <v>248740.71445212988</v>
       </c>
       <c r="L6" s="104">
         <f t="shared" si="1"/>
-        <v>242967.61613623987</v>
+        <v>259934.04660247569</v>
       </c>
       <c r="N6" s="115"/>
       <c r="O6" s="90"/>
@@ -22420,23 +23583,23 @@
       </c>
       <c r="H7" s="104">
         <f>G7*(1+H16)</f>
-        <v>34382.160000000003</v>
+        <v>38764.199999999997</v>
       </c>
       <c r="I7" s="104">
         <f t="shared" ref="I7:L7" si="2">H7*(1+I16)</f>
-        <v>35069.803200000002</v>
+        <v>40702.409999999996</v>
       </c>
       <c r="J7" s="104">
         <f t="shared" si="2"/>
-        <v>35771.199264000003</v>
+        <v>44772.650999999998</v>
       </c>
       <c r="K7" s="104">
         <f t="shared" si="2"/>
-        <v>36486.623249280005</v>
+        <v>46115.830529999999</v>
       </c>
       <c r="L7" s="104">
         <f t="shared" si="2"/>
-        <v>37216.355714265606</v>
+        <v>50266.255277700002</v>
       </c>
       <c r="N7" s="115"/>
       <c r="O7" s="90"/>
@@ -22705,23 +23868,23 @@
       </c>
       <c r="H10" s="104">
         <f t="shared" ref="H10:L10" si="6">G10*(1+H19)</f>
-        <v>120073.8</v>
+        <v>125531.7</v>
       </c>
       <c r="I10" s="104">
         <f t="shared" si="6"/>
-        <v>132081.18000000002</v>
+        <v>141850.821</v>
       </c>
       <c r="J10" s="104">
         <f t="shared" si="6"/>
-        <v>145289.29800000004</v>
+        <v>158872.91952000002</v>
       </c>
       <c r="K10" s="104">
         <f t="shared" si="6"/>
-        <v>159818.22780000005</v>
+        <v>182703.85744800002</v>
       </c>
       <c r="L10" s="104">
         <f t="shared" si="6"/>
-        <v>175800.05058000007</v>
+        <v>208282.39749072006</v>
       </c>
       <c r="N10" s="115"/>
       <c r="O10" s="90"/>
@@ -22799,23 +23962,23 @@
       </c>
       <c r="H11" s="109">
         <f>SUM(H6:H10)</f>
-        <v>434357.08500000002</v>
+        <v>447340.815</v>
       </c>
       <c r="I11" s="109">
         <f t="shared" ref="I11:L11" si="7">SUM(I6:I10)</f>
-        <v>453848.45332500001</v>
+        <v>475336.03063499997</v>
       </c>
       <c r="J11" s="109">
         <f t="shared" si="7"/>
-        <v>474750.19942462503</v>
+        <v>506344.383478845</v>
       </c>
       <c r="K11" s="109">
         <f t="shared" si="7"/>
-        <v>497188.50874625816</v>
+        <v>542553.17067444802</v>
       </c>
       <c r="L11" s="109">
         <f t="shared" si="7"/>
-        <v>521301.75451604521</v>
+        <v>583800.43145643547</v>
       </c>
       <c r="O11" s="90"/>
       <c r="Q11" s="91"/>
@@ -22876,33 +24039,33 @@
       <c r="Q12" s="91"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="201" t="s">
+      <c r="C13" s="212" t="s">
         <v>116</v>
       </c>
-      <c r="D13" s="201"/>
-      <c r="E13" s="201"/>
-      <c r="F13" s="201"/>
-      <c r="G13" s="201"/>
-      <c r="H13" s="201"/>
-      <c r="I13" s="201"/>
-      <c r="J13" s="201"/>
-      <c r="K13" s="201"/>
-      <c r="L13" s="201"/>
+      <c r="D13" s="212"/>
+      <c r="E13" s="212"/>
+      <c r="F13" s="212"/>
+      <c r="G13" s="212"/>
+      <c r="H13" s="212"/>
+      <c r="I13" s="212"/>
+      <c r="J13" s="212"/>
+      <c r="K13" s="212"/>
+      <c r="L13" s="212"/>
       <c r="O13" s="90"/>
       <c r="Q13" s="91"/>
-      <c r="S13" s="197" t="s">
+      <c r="S13" s="219" t="s">
         <v>116</v>
       </c>
-      <c r="T13" s="198"/>
-      <c r="U13" s="198"/>
-      <c r="V13" s="198"/>
-      <c r="W13" s="198"/>
-      <c r="X13" s="198"/>
-      <c r="Y13" s="198"/>
-      <c r="Z13" s="198"/>
-      <c r="AA13" s="198"/>
-      <c r="AB13" s="198"/>
-      <c r="AC13" s="198"/>
+      <c r="T13" s="220"/>
+      <c r="U13" s="220"/>
+      <c r="V13" s="220"/>
+      <c r="W13" s="220"/>
+      <c r="X13" s="220"/>
+      <c r="Y13" s="220"/>
+      <c r="Z13" s="220"/>
+      <c r="AA13" s="220"/>
+      <c r="AB13" s="220"/>
+      <c r="AC13" s="220"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
@@ -23005,7 +24168,7 @@
       </c>
       <c r="C15" s="81"/>
       <c r="D15" s="111">
-        <f t="shared" ref="D15:G20" si="10">D6/C6-1</f>
+        <f t="shared" ref="D15:H20" si="10">D6/C6-1</f>
         <v>7.0405734139696641E-2</v>
       </c>
       <c r="E15" s="111">
@@ -23021,19 +24184,19 @@
         <v>4.1767942619406195E-2</v>
       </c>
       <c r="H15" s="113">
-        <v>0.03</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="I15" s="113">
-        <v>0.03</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="J15" s="113">
-        <v>0.03</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="K15" s="113">
-        <v>0.03</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="L15" s="113">
-        <v>0.03</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="O15" s="90"/>
       <c r="Q15" s="91"/>
@@ -23100,19 +24263,19 @@
         <v>0.12419957310565644</v>
       </c>
       <c r="H16" s="113">
-        <v>0.02</v>
+        <v>0.15</v>
       </c>
       <c r="I16" s="113">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="J16" s="113">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="K16" s="113">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="L16" s="113">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="O16" s="90"/>
       <c r="Q16" s="91"/>
@@ -23337,19 +24500,19 @@
         <v>0.13506431386413498</v>
       </c>
       <c r="H19" s="113">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I19" s="113">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="J19" s="113">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="K19" s="113">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="L19" s="113">
-        <v>0.1</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="O19" s="90"/>
       <c r="Q19" s="91"/>
@@ -23415,24 +24578,24 @@
         <v>6.425511782832749E-2</v>
       </c>
       <c r="H20" s="179">
-        <f t="shared" ref="H20:L20" si="12">H11/G11-1</f>
-        <v>4.3723667042322667E-2</v>
+        <f t="shared" si="10"/>
+        <v>7.4922481924063034E-2</v>
       </c>
       <c r="I20" s="179">
-        <f t="shared" si="12"/>
-        <v>4.4874065597433566E-2</v>
+        <f t="shared" ref="I20" si="12">I11/H11-1</f>
+        <v>6.2581402582279511E-2</v>
       </c>
       <c r="J20" s="179">
-        <f t="shared" si="12"/>
-        <v>4.6054461454024809E-2</v>
+        <f t="shared" ref="J20" si="13">J11/I11-1</f>
+        <v>6.5234593730294499E-2</v>
       </c>
       <c r="K20" s="179">
-        <f t="shared" si="12"/>
-        <v>4.7263401571662866E-2</v>
+        <f t="shared" ref="K20" si="14">K11/J11-1</f>
+        <v>7.1510198151760074E-2</v>
       </c>
       <c r="L20" s="179">
-        <f t="shared" si="12"/>
-        <v>4.849920170237354E-2</v>
+        <f t="shared" ref="L20" si="15">L11/K11-1</f>
+        <v>7.6024365926592896E-2</v>
       </c>
       <c r="O20" s="90"/>
       <c r="Q20" s="91"/>
@@ -23484,35 +24647,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="196" t="s">
+      <c r="C2" s="208" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="196"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="199"/>
-      <c r="H2" s="200" t="s">
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="209"/>
+      <c r="H2" s="210" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="196"/>
-      <c r="J2" s="196"/>
-      <c r="K2" s="196"/>
-      <c r="L2" s="196"/>
-      <c r="P2" s="196" t="s">
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
+      <c r="P2" s="208" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="196"/>
-      <c r="R2" s="196"/>
-      <c r="S2" s="196"/>
-      <c r="T2" s="196"/>
-      <c r="U2" s="196"/>
-      <c r="V2" s="196"/>
-      <c r="W2" s="196"/>
-      <c r="X2" s="196" t="s">
+      <c r="Q2" s="208"/>
+      <c r="R2" s="208"/>
+      <c r="S2" s="208"/>
+      <c r="T2" s="208"/>
+      <c r="U2" s="208"/>
+      <c r="V2" s="208"/>
+      <c r="W2" s="208"/>
+      <c r="X2" s="208" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="196"/>
-      <c r="Z2" s="196"/>
+      <c r="Y2" s="208"/>
+      <c r="Z2" s="208"/>
       <c r="AB2" s="117" t="s">
         <v>75</v>
       </c>
@@ -23521,31 +24684,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="201" t="s">
+      <c r="C4" s="212" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="201"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="201"/>
-      <c r="G4" s="201"/>
-      <c r="H4" s="201"/>
-      <c r="I4" s="201"/>
-      <c r="J4" s="201"/>
-      <c r="K4" s="201"/>
-      <c r="L4" s="201"/>
-      <c r="P4" s="198" t="s">
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="212"/>
+      <c r="H4" s="212"/>
+      <c r="I4" s="212"/>
+      <c r="J4" s="212"/>
+      <c r="K4" s="212"/>
+      <c r="L4" s="212"/>
+      <c r="P4" s="220" t="s">
         <v>114</v>
       </c>
-      <c r="Q4" s="198"/>
-      <c r="R4" s="198"/>
-      <c r="S4" s="198"/>
-      <c r="T4" s="198"/>
-      <c r="U4" s="198"/>
-      <c r="V4" s="198"/>
-      <c r="W4" s="198"/>
-      <c r="X4" s="198"/>
-      <c r="Y4" s="198"/>
-      <c r="Z4" s="198"/>
+      <c r="Q4" s="220"/>
+      <c r="R4" s="220"/>
+      <c r="S4" s="220"/>
+      <c r="T4" s="220"/>
+      <c r="U4" s="220"/>
+      <c r="V4" s="220"/>
+      <c r="W4" s="220"/>
+      <c r="X4" s="220"/>
+      <c r="Y4" s="220"/>
+      <c r="Z4" s="220"/>
       <c r="AB4" s="119" t="s">
         <v>121</v>
       </c>
@@ -23668,23 +24831,23 @@
       </c>
       <c r="H6" s="107">
         <f>Revenue!H11</f>
-        <v>434357.08500000002</v>
+        <v>447340.815</v>
       </c>
       <c r="I6" s="107">
         <f>Revenue!I11</f>
-        <v>453848.45332500001</v>
+        <v>475336.03063499997</v>
       </c>
       <c r="J6" s="107">
         <f>Revenue!J11</f>
-        <v>474750.19942462503</v>
+        <v>506344.383478845</v>
       </c>
       <c r="K6" s="107">
         <f>Revenue!K11</f>
-        <v>497188.50874625816</v>
+        <v>542553.17067444802</v>
       </c>
       <c r="L6" s="107">
         <f>Revenue!L11</f>
-        <v>521301.75451604521</v>
+        <v>583800.43145643547</v>
       </c>
       <c r="N6" s="91"/>
       <c r="O6" s="7" t="s">
@@ -23746,32 +24909,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="201" t="s">
+      <c r="C9" s="212" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="201"/>
-      <c r="E9" s="201"/>
-      <c r="F9" s="201"/>
-      <c r="G9" s="201"/>
-      <c r="H9" s="201"/>
-      <c r="I9" s="201"/>
-      <c r="J9" s="201"/>
-      <c r="K9" s="201"/>
-      <c r="L9" s="201"/>
+      <c r="D9" s="212"/>
+      <c r="E9" s="212"/>
+      <c r="F9" s="212"/>
+      <c r="G9" s="212"/>
+      <c r="H9" s="212"/>
+      <c r="I9" s="212"/>
+      <c r="J9" s="212"/>
+      <c r="K9" s="212"/>
+      <c r="L9" s="212"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="198" t="s">
+      <c r="P9" s="220" t="s">
         <v>128</v>
       </c>
-      <c r="Q9" s="198"/>
-      <c r="R9" s="198"/>
-      <c r="S9" s="198"/>
-      <c r="T9" s="198"/>
-      <c r="U9" s="198"/>
-      <c r="V9" s="198"/>
-      <c r="W9" s="198"/>
-      <c r="X9" s="198"/>
-      <c r="Y9" s="198"/>
-      <c r="Z9" s="198"/>
+      <c r="Q9" s="220"/>
+      <c r="R9" s="220"/>
+      <c r="S9" s="220"/>
+      <c r="T9" s="220"/>
+      <c r="U9" s="220"/>
+      <c r="V9" s="220"/>
+      <c r="W9" s="220"/>
+      <c r="X9" s="220"/>
+      <c r="Y9" s="220"/>
+      <c r="Z9" s="220"/>
       <c r="AB9" s="119" t="str">
         <f>AB4</f>
         <v>Q1-Q2-Q3</v>
@@ -23900,23 +25063,23 @@
       </c>
       <c r="H11" s="21">
         <f t="shared" ref="H11:L13" si="3">H19*H$6</f>
-        <v>229340.54088000002</v>
+        <v>236195.95032</v>
       </c>
       <c r="I11" s="21">
         <f t="shared" si="3"/>
-        <v>238270.43799562502</v>
+        <v>249551.41608337499</v>
       </c>
       <c r="J11" s="21">
         <f t="shared" si="3"/>
-        <v>247344.85390022965</v>
+        <v>263805.42379247828</v>
       </c>
       <c r="K11" s="21">
         <f t="shared" si="3"/>
-        <v>258538.02454805427</v>
+        <v>282127.64875071298</v>
       </c>
       <c r="L11" s="21">
         <f t="shared" si="3"/>
-        <v>268470.40357576328</v>
+        <v>300657.22220006428</v>
       </c>
       <c r="N11" s="91"/>
       <c r="O11" s="7" t="s">
@@ -23991,23 +25154,23 @@
       </c>
       <c r="H12" s="20">
         <f t="shared" si="3"/>
-        <v>38223.423479999998</v>
+        <v>39365.991719999998</v>
       </c>
       <c r="I12" s="20">
         <f t="shared" si="3"/>
-        <v>41754.057705899999</v>
+        <v>43730.914818419995</v>
       </c>
       <c r="J12" s="20">
         <f t="shared" si="3"/>
-        <v>45101.268945339376</v>
+        <v>48102.716430490276</v>
       </c>
       <c r="K12" s="20">
         <f t="shared" si="3"/>
-        <v>49718.850874625816</v>
+        <v>54255.317067444805</v>
       </c>
       <c r="L12" s="20">
         <f t="shared" si="3"/>
-        <v>52130.175451604526</v>
+        <v>58380.043145643547</v>
       </c>
       <c r="N12" s="91"/>
       <c r="O12" s="1" t="s">
@@ -24082,23 +25245,23 @@
       </c>
       <c r="H13" s="20">
         <f t="shared" si="3"/>
-        <v>29536.281780000005</v>
+        <v>30419.175420000003</v>
       </c>
       <c r="I13" s="20">
         <f t="shared" si="3"/>
-        <v>30407.846372775002</v>
+        <v>31847.514052545001</v>
       </c>
       <c r="J13" s="20">
         <f t="shared" si="3"/>
-        <v>32757.763760299131</v>
+        <v>34937.762460040307</v>
       </c>
       <c r="K13" s="20">
         <f t="shared" si="3"/>
-        <v>34803.195612238072</v>
+        <v>37978.721947211365</v>
       </c>
       <c r="L13" s="20">
         <f t="shared" si="3"/>
-        <v>35448.519307091075</v>
+        <v>39698.429339037611</v>
       </c>
       <c r="M13" s="115"/>
       <c r="N13" s="115"/>
@@ -24174,23 +25337,23 @@
       </c>
       <c r="H14" s="21">
         <f>SUM(H12:H13)</f>
-        <v>67759.705260000002</v>
+        <v>69785.167140000005</v>
       </c>
       <c r="I14" s="21">
         <f>SUM(I12:I13)</f>
-        <v>72161.904078674997</v>
+        <v>75578.428870964999</v>
       </c>
       <c r="J14" s="21">
         <f>SUM(J12:J13)</f>
-        <v>77859.032705638499</v>
+        <v>83040.47889053059</v>
       </c>
       <c r="K14" s="21">
         <f>SUM(K12:K13)</f>
-        <v>84522.046486863896</v>
+        <v>92234.039014656169</v>
       </c>
       <c r="L14" s="21">
         <f>SUM(L12:L13)</f>
-        <v>87578.694758695608</v>
+        <v>98078.472484681159</v>
       </c>
       <c r="M14" s="115"/>
       <c r="N14" s="115"/>
@@ -24241,31 +25404,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="201" t="s">
+      <c r="C17" s="212" t="s">
         <v>126</v>
       </c>
-      <c r="D17" s="201"/>
-      <c r="E17" s="201"/>
-      <c r="F17" s="201"/>
-      <c r="G17" s="201"/>
-      <c r="H17" s="201"/>
-      <c r="I17" s="201"/>
-      <c r="J17" s="201"/>
-      <c r="K17" s="201"/>
-      <c r="L17" s="201"/>
-      <c r="P17" s="198" t="s">
+      <c r="D17" s="212"/>
+      <c r="E17" s="212"/>
+      <c r="F17" s="212"/>
+      <c r="G17" s="212"/>
+      <c r="H17" s="212"/>
+      <c r="I17" s="212"/>
+      <c r="J17" s="212"/>
+      <c r="K17" s="212"/>
+      <c r="L17" s="212"/>
+      <c r="P17" s="220" t="s">
         <v>126</v>
       </c>
-      <c r="Q17" s="198"/>
-      <c r="R17" s="198"/>
-      <c r="S17" s="198"/>
-      <c r="T17" s="198"/>
-      <c r="U17" s="198"/>
-      <c r="V17" s="198"/>
-      <c r="W17" s="198"/>
-      <c r="X17" s="198"/>
-      <c r="Y17" s="198"/>
-      <c r="Z17" s="198"/>
+      <c r="Q17" s="220"/>
+      <c r="R17" s="220"/>
+      <c r="S17" s="220"/>
+      <c r="T17" s="220"/>
+      <c r="U17" s="220"/>
+      <c r="V17" s="220"/>
+      <c r="W17" s="220"/>
+      <c r="X17" s="220"/>
+      <c r="Y17" s="220"/>
+      <c r="Z17" s="220"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="7" t="s">
@@ -24655,60 +25818,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="196" t="s">
+      <c r="C3" s="208" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="196"/>
-      <c r="E3" s="196"/>
-      <c r="F3" s="196"/>
-      <c r="G3" s="199"/>
-      <c r="H3" s="200" t="s">
+      <c r="D3" s="208"/>
+      <c r="E3" s="208"/>
+      <c r="F3" s="208"/>
+      <c r="G3" s="209"/>
+      <c r="H3" s="210" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="196"/>
-      <c r="J3" s="196"/>
-      <c r="K3" s="196"/>
-      <c r="L3" s="196"/>
-      <c r="P3" s="202"/>
-      <c r="Q3" s="202"/>
-      <c r="R3" s="202"/>
-      <c r="S3" s="202"/>
-      <c r="T3" s="202"/>
-      <c r="U3" s="202"/>
-      <c r="V3" s="202"/>
-      <c r="W3" s="202"/>
-      <c r="X3" s="202"/>
-      <c r="Y3" s="202"/>
-      <c r="Z3" s="202"/>
+      <c r="I3" s="208"/>
+      <c r="J3" s="208"/>
+      <c r="K3" s="208"/>
+      <c r="L3" s="208"/>
+      <c r="P3" s="211"/>
+      <c r="Q3" s="211"/>
+      <c r="R3" s="211"/>
+      <c r="S3" s="211"/>
+      <c r="T3" s="211"/>
+      <c r="U3" s="211"/>
+      <c r="V3" s="211"/>
+      <c r="W3" s="211"/>
+      <c r="X3" s="211"/>
+      <c r="Y3" s="211"/>
+      <c r="Z3" s="211"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="201" t="s">
+      <c r="C5" s="212" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="201"/>
-      <c r="E5" s="201"/>
-      <c r="F5" s="201"/>
-      <c r="G5" s="201"/>
-      <c r="H5" s="201"/>
-      <c r="I5" s="201"/>
-      <c r="J5" s="201"/>
-      <c r="K5" s="201"/>
-      <c r="L5" s="201"/>
-      <c r="P5" s="202"/>
-      <c r="Q5" s="202"/>
-      <c r="R5" s="202"/>
-      <c r="S5" s="202"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="202"/>
-      <c r="W5" s="202"/>
-      <c r="X5" s="202"/>
-      <c r="Y5" s="202"/>
-      <c r="Z5" s="202"/>
+      <c r="D5" s="212"/>
+      <c r="E5" s="212"/>
+      <c r="F5" s="212"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="212"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="212"/>
+      <c r="K5" s="212"/>
+      <c r="L5" s="212"/>
+      <c r="P5" s="211"/>
+      <c r="Q5" s="211"/>
+      <c r="R5" s="211"/>
+      <c r="S5" s="211"/>
+      <c r="T5" s="211"/>
+      <c r="U5" s="211"/>
+      <c r="V5" s="211"/>
+      <c r="W5" s="211"/>
+      <c r="X5" s="211"/>
+      <c r="Y5" s="211"/>
+      <c r="Z5" s="211"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -24795,23 +25958,23 @@
       </c>
       <c r="H7" s="107">
         <f>Revenue!H11</f>
-        <v>434357.08500000002</v>
+        <v>447340.815</v>
       </c>
       <c r="I7" s="107">
         <f>Revenue!I11</f>
-        <v>453848.45332500001</v>
+        <v>475336.03063499997</v>
       </c>
       <c r="J7" s="107">
         <f>Revenue!J11</f>
-        <v>474750.19942462503</v>
+        <v>506344.383478845</v>
       </c>
       <c r="K7" s="107">
         <f>Revenue!K11</f>
-        <v>497188.50874625816</v>
+        <v>542553.17067444802</v>
       </c>
       <c r="L7" s="107">
         <f>Revenue!L11</f>
-        <v>521301.75451604521</v>
+        <v>583800.43145643547</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="7"/>
@@ -24854,23 +26017,23 @@
       </c>
       <c r="H8" s="132">
         <f>'COGS &amp; OpEx'!H11</f>
-        <v>229340.54088000002</v>
+        <v>236195.95032</v>
       </c>
       <c r="I8" s="132">
         <f>'COGS &amp; OpEx'!I11</f>
-        <v>238270.43799562502</v>
+        <v>249551.41608337499</v>
       </c>
       <c r="J8" s="132">
         <f>'COGS &amp; OpEx'!J11</f>
-        <v>247344.85390022965</v>
+        <v>263805.42379247828</v>
       </c>
       <c r="K8" s="132">
         <f>'COGS &amp; OpEx'!K11</f>
-        <v>258538.02454805427</v>
+        <v>282127.64875071298</v>
       </c>
       <c r="L8" s="132">
         <f>'COGS &amp; OpEx'!L11</f>
-        <v>268470.40357576328</v>
+        <v>300657.22220006428</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="7"/>
@@ -24894,30 +26057,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="201" t="s">
+      <c r="C11" s="212" t="s">
         <v>134</v>
       </c>
-      <c r="D11" s="201"/>
-      <c r="E11" s="201"/>
-      <c r="F11" s="201"/>
-      <c r="G11" s="201"/>
-      <c r="H11" s="201"/>
-      <c r="I11" s="201"/>
-      <c r="J11" s="201"/>
-      <c r="K11" s="201"/>
-      <c r="L11" s="201"/>
+      <c r="D11" s="212"/>
+      <c r="E11" s="212"/>
+      <c r="F11" s="212"/>
+      <c r="G11" s="212"/>
+      <c r="H11" s="212"/>
+      <c r="I11" s="212"/>
+      <c r="J11" s="212"/>
+      <c r="K11" s="212"/>
+      <c r="L11" s="212"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="202"/>
-      <c r="Q11" s="202"/>
-      <c r="R11" s="202"/>
-      <c r="S11" s="202"/>
-      <c r="T11" s="202"/>
-      <c r="U11" s="202"/>
-      <c r="V11" s="202"/>
-      <c r="W11" s="202"/>
-      <c r="X11" s="202"/>
-      <c r="Y11" s="202"/>
-      <c r="Z11" s="202"/>
+      <c r="P11" s="211"/>
+      <c r="Q11" s="211"/>
+      <c r="R11" s="211"/>
+      <c r="S11" s="211"/>
+      <c r="T11" s="211"/>
+      <c r="U11" s="211"/>
+      <c r="V11" s="211"/>
+      <c r="W11" s="211"/>
+      <c r="X11" s="211"/>
+      <c r="Y11" s="211"/>
+      <c r="Z11" s="211"/>
       <c r="AB11" s="123"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -25005,23 +26168,23 @@
       </c>
       <c r="H13" s="34">
         <f>H20*H7/365</f>
-        <v>44030.718205479454</v>
+        <v>45346.877136986303</v>
       </c>
       <c r="I13" s="34">
         <f>I20*I7/365</f>
-        <v>49736.816802739733</v>
+        <v>52091.61979561644</v>
       </c>
       <c r="J13" s="34">
         <f>J20*J7/365</f>
-        <v>55929.47554865446</v>
+        <v>59651.530108466672</v>
       </c>
       <c r="K13" s="34">
         <f>K20*K7/365</f>
-        <v>61297.213407072923</v>
+        <v>66890.116932466204</v>
       </c>
       <c r="L13" s="34">
         <f>L20*L7/365</f>
-        <v>64270.079323895989</v>
+        <v>71975.395659012589</v>
       </c>
       <c r="N13" s="91"/>
       <c r="O13" s="7"/>
@@ -25064,23 +26227,23 @@
       </c>
       <c r="H14" s="34">
         <f>H21*H8/365</f>
-        <v>6283.3024898630147</v>
+        <v>6471.1219265753425</v>
       </c>
       <c r="I14" s="34">
         <f t="shared" ref="I14:L14" si="1">I21*I8/365</f>
-        <v>7180.7529258955483</v>
+        <v>7520.727607992123</v>
       </c>
       <c r="J14" s="34">
         <f t="shared" si="1"/>
-        <v>7454.2284737055506</v>
+        <v>7950.3004430609899</v>
       </c>
       <c r="K14" s="34">
         <f t="shared" si="1"/>
-        <v>8499.8802591141139</v>
+        <v>9275.4295479686461</v>
       </c>
       <c r="L14" s="34">
         <f t="shared" si="1"/>
-        <v>8826.4242271483818</v>
+        <v>9884.6210038377303</v>
       </c>
       <c r="N14" s="91"/>
       <c r="O14" s="7"/>
@@ -25123,23 +26286,23 @@
       </c>
       <c r="H15" s="20">
         <f>H22*H8/365</f>
-        <v>74771.299629369867</v>
+        <v>77006.350926246581</v>
       </c>
       <c r="I15" s="20">
         <f>I22*I8/365</f>
-        <v>81599.465066994875</v>
+        <v>85462.813727183209</v>
       </c>
       <c r="J15" s="20">
         <f>J22*J8/365</f>
-        <v>88095.42741652015</v>
+        <v>93958.09614526623</v>
       </c>
       <c r="K15" s="20">
         <f>K22*K8/365</f>
-        <v>94915.329560107581</v>
+        <v>103575.62995231654</v>
       </c>
       <c r="L15" s="20">
         <f>L22*L8/365</f>
-        <v>98561.737203156925</v>
+        <v>110378.26787618799</v>
       </c>
       <c r="N15" s="91"/>
       <c r="P15" s="126"/>
@@ -25159,18 +26322,18 @@
       <c r="D16" s="20"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="201" t="s">
+      <c r="C18" s="212" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="201"/>
-      <c r="E18" s="201"/>
-      <c r="F18" s="201"/>
-      <c r="G18" s="201"/>
-      <c r="H18" s="201"/>
-      <c r="I18" s="201"/>
-      <c r="J18" s="201"/>
-      <c r="K18" s="201"/>
-      <c r="L18" s="201"/>
+      <c r="D18" s="212"/>
+      <c r="E18" s="212"/>
+      <c r="F18" s="212"/>
+      <c r="G18" s="212"/>
+      <c r="H18" s="212"/>
+      <c r="I18" s="212"/>
+      <c r="J18" s="212"/>
+      <c r="K18" s="212"/>
+      <c r="L18" s="212"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -25383,23 +26546,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="202"/>
-      <c r="C25" s="202"/>
+      <c r="B25" s="211"/>
+      <c r="C25" s="211"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="122"/>
-      <c r="C26" s="201" t="s">
+      <c r="C26" s="212" t="s">
         <v>302</v>
       </c>
-      <c r="D26" s="201"/>
-      <c r="E26" s="201"/>
-      <c r="F26" s="201"/>
-      <c r="G26" s="201"/>
-      <c r="H26" s="201"/>
-      <c r="I26" s="201"/>
-      <c r="J26" s="201"/>
-      <c r="K26" s="201"/>
-      <c r="L26" s="201"/>
+      <c r="D26" s="212"/>
+      <c r="E26" s="212"/>
+      <c r="F26" s="212"/>
+      <c r="G26" s="212"/>
+      <c r="H26" s="212"/>
+      <c r="I26" s="212"/>
+      <c r="J26" s="212"/>
+      <c r="K26" s="212"/>
+      <c r="L26" s="212"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
@@ -25472,23 +26635,23 @@
       </c>
       <c r="H28" s="34">
         <f>-(H13-G13)</f>
-        <v>-4253.7182054794539</v>
+        <v>-5569.8771369863025</v>
       </c>
       <c r="I28" s="34">
         <f t="shared" ref="I28:L28" si="6">-(I13-H13)</f>
-        <v>-5706.0985972602793</v>
+        <v>-6744.7426586301372</v>
       </c>
       <c r="J28" s="34">
         <f t="shared" si="6"/>
-        <v>-6192.6587459147268</v>
+        <v>-7559.910312850232</v>
       </c>
       <c r="K28" s="34">
         <f t="shared" si="6"/>
-        <v>-5367.7378584184626</v>
+        <v>-7238.5868239995325</v>
       </c>
       <c r="L28" s="34">
         <f t="shared" si="6"/>
-        <v>-2972.8659168230661</v>
+        <v>-5085.2787265463849</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
@@ -25517,23 +26680,23 @@
       </c>
       <c r="H29" s="34">
         <f>-(H14-G14)</f>
-        <v>-565.30248986301467</v>
+        <v>-753.12192657534251</v>
       </c>
       <c r="I29" s="34">
         <f t="shared" ref="I29:L29" si="7">-(I14-H14)</f>
-        <v>-897.45043603253362</v>
+        <v>-1049.6056814167805</v>
       </c>
       <c r="J29" s="34">
         <f t="shared" si="7"/>
-        <v>-273.47554781000235</v>
+        <v>-429.57283506886688</v>
       </c>
       <c r="K29" s="34">
         <f t="shared" si="7"/>
-        <v>-1045.6517854085632</v>
+        <v>-1325.1291049076563</v>
       </c>
       <c r="L29" s="34">
         <f t="shared" si="7"/>
-        <v>-326.54396803426789</v>
+        <v>-609.19145586908417</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.2">
@@ -25562,23 +26725,23 @@
       </c>
       <c r="H30" s="20">
         <f>H15-G15</f>
-        <v>4911.299629369867</v>
+        <v>7146.3509262465814</v>
       </c>
       <c r="I30" s="20">
         <f t="shared" ref="I30:L30" si="8">I15-H15</f>
-        <v>6828.1654376250081</v>
+        <v>8456.4628009366279</v>
       </c>
       <c r="J30" s="20">
         <f t="shared" si="8"/>
-        <v>6495.9623495252745</v>
+        <v>8495.2824180830212</v>
       </c>
       <c r="K30" s="20">
         <f t="shared" si="8"/>
-        <v>6819.9021435874311</v>
+        <v>9617.5338070503058</v>
       </c>
       <c r="L30" s="20">
         <f t="shared" si="8"/>
-        <v>3646.4076430493442</v>
+        <v>6802.637923871458</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
@@ -25591,18 +26754,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="122"/>
-      <c r="C33" s="201" t="s">
+      <c r="C33" s="212" t="s">
         <v>305</v>
       </c>
-      <c r="D33" s="201"/>
-      <c r="E33" s="201"/>
-      <c r="F33" s="201"/>
-      <c r="G33" s="201"/>
-      <c r="H33" s="201"/>
-      <c r="I33" s="201"/>
-      <c r="J33" s="201"/>
-      <c r="K33" s="201"/>
-      <c r="L33" s="201"/>
+      <c r="D33" s="212"/>
+      <c r="E33" s="212"/>
+      <c r="F33" s="212"/>
+      <c r="G33" s="212"/>
+      <c r="H33" s="212"/>
+      <c r="I33" s="212"/>
+      <c r="J33" s="212"/>
+      <c r="K33" s="212"/>
+      <c r="L33" s="212"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
@@ -25675,23 +26838,23 @@
       </c>
       <c r="H35" s="34">
         <f>H36+H28+H29+H30</f>
-        <v>-8594.8627659726008</v>
+        <v>-8123.4644373150641</v>
       </c>
       <c r="I35" s="34">
         <f t="shared" ref="I35:L35" si="10">I36+I28+I29+I30</f>
-        <v>-8852.3526621678047</v>
+        <v>-8844.606151810287</v>
       </c>
       <c r="J35" s="34">
         <f t="shared" si="10"/>
-        <v>-9465.1759326919564</v>
+        <v>-9621.0883994129763</v>
       </c>
       <c r="K35" s="34">
         <f t="shared" si="10"/>
-        <v>-9537.2576751647575</v>
+        <v>-9797.2455353458463</v>
       </c>
       <c r="L35" s="34">
         <f t="shared" si="10"/>
-        <v>-10079.037332128893</v>
+        <v>-10567.840887672719</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.2">
@@ -25720,23 +26883,23 @@
       </c>
       <c r="H36" s="20">
         <f>H7*H37</f>
-        <v>-8687.1417000000001</v>
+        <v>-8946.8163000000004</v>
       </c>
       <c r="I36" s="20">
         <f>I7*I37</f>
-        <v>-9076.9690664999998</v>
+        <v>-9506.720612699999</v>
       </c>
       <c r="J36" s="20">
         <f>J7*J37</f>
-        <v>-9495.0039884925009</v>
+        <v>-10126.887669576899</v>
       </c>
       <c r="K36" s="20">
         <f>K7*K37</f>
-        <v>-9943.7701749251628</v>
+        <v>-10851.063413488961</v>
       </c>
       <c r="L36" s="20">
         <f>L7*L37</f>
-        <v>-10426.035090320904</v>
+        <v>-11676.00862912871</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.2">
@@ -25786,18 +26949,18 @@
       <c r="C39" s="131"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="201" t="s">
+      <c r="C40" s="212" t="s">
         <v>308</v>
       </c>
-      <c r="D40" s="201"/>
-      <c r="E40" s="201"/>
-      <c r="F40" s="201"/>
-      <c r="G40" s="201"/>
-      <c r="H40" s="201"/>
-      <c r="I40" s="201"/>
-      <c r="J40" s="201"/>
-      <c r="K40" s="201"/>
-      <c r="L40" s="201"/>
+      <c r="D40" s="212"/>
+      <c r="E40" s="212"/>
+      <c r="F40" s="212"/>
+      <c r="G40" s="212"/>
+      <c r="H40" s="212"/>
+      <c r="I40" s="212"/>
+      <c r="J40" s="212"/>
+      <c r="K40" s="212"/>
+      <c r="L40" s="212"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
@@ -25870,23 +27033,23 @@
       </c>
       <c r="H42" s="34">
         <f>H7*H43</f>
-        <v>12596.355465000001</v>
+        <v>12972.883635</v>
       </c>
       <c r="I42" s="34">
         <f>I7*I43</f>
-        <v>13161.605146425001</v>
+        <v>13784.744888415</v>
       </c>
       <c r="J42" s="34">
         <f>J7*J43</f>
-        <v>13767.755783314127</v>
+        <v>14683.987120886506</v>
       </c>
       <c r="K42" s="34">
         <f>K7*K43</f>
-        <v>14418.466753641487</v>
+        <v>15734.041949558994</v>
       </c>
       <c r="L42" s="34">
         <f>L7*L43</f>
-        <v>15117.750880965312</v>
+        <v>16930.212512236631</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -25959,7 +27122,7 @@
       </c>
       <c r="I44" s="182">
         <f t="shared" si="13"/>
-        <v>0.96666666666666667</v>
+        <v>0.96666666666666679</v>
       </c>
       <c r="J44" s="182">
         <f t="shared" si="13"/>
@@ -25971,7 +27134,7 @@
       </c>
       <c r="L44" s="182">
         <f t="shared" si="13"/>
-        <v>0.96666666666666679</v>
+        <v>0.9666666666666669</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
@@ -26000,23 +27163,23 @@
       </c>
       <c r="H45" s="34">
         <f>H7*H46</f>
-        <v>13030.71255</v>
+        <v>13420.22445</v>
       </c>
       <c r="I45" s="34">
         <f>I7*I46</f>
-        <v>13615.453599750001</v>
+        <v>14260.080919049999</v>
       </c>
       <c r="J45" s="34">
         <f>J7*J46</f>
-        <v>14242.50598273875</v>
+        <v>15190.331504365349</v>
       </c>
       <c r="K45" s="34">
         <f>K7*K46</f>
-        <v>14915.655262387743</v>
+        <v>16276.59512023344</v>
       </c>
       <c r="L45" s="34">
         <f>L7*L46</f>
-        <v>15639.052635481356</v>
+        <v>17514.012943693062</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.2">
@@ -26061,6 +27224,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -26068,12 +27237,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/AAPL.xlsx
+++ b/AAPL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12E9FBC-E5AA-CA44-8942-81CF0F55297D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D70496-66E8-854C-9611-097AC9119362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="15" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="350">
   <si>
     <t>Date</t>
   </si>
@@ -1227,6 +1227,9 @@
   </si>
   <si>
     <t>EBIT margin</t>
+  </si>
+  <si>
+    <t>WACC set manually</t>
   </si>
 </sst>
 </file>
@@ -2113,6 +2116,18 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2124,18 +2139,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2252,22 +2255,17 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="4">
-          <cell r="C4">
-            <v>106.24</v>
-          </cell>
-        </row>
         <row r="10">
           <cell r="C10">
-            <v>43.36</v>
+            <v>43.54</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>270.70999999999998</v>
+            <v>270.32</v>
           </cell>
           <cell r="F17">
-            <v>1.06</v>
+            <v>1.075</v>
           </cell>
         </row>
       </sheetData>
@@ -2721,7 +2719,7 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$17</f>
-        <v>270.70999999999998</v>
+        <v>270.32</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2747,7 +2745,7 @@
       </c>
       <c r="C11" s="93">
         <f>$C$3/'Statement Q'!$N$19</f>
-        <v>34.292415709349022</v>
+        <v>34.243012133098986</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2756,7 +2754,7 @@
       </c>
       <c r="C12" s="93">
         <f>$C$3/Statements!W18</f>
-        <v>34.292415709349022</v>
+        <v>34.243012133098986</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2765,7 +2763,7 @@
       </c>
       <c r="C13" s="98">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$17)</f>
-        <v>9.2715799544094928</v>
+        <v>9.2582227966309851</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -2774,7 +2772,7 @@
       </c>
       <c r="C15" s="20">
         <f>C3*'Statement Q'!N100</f>
-        <v>3974293.51</v>
+        <v>3968567.92</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -2801,7 +2799,7 @@
       </c>
       <c r="C18" s="20">
         <f>C15+C17-C16</f>
-        <v>3920007.51</v>
+        <v>3914281.92</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -3021,60 +3019,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="208" t="s">
+      <c r="C2" s="212" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="208"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="209"/>
-      <c r="H2" s="210" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="213"/>
+      <c r="H2" s="214" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="208"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="208"/>
-      <c r="L2" s="208"/>
-      <c r="S2" s="211"/>
-      <c r="T2" s="211"/>
-      <c r="U2" s="211"/>
-      <c r="V2" s="211"/>
-      <c r="W2" s="211"/>
-      <c r="X2" s="211"/>
-      <c r="Y2" s="211"/>
-      <c r="Z2" s="211"/>
-      <c r="AA2" s="211"/>
-      <c r="AB2" s="211"/>
-      <c r="AC2" s="211"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
+      <c r="S2" s="215"/>
+      <c r="T2" s="215"/>
+      <c r="U2" s="215"/>
+      <c r="V2" s="215"/>
+      <c r="W2" s="215"/>
+      <c r="X2" s="215"/>
+      <c r="Y2" s="215"/>
+      <c r="Z2" s="215"/>
+      <c r="AA2" s="215"/>
+      <c r="AB2" s="215"/>
+      <c r="AC2" s="215"/>
       <c r="AE2" s="122"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="212" t="s">
+      <c r="C4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="212"/>
-      <c r="G4" s="212"/>
-      <c r="H4" s="212"/>
-      <c r="I4" s="212"/>
-      <c r="J4" s="212"/>
-      <c r="K4" s="212"/>
-      <c r="L4" s="212"/>
-      <c r="S4" s="211"/>
-      <c r="T4" s="211"/>
-      <c r="U4" s="211"/>
-      <c r="V4" s="211"/>
-      <c r="W4" s="211"/>
-      <c r="X4" s="211"/>
-      <c r="Y4" s="211"/>
-      <c r="Z4" s="211"/>
-      <c r="AA4" s="211"/>
-      <c r="AB4" s="211"/>
-      <c r="AC4" s="211"/>
+      <c r="D4" s="211"/>
+      <c r="E4" s="211"/>
+      <c r="F4" s="211"/>
+      <c r="G4" s="211"/>
+      <c r="H4" s="211"/>
+      <c r="I4" s="211"/>
+      <c r="J4" s="211"/>
+      <c r="K4" s="211"/>
+      <c r="L4" s="211"/>
+      <c r="S4" s="215"/>
+      <c r="T4" s="215"/>
+      <c r="U4" s="215"/>
+      <c r="V4" s="215"/>
+      <c r="W4" s="215"/>
+      <c r="X4" s="215"/>
+      <c r="Y4" s="215"/>
+      <c r="Z4" s="215"/>
+      <c r="AA4" s="215"/>
+      <c r="AB4" s="215"/>
+      <c r="AC4" s="215"/>
       <c r="AE4" s="123"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -3559,18 +3557,18 @@
       <c r="AE12" s="104"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C15" s="212" t="s">
+      <c r="C15" s="211" t="s">
         <v>142</v>
       </c>
-      <c r="D15" s="212"/>
-      <c r="E15" s="212"/>
-      <c r="F15" s="212"/>
-      <c r="G15" s="212"/>
-      <c r="H15" s="212"/>
-      <c r="I15" s="212"/>
-      <c r="J15" s="212"/>
-      <c r="K15" s="212"/>
-      <c r="L15" s="212"/>
+      <c r="D15" s="211"/>
+      <c r="E15" s="211"/>
+      <c r="F15" s="211"/>
+      <c r="G15" s="211"/>
+      <c r="H15" s="211"/>
+      <c r="I15" s="211"/>
+      <c r="J15" s="211"/>
+      <c r="K15" s="211"/>
+      <c r="L15" s="211"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C16" s="62">
@@ -3655,18 +3653,18 @@
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C20" s="212" t="s">
+      <c r="C20" s="211" t="s">
         <v>314</v>
       </c>
-      <c r="D20" s="212"/>
-      <c r="E20" s="212"/>
-      <c r="F20" s="212"/>
-      <c r="G20" s="212"/>
-      <c r="H20" s="212"/>
-      <c r="I20" s="212"/>
-      <c r="J20" s="212"/>
-      <c r="K20" s="212"/>
-      <c r="L20" s="212"/>
+      <c r="D20" s="211"/>
+      <c r="E20" s="211"/>
+      <c r="F20" s="211"/>
+      <c r="G20" s="211"/>
+      <c r="H20" s="211"/>
+      <c r="I20" s="211"/>
+      <c r="J20" s="211"/>
+      <c r="K20" s="211"/>
+      <c r="L20" s="211"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
@@ -3858,18 +3856,18 @@
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="212" t="s">
+      <c r="C27" s="211" t="s">
         <v>145</v>
       </c>
-      <c r="D27" s="212"/>
-      <c r="E27" s="212"/>
-      <c r="F27" s="212"/>
-      <c r="G27" s="212"/>
-      <c r="H27" s="212"/>
-      <c r="I27" s="212"/>
-      <c r="J27" s="212"/>
-      <c r="K27" s="212"/>
-      <c r="L27" s="212"/>
+      <c r="D27" s="211"/>
+      <c r="E27" s="211"/>
+      <c r="F27" s="211"/>
+      <c r="G27" s="211"/>
+      <c r="H27" s="211"/>
+      <c r="I27" s="211"/>
+      <c r="J27" s="211"/>
+      <c r="K27" s="211"/>
+      <c r="L27" s="211"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
@@ -4076,10 +4074,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="208" t="s">
+      <c r="B4" s="212" t="s">
         <v>160</v>
       </c>
-      <c r="C4" s="208"/>
+      <c r="C4" s="212"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -4096,7 +4094,7 @@
       </c>
       <c r="C6" s="145">
         <f>Overview!C3</f>
-        <v>270.70999999999998</v>
+        <v>270.32</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4105,7 +4103,7 @@
       </c>
       <c r="C7" s="147">
         <f>C5*C6</f>
-        <v>3974293.51</v>
+        <v>3968567.92</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4123,7 +4121,7 @@
       </c>
       <c r="C9" s="170">
         <f>[1]Sheet1!$C$10/1000</f>
-        <v>4.3360000000000003E-2</v>
+        <v>4.3540000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4132,7 +4130,7 @@
       </c>
       <c r="C10" s="145">
         <f>[1]Sheet1!$F$17</f>
-        <v>1.06</v>
+        <v>1.075</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4161,10 +4159,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="208" t="s">
+      <c r="B15" s="212" t="s">
         <v>166</v>
       </c>
-      <c r="C15" s="208"/>
+      <c r="C15" s="212"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -4172,7 +4170,7 @@
       </c>
       <c r="C16" s="148">
         <f>C8/(C8+C7)</f>
-        <v>2.2266518429206541E-2</v>
+        <v>2.2297926790704917E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4181,7 +4179,7 @@
       </c>
       <c r="C17" s="148">
         <f>C7/(C8+C7)</f>
-        <v>0.97773348157079343</v>
+        <v>0.97770207320929503</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4199,7 +4197,7 @@
       </c>
       <c r="C19" s="148">
         <f>C9+C10*C11</f>
-        <v>9.6360000000000001E-2</v>
+        <v>9.7290000000000001E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4208,10 +4206,17 @@
       </c>
       <c r="C20" s="148">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>9.5005973014319955E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
+        <v>9.5913325999941873E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C21" s="146">
+        <v>0.08</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B4:C4"/>
@@ -4255,60 +4260,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="208" t="s">
+      <c r="C3" s="212" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="208"/>
-      <c r="E3" s="208"/>
-      <c r="F3" s="208"/>
-      <c r="G3" s="209"/>
-      <c r="H3" s="210" t="s">
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="213"/>
+      <c r="H3" s="214" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="208"/>
-      <c r="J3" s="208"/>
-      <c r="K3" s="208"/>
-      <c r="L3" s="208"/>
-      <c r="P3" s="211"/>
-      <c r="Q3" s="211"/>
-      <c r="R3" s="211"/>
-      <c r="S3" s="211"/>
-      <c r="T3" s="211"/>
-      <c r="U3" s="211"/>
-      <c r="V3" s="211"/>
-      <c r="W3" s="211"/>
-      <c r="X3" s="211"/>
-      <c r="Y3" s="211"/>
-      <c r="Z3" s="211"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212"/>
+      <c r="L3" s="212"/>
+      <c r="P3" s="215"/>
+      <c r="Q3" s="215"/>
+      <c r="R3" s="215"/>
+      <c r="S3" s="215"/>
+      <c r="T3" s="215"/>
+      <c r="U3" s="215"/>
+      <c r="V3" s="215"/>
+      <c r="W3" s="215"/>
+      <c r="X3" s="215"/>
+      <c r="Y3" s="215"/>
+      <c r="Z3" s="215"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="212" t="s">
+      <c r="C5" s="211" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="212"/>
-      <c r="E5" s="212"/>
-      <c r="F5" s="212"/>
-      <c r="G5" s="212"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="212"/>
-      <c r="K5" s="212"/>
-      <c r="L5" s="212"/>
-      <c r="P5" s="211"/>
-      <c r="Q5" s="211"/>
-      <c r="R5" s="211"/>
-      <c r="S5" s="211"/>
-      <c r="T5" s="211"/>
-      <c r="U5" s="211"/>
-      <c r="V5" s="211"/>
-      <c r="W5" s="211"/>
-      <c r="X5" s="211"/>
-      <c r="Y5" s="211"/>
-      <c r="Z5" s="211"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="211"/>
+      <c r="P5" s="215"/>
+      <c r="Q5" s="215"/>
+      <c r="R5" s="215"/>
+      <c r="S5" s="215"/>
+      <c r="T5" s="215"/>
+      <c r="U5" s="215"/>
+      <c r="V5" s="215"/>
+      <c r="W5" s="215"/>
+      <c r="X5" s="215"/>
+      <c r="Y5" s="215"/>
+      <c r="Z5" s="215"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -4461,7 +4466,7 @@
       </c>
       <c r="L8" s="133">
         <f>L7*(1+C14)/(C15-C14)</f>
-        <v>1977341.8222535548</v>
+        <v>2516831.6045230655</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="7"/>
@@ -4515,23 +4520,23 @@
       <c r="G10" s="150"/>
       <c r="H10" s="133">
         <f>H7/(1+$C$15)^H9</f>
-        <v>94157.802190305141</v>
+        <v>95466.070189152728</v>
       </c>
       <c r="I10" s="133">
         <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>91192.220033433419</v>
+        <v>93743.951050476753</v>
       </c>
       <c r="J10" s="133">
         <f t="shared" si="0"/>
-        <v>88256.236972329716</v>
+        <v>91986.396133258022</v>
       </c>
       <c r="K10" s="133">
         <f t="shared" si="0"/>
-        <v>85227.88299488007</v>
+        <v>90064.290409348134</v>
       </c>
       <c r="L10" s="133">
         <f t="shared" si="0"/>
-        <v>85784.83932202826</v>
+        <v>91912.420964979916</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -4550,14 +4555,14 @@
       <c r="K11" s="130"/>
       <c r="L11" s="133">
         <f>L8/(1+C15)^L9</f>
-        <v>1256027.9718859517</v>
+        <v>1712913.2998018982</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="208" t="s">
+      <c r="B13" s="212" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="208"/>
+      <c r="C13" s="212"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -4572,15 +4577,15 @@
         <v>156</v>
       </c>
       <c r="C15" s="149">
-        <f>WACC!C20</f>
-        <v>9.5005973014319955E-2</v>
+        <f>WACC!C21</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="208" t="s">
+      <c r="B18" s="212" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="208"/>
+      <c r="C18" s="212"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -4588,7 +4593,7 @@
       </c>
       <c r="C19" s="104">
         <f>SUM(H10:L10)</f>
-        <v>444618.98151297664</v>
+        <v>463173.12874721555</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -4597,7 +4602,7 @@
       </c>
       <c r="C20" s="104">
         <f>L11</f>
-        <v>1256027.9718859517</v>
+        <v>1712913.2998018982</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -4606,7 +4611,7 @@
       </c>
       <c r="C21" s="109">
         <f>C19+C20</f>
-        <v>1700646.9533989283</v>
+        <v>2176086.4285491137</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -4633,7 +4638,7 @@
       </c>
       <c r="C24" s="109">
         <f>C21+C22-C23</f>
-        <v>1754932.9533989283</v>
+        <v>2230372.4285491137</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -4651,7 +4656,7 @@
       </c>
       <c r="C26" s="152">
         <f>C24/C25</f>
-        <v>119.5376986171874</v>
+        <v>151.9223778045851</v>
       </c>
     </row>
   </sheetData>
@@ -4694,37 +4699,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="208" t="s">
+      <c r="C2" s="212" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="208"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="209"/>
-      <c r="H2" s="210" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="213"/>
+      <c r="H2" s="214" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="208"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="208"/>
-      <c r="L2" s="208"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="212" t="s">
+      <c r="C4" s="211" t="s">
         <v>318</v>
       </c>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="212"/>
-      <c r="G4" s="212"/>
-      <c r="H4" s="212"/>
-      <c r="I4" s="212"/>
-      <c r="J4" s="212"/>
-      <c r="K4" s="212"/>
-      <c r="L4" s="212"/>
+      <c r="D4" s="211"/>
+      <c r="E4" s="211"/>
+      <c r="F4" s="211"/>
+      <c r="G4" s="211"/>
+      <c r="H4" s="211"/>
+      <c r="I4" s="211"/>
+      <c r="J4" s="211"/>
+      <c r="K4" s="211"/>
+      <c r="L4" s="211"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -4913,18 +4918,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="212" t="s">
+      <c r="C10" s="211" t="s">
         <v>116</v>
       </c>
-      <c r="D10" s="212"/>
-      <c r="E10" s="212"/>
-      <c r="F10" s="212"/>
-      <c r="G10" s="212"/>
-      <c r="H10" s="212"/>
-      <c r="I10" s="212"/>
-      <c r="J10" s="212"/>
-      <c r="K10" s="212"/>
-      <c r="L10" s="212"/>
+      <c r="D10" s="211"/>
+      <c r="E10" s="211"/>
+      <c r="F10" s="211"/>
+      <c r="G10" s="211"/>
+      <c r="H10" s="211"/>
+      <c r="I10" s="211"/>
+      <c r="J10" s="211"/>
+      <c r="K10" s="211"/>
+      <c r="L10" s="211"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5106,18 +5111,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="212" t="s">
+      <c r="C16" s="211" t="s">
         <v>217</v>
       </c>
-      <c r="D16" s="212"/>
-      <c r="E16" s="212"/>
-      <c r="F16" s="212"/>
-      <c r="G16" s="212"/>
-      <c r="H16" s="212"/>
-      <c r="I16" s="212"/>
-      <c r="J16" s="212"/>
-      <c r="K16" s="212"/>
-      <c r="L16" s="212"/>
+      <c r="D16" s="211"/>
+      <c r="E16" s="211"/>
+      <c r="F16" s="211"/>
+      <c r="G16" s="211"/>
+      <c r="H16" s="211"/>
+      <c r="I16" s="211"/>
+      <c r="J16" s="211"/>
+      <c r="K16" s="211"/>
+      <c r="L16" s="211"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -5251,18 +5256,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="212" t="s">
+      <c r="C21" s="211" t="s">
         <v>319</v>
       </c>
-      <c r="D21" s="212"/>
-      <c r="E21" s="212"/>
-      <c r="F21" s="212"/>
-      <c r="G21" s="212"/>
-      <c r="H21" s="212"/>
-      <c r="I21" s="212"/>
-      <c r="J21" s="212"/>
-      <c r="K21" s="212"/>
-      <c r="L21" s="212"/>
+      <c r="D21" s="211"/>
+      <c r="E21" s="211"/>
+      <c r="F21" s="211"/>
+      <c r="G21" s="211"/>
+      <c r="H21" s="211"/>
+      <c r="I21" s="211"/>
+      <c r="J21" s="211"/>
+      <c r="K21" s="211"/>
+      <c r="L21" s="211"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -5346,18 +5351,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="212" t="s">
+      <c r="C26" s="211" t="s">
         <v>320</v>
       </c>
-      <c r="D26" s="212"/>
-      <c r="E26" s="212"/>
-      <c r="F26" s="212"/>
-      <c r="G26" s="212"/>
-      <c r="H26" s="212"/>
-      <c r="I26" s="212"/>
-      <c r="J26" s="212"/>
-      <c r="K26" s="212"/>
-      <c r="L26" s="212"/>
+      <c r="D26" s="211"/>
+      <c r="E26" s="211"/>
+      <c r="F26" s="211"/>
+      <c r="G26" s="211"/>
+      <c r="H26" s="211"/>
+      <c r="I26" s="211"/>
+      <c r="J26" s="211"/>
+      <c r="K26" s="211"/>
+      <c r="L26" s="211"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -5627,10 +5632,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="208" t="s">
+      <c r="B37" s="212" t="s">
         <v>324</v>
       </c>
-      <c r="C37" s="208"/>
+      <c r="C37" s="212"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -5647,8 +5652,8 @@
         <v>156</v>
       </c>
       <c r="C39" s="138">
-        <f>WACC!C20</f>
-        <v>9.5005973014319955E-2</v>
+        <f>WACC!C21</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -5692,14 +5697,14 @@
       </c>
       <c r="C44" s="152">
         <f>C43/(1+C48)^5</f>
-        <v>218.82985823559341</v>
+        <v>234.46079993638196</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="208" t="s">
+      <c r="B46" s="212" t="s">
         <v>193</v>
       </c>
-      <c r="C46" s="208"/>
+      <c r="C46" s="212"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -5715,8 +5720,8 @@
         <v>156</v>
       </c>
       <c r="C48" s="138">
-        <f>WACC!C20</f>
-        <v>9.5005973014319955E-2</v>
+        <f>WACC!C21</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -5751,14 +5756,14 @@
       </c>
       <c r="C52" s="152">
         <f>C51/(1+C48)^5</f>
-        <v>195.14235575789263</v>
+        <v>209.08130728306443</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="208" t="s">
+      <c r="B54" s="212" t="s">
         <v>328</v>
       </c>
-      <c r="C54" s="208"/>
+      <c r="C54" s="212"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -5774,8 +5779,8 @@
         <v>156</v>
       </c>
       <c r="C56" s="138">
-        <f>WACC!C20</f>
-        <v>9.5005973014319955E-2</v>
+        <f>WACC!C21</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -5819,7 +5824,7 @@
       </c>
       <c r="C61" s="152">
         <f>C60/(1+C56)^5</f>
-        <v>191.36624469530753</v>
+        <v>205.03546990273239</v>
       </c>
     </row>
   </sheetData>
@@ -5868,10 +5873,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="208" t="s">
+      <c r="B4" s="212" t="s">
         <v>201</v>
       </c>
-      <c r="C4" s="208"/>
+      <c r="C4" s="212"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -5880,7 +5885,7 @@
       </c>
       <c r="C5" s="167">
         <f>DCF!C26</f>
-        <v>119.5376986171874</v>
+        <v>151.9223778045851</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -5889,7 +5894,7 @@
       </c>
       <c r="C6" s="167">
         <f>Multiples!C44</f>
-        <v>218.82985823559341</v>
+        <v>234.46079993638196</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -5898,7 +5903,7 @@
       </c>
       <c r="C7" s="167">
         <f>Multiples!C52</f>
-        <v>195.14235575789263</v>
+        <v>209.08130728306443</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -5907,7 +5912,7 @@
       </c>
       <c r="C8" s="167">
         <f>Multiples!C61</f>
-        <v>191.36624469530753</v>
+        <v>205.03546990273239</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -5916,7 +5921,7 @@
       </c>
       <c r="C9" s="152">
         <f>AVERAGE(C5:C8)</f>
-        <v>181.21903932649522</v>
+        <v>200.12498873169099</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -5925,7 +5930,7 @@
       </c>
       <c r="C10" s="35">
         <f>Overview!C3</f>
-        <v>270.70999999999998</v>
+        <v>270.32</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5934,7 +5939,7 @@
       </c>
       <c r="C11" s="89">
         <f>(C9-C10)/C10</f>
-        <v>-0.33057870294228053</v>
+        <v>-0.2596737617205867</v>
       </c>
     </row>
   </sheetData>
@@ -5978,60 +5983,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="208" t="s">
+      <c r="C3" s="212" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="208"/>
-      <c r="E3" s="208"/>
-      <c r="F3" s="208"/>
-      <c r="G3" s="209"/>
-      <c r="H3" s="210" t="s">
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="213"/>
+      <c r="H3" s="214" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="208"/>
-      <c r="J3" s="208"/>
-      <c r="K3" s="208"/>
-      <c r="L3" s="208"/>
-      <c r="P3" s="211"/>
-      <c r="Q3" s="211"/>
-      <c r="R3" s="211"/>
-      <c r="S3" s="211"/>
-      <c r="T3" s="211"/>
-      <c r="U3" s="211"/>
-      <c r="V3" s="211"/>
-      <c r="W3" s="211"/>
-      <c r="X3" s="211"/>
-      <c r="Y3" s="211"/>
-      <c r="Z3" s="211"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212"/>
+      <c r="L3" s="212"/>
+      <c r="P3" s="215"/>
+      <c r="Q3" s="215"/>
+      <c r="R3" s="215"/>
+      <c r="S3" s="215"/>
+      <c r="T3" s="215"/>
+      <c r="U3" s="215"/>
+      <c r="V3" s="215"/>
+      <c r="W3" s="215"/>
+      <c r="X3" s="215"/>
+      <c r="Y3" s="215"/>
+      <c r="Z3" s="215"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="212" t="s">
+      <c r="C5" s="211" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="212"/>
-      <c r="E5" s="212"/>
-      <c r="F5" s="212"/>
-      <c r="G5" s="212"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="212"/>
-      <c r="K5" s="212"/>
-      <c r="L5" s="212"/>
-      <c r="P5" s="211"/>
-      <c r="Q5" s="211"/>
-      <c r="R5" s="211"/>
-      <c r="S5" s="211"/>
-      <c r="T5" s="211"/>
-      <c r="U5" s="211"/>
-      <c r="V5" s="211"/>
-      <c r="W5" s="211"/>
-      <c r="X5" s="211"/>
-      <c r="Y5" s="211"/>
-      <c r="Z5" s="211"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="211"/>
+      <c r="P5" s="215"/>
+      <c r="Q5" s="215"/>
+      <c r="R5" s="215"/>
+      <c r="S5" s="215"/>
+      <c r="T5" s="215"/>
+      <c r="U5" s="215"/>
+      <c r="V5" s="215"/>
+      <c r="W5" s="215"/>
+      <c r="X5" s="215"/>
+      <c r="Y5" s="215"/>
+      <c r="Z5" s="215"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -6118,23 +6123,23 @@
       </c>
       <c r="H7" s="133">
         <f>G7*(1+$C$17)</f>
-        <v>113005.69837917863</v>
+        <v>107398.54540616595</v>
       </c>
       <c r="I7" s="133">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>148037.46487672403</v>
+        <v>133711.18903067661</v>
       </c>
       <c r="J7" s="133">
         <f t="shared" si="0"/>
-        <v>193929.0789885085</v>
+        <v>166470.43034319239</v>
       </c>
       <c r="K7" s="133">
         <f t="shared" si="0"/>
-        <v>254047.09347494613</v>
+        <v>207255.68577727454</v>
       </c>
       <c r="L7" s="133">
         <f t="shared" si="0"/>
-        <v>332801.69245217944</v>
+        <v>258033.32879270683</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="7"/>
@@ -6166,7 +6171,7 @@
       <c r="K8" s="130"/>
       <c r="L8" s="133">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>4872751.8535269313</v>
+        <v>4808802.9456822639</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="7"/>
@@ -6220,23 +6225,23 @@
       <c r="G10" s="150"/>
       <c r="H10" s="133">
         <f>H7/(1+$C$21)^H9</f>
-        <v>103200.98808967939</v>
+        <v>99443.0975983018</v>
       </c>
       <c r="I10" s="133">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>123463.52232702571</v>
+        <v>114635.79306470903</v>
       </c>
       <c r="J10" s="133">
         <f t="shared" si="1"/>
-        <v>147704.41279253969</v>
+        <v>132149.59478292844</v>
       </c>
       <c r="K10" s="133">
         <f t="shared" si="1"/>
-        <v>176704.77196172933</v>
+        <v>152339.11620809807</v>
       </c>
       <c r="L10" s="133">
         <f t="shared" si="1"/>
-        <v>211399.07632890897</v>
+        <v>175613.14785100197</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -6255,15 +6260,15 @@
       <c r="K11" s="130"/>
       <c r="L11" s="133">
         <f>L8/(1+C21)^L9</f>
-        <v>3095222.3632804621</v>
+        <v>3272790.4826777643</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="213" t="s">
+      <c r="B14" s="208" t="s">
         <v>334</v>
       </c>
-      <c r="C14" s="214"/>
+      <c r="C14" s="209"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="193" t="s">
@@ -6271,7 +6276,7 @@
       </c>
       <c r="C15" s="194">
         <f>Overview!C3</f>
-        <v>270.70999999999998</v>
+        <v>270.32</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6280,7 +6285,7 @@
       </c>
       <c r="C16" s="194">
         <f>C36</f>
-        <v>266.46557692121416</v>
+        <v>272.54664070450264</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6288,22 +6293,22 @@
         <v>337</v>
       </c>
       <c r="C17" s="196">
-        <v>0.31</v>
-      </c>
-      <c r="E17" s="215" t="s">
+        <v>0.245</v>
+      </c>
+      <c r="E17" s="210" t="s">
         <v>338</v>
       </c>
-      <c r="F17" s="215"/>
-      <c r="G17" s="215"/>
-      <c r="H17" s="215"/>
-      <c r="I17" s="215"/>
+      <c r="F17" s="210"/>
+      <c r="G17" s="210"/>
+      <c r="H17" s="210"/>
+      <c r="I17" s="210"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="213" t="s">
+      <c r="B19" s="208" t="s">
         <v>181</v>
       </c>
-      <c r="C19" s="214"/>
+      <c r="C19" s="209"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="197" t="s">
@@ -6318,8 +6323,8 @@
         <v>156</v>
       </c>
       <c r="C21" s="199">
-        <f>WACC!C20</f>
-        <v>9.5005973014319955E-2</v>
+        <f>WACC!C21</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -6337,7 +6342,7 @@
       </c>
       <c r="C23" s="200">
         <f>C15*C22</f>
-        <v>3974293.51</v>
+        <v>3968567.92</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6364,15 +6369,15 @@
       </c>
       <c r="C26" s="201">
         <f>C23+C25-C24</f>
-        <v>3920007.51</v>
+        <v>3914281.92</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="213" t="s">
+      <c r="B28" s="208" t="s">
         <v>80</v>
       </c>
-      <c r="C28" s="214"/>
+      <c r="C28" s="209"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="197" t="s">
@@ -6380,7 +6385,7 @@
       </c>
       <c r="C29" s="200">
         <f>SUM(H10:L10)</f>
-        <v>762472.77149988315</v>
+        <v>674180.7495050393</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -6389,7 +6394,7 @@
       </c>
       <c r="C30" s="200">
         <f>L11</f>
-        <v>3095222.3632804621</v>
+        <v>3272790.4826777643</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -6398,7 +6403,7 @@
       </c>
       <c r="C31" s="203">
         <f>C29+C30</f>
-        <v>3857695.1347803455</v>
+        <v>3946971.2321828036</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -6425,7 +6430,7 @@
       </c>
       <c r="C34" s="203">
         <f>C31+C32-C33</f>
-        <v>3911981.1347803455</v>
+        <v>4001257.2321828036</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -6443,22 +6448,22 @@
       </c>
       <c r="C36" s="206">
         <f>C34/C35</f>
-        <v>266.46557692121416</v>
+        <v>272.54664070450264</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="212" t="s">
+      <c r="C39" s="211" t="s">
         <v>340</v>
       </c>
-      <c r="D39" s="212"/>
-      <c r="E39" s="212"/>
-      <c r="F39" s="212"/>
-      <c r="G39" s="212"/>
-      <c r="H39" s="212"/>
-      <c r="I39" s="212"/>
-      <c r="J39" s="212"/>
-      <c r="K39" s="212"/>
-      <c r="L39" s="212"/>
+      <c r="D39" s="211"/>
+      <c r="E39" s="211"/>
+      <c r="F39" s="211"/>
+      <c r="G39" s="211"/>
+      <c r="H39" s="211"/>
+      <c r="I39" s="211"/>
+      <c r="J39" s="211"/>
+      <c r="K39" s="211"/>
+      <c r="L39" s="211"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="62">
@@ -6528,23 +6533,23 @@
       </c>
       <c r="H41" s="174">
         <f t="shared" si="3"/>
-        <v>113005.69837917863</v>
+        <v>107398.54540616595</v>
       </c>
       <c r="I41" s="174">
         <f t="shared" si="3"/>
-        <v>148037.46487672403</v>
+        <v>133711.18903067661</v>
       </c>
       <c r="J41" s="174">
         <f t="shared" si="3"/>
-        <v>193929.0789885085</v>
+        <v>166470.43034319239</v>
       </c>
       <c r="K41" s="174">
         <f t="shared" si="3"/>
-        <v>254047.09347494613</v>
+        <v>207255.68577727454</v>
       </c>
       <c r="L41" s="174">
         <f t="shared" si="3"/>
-        <v>332801.69245217944</v>
+        <v>258033.32879270683</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
@@ -6573,23 +6578,23 @@
       </c>
       <c r="H42" s="174">
         <f>H41/H43</f>
-        <v>141257.12297397328</v>
+        <v>134248.18175770744</v>
       </c>
       <c r="I42" s="174">
         <f t="shared" ref="I42:L42" si="4">I41/I43</f>
-        <v>185046.83109590501</v>
+        <v>167138.98628834577</v>
       </c>
       <c r="J42" s="174">
         <f t="shared" si="4"/>
-        <v>242411.34873563561</v>
+        <v>208088.03792899047</v>
       </c>
       <c r="K42" s="174">
         <f t="shared" si="4"/>
-        <v>317558.86684368266</v>
+        <v>259069.60722159318</v>
       </c>
       <c r="L42" s="174">
         <f t="shared" si="4"/>
-        <v>416002.11556522426</v>
+        <v>322541.66099088354</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -6658,23 +6663,23 @@
       </c>
       <c r="H44" s="174">
         <f>H41/H45</f>
-        <v>491329.12338773318</v>
+        <v>466950.19741811283</v>
       </c>
       <c r="I44" s="174">
         <f t="shared" ref="I44:L44" si="6">I41/I45</f>
-        <v>643641.15163793054</v>
+        <v>581352.99578555045</v>
       </c>
       <c r="J44" s="174">
         <f t="shared" si="6"/>
-        <v>843169.90864568902</v>
+        <v>723784.47975301032</v>
       </c>
       <c r="K44" s="174">
         <f t="shared" si="6"/>
-        <v>1104552.5803258526</v>
+        <v>901111.67729249795</v>
       </c>
       <c r="L44" s="174">
         <f t="shared" si="6"/>
-        <v>1446963.880226867</v>
+        <v>1121884.03822916</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
@@ -6740,23 +6745,23 @@
       </c>
       <c r="H46" s="207">
         <f t="shared" si="8"/>
-        <v>0.31000000000000005</v>
+        <v>0.24500000000000011</v>
       </c>
       <c r="I46" s="207">
         <f t="shared" si="8"/>
-        <v>0.31000000000000028</v>
+        <v>0.24500000000000011</v>
       </c>
       <c r="J46" s="207">
         <f t="shared" si="8"/>
-        <v>0.31000000000000005</v>
+        <v>0.24500000000000011</v>
       </c>
       <c r="K46" s="207">
         <f t="shared" si="8"/>
-        <v>0.31000000000000005</v>
+        <v>0.24500000000000011</v>
       </c>
       <c r="L46" s="207">
         <f t="shared" si="8"/>
-        <v>0.31000000000000005</v>
+        <v>0.24500000000000011</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.2">
@@ -6782,23 +6787,23 @@
       </c>
       <c r="H47" s="207">
         <f t="shared" si="9"/>
-        <v>6.1684501871276165E-2</v>
+        <v>9.0054998700295208E-3</v>
       </c>
       <c r="I47" s="207">
         <f t="shared" si="9"/>
-        <v>0.31000000000000005</v>
+        <v>0.24500000000000011</v>
       </c>
       <c r="J47" s="207">
         <f t="shared" si="9"/>
-        <v>0.31000000000000028</v>
+        <v>0.24499999999999988</v>
       </c>
       <c r="K47" s="207">
         <f t="shared" si="9"/>
-        <v>0.31000000000000005</v>
+        <v>0.24500000000000033</v>
       </c>
       <c r="L47" s="207">
         <f t="shared" si="9"/>
-        <v>0.30999999999999983</v>
+        <v>0.24500000000000011</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.2">
@@ -6824,23 +6829,23 @@
       </c>
       <c r="H48" s="207">
         <f t="shared" si="10"/>
-        <v>0.1806226998390843</v>
+        <v>0.12204218419821378</v>
       </c>
       <c r="I48" s="207">
         <f t="shared" si="10"/>
-        <v>0.31000000000000005</v>
+        <v>0.24499999999999988</v>
       </c>
       <c r="J48" s="207">
         <f t="shared" si="10"/>
-        <v>0.31000000000000005</v>
+        <v>0.24500000000000011</v>
       </c>
       <c r="K48" s="207">
         <f t="shared" si="10"/>
-        <v>0.31000000000000005</v>
+        <v>0.24500000000000011</v>
       </c>
       <c r="L48" s="207">
         <f t="shared" si="10"/>
-        <v>0.31000000000000005</v>
+        <v>0.24500000000000011</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
@@ -6873,11 +6878,11 @@
       </c>
       <c r="I49" s="207">
         <f t="shared" si="11"/>
-        <v>0.28749999999999998</v>
+        <v>0.28750000000000003</v>
       </c>
       <c r="J49" s="207">
         <f t="shared" si="11"/>
-        <v>0.28750000000000003</v>
+        <v>0.28749999999999998</v>
       </c>
       <c r="K49" s="207">
         <f t="shared" si="11"/>
@@ -6885,22 +6890,22 @@
       </c>
       <c r="L49" s="207">
         <f t="shared" si="11"/>
-        <v>0.28749999999999998</v>
+        <v>0.28750000000000003</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -23298,36 +23303,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="208" t="s">
+      <c r="C2" s="212" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="208"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="209"/>
-      <c r="H2" s="210" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="213"/>
+      <c r="H2" s="214" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="208"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="208"/>
-      <c r="L2" s="208"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
       <c r="O2" s="90"/>
-      <c r="S2" s="208" t="s">
+      <c r="S2" s="212" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="208"/>
-      <c r="U2" s="208"/>
-      <c r="V2" s="208"/>
-      <c r="W2" s="208"/>
-      <c r="X2" s="208"/>
-      <c r="Y2" s="208"/>
-      <c r="Z2" s="208"/>
-      <c r="AA2" s="208" t="s">
+      <c r="T2" s="212"/>
+      <c r="U2" s="212"/>
+      <c r="V2" s="212"/>
+      <c r="W2" s="212"/>
+      <c r="X2" s="212"/>
+      <c r="Y2" s="212"/>
+      <c r="Z2" s="212"/>
+      <c r="AA2" s="212" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="208"/>
-      <c r="AC2" s="208"/>
+      <c r="AB2" s="212"/>
+      <c r="AC2" s="212"/>
       <c r="AE2" s="117" t="s">
         <v>75</v>
       </c>
@@ -23338,18 +23343,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="212" t="s">
+      <c r="C4" s="211" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="212"/>
-      <c r="G4" s="212"/>
-      <c r="H4" s="212"/>
-      <c r="I4" s="212"/>
-      <c r="J4" s="212"/>
-      <c r="K4" s="212"/>
-      <c r="L4" s="212"/>
+      <c r="D4" s="211"/>
+      <c r="E4" s="211"/>
+      <c r="F4" s="211"/>
+      <c r="G4" s="211"/>
+      <c r="H4" s="211"/>
+      <c r="I4" s="211"/>
+      <c r="J4" s="211"/>
+      <c r="K4" s="211"/>
+      <c r="L4" s="211"/>
       <c r="O4" s="90"/>
       <c r="S4" s="219" t="s">
         <v>114</v>
@@ -24039,18 +24044,18 @@
       <c r="Q12" s="91"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="212" t="s">
+      <c r="C13" s="211" t="s">
         <v>116</v>
       </c>
-      <c r="D13" s="212"/>
-      <c r="E13" s="212"/>
-      <c r="F13" s="212"/>
-      <c r="G13" s="212"/>
-      <c r="H13" s="212"/>
-      <c r="I13" s="212"/>
-      <c r="J13" s="212"/>
-      <c r="K13" s="212"/>
-      <c r="L13" s="212"/>
+      <c r="D13" s="211"/>
+      <c r="E13" s="211"/>
+      <c r="F13" s="211"/>
+      <c r="G13" s="211"/>
+      <c r="H13" s="211"/>
+      <c r="I13" s="211"/>
+      <c r="J13" s="211"/>
+      <c r="K13" s="211"/>
+      <c r="L13" s="211"/>
       <c r="O13" s="90"/>
       <c r="Q13" s="91"/>
       <c r="S13" s="219" t="s">
@@ -24647,35 +24652,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="208" t="s">
+      <c r="C2" s="212" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="208"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="209"/>
-      <c r="H2" s="210" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="213"/>
+      <c r="H2" s="214" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="208"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="208"/>
-      <c r="L2" s="208"/>
-      <c r="P2" s="208" t="s">
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
+      <c r="P2" s="212" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="208"/>
-      <c r="R2" s="208"/>
-      <c r="S2" s="208"/>
-      <c r="T2" s="208"/>
-      <c r="U2" s="208"/>
-      <c r="V2" s="208"/>
-      <c r="W2" s="208"/>
-      <c r="X2" s="208" t="s">
+      <c r="Q2" s="212"/>
+      <c r="R2" s="212"/>
+      <c r="S2" s="212"/>
+      <c r="T2" s="212"/>
+      <c r="U2" s="212"/>
+      <c r="V2" s="212"/>
+      <c r="W2" s="212"/>
+      <c r="X2" s="212" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="208"/>
-      <c r="Z2" s="208"/>
+      <c r="Y2" s="212"/>
+      <c r="Z2" s="212"/>
       <c r="AB2" s="117" t="s">
         <v>75</v>
       </c>
@@ -24684,18 +24689,18 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="212" t="s">
+      <c r="C4" s="211" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="212"/>
-      <c r="G4" s="212"/>
-      <c r="H4" s="212"/>
-      <c r="I4" s="212"/>
-      <c r="J4" s="212"/>
-      <c r="K4" s="212"/>
-      <c r="L4" s="212"/>
+      <c r="D4" s="211"/>
+      <c r="E4" s="211"/>
+      <c r="F4" s="211"/>
+      <c r="G4" s="211"/>
+      <c r="H4" s="211"/>
+      <c r="I4" s="211"/>
+      <c r="J4" s="211"/>
+      <c r="K4" s="211"/>
+      <c r="L4" s="211"/>
       <c r="P4" s="220" t="s">
         <v>114</v>
       </c>
@@ -24909,18 +24914,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="212" t="s">
+      <c r="C9" s="211" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="212"/>
-      <c r="E9" s="212"/>
-      <c r="F9" s="212"/>
-      <c r="G9" s="212"/>
-      <c r="H9" s="212"/>
-      <c r="I9" s="212"/>
-      <c r="J9" s="212"/>
-      <c r="K9" s="212"/>
-      <c r="L9" s="212"/>
+      <c r="D9" s="211"/>
+      <c r="E9" s="211"/>
+      <c r="F9" s="211"/>
+      <c r="G9" s="211"/>
+      <c r="H9" s="211"/>
+      <c r="I9" s="211"/>
+      <c r="J9" s="211"/>
+      <c r="K9" s="211"/>
+      <c r="L9" s="211"/>
       <c r="N9" s="91"/>
       <c r="P9" s="220" t="s">
         <v>128</v>
@@ -25404,18 +25409,18 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="212" t="s">
+      <c r="C17" s="211" t="s">
         <v>126</v>
       </c>
-      <c r="D17" s="212"/>
-      <c r="E17" s="212"/>
-      <c r="F17" s="212"/>
-      <c r="G17" s="212"/>
-      <c r="H17" s="212"/>
-      <c r="I17" s="212"/>
-      <c r="J17" s="212"/>
-      <c r="K17" s="212"/>
-      <c r="L17" s="212"/>
+      <c r="D17" s="211"/>
+      <c r="E17" s="211"/>
+      <c r="F17" s="211"/>
+      <c r="G17" s="211"/>
+      <c r="H17" s="211"/>
+      <c r="I17" s="211"/>
+      <c r="J17" s="211"/>
+      <c r="K17" s="211"/>
+      <c r="L17" s="211"/>
       <c r="P17" s="220" t="s">
         <v>126</v>
       </c>
@@ -25818,60 +25823,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="208" t="s">
+      <c r="C3" s="212" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="208"/>
-      <c r="E3" s="208"/>
-      <c r="F3" s="208"/>
-      <c r="G3" s="209"/>
-      <c r="H3" s="210" t="s">
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="213"/>
+      <c r="H3" s="214" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="208"/>
-      <c r="J3" s="208"/>
-      <c r="K3" s="208"/>
-      <c r="L3" s="208"/>
-      <c r="P3" s="211"/>
-      <c r="Q3" s="211"/>
-      <c r="R3" s="211"/>
-      <c r="S3" s="211"/>
-      <c r="T3" s="211"/>
-      <c r="U3" s="211"/>
-      <c r="V3" s="211"/>
-      <c r="W3" s="211"/>
-      <c r="X3" s="211"/>
-      <c r="Y3" s="211"/>
-      <c r="Z3" s="211"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212"/>
+      <c r="L3" s="212"/>
+      <c r="P3" s="215"/>
+      <c r="Q3" s="215"/>
+      <c r="R3" s="215"/>
+      <c r="S3" s="215"/>
+      <c r="T3" s="215"/>
+      <c r="U3" s="215"/>
+      <c r="V3" s="215"/>
+      <c r="W3" s="215"/>
+      <c r="X3" s="215"/>
+      <c r="Y3" s="215"/>
+      <c r="Z3" s="215"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="212" t="s">
+      <c r="C5" s="211" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="212"/>
-      <c r="E5" s="212"/>
-      <c r="F5" s="212"/>
-      <c r="G5" s="212"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="212"/>
-      <c r="K5" s="212"/>
-      <c r="L5" s="212"/>
-      <c r="P5" s="211"/>
-      <c r="Q5" s="211"/>
-      <c r="R5" s="211"/>
-      <c r="S5" s="211"/>
-      <c r="T5" s="211"/>
-      <c r="U5" s="211"/>
-      <c r="V5" s="211"/>
-      <c r="W5" s="211"/>
-      <c r="X5" s="211"/>
-      <c r="Y5" s="211"/>
-      <c r="Z5" s="211"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="211"/>
+      <c r="P5" s="215"/>
+      <c r="Q5" s="215"/>
+      <c r="R5" s="215"/>
+      <c r="S5" s="215"/>
+      <c r="T5" s="215"/>
+      <c r="U5" s="215"/>
+      <c r="V5" s="215"/>
+      <c r="W5" s="215"/>
+      <c r="X5" s="215"/>
+      <c r="Y5" s="215"/>
+      <c r="Z5" s="215"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -26057,30 +26062,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="212" t="s">
+      <c r="C11" s="211" t="s">
         <v>134</v>
       </c>
-      <c r="D11" s="212"/>
-      <c r="E11" s="212"/>
-      <c r="F11" s="212"/>
-      <c r="G11" s="212"/>
-      <c r="H11" s="212"/>
-      <c r="I11" s="212"/>
-      <c r="J11" s="212"/>
-      <c r="K11" s="212"/>
-      <c r="L11" s="212"/>
+      <c r="D11" s="211"/>
+      <c r="E11" s="211"/>
+      <c r="F11" s="211"/>
+      <c r="G11" s="211"/>
+      <c r="H11" s="211"/>
+      <c r="I11" s="211"/>
+      <c r="J11" s="211"/>
+      <c r="K11" s="211"/>
+      <c r="L11" s="211"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="211"/>
-      <c r="Q11" s="211"/>
-      <c r="R11" s="211"/>
-      <c r="S11" s="211"/>
-      <c r="T11" s="211"/>
-      <c r="U11" s="211"/>
-      <c r="V11" s="211"/>
-      <c r="W11" s="211"/>
-      <c r="X11" s="211"/>
-      <c r="Y11" s="211"/>
-      <c r="Z11" s="211"/>
+      <c r="P11" s="215"/>
+      <c r="Q11" s="215"/>
+      <c r="R11" s="215"/>
+      <c r="S11" s="215"/>
+      <c r="T11" s="215"/>
+      <c r="U11" s="215"/>
+      <c r="V11" s="215"/>
+      <c r="W11" s="215"/>
+      <c r="X11" s="215"/>
+      <c r="Y11" s="215"/>
+      <c r="Z11" s="215"/>
       <c r="AB11" s="123"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -26322,18 +26327,18 @@
       <c r="D16" s="20"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="212" t="s">
+      <c r="C18" s="211" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="212"/>
-      <c r="E18" s="212"/>
-      <c r="F18" s="212"/>
-      <c r="G18" s="212"/>
-      <c r="H18" s="212"/>
-      <c r="I18" s="212"/>
-      <c r="J18" s="212"/>
-      <c r="K18" s="212"/>
-      <c r="L18" s="212"/>
+      <c r="D18" s="211"/>
+      <c r="E18" s="211"/>
+      <c r="F18" s="211"/>
+      <c r="G18" s="211"/>
+      <c r="H18" s="211"/>
+      <c r="I18" s="211"/>
+      <c r="J18" s="211"/>
+      <c r="K18" s="211"/>
+      <c r="L18" s="211"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -26546,23 +26551,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="211"/>
-      <c r="C25" s="211"/>
+      <c r="B25" s="215"/>
+      <c r="C25" s="215"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="122"/>
-      <c r="C26" s="212" t="s">
+      <c r="C26" s="211" t="s">
         <v>302</v>
       </c>
-      <c r="D26" s="212"/>
-      <c r="E26" s="212"/>
-      <c r="F26" s="212"/>
-      <c r="G26" s="212"/>
-      <c r="H26" s="212"/>
-      <c r="I26" s="212"/>
-      <c r="J26" s="212"/>
-      <c r="K26" s="212"/>
-      <c r="L26" s="212"/>
+      <c r="D26" s="211"/>
+      <c r="E26" s="211"/>
+      <c r="F26" s="211"/>
+      <c r="G26" s="211"/>
+      <c r="H26" s="211"/>
+      <c r="I26" s="211"/>
+      <c r="J26" s="211"/>
+      <c r="K26" s="211"/>
+      <c r="L26" s="211"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
@@ -26754,18 +26759,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="122"/>
-      <c r="C33" s="212" t="s">
+      <c r="C33" s="211" t="s">
         <v>305</v>
       </c>
-      <c r="D33" s="212"/>
-      <c r="E33" s="212"/>
-      <c r="F33" s="212"/>
-      <c r="G33" s="212"/>
-      <c r="H33" s="212"/>
-      <c r="I33" s="212"/>
-      <c r="J33" s="212"/>
-      <c r="K33" s="212"/>
-      <c r="L33" s="212"/>
+      <c r="D33" s="211"/>
+      <c r="E33" s="211"/>
+      <c r="F33" s="211"/>
+      <c r="G33" s="211"/>
+      <c r="H33" s="211"/>
+      <c r="I33" s="211"/>
+      <c r="J33" s="211"/>
+      <c r="K33" s="211"/>
+      <c r="L33" s="211"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
@@ -26949,18 +26954,18 @@
       <c r="C39" s="131"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="212" t="s">
+      <c r="C40" s="211" t="s">
         <v>308</v>
       </c>
-      <c r="D40" s="212"/>
-      <c r="E40" s="212"/>
-      <c r="F40" s="212"/>
-      <c r="G40" s="212"/>
-      <c r="H40" s="212"/>
-      <c r="I40" s="212"/>
-      <c r="J40" s="212"/>
-      <c r="K40" s="212"/>
-      <c r="L40" s="212"/>
+      <c r="D40" s="211"/>
+      <c r="E40" s="211"/>
+      <c r="F40" s="211"/>
+      <c r="G40" s="211"/>
+      <c r="H40" s="211"/>
+      <c r="I40" s="211"/>
+      <c r="J40" s="211"/>
+      <c r="K40" s="211"/>
+      <c r="L40" s="211"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
@@ -27224,12 +27229,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -27237,6 +27236,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/AAPL.xlsx
+++ b/AAPL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D70496-66E8-854C-9611-097AC9119362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756A5BDB-03EB-C34F-B29B-124A002778CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="15" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="12" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="350">
   <si>
     <t>Date</t>
   </si>
@@ -2116,30 +2116,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2149,11 +2125,35 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2257,15 +2257,15 @@
       <sheetData sheetId="0">
         <row r="10">
           <cell r="C10">
-            <v>43.54</v>
+            <v>43.9</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>270.32</v>
+            <v>285.12</v>
           </cell>
           <cell r="F17">
-            <v>1.075</v>
+            <v>1.0647</v>
           </cell>
         </row>
       </sheetData>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$17</f>
-        <v>270.32</v>
+        <v>285.12</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="C11" s="93">
         <f>$C$3/'Statement Q'!$N$19</f>
-        <v>34.243012133098986</v>
+        <v>36.117814513869433</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2753,8 +2753,8 @@
         <v>190</v>
       </c>
       <c r="C12" s="93">
-        <f>$C$3/Statements!W18</f>
-        <v>34.243012133098986</v>
+        <f>$C$3/Statements!W19</f>
+        <v>36.117814513869433</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="C13" s="98">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$17)</f>
-        <v>9.2582227966309851</v>
+        <v>9.7651098097640823</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="C15" s="20">
         <f>C3*'Statement Q'!N100</f>
-        <v>3968567.92</v>
+        <v>4185846.72</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -2780,7 +2780,7 @@
         <v>150</v>
       </c>
       <c r="C16" s="20">
-        <f>Statements!W21+Statements!W27</f>
+        <f>Statements!W22+Statements!W28</f>
         <v>144795</v>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
         <v>146</v>
       </c>
       <c r="C17" s="20">
-        <f>Statements!W35+Statements!W36+Statements!W38</f>
+        <f>Statements!W36+Statements!W37+Statements!W39</f>
         <v>90509</v>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="C18" s="20">
         <f>C15+C17-C16</f>
-        <v>3914281.92</v>
+        <v>4131560.7200000007</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -2946,7 +2946,7 @@
         <v>146</v>
       </c>
       <c r="C45" s="20">
-        <f>Statements!W35+Statements!W36+Statements!W38</f>
+        <f>Statements!W36+Statements!W37+Statements!W39</f>
         <v>90509</v>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
         <v>147</v>
       </c>
       <c r="C46" s="20">
-        <f>Statements!W45</f>
+        <f>Statements!W46</f>
         <v>88190</v>
       </c>
     </row>
@@ -2964,8 +2964,8 @@
         <v>150</v>
       </c>
       <c r="C47" s="20">
-        <f>Statements!W21+Statements!W27</f>
-        <v>144795</v>
+        <f>Statements!W22</f>
+        <v>66907</v>
       </c>
       <c r="D47" s="20"/>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C48" s="159">
         <f>C44/(C45+C46-C47)</f>
-        <v>3.5113546987136846</v>
+        <v>1.0649149286638468</v>
       </c>
       <c r="D48" s="159"/>
     </row>
@@ -3019,60 +3019,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="212"/>
-      <c r="F2" s="212"/>
-      <c r="G2" s="213"/>
-      <c r="H2" s="214" t="s">
+      <c r="D2" s="211"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="215" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="212"/>
-      <c r="J2" s="212"/>
-      <c r="K2" s="212"/>
-      <c r="L2" s="212"/>
-      <c r="S2" s="215"/>
-      <c r="T2" s="215"/>
-      <c r="U2" s="215"/>
-      <c r="V2" s="215"/>
-      <c r="W2" s="215"/>
-      <c r="X2" s="215"/>
-      <c r="Y2" s="215"/>
-      <c r="Z2" s="215"/>
-      <c r="AA2" s="215"/>
-      <c r="AB2" s="215"/>
-      <c r="AC2" s="215"/>
+      <c r="I2" s="211"/>
+      <c r="J2" s="211"/>
+      <c r="K2" s="211"/>
+      <c r="L2" s="211"/>
+      <c r="S2" s="217"/>
+      <c r="T2" s="217"/>
+      <c r="U2" s="217"/>
+      <c r="V2" s="217"/>
+      <c r="W2" s="217"/>
+      <c r="X2" s="217"/>
+      <c r="Y2" s="217"/>
+      <c r="Z2" s="217"/>
+      <c r="AA2" s="217"/>
+      <c r="AB2" s="217"/>
+      <c r="AC2" s="217"/>
       <c r="AE2" s="122"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="211" t="s">
+      <c r="C4" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="211"/>
-      <c r="E4" s="211"/>
-      <c r="F4" s="211"/>
-      <c r="G4" s="211"/>
-      <c r="H4" s="211"/>
-      <c r="I4" s="211"/>
-      <c r="J4" s="211"/>
-      <c r="K4" s="211"/>
-      <c r="L4" s="211"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="215"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="215"/>
-      <c r="Y4" s="215"/>
-      <c r="Z4" s="215"/>
-      <c r="AA4" s="215"/>
-      <c r="AB4" s="215"/>
-      <c r="AC4" s="215"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
+      <c r="S4" s="217"/>
+      <c r="T4" s="217"/>
+      <c r="U4" s="217"/>
+      <c r="V4" s="217"/>
+      <c r="W4" s="217"/>
+      <c r="X4" s="217"/>
+      <c r="Y4" s="217"/>
+      <c r="Z4" s="217"/>
+      <c r="AA4" s="217"/>
+      <c r="AB4" s="217"/>
+      <c r="AC4" s="217"/>
       <c r="AE4" s="123"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -3557,18 +3557,18 @@
       <c r="AE12" s="104"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C15" s="211" t="s">
+      <c r="C15" s="216" t="s">
         <v>142</v>
       </c>
-      <c r="D15" s="211"/>
-      <c r="E15" s="211"/>
-      <c r="F15" s="211"/>
-      <c r="G15" s="211"/>
-      <c r="H15" s="211"/>
-      <c r="I15" s="211"/>
-      <c r="J15" s="211"/>
-      <c r="K15" s="211"/>
-      <c r="L15" s="211"/>
+      <c r="D15" s="216"/>
+      <c r="E15" s="216"/>
+      <c r="F15" s="216"/>
+      <c r="G15" s="216"/>
+      <c r="H15" s="216"/>
+      <c r="I15" s="216"/>
+      <c r="J15" s="216"/>
+      <c r="K15" s="216"/>
+      <c r="L15" s="216"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C16" s="62">
@@ -3653,18 +3653,18 @@
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C20" s="211" t="s">
+      <c r="C20" s="216" t="s">
         <v>314</v>
       </c>
-      <c r="D20" s="211"/>
-      <c r="E20" s="211"/>
-      <c r="F20" s="211"/>
-      <c r="G20" s="211"/>
-      <c r="H20" s="211"/>
-      <c r="I20" s="211"/>
-      <c r="J20" s="211"/>
-      <c r="K20" s="211"/>
-      <c r="L20" s="211"/>
+      <c r="D20" s="216"/>
+      <c r="E20" s="216"/>
+      <c r="F20" s="216"/>
+      <c r="G20" s="216"/>
+      <c r="H20" s="216"/>
+      <c r="I20" s="216"/>
+      <c r="J20" s="216"/>
+      <c r="K20" s="216"/>
+      <c r="L20" s="216"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
@@ -3856,18 +3856,18 @@
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="211" t="s">
+      <c r="C27" s="216" t="s">
         <v>145</v>
       </c>
-      <c r="D27" s="211"/>
-      <c r="E27" s="211"/>
-      <c r="F27" s="211"/>
-      <c r="G27" s="211"/>
-      <c r="H27" s="211"/>
-      <c r="I27" s="211"/>
-      <c r="J27" s="211"/>
-      <c r="K27" s="211"/>
-      <c r="L27" s="211"/>
+      <c r="D27" s="216"/>
+      <c r="E27" s="216"/>
+      <c r="F27" s="216"/>
+      <c r="G27" s="216"/>
+      <c r="H27" s="216"/>
+      <c r="I27" s="216"/>
+      <c r="J27" s="216"/>
+      <c r="K27" s="216"/>
+      <c r="L27" s="216"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
@@ -4074,10 +4074,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="212" t="s">
+      <c r="B4" s="211" t="s">
         <v>160</v>
       </c>
-      <c r="C4" s="212"/>
+      <c r="C4" s="211"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="C6" s="145">
         <f>Overview!C3</f>
-        <v>270.32</v>
+        <v>285.12</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="C7" s="147">
         <f>C5*C6</f>
-        <v>3968567.92</v>
+        <v>4185846.72</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4111,7 +4111,7 @@
         <v>146</v>
       </c>
       <c r="C8" s="132">
-        <f>Statements!W35+Statements!W36+Statements!W38</f>
+        <f>Statements!W36+Statements!W37+Statements!W39</f>
         <v>90509</v>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="C9" s="170">
         <f>[1]Sheet1!$C$10/1000</f>
-        <v>4.3540000000000002E-2</v>
+        <v>4.3900000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="C10" s="145">
         <f>[1]Sheet1!$F$17</f>
-        <v>1.075</v>
+        <v>1.0647</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4159,10 +4159,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="212" t="s">
+      <c r="B15" s="211" t="s">
         <v>166</v>
       </c>
-      <c r="C15" s="212"/>
+      <c r="C15" s="211"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="C16" s="148">
         <f>C8/(C8+C7)</f>
-        <v>2.2297926790704917E-2</v>
+        <v>2.1164983908307792E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C17" s="148">
         <f>C7/(C8+C7)</f>
-        <v>0.97770207320929503</v>
+        <v>0.9788350160916921</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="C19" s="148">
         <f>C9+C10*C11</f>
-        <v>9.7290000000000001E-2</v>
+        <v>9.7134999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="C20" s="148">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>9.5913325999941873E-2</v>
+        <v>9.5831554466006844E-2</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4260,60 +4260,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="212" t="s">
+      <c r="C3" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="212"/>
-      <c r="G3" s="213"/>
-      <c r="H3" s="214" t="s">
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="215" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="212"/>
-      <c r="J3" s="212"/>
-      <c r="K3" s="212"/>
-      <c r="L3" s="212"/>
-      <c r="P3" s="215"/>
-      <c r="Q3" s="215"/>
-      <c r="R3" s="215"/>
-      <c r="S3" s="215"/>
-      <c r="T3" s="215"/>
-      <c r="U3" s="215"/>
-      <c r="V3" s="215"/>
-      <c r="W3" s="215"/>
-      <c r="X3" s="215"/>
-      <c r="Y3" s="215"/>
-      <c r="Z3" s="215"/>
+      <c r="I3" s="211"/>
+      <c r="J3" s="211"/>
+      <c r="K3" s="211"/>
+      <c r="L3" s="211"/>
+      <c r="P3" s="217"/>
+      <c r="Q3" s="217"/>
+      <c r="R3" s="217"/>
+      <c r="S3" s="217"/>
+      <c r="T3" s="217"/>
+      <c r="U3" s="217"/>
+      <c r="V3" s="217"/>
+      <c r="W3" s="217"/>
+      <c r="X3" s="217"/>
+      <c r="Y3" s="217"/>
+      <c r="Z3" s="217"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="211" t="s">
+      <c r="C5" s="216" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="211"/>
-      <c r="E5" s="211"/>
-      <c r="F5" s="211"/>
-      <c r="G5" s="211"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="211"/>
-      <c r="K5" s="211"/>
-      <c r="L5" s="211"/>
-      <c r="P5" s="215"/>
-      <c r="Q5" s="215"/>
-      <c r="R5" s="215"/>
-      <c r="S5" s="215"/>
-      <c r="T5" s="215"/>
-      <c r="U5" s="215"/>
-      <c r="V5" s="215"/>
-      <c r="W5" s="215"/>
-      <c r="X5" s="215"/>
-      <c r="Y5" s="215"/>
-      <c r="Z5" s="215"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="216"/>
+      <c r="K5" s="216"/>
+      <c r="L5" s="216"/>
+      <c r="P5" s="217"/>
+      <c r="Q5" s="217"/>
+      <c r="R5" s="217"/>
+      <c r="S5" s="217"/>
+      <c r="T5" s="217"/>
+      <c r="U5" s="217"/>
+      <c r="V5" s="217"/>
+      <c r="W5" s="217"/>
+      <c r="X5" s="217"/>
+      <c r="Y5" s="217"/>
+      <c r="Z5" s="217"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -4559,10 +4559,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="212" t="s">
+      <c r="B13" s="211" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="212"/>
+      <c r="C13" s="211"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -4582,10 +4582,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="212" t="s">
+      <c r="B18" s="211" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="212"/>
+      <c r="C18" s="211"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -4619,7 +4619,7 @@
         <v>174</v>
       </c>
       <c r="C22" s="20">
-        <f>Statements!W21+Statements!W27</f>
+        <f>Statements!W22+Statements!W28</f>
         <v>144795</v>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
         <v>175</v>
       </c>
       <c r="C23" s="20">
-        <f>Statements!W35+Statements!W36+Statements!W38</f>
+        <f>Statements!W36+Statements!W37+Statements!W39</f>
         <v>90509</v>
       </c>
     </row>
@@ -4699,37 +4699,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="212"/>
-      <c r="F2" s="212"/>
-      <c r="G2" s="213"/>
-      <c r="H2" s="214" t="s">
+      <c r="D2" s="211"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="215" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="212"/>
-      <c r="J2" s="212"/>
-      <c r="K2" s="212"/>
-      <c r="L2" s="212"/>
+      <c r="I2" s="211"/>
+      <c r="J2" s="211"/>
+      <c r="K2" s="211"/>
+      <c r="L2" s="211"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="211" t="s">
+      <c r="C4" s="216" t="s">
         <v>318</v>
       </c>
-      <c r="D4" s="211"/>
-      <c r="E4" s="211"/>
-      <c r="F4" s="211"/>
-      <c r="G4" s="211"/>
-      <c r="H4" s="211"/>
-      <c r="I4" s="211"/>
-      <c r="J4" s="211"/>
-      <c r="K4" s="211"/>
-      <c r="L4" s="211"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -4918,18 +4918,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="211" t="s">
+      <c r="C10" s="216" t="s">
         <v>116</v>
       </c>
-      <c r="D10" s="211"/>
-      <c r="E10" s="211"/>
-      <c r="F10" s="211"/>
-      <c r="G10" s="211"/>
-      <c r="H10" s="211"/>
-      <c r="I10" s="211"/>
-      <c r="J10" s="211"/>
-      <c r="K10" s="211"/>
-      <c r="L10" s="211"/>
+      <c r="D10" s="216"/>
+      <c r="E10" s="216"/>
+      <c r="F10" s="216"/>
+      <c r="G10" s="216"/>
+      <c r="H10" s="216"/>
+      <c r="I10" s="216"/>
+      <c r="J10" s="216"/>
+      <c r="K10" s="216"/>
+      <c r="L10" s="216"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5111,18 +5111,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="211" t="s">
+      <c r="C16" s="216" t="s">
         <v>217</v>
       </c>
-      <c r="D16" s="211"/>
-      <c r="E16" s="211"/>
-      <c r="F16" s="211"/>
-      <c r="G16" s="211"/>
-      <c r="H16" s="211"/>
-      <c r="I16" s="211"/>
-      <c r="J16" s="211"/>
-      <c r="K16" s="211"/>
-      <c r="L16" s="211"/>
+      <c r="D16" s="216"/>
+      <c r="E16" s="216"/>
+      <c r="F16" s="216"/>
+      <c r="G16" s="216"/>
+      <c r="H16" s="216"/>
+      <c r="I16" s="216"/>
+      <c r="J16" s="216"/>
+      <c r="K16" s="216"/>
+      <c r="L16" s="216"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -5256,18 +5256,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="211" t="s">
+      <c r="C21" s="216" t="s">
         <v>319</v>
       </c>
-      <c r="D21" s="211"/>
-      <c r="E21" s="211"/>
-      <c r="F21" s="211"/>
-      <c r="G21" s="211"/>
-      <c r="H21" s="211"/>
-      <c r="I21" s="211"/>
-      <c r="J21" s="211"/>
-      <c r="K21" s="211"/>
-      <c r="L21" s="211"/>
+      <c r="D21" s="216"/>
+      <c r="E21" s="216"/>
+      <c r="F21" s="216"/>
+      <c r="G21" s="216"/>
+      <c r="H21" s="216"/>
+      <c r="I21" s="216"/>
+      <c r="J21" s="216"/>
+      <c r="K21" s="216"/>
+      <c r="L21" s="216"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -5351,18 +5351,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="211" t="s">
+      <c r="C26" s="216" t="s">
         <v>320</v>
       </c>
-      <c r="D26" s="211"/>
-      <c r="E26" s="211"/>
-      <c r="F26" s="211"/>
-      <c r="G26" s="211"/>
-      <c r="H26" s="211"/>
-      <c r="I26" s="211"/>
-      <c r="J26" s="211"/>
-      <c r="K26" s="211"/>
-      <c r="L26" s="211"/>
+      <c r="D26" s="216"/>
+      <c r="E26" s="216"/>
+      <c r="F26" s="216"/>
+      <c r="G26" s="216"/>
+      <c r="H26" s="216"/>
+      <c r="I26" s="216"/>
+      <c r="J26" s="216"/>
+      <c r="K26" s="216"/>
+      <c r="L26" s="216"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -5475,23 +5475,23 @@
         <v>146</v>
       </c>
       <c r="C30" s="103">
-        <f>Statements!H35+Statements!H36+Statements!H38</f>
+        <f>Statements!H36+Statements!H37+Statements!H39</f>
         <v>124719</v>
       </c>
       <c r="D30" s="191">
-        <f>Statements!I35+Statements!I36+Statements!I38</f>
+        <f>Statements!I36+Statements!I37+Statements!I39</f>
         <v>120069</v>
       </c>
       <c r="E30" s="191">
-        <f>Statements!J35+Statements!J36+Statements!J38</f>
+        <f>Statements!J36+Statements!J37+Statements!J39</f>
         <v>111088</v>
       </c>
       <c r="F30" s="191">
-        <f>Statements!K35+Statements!K36+Statements!K38</f>
+        <f>Statements!K36+Statements!K37+Statements!K39</f>
         <v>106629</v>
       </c>
       <c r="G30" s="192">
-        <f>Statements!L35+Statements!L36+Statements!L38</f>
+        <f>Statements!L36+Statements!L37+Statements!L39</f>
         <v>98657</v>
       </c>
       <c r="H30" s="130"/>
@@ -5506,23 +5506,23 @@
         <v>150</v>
       </c>
       <c r="C31" s="191">
-        <f>Statements!H21</f>
+        <f>Statements!H22</f>
         <v>62639</v>
       </c>
       <c r="D31" s="191">
-        <f>Statements!I21</f>
+        <f>Statements!I22</f>
         <v>48304</v>
       </c>
       <c r="E31" s="191">
-        <f>Statements!J21</f>
+        <f>Statements!J22</f>
         <v>61555</v>
       </c>
       <c r="F31" s="191">
-        <f>Statements!K21</f>
+        <f>Statements!K22</f>
         <v>65171</v>
       </c>
       <c r="G31" s="192">
-        <f>Statements!L21</f>
+        <f>Statements!L22</f>
         <v>54697</v>
       </c>
       <c r="H31" s="130"/>
@@ -5632,10 +5632,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="212" t="s">
+      <c r="B37" s="211" t="s">
         <v>324</v>
       </c>
-      <c r="C37" s="212"/>
+      <c r="C37" s="211"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -5701,10 +5701,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="212" t="s">
+      <c r="B46" s="211" t="s">
         <v>193</v>
       </c>
-      <c r="C46" s="212"/>
+      <c r="C46" s="211"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -5760,10 +5760,10 @@
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="212" t="s">
+      <c r="B54" s="211" t="s">
         <v>328</v>
       </c>
-      <c r="C54" s="212"/>
+      <c r="C54" s="211"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -5873,10 +5873,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="212" t="s">
+      <c r="B4" s="211" t="s">
         <v>201</v>
       </c>
-      <c r="C4" s="212"/>
+      <c r="C4" s="211"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C10" s="35">
         <f>Overview!C3</f>
-        <v>270.32</v>
+        <v>285.12</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="C11" s="89">
         <f>(C9-C10)/C10</f>
-        <v>-0.2596737617205867</v>
+        <v>-0.29810259283217244</v>
       </c>
     </row>
   </sheetData>
@@ -5983,60 +5983,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="212" t="s">
+      <c r="C3" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="212"/>
-      <c r="G3" s="213"/>
-      <c r="H3" s="214" t="s">
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="215" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="212"/>
-      <c r="J3" s="212"/>
-      <c r="K3" s="212"/>
-      <c r="L3" s="212"/>
-      <c r="P3" s="215"/>
-      <c r="Q3" s="215"/>
-      <c r="R3" s="215"/>
-      <c r="S3" s="215"/>
-      <c r="T3" s="215"/>
-      <c r="U3" s="215"/>
-      <c r="V3" s="215"/>
-      <c r="W3" s="215"/>
-      <c r="X3" s="215"/>
-      <c r="Y3" s="215"/>
-      <c r="Z3" s="215"/>
+      <c r="I3" s="211"/>
+      <c r="J3" s="211"/>
+      <c r="K3" s="211"/>
+      <c r="L3" s="211"/>
+      <c r="P3" s="217"/>
+      <c r="Q3" s="217"/>
+      <c r="R3" s="217"/>
+      <c r="S3" s="217"/>
+      <c r="T3" s="217"/>
+      <c r="U3" s="217"/>
+      <c r="V3" s="217"/>
+      <c r="W3" s="217"/>
+      <c r="X3" s="217"/>
+      <c r="Y3" s="217"/>
+      <c r="Z3" s="217"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="211" t="s">
+      <c r="C5" s="216" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="211"/>
-      <c r="E5" s="211"/>
-      <c r="F5" s="211"/>
-      <c r="G5" s="211"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="211"/>
-      <c r="K5" s="211"/>
-      <c r="L5" s="211"/>
-      <c r="P5" s="215"/>
-      <c r="Q5" s="215"/>
-      <c r="R5" s="215"/>
-      <c r="S5" s="215"/>
-      <c r="T5" s="215"/>
-      <c r="U5" s="215"/>
-      <c r="V5" s="215"/>
-      <c r="W5" s="215"/>
-      <c r="X5" s="215"/>
-      <c r="Y5" s="215"/>
-      <c r="Z5" s="215"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="216"/>
+      <c r="K5" s="216"/>
+      <c r="L5" s="216"/>
+      <c r="P5" s="217"/>
+      <c r="Q5" s="217"/>
+      <c r="R5" s="217"/>
+      <c r="S5" s="217"/>
+      <c r="T5" s="217"/>
+      <c r="U5" s="217"/>
+      <c r="V5" s="217"/>
+      <c r="W5" s="217"/>
+      <c r="X5" s="217"/>
+      <c r="Y5" s="217"/>
+      <c r="Z5" s="217"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -6265,10 +6265,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="208" t="s">
+      <c r="B14" s="218" t="s">
         <v>334</v>
       </c>
-      <c r="C14" s="209"/>
+      <c r="C14" s="219"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="193" t="s">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="C15" s="194">
         <f>Overview!C3</f>
-        <v>270.32</v>
+        <v>285.12</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6295,20 +6295,20 @@
       <c r="C17" s="196">
         <v>0.245</v>
       </c>
-      <c r="E17" s="210" t="s">
+      <c r="E17" s="220" t="s">
         <v>338</v>
       </c>
-      <c r="F17" s="210"/>
-      <c r="G17" s="210"/>
-      <c r="H17" s="210"/>
-      <c r="I17" s="210"/>
+      <c r="F17" s="220"/>
+      <c r="G17" s="220"/>
+      <c r="H17" s="220"/>
+      <c r="I17" s="220"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="208" t="s">
+      <c r="B19" s="218" t="s">
         <v>181</v>
       </c>
-      <c r="C19" s="209"/>
+      <c r="C19" s="219"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="197" t="s">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="C23" s="200">
         <f>C15*C22</f>
-        <v>3968567.92</v>
+        <v>4185846.72</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6350,7 +6350,7 @@
         <v>150</v>
       </c>
       <c r="C24" s="200">
-        <f>Statements!W21+Statements!W27</f>
+        <f>Statements!W22+Statements!W28</f>
         <v>144795</v>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
         <v>146</v>
       </c>
       <c r="C25" s="200">
-        <f>Statements!W35+Statements!W36+Statements!W38</f>
+        <f>Statements!W36+Statements!W37+Statements!W39</f>
         <v>90509</v>
       </c>
     </row>
@@ -6369,15 +6369,15 @@
       </c>
       <c r="C26" s="201">
         <f>C23+C25-C24</f>
-        <v>3914281.92</v>
+        <v>4131560.7200000007</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="208" t="s">
+      <c r="B28" s="218" t="s">
         <v>80</v>
       </c>
-      <c r="C28" s="209"/>
+      <c r="C28" s="219"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="197" t="s">
@@ -6411,7 +6411,7 @@
         <v>174</v>
       </c>
       <c r="C32" s="204">
-        <f>Statements!W21+Statements!W27</f>
+        <f>Statements!W22+Statements!W28</f>
         <v>144795</v>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
         <v>175</v>
       </c>
       <c r="C33" s="204">
-        <f>Statements!W35+Statements!W36+Statements!W38</f>
+        <f>Statements!W36+Statements!W37+Statements!W39</f>
         <v>90509</v>
       </c>
     </row>
@@ -6452,18 +6452,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="211" t="s">
+      <c r="C39" s="216" t="s">
         <v>340</v>
       </c>
-      <c r="D39" s="211"/>
-      <c r="E39" s="211"/>
-      <c r="F39" s="211"/>
-      <c r="G39" s="211"/>
-      <c r="H39" s="211"/>
-      <c r="I39" s="211"/>
-      <c r="J39" s="211"/>
-      <c r="K39" s="211"/>
-      <c r="L39" s="211"/>
+      <c r="D39" s="216"/>
+      <c r="E39" s="216"/>
+      <c r="F39" s="216"/>
+      <c r="G39" s="216"/>
+      <c r="H39" s="216"/>
+      <c r="I39" s="216"/>
+      <c r="J39" s="216"/>
+      <c r="K39" s="216"/>
+      <c r="L39" s="216"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="62">
@@ -13291,11 +13291,11 @@
         <v>75</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="216" t="s">
+      <c r="P4" s="208" t="s">
         <v>76</v>
       </c>
-      <c r="Q4" s="217"/>
-      <c r="R4" s="218"/>
+      <c r="Q4" s="209"/>
+      <c r="R4" s="210"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -17036,7 +17036,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8047DB4-BCDE-EC47-A3C5-C98010D5458E}">
-  <dimension ref="B2:W89"/>
+  <dimension ref="B2:W91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
@@ -17388,7 +17388,7 @@
         <v>74525</v>
       </c>
       <c r="W6" s="133">
-        <f t="shared" ref="W6:W16" si="0">SUM(R6:U6)</f>
+        <f t="shared" ref="W6:W17" si="0">SUM(R6:U6)</f>
         <v>229460</v>
       </c>
     </row>
@@ -17802,7 +17802,7 @@
         <v>215</v>
       </c>
       <c r="C12" s="169">
-        <f t="shared" ref="C12:L12" si="1">C11+C50</f>
+        <f t="shared" ref="C12:L12" si="1">C11+C51</f>
         <v>70529</v>
       </c>
       <c r="D12" s="169">
@@ -17842,7 +17842,7 @@
         <v>144748</v>
       </c>
       <c r="N12" s="169">
-        <f t="shared" ref="N12:U12" si="2">N11+N50</f>
+        <f t="shared" ref="N12:U12" si="2">N11+N51</f>
         <v>27900</v>
       </c>
       <c r="O12" s="169">
@@ -17879,5373 +17879,5481 @@
       </c>
     </row>
     <row r="13" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="78" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="169">
+        <f>C11*(1-'Statement Y'!C119)</f>
+        <v>44683.511829498791</v>
+      </c>
+      <c r="D13" s="169">
+        <f>D11*(1-'Statement Y'!D119)</f>
+        <v>46280.075270327201</v>
+      </c>
+      <c r="E13" s="169">
+        <f>E11*(1-'Statement Y'!E119)</f>
+        <v>57893.760723152685</v>
+      </c>
+      <c r="F13" s="169">
+        <f>F11*(1-'Statement Y'!F119)</f>
+        <v>53737.105131052529</v>
+      </c>
+      <c r="G13" s="169">
+        <f>G11*(1-'Statement Y'!G119)</f>
+        <v>56723.858162793818</v>
+      </c>
+      <c r="H13" s="169">
+        <f>H11*(1-'Statement Y'!H119)</f>
+        <v>94456.319832977737</v>
+      </c>
+      <c r="I13" s="169">
+        <f>I11*(1-'Statement Y'!I119)</f>
+        <v>100082.87709797402</v>
+      </c>
+      <c r="J13" s="169">
+        <f>J11*(1-'Statement Y'!J119)</f>
+        <v>97476.836665611598</v>
+      </c>
+      <c r="K13" s="169">
+        <f>K11*(1-'Statement Y'!K119)</f>
+        <v>93531.80528809168</v>
+      </c>
+      <c r="L13" s="169">
+        <f>L11*(1-'Statement Y'!L119)</f>
+        <v>112280.89189250277</v>
+      </c>
+      <c r="N13" s="169"/>
+      <c r="O13" s="169"/>
+      <c r="P13" s="169"/>
+      <c r="Q13" s="169"/>
+      <c r="R13" s="169"/>
+      <c r="S13" s="169"/>
+      <c r="T13" s="169"/>
+      <c r="U13" s="169"/>
+      <c r="W13" s="169"/>
+    </row>
+    <row r="14" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="C13" s="133">
+      <c r="C14" s="133">
         <f>'Statement Y'!C12</f>
         <v>1348</v>
       </c>
-      <c r="D13" s="133">
+      <c r="D14" s="133">
         <f>'Statement Y'!D12</f>
         <v>2745</v>
       </c>
-      <c r="E13" s="133">
+      <c r="E14" s="133">
         <f>'Statement Y'!E12</f>
         <v>2005</v>
       </c>
-      <c r="F13" s="133">
+      <c r="F14" s="133">
         <f>'Statement Y'!F12</f>
         <v>1807</v>
       </c>
-      <c r="G13" s="133">
+      <c r="G14" s="133">
         <f>'Statement Y'!G12</f>
         <v>803</v>
       </c>
-      <c r="H13" s="133">
+      <c r="H14" s="133">
         <f>'Statement Y'!H12</f>
         <v>258</v>
       </c>
-      <c r="I13" s="133">
+      <c r="I14" s="133">
         <f>'Statement Y'!I12</f>
         <v>-334</v>
       </c>
-      <c r="J13" s="133">
+      <c r="J14" s="133">
         <f>'Statement Y'!J12</f>
         <v>-565</v>
       </c>
-      <c r="K13" s="133">
+      <c r="K14" s="133">
         <f>'Statement Y'!K12</f>
         <v>269</v>
       </c>
-      <c r="L13" s="133">
+      <c r="L14" s="133">
         <f>'Statement Y'!L12</f>
         <v>-321</v>
       </c>
-      <c r="N13" s="133">
+      <c r="N14" s="133">
         <f>'Statement Q'!C12</f>
         <v>158</v>
       </c>
-      <c r="O13" s="133">
+      <c r="O14" s="133">
         <f>'Statement Q'!D12</f>
         <v>142</v>
       </c>
-      <c r="P13" s="133">
+      <c r="P14" s="133">
         <f>'Statement Q'!E12</f>
         <v>19</v>
       </c>
-      <c r="Q13" s="133">
+      <c r="Q14" s="133">
         <f>'Statement Q'!F12</f>
         <v>-248</v>
       </c>
-      <c r="R13" s="133">
+      <c r="R14" s="133">
         <f>'Statement Q'!G12</f>
         <v>-279</v>
       </c>
-      <c r="S13" s="133">
+      <c r="S14" s="133">
         <f>'Statement Q'!H12</f>
         <v>-171</v>
       </c>
-      <c r="T13" s="133">
+      <c r="T14" s="133">
         <f>'Statement Q'!I12</f>
         <v>377</v>
       </c>
-      <c r="U13" s="133">
+      <c r="U14" s="133">
         <f>'Statement Q'!J12</f>
         <v>150</v>
       </c>
-      <c r="W13" s="133">
+      <c r="W14" s="133">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="17" t="s">
+    <row r="15" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="153">
+      <c r="C15" s="153">
         <f>'Statement Y'!C13</f>
         <v>61372</v>
       </c>
-      <c r="D14" s="153">
+      <c r="D15" s="153">
         <f>'Statement Y'!D13</f>
         <v>64089</v>
       </c>
-      <c r="E14" s="153">
+      <c r="E15" s="153">
         <f>'Statement Y'!E13</f>
         <v>72903</v>
       </c>
-      <c r="F14" s="153">
+      <c r="F15" s="153">
         <f>'Statement Y'!F13</f>
         <v>65737</v>
       </c>
-      <c r="G14" s="153">
+      <c r="G15" s="153">
         <f>'Statement Y'!G13</f>
         <v>67091</v>
       </c>
-      <c r="H14" s="153">
+      <c r="H15" s="153">
         <f>'Statement Y'!H13</f>
         <v>109207</v>
       </c>
-      <c r="I14" s="153">
+      <c r="I15" s="153">
         <f>'Statement Y'!I13</f>
         <v>119103</v>
       </c>
-      <c r="J14" s="153">
+      <c r="J15" s="153">
         <f>'Statement Y'!J13</f>
         <v>113736</v>
       </c>
-      <c r="K14" s="153">
+      <c r="K15" s="153">
         <f>'Statement Y'!K13</f>
         <v>123485</v>
       </c>
-      <c r="L14" s="153">
+      <c r="L15" s="153">
         <f>'Statement Y'!L13</f>
         <v>132729</v>
       </c>
-      <c r="N14" s="153">
+      <c r="N15" s="153">
         <f>'Statement Q'!C13</f>
         <v>28058</v>
       </c>
-      <c r="O14" s="153">
+      <c r="O15" s="153">
         <f>'Statement Q'!D13</f>
         <v>25494</v>
       </c>
-      <c r="P14" s="153">
+      <c r="P15" s="153">
         <f>'Statement Q'!E13</f>
         <v>29610</v>
       </c>
-      <c r="Q14" s="153">
+      <c r="Q15" s="153">
         <f>'Statement Q'!F13</f>
         <v>42584</v>
       </c>
-      <c r="R14" s="153">
+      <c r="R15" s="153">
         <f>'Statement Q'!G13</f>
         <v>29310</v>
       </c>
-      <c r="S14" s="153">
+      <c r="S15" s="153">
         <f>'Statement Q'!H13</f>
         <v>28031</v>
       </c>
-      <c r="T14" s="153">
+      <c r="T15" s="153">
         <f>'Statement Q'!I13</f>
         <v>32804</v>
       </c>
-      <c r="U14" s="153">
+      <c r="U15" s="153">
         <f>'Statement Q'!J13</f>
         <v>51002</v>
       </c>
-      <c r="W14" s="153">
+      <c r="W15" s="153">
         <f t="shared" si="0"/>
         <v>141147</v>
       </c>
     </row>
-    <row r="15" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="12" t="s">
+    <row r="16" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="133">
+      <c r="C16" s="133">
         <f>'Statement Y'!C14</f>
         <v>-15685</v>
       </c>
-      <c r="D15" s="133">
+      <c r="D16" s="133">
         <f>'Statement Y'!D14</f>
         <v>-15738</v>
       </c>
-      <c r="E15" s="133">
+      <c r="E16" s="133">
         <f>'Statement Y'!E14</f>
         <v>-13372</v>
       </c>
-      <c r="F15" s="133">
+      <c r="F16" s="133">
         <f>'Statement Y'!F14</f>
         <v>-10481</v>
       </c>
-      <c r="G15" s="133">
+      <c r="G16" s="133">
         <f>'Statement Y'!G14</f>
         <v>-9680</v>
       </c>
-      <c r="H15" s="133">
+      <c r="H16" s="133">
         <f>'Statement Y'!H14</f>
         <v>-14527</v>
       </c>
-      <c r="I15" s="133">
+      <c r="I16" s="133">
         <f>'Statement Y'!I14</f>
         <v>-19300</v>
       </c>
-      <c r="J15" s="133">
+      <c r="J16" s="133">
         <f>'Statement Y'!J14</f>
         <v>-16741</v>
       </c>
-      <c r="K15" s="133">
+      <c r="K16" s="133">
         <f>'Statement Y'!K14</f>
         <v>-29749</v>
       </c>
-      <c r="L15" s="133">
+      <c r="L16" s="133">
         <f>'Statement Y'!L14</f>
         <v>-20719</v>
       </c>
-      <c r="N15" s="133">
+      <c r="N16" s="133">
         <f>'Statement Q'!C14</f>
         <v>-4422</v>
       </c>
-      <c r="O15" s="133">
+      <c r="O16" s="133">
         <f>'Statement Q'!D14</f>
         <v>-4046</v>
       </c>
-      <c r="P15" s="133">
+      <c r="P16" s="133">
         <f>'Statement Q'!E14</f>
         <v>-14874</v>
       </c>
-      <c r="Q15" s="133">
+      <c r="Q16" s="133">
         <f>'Statement Q'!F14</f>
         <v>-6254</v>
       </c>
-      <c r="R15" s="133">
+      <c r="R16" s="133">
         <f>'Statement Q'!G14</f>
         <v>-4530</v>
       </c>
-      <c r="S15" s="133">
+      <c r="S16" s="133">
         <f>'Statement Q'!H14</f>
         <v>-4597</v>
       </c>
-      <c r="T15" s="133">
+      <c r="T16" s="133">
         <f>'Statement Q'!I14</f>
         <v>-5338</v>
       </c>
-      <c r="U15" s="133">
+      <c r="U16" s="133">
         <f>'Statement Q'!J14</f>
         <v>-8905</v>
       </c>
-      <c r="W15" s="133">
+      <c r="W16" s="133">
         <f t="shared" si="0"/>
         <v>-23370</v>
       </c>
     </row>
-    <row r="16" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="17" t="s">
+    <row r="17" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="153">
+      <c r="C17" s="153">
         <f>'Statement Y'!C15</f>
         <v>45687</v>
       </c>
-      <c r="D16" s="153">
+      <c r="D17" s="153">
         <f>'Statement Y'!D15</f>
         <v>48351</v>
       </c>
-      <c r="E16" s="153">
+      <c r="E17" s="153">
         <f>'Statement Y'!E15</f>
         <v>59531</v>
       </c>
-      <c r="F16" s="153">
+      <c r="F17" s="153">
         <f>'Statement Y'!F15</f>
         <v>55256</v>
       </c>
-      <c r="G16" s="153">
+      <c r="G17" s="153">
         <f>'Statement Y'!G15</f>
         <v>57411</v>
       </c>
-      <c r="H16" s="153">
+      <c r="H17" s="153">
         <f>'Statement Y'!H15</f>
         <v>94680</v>
       </c>
-      <c r="I16" s="153">
+      <c r="I17" s="153">
         <f>'Statement Y'!I15</f>
         <v>99803</v>
       </c>
-      <c r="J16" s="153">
+      <c r="J17" s="153">
         <f>'Statement Y'!J15</f>
         <v>96995</v>
       </c>
-      <c r="K16" s="153">
+      <c r="K17" s="153">
         <f>'Statement Y'!K15</f>
         <v>93736</v>
       </c>
-      <c r="L16" s="153">
+      <c r="L17" s="153">
         <f>'Statement Y'!L15</f>
         <v>112010</v>
       </c>
-      <c r="N16" s="153">
+      <c r="N17" s="153">
         <f>'Statement Q'!C15</f>
         <v>23636</v>
       </c>
-      <c r="O16" s="153">
+      <c r="O17" s="153">
         <f>'Statement Q'!D15</f>
         <v>21448</v>
       </c>
-      <c r="P16" s="153">
+      <c r="P17" s="153">
         <f>'Statement Q'!E15</f>
         <v>14736</v>
       </c>
-      <c r="Q16" s="153">
+      <c r="Q17" s="153">
         <f>'Statement Q'!F15</f>
         <v>36330</v>
       </c>
-      <c r="R16" s="153">
+      <c r="R17" s="153">
         <f>'Statement Q'!G15</f>
         <v>24780</v>
       </c>
-      <c r="S16" s="153">
+      <c r="S17" s="153">
         <f>'Statement Q'!H15</f>
         <v>23434</v>
       </c>
-      <c r="T16" s="153">
+      <c r="T17" s="153">
         <f>'Statement Q'!I15</f>
         <v>27466</v>
       </c>
-      <c r="U16" s="153">
+      <c r="U17" s="153">
         <f>'Statement Q'!J15</f>
         <v>42097</v>
       </c>
-      <c r="W16" s="153">
+      <c r="W17" s="153">
         <f t="shared" si="0"/>
         <v>117777</v>
       </c>
     </row>
-    <row r="17" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="12" t="s">
+    <row r="18" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="133">
+      <c r="C18" s="133">
         <f>'Statement Y'!C19</f>
         <v>22000</v>
       </c>
-      <c r="D17" s="133">
+      <c r="D18" s="133">
         <f>'Statement Y'!D19</f>
         <v>21008</v>
       </c>
-      <c r="E17" s="133">
+      <c r="E18" s="133">
         <f>'Statement Y'!E19</f>
         <v>20000</v>
       </c>
-      <c r="F17" s="133">
+      <c r="F18" s="133">
         <f>'Statement Y'!F19</f>
         <v>18596</v>
       </c>
-      <c r="G17" s="133">
+      <c r="G18" s="133">
         <f>'Statement Y'!G19</f>
         <v>17528</v>
       </c>
-      <c r="H17" s="133">
+      <c r="H18" s="133">
         <f>'Statement Y'!H19</f>
         <v>16865</v>
       </c>
-      <c r="I17" s="133">
+      <c r="I18" s="133">
         <f>'Statement Y'!I19</f>
         <v>16326</v>
       </c>
-      <c r="J17" s="133">
+      <c r="J18" s="133">
         <f>'Statement Y'!J19</f>
         <v>15813</v>
       </c>
-      <c r="K17" s="133">
+      <c r="K18" s="133">
         <f>'Statement Y'!K19</f>
         <v>15408</v>
       </c>
-      <c r="L17" s="133">
+      <c r="L18" s="133">
         <f>'Statement Y'!L19</f>
         <v>15005</v>
       </c>
-      <c r="N17" s="133">
+      <c r="N18" s="133">
         <f>'Statement Q'!C17</f>
         <v>15465</v>
       </c>
-      <c r="O17" s="133">
+      <c r="O18" s="133">
         <f>'Statement Q'!D17</f>
         <v>15348</v>
       </c>
-      <c r="P17" s="133">
+      <c r="P18" s="133">
         <f>'Statement Q'!E17</f>
         <v>15242</v>
       </c>
-      <c r="Q17" s="133">
+      <c r="Q18" s="133">
         <f>'Statement Q'!F17</f>
         <v>15151</v>
       </c>
-      <c r="R17" s="133">
+      <c r="R18" s="133">
         <f>'Statement Q'!G17</f>
         <v>15056</v>
       </c>
-      <c r="S17" s="133">
+      <c r="S18" s="133">
         <f>'Statement Q'!H17</f>
         <v>14948</v>
       </c>
-      <c r="T17" s="133">
+      <c r="T18" s="133">
         <f>'Statement Q'!I17</f>
         <v>14864</v>
       </c>
-      <c r="U17" s="133">
+      <c r="U18" s="133">
         <f>'Statement Q'!J17</f>
         <v>14810</v>
       </c>
-      <c r="W17" s="133">
-        <f>AVERAGE(R17:U17)</f>
+      <c r="W18" s="133">
+        <f>AVERAGE(R18:U18)</f>
         <v>14919.5</v>
       </c>
     </row>
-    <row r="18" spans="2:23" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
+    <row r="19" spans="2:23" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="154">
+      <c r="C19" s="154">
         <f>'Statement Y'!C23</f>
         <v>2.0775000000000001</v>
       </c>
-      <c r="D18" s="154">
+      <c r="D19" s="154">
         <f>'Statement Y'!D23</f>
         <v>2.3025000000000002</v>
       </c>
-      <c r="E18" s="154">
+      <c r="E19" s="154">
         <f>'Statement Y'!E23</f>
         <v>2.9775</v>
       </c>
-      <c r="F18" s="154">
+      <c r="F19" s="154">
         <f>'Statement Y'!F23</f>
         <v>2.9725000000000001</v>
       </c>
-      <c r="G18" s="154">
+      <c r="G19" s="154">
         <f>'Statement Y'!G23</f>
         <v>3.28</v>
       </c>
-      <c r="H18" s="154">
+      <c r="H19" s="154">
         <f>'Statement Y'!H23</f>
         <v>5.61</v>
       </c>
-      <c r="I18" s="154">
+      <c r="I19" s="154">
         <f>'Statement Y'!I23</f>
         <v>6.11</v>
       </c>
-      <c r="J18" s="154">
+      <c r="J19" s="154">
         <f>'Statement Y'!J23</f>
         <v>6.13</v>
       </c>
-      <c r="K18" s="154">
+      <c r="K19" s="154">
         <f>'Statement Y'!K23</f>
         <v>6.08</v>
       </c>
-      <c r="L18" s="154">
+      <c r="L19" s="154">
         <f>'Statement Y'!L23</f>
         <v>7.46</v>
       </c>
-      <c r="N18" s="155">
+      <c r="N19" s="155">
         <f>'Statement Q'!C19</f>
         <v>1.53</v>
       </c>
-      <c r="O18" s="155">
+      <c r="O19" s="155">
         <f>'Statement Q'!D19</f>
         <v>1.4</v>
       </c>
-      <c r="P18" s="155">
+      <c r="P19" s="155">
         <f>'Statement Q'!E19</f>
         <v>0.97</v>
       </c>
-      <c r="Q18" s="155">
+      <c r="Q19" s="155">
         <f>'Statement Q'!F19</f>
         <v>2.4</v>
       </c>
-      <c r="R18" s="155">
+      <c r="R19" s="155">
         <f>'Statement Q'!G19</f>
         <v>1.65</v>
       </c>
-      <c r="S18" s="155">
+      <c r="S19" s="155">
         <f>'Statement Q'!H19</f>
         <v>1.57</v>
       </c>
-      <c r="T18" s="155">
+      <c r="T19" s="155">
         <f>'Statement Q'!I19</f>
         <v>1.85</v>
       </c>
-      <c r="U18" s="155">
+      <c r="U19" s="155">
         <f>'Statement Q'!J19</f>
         <v>2.84</v>
       </c>
-      <c r="W18" s="155">
-        <f>W16/W17</f>
+      <c r="W19" s="155">
+        <f>W17/W18</f>
         <v>7.8941653540668257</v>
       </c>
     </row>
-    <row r="20" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="15" t="s">
+    <row r="21" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="W20" s="14"/>
-    </row>
-    <row r="21" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="9" t="s">
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="W21" s="14"/>
+    </row>
+    <row r="22" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="133">
+      <c r="C22" s="133">
         <f>'Statement Y'!C26+'Statement Y'!C27</f>
         <v>67155</v>
       </c>
-      <c r="D21" s="133">
+      <c r="D22" s="133">
         <f>'Statement Y'!D26+'Statement Y'!D27</f>
         <v>74181</v>
       </c>
-      <c r="E21" s="133">
+      <c r="E22" s="133">
         <f>'Statement Y'!E26+'Statement Y'!E27</f>
         <v>66301</v>
       </c>
-      <c r="F21" s="133">
+      <c r="F22" s="133">
         <f>'Statement Y'!F26+'Statement Y'!F27</f>
         <v>100557</v>
       </c>
-      <c r="G21" s="133">
+      <c r="G22" s="133">
         <f>'Statement Y'!G26+'Statement Y'!G27</f>
         <v>90943</v>
       </c>
-      <c r="H21" s="133">
+      <c r="H22" s="133">
         <f>'Statement Y'!H26+'Statement Y'!H27</f>
         <v>62639</v>
       </c>
-      <c r="I21" s="133">
+      <c r="I22" s="133">
         <f>'Statement Y'!I26+'Statement Y'!I27</f>
         <v>48304</v>
       </c>
-      <c r="J21" s="133">
+      <c r="J22" s="133">
         <f>'Statement Y'!J26+'Statement Y'!J27</f>
         <v>61555</v>
       </c>
-      <c r="K21" s="133">
+      <c r="K22" s="133">
         <f>'Statement Y'!K26+'Statement Y'!K27</f>
         <v>65171</v>
       </c>
-      <c r="L21" s="133">
+      <c r="L22" s="133">
         <f>'Statement Y'!L26+'Statement Y'!L27</f>
         <v>54697</v>
       </c>
-      <c r="N21" s="133">
+      <c r="N22" s="133">
         <f>'Statement Q'!C22+'Statement Q'!C23</f>
         <v>67150</v>
       </c>
-      <c r="O21" s="133">
+      <c r="O22" s="133">
         <f>'Statement Q'!D22+'Statement Q'!D23</f>
         <v>61801</v>
       </c>
-      <c r="P21" s="133">
+      <c r="P22" s="133">
         <f>'Statement Q'!E22+'Statement Q'!E23</f>
         <v>65171</v>
       </c>
-      <c r="Q21" s="133">
+      <c r="Q22" s="133">
         <f>'Statement Q'!F22+'Statement Q'!F23</f>
         <v>53775</v>
       </c>
-      <c r="R21" s="133">
+      <c r="R22" s="133">
         <f>'Statement Q'!G22+'Statement Q'!G23</f>
         <v>48498</v>
       </c>
-      <c r="S21" s="133">
+      <c r="S22" s="133">
         <f>'Statement Q'!H22+'Statement Q'!H23</f>
         <v>55372</v>
       </c>
-      <c r="T21" s="133">
+      <c r="T22" s="133">
         <f>'Statement Q'!I22+'Statement Q'!I23</f>
         <v>54697</v>
       </c>
-      <c r="U21" s="133">
+      <c r="U22" s="133">
         <f>'Statement Q'!J22+'Statement Q'!J23</f>
         <v>66907</v>
       </c>
-      <c r="W21" s="133">
-        <f>U21</f>
+      <c r="W22" s="133">
+        <f>U22</f>
         <v>66907</v>
       </c>
     </row>
-    <row r="22" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="9" t="s">
+    <row r="23" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="133">
+      <c r="C23" s="133">
         <f>'Statement Y'!C28</f>
         <v>15754</v>
       </c>
-      <c r="D22" s="133">
+      <c r="D23" s="133">
         <f>'Statement Y'!D28</f>
         <v>17874</v>
       </c>
-      <c r="E22" s="133">
+      <c r="E23" s="133">
         <f>'Statement Y'!E28</f>
         <v>23186</v>
       </c>
-      <c r="F22" s="133">
+      <c r="F23" s="133">
         <f>'Statement Y'!F28</f>
         <v>22926</v>
       </c>
-      <c r="G22" s="133">
+      <c r="G23" s="133">
         <f>'Statement Y'!G28</f>
         <v>16120</v>
       </c>
-      <c r="H22" s="133">
+      <c r="H23" s="133">
         <f>'Statement Y'!H28</f>
         <v>26278</v>
       </c>
-      <c r="I22" s="133">
+      <c r="I23" s="133">
         <f>'Statement Y'!I28</f>
         <v>28184</v>
       </c>
-      <c r="J22" s="133">
+      <c r="J23" s="133">
         <f>'Statement Y'!J28</f>
         <v>29508</v>
       </c>
-      <c r="K22" s="133">
+      <c r="K23" s="133">
         <f>'Statement Y'!K28</f>
         <v>33410</v>
       </c>
-      <c r="L22" s="133">
+      <c r="L23" s="133">
         <f>'Statement Y'!L28</f>
         <v>39777</v>
       </c>
-      <c r="N22" s="133">
+      <c r="N23" s="133">
         <f>'Statement Q'!C24</f>
         <v>21837</v>
       </c>
-      <c r="O22" s="133">
+      <c r="O23" s="133">
         <f>'Statement Q'!D24</f>
         <v>22795</v>
       </c>
-      <c r="P22" s="133">
+      <c r="P23" s="133">
         <f>'Statement Q'!E24</f>
         <v>33410</v>
       </c>
-      <c r="Q22" s="133">
+      <c r="Q23" s="133">
         <f>'Statement Q'!F24</f>
         <v>29639</v>
       </c>
-      <c r="R22" s="133">
+      <c r="R23" s="133">
         <f>'Statement Q'!G24</f>
         <v>26136</v>
       </c>
-      <c r="S22" s="133">
+      <c r="S23" s="133">
         <f>'Statement Q'!H24</f>
         <v>27557</v>
       </c>
-      <c r="T22" s="133">
+      <c r="T23" s="133">
         <f>'Statement Q'!I24</f>
         <v>39777</v>
       </c>
-      <c r="U22" s="133">
+      <c r="U23" s="133">
         <f>'Statement Q'!J24</f>
         <v>39921</v>
       </c>
-      <c r="W22" s="133">
-        <f t="shared" ref="W22:W46" si="3">U22</f>
+      <c r="W23" s="133">
+        <f t="shared" ref="W23:W47" si="3">U23</f>
         <v>39921</v>
       </c>
     </row>
-    <row r="23" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="9" t="s">
+    <row r="24" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="C23" s="133">
+      <c r="C24" s="133">
         <f>'Statement Y'!C29</f>
         <v>13545</v>
       </c>
-      <c r="D23" s="133">
+      <c r="D24" s="133">
         <f>'Statement Y'!D29</f>
         <v>17799</v>
       </c>
-      <c r="E23" s="133">
+      <c r="E24" s="133">
         <f>'Statement Y'!E29</f>
         <v>25809</v>
       </c>
-      <c r="F23" s="133">
+      <c r="F24" s="133">
         <f>'Statement Y'!F29</f>
         <v>22878</v>
       </c>
-      <c r="G23" s="133">
+      <c r="G24" s="133">
         <f>'Statement Y'!G29</f>
         <v>21325</v>
       </c>
-      <c r="H23" s="133">
+      <c r="H24" s="133">
         <f>'Statement Y'!H29</f>
         <v>25228</v>
       </c>
-      <c r="I23" s="133">
+      <c r="I24" s="133">
         <f>'Statement Y'!I29</f>
         <v>32748</v>
       </c>
-      <c r="J23" s="133">
+      <c r="J24" s="133">
         <f>'Statement Y'!J29</f>
         <v>31477</v>
       </c>
-      <c r="K23" s="133">
+      <c r="K24" s="133">
         <f>'Statement Y'!K29</f>
         <v>32833</v>
       </c>
-      <c r="L23" s="133">
+      <c r="L24" s="133">
         <f>'Statement Y'!L29</f>
         <v>33180</v>
       </c>
-      <c r="N23" s="133">
+      <c r="N24" s="133">
         <f>'Statement Q'!C25</f>
         <v>19313</v>
       </c>
-      <c r="O23" s="133">
+      <c r="O24" s="133">
         <f>'Statement Q'!D25</f>
         <v>20377</v>
       </c>
-      <c r="P23" s="133">
+      <c r="P24" s="133">
         <f>'Statement Q'!E25</f>
         <v>32833</v>
       </c>
-      <c r="Q23" s="133">
+      <c r="Q24" s="133">
         <f>'Statement Q'!F25</f>
         <v>29667</v>
       </c>
-      <c r="R23" s="133">
+      <c r="R24" s="133">
         <f>'Statement Q'!G25</f>
         <v>23662</v>
       </c>
-      <c r="S23" s="133">
+      <c r="S24" s="133">
         <f>'Statement Q'!H25</f>
         <v>19278</v>
       </c>
-      <c r="T23" s="133">
+      <c r="T24" s="133">
         <f>'Statement Q'!I25</f>
         <v>33180</v>
       </c>
-      <c r="U23" s="133">
+      <c r="U24" s="133">
         <f>'Statement Q'!J25</f>
         <v>30399</v>
       </c>
-      <c r="W23" s="133">
+      <c r="W24" s="133">
         <f t="shared" si="3"/>
         <v>30399</v>
       </c>
     </row>
-    <row r="24" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="9" t="s">
+    <row r="25" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="C24" s="133">
+      <c r="C25" s="133">
         <f>'Statement Y'!C30</f>
         <v>2132</v>
       </c>
-      <c r="D24" s="133">
+      <c r="D25" s="133">
         <f>'Statement Y'!D30</f>
         <v>4855</v>
       </c>
-      <c r="E24" s="133">
+      <c r="E25" s="133">
         <f>'Statement Y'!E30</f>
         <v>3956</v>
       </c>
-      <c r="F24" s="133">
+      <c r="F25" s="133">
         <f>'Statement Y'!F30</f>
         <v>4106</v>
       </c>
-      <c r="G24" s="133">
+      <c r="G25" s="133">
         <f>'Statement Y'!G30</f>
         <v>4061</v>
       </c>
-      <c r="H24" s="133">
+      <c r="H25" s="133">
         <f>'Statement Y'!H30</f>
         <v>6580</v>
       </c>
-      <c r="I24" s="133">
+      <c r="I25" s="133">
         <f>'Statement Y'!I30</f>
         <v>4946</v>
       </c>
-      <c r="J24" s="133">
+      <c r="J25" s="133">
         <f>'Statement Y'!J30</f>
         <v>6331</v>
       </c>
-      <c r="K24" s="133">
+      <c r="K25" s="133">
         <f>'Statement Y'!K30</f>
         <v>7286</v>
       </c>
-      <c r="L24" s="133">
+      <c r="L25" s="133">
         <f>'Statement Y'!L30</f>
         <v>5718</v>
       </c>
-      <c r="N24" s="133">
+      <c r="N25" s="133">
         <f>'Statement Q'!C26</f>
         <v>6232</v>
       </c>
-      <c r="O24" s="133">
+      <c r="O25" s="133">
         <f>'Statement Q'!D26</f>
         <v>6165</v>
       </c>
-      <c r="P24" s="133">
+      <c r="P25" s="133">
         <f>'Statement Q'!E26</f>
         <v>7286</v>
       </c>
-      <c r="Q24" s="133">
+      <c r="Q25" s="133">
         <f>'Statement Q'!F26</f>
         <v>6911</v>
       </c>
-      <c r="R24" s="133">
+      <c r="R25" s="133">
         <f>'Statement Q'!G26</f>
         <v>6269</v>
       </c>
-      <c r="S24" s="133">
+      <c r="S25" s="133">
         <f>'Statement Q'!H26</f>
         <v>5925</v>
       </c>
-      <c r="T24" s="133">
+      <c r="T25" s="133">
         <f>'Statement Q'!I26</f>
         <v>5718</v>
       </c>
-      <c r="U24" s="133">
+      <c r="U25" s="133">
         <f>'Statement Q'!J26</f>
         <v>5875</v>
       </c>
-      <c r="W24" s="133">
+      <c r="W25" s="133">
         <f t="shared" si="3"/>
         <v>5875</v>
       </c>
     </row>
-    <row r="25" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="9" t="s">
+    <row r="26" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="C25" s="133">
+      <c r="C26" s="133">
         <f>'Statement Y'!C31</f>
         <v>8283</v>
       </c>
-      <c r="D25" s="133">
+      <c r="D26" s="133">
         <f>'Statement Y'!D31</f>
         <v>13936</v>
       </c>
-      <c r="E25" s="133">
+      <c r="E26" s="133">
         <f>'Statement Y'!E31</f>
         <v>12087</v>
       </c>
-      <c r="F25" s="133">
+      <c r="F26" s="133">
         <f>'Statement Y'!F31</f>
         <v>12352</v>
       </c>
-      <c r="G25" s="133">
+      <c r="G26" s="133">
         <f>'Statement Y'!G31</f>
         <v>11264</v>
       </c>
-      <c r="H25" s="133">
+      <c r="H26" s="133">
         <f>'Statement Y'!H31</f>
         <v>14111</v>
       </c>
-      <c r="I25" s="133">
+      <c r="I26" s="133">
         <f>'Statement Y'!I31</f>
         <v>21223</v>
       </c>
-      <c r="J25" s="133">
+      <c r="J26" s="133">
         <f>'Statement Y'!J31</f>
         <v>14695</v>
       </c>
-      <c r="K25" s="133">
+      <c r="K26" s="133">
         <f>'Statement Y'!K31</f>
         <v>14287</v>
       </c>
-      <c r="L25" s="133">
+      <c r="L26" s="133">
         <f>'Statement Y'!L31</f>
         <v>14585</v>
       </c>
-      <c r="N25" s="133">
+      <c r="N26" s="133">
         <f>'Statement Q'!C27</f>
         <v>13884</v>
       </c>
-      <c r="O25" s="133">
+      <c r="O26" s="133">
         <f>'Statement Q'!D27</f>
         <v>14297</v>
       </c>
-      <c r="P25" s="133">
+      <c r="P26" s="133">
         <f>'Statement Q'!E27</f>
         <v>14287</v>
       </c>
-      <c r="Q25" s="133">
+      <c r="Q26" s="133">
         <f>'Statement Q'!F27</f>
         <v>13248</v>
       </c>
-      <c r="R25" s="133">
+      <c r="R26" s="133">
         <f>'Statement Q'!G27</f>
         <v>14109</v>
       </c>
-      <c r="S25" s="133">
+      <c r="S26" s="133">
         <f>'Statement Q'!H27</f>
         <v>14359</v>
       </c>
-      <c r="T25" s="133">
+      <c r="T26" s="133">
         <f>'Statement Q'!I27</f>
         <v>14585</v>
       </c>
-      <c r="U25" s="133">
+      <c r="U26" s="133">
         <f>'Statement Q'!J27</f>
         <v>15002</v>
       </c>
-      <c r="W25" s="133">
+      <c r="W26" s="133">
         <f t="shared" si="3"/>
         <v>15002</v>
       </c>
     </row>
-    <row r="26" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="11" t="s">
+    <row r="27" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="156">
+      <c r="C27" s="156">
         <f>'Statement Y'!C32</f>
         <v>106869</v>
       </c>
-      <c r="D26" s="156">
+      <c r="D27" s="156">
         <f>'Statement Y'!D32</f>
         <v>128645</v>
       </c>
-      <c r="E26" s="156">
+      <c r="E27" s="156">
         <f>'Statement Y'!E32</f>
         <v>131339</v>
       </c>
-      <c r="F26" s="156">
+      <c r="F27" s="156">
         <f>'Statement Y'!F32</f>
         <v>162819</v>
       </c>
-      <c r="G26" s="156">
+      <c r="G27" s="156">
         <f>'Statement Y'!G32</f>
         <v>143713</v>
       </c>
-      <c r="H26" s="156">
+      <c r="H27" s="156">
         <f>'Statement Y'!H32</f>
         <v>134846</v>
       </c>
-      <c r="I26" s="156">
+      <c r="I27" s="156">
         <f>'Statement Y'!I32</f>
         <v>135405</v>
       </c>
-      <c r="J26" s="156">
+      <c r="J27" s="156">
         <f>'Statement Y'!J32</f>
         <v>143566</v>
       </c>
-      <c r="K26" s="156">
+      <c r="K27" s="156">
         <f>'Statement Y'!K32</f>
         <v>152987</v>
       </c>
-      <c r="L26" s="156">
+      <c r="L27" s="156">
         <f>'Statement Y'!L32</f>
         <v>147957</v>
       </c>
-      <c r="N26" s="156">
+      <c r="N27" s="156">
         <f>'Statement Q'!C28</f>
         <v>128416</v>
       </c>
-      <c r="O26" s="156">
+      <c r="O27" s="156">
         <f>'Statement Q'!D28</f>
         <v>125435</v>
       </c>
-      <c r="P26" s="156">
+      <c r="P27" s="156">
         <f>'Statement Q'!E28</f>
         <v>152987</v>
       </c>
-      <c r="Q26" s="156">
+      <c r="Q27" s="156">
         <f>'Statement Q'!F28</f>
         <v>133240</v>
       </c>
-      <c r="R26" s="156">
+      <c r="R27" s="156">
         <f>'Statement Q'!G28</f>
         <v>118674</v>
       </c>
-      <c r="S26" s="156">
+      <c r="S27" s="156">
         <f>'Statement Q'!H28</f>
         <v>122491</v>
       </c>
-      <c r="T26" s="156">
+      <c r="T27" s="156">
         <f>'Statement Q'!I28</f>
         <v>147957</v>
       </c>
-      <c r="U26" s="156">
+      <c r="U27" s="156">
         <f>'Statement Q'!J28</f>
         <v>158104</v>
       </c>
-      <c r="W26" s="156">
+      <c r="W27" s="156">
         <f t="shared" si="3"/>
         <v>158104</v>
       </c>
     </row>
-    <row r="27" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="9" t="s">
+    <row r="28" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="C27" s="133">
+      <c r="C28" s="133">
         <f>'Statement Y'!C33</f>
         <v>170430</v>
       </c>
-      <c r="D27" s="133">
+      <c r="D28" s="133">
         <f>'Statement Y'!D33</f>
         <v>194714</v>
       </c>
-      <c r="E27" s="133">
+      <c r="E28" s="133">
         <f>'Statement Y'!E33</f>
         <v>170799</v>
       </c>
-      <c r="F27" s="133">
+      <c r="F28" s="133">
         <f>'Statement Y'!F33</f>
         <v>105341</v>
       </c>
-      <c r="G27" s="133">
+      <c r="G28" s="133">
         <f>'Statement Y'!G33</f>
         <v>100887</v>
       </c>
-      <c r="H27" s="133">
+      <c r="H28" s="133">
         <f>'Statement Y'!H33</f>
         <v>127877</v>
       </c>
-      <c r="I27" s="133">
+      <c r="I28" s="133">
         <f>'Statement Y'!I33</f>
         <v>120805</v>
       </c>
-      <c r="J27" s="133">
+      <c r="J28" s="133">
         <f>'Statement Y'!J33</f>
         <v>100544</v>
       </c>
-      <c r="K27" s="133">
+      <c r="K28" s="133">
         <f>'Statement Y'!K33</f>
         <v>91479</v>
       </c>
-      <c r="L27" s="133">
+      <c r="L28" s="133">
         <f>'Statement Y'!L33</f>
         <v>77723</v>
       </c>
-      <c r="N27" s="133">
+      <c r="N28" s="133">
         <f>'Statement Q'!C29</f>
         <v>95187</v>
       </c>
-      <c r="O27" s="133">
+      <c r="O28" s="133">
         <f>'Statement Q'!D29</f>
         <v>91240</v>
       </c>
-      <c r="P27" s="133">
+      <c r="P28" s="133">
         <f>'Statement Q'!E29</f>
         <v>91479</v>
       </c>
-      <c r="Q27" s="133">
+      <c r="Q28" s="133">
         <f>'Statement Q'!F29</f>
         <v>87593</v>
       </c>
-      <c r="R27" s="133">
+      <c r="R28" s="133">
         <f>'Statement Q'!G29</f>
         <v>84424</v>
       </c>
-      <c r="S27" s="133">
+      <c r="S28" s="133">
         <f>'Statement Q'!H29</f>
         <v>77614</v>
       </c>
-      <c r="T27" s="133">
+      <c r="T28" s="133">
         <f>'Statement Q'!I29</f>
         <v>77723</v>
       </c>
-      <c r="U27" s="133">
+      <c r="U28" s="133">
         <f>'Statement Q'!J29</f>
         <v>77888</v>
       </c>
-      <c r="W27" s="133">
+      <c r="W28" s="133">
         <f t="shared" si="3"/>
         <v>77888</v>
       </c>
     </row>
-    <row r="28" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="9" t="s">
+    <row r="29" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="133">
+      <c r="C29" s="133">
         <f>'Statement Y'!C34</f>
         <v>27010</v>
       </c>
-      <c r="D28" s="133">
+      <c r="D29" s="133">
         <f>'Statement Y'!D34</f>
         <v>33783</v>
       </c>
-      <c r="E28" s="133">
+      <c r="E29" s="133">
         <f>'Statement Y'!E34</f>
         <v>41304</v>
       </c>
-      <c r="F28" s="133">
+      <c r="F29" s="133">
         <f>'Statement Y'!F34</f>
         <v>37378</v>
       </c>
-      <c r="G28" s="133">
+      <c r="G29" s="133">
         <f>'Statement Y'!G34</f>
         <v>36766</v>
       </c>
-      <c r="H28" s="133">
+      <c r="H29" s="133">
         <f>'Statement Y'!H34</f>
         <v>39440</v>
       </c>
-      <c r="I28" s="133">
+      <c r="I29" s="133">
         <f>'Statement Y'!I34</f>
         <v>42117</v>
       </c>
-      <c r="J28" s="133">
+      <c r="J29" s="133">
         <f>'Statement Y'!J34</f>
         <v>43715</v>
       </c>
-      <c r="K28" s="133">
+      <c r="K29" s="133">
         <f>'Statement Y'!K34</f>
         <v>45680</v>
       </c>
-      <c r="L28" s="133">
+      <c r="L29" s="133">
         <f>'Statement Y'!L34</f>
         <v>49834</v>
       </c>
-      <c r="N28" s="133">
+      <c r="N29" s="133">
         <f>'Statement Q'!C30</f>
         <v>43546</v>
       </c>
-      <c r="O28" s="133">
+      <c r="O29" s="133">
         <f>'Statement Q'!D30</f>
         <v>44502</v>
       </c>
-      <c r="P28" s="133">
+      <c r="P29" s="133">
         <f>'Statement Q'!E30</f>
         <v>45680</v>
       </c>
-      <c r="Q28" s="133">
+      <c r="Q29" s="133">
         <f>'Statement Q'!F30</f>
         <v>46069</v>
       </c>
-      <c r="R28" s="133">
+      <c r="R29" s="133">
         <f>'Statement Q'!G30</f>
         <v>46876</v>
       </c>
-      <c r="S28" s="133">
+      <c r="S29" s="133">
         <f>'Statement Q'!H30</f>
         <v>48508</v>
       </c>
-      <c r="T28" s="133">
+      <c r="T29" s="133">
         <f>'Statement Q'!I30</f>
         <v>49834</v>
       </c>
-      <c r="U28" s="133">
+      <c r="U29" s="133">
         <f>'Statement Q'!J30</f>
         <v>50159</v>
       </c>
-      <c r="W28" s="133">
+      <c r="W29" s="133">
         <f t="shared" si="3"/>
         <v>50159</v>
       </c>
     </row>
-    <row r="29" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="9" t="s">
+    <row r="30" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="133">
+      <c r="C30" s="133">
         <f>'Statement Y'!C35</f>
         <v>17377</v>
       </c>
-      <c r="D29" s="133">
+      <c r="D30" s="133">
         <f>'Statement Y'!D35</f>
         <v>18177</v>
       </c>
-      <c r="E29" s="133">
+      <c r="E30" s="133">
         <f>'Statement Y'!E35</f>
         <v>22283</v>
       </c>
-      <c r="F29" s="133">
+      <c r="F30" s="133">
         <f>'Statement Y'!F35</f>
         <v>32978</v>
       </c>
-      <c r="G29" s="133">
+      <c r="G30" s="133">
         <f>'Statement Y'!G35</f>
         <v>42522</v>
       </c>
-      <c r="H29" s="133">
+      <c r="H30" s="133">
         <f>'Statement Y'!H35</f>
         <v>48849</v>
       </c>
-      <c r="I29" s="133">
+      <c r="I30" s="133">
         <f>'Statement Y'!I35</f>
         <v>54428</v>
       </c>
-      <c r="J29" s="133">
+      <c r="J30" s="133">
         <f>'Statement Y'!J35</f>
         <v>64758</v>
       </c>
-      <c r="K29" s="133">
+      <c r="K30" s="133">
         <f>'Statement Y'!K35</f>
         <v>74834</v>
       </c>
-      <c r="L29" s="133">
+      <c r="L30" s="133">
         <f>'Statement Y'!L35</f>
         <v>83727</v>
       </c>
-      <c r="N29" s="133">
+      <c r="N30" s="133">
         <f>'Statement Q'!C31</f>
         <v>70262</v>
       </c>
-      <c r="O29" s="133">
+      <c r="O30" s="133">
         <f>'Statement Q'!D31</f>
         <v>70435</v>
       </c>
-      <c r="P29" s="133">
+      <c r="P30" s="133">
         <f>'Statement Q'!E31</f>
         <v>74834</v>
       </c>
-      <c r="Q29" s="133">
+      <c r="Q30" s="133">
         <f>'Statement Q'!F31</f>
         <v>77183</v>
       </c>
-      <c r="R29" s="133">
+      <c r="R30" s="133">
         <f>'Statement Q'!G31</f>
         <v>81259</v>
       </c>
-      <c r="S29" s="133">
+      <c r="S30" s="133">
         <f>'Statement Q'!H31</f>
         <v>82882</v>
       </c>
-      <c r="T29" s="133">
+      <c r="T30" s="133">
         <f>'Statement Q'!I31</f>
         <v>83727</v>
       </c>
-      <c r="U29" s="133">
+      <c r="U30" s="133">
         <f>'Statement Q'!J31</f>
         <v>93146</v>
       </c>
-      <c r="W29" s="133">
+      <c r="W30" s="133">
         <f t="shared" si="3"/>
         <v>93146</v>
       </c>
     </row>
-    <row r="30" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="11" t="s">
+    <row r="31" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="156">
+      <c r="C31" s="156">
         <f>'Statement Y'!C36</f>
         <v>214817</v>
       </c>
-      <c r="D30" s="156">
+      <c r="D31" s="156">
         <f>'Statement Y'!D36</f>
         <v>246674</v>
       </c>
-      <c r="E30" s="156">
+      <c r="E31" s="156">
         <f>'Statement Y'!E36</f>
         <v>234386</v>
       </c>
-      <c r="F30" s="156">
+      <c r="F31" s="156">
         <f>'Statement Y'!F36</f>
         <v>175697</v>
       </c>
-      <c r="G30" s="156">
+      <c r="G31" s="156">
         <f>'Statement Y'!G36</f>
         <v>180175</v>
       </c>
-      <c r="H30" s="156">
+      <c r="H31" s="156">
         <f>'Statement Y'!H36</f>
         <v>216166</v>
       </c>
-      <c r="I30" s="156">
+      <c r="I31" s="156">
         <f>'Statement Y'!I36</f>
         <v>217350</v>
       </c>
-      <c r="J30" s="156">
+      <c r="J31" s="156">
         <f>'Statement Y'!J36</f>
         <v>209017</v>
       </c>
-      <c r="K30" s="156">
+      <c r="K31" s="156">
         <f>'Statement Y'!K36</f>
         <v>211993</v>
       </c>
-      <c r="L30" s="156">
+      <c r="L31" s="156">
         <f>'Statement Y'!L36</f>
         <v>211284</v>
       </c>
-      <c r="N30" s="156">
+      <c r="N31" s="156">
         <f>'Statement Q'!C32</f>
         <v>208995</v>
       </c>
-      <c r="O30" s="156">
+      <c r="O31" s="156">
         <f>'Statement Q'!D32</f>
         <v>206177</v>
       </c>
-      <c r="P30" s="156">
+      <c r="P31" s="156">
         <f>'Statement Q'!E32</f>
         <v>211993</v>
       </c>
-      <c r="Q30" s="156">
+      <c r="Q31" s="156">
         <f>'Statement Q'!F32</f>
         <v>210845</v>
       </c>
-      <c r="R30" s="156">
+      <c r="R31" s="156">
         <f>'Statement Q'!G32</f>
         <v>212559</v>
       </c>
-      <c r="S30" s="156">
+      <c r="S31" s="156">
         <f>'Statement Q'!H32</f>
         <v>209004</v>
       </c>
-      <c r="T30" s="156">
+      <c r="T31" s="156">
         <f>'Statement Q'!I32</f>
         <v>211284</v>
       </c>
-      <c r="U30" s="156">
+      <c r="U31" s="156">
         <f>'Statement Q'!J32</f>
         <v>221193</v>
       </c>
-      <c r="W30" s="156">
+      <c r="W31" s="156">
         <f t="shared" si="3"/>
         <v>221193</v>
       </c>
     </row>
-    <row r="31" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="17" t="s">
+    <row r="32" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="153">
+      <c r="C32" s="153">
         <f>'Statement Y'!C37</f>
         <v>321686</v>
       </c>
-      <c r="D31" s="153">
+      <c r="D32" s="153">
         <f>'Statement Y'!D37</f>
         <v>375319</v>
       </c>
-      <c r="E31" s="153">
+      <c r="E32" s="153">
         <f>'Statement Y'!E37</f>
         <v>365725</v>
       </c>
-      <c r="F31" s="153">
+      <c r="F32" s="153">
         <f>'Statement Y'!F37</f>
         <v>338516</v>
       </c>
-      <c r="G31" s="153">
+      <c r="G32" s="153">
         <f>'Statement Y'!G37</f>
         <v>323888</v>
       </c>
-      <c r="H31" s="153">
+      <c r="H32" s="153">
         <f>'Statement Y'!H37</f>
         <v>351002</v>
       </c>
-      <c r="I31" s="153">
+      <c r="I32" s="153">
         <f>'Statement Y'!I37</f>
         <v>352755</v>
       </c>
-      <c r="J31" s="153">
+      <c r="J32" s="153">
         <f>'Statement Y'!J37</f>
         <v>352583</v>
       </c>
-      <c r="K31" s="153">
+      <c r="K32" s="153">
         <f>'Statement Y'!K37</f>
         <v>364980</v>
       </c>
-      <c r="L31" s="153">
+      <c r="L32" s="153">
         <f>'Statement Y'!L37</f>
         <v>359241</v>
       </c>
-      <c r="N31" s="153">
+      <c r="N32" s="153">
         <f>'Statement Q'!C33</f>
         <v>337411</v>
       </c>
-      <c r="O31" s="153">
+      <c r="O32" s="153">
         <f>'Statement Q'!D33</f>
         <v>331612</v>
       </c>
-      <c r="P31" s="153">
+      <c r="P32" s="153">
         <f>'Statement Q'!E33</f>
         <v>364980</v>
       </c>
-      <c r="Q31" s="153">
+      <c r="Q32" s="153">
         <f>'Statement Q'!F33</f>
         <v>344085</v>
       </c>
-      <c r="R31" s="153">
+      <c r="R32" s="153">
         <f>'Statement Q'!G33</f>
         <v>331233</v>
       </c>
-      <c r="S31" s="153">
+      <c r="S32" s="153">
         <f>'Statement Q'!H33</f>
         <v>331495</v>
       </c>
-      <c r="T31" s="153">
+      <c r="T32" s="153">
         <f>'Statement Q'!I33</f>
         <v>359241</v>
       </c>
-      <c r="U31" s="153">
+      <c r="U32" s="153">
         <f>'Statement Q'!J33</f>
         <v>379297</v>
       </c>
-      <c r="W31" s="153">
+      <c r="W32" s="153">
         <f t="shared" si="3"/>
         <v>379297</v>
       </c>
     </row>
-    <row r="32" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="9" t="s">
+    <row r="33" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="133">
+      <c r="C33" s="133">
         <f>'Statement Y'!C38</f>
         <v>37294</v>
       </c>
-      <c r="D32" s="133">
+      <c r="D33" s="133">
         <f>'Statement Y'!D38</f>
         <v>49049</v>
       </c>
-      <c r="E32" s="133">
+      <c r="E33" s="133">
         <f>'Statement Y'!E38</f>
         <v>55888</v>
       </c>
-      <c r="F32" s="133">
+      <c r="F33" s="133">
         <f>'Statement Y'!F38</f>
         <v>46236</v>
       </c>
-      <c r="G32" s="133">
+      <c r="G33" s="133">
         <f>'Statement Y'!G38</f>
         <v>42296</v>
       </c>
-      <c r="H32" s="133">
+      <c r="H33" s="133">
         <f>'Statement Y'!H38</f>
         <v>54763</v>
       </c>
-      <c r="I32" s="133">
+      <c r="I33" s="133">
         <f>'Statement Y'!I38</f>
         <v>64115</v>
       </c>
-      <c r="J32" s="133">
+      <c r="J33" s="133">
         <f>'Statement Y'!J38</f>
         <v>62611</v>
       </c>
-      <c r="K32" s="133">
+      <c r="K33" s="133">
         <f>'Statement Y'!K38</f>
         <v>68960</v>
       </c>
-      <c r="L32" s="133">
+      <c r="L33" s="133">
         <f>'Statement Y'!L38</f>
         <v>69860</v>
       </c>
-      <c r="N32" s="133">
+      <c r="N33" s="133">
         <f>'Statement Q'!C34</f>
         <v>45753</v>
       </c>
-      <c r="O32" s="133">
+      <c r="O33" s="133">
         <f>'Statement Q'!D34</f>
         <v>47574</v>
       </c>
-      <c r="P32" s="133">
+      <c r="P33" s="133">
         <f>'Statement Q'!E34</f>
         <v>68960</v>
       </c>
-      <c r="Q32" s="133">
+      <c r="Q33" s="133">
         <f>'Statement Q'!F34</f>
         <v>61910</v>
       </c>
-      <c r="R32" s="133">
+      <c r="R33" s="133">
         <f>'Statement Q'!G34</f>
         <v>54126</v>
       </c>
-      <c r="S32" s="133">
+      <c r="S33" s="133">
         <f>'Statement Q'!H34</f>
         <v>50374</v>
       </c>
-      <c r="T32" s="133">
+      <c r="T33" s="133">
         <f>'Statement Q'!I34</f>
         <v>69860</v>
       </c>
-      <c r="U32" s="133">
+      <c r="U33" s="133">
         <f>'Statement Q'!J34</f>
         <v>70587</v>
       </c>
-      <c r="W32" s="133">
+      <c r="W33" s="133">
         <f t="shared" si="3"/>
         <v>70587</v>
       </c>
     </row>
-    <row r="33" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="9" t="s">
+    <row r="34" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="C33" s="133">
+      <c r="C34" s="133">
         <f>'Statement Y'!C39</f>
         <v>22027</v>
       </c>
-      <c r="D33" s="133">
+      <c r="D34" s="133">
         <f>'Statement Y'!D39</f>
         <v>25744</v>
       </c>
-      <c r="E33" s="133">
+      <c r="E34" s="133">
         <f>'Statement Y'!E39</f>
         <v>33327</v>
       </c>
-      <c r="F33" s="133">
+      <c r="F34" s="133">
         <f>'Statement Y'!F39</f>
         <v>37720</v>
       </c>
-      <c r="G33" s="133">
+      <c r="G34" s="133">
         <f>'Statement Y'!G39</f>
         <v>42684</v>
       </c>
-      <c r="H33" s="133">
+      <c r="H34" s="133">
         <f>'Statement Y'!H39</f>
         <v>47493</v>
       </c>
-      <c r="I33" s="133">
+      <c r="I34" s="133">
         <f>'Statement Y'!I39</f>
         <v>60845</v>
       </c>
-      <c r="J33" s="133">
+      <c r="J34" s="133">
         <f>'Statement Y'!J39</f>
         <v>58829</v>
       </c>
-      <c r="K33" s="133">
+      <c r="K34" s="133">
         <f>'Statement Y'!K39</f>
         <v>78304</v>
       </c>
-      <c r="L33" s="133">
+      <c r="L34" s="133">
         <f>'Statement Y'!L39</f>
         <v>66387</v>
       </c>
-      <c r="N33" s="133">
+      <c r="N34" s="133">
         <f>'Statement Q'!C35</f>
         <v>57298</v>
       </c>
-      <c r="O33" s="133">
+      <c r="O34" s="133">
         <f>'Statement Q'!D35</f>
         <v>60889</v>
       </c>
-      <c r="P33" s="133">
+      <c r="P34" s="133">
         <f>'Statement Q'!E35</f>
         <v>78304</v>
       </c>
-      <c r="Q33" s="133">
+      <c r="Q34" s="133">
         <f>'Statement Q'!F35</f>
         <v>61151</v>
       </c>
-      <c r="R33" s="133">
+      <c r="R34" s="133">
         <f>'Statement Q'!G35</f>
         <v>61849</v>
       </c>
-      <c r="S33" s="133">
+      <c r="S34" s="133">
         <f>'Statement Q'!H35</f>
         <v>62499</v>
       </c>
-      <c r="T33" s="133">
+      <c r="T34" s="133">
         <f>'Statement Q'!I35</f>
         <v>66387</v>
       </c>
-      <c r="U33" s="133">
+      <c r="U34" s="133">
         <f>'Statement Q'!J35</f>
         <v>68543</v>
       </c>
-      <c r="W33" s="133">
+      <c r="W34" s="133">
         <f t="shared" si="3"/>
         <v>68543</v>
       </c>
     </row>
-    <row r="34" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="9" t="s">
+    <row r="35" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C34" s="133">
+      <c r="C35" s="133">
         <f>'Statement Y'!C40</f>
         <v>8080</v>
       </c>
-      <c r="D34" s="133">
+      <c r="D35" s="133">
         <f>'Statement Y'!D40</f>
         <v>7548</v>
       </c>
-      <c r="E34" s="133">
+      <c r="E35" s="133">
         <f>'Statement Y'!E40</f>
         <v>5966</v>
       </c>
-      <c r="F34" s="133">
+      <c r="F35" s="133">
         <f>'Statement Y'!F40</f>
         <v>5522</v>
       </c>
-      <c r="G34" s="133">
+      <c r="G35" s="133">
         <f>'Statement Y'!G40</f>
         <v>6643</v>
       </c>
-      <c r="H34" s="133">
+      <c r="H35" s="133">
         <f>'Statement Y'!H40</f>
         <v>7612</v>
       </c>
-      <c r="I34" s="133">
+      <c r="I35" s="133">
         <f>'Statement Y'!I40</f>
         <v>7912</v>
       </c>
-      <c r="J34" s="133">
+      <c r="J35" s="133">
         <f>'Statement Y'!J40</f>
         <v>8061</v>
       </c>
-      <c r="K34" s="133">
+      <c r="K35" s="133">
         <f>'Statement Y'!K40</f>
         <v>8249</v>
       </c>
-      <c r="L34" s="133">
+      <c r="L35" s="133">
         <f>'Statement Y'!L40</f>
         <v>9055</v>
       </c>
-      <c r="N34" s="133">
+      <c r="N35" s="133">
         <f>'Statement Q'!C36</f>
         <v>8012</v>
       </c>
-      <c r="O34" s="133">
+      <c r="O35" s="133">
         <f>'Statement Q'!D36</f>
         <v>8053</v>
       </c>
-      <c r="P34" s="133">
+      <c r="P35" s="133">
         <f>'Statement Q'!E36</f>
         <v>8249</v>
       </c>
-      <c r="Q34" s="133">
+      <c r="Q35" s="133">
         <f>'Statement Q'!F36</f>
         <v>8461</v>
       </c>
-      <c r="R34" s="133">
+      <c r="R35" s="133">
         <f>'Statement Q'!G36</f>
         <v>8976</v>
       </c>
-      <c r="S34" s="133">
+      <c r="S35" s="133">
         <f>'Statement Q'!H36</f>
         <v>8979</v>
       </c>
-      <c r="T34" s="133">
+      <c r="T35" s="133">
         <f>'Statement Q'!I36</f>
         <v>9055</v>
       </c>
-      <c r="U34" s="133">
+      <c r="U35" s="133">
         <f>'Statement Q'!J36</f>
         <v>9413</v>
       </c>
-      <c r="W34" s="133">
+      <c r="W35" s="133">
         <f t="shared" si="3"/>
         <v>9413</v>
       </c>
     </row>
-    <row r="35" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="9" t="s">
+    <row r="36" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="C35" s="133">
+      <c r="C36" s="133">
         <f>'Statement Y'!C41</f>
         <v>8105</v>
       </c>
-      <c r="D35" s="133">
+      <c r="D36" s="133">
         <f>'Statement Y'!D41</f>
         <v>11977</v>
       </c>
-      <c r="E35" s="133">
+      <c r="E36" s="133">
         <f>'Statement Y'!E41</f>
         <v>11964</v>
       </c>
-      <c r="F35" s="133">
+      <c r="F36" s="133">
         <f>'Statement Y'!F41</f>
         <v>5980</v>
       </c>
-      <c r="G35" s="133">
+      <c r="G36" s="133">
         <f>'Statement Y'!G41</f>
         <v>4996</v>
       </c>
-      <c r="H35" s="133">
+      <c r="H36" s="133">
         <f>'Statement Y'!H41</f>
         <v>6000</v>
       </c>
-      <c r="I35" s="133">
+      <c r="I36" s="133">
         <f>'Statement Y'!I41</f>
         <v>9982</v>
       </c>
-      <c r="J35" s="133">
+      <c r="J36" s="133">
         <f>'Statement Y'!J41</f>
         <v>5985</v>
       </c>
-      <c r="K35" s="133">
+      <c r="K36" s="133">
         <f>'Statement Y'!K41</f>
         <v>9967</v>
       </c>
-      <c r="L35" s="133">
+      <c r="L36" s="133">
         <f>'Statement Y'!L41</f>
         <v>7979</v>
       </c>
-      <c r="N35" s="133">
+      <c r="N36" s="133">
         <f>'Statement Q'!C37</f>
         <v>1997</v>
       </c>
-      <c r="O35" s="133">
+      <c r="O36" s="133">
         <f>'Statement Q'!D37</f>
         <v>2994</v>
       </c>
-      <c r="P35" s="133">
+      <c r="P36" s="133">
         <f>'Statement Q'!E37</f>
         <v>9967</v>
       </c>
-      <c r="Q35" s="133">
+      <c r="Q36" s="133">
         <f>'Statement Q'!F37</f>
         <v>1995</v>
       </c>
-      <c r="R35" s="133">
+      <c r="R36" s="133">
         <f>'Statement Q'!G37</f>
         <v>5982</v>
       </c>
-      <c r="S35" s="133">
+      <c r="S36" s="133">
         <f>'Statement Q'!H37</f>
         <v>9923</v>
       </c>
-      <c r="T35" s="133">
+      <c r="T36" s="133">
         <f>'Statement Q'!I37</f>
         <v>7979</v>
       </c>
-      <c r="U35" s="133">
+      <c r="U36" s="133">
         <f>'Statement Q'!J37</f>
         <v>1997</v>
       </c>
-      <c r="W35" s="133">
+      <c r="W36" s="133">
         <f t="shared" si="3"/>
         <v>1997</v>
       </c>
     </row>
-    <row r="36" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="9" t="s">
+    <row r="37" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="C36" s="133">
+      <c r="C37" s="133">
         <f>'Statement Y'!C42</f>
         <v>3500</v>
       </c>
-      <c r="D36" s="133">
+      <c r="D37" s="133">
         <f>'Statement Y'!D42</f>
         <v>6496</v>
       </c>
-      <c r="E36" s="133">
+      <c r="E37" s="133">
         <f>'Statement Y'!E42</f>
         <v>8784</v>
       </c>
-      <c r="F36" s="133">
+      <c r="F37" s="133">
         <f>'Statement Y'!F42</f>
         <v>10260</v>
       </c>
-      <c r="G36" s="133">
+      <c r="G37" s="133">
         <f>'Statement Y'!G42</f>
         <v>8773</v>
       </c>
-      <c r="H36" s="133">
+      <c r="H37" s="133">
         <f>'Statement Y'!H42</f>
         <v>9613</v>
       </c>
-      <c r="I36" s="133">
+      <c r="I37" s="133">
         <f>'Statement Y'!I42</f>
         <v>11128</v>
       </c>
-      <c r="J36" s="133">
+      <c r="J37" s="133">
         <f>'Statement Y'!J42</f>
         <v>9822</v>
       </c>
-      <c r="K36" s="133">
+      <c r="K37" s="133">
         <f>'Statement Y'!K42</f>
         <v>10912</v>
       </c>
-      <c r="L36" s="133">
+      <c r="L37" s="133">
         <f>'Statement Y'!L42</f>
         <v>12350</v>
       </c>
-      <c r="N36" s="133">
+      <c r="N37" s="133">
         <f>'Statement Q'!C38</f>
         <v>10762</v>
       </c>
-      <c r="O36" s="133">
+      <c r="O37" s="133">
         <f>'Statement Q'!D38</f>
         <v>12114</v>
       </c>
-      <c r="P36" s="133">
+      <c r="P37" s="133">
         <f>'Statement Q'!E38</f>
         <v>10912</v>
       </c>
-      <c r="Q36" s="133">
+      <c r="Q37" s="133">
         <f>'Statement Q'!F38</f>
         <v>10848</v>
       </c>
-      <c r="R36" s="133">
+      <c r="R37" s="133">
         <f>'Statement Q'!G38</f>
         <v>13638</v>
       </c>
-      <c r="S36" s="133">
+      <c r="S37" s="133">
         <f>'Statement Q'!H38</f>
         <v>9345</v>
       </c>
-      <c r="T36" s="133">
+      <c r="T37" s="133">
         <f>'Statement Q'!I38</f>
         <v>12350</v>
       </c>
-      <c r="U36" s="133">
+      <c r="U37" s="133">
         <f>'Statement Q'!J38</f>
         <v>11827</v>
       </c>
-      <c r="W36" s="133">
-        <f>U36</f>
+      <c r="W37" s="133">
+        <f>U37</f>
         <v>11827</v>
       </c>
     </row>
-    <row r="37" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="11" t="s">
+    <row r="38" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C37" s="156">
+      <c r="C38" s="156">
         <f>'Statement Y'!C43</f>
         <v>79006</v>
       </c>
-      <c r="D37" s="156">
+      <c r="D38" s="156">
         <f>'Statement Y'!D43</f>
         <v>100814</v>
       </c>
-      <c r="E37" s="156">
+      <c r="E38" s="156">
         <f>'Statement Y'!E43</f>
         <v>115929</v>
       </c>
-      <c r="F37" s="156">
+      <c r="F38" s="156">
         <f>'Statement Y'!F43</f>
         <v>105718</v>
       </c>
-      <c r="G37" s="156">
+      <c r="G38" s="156">
         <f>'Statement Y'!G43</f>
         <v>105392</v>
       </c>
-      <c r="H37" s="156">
+      <c r="H38" s="156">
         <f>'Statement Y'!H43</f>
         <v>125481</v>
       </c>
-      <c r="I37" s="156">
+      <c r="I38" s="156">
         <f>'Statement Y'!I43</f>
         <v>153982</v>
       </c>
-      <c r="J37" s="156">
+      <c r="J38" s="156">
         <f>'Statement Y'!J43</f>
         <v>145308</v>
       </c>
-      <c r="K37" s="156">
+      <c r="K38" s="156">
         <f>'Statement Y'!K43</f>
         <v>176392</v>
       </c>
-      <c r="L37" s="156">
+      <c r="L38" s="156">
         <f>'Statement Y'!L43</f>
         <v>165631</v>
       </c>
-      <c r="N37" s="156">
+      <c r="N38" s="156">
         <f>'Statement Q'!C39</f>
         <v>123822</v>
       </c>
-      <c r="O37" s="156">
+      <c r="O38" s="156">
         <f>'Statement Q'!D39</f>
         <v>131624</v>
       </c>
-      <c r="P37" s="156">
+      <c r="P38" s="156">
         <f>'Statement Q'!E39</f>
         <v>176392</v>
       </c>
-      <c r="Q37" s="156">
+      <c r="Q38" s="156">
         <f>'Statement Q'!F39</f>
         <v>144365</v>
       </c>
-      <c r="R37" s="156">
+      <c r="R38" s="156">
         <f>'Statement Q'!G39</f>
         <v>144571</v>
       </c>
-      <c r="S37" s="156">
+      <c r="S38" s="156">
         <f>'Statement Q'!H39</f>
         <v>141120</v>
       </c>
-      <c r="T37" s="156">
+      <c r="T38" s="156">
         <f>'Statement Q'!I39</f>
         <v>165361</v>
       </c>
-      <c r="U37" s="156">
+      <c r="U38" s="156">
         <f>'Statement Q'!J39</f>
         <v>162367</v>
       </c>
-      <c r="W37" s="156">
+      <c r="W38" s="156">
         <f t="shared" si="3"/>
         <v>162367</v>
       </c>
     </row>
-    <row r="38" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="9" t="s">
+    <row r="39" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="C38" s="133">
+      <c r="C39" s="133">
         <f>'Statement Y'!C44</f>
         <v>75427</v>
       </c>
-      <c r="D38" s="133">
+      <c r="D39" s="133">
         <f>'Statement Y'!D44</f>
         <v>97207</v>
       </c>
-      <c r="E38" s="133">
+      <c r="E39" s="133">
         <f>'Statement Y'!E44</f>
         <v>93735</v>
       </c>
-      <c r="F38" s="133">
+      <c r="F39" s="133">
         <f>'Statement Y'!F44</f>
         <v>91807</v>
       </c>
-      <c r="G38" s="133">
+      <c r="G39" s="133">
         <f>'Statement Y'!G44</f>
         <v>98667</v>
       </c>
-      <c r="H38" s="133">
+      <c r="H39" s="133">
         <f>'Statement Y'!H44</f>
         <v>109106</v>
       </c>
-      <c r="I38" s="133">
+      <c r="I39" s="133">
         <f>'Statement Y'!I44</f>
         <v>98959</v>
       </c>
-      <c r="J38" s="133">
+      <c r="J39" s="133">
         <f>'Statement Y'!J44</f>
         <v>95281</v>
       </c>
-      <c r="K38" s="133">
+      <c r="K39" s="133">
         <f>'Statement Y'!K44</f>
         <v>85750</v>
       </c>
-      <c r="L38" s="133">
+      <c r="L39" s="133">
         <f>'Statement Y'!L44</f>
         <v>78328</v>
       </c>
-      <c r="N38" s="133">
+      <c r="N39" s="133">
         <f>'Statement Q'!C40</f>
         <v>91831</v>
       </c>
-      <c r="O38" s="133">
+      <c r="O39" s="133">
         <f>'Statement Q'!D40</f>
         <v>86196</v>
       </c>
-      <c r="P38" s="133">
+      <c r="P39" s="133">
         <f>'Statement Q'!E40</f>
         <v>85750</v>
       </c>
-      <c r="Q38" s="133">
+      <c r="Q39" s="133">
         <f>'Statement Q'!F40</f>
         <v>83956</v>
       </c>
-      <c r="R38" s="133">
+      <c r="R39" s="133">
         <f>'Statement Q'!G40</f>
         <v>78566</v>
       </c>
-      <c r="S38" s="133">
+      <c r="S39" s="133">
         <f>'Statement Q'!H40</f>
         <v>82430</v>
       </c>
-      <c r="T38" s="133">
+      <c r="T39" s="133">
         <f>'Statement Q'!I40</f>
         <v>78328</v>
       </c>
-      <c r="U38" s="133">
+      <c r="U39" s="133">
         <f>'Statement Q'!J40</f>
         <v>76685</v>
       </c>
-      <c r="W38" s="133">
+      <c r="W39" s="133">
         <f t="shared" si="3"/>
         <v>76685</v>
       </c>
     </row>
-    <row r="39" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="9" t="s">
+    <row r="40" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="133">
+      <c r="C40" s="133">
         <f>'Statement Y'!C45</f>
         <v>39004</v>
       </c>
-      <c r="D39" s="133">
+      <c r="D40" s="133">
         <f>'Statement Y'!D45</f>
         <v>43251</v>
       </c>
-      <c r="E39" s="133">
+      <c r="E40" s="133">
         <f>'Statement Y'!E45</f>
         <v>48914</v>
       </c>
-      <c r="F39" s="133">
+      <c r="F40" s="133">
         <f>'Statement Y'!F45</f>
         <v>50503</v>
       </c>
-      <c r="G39" s="133">
+      <c r="G40" s="133">
         <f>'Statement Y'!G45</f>
         <v>54490</v>
       </c>
-      <c r="H39" s="133">
+      <c r="H40" s="133">
         <f>'Statement Y'!H45</f>
         <v>53325</v>
       </c>
-      <c r="I39" s="133">
+      <c r="I40" s="133">
         <f>'Statement Y'!I45</f>
         <v>49142</v>
       </c>
-      <c r="J39" s="133">
+      <c r="J40" s="133">
         <f>'Statement Y'!J45</f>
         <v>49848</v>
       </c>
-      <c r="K39" s="133">
+      <c r="K40" s="133">
         <f>'Statement Y'!K45</f>
         <v>45888</v>
       </c>
-      <c r="L39" s="133">
+      <c r="L40" s="133">
         <f>'Statement Y'!L45</f>
         <v>41549</v>
       </c>
-      <c r="N39" s="133">
+      <c r="N40" s="133">
         <f>'Statement Q'!C41</f>
         <v>47564</v>
       </c>
-      <c r="O39" s="133">
+      <c r="O40" s="133">
         <f>'Statement Q'!D41</f>
         <v>47084</v>
       </c>
-      <c r="P39" s="133">
+      <c r="P40" s="133">
         <f>'Statement Q'!E41</f>
         <v>45888</v>
       </c>
-      <c r="Q39" s="133">
+      <c r="Q40" s="133">
         <f>'Statement Q'!F41</f>
         <v>49006</v>
       </c>
-      <c r="R39" s="133">
+      <c r="R40" s="133">
         <f>'Statement Q'!G41</f>
         <v>41300</v>
       </c>
-      <c r="S39" s="133">
+      <c r="S40" s="133">
         <f>'Statement Q'!H41</f>
         <v>42115</v>
       </c>
-      <c r="T39" s="133">
+      <c r="T40" s="133">
         <f>'Statement Q'!I41</f>
         <v>41549</v>
       </c>
-      <c r="U39" s="133">
+      <c r="U40" s="133">
         <f>'Statement Q'!J41</f>
         <v>52055</v>
       </c>
-      <c r="W39" s="133">
+      <c r="W40" s="133">
         <f t="shared" si="3"/>
         <v>52055</v>
       </c>
     </row>
-    <row r="40" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="11" t="s">
+    <row r="41" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C40" s="156">
+      <c r="C41" s="156">
         <f>'Statement Y'!C46</f>
         <v>114431</v>
       </c>
-      <c r="D40" s="156">
+      <c r="D41" s="156">
         <f>'Statement Y'!D46</f>
         <v>140458</v>
       </c>
-      <c r="E40" s="156">
+      <c r="E41" s="156">
         <f>'Statement Y'!E46</f>
         <v>142649</v>
       </c>
-      <c r="F40" s="156">
+      <c r="F41" s="156">
         <f>'Statement Y'!F46</f>
         <v>142310</v>
       </c>
-      <c r="G40" s="156">
+      <c r="G41" s="156">
         <f>'Statement Y'!G46</f>
         <v>153157</v>
       </c>
-      <c r="H40" s="156">
+      <c r="H41" s="156">
         <f>'Statement Y'!H46</f>
         <v>162431</v>
       </c>
-      <c r="I40" s="156">
+      <c r="I41" s="156">
         <f>'Statement Y'!I46</f>
         <v>148101</v>
       </c>
-      <c r="J40" s="156">
+      <c r="J41" s="156">
         <f>'Statement Y'!J46</f>
         <v>145129</v>
       </c>
-      <c r="K40" s="156">
+      <c r="K41" s="156">
         <f>'Statement Y'!K46</f>
         <v>131638</v>
       </c>
-      <c r="L40" s="156">
+      <c r="L41" s="156">
         <f>'Statement Y'!L46</f>
         <v>119877</v>
       </c>
-      <c r="N40" s="156">
+      <c r="N41" s="156">
         <f>'Statement Q'!C42</f>
         <v>139395</v>
       </c>
-      <c r="O40" s="156">
+      <c r="O41" s="156">
         <f>'Statement Q'!D42</f>
         <v>133280</v>
       </c>
-      <c r="P40" s="156">
+      <c r="P41" s="156">
         <f>'Statement Q'!E42</f>
         <v>131638</v>
       </c>
-      <c r="Q40" s="156">
+      <c r="Q41" s="156">
         <f>'Statement Q'!F42</f>
         <v>132962</v>
       </c>
-      <c r="R40" s="156">
+      <c r="R41" s="156">
         <f>'Statement Q'!G42</f>
         <v>119866</v>
       </c>
-      <c r="S40" s="156">
+      <c r="S41" s="156">
         <f>'Statement Q'!H42</f>
         <v>124545</v>
       </c>
-      <c r="T40" s="156">
+      <c r="T41" s="156">
         <f>'Statement Q'!I42</f>
         <v>119877</v>
       </c>
-      <c r="U40" s="156">
+      <c r="U41" s="156">
         <f>'Statement Q'!J42</f>
         <v>128740</v>
       </c>
-      <c r="W40" s="156">
+      <c r="W41" s="156">
         <f t="shared" si="3"/>
         <v>128740</v>
       </c>
     </row>
-    <row r="41" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="17" t="s">
+    <row r="42" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="153">
+      <c r="C42" s="153">
         <f>'Statement Y'!C47</f>
         <v>193437</v>
       </c>
-      <c r="D41" s="153">
+      <c r="D42" s="153">
         <f>'Statement Y'!D47</f>
         <v>241272</v>
       </c>
-      <c r="E41" s="153">
+      <c r="E42" s="153">
         <f>'Statement Y'!E47</f>
         <v>258578</v>
       </c>
-      <c r="F41" s="153">
+      <c r="F42" s="153">
         <f>'Statement Y'!F47</f>
         <v>248028</v>
       </c>
-      <c r="G41" s="153">
+      <c r="G42" s="153">
         <f>'Statement Y'!G47</f>
         <v>258549</v>
       </c>
-      <c r="H41" s="153">
+      <c r="H42" s="153">
         <f>'Statement Y'!H47</f>
         <v>287912</v>
       </c>
-      <c r="I41" s="153">
+      <c r="I42" s="153">
         <f>'Statement Y'!I47</f>
         <v>302083</v>
       </c>
-      <c r="J41" s="153">
+      <c r="J42" s="153">
         <f>'Statement Y'!J47</f>
         <v>290437</v>
       </c>
-      <c r="K41" s="153">
+      <c r="K42" s="153">
         <f>'Statement Y'!K47</f>
         <v>308030</v>
       </c>
-      <c r="L41" s="153">
+      <c r="L42" s="153">
         <f>'Statement Y'!L47</f>
         <v>285508</v>
       </c>
-      <c r="N41" s="153">
+      <c r="N42" s="153">
         <f>'Statement Q'!C43</f>
         <v>263217</v>
       </c>
-      <c r="O41" s="153">
+      <c r="O42" s="153">
         <f>'Statement Q'!D43</f>
         <v>264904</v>
       </c>
-      <c r="P41" s="153">
+      <c r="P42" s="153">
         <f>'Statement Q'!E43</f>
         <v>308030</v>
       </c>
-      <c r="Q41" s="153">
+      <c r="Q42" s="153">
         <f>'Statement Q'!F43</f>
         <v>277327</v>
       </c>
-      <c r="R41" s="153">
+      <c r="R42" s="153">
         <f>'Statement Q'!G43</f>
         <v>264437</v>
       </c>
-      <c r="S41" s="153">
+      <c r="S42" s="153">
         <f>'Statement Q'!H43</f>
         <v>265665</v>
       </c>
-      <c r="T41" s="153">
+      <c r="T42" s="153">
         <f>'Statement Q'!I43</f>
         <v>285508</v>
       </c>
-      <c r="U41" s="153">
+      <c r="U42" s="153">
         <f>'Statement Q'!J43</f>
         <v>291107</v>
       </c>
-      <c r="W41" s="153">
+      <c r="W42" s="153">
         <f t="shared" si="3"/>
         <v>291107</v>
       </c>
     </row>
-    <row r="42" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="9" t="s">
+    <row r="43" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="C42" s="133">
+      <c r="C43" s="133">
         <f>'Statement Y'!C48</f>
         <v>31251</v>
       </c>
-      <c r="D42" s="133">
+      <c r="D43" s="133">
         <f>'Statement Y'!D48</f>
         <v>35867</v>
       </c>
-      <c r="E42" s="133">
+      <c r="E43" s="133">
         <f>'Statement Y'!E48</f>
         <v>40201</v>
       </c>
-      <c r="F42" s="133">
+      <c r="F43" s="133">
         <f>'Statement Y'!F48</f>
         <v>45174</v>
       </c>
-      <c r="G42" s="133">
+      <c r="G43" s="133">
         <f>'Statement Y'!G48</f>
         <v>50779</v>
       </c>
-      <c r="H42" s="133">
+      <c r="H43" s="133">
         <f>'Statement Y'!H48</f>
         <v>57365</v>
       </c>
-      <c r="I42" s="133">
+      <c r="I43" s="133">
         <f>'Statement Y'!I48</f>
         <v>64849</v>
       </c>
-      <c r="J42" s="133">
+      <c r="J43" s="133">
         <f>'Statement Y'!J48</f>
         <v>73812</v>
       </c>
-      <c r="K42" s="133">
+      <c r="K43" s="133">
         <f>'Statement Y'!K48</f>
         <v>83276</v>
       </c>
-      <c r="L42" s="133">
+      <c r="L43" s="133">
         <f>'Statement Y'!L48</f>
         <v>93568</v>
       </c>
-      <c r="N42" s="133">
+      <c r="N43" s="133">
         <f>'Statement Q'!C44</f>
         <v>78815</v>
       </c>
-      <c r="O42" s="133">
+      <c r="O43" s="133">
         <f>'Statement Q'!D44</f>
         <v>79850</v>
       </c>
-      <c r="P42" s="133">
+      <c r="P43" s="133">
         <f>'Statement Q'!E44</f>
         <v>83276</v>
       </c>
-      <c r="Q42" s="133">
+      <c r="Q43" s="133">
         <f>'Statement Q'!F44</f>
         <v>84768</v>
       </c>
-      <c r="R42" s="133">
+      <c r="R43" s="133">
         <f>'Statement Q'!G44</f>
         <v>88711</v>
       </c>
-      <c r="S42" s="133">
+      <c r="S43" s="133">
         <f>'Statement Q'!H44</f>
         <v>89806</v>
       </c>
-      <c r="T42" s="133">
+      <c r="T43" s="133">
         <f>'Statement Q'!I44</f>
         <v>93568</v>
       </c>
-      <c r="U42" s="133">
+      <c r="U43" s="133">
         <f>'Statement Q'!J44</f>
         <v>95221</v>
       </c>
-      <c r="W42" s="133">
+      <c r="W43" s="133">
         <f t="shared" si="3"/>
         <v>95221</v>
       </c>
     </row>
-    <row r="43" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="9" t="s">
+    <row r="44" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C43" s="133">
+      <c r="C44" s="133">
         <f>'Statement Y'!C49</f>
         <v>96364</v>
       </c>
-      <c r="D43" s="133">
+      <c r="D44" s="133">
         <f>'Statement Y'!D49</f>
         <v>98330</v>
       </c>
-      <c r="E43" s="133">
+      <c r="E44" s="133">
         <f>'Statement Y'!E49</f>
         <v>70400</v>
       </c>
-      <c r="F43" s="133">
+      <c r="F44" s="133">
         <f>'Statement Y'!F49</f>
         <v>45898</v>
       </c>
-      <c r="G43" s="133">
+      <c r="G44" s="133">
         <f>'Statement Y'!G49</f>
         <v>14966</v>
       </c>
-      <c r="H43" s="133">
+      <c r="H44" s="133">
         <f>'Statement Y'!H49</f>
         <v>5562</v>
       </c>
-      <c r="I43" s="133">
+      <c r="I44" s="133">
         <f>'Statement Y'!I49</f>
         <v>-3068</v>
       </c>
-      <c r="J43" s="133">
+      <c r="J44" s="133">
         <f>'Statement Y'!J49</f>
         <v>-214</v>
       </c>
-      <c r="K43" s="133">
+      <c r="K44" s="133">
         <f>'Statement Y'!K49</f>
         <v>-19154</v>
       </c>
-      <c r="L43" s="133">
+      <c r="L44" s="133">
         <f>'Statement Y'!L49</f>
         <v>-14264</v>
       </c>
-      <c r="N43" s="133">
+      <c r="N44" s="133">
         <f>'Statement Q'!C45</f>
         <v>4339</v>
       </c>
-      <c r="O43" s="133">
+      <c r="O44" s="133">
         <f>'Statement Q'!D45</f>
         <v>-4726</v>
       </c>
-      <c r="P43" s="133">
+      <c r="P44" s="133">
         <f>'Statement Q'!E45</f>
         <v>-19154</v>
       </c>
-      <c r="Q43" s="133">
+      <c r="Q44" s="133">
         <f>'Statement Q'!F45</f>
         <v>-11221</v>
       </c>
-      <c r="R43" s="133">
+      <c r="R44" s="133">
         <f>'Statement Q'!G45</f>
         <v>-15552</v>
       </c>
-      <c r="S43" s="133">
+      <c r="S44" s="133">
         <f>'Statement Q'!H45</f>
         <v>-17607</v>
       </c>
-      <c r="T43" s="133">
+      <c r="T44" s="133">
         <f>'Statement Q'!I45</f>
         <v>-14264</v>
       </c>
-      <c r="U43" s="133">
+      <c r="U44" s="133">
         <f>'Statement Q'!J45</f>
         <v>-2177</v>
       </c>
-      <c r="W43" s="133">
+      <c r="W44" s="133">
         <f t="shared" si="3"/>
         <v>-2177</v>
       </c>
     </row>
-    <row r="44" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="9" t="s">
+    <row r="45" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="C44" s="133">
+      <c r="C45" s="133">
         <f>'Statement Y'!C50</f>
         <v>634</v>
       </c>
-      <c r="D44" s="133">
+      <c r="D45" s="133">
         <f>'Statement Y'!D50</f>
         <v>-150</v>
       </c>
-      <c r="E44" s="133">
+      <c r="E45" s="133">
         <f>'Statement Y'!E50</f>
         <v>-3454</v>
       </c>
-      <c r="F44" s="133">
+      <c r="F45" s="133">
         <f>'Statement Y'!F50</f>
         <v>-584</v>
       </c>
-      <c r="G44" s="133">
+      <c r="G45" s="133">
         <f>'Statement Y'!G50</f>
         <v>-406</v>
       </c>
-      <c r="H44" s="133">
+      <c r="H45" s="133">
         <f>'Statement Y'!H50</f>
         <v>163</v>
       </c>
-      <c r="I44" s="133">
+      <c r="I45" s="133">
         <f>'Statement Y'!I50</f>
         <v>-11109</v>
       </c>
-      <c r="J44" s="133">
+      <c r="J45" s="133">
         <f>'Statement Y'!J50</f>
         <v>-11452</v>
       </c>
-      <c r="K44" s="133">
+      <c r="K45" s="133">
         <f>'Statement Y'!K50</f>
         <v>-7172</v>
       </c>
-      <c r="L44" s="133">
+      <c r="L45" s="133">
         <f>'Statement Y'!L50</f>
         <v>-5571</v>
       </c>
-      <c r="N44" s="133">
+      <c r="N45" s="133">
         <f>'Statement Q'!C46</f>
         <v>-8960</v>
       </c>
-      <c r="O44" s="133">
+      <c r="O45" s="133">
         <f>'Statement Q'!D46</f>
         <v>-8416</v>
       </c>
-      <c r="P44" s="133">
+      <c r="P45" s="133">
         <f>'Statement Q'!E46</f>
         <v>-7172</v>
       </c>
-      <c r="Q44" s="133">
+      <c r="Q45" s="133">
         <f>'Statement Q'!F46</f>
         <v>-6789</v>
       </c>
-      <c r="R44" s="133">
+      <c r="R45" s="133">
         <f>'Statement Q'!G46</f>
         <v>-6363</v>
       </c>
-      <c r="S44" s="133">
+      <c r="S45" s="133">
         <f>'Statement Q'!H46</f>
         <v>-6369</v>
       </c>
-      <c r="T44" s="133">
+      <c r="T45" s="133">
         <f>'Statement Q'!I46</f>
         <v>-5571</v>
       </c>
-      <c r="U44" s="133">
+      <c r="U45" s="133">
         <f>'Statement Q'!J46</f>
         <v>-4854</v>
       </c>
-      <c r="W44" s="133">
+      <c r="W45" s="133">
         <f t="shared" si="3"/>
         <v>-4854</v>
       </c>
     </row>
-    <row r="45" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="11" t="s">
+    <row r="46" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C45" s="156">
+      <c r="C46" s="156">
         <f>'Statement Y'!C51</f>
         <v>128249</v>
       </c>
-      <c r="D45" s="156">
+      <c r="D46" s="156">
         <f>'Statement Y'!D51</f>
         <v>134047</v>
       </c>
-      <c r="E45" s="156">
+      <c r="E46" s="156">
         <f>'Statement Y'!E51</f>
         <v>107147</v>
       </c>
-      <c r="F45" s="156">
+      <c r="F46" s="156">
         <f>'Statement Y'!F51</f>
         <v>90488</v>
       </c>
-      <c r="G45" s="156">
+      <c r="G46" s="156">
         <f>'Statement Y'!G51</f>
         <v>65339</v>
       </c>
-      <c r="H45" s="156">
+      <c r="H46" s="156">
         <f>'Statement Y'!H51</f>
         <v>63090</v>
       </c>
-      <c r="I45" s="156">
+      <c r="I46" s="156">
         <f>'Statement Y'!I51</f>
         <v>50672</v>
       </c>
-      <c r="J45" s="156">
+      <c r="J46" s="156">
         <f>'Statement Y'!J51</f>
         <v>62146</v>
       </c>
-      <c r="K45" s="156">
+      <c r="K46" s="156">
         <f>'Statement Y'!K51</f>
         <v>56950</v>
       </c>
-      <c r="L45" s="156">
+      <c r="L46" s="156">
         <f>'Statement Y'!L51</f>
         <v>73733</v>
       </c>
-      <c r="N45" s="156">
+      <c r="N46" s="156">
         <f>'Statement Q'!C47</f>
         <v>74194</v>
       </c>
-      <c r="O45" s="156">
+      <c r="O46" s="156">
         <f>'Statement Q'!D47</f>
         <v>66708</v>
       </c>
-      <c r="P45" s="156">
+      <c r="P46" s="156">
         <f>'Statement Q'!E47</f>
         <v>56950</v>
       </c>
-      <c r="Q45" s="156">
+      <c r="Q46" s="156">
         <f>'Statement Q'!F47</f>
         <v>66758</v>
       </c>
-      <c r="R45" s="156">
+      <c r="R46" s="156">
         <f>'Statement Q'!G47</f>
         <v>66796</v>
       </c>
-      <c r="S45" s="156">
+      <c r="S46" s="156">
         <f>'Statement Q'!H47</f>
         <v>65830</v>
       </c>
-      <c r="T45" s="156">
+      <c r="T46" s="156">
         <f>'Statement Q'!I47</f>
         <v>73733</v>
       </c>
-      <c r="U45" s="156">
+      <c r="U46" s="156">
         <f>'Statement Q'!J47</f>
         <v>88190</v>
       </c>
-      <c r="W45" s="156">
+      <c r="W46" s="156">
         <f t="shared" si="3"/>
         <v>88190</v>
       </c>
     </row>
-    <row r="46" spans="2:23" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="19" t="s">
+    <row r="47" spans="2:23" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C46" s="157">
+      <c r="C47" s="157">
         <f>'Statement Y'!C52</f>
         <v>321686</v>
       </c>
-      <c r="D46" s="157">
+      <c r="D47" s="157">
         <f>'Statement Y'!D52</f>
         <v>375319</v>
       </c>
-      <c r="E46" s="157">
+      <c r="E47" s="157">
         <f>'Statement Y'!E52</f>
         <v>365725</v>
       </c>
-      <c r="F46" s="157">
+      <c r="F47" s="157">
         <f>'Statement Y'!F52</f>
         <v>338516</v>
       </c>
-      <c r="G46" s="157">
+      <c r="G47" s="157">
         <f>'Statement Y'!G52</f>
         <v>323888</v>
       </c>
-      <c r="H46" s="157">
+      <c r="H47" s="157">
         <f>'Statement Y'!H52</f>
         <v>351002</v>
       </c>
-      <c r="I46" s="157">
+      <c r="I47" s="157">
         <f>'Statement Y'!I52</f>
         <v>352755</v>
       </c>
-      <c r="J46" s="157">
+      <c r="J47" s="157">
         <f>'Statement Y'!J52</f>
         <v>352583</v>
       </c>
-      <c r="K46" s="157">
+      <c r="K47" s="157">
         <f>'Statement Y'!K52</f>
         <v>364980</v>
       </c>
-      <c r="L46" s="157">
+      <c r="L47" s="157">
         <f>'Statement Y'!L52</f>
         <v>359241</v>
       </c>
-      <c r="N46" s="157">
+      <c r="N47" s="157">
         <f>'Statement Q'!C48</f>
         <v>337411</v>
       </c>
-      <c r="O46" s="157">
+      <c r="O47" s="157">
         <f>'Statement Q'!D48</f>
         <v>331612</v>
       </c>
-      <c r="P46" s="157">
+      <c r="P47" s="157">
         <f>'Statement Q'!E48</f>
         <v>364980</v>
       </c>
-      <c r="Q46" s="157">
+      <c r="Q47" s="157">
         <f>'Statement Q'!F48</f>
         <v>344085</v>
       </c>
-      <c r="R46" s="157">
+      <c r="R47" s="157">
         <f>'Statement Q'!G48</f>
         <v>331233</v>
       </c>
-      <c r="S46" s="157">
+      <c r="S47" s="157">
         <f>'Statement Q'!H48</f>
         <v>331495</v>
       </c>
-      <c r="T46" s="157">
+      <c r="T47" s="157">
         <f>'Statement Q'!I48</f>
         <v>359241</v>
       </c>
-      <c r="U46" s="157">
+      <c r="U47" s="157">
         <f>'Statement Q'!J48</f>
         <v>379297</v>
       </c>
-      <c r="W46" s="157">
+      <c r="W47" s="157">
         <f t="shared" si="3"/>
         <v>379297</v>
       </c>
     </row>
-    <row r="48" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="15" t="s">
+    <row r="49" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
-      <c r="N48" s="14"/>
-      <c r="O48" s="14"/>
-      <c r="P48" s="14"/>
-      <c r="Q48" s="14"/>
-      <c r="R48" s="14"/>
-      <c r="S48" s="14"/>
-      <c r="T48" s="14"/>
-      <c r="U48" s="14"/>
-      <c r="W48" s="14"/>
-    </row>
-    <row r="49" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="9" t="s">
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="14"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="14"/>
+      <c r="P49" s="14"/>
+      <c r="Q49" s="14"/>
+      <c r="R49" s="14"/>
+      <c r="S49" s="14"/>
+      <c r="T49" s="14"/>
+      <c r="U49" s="14"/>
+      <c r="W49" s="14"/>
+    </row>
+    <row r="50" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="133">
+      <c r="C50" s="133">
         <f>'Statement Y'!C55</f>
         <v>45687</v>
       </c>
-      <c r="D49" s="133">
+      <c r="D50" s="133">
         <f>'Statement Y'!D55</f>
         <v>48351</v>
       </c>
-      <c r="E49" s="133">
+      <c r="E50" s="133">
         <f>'Statement Y'!E55</f>
         <v>59531</v>
       </c>
-      <c r="F49" s="133">
+      <c r="F50" s="133">
         <f>'Statement Y'!F55</f>
         <v>55256</v>
       </c>
-      <c r="G49" s="133">
+      <c r="G50" s="133">
         <f>'Statement Y'!G55</f>
         <v>57411</v>
       </c>
-      <c r="H49" s="133">
+      <c r="H50" s="133">
         <f>'Statement Y'!H55</f>
         <v>94680</v>
       </c>
-      <c r="I49" s="133">
+      <c r="I50" s="133">
         <f>'Statement Y'!I55</f>
         <v>99803</v>
       </c>
-      <c r="J49" s="133">
+      <c r="J50" s="133">
         <f>'Statement Y'!J55</f>
         <v>96995</v>
       </c>
-      <c r="K49" s="133">
+      <c r="K50" s="133">
         <f>'Statement Y'!K55</f>
         <v>93736</v>
       </c>
-      <c r="L49" s="133">
+      <c r="L50" s="133">
         <f>'Statement Y'!L55</f>
         <v>112010</v>
       </c>
-      <c r="N49" s="133">
+      <c r="N50" s="133">
         <f>'Statement Q'!C51</f>
         <v>23636</v>
       </c>
-      <c r="O49" s="133">
+      <c r="O50" s="133">
         <f>'Statement Q'!D51</f>
         <v>21448</v>
       </c>
-      <c r="P49" s="133">
+      <c r="P50" s="133">
         <f>'Statement Q'!E51</f>
         <v>14736</v>
       </c>
-      <c r="Q49" s="133">
+      <c r="Q50" s="133">
         <f>'Statement Q'!F51</f>
         <v>36330</v>
       </c>
-      <c r="R49" s="133">
+      <c r="R50" s="133">
         <f>'Statement Q'!G51</f>
         <v>24780</v>
       </c>
-      <c r="S49" s="133">
+      <c r="S50" s="133">
         <f>'Statement Q'!H51</f>
         <v>23434</v>
       </c>
-      <c r="T49" s="133">
+      <c r="T50" s="133">
         <f>'Statement Q'!I51</f>
         <v>27466</v>
       </c>
-      <c r="U49" s="133">
+      <c r="U50" s="133">
         <f>'Statement Q'!J51</f>
         <v>42097</v>
       </c>
-      <c r="W49" s="133">
-        <f>SUM(R49:U49)</f>
+      <c r="W50" s="133">
+        <f>SUM(R50:U50)</f>
         <v>117777</v>
       </c>
     </row>
-    <row r="50" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="9" t="s">
+    <row r="51" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C50" s="133">
+      <c r="C51" s="133">
         <f>'Statement Y'!C56</f>
         <v>10505</v>
       </c>
-      <c r="D50" s="133">
+      <c r="D51" s="133">
         <f>'Statement Y'!D56</f>
         <v>10157</v>
       </c>
-      <c r="E50" s="133">
+      <c r="E51" s="133">
         <f>'Statement Y'!E56</f>
         <v>10903</v>
       </c>
-      <c r="F50" s="133">
+      <c r="F51" s="133">
         <f>'Statement Y'!F56</f>
         <v>12547</v>
       </c>
-      <c r="G50" s="133">
+      <c r="G51" s="133">
         <f>'Statement Y'!G56</f>
         <v>11056</v>
       </c>
-      <c r="H50" s="133">
+      <c r="H51" s="133">
         <f>'Statement Y'!H56</f>
         <v>11284</v>
       </c>
-      <c r="I50" s="133">
+      <c r="I51" s="133">
         <f>'Statement Y'!I56</f>
         <v>11104</v>
       </c>
-      <c r="J50" s="133">
+      <c r="J51" s="133">
         <f>'Statement Y'!J56</f>
         <v>11519</v>
       </c>
-      <c r="K50" s="133">
+      <c r="K51" s="133">
         <f>'Statement Y'!K56</f>
         <v>11445</v>
       </c>
-      <c r="L50" s="133">
+      <c r="L51" s="133">
         <f>'Statement Y'!L56</f>
         <v>11698</v>
       </c>
-      <c r="N50" s="133">
+      <c r="N51" s="133">
         <f>'Statement Q'!C52</f>
         <v>0</v>
       </c>
-      <c r="O50" s="133">
+      <c r="O51" s="133">
         <f>'Statement Q'!D52</f>
         <v>0</v>
       </c>
-      <c r="P50" s="133">
+      <c r="P51" s="133">
         <f>'Statement Q'!E52</f>
         <v>0</v>
       </c>
-      <c r="Q50" s="133">
+      <c r="Q51" s="133">
         <f>'Statement Q'!F52</f>
         <v>3080</v>
       </c>
-      <c r="R50" s="133">
+      <c r="R51" s="133">
         <f>'Statement Q'!G52</f>
         <v>2661</v>
       </c>
-      <c r="S50" s="133">
+      <c r="S51" s="133">
         <f>'Statement Q'!H52</f>
         <v>2830</v>
       </c>
-      <c r="T50" s="133">
+      <c r="T51" s="133">
         <f>'Statement Q'!I52</f>
         <v>3127</v>
       </c>
-      <c r="U50" s="133">
+      <c r="U51" s="133">
         <f>'Statement Q'!J52</f>
         <v>3214</v>
       </c>
-      <c r="W50" s="133">
-        <f t="shared" ref="W50:W64" si="4">SUM(R50:U50)</f>
+      <c r="W51" s="133">
+        <f t="shared" ref="W51:W65" si="4">SUM(R51:U51)</f>
         <v>11832</v>
       </c>
     </row>
-    <row r="51" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="12" t="s">
+    <row r="52" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C51" s="133">
+      <c r="C52" s="133">
         <f>'Statement Y'!C57</f>
         <v>4210</v>
       </c>
-      <c r="D51" s="133">
+      <c r="D52" s="133">
         <f>'Statement Y'!D57</f>
         <v>4840</v>
       </c>
-      <c r="E51" s="133">
+      <c r="E52" s="133">
         <f>'Statement Y'!E57</f>
         <v>5340</v>
       </c>
-      <c r="F51" s="133">
+      <c r="F52" s="133">
         <f>'Statement Y'!F57</f>
         <v>6068</v>
       </c>
-      <c r="G51" s="133">
+      <c r="G52" s="133">
         <f>'Statement Y'!G57</f>
         <v>6829</v>
       </c>
-      <c r="H51" s="133">
+      <c r="H52" s="133">
         <f>'Statement Y'!H57</f>
         <v>7906</v>
       </c>
-      <c r="I51" s="133">
+      <c r="I52" s="133">
         <f>'Statement Y'!I57</f>
         <v>9038</v>
       </c>
-      <c r="J51" s="133">
+      <c r="J52" s="133">
         <f>'Statement Y'!J57</f>
         <v>10833</v>
       </c>
-      <c r="K51" s="133">
+      <c r="K52" s="133">
         <f>'Statement Y'!K57</f>
         <v>11688</v>
       </c>
-      <c r="L51" s="133">
+      <c r="L52" s="133">
         <f>'Statement Y'!L57</f>
         <v>12863</v>
       </c>
-      <c r="N51" s="133">
+      <c r="N52" s="133">
         <f>'Statement Q'!C53</f>
         <v>0</v>
       </c>
-      <c r="O51" s="133">
+      <c r="O52" s="133">
         <f>'Statement Q'!D53</f>
         <v>0</v>
       </c>
-      <c r="P51" s="133">
+      <c r="P52" s="133">
         <f>'Statement Q'!E53</f>
         <v>0</v>
       </c>
-      <c r="Q51" s="133">
+      <c r="Q52" s="133">
         <f>'Statement Q'!F53</f>
         <v>3286</v>
       </c>
-      <c r="R51" s="133">
+      <c r="R52" s="133">
         <f>'Statement Q'!G53</f>
         <v>3226</v>
       </c>
-      <c r="S51" s="133">
+      <c r="S52" s="133">
         <f>'Statement Q'!H53</f>
         <v>3168</v>
       </c>
-      <c r="T51" s="133">
+      <c r="T52" s="133">
         <f>'Statement Q'!I53</f>
         <v>3183</v>
       </c>
-      <c r="U51" s="133">
+      <c r="U52" s="133">
         <f>'Statement Q'!J53</f>
         <v>3594</v>
       </c>
-      <c r="W51" s="133">
+      <c r="W52" s="133">
         <f t="shared" si="4"/>
         <v>13171</v>
       </c>
     </row>
-    <row r="52" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="12" t="s">
+    <row r="53" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="C52" s="133">
+      <c r="C53" s="133">
         <f>'Statement Y'!C58</f>
         <v>4938</v>
       </c>
-      <c r="D52" s="133">
+      <c r="D53" s="133">
         <f>'Statement Y'!D58</f>
         <v>5966</v>
       </c>
-      <c r="E52" s="133">
+      <c r="E53" s="133">
         <f>'Statement Y'!E58</f>
         <v>-32590</v>
       </c>
-      <c r="F52" s="133">
+      <c r="F53" s="133">
         <f>'Statement Y'!F58</f>
         <v>-340</v>
       </c>
-      <c r="G52" s="133">
+      <c r="G53" s="133">
         <f>'Statement Y'!G58</f>
         <v>-215</v>
       </c>
-      <c r="H52" s="133">
+      <c r="H53" s="133">
         <f>'Statement Y'!H58</f>
         <v>-4774</v>
       </c>
-      <c r="I52" s="133">
+      <c r="I53" s="133">
         <f>'Statement Y'!I58</f>
         <v>895</v>
       </c>
-      <c r="J52" s="133">
+      <c r="J53" s="133">
         <f>'Statement Y'!J58</f>
         <v>0</v>
       </c>
-      <c r="K52" s="133">
+      <c r="K53" s="133">
         <f>'Statement Y'!K58</f>
         <v>0</v>
       </c>
-      <c r="L52" s="133">
+      <c r="L53" s="133">
         <f>'Statement Y'!L58</f>
         <v>0</v>
       </c>
-      <c r="N52" s="133">
-        <v>0</v>
-      </c>
-      <c r="O52" s="133">
-        <v>0</v>
-      </c>
-      <c r="P52" s="133">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="133">
-        <v>0</v>
-      </c>
-      <c r="R52" s="133">
-        <v>0</v>
-      </c>
-      <c r="S52" s="133">
-        <v>0</v>
-      </c>
-      <c r="T52" s="133">
-        <v>0</v>
-      </c>
-      <c r="U52" s="133">
-        <v>0</v>
-      </c>
-      <c r="W52" s="133">
+      <c r="N53" s="133">
+        <v>0</v>
+      </c>
+      <c r="O53" s="133">
+        <v>0</v>
+      </c>
+      <c r="P53" s="133">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="133">
+        <v>0</v>
+      </c>
+      <c r="R53" s="133">
+        <v>0</v>
+      </c>
+      <c r="S53" s="133">
+        <v>0</v>
+      </c>
+      <c r="T53" s="133">
+        <v>0</v>
+      </c>
+      <c r="U53" s="133">
+        <v>0</v>
+      </c>
+      <c r="W53" s="133">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="12" t="s">
+    <row r="54" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="C53" s="133">
+      <c r="C54" s="133">
         <f>'Statement Y'!C59</f>
         <v>0</v>
       </c>
-      <c r="D53" s="133">
+      <c r="D54" s="133">
         <f>'Statement Y'!D59</f>
         <v>-166</v>
       </c>
-      <c r="E53" s="133">
+      <c r="E54" s="133">
         <f>'Statement Y'!E59</f>
         <v>-444</v>
       </c>
-      <c r="F53" s="133">
+      <c r="F54" s="133">
         <f>'Statement Y'!F59</f>
         <v>-652</v>
       </c>
-      <c r="G53" s="133">
+      <c r="G54" s="133">
         <f>'Statement Y'!G59</f>
         <v>-97</v>
       </c>
-      <c r="H53" s="133">
+      <c r="H54" s="133">
         <f>'Statement Y'!H59</f>
         <v>-147</v>
       </c>
-      <c r="I53" s="133">
+      <c r="I54" s="133">
         <f>'Statement Y'!I59</f>
         <v>111</v>
       </c>
-      <c r="J53" s="133">
+      <c r="J54" s="133">
         <f>'Statement Y'!J59</f>
         <v>-2227</v>
       </c>
-      <c r="K53" s="133">
+      <c r="K54" s="133">
         <f>'Statement Y'!K59</f>
         <v>-2266</v>
       </c>
-      <c r="L53" s="133">
+      <c r="L54" s="133">
         <f>'Statement Y'!L59</f>
         <v>-89</v>
       </c>
-      <c r="N53" s="133">
+      <c r="N54" s="133">
         <f>'Statement Q'!C54</f>
         <v>0</v>
       </c>
-      <c r="O53" s="133">
+      <c r="O54" s="133">
         <f>'Statement Q'!D54</f>
         <v>0</v>
       </c>
-      <c r="P53" s="133">
+      <c r="P54" s="133">
         <f>'Statement Q'!E54</f>
         <v>0</v>
       </c>
-      <c r="Q53" s="133">
+      <c r="Q54" s="133">
         <f>'Statement Q'!F54</f>
         <v>-2009</v>
       </c>
-      <c r="R53" s="133">
+      <c r="R54" s="133">
         <f>'Statement Q'!G54</f>
         <v>-208</v>
       </c>
-      <c r="S53" s="133">
+      <c r="S54" s="133">
         <f>'Statement Q'!H54</f>
         <v>469</v>
       </c>
-      <c r="T53" s="133">
+      <c r="T54" s="133">
         <f>'Statement Q'!I54</f>
         <v>1659</v>
       </c>
-      <c r="U53" s="133">
+      <c r="U54" s="133">
         <f>'Statement Q'!J54</f>
         <v>-528</v>
       </c>
-      <c r="W53" s="133">
+      <c r="W54" s="133">
         <f t="shared" si="4"/>
         <v>1392</v>
       </c>
     </row>
-    <row r="54" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="9" t="s">
+    <row r="55" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="C54" s="133">
+      <c r="C55" s="133">
         <f>SUM('Statement Y'!C60:C66)</f>
         <v>484</v>
       </c>
-      <c r="D54" s="133">
+      <c r="D55" s="133">
         <f>SUM('Statement Y'!D60:D66)</f>
         <v>-4923</v>
       </c>
-      <c r="E54" s="133">
+      <c r="E55" s="133">
         <f>SUM('Statement Y'!E60:E66)</f>
         <v>34694</v>
       </c>
-      <c r="F54" s="133">
+      <c r="F55" s="133">
         <f>SUM('Statement Y'!F60:F66)</f>
         <v>-3488</v>
       </c>
-      <c r="G54" s="133">
+      <c r="G55" s="133">
         <f>SUM('Statement Y'!G60:G66)</f>
         <v>5690</v>
       </c>
-      <c r="H54" s="133">
+      <c r="H55" s="133">
         <f>SUM('Statement Y'!H60:H66)</f>
         <v>-4911</v>
       </c>
-      <c r="I54" s="133">
+      <c r="I55" s="133">
         <f>SUM('Statement Y'!I60:I66)</f>
         <v>1200</v>
       </c>
-      <c r="J54" s="133">
+      <c r="J55" s="133">
         <f>SUM('Statement Y'!J60:J66)</f>
         <v>-6577</v>
       </c>
-      <c r="K54" s="133">
+      <c r="K55" s="133">
         <f>SUM('Statement Y'!K60:K66)</f>
         <v>3651</v>
       </c>
-      <c r="L54" s="133">
+      <c r="L55" s="133">
         <f>SUM('Statement Y'!L60:L66)</f>
         <v>-25000</v>
       </c>
-      <c r="N54" s="133">
+      <c r="N55" s="133">
         <f>SUM('Statement Q'!C55:C60)</f>
         <v>0</v>
       </c>
-      <c r="O54" s="133">
+      <c r="O55" s="133">
         <f>SUM('Statement Q'!D55:D60)</f>
         <v>0</v>
       </c>
-      <c r="P54" s="133">
+      <c r="P55" s="133">
         <f>SUM('Statement Q'!E55:E60)</f>
         <v>0</v>
       </c>
-      <c r="Q54" s="133">
+      <c r="Q55" s="133">
         <f>SUM('Statement Q'!F55:F60)</f>
         <v>-10752</v>
       </c>
-      <c r="R54" s="133">
+      <c r="R55" s="133">
         <f>SUM('Statement Q'!G55:G60)</f>
         <v>-6507</v>
       </c>
-      <c r="S54" s="133">
+      <c r="S55" s="133">
         <f>SUM('Statement Q'!H55:H60)</f>
         <v>-2034</v>
       </c>
-      <c r="T54" s="133">
+      <c r="T55" s="133">
         <f>SUM('Statement Q'!I55:I60)</f>
         <v>-5707</v>
       </c>
-      <c r="U54" s="133">
+      <c r="U55" s="133">
         <f>SUM('Statement Q'!J55:J60)</f>
         <v>5548</v>
       </c>
-      <c r="W54" s="133">
+      <c r="W55" s="133">
         <f t="shared" si="4"/>
         <v>-8700</v>
       </c>
     </row>
-    <row r="55" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="17" t="s">
+    <row r="56" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C55" s="153">
+      <c r="C56" s="153">
         <f>'Statement Y'!C67</f>
         <v>65824</v>
       </c>
-      <c r="D55" s="153">
+      <c r="D56" s="153">
         <f>'Statement Y'!D67</f>
         <v>64225</v>
       </c>
-      <c r="E55" s="153">
+      <c r="E56" s="153">
         <f>'Statement Y'!E67</f>
         <v>77434</v>
       </c>
-      <c r="F55" s="153">
+      <c r="F56" s="153">
         <f>'Statement Y'!F67</f>
         <v>69391</v>
       </c>
-      <c r="G55" s="153">
+      <c r="G56" s="153">
         <f>'Statement Y'!G67</f>
         <v>80674</v>
       </c>
-      <c r="H55" s="153">
+      <c r="H56" s="153">
         <f>'Statement Y'!H67</f>
         <v>104038</v>
       </c>
-      <c r="I55" s="153">
+      <c r="I56" s="153">
         <f>'Statement Y'!I67</f>
         <v>122151</v>
       </c>
-      <c r="J55" s="153">
+      <c r="J56" s="153">
         <f>'Statement Y'!J67</f>
         <v>110543</v>
       </c>
-      <c r="K55" s="153">
+      <c r="K56" s="153">
         <f>'Statement Y'!K67</f>
         <v>118254</v>
       </c>
-      <c r="L55" s="153">
+      <c r="L56" s="153">
         <f>'Statement Y'!L67</f>
         <v>111482</v>
       </c>
-      <c r="N55" s="153">
+      <c r="N56" s="153">
         <f>'Statement Q'!C61</f>
         <v>0</v>
       </c>
-      <c r="O55" s="153">
+      <c r="O56" s="153">
         <f>'Statement Q'!D61</f>
         <v>0</v>
       </c>
-      <c r="P55" s="153">
+      <c r="P56" s="153">
         <f>'Statement Q'!E61</f>
         <v>0</v>
       </c>
-      <c r="Q55" s="153">
+      <c r="Q56" s="153">
         <f>'Statement Q'!F61</f>
         <v>29935</v>
       </c>
-      <c r="R55" s="153">
+      <c r="R56" s="153">
         <f>'Statement Q'!G61</f>
         <v>23952</v>
       </c>
-      <c r="S55" s="153">
+      <c r="S56" s="153">
         <f>'Statement Q'!H61</f>
         <v>27867</v>
       </c>
-      <c r="T55" s="153">
+      <c r="T56" s="153">
         <f>'Statement Q'!I61</f>
         <v>29728</v>
       </c>
-      <c r="U55" s="153">
+      <c r="U56" s="153">
         <f>'Statement Q'!J61</f>
         <v>53925</v>
       </c>
-      <c r="W55" s="153">
+      <c r="W56" s="153">
         <f t="shared" si="4"/>
         <v>135472</v>
       </c>
     </row>
-    <row r="56" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="9" t="s">
+    <row r="57" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="133">
+      <c r="C57" s="133">
         <f>'Statement Y'!C71</f>
         <v>-12734</v>
       </c>
-      <c r="D56" s="133">
+      <c r="D57" s="133">
         <f>'Statement Y'!D71</f>
         <v>-12451</v>
       </c>
-      <c r="E56" s="133">
+      <c r="E57" s="133">
         <f>'Statement Y'!E71</f>
         <v>-13313</v>
       </c>
-      <c r="F56" s="133">
+      <c r="F57" s="133">
         <f>'Statement Y'!F71</f>
         <v>-10495</v>
       </c>
-      <c r="G56" s="133">
+      <c r="G57" s="133">
         <f>'Statement Y'!G71</f>
         <v>-7309</v>
       </c>
-      <c r="H56" s="133">
+      <c r="H57" s="133">
         <f>'Statement Y'!H71</f>
         <v>-11085</v>
       </c>
-      <c r="I56" s="133">
+      <c r="I57" s="133">
         <f>'Statement Y'!I71</f>
         <v>-10708</v>
       </c>
-      <c r="J56" s="133">
+      <c r="J57" s="133">
         <f>'Statement Y'!J71</f>
         <v>-10959</v>
       </c>
-      <c r="K56" s="133">
+      <c r="K57" s="133">
         <f>'Statement Y'!K71</f>
         <v>-9447</v>
       </c>
-      <c r="L56" s="133">
+      <c r="L57" s="133">
         <f>'Statement Y'!L71</f>
         <v>-12715</v>
       </c>
-      <c r="N56" s="133">
+      <c r="N57" s="133">
         <f>'Statement Q'!C65</f>
         <v>0</v>
       </c>
-      <c r="O56" s="133">
+      <c r="O57" s="133">
         <f>'Statement Q'!D65</f>
         <v>0</v>
       </c>
-      <c r="P56" s="133">
+      <c r="P57" s="133">
         <f>'Statement Q'!E65</f>
         <v>0</v>
       </c>
-      <c r="Q56" s="133">
+      <c r="Q57" s="133">
         <f>'Statement Q'!F65</f>
         <v>-2940</v>
       </c>
-      <c r="R56" s="133">
+      <c r="R57" s="133">
         <f>'Statement Q'!G65</f>
         <v>-3071</v>
       </c>
-      <c r="S56" s="133">
+      <c r="S57" s="133">
         <f>'Statement Q'!H65</f>
         <v>-3462</v>
       </c>
-      <c r="T56" s="133">
+      <c r="T57" s="133">
         <f>'Statement Q'!I65</f>
         <v>-3242</v>
       </c>
-      <c r="U56" s="133">
+      <c r="U57" s="133">
         <f>'Statement Q'!J65</f>
         <v>-2373</v>
       </c>
-      <c r="W56" s="133">
+      <c r="W57" s="133">
         <f t="shared" si="4"/>
         <v>-12148</v>
       </c>
     </row>
-    <row r="57" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="17" t="s">
+    <row r="58" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C57" s="153">
+      <c r="C58" s="153">
         <f>'Statement Y'!C78</f>
         <v>-45977</v>
       </c>
-      <c r="D57" s="153">
+      <c r="D58" s="153">
         <f>'Statement Y'!D78</f>
         <v>-46446</v>
       </c>
-      <c r="E57" s="153">
+      <c r="E58" s="153">
         <f>'Statement Y'!E78</f>
         <v>16066</v>
       </c>
-      <c r="F57" s="153">
+      <c r="F58" s="153">
         <f>'Statement Y'!F78</f>
         <v>45896</v>
       </c>
-      <c r="G57" s="153">
+      <c r="G58" s="153">
         <f>'Statement Y'!G78</f>
         <v>-4289</v>
       </c>
-      <c r="H57" s="153">
+      <c r="H58" s="153">
         <f>'Statement Y'!H78</f>
         <v>-14545</v>
       </c>
-      <c r="I57" s="153">
+      <c r="I58" s="153">
         <f>'Statement Y'!I78</f>
         <v>-22354</v>
       </c>
-      <c r="J57" s="153">
+      <c r="J58" s="153">
         <f>'Statement Y'!J78</f>
         <v>3705</v>
       </c>
-      <c r="K57" s="153">
+      <c r="K58" s="153">
         <f>'Statement Y'!K78</f>
         <v>2935</v>
       </c>
-      <c r="L57" s="153">
+      <c r="L58" s="153">
         <f>'Statement Y'!L78</f>
         <v>15195</v>
       </c>
-      <c r="N57" s="153">
+      <c r="N58" s="153">
         <f>'Statement Q'!C67</f>
         <v>0</v>
       </c>
-      <c r="O57" s="153">
+      <c r="O58" s="153">
         <f>'Statement Q'!D67</f>
         <v>0</v>
       </c>
-      <c r="P57" s="153">
+      <c r="P58" s="153">
         <f>'Statement Q'!E67</f>
         <v>0</v>
       </c>
-      <c r="Q57" s="153">
+      <c r="Q58" s="153">
         <f>'Statement Q'!F67</f>
         <v>9792</v>
       </c>
-      <c r="R57" s="153">
+      <c r="R58" s="153">
         <f>'Statement Q'!G67</f>
         <v>2917</v>
       </c>
-      <c r="S57" s="153">
+      <c r="S58" s="153">
         <f>'Statement Q'!H67</f>
         <v>5073</v>
       </c>
-      <c r="T57" s="153">
+      <c r="T58" s="153">
         <f>'Statement Q'!I67</f>
         <v>-2587</v>
       </c>
-      <c r="U57" s="153">
+      <c r="U58" s="153">
         <f>'Statement Q'!J67</f>
         <v>-4886</v>
       </c>
-      <c r="W57" s="153">
+      <c r="W58" s="153">
         <f t="shared" si="4"/>
         <v>517</v>
       </c>
     </row>
-    <row r="58" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="9" t="s">
+    <row r="59" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C58" s="133">
+      <c r="C59" s="133">
         <f>'Statement Y'!C79</f>
         <v>495</v>
       </c>
-      <c r="D58" s="133">
+      <c r="D59" s="133">
         <f>'Statement Y'!D79</f>
         <v>555</v>
       </c>
-      <c r="E58" s="133">
+      <c r="E59" s="133">
         <f>'Statement Y'!E79</f>
         <v>669</v>
       </c>
-      <c r="F58" s="133">
+      <c r="F59" s="133">
         <f>'Statement Y'!F79</f>
         <v>781</v>
       </c>
-      <c r="G58" s="133">
+      <c r="G59" s="133">
         <f>'Statement Y'!G79</f>
         <v>0</v>
       </c>
-      <c r="H58" s="133">
+      <c r="H59" s="133">
         <f>'Statement Y'!H79</f>
         <v>0</v>
       </c>
-      <c r="I58" s="133">
+      <c r="I59" s="133">
         <f>'Statement Y'!I79</f>
         <v>0</v>
       </c>
-      <c r="J58" s="133">
+      <c r="J59" s="133">
         <f>'Statement Y'!J79</f>
         <v>0</v>
       </c>
-      <c r="K58" s="133">
+      <c r="K59" s="133">
         <f>'Statement Y'!K79</f>
         <v>0</v>
       </c>
-      <c r="L58" s="133">
+      <c r="L59" s="133">
         <f>'Statement Y'!L79</f>
         <v>0</v>
       </c>
-      <c r="N58" s="133">
-        <v>0</v>
-      </c>
-      <c r="O58" s="133">
-        <v>0</v>
-      </c>
-      <c r="P58" s="133">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="133">
-        <v>0</v>
-      </c>
-      <c r="R58" s="133">
-        <v>0</v>
-      </c>
-      <c r="S58" s="133">
-        <v>0</v>
-      </c>
-      <c r="T58" s="133">
-        <v>0</v>
-      </c>
-      <c r="U58" s="133">
-        <v>0</v>
-      </c>
-      <c r="W58" s="133">
+      <c r="N59" s="133">
+        <v>0</v>
+      </c>
+      <c r="O59" s="133">
+        <v>0</v>
+      </c>
+      <c r="P59" s="133">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="133">
+        <v>0</v>
+      </c>
+      <c r="R59" s="133">
+        <v>0</v>
+      </c>
+      <c r="S59" s="133">
+        <v>0</v>
+      </c>
+      <c r="T59" s="133">
+        <v>0</v>
+      </c>
+      <c r="U59" s="133">
+        <v>0</v>
+      </c>
+      <c r="W59" s="133">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="9" t="s">
+    <row r="60" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C59" s="133">
+      <c r="C60" s="133">
         <f>'Statement Y'!C86</f>
         <v>-397</v>
       </c>
-      <c r="D59" s="133">
+      <c r="D60" s="133">
         <f>'Statement Y'!D86</f>
         <v>3852</v>
       </c>
-      <c r="E59" s="133">
+      <c r="E60" s="133">
         <f>'Statement Y'!E86</f>
         <v>-37</v>
       </c>
-      <c r="F59" s="133">
+      <c r="F60" s="133">
         <f>'Statement Y'!F86</f>
         <v>-5977</v>
       </c>
-      <c r="G59" s="133">
+      <c r="G60" s="133">
         <f>'Statement Y'!G86</f>
         <v>-963</v>
       </c>
-      <c r="H59" s="133">
+      <c r="H60" s="133">
         <f>'Statement Y'!H86</f>
         <v>1022</v>
       </c>
-      <c r="I59" s="133">
+      <c r="I60" s="133">
         <f>'Statement Y'!I86</f>
         <v>3955</v>
       </c>
-      <c r="J59" s="133">
+      <c r="J60" s="133">
         <f>'Statement Y'!J86</f>
         <v>-3978</v>
       </c>
-      <c r="K59" s="133">
+      <c r="K60" s="133">
         <f>'Statement Y'!K86</f>
         <v>3960</v>
       </c>
-      <c r="L59" s="133">
+      <c r="L60" s="133">
         <f>'Statement Y'!L86</f>
         <v>-2032</v>
       </c>
-      <c r="N59" s="133">
+      <c r="N60" s="133">
         <f>'Statement Q'!C70</f>
         <v>0</v>
       </c>
-      <c r="O59" s="133">
+      <c r="O60" s="133">
         <f>'Statement Q'!D70</f>
         <v>0</v>
       </c>
-      <c r="P59" s="133">
+      <c r="P60" s="133">
         <f>'Statement Q'!E70</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="133">
+      <c r="Q60" s="133">
         <f>'Statement Q'!F70</f>
         <v>-23606</v>
       </c>
-      <c r="R59" s="133">
+      <c r="R60" s="133">
         <f>'Statement Q'!G70</f>
         <v>-25898</v>
       </c>
-      <c r="S59" s="133">
+      <c r="S60" s="133">
         <f>'Statement Q'!H70</f>
         <v>-21075</v>
       </c>
-      <c r="T59" s="133">
+      <c r="T60" s="133">
         <f>'Statement Q'!I70</f>
         <v>-20132</v>
       </c>
-      <c r="U59" s="133">
+      <c r="U60" s="133">
         <f>'Statement Q'!J70</f>
         <v>-24701</v>
       </c>
-      <c r="W59" s="133">
+      <c r="W60" s="133">
         <f t="shared" si="4"/>
         <v>-91806</v>
       </c>
     </row>
-    <row r="60" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="9" t="s">
+    <row r="61" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="C60" s="133">
+      <c r="C61" s="133">
         <f>'Statement Y'!C82</f>
         <v>-12150</v>
       </c>
-      <c r="D60" s="133">
+      <c r="D61" s="133">
         <f>'Statement Y'!D82</f>
         <v>-12769</v>
       </c>
-      <c r="E60" s="133">
+      <c r="E61" s="133">
         <f>'Statement Y'!E82</f>
         <v>-13712</v>
       </c>
-      <c r="F60" s="133">
+      <c r="F61" s="133">
         <f>'Statement Y'!F82</f>
         <v>-14119</v>
       </c>
-      <c r="G60" s="133">
+      <c r="G61" s="133">
         <f>'Statement Y'!G82</f>
         <v>-14081</v>
       </c>
-      <c r="H60" s="133">
+      <c r="H61" s="133">
         <f>'Statement Y'!H82</f>
         <v>-14467</v>
       </c>
-      <c r="I60" s="133">
+      <c r="I61" s="133">
         <f>'Statement Y'!I82</f>
         <v>-14841</v>
       </c>
-      <c r="J60" s="133">
+      <c r="J61" s="133">
         <f>'Statement Y'!J82</f>
         <v>-15025</v>
       </c>
-      <c r="K60" s="133">
+      <c r="K61" s="133">
         <f>'Statement Y'!K82</f>
         <v>-15234</v>
       </c>
-      <c r="L60" s="133">
+      <c r="L61" s="133">
         <f>'Statement Y'!L82</f>
         <v>-15421</v>
       </c>
-      <c r="N60" s="133">
+      <c r="N61" s="133">
         <f>'Statement Q'!C69</f>
         <v>0</v>
       </c>
-      <c r="O60" s="133">
+      <c r="O61" s="133">
         <f>'Statement Q'!D69</f>
         <v>0</v>
       </c>
-      <c r="P60" s="133">
+      <c r="P61" s="133">
         <f>'Statement Q'!E69</f>
         <v>0</v>
       </c>
-      <c r="Q60" s="133">
+      <c r="Q61" s="133">
         <f>'Statement Q'!F69</f>
         <v>-3856</v>
       </c>
-      <c r="R60" s="133">
+      <c r="R61" s="133">
         <f>'Statement Q'!G69</f>
         <v>-3758</v>
       </c>
-      <c r="S60" s="133">
+      <c r="S61" s="133">
         <f>'Statement Q'!H69</f>
         <v>-3945</v>
       </c>
-      <c r="T60" s="133">
+      <c r="T61" s="133">
         <f>'Statement Q'!I69</f>
         <v>-3862</v>
       </c>
-      <c r="U60" s="133">
+      <c r="U61" s="133">
         <f>'Statement Q'!J69</f>
         <v>-3921</v>
       </c>
-      <c r="W60" s="133">
+      <c r="W61" s="133">
         <f t="shared" si="4"/>
         <v>-15486</v>
       </c>
     </row>
-    <row r="61" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="9" t="s">
+    <row r="62" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="C61" s="133">
+      <c r="C62" s="133">
         <f>'Statement Y'!C84</f>
         <v>24954</v>
       </c>
-      <c r="D61" s="133">
+      <c r="D62" s="133">
         <f>'Statement Y'!D84</f>
         <v>28662</v>
       </c>
-      <c r="E61" s="133">
+      <c r="E62" s="133">
         <f>'Statement Y'!E84</f>
         <v>6969</v>
       </c>
-      <c r="F61" s="133">
+      <c r="F62" s="133">
         <f>'Statement Y'!F84</f>
         <v>6963</v>
       </c>
-      <c r="G61" s="133">
+      <c r="G62" s="133">
         <f>'Statement Y'!G84</f>
         <v>16091</v>
       </c>
-      <c r="H61" s="133">
+      <c r="H62" s="133">
         <f>'Statement Y'!H84</f>
         <v>20393</v>
       </c>
-      <c r="I61" s="133">
+      <c r="I62" s="133">
         <f>'Statement Y'!I84</f>
         <v>5465</v>
       </c>
-      <c r="J61" s="133">
+      <c r="J62" s="133">
         <f>'Statement Y'!J84</f>
         <v>5228</v>
       </c>
-      <c r="K61" s="133">
+      <c r="K62" s="133">
         <f>'Statement Y'!K84</f>
         <v>0</v>
       </c>
-      <c r="L61" s="133">
+      <c r="L62" s="133">
         <f>'Statement Y'!L84</f>
         <v>4481</v>
       </c>
-      <c r="N61" s="133">
+      <c r="N62" s="133">
         <f>'Statement Q'!C71</f>
         <v>0</v>
       </c>
-      <c r="O61" s="133">
+      <c r="O62" s="133">
         <f>'Statement Q'!D71</f>
         <v>0</v>
       </c>
-      <c r="P61" s="133">
+      <c r="P62" s="133">
         <f>'Statement Q'!E71</f>
         <v>0</v>
       </c>
-      <c r="Q61" s="133">
+      <c r="Q62" s="133">
         <f>'Statement Q'!F71</f>
         <v>0</v>
       </c>
-      <c r="R61" s="133">
+      <c r="R62" s="133">
         <f>'Statement Q'!G71</f>
         <v>0</v>
       </c>
-      <c r="S61" s="133">
+      <c r="S62" s="133">
         <f>'Statement Q'!H71</f>
         <v>4481</v>
       </c>
-      <c r="T61" s="133">
+      <c r="T62" s="133">
         <f>'Statement Q'!I71</f>
         <v>0</v>
       </c>
-      <c r="U61" s="133">
+      <c r="U62" s="133">
         <f>'Statement Q'!J71</f>
         <v>0</v>
       </c>
-      <c r="W61" s="133">
+      <c r="W62" s="133">
         <f t="shared" si="4"/>
         <v>4481</v>
       </c>
     </row>
-    <row r="62" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="9" t="s">
+    <row r="63" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="C62" s="133">
+      <c r="C63" s="133">
         <f>'Statement Y'!C85</f>
         <v>-2500</v>
       </c>
-      <c r="D62" s="133">
+      <c r="D63" s="133">
         <f>'Statement Y'!D85</f>
         <v>-3500</v>
       </c>
-      <c r="E62" s="133">
+      <c r="E63" s="133">
         <f>'Statement Y'!E85</f>
         <v>-6500</v>
       </c>
-      <c r="F62" s="133">
+      <c r="F63" s="133">
         <f>'Statement Y'!F85</f>
         <v>-8805</v>
       </c>
-      <c r="G62" s="133">
+      <c r="G63" s="133">
         <f>'Statement Y'!G85</f>
         <v>-12629</v>
       </c>
-      <c r="H62" s="133">
+      <c r="H63" s="133">
         <f>'Statement Y'!H85</f>
         <v>-8750</v>
       </c>
-      <c r="I62" s="133">
+      <c r="I63" s="133">
         <f>'Statement Y'!I85</f>
         <v>-9543</v>
       </c>
-      <c r="J62" s="133">
+      <c r="J63" s="133">
         <f>'Statement Y'!J85</f>
         <v>-11151</v>
       </c>
-      <c r="K62" s="133">
+      <c r="K63" s="133">
         <f>'Statement Y'!K85</f>
         <v>-9958</v>
       </c>
-      <c r="L62" s="133">
+      <c r="L63" s="133">
         <f>'Statement Y'!L85</f>
         <v>-10932</v>
       </c>
-      <c r="N62" s="133">
+      <c r="N63" s="133">
         <f>'Statement Q'!C72</f>
         <v>0</v>
       </c>
-      <c r="O62" s="133">
+      <c r="O63" s="133">
         <f>'Statement Q'!D72</f>
         <v>0</v>
       </c>
-      <c r="P62" s="133">
+      <c r="P63" s="133">
         <f>'Statement Q'!E72</f>
         <v>0</v>
       </c>
-      <c r="Q62" s="133">
+      <c r="Q63" s="133">
         <f>'Statement Q'!F72</f>
         <v>-1009</v>
       </c>
-      <c r="R62" s="133">
+      <c r="R63" s="133">
         <f>'Statement Q'!G72</f>
         <v>-3000</v>
       </c>
-      <c r="S62" s="133">
+      <c r="S63" s="133">
         <f>'Statement Q'!H72</f>
         <v>-5673</v>
       </c>
-      <c r="T62" s="133">
+      <c r="T63" s="133">
         <f>'Statement Q'!I72</f>
         <v>-1250</v>
       </c>
-      <c r="U62" s="133">
+      <c r="U63" s="133">
         <f>'Statement Q'!J72</f>
         <v>-2164</v>
       </c>
-      <c r="W62" s="133">
+      <c r="W63" s="133">
         <f t="shared" si="4"/>
         <v>-12087</v>
       </c>
     </row>
-    <row r="63" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="17" t="s">
+    <row r="64" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C63" s="153">
+      <c r="C64" s="153">
         <f>'Statement Y'!C88</f>
         <v>-20483</v>
       </c>
-      <c r="D63" s="153">
+      <c r="D64" s="153">
         <f>'Statement Y'!D88</f>
         <v>-17974</v>
       </c>
-      <c r="E63" s="153">
+      <c r="E64" s="153">
         <f>'Statement Y'!E88</f>
         <v>-87876</v>
       </c>
-      <c r="F63" s="153">
+      <c r="F64" s="153">
         <f>'Statement Y'!F88</f>
         <v>-90976</v>
       </c>
-      <c r="G63" s="153">
+      <c r="G64" s="153">
         <f>'Statement Y'!G88</f>
         <v>-86820</v>
       </c>
-      <c r="H63" s="153">
+      <c r="H64" s="153">
         <f>'Statement Y'!H88</f>
         <v>-93353</v>
       </c>
-      <c r="I63" s="153">
+      <c r="I64" s="153">
         <f>'Statement Y'!I88</f>
         <v>-110749</v>
       </c>
-      <c r="J63" s="153">
+      <c r="J64" s="153">
         <f>'Statement Y'!J88</f>
         <v>-108488</v>
       </c>
-      <c r="K63" s="153">
+      <c r="K64" s="153">
         <f>'Statement Y'!K88</f>
         <v>-121983</v>
       </c>
-      <c r="L63" s="153">
+      <c r="L64" s="153">
         <f>'Statement Y'!L88</f>
         <v>-120686</v>
       </c>
-      <c r="N63" s="153">
+      <c r="N64" s="153">
         <f>'Statement Q'!C75</f>
         <v>0</v>
       </c>
-      <c r="O63" s="153">
+      <c r="O64" s="153">
         <f>'Statement Q'!D75</f>
         <v>0</v>
       </c>
-      <c r="P63" s="153">
+      <c r="P64" s="153">
         <f>'Statement Q'!E75</f>
         <v>0</v>
       </c>
-      <c r="Q63" s="153">
+      <c r="Q64" s="153">
         <f>'Statement Q'!F75</f>
         <v>-39371</v>
       </c>
-      <c r="R63" s="153">
+      <c r="R64" s="153">
         <f>'Statement Q'!G75</f>
         <v>-29006</v>
       </c>
-      <c r="S63" s="153">
+      <c r="S64" s="153">
         <f>'Statement Q'!H75</f>
         <v>-24833</v>
       </c>
-      <c r="T63" s="153">
+      <c r="T64" s="153">
         <f>'Statement Q'!I75</f>
         <v>-27476</v>
       </c>
-      <c r="U63" s="153">
+      <c r="U64" s="153">
         <f>'Statement Q'!J75</f>
         <v>-39656</v>
       </c>
-      <c r="W63" s="153">
+      <c r="W64" s="153">
         <f t="shared" si="4"/>
         <v>-120971</v>
       </c>
     </row>
-    <row r="64" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="11" t="s">
+    <row r="65" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C64" s="156">
+      <c r="C65" s="156">
         <f>'Statement Y'!C89</f>
         <v>-636</v>
       </c>
-      <c r="D64" s="156">
+      <c r="D65" s="156">
         <f>'Statement Y'!D89</f>
         <v>-195</v>
       </c>
-      <c r="E64" s="156">
+      <c r="E65" s="156">
         <f>'Statement Y'!E89</f>
         <v>5624</v>
       </c>
-      <c r="F64" s="156">
+      <c r="F65" s="156">
         <f>'Statement Y'!F89</f>
         <v>24311</v>
       </c>
-      <c r="G64" s="156">
+      <c r="G65" s="156">
         <f>'Statement Y'!G89</f>
         <v>-10435</v>
       </c>
-      <c r="H64" s="156">
+      <c r="H65" s="156">
         <f>'Statement Y'!H89</f>
         <v>-3860</v>
       </c>
-      <c r="I64" s="156">
+      <c r="I65" s="156">
         <f>'Statement Y'!I89</f>
         <v>-10952</v>
       </c>
-      <c r="J64" s="156">
+      <c r="J65" s="156">
         <f>'Statement Y'!J89</f>
         <v>5760</v>
       </c>
-      <c r="K64" s="156">
+      <c r="K65" s="156">
         <f>'Statement Y'!K89</f>
         <v>-794</v>
       </c>
-      <c r="L64" s="156">
+      <c r="L65" s="156">
         <f>'Statement Y'!L89</f>
         <v>5991</v>
       </c>
-      <c r="N64" s="156">
+      <c r="N65" s="156">
         <f>'Statement Q'!C76</f>
         <v>0</v>
       </c>
-      <c r="O64" s="156">
+      <c r="O65" s="156">
         <f>'Statement Q'!D76</f>
         <v>0</v>
       </c>
-      <c r="P64" s="156">
+      <c r="P65" s="156">
         <f>'Statement Q'!E76</f>
         <v>0</v>
       </c>
-      <c r="Q64" s="156">
+      <c r="Q65" s="156">
         <f>'Statement Q'!F76</f>
         <v>356</v>
       </c>
-      <c r="R64" s="156">
+      <c r="R65" s="156">
         <f>'Statement Q'!G76</f>
         <v>-2137</v>
       </c>
-      <c r="S64" s="156">
+      <c r="S65" s="156">
         <f>'Statement Q'!H76</f>
         <v>8107</v>
       </c>
-      <c r="T64" s="156">
+      <c r="T65" s="156">
         <f>'Statement Q'!I76</f>
         <v>-335</v>
       </c>
-      <c r="U64" s="156">
+      <c r="U65" s="156">
         <f>'Statement Q'!J76</f>
         <v>9383</v>
       </c>
-      <c r="W64" s="156">
+      <c r="W65" s="156">
         <f t="shared" si="4"/>
         <v>15018</v>
       </c>
     </row>
-    <row r="65" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="11" t="s">
+    <row r="66" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C65" s="156">
+      <c r="C66" s="156">
         <f>'Statement Y'!C90</f>
         <v>21120</v>
       </c>
-      <c r="D65" s="156">
+      <c r="D66" s="156">
         <f>'Statement Y'!D90</f>
         <v>20484</v>
       </c>
-      <c r="E65" s="156">
+      <c r="E66" s="156">
         <f>'Statement Y'!E90</f>
         <v>20289</v>
       </c>
-      <c r="F65" s="156">
+      <c r="F66" s="156">
         <f>'Statement Y'!F90</f>
         <v>25913</v>
       </c>
-      <c r="G65" s="156">
+      <c r="G66" s="156">
         <f>'Statement Y'!G90</f>
         <v>50224</v>
       </c>
-      <c r="H65" s="156">
+      <c r="H66" s="156">
         <f>'Statement Y'!H90</f>
         <v>39789</v>
       </c>
-      <c r="I65" s="156">
+      <c r="I66" s="156">
         <f>'Statement Y'!I90</f>
         <v>35929</v>
       </c>
-      <c r="J65" s="156">
+      <c r="J66" s="156">
         <f>'Statement Y'!J90</f>
         <v>24977</v>
       </c>
-      <c r="K65" s="156">
+      <c r="K66" s="156">
         <f>'Statement Y'!K90</f>
         <v>30737</v>
       </c>
-      <c r="L65" s="156">
+      <c r="L66" s="156">
         <f>'Statement Y'!L90</f>
         <v>29943</v>
       </c>
-      <c r="N65" s="156">
+      <c r="N66" s="156">
         <f>'Statement Q'!C77</f>
         <v>0</v>
       </c>
-      <c r="O65" s="156">
+      <c r="O66" s="156">
         <f>'Statement Q'!D77</f>
         <v>0</v>
       </c>
-      <c r="P65" s="156">
+      <c r="P66" s="156">
         <f>'Statement Q'!E77</f>
         <v>0</v>
       </c>
-      <c r="Q65" s="156">
+      <c r="Q66" s="156">
         <f>'Statement Q'!F77</f>
         <v>29943</v>
       </c>
-      <c r="R65" s="156">
+      <c r="R66" s="156">
         <f>'Statement Q'!G77</f>
         <v>30299</v>
       </c>
-      <c r="S65" s="156">
+      <c r="S66" s="156">
         <f>'Statement Q'!H77</f>
         <v>28162</v>
       </c>
-      <c r="T65" s="156">
+      <c r="T66" s="156">
         <f>'Statement Q'!I77</f>
         <v>36269</v>
       </c>
-      <c r="U65" s="156">
+      <c r="U66" s="156">
         <f>'Statement Q'!J77</f>
         <v>35934</v>
       </c>
-      <c r="W65" s="156">
-        <f>R65</f>
+      <c r="W66" s="156">
+        <f>R66</f>
         <v>30299</v>
       </c>
     </row>
-    <row r="66" spans="2:23" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="19" t="s">
+    <row r="67" spans="2:23" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="C66" s="157">
+      <c r="C67" s="157">
         <f>'Statement Y'!C91</f>
         <v>20484</v>
       </c>
-      <c r="D66" s="157">
+      <c r="D67" s="157">
         <f>'Statement Y'!D91</f>
         <v>20289</v>
       </c>
-      <c r="E66" s="157">
+      <c r="E67" s="157">
         <f>'Statement Y'!E91</f>
         <v>25913</v>
       </c>
-      <c r="F66" s="157">
+      <c r="F67" s="157">
         <f>'Statement Y'!F91</f>
         <v>50224</v>
       </c>
-      <c r="G66" s="157">
+      <c r="G67" s="157">
         <f>'Statement Y'!G91</f>
         <v>39789</v>
       </c>
-      <c r="H66" s="157">
+      <c r="H67" s="157">
         <f>'Statement Y'!H91</f>
         <v>35929</v>
       </c>
-      <c r="I66" s="157">
+      <c r="I67" s="157">
         <f>'Statement Y'!I91</f>
         <v>24977</v>
       </c>
-      <c r="J66" s="157">
+      <c r="J67" s="157">
         <f>'Statement Y'!J91</f>
         <v>30737</v>
       </c>
-      <c r="K66" s="157">
+      <c r="K67" s="157">
         <f>'Statement Y'!K91</f>
         <v>29943</v>
       </c>
-      <c r="L66" s="157">
+      <c r="L67" s="157">
         <f>'Statement Y'!L91</f>
         <v>35934</v>
       </c>
-      <c r="N66" s="157">
+      <c r="N67" s="157">
         <f>'Statement Q'!C78</f>
         <v>0</v>
       </c>
-      <c r="O66" s="157">
+      <c r="O67" s="157">
         <f>'Statement Q'!D78</f>
         <v>0</v>
       </c>
-      <c r="P66" s="157">
+      <c r="P67" s="157">
         <f>'Statement Q'!E78</f>
         <v>0</v>
       </c>
-      <c r="Q66" s="157">
+      <c r="Q67" s="157">
         <f>'Statement Q'!F78</f>
         <v>30299</v>
       </c>
-      <c r="R66" s="157">
+      <c r="R67" s="157">
         <f>'Statement Q'!G78</f>
         <v>28162</v>
       </c>
-      <c r="S66" s="157">
+      <c r="S67" s="157">
         <f>'Statement Q'!H78</f>
         <v>36269</v>
       </c>
-      <c r="T66" s="157">
+      <c r="T67" s="157">
         <f>'Statement Q'!I78</f>
         <v>35934</v>
       </c>
-      <c r="U66" s="157">
+      <c r="U67" s="157">
         <f>'Statement Q'!J78</f>
         <v>45317</v>
       </c>
-      <c r="W66" s="157">
-        <f>U66</f>
+      <c r="W67" s="157">
+        <f>U67</f>
         <v>45317</v>
       </c>
     </row>
-    <row r="68" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="15" t="s">
+    <row r="69" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="C68" s="158"/>
-      <c r="D68" s="158"/>
-      <c r="E68" s="158"/>
-      <c r="F68" s="158"/>
-      <c r="G68" s="158"/>
-      <c r="H68" s="158"/>
-      <c r="I68" s="158"/>
-      <c r="J68" s="158"/>
-      <c r="K68" s="158"/>
-      <c r="L68" s="158"/>
-      <c r="N68" s="158"/>
-      <c r="O68" s="158"/>
-      <c r="P68" s="158"/>
-      <c r="Q68" s="158"/>
-      <c r="R68" s="158"/>
-      <c r="S68" s="158"/>
-      <c r="T68" s="158"/>
-      <c r="U68" s="158"/>
-      <c r="W68" s="158"/>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B69" s="9" t="s">
+      <c r="C69" s="158"/>
+      <c r="D69" s="158"/>
+      <c r="E69" s="158"/>
+      <c r="F69" s="158"/>
+      <c r="G69" s="158"/>
+      <c r="H69" s="158"/>
+      <c r="I69" s="158"/>
+      <c r="J69" s="158"/>
+      <c r="K69" s="158"/>
+      <c r="L69" s="158"/>
+      <c r="N69" s="158"/>
+      <c r="O69" s="158"/>
+      <c r="P69" s="158"/>
+      <c r="Q69" s="158"/>
+      <c r="R69" s="158"/>
+      <c r="S69" s="158"/>
+      <c r="T69" s="158"/>
+      <c r="U69" s="158"/>
+      <c r="W69" s="158"/>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B70" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="C69" s="159">
-        <f t="shared" ref="C69:L69" si="5">C16/C5</f>
+      <c r="C70" s="159">
+        <f t="shared" ref="C70:L70" si="5">C17/C5</f>
         <v>0.211867983064288</v>
       </c>
-      <c r="D69" s="159">
+      <c r="D70" s="159">
         <f t="shared" si="5"/>
         <v>0.21092420845075338</v>
       </c>
-      <c r="E69" s="159">
+      <c r="E70" s="159">
         <f t="shared" si="5"/>
         <v>0.22414202074587247</v>
       </c>
-      <c r="F69" s="159">
+      <c r="F70" s="159">
         <f t="shared" si="5"/>
         <v>0.21238094505984456</v>
       </c>
-      <c r="G69" s="159">
+      <c r="G70" s="159">
         <f t="shared" si="5"/>
         <v>0.20913611278072236</v>
       </c>
-      <c r="H69" s="159">
+      <c r="H70" s="159">
         <f t="shared" si="5"/>
         <v>0.25881793355694238</v>
       </c>
-      <c r="I69" s="159">
+      <c r="I70" s="159">
         <f t="shared" si="5"/>
         <v>0.25309640705199732</v>
       </c>
-      <c r="J69" s="159">
+      <c r="J70" s="159">
         <f t="shared" si="5"/>
         <v>0.25306234264320282</v>
       </c>
-      <c r="K69" s="159">
+      <c r="K70" s="159">
         <f t="shared" si="5"/>
         <v>0.23971255769943867</v>
       </c>
-      <c r="L69" s="159">
+      <c r="L70" s="159">
         <f t="shared" si="5"/>
         <v>0.26915064121818238</v>
       </c>
-      <c r="N69" s="162"/>
-      <c r="O69" s="162"/>
-      <c r="P69" s="162"/>
-      <c r="Q69" s="162"/>
-      <c r="R69" s="162"/>
-      <c r="S69" s="162"/>
-      <c r="T69" s="162"/>
-      <c r="U69" s="162"/>
-      <c r="W69" s="89">
-        <f>W16/W5</f>
+      <c r="N70" s="162"/>
+      <c r="O70" s="162"/>
+      <c r="P70" s="162"/>
+      <c r="Q70" s="162"/>
+      <c r="R70" s="162"/>
+      <c r="S70" s="162"/>
+      <c r="T70" s="162"/>
+      <c r="U70" s="162"/>
+      <c r="W70" s="89">
+        <f>W17/W5</f>
         <v>0.27036823631768275</v>
       </c>
     </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B70" s="9" t="s">
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B71" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C70" s="160">
-        <f t="shared" ref="C70:L70" si="6">C5/C31</f>
+      <c r="C71" s="160">
+        <f t="shared" ref="C71:L71" si="6">C5/C32</f>
         <v>0.67034002101428103</v>
       </c>
-      <c r="D70" s="160">
+      <c r="D71" s="160">
         <f t="shared" si="6"/>
         <v>0.61077110404749024</v>
       </c>
-      <c r="E70" s="160">
+      <c r="E71" s="160">
         <f t="shared" si="6"/>
         <v>0.7262150522933899</v>
       </c>
-      <c r="F70" s="160">
+      <c r="F71" s="160">
         <f t="shared" si="6"/>
         <v>0.76857223883066084</v>
       </c>
-      <c r="G70" s="160">
+      <c r="G71" s="160">
         <f t="shared" si="6"/>
         <v>0.84756150274168851</v>
       </c>
-      <c r="H70" s="160">
+      <c r="H71" s="160">
         <f t="shared" si="6"/>
         <v>1.0422077367080529</v>
       </c>
-      <c r="I70" s="160">
+      <c r="I71" s="160">
         <f t="shared" si="6"/>
         <v>1.1178523337727317</v>
       </c>
-      <c r="J70" s="160">
+      <c r="J71" s="160">
         <f t="shared" si="6"/>
         <v>1.0870773690166571</v>
       </c>
-      <c r="K70" s="160">
+      <c r="K71" s="160">
         <f t="shared" si="6"/>
         <v>1.0713874732862074</v>
       </c>
-      <c r="L70" s="160">
+      <c r="L71" s="160">
         <f t="shared" si="6"/>
         <v>1.1584451663368045</v>
       </c>
-      <c r="N70" s="163"/>
-      <c r="O70" s="163"/>
-      <c r="P70" s="163"/>
-      <c r="Q70" s="163"/>
-      <c r="R70" s="163"/>
-      <c r="S70" s="163"/>
-      <c r="T70" s="163"/>
-      <c r="U70" s="163"/>
-      <c r="W70" s="166">
-        <f>W5/W31</f>
+      <c r="N71" s="163"/>
+      <c r="O71" s="163"/>
+      <c r="P71" s="163"/>
+      <c r="Q71" s="163"/>
+      <c r="R71" s="163"/>
+      <c r="S71" s="163"/>
+      <c r="T71" s="163"/>
+      <c r="U71" s="163"/>
+      <c r="W71" s="166">
+        <f>W5/W32</f>
         <v>1.1484852239801528</v>
       </c>
     </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B71" s="11" t="s">
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B72" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C71" s="161">
-        <f>C69*C70</f>
+      <c r="C72" s="161">
+        <f>C70*C71</f>
         <v>0.14202358821956815</v>
       </c>
-      <c r="D71" s="161">
-        <f t="shared" ref="D71:H71" si="7">D69*D70</f>
+      <c r="D72" s="161">
+        <f t="shared" ref="D72:H72" si="7">D70*D71</f>
         <v>0.1288264116658096</v>
       </c>
-      <c r="E71" s="161">
+      <c r="E72" s="161">
         <f t="shared" si="7"/>
         <v>0.16277530931710987</v>
       </c>
-      <c r="F71" s="161">
+      <c r="F72" s="161">
         <f t="shared" si="7"/>
         <v>0.1632300984296163</v>
       </c>
-      <c r="G71" s="161">
+      <c r="G72" s="161">
         <f t="shared" si="7"/>
         <v>0.1772557180259843</v>
       </c>
-      <c r="H71" s="161">
+      <c r="H72" s="161">
         <f t="shared" si="7"/>
         <v>0.26974205275183616</v>
       </c>
-      <c r="I71" s="161">
-        <f t="shared" ref="I71:L71" si="8">I69*I70</f>
+      <c r="I72" s="161">
+        <f t="shared" ref="I72:L72" si="8">I70*I71</f>
         <v>0.28292440929256846</v>
       </c>
-      <c r="J71" s="161">
+      <c r="J72" s="161">
         <f t="shared" si="8"/>
         <v>0.2750983456377647</v>
       </c>
-      <c r="K71" s="161">
+      <c r="K72" s="161">
         <f t="shared" si="8"/>
         <v>0.25682503150857577</v>
       </c>
-      <c r="L71" s="161">
+      <c r="L72" s="161">
         <f t="shared" si="8"/>
         <v>0.31179625933565486</v>
       </c>
-      <c r="N71" s="164"/>
-      <c r="O71" s="164"/>
-      <c r="P71" s="164"/>
-      <c r="Q71" s="164"/>
-      <c r="R71" s="164"/>
-      <c r="S71" s="164"/>
-      <c r="T71" s="164"/>
-      <c r="U71" s="164"/>
-      <c r="W71" s="161">
-        <f t="shared" ref="W71" si="9">W69*W70</f>
+      <c r="N72" s="164"/>
+      <c r="O72" s="164"/>
+      <c r="P72" s="164"/>
+      <c r="Q72" s="164"/>
+      <c r="R72" s="164"/>
+      <c r="S72" s="164"/>
+      <c r="T72" s="164"/>
+      <c r="U72" s="164"/>
+      <c r="W72" s="161">
+        <f t="shared" ref="W72" si="9">W70*W71</f>
         <v>0.31051392444443277</v>
       </c>
     </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B72" s="9" t="s">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B73" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="C72" s="160">
-        <f t="shared" ref="C72:L72" si="10">C31/C45</f>
+      <c r="C73" s="160">
+        <f t="shared" ref="C73:L73" si="10">C32/C46</f>
         <v>2.5082924623193943</v>
       </c>
-      <c r="D72" s="160">
+      <c r="D73" s="160">
         <f t="shared" si="10"/>
         <v>2.7999060031183092</v>
       </c>
-      <c r="E72" s="160">
+      <c r="E73" s="160">
         <f t="shared" si="10"/>
         <v>3.4133013523477094</v>
       </c>
-      <c r="F72" s="160">
+      <c r="F73" s="160">
         <f t="shared" si="10"/>
         <v>3.7410043320661304</v>
       </c>
-      <c r="G72" s="160">
+      <c r="G73" s="160">
         <f t="shared" si="10"/>
         <v>4.9570394404566951</v>
       </c>
-      <c r="H72" s="160">
+      <c r="H73" s="160">
         <f t="shared" si="10"/>
         <v>5.5635124425423994</v>
       </c>
-      <c r="I72" s="160">
+      <c r="I73" s="160">
         <f t="shared" si="10"/>
         <v>6.9615369434796337</v>
       </c>
-      <c r="J72" s="160">
+      <c r="J73" s="160">
         <f t="shared" si="10"/>
         <v>5.6734624915521517</v>
       </c>
-      <c r="K72" s="160">
+      <c r="K73" s="160">
         <f t="shared" si="10"/>
         <v>6.408779631255487</v>
       </c>
-      <c r="L72" s="160">
+      <c r="L73" s="160">
         <f t="shared" si="10"/>
         <v>4.8721874872852045</v>
       </c>
-      <c r="N72" s="165"/>
-      <c r="O72" s="165"/>
-      <c r="P72" s="165"/>
-      <c r="Q72" s="165"/>
-      <c r="R72" s="165"/>
-      <c r="S72" s="165"/>
-      <c r="T72" s="165"/>
-      <c r="U72" s="165"/>
-      <c r="W72" s="160">
-        <f>W31/W45</f>
+      <c r="N73" s="165"/>
+      <c r="O73" s="165"/>
+      <c r="P73" s="165"/>
+      <c r="Q73" s="165"/>
+      <c r="R73" s="165"/>
+      <c r="S73" s="165"/>
+      <c r="T73" s="165"/>
+      <c r="U73" s="165"/>
+      <c r="W73" s="160">
+        <f>W32/W46</f>
         <v>4.3009071323279287</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B73" s="11" t="s">
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B74" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="C73" s="161">
-        <f>C71*C72</f>
+      <c r="C74" s="161">
+        <f>C72*C73</f>
         <v>0.35623669580269629</v>
       </c>
-      <c r="D73" s="161">
-        <f t="shared" ref="D73:H73" si="11">D71*D72</f>
+      <c r="D74" s="161">
+        <f t="shared" ref="D74:H74" si="11">D72*D73</f>
         <v>0.36070184338329087</v>
       </c>
-      <c r="E73" s="161">
+      <c r="E74" s="161">
         <f t="shared" si="11"/>
         <v>0.55560118342090781</v>
       </c>
-      <c r="F73" s="161">
+      <c r="F74" s="161">
         <f t="shared" si="11"/>
         <v>0.61064450534877546</v>
       </c>
-      <c r="G73" s="161">
+      <c r="G74" s="161">
         <f t="shared" si="11"/>
         <v>0.87866358530127497</v>
       </c>
-      <c r="H73" s="161">
+      <c r="H74" s="161">
         <f t="shared" si="11"/>
         <v>1.5007132667617686</v>
       </c>
-      <c r="I73" s="161">
-        <f t="shared" ref="I73:L73" si="12">I71*I72</f>
+      <c r="I74" s="161">
+        <f t="shared" ref="I74:L74" si="12">I72*I73</f>
         <v>1.9695887275023678</v>
       </c>
-      <c r="J73" s="161">
+      <c r="J74" s="161">
         <f t="shared" si="12"/>
         <v>1.5607601454639075</v>
       </c>
-      <c r="K73" s="161">
+      <c r="K74" s="161">
         <f t="shared" si="12"/>
         <v>1.6459350307287091</v>
       </c>
-      <c r="L73" s="161">
+      <c r="L74" s="161">
         <f t="shared" si="12"/>
         <v>1.5191298333175103</v>
       </c>
-      <c r="N73" s="164"/>
-      <c r="O73" s="164"/>
-      <c r="P73" s="164"/>
-      <c r="Q73" s="164"/>
-      <c r="R73" s="164"/>
-      <c r="S73" s="164"/>
-      <c r="T73" s="164"/>
-      <c r="U73" s="164"/>
-      <c r="W73" s="161">
-        <f t="shared" ref="W73" si="13">W71*W72</f>
+      <c r="N74" s="164"/>
+      <c r="O74" s="164"/>
+      <c r="P74" s="164"/>
+      <c r="Q74" s="164"/>
+      <c r="R74" s="164"/>
+      <c r="S74" s="164"/>
+      <c r="T74" s="164"/>
+      <c r="U74" s="164"/>
+      <c r="W74" s="161">
+        <f t="shared" ref="W74" si="13">W72*W73</f>
         <v>1.3354915523301965</v>
       </c>
     </row>
-    <row r="75" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="158" t="s">
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B75" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="C75" s="161">
+        <f>C13/(C36+C37+C39+C46-C22)</f>
+        <v>0.30165880284014146</v>
+      </c>
+      <c r="D75" s="161">
+        <f t="shared" ref="D75:L75" si="14">D13/(D36+D37+D39+D46-D22)</f>
+        <v>0.26363503167447394</v>
+      </c>
+      <c r="E75" s="161">
+        <f t="shared" si="14"/>
+        <v>0.37271701178242755</v>
+      </c>
+      <c r="F75" s="161">
+        <f t="shared" si="14"/>
+        <v>0.54846093134226592</v>
+      </c>
+      <c r="G75" s="161">
+        <f t="shared" si="14"/>
+        <v>0.65325983695865375</v>
+      </c>
+      <c r="H75" s="161">
+        <f t="shared" si="14"/>
+        <v>0.75462426965708829</v>
+      </c>
+      <c r="I75" s="161">
+        <f t="shared" si="14"/>
+        <v>0.81742346756269768</v>
+      </c>
+      <c r="J75" s="161">
+        <f t="shared" si="14"/>
+        <v>0.8728304933390485</v>
+      </c>
+      <c r="K75" s="161">
+        <f t="shared" si="14"/>
+        <v>0.95044920421197143</v>
+      </c>
+      <c r="L75" s="161">
+        <f t="shared" si="14"/>
+        <v>0.95401503821385103</v>
+      </c>
+      <c r="N75" s="164"/>
+      <c r="O75" s="164"/>
+      <c r="P75" s="164"/>
+      <c r="Q75" s="164"/>
+      <c r="R75" s="164"/>
+      <c r="S75" s="164"/>
+      <c r="T75" s="164"/>
+      <c r="U75" s="164"/>
+      <c r="W75" s="161"/>
+    </row>
+    <row r="77" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="158" t="s">
         <v>116</v>
       </c>
-      <c r="C75" s="158"/>
-      <c r="D75" s="158"/>
-      <c r="E75" s="158"/>
-      <c r="F75" s="158"/>
-      <c r="G75" s="158"/>
-      <c r="H75" s="158"/>
-      <c r="I75" s="158"/>
-      <c r="J75" s="158"/>
-      <c r="K75" s="158"/>
-      <c r="L75" s="158"/>
-      <c r="N75" s="158"/>
-      <c r="O75" s="158"/>
-      <c r="P75" s="158"/>
-      <c r="Q75" s="158"/>
-      <c r="R75" s="158"/>
-      <c r="S75" s="158"/>
-      <c r="T75" s="158"/>
-      <c r="U75" s="158"/>
-      <c r="W75" s="158"/>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B76" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" s="163"/>
-      <c r="D76" s="161">
-        <f t="shared" ref="D76:L76" si="14">(D5-C5)/C5</f>
-        <v>6.3045181993980681E-2</v>
-      </c>
-      <c r="E76" s="161">
-        <f t="shared" si="14"/>
-        <v>0.15861957650261305</v>
-      </c>
-      <c r="F76" s="161">
-        <f t="shared" si="14"/>
-        <v>-2.0410775805267418E-2</v>
-      </c>
-      <c r="G76" s="161">
-        <f t="shared" si="14"/>
-        <v>5.5120803769784836E-2</v>
-      </c>
-      <c r="H76" s="161">
-        <f t="shared" si="14"/>
-        <v>0.33259384733074693</v>
-      </c>
-      <c r="I76" s="161">
-        <f t="shared" si="14"/>
-        <v>7.7937876041846058E-2</v>
-      </c>
-      <c r="J76" s="161">
-        <f t="shared" si="14"/>
-        <v>-2.8004605303199367E-2</v>
-      </c>
-      <c r="K76" s="161">
-        <f t="shared" si="14"/>
-        <v>2.0219940775141214E-2</v>
-      </c>
-      <c r="L76" s="161">
-        <f t="shared" si="14"/>
-        <v>6.4255117828327393E-2</v>
-      </c>
-      <c r="N76" s="163"/>
-      <c r="O76" s="161">
-        <f t="shared" ref="O76:U77" si="15">(O5-N5)/N5</f>
-        <v>-5.4830143356142495E-2</v>
-      </c>
-      <c r="P76" s="161">
-        <f t="shared" si="15"/>
-        <v>0.10670692609907084</v>
-      </c>
-      <c r="Q76" s="161">
-        <f t="shared" si="15"/>
-        <v>0.30938586326767092</v>
-      </c>
-      <c r="R76" s="161">
-        <f t="shared" si="15"/>
-        <v>-0.23283185840707965</v>
-      </c>
-      <c r="S76" s="161">
-        <f t="shared" si="15"/>
-        <v>-1.3873887100326136E-2</v>
-      </c>
-      <c r="T76" s="161">
-        <f t="shared" si="15"/>
-        <v>8.9646518354672675E-2</v>
-      </c>
-      <c r="U76" s="161">
-        <f t="shared" si="15"/>
-        <v>0.40296293404641542</v>
-      </c>
-      <c r="W76" s="163"/>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B77" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C77" s="163"/>
-      <c r="D77" s="159">
-        <f t="shared" ref="D77:L77" si="16">(D6-C6)/C6</f>
-        <v>7.3620752648885637E-2</v>
-      </c>
-      <c r="E77" s="159">
-        <f t="shared" si="16"/>
-        <v>0.16099483863649255</v>
-      </c>
-      <c r="F77" s="159">
-        <f t="shared" si="16"/>
-        <v>-1.2054520139720071E-2</v>
-      </c>
-      <c r="G77" s="159">
-        <f t="shared" si="16"/>
-        <v>4.8070860787973943E-2</v>
-      </c>
-      <c r="H77" s="159">
-        <f t="shared" si="16"/>
-        <v>0.25608785142634716</v>
-      </c>
-      <c r="I77" s="159">
-        <f t="shared" si="16"/>
-        <v>4.9605363858747961E-2</v>
-      </c>
-      <c r="J77" s="159">
-        <f t="shared" si="16"/>
-        <v>-4.2089771232766408E-2</v>
-      </c>
-      <c r="K77" s="159">
-        <f t="shared" si="16"/>
-        <v>-1.7675600199872046E-2</v>
-      </c>
-      <c r="L77" s="159">
-        <f t="shared" si="16"/>
-        <v>5.0429755837833726E-2</v>
-      </c>
-      <c r="N77" s="163"/>
-      <c r="O77" s="159">
-        <f t="shared" si="15"/>
-        <v>-4.9152262695433359E-2</v>
-      </c>
-      <c r="P77" s="159">
-        <f t="shared" si="15"/>
-        <v>0.10742098527083017</v>
-      </c>
-      <c r="Q77" s="159">
-        <f t="shared" si="15"/>
-        <v>0.29331452860864626</v>
-      </c>
-      <c r="R77" s="159">
-        <f t="shared" si="15"/>
-        <v>-0.23525937145020825</v>
-      </c>
-      <c r="S77" s="159">
-        <f t="shared" si="15"/>
-        <v>-3.4460904697773903E-3</v>
-      </c>
-      <c r="T77" s="159">
-        <f t="shared" si="15"/>
-        <v>7.5658809968599708E-2</v>
-      </c>
-      <c r="U77" s="159">
-        <f t="shared" si="15"/>
-        <v>0.37690531177829101</v>
-      </c>
-      <c r="W77" s="163"/>
+      <c r="C77" s="158"/>
+      <c r="D77" s="158"/>
+      <c r="E77" s="158"/>
+      <c r="F77" s="158"/>
+      <c r="G77" s="158"/>
+      <c r="H77" s="158"/>
+      <c r="I77" s="158"/>
+      <c r="J77" s="158"/>
+      <c r="K77" s="158"/>
+      <c r="L77" s="158"/>
+      <c r="N77" s="158"/>
+      <c r="O77" s="158"/>
+      <c r="P77" s="158"/>
+      <c r="Q77" s="158"/>
+      <c r="R77" s="158"/>
+      <c r="S77" s="158"/>
+      <c r="T77" s="158"/>
+      <c r="U77" s="158"/>
+      <c r="W77" s="158"/>
     </row>
     <row r="78" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B78" s="11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C78" s="163"/>
       <c r="D78" s="161">
-        <f t="shared" ref="D78:L78" si="17">IF(C7=0,
+        <f t="shared" ref="D78:L78" si="15">(D5-C5)/C5</f>
+        <v>6.3045181993980681E-2</v>
+      </c>
+      <c r="E78" s="161">
+        <f t="shared" si="15"/>
+        <v>0.15861957650261305</v>
+      </c>
+      <c r="F78" s="161">
+        <f t="shared" si="15"/>
+        <v>-2.0410775805267418E-2</v>
+      </c>
+      <c r="G78" s="161">
+        <f t="shared" si="15"/>
+        <v>5.5120803769784836E-2</v>
+      </c>
+      <c r="H78" s="161">
+        <f t="shared" si="15"/>
+        <v>0.33259384733074693</v>
+      </c>
+      <c r="I78" s="161">
+        <f t="shared" si="15"/>
+        <v>7.7937876041846058E-2</v>
+      </c>
+      <c r="J78" s="161">
+        <f t="shared" si="15"/>
+        <v>-2.8004605303199367E-2</v>
+      </c>
+      <c r="K78" s="161">
+        <f t="shared" si="15"/>
+        <v>2.0219940775141214E-2</v>
+      </c>
+      <c r="L78" s="161">
+        <f t="shared" si="15"/>
+        <v>6.4255117828327393E-2</v>
+      </c>
+      <c r="N78" s="163"/>
+      <c r="O78" s="161">
+        <f t="shared" ref="O78:U79" si="16">(O5-N5)/N5</f>
+        <v>-5.4830143356142495E-2</v>
+      </c>
+      <c r="P78" s="161">
+        <f t="shared" si="16"/>
+        <v>0.10670692609907084</v>
+      </c>
+      <c r="Q78" s="161">
+        <f t="shared" si="16"/>
+        <v>0.30938586326767092</v>
+      </c>
+      <c r="R78" s="161">
+        <f t="shared" si="16"/>
+        <v>-0.23283185840707965</v>
+      </c>
+      <c r="S78" s="161">
+        <f t="shared" si="16"/>
+        <v>-1.3873887100326136E-2</v>
+      </c>
+      <c r="T78" s="161">
+        <f t="shared" si="16"/>
+        <v>8.9646518354672675E-2</v>
+      </c>
+      <c r="U78" s="161">
+        <f t="shared" si="16"/>
+        <v>0.40296293404641542</v>
+      </c>
+      <c r="W78" s="163"/>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B79" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="163"/>
+      <c r="D79" s="159">
+        <f t="shared" ref="D79:L79" si="17">(D6-C6)/C6</f>
+        <v>7.3620752648885637E-2</v>
+      </c>
+      <c r="E79" s="159">
+        <f t="shared" si="17"/>
+        <v>0.16099483863649255</v>
+      </c>
+      <c r="F79" s="159">
+        <f t="shared" si="17"/>
+        <v>-1.2054520139720071E-2</v>
+      </c>
+      <c r="G79" s="159">
+        <f t="shared" si="17"/>
+        <v>4.8070860787973943E-2</v>
+      </c>
+      <c r="H79" s="159">
+        <f t="shared" si="17"/>
+        <v>0.25608785142634716</v>
+      </c>
+      <c r="I79" s="159">
+        <f t="shared" si="17"/>
+        <v>4.9605363858747961E-2</v>
+      </c>
+      <c r="J79" s="159">
+        <f t="shared" si="17"/>
+        <v>-4.2089771232766408E-2</v>
+      </c>
+      <c r="K79" s="159">
+        <f t="shared" si="17"/>
+        <v>-1.7675600199872046E-2</v>
+      </c>
+      <c r="L79" s="159">
+        <f t="shared" si="17"/>
+        <v>5.0429755837833726E-2</v>
+      </c>
+      <c r="N79" s="163"/>
+      <c r="O79" s="159">
+        <f t="shared" si="16"/>
+        <v>-4.9152262695433359E-2</v>
+      </c>
+      <c r="P79" s="159">
+        <f t="shared" si="16"/>
+        <v>0.10742098527083017</v>
+      </c>
+      <c r="Q79" s="159">
+        <f t="shared" si="16"/>
+        <v>0.29331452860864626</v>
+      </c>
+      <c r="R79" s="159">
+        <f t="shared" si="16"/>
+        <v>-0.23525937145020825</v>
+      </c>
+      <c r="S79" s="159">
+        <f t="shared" si="16"/>
+        <v>-3.4460904697773903E-3</v>
+      </c>
+      <c r="T79" s="159">
+        <f t="shared" si="16"/>
+        <v>7.5658809968599708E-2</v>
+      </c>
+      <c r="U79" s="159">
+        <f t="shared" si="16"/>
+        <v>0.37690531177829101</v>
+      </c>
+      <c r="W79" s="163"/>
+    </row>
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B80" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80" s="163"/>
+      <c r="D80" s="161">
+        <f t="shared" ref="D80:L80" si="18">IF(C7=0,
 IF(D7=0,0,IF(D7&gt;0,1,-1)),
 (D7-C7)/ABS(C7)
 )</f>
         <v>4.6556614409645987E-2</v>
       </c>
-      <c r="E78" s="161">
-        <f t="shared" si="17"/>
+      <c r="E80" s="161">
+        <f t="shared" si="18"/>
         <v>0.15482049304878326</v>
       </c>
-      <c r="F78" s="161">
-        <f t="shared" si="17"/>
+      <c r="F80" s="161">
+        <f t="shared" si="18"/>
         <v>-3.3847543671874231E-2</v>
       </c>
-      <c r="G78" s="161">
-        <f t="shared" si="17"/>
+      <c r="G80" s="161">
+        <f t="shared" si="18"/>
         <v>6.6712740873241722E-2</v>
       </c>
-      <c r="H78" s="161">
-        <f t="shared" si="17"/>
+      <c r="H80" s="161">
+        <f t="shared" si="18"/>
         <v>0.45619116582186819</v>
       </c>
-      <c r="I78" s="161">
-        <f t="shared" si="17"/>
+      <c r="I80" s="161">
+        <f t="shared" si="18"/>
         <v>0.11741997958596143</v>
       </c>
-      <c r="J78" s="161">
-        <f t="shared" si="17"/>
+      <c r="J80" s="161">
+        <f t="shared" si="18"/>
         <v>-9.5677530418896602E-3</v>
       </c>
-      <c r="K78" s="161">
-        <f t="shared" si="17"/>
+      <c r="K80" s="161">
+        <f t="shared" si="18"/>
         <v>6.8194717052522058E-2</v>
       </c>
-      <c r="L78" s="161">
-        <f t="shared" si="17"/>
+      <c r="L80" s="161">
+        <f t="shared" si="18"/>
         <v>8.0350669404426533E-2</v>
       </c>
-      <c r="N78" s="163"/>
-      <c r="O78" s="161">
-        <f t="shared" ref="O78:U78" si="18">IF(N7=0,
+      <c r="N80" s="163"/>
+      <c r="O80" s="161">
+        <f t="shared" ref="O80:U80" si="19">IF(N7=0,
 IF(O7=0,0,IF(O7&gt;0,1,-1)),
 (O7-N7)/ABS(N7)
 )</f>
         <v>-6.1342291405455274E-2</v>
       </c>
-      <c r="P78" s="161">
-        <f t="shared" si="18"/>
+      <c r="P80" s="161">
+        <f t="shared" si="19"/>
         <v>0.1058773123645345</v>
       </c>
-      <c r="Q78" s="161">
-        <f t="shared" si="18"/>
+      <c r="Q80" s="161">
+        <f t="shared" si="19"/>
         <v>0.32808404931744112</v>
       </c>
-      <c r="R78" s="161">
-        <f t="shared" si="18"/>
+      <c r="R80" s="161">
+        <f t="shared" si="19"/>
         <v>-0.23008151008151009</v>
       </c>
-      <c r="S78" s="161">
-        <f t="shared" si="18"/>
+      <c r="S80" s="161">
+        <f t="shared" si="19"/>
         <v>-2.5609022221231639E-2</v>
       </c>
-      <c r="T78" s="161">
-        <f t="shared" si="18"/>
+      <c r="T80" s="161">
+        <f t="shared" si="19"/>
         <v>0.10574591701358708</v>
       </c>
-      <c r="U78" s="161">
-        <f t="shared" si="18"/>
+      <c r="U80" s="161">
+        <f t="shared" si="19"/>
         <v>0.43213835046854637</v>
       </c>
-      <c r="W78" s="163"/>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B79" s="12" t="s">
+      <c r="W80" s="163"/>
+    </row>
+    <row r="81" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B81" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C79" s="163"/>
-      <c r="D79" s="159">
-        <f t="shared" ref="D79:L79" si="19">IF(C10=0,
+      <c r="C81" s="163"/>
+      <c r="D81" s="159">
+        <f t="shared" ref="D81:L81" si="20">IF(C10=0,
 IF(D10=0,0,IF(D10&gt;0,1,-1)),
 (D10-C10)/ABS(C10)
 )</f>
         <v>0.10738891868476422</v>
       </c>
-      <c r="E79" s="159">
-        <f t="shared" si="19"/>
+      <c r="E81" s="159">
+        <f t="shared" si="20"/>
         <v>0.15270844199389016</v>
       </c>
-      <c r="F79" s="159">
-        <f t="shared" si="19"/>
+      <c r="F81" s="159">
+        <f t="shared" si="20"/>
         <v>0.11379722698038201</v>
       </c>
-      <c r="G79" s="159">
-        <f t="shared" si="19"/>
+      <c r="G81" s="159">
+        <f t="shared" si="20"/>
         <v>0.12204747257849226</v>
       </c>
-      <c r="H79" s="159">
-        <f t="shared" si="19"/>
+      <c r="H81" s="159">
+        <f t="shared" si="20"/>
         <v>0.13496948381090307</v>
       </c>
-      <c r="I79" s="159">
-        <f t="shared" si="19"/>
+      <c r="I81" s="159">
+        <f t="shared" si="20"/>
         <v>0.16993642764372138</v>
       </c>
-      <c r="J79" s="159">
-        <f t="shared" si="19"/>
+      <c r="J81" s="159">
+        <f t="shared" si="20"/>
         <v>6.8205278021228943E-2</v>
       </c>
-      <c r="K79" s="159">
-        <f t="shared" si="19"/>
+      <c r="K81" s="159">
+        <f t="shared" si="20"/>
         <v>4.7769249001768557E-2</v>
       </c>
-      <c r="L79" s="159">
-        <f t="shared" si="19"/>
+      <c r="L81" s="159">
+        <f t="shared" si="20"/>
         <v>8.1507647867471764E-2</v>
       </c>
-      <c r="N79" s="163"/>
-      <c r="O79" s="159">
-        <f t="shared" ref="O79:U80" si="20">IF(N10=0,
+      <c r="N81" s="163"/>
+      <c r="O81" s="159">
+        <f t="shared" ref="O81:U82" si="21">IF(N10=0,
 IF(O10=0,0,IF(O10&gt;0,1,-1)),
 (O10-N10)/ABS(N10)
 )</f>
         <v>-3.1313061025676709E-3</v>
       </c>
-      <c r="P79" s="159">
-        <f t="shared" si="20"/>
+      <c r="P81" s="159">
+        <f t="shared" si="21"/>
         <v>-2.6525198938992041E-3</v>
       </c>
-      <c r="Q79" s="159">
-        <f t="shared" si="20"/>
+      <c r="Q81" s="159">
+        <f t="shared" si="21"/>
         <v>8.0837066069428892E-2</v>
       </c>
-      <c r="R79" s="159">
-        <f t="shared" si="20"/>
+      <c r="R81" s="159">
+        <f t="shared" si="21"/>
         <v>-1.0684452502752056E-2</v>
       </c>
-      <c r="S79" s="159">
-        <f t="shared" si="20"/>
+      <c r="S81" s="159">
+        <f t="shared" si="21"/>
         <v>1.5577955229742113E-2</v>
       </c>
-      <c r="T79" s="159">
-        <f t="shared" si="20"/>
+      <c r="T81" s="159">
+        <f t="shared" si="21"/>
         <v>2.5650940964166022E-2</v>
       </c>
-      <c r="U79" s="159">
-        <f t="shared" si="20"/>
+      <c r="U81" s="159">
+        <f t="shared" si="21"/>
         <v>0.15489506095262034</v>
       </c>
-      <c r="W79" s="163"/>
-    </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B80" s="11" t="s">
+      <c r="W81" s="163"/>
+    </row>
+    <row r="82" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B82" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C80" s="163"/>
-      <c r="D80" s="161">
-        <f t="shared" ref="D80:L80" si="21">IF(C11=0,
+      <c r="C82" s="163"/>
+      <c r="D82" s="161">
+        <f t="shared" ref="D82:L82" si="22">IF(C11=0,
 IF(D11=0,0,IF(D11&gt;0,1,-1)),
 (D11-C11)/ABS(C11)
 )</f>
         <v>2.1991203518592562E-2</v>
       </c>
-      <c r="E80" s="161">
+      <c r="E82" s="161">
+        <f t="shared" si="22"/>
+        <v>0.15574465310380803</v>
+      </c>
+      <c r="F82" s="161">
+        <f t="shared" si="22"/>
+        <v>-9.8282038985584921E-2</v>
+      </c>
+      <c r="G82" s="161">
+        <f t="shared" si="22"/>
+        <v>3.6884091975598311E-2</v>
+      </c>
+      <c r="H82" s="161">
+        <f t="shared" si="22"/>
+        <v>0.64357048032826458</v>
+      </c>
+      <c r="I82" s="161">
+        <f t="shared" si="22"/>
+        <v>9.6265225013538444E-2</v>
+      </c>
+      <c r="J82" s="161">
+        <f t="shared" si="22"/>
+        <v>-4.3001749876503931E-2</v>
+      </c>
+      <c r="K82" s="161">
+        <f t="shared" si="22"/>
+        <v>7.799581805933456E-2</v>
+      </c>
+      <c r="L82" s="161">
+        <f t="shared" si="22"/>
+        <v>7.9811063498246987E-2</v>
+      </c>
+      <c r="N82" s="163"/>
+      <c r="O82" s="161">
         <f t="shared" si="21"/>
-        <v>0.15574465310380803</v>
-      </c>
-      <c r="F80" s="161">
+        <v>-9.1326164874551974E-2</v>
+      </c>
+      <c r="P82" s="161">
         <f t="shared" si="21"/>
-        <v>-9.8282038985584921E-2</v>
-      </c>
-      <c r="G80" s="161">
+        <v>0.16720574313663616</v>
+      </c>
+      <c r="Q82" s="161">
         <f t="shared" si="21"/>
-        <v>3.6884091975598311E-2</v>
-      </c>
-      <c r="H80" s="161">
+        <v>0.44746713527761822</v>
+      </c>
+      <c r="R82" s="161">
         <f t="shared" si="21"/>
-        <v>0.64357048032826458</v>
-      </c>
-      <c r="I80" s="161">
+        <v>-0.30918472170339933</v>
+      </c>
+      <c r="S82" s="161">
         <f t="shared" si="21"/>
-        <v>9.6265225013538444E-2</v>
-      </c>
-      <c r="J80" s="161">
+        <v>-4.6875528067863055E-2</v>
+      </c>
+      <c r="T82" s="161">
         <f t="shared" si="21"/>
-        <v>-4.3001749876503931E-2</v>
-      </c>
-      <c r="K80" s="161">
+        <v>0.14981207006595276</v>
+      </c>
+      <c r="U82" s="161">
         <f t="shared" si="21"/>
-        <v>7.799581805933456E-2</v>
-      </c>
-      <c r="L80" s="161">
-        <f t="shared" si="21"/>
-        <v>7.9811063498246987E-2</v>
-      </c>
-      <c r="N80" s="163"/>
-      <c r="O80" s="161">
-        <f t="shared" si="20"/>
-        <v>-9.1326164874551974E-2</v>
-      </c>
-      <c r="P80" s="161">
-        <f t="shared" si="20"/>
-        <v>0.16720574313663616</v>
-      </c>
-      <c r="Q80" s="161">
-        <f t="shared" si="20"/>
-        <v>0.44746713527761822</v>
-      </c>
-      <c r="R80" s="161">
-        <f t="shared" si="20"/>
-        <v>-0.30918472170339933</v>
-      </c>
-      <c r="S80" s="161">
-        <f t="shared" si="20"/>
-        <v>-4.6875528067863055E-2</v>
-      </c>
-      <c r="T80" s="161">
-        <f t="shared" si="20"/>
-        <v>0.14981207006595276</v>
-      </c>
-      <c r="U80" s="161">
-        <f t="shared" si="20"/>
         <v>0.56819934005612605</v>
       </c>
-      <c r="W80" s="163"/>
-    </row>
-    <row r="81" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B81" s="11" t="s">
+      <c r="W82" s="163"/>
+    </row>
+    <row r="83" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B83" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C81" s="163"/>
-      <c r="D81" s="161">
-        <f t="shared" ref="D81:L81" si="22">IF(C14=0,
-IF(D14=0,0,IF(D14&gt;0,1,-1)),
-(D14-C14)/ABS(C14)
+      <c r="C83" s="163"/>
+      <c r="D83" s="161">
+        <f t="shared" ref="D83:L83" si="23">IF(C15=0,
+IF(D15=0,0,IF(D15&gt;0,1,-1)),
+(D15-C15)/ABS(C15)
 )</f>
         <v>4.4271003063286192E-2</v>
       </c>
-      <c r="E81" s="161">
-        <f t="shared" si="22"/>
+      <c r="E83" s="161">
+        <f t="shared" si="23"/>
         <v>0.13752750081917334</v>
       </c>
-      <c r="F81" s="161">
-        <f t="shared" si="22"/>
+      <c r="F83" s="161">
+        <f t="shared" si="23"/>
         <v>-9.8294994719010195E-2</v>
       </c>
-      <c r="G81" s="161">
-        <f t="shared" si="22"/>
+      <c r="G83" s="161">
+        <f t="shared" si="23"/>
         <v>2.0597228349331427E-2</v>
       </c>
-      <c r="H81" s="161">
-        <f t="shared" si="22"/>
+      <c r="H83" s="161">
+        <f t="shared" si="23"/>
         <v>0.62774440685039723</v>
       </c>
-      <c r="I81" s="161">
-        <f t="shared" si="22"/>
+      <c r="I83" s="161">
+        <f t="shared" si="23"/>
         <v>9.0616901846951203E-2</v>
       </c>
-      <c r="J81" s="161">
-        <f t="shared" si="22"/>
+      <c r="J83" s="161">
+        <f t="shared" si="23"/>
         <v>-4.5061837233319059E-2</v>
       </c>
-      <c r="K81" s="161">
-        <f t="shared" si="22"/>
+      <c r="K83" s="161">
+        <f t="shared" si="23"/>
         <v>8.5716044172469585E-2</v>
       </c>
-      <c r="L81" s="161">
-        <f t="shared" si="22"/>
+      <c r="L83" s="161">
+        <f t="shared" si="23"/>
         <v>7.4859294651172206E-2</v>
       </c>
-      <c r="N81" s="163"/>
-      <c r="O81" s="161">
-        <f t="shared" ref="O81:U81" si="23">IF(N14=0,
-IF(O14=0,0,IF(O14&gt;0,1,-1)),
-(O14-N14)/ABS(N14)
+      <c r="N83" s="163"/>
+      <c r="O83" s="161">
+        <f t="shared" ref="O83:U83" si="24">IF(N15=0,
+IF(O15=0,0,IF(O15&gt;0,1,-1)),
+(O15-N15)/ABS(N15)
 )</f>
         <v>-9.1382137001924588E-2</v>
       </c>
-      <c r="P81" s="161">
-        <f t="shared" si="23"/>
+      <c r="P83" s="161">
+        <f t="shared" si="24"/>
         <v>0.16144975288303129</v>
       </c>
-      <c r="Q81" s="161">
-        <f t="shared" si="23"/>
+      <c r="Q83" s="161">
+        <f t="shared" si="24"/>
         <v>0.43816278284363391</v>
       </c>
-      <c r="R81" s="161">
-        <f t="shared" si="23"/>
+      <c r="R83" s="161">
+        <f t="shared" si="24"/>
         <v>-0.311713319556641</v>
       </c>
-      <c r="S81" s="161">
-        <f t="shared" si="23"/>
+      <c r="S83" s="161">
+        <f t="shared" si="24"/>
         <v>-4.3636983964517227E-2</v>
       </c>
-      <c r="T81" s="161">
-        <f t="shared" si="23"/>
+      <c r="T83" s="161">
+        <f t="shared" si="24"/>
         <v>0.17027576611608577</v>
       </c>
-      <c r="U81" s="161">
-        <f t="shared" si="23"/>
+      <c r="U83" s="161">
+        <f t="shared" si="24"/>
         <v>0.55474942080234113</v>
       </c>
-      <c r="W81" s="163"/>
-    </row>
-    <row r="82" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B82" s="11" t="s">
+      <c r="W83" s="163"/>
+    </row>
+    <row r="84" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B84" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C82" s="163"/>
-      <c r="D82" s="161">
-        <f t="shared" ref="D82:L82" si="24">IF(C16=0,
-IF(D16=0,0,IF(D16&gt;0,1,-1)),
-(D16-C16)/ABS(C16)
+      <c r="C84" s="163"/>
+      <c r="D84" s="161">
+        <f t="shared" ref="D84:L84" si="25">IF(C17=0,
+IF(D17=0,0,IF(D17&gt;0,1,-1)),
+(D17-C17)/ABS(C17)
 )</f>
         <v>5.8309803664061986E-2</v>
       </c>
-      <c r="E82" s="161">
-        <f t="shared" si="24"/>
+      <c r="E84" s="161">
+        <f t="shared" si="25"/>
         <v>0.23122582780087278</v>
       </c>
-      <c r="F82" s="161">
-        <f t="shared" si="24"/>
+      <c r="F84" s="161">
+        <f t="shared" si="25"/>
         <v>-7.1811325191916811E-2</v>
       </c>
-      <c r="G82" s="161">
-        <f t="shared" si="24"/>
+      <c r="G84" s="161">
+        <f t="shared" si="25"/>
         <v>3.9000289561314606E-2</v>
       </c>
-      <c r="H82" s="161">
-        <f t="shared" si="24"/>
+      <c r="H84" s="161">
+        <f t="shared" si="25"/>
         <v>0.64916131055024295</v>
       </c>
-      <c r="I82" s="161">
-        <f t="shared" si="24"/>
+      <c r="I84" s="161">
+        <f t="shared" si="25"/>
         <v>5.4108576256865229E-2</v>
       </c>
-      <c r="J82" s="161">
-        <f t="shared" si="24"/>
+      <c r="J84" s="161">
+        <f t="shared" si="25"/>
         <v>-2.8135426790777834E-2</v>
       </c>
-      <c r="K82" s="161">
-        <f t="shared" si="24"/>
+      <c r="K84" s="161">
+        <f t="shared" si="25"/>
         <v>-3.3599670086086914E-2</v>
       </c>
-      <c r="L82" s="161">
-        <f t="shared" si="24"/>
+      <c r="L84" s="161">
+        <f t="shared" si="25"/>
         <v>0.19495177946573355</v>
       </c>
-      <c r="N82" s="163"/>
-      <c r="O82" s="161">
-        <f t="shared" ref="O82:U82" si="25">IF(N16=0,
-IF(O16=0,0,IF(O16&gt;0,1,-1)),
-(O16-N16)/ABS(N16)
+      <c r="N84" s="163"/>
+      <c r="O84" s="161">
+        <f t="shared" ref="O84:U84" si="26">IF(N17=0,
+IF(O17=0,0,IF(O17&gt;0,1,-1)),
+(O17-N17)/ABS(N17)
 )</f>
         <v>-9.2570654933152821E-2</v>
       </c>
-      <c r="P82" s="161">
-        <f t="shared" si="25"/>
+      <c r="P84" s="161">
+        <f t="shared" si="26"/>
         <v>-0.31294293174188736</v>
       </c>
-      <c r="Q82" s="161">
-        <f t="shared" si="25"/>
+      <c r="Q84" s="161">
+        <f t="shared" si="26"/>
         <v>1.4653908794788273</v>
       </c>
-      <c r="R82" s="161">
-        <f t="shared" si="25"/>
+      <c r="R84" s="161">
+        <f t="shared" si="26"/>
         <v>-0.31791907514450868</v>
       </c>
-      <c r="S82" s="161">
-        <f t="shared" si="25"/>
+      <c r="S84" s="161">
+        <f t="shared" si="26"/>
         <v>-5.4317998385794999E-2</v>
       </c>
-      <c r="T82" s="161">
-        <f t="shared" si="25"/>
+      <c r="T84" s="161">
+        <f t="shared" si="26"/>
         <v>0.17205769394896306</v>
       </c>
-      <c r="U82" s="161">
-        <f t="shared" si="25"/>
+      <c r="U84" s="161">
+        <f t="shared" si="26"/>
         <v>0.53269496832447394</v>
       </c>
-      <c r="W82" s="163"/>
-    </row>
-    <row r="83" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B83" s="12" t="s">
+      <c r="W84" s="163"/>
+    </row>
+    <row r="85" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B85" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C83" s="163"/>
-      <c r="D83" s="159">
-        <f>(D17-C17)/C17</f>
+      <c r="C85" s="163"/>
+      <c r="D85" s="159">
+        <f>(D18-C18)/C18</f>
         <v>-4.5090909090909091E-2</v>
       </c>
-      <c r="E83" s="159">
-        <f t="shared" ref="E83:L83" si="26">(E17-D17)/D17</f>
+      <c r="E85" s="159">
+        <f t="shared" ref="E85:L85" si="27">(E18-D18)/D18</f>
         <v>-4.7981721249047982E-2</v>
       </c>
-      <c r="F83" s="159">
-        <f t="shared" si="26"/>
+      <c r="F85" s="159">
+        <f t="shared" si="27"/>
         <v>-7.0199999999999999E-2</v>
       </c>
-      <c r="G83" s="159">
-        <f t="shared" si="26"/>
+      <c r="G85" s="159">
+        <f t="shared" si="27"/>
         <v>-5.7431705743170573E-2</v>
       </c>
-      <c r="H83" s="159">
-        <f t="shared" si="26"/>
+      <c r="H85" s="159">
+        <f t="shared" si="27"/>
         <v>-3.7825193975353721E-2</v>
       </c>
-      <c r="I83" s="159">
-        <f t="shared" si="26"/>
+      <c r="I85" s="159">
+        <f t="shared" si="27"/>
         <v>-3.1959679810257928E-2</v>
       </c>
-      <c r="J83" s="159">
-        <f t="shared" si="26"/>
+      <c r="J85" s="159">
+        <f t="shared" si="27"/>
         <v>-3.1422271223814774E-2</v>
       </c>
-      <c r="K83" s="159">
-        <f t="shared" si="26"/>
+      <c r="K85" s="159">
+        <f t="shared" si="27"/>
         <v>-2.5611838360842343E-2</v>
       </c>
-      <c r="L83" s="159">
-        <f t="shared" si="26"/>
+      <c r="L85" s="159">
+        <f t="shared" si="27"/>
         <v>-2.6155244029075805E-2</v>
       </c>
-      <c r="N83" s="163"/>
-      <c r="O83" s="159">
-        <f>(O17-N17)/N17</f>
+      <c r="N85" s="163"/>
+      <c r="O85" s="159">
+        <f>(O18-N18)/N18</f>
         <v>-7.5654704170708053E-3</v>
       </c>
-      <c r="P83" s="159">
-        <f t="shared" ref="P83:U83" si="27">(P17-O17)/O17</f>
+      <c r="P85" s="159">
+        <f t="shared" ref="P85:U85" si="28">(P18-O18)/O18</f>
         <v>-6.9064373208235601E-3</v>
       </c>
-      <c r="Q83" s="159">
-        <f t="shared" si="27"/>
+      <c r="Q85" s="159">
+        <f t="shared" si="28"/>
         <v>-5.9703450990683639E-3</v>
       </c>
-      <c r="R83" s="159">
-        <f t="shared" si="27"/>
+      <c r="R85" s="159">
+        <f t="shared" si="28"/>
         <v>-6.2702131872483663E-3</v>
       </c>
-      <c r="S83" s="159">
-        <f t="shared" si="27"/>
+      <c r="S85" s="159">
+        <f t="shared" si="28"/>
         <v>-7.1732199787460146E-3</v>
       </c>
-      <c r="T83" s="159">
-        <f t="shared" si="27"/>
+      <c r="T85" s="159">
+        <f t="shared" si="28"/>
         <v>-5.6194808670056197E-3</v>
       </c>
-      <c r="U83" s="159">
-        <f t="shared" si="27"/>
+      <c r="U85" s="159">
+        <f t="shared" si="28"/>
         <v>-3.6329386437029061E-3</v>
       </c>
-      <c r="W83" s="163"/>
-    </row>
-    <row r="84" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B84" s="12" t="s">
+      <c r="W85" s="163"/>
+    </row>
+    <row r="86" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B86" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C84" s="163"/>
-      <c r="D84" s="159">
-        <f t="shared" ref="D84:L84" si="28">IF(C18=0,
-IF(D18=0,0,IF(D18&gt;0,1,-1)),
-(D18-C18)/ABS(C18)
+      <c r="C86" s="163"/>
+      <c r="D86" s="159">
+        <f t="shared" ref="D86:L86" si="29">IF(C19=0,
+IF(D19=0,0,IF(D19&gt;0,1,-1)),
+(D19-C19)/ABS(C19)
 )</f>
         <v>0.10830324909747296</v>
       </c>
-      <c r="E84" s="159">
-        <f t="shared" si="28"/>
+      <c r="E86" s="159">
+        <f t="shared" si="29"/>
         <v>0.29315960912052108</v>
       </c>
-      <c r="F84" s="159">
-        <f t="shared" si="28"/>
+      <c r="F86" s="159">
+        <f t="shared" si="29"/>
         <v>-1.679261125104918E-3</v>
       </c>
-      <c r="G84" s="159">
-        <f t="shared" si="28"/>
+      <c r="G86" s="159">
+        <f t="shared" si="29"/>
         <v>0.10344827586206885</v>
       </c>
-      <c r="H84" s="159">
-        <f t="shared" si="28"/>
+      <c r="H86" s="159">
+        <f t="shared" si="29"/>
         <v>0.71036585365853677</v>
       </c>
-      <c r="I84" s="159">
-        <f t="shared" si="28"/>
+      <c r="I86" s="159">
+        <f t="shared" si="29"/>
         <v>8.9126559714795009E-2</v>
       </c>
-      <c r="J84" s="159">
-        <f t="shared" si="28"/>
+      <c r="J86" s="159">
+        <f t="shared" si="29"/>
         <v>3.2733224222585224E-3</v>
       </c>
-      <c r="K84" s="159">
-        <f t="shared" si="28"/>
+      <c r="K86" s="159">
+        <f t="shared" si="29"/>
         <v>-8.1566068515497268E-3</v>
       </c>
-      <c r="L84" s="159">
-        <f t="shared" si="28"/>
+      <c r="L86" s="159">
+        <f t="shared" si="29"/>
         <v>0.2269736842105263</v>
       </c>
-      <c r="N84" s="163"/>
-      <c r="O84" s="159">
-        <f t="shared" ref="O84:U84" si="29">IF(N18=0,
-IF(O18=0,0,IF(O18&gt;0,1,-1)),
-(O18-N18)/ABS(N18)
+      <c r="N86" s="163"/>
+      <c r="O86" s="159">
+        <f t="shared" ref="O86:U86" si="30">IF(N19=0,
+IF(O19=0,0,IF(O19&gt;0,1,-1)),
+(O19-N19)/ABS(N19)
 )</f>
         <v>-8.4967320261437981E-2</v>
       </c>
-      <c r="P84" s="159">
-        <f t="shared" si="29"/>
+      <c r="P86" s="159">
+        <f t="shared" si="30"/>
         <v>-0.30714285714285711</v>
       </c>
-      <c r="Q84" s="159">
-        <f t="shared" si="29"/>
+      <c r="Q86" s="159">
+        <f t="shared" si="30"/>
         <v>1.4742268041237112</v>
       </c>
-      <c r="R84" s="159">
-        <f t="shared" si="29"/>
+      <c r="R86" s="159">
+        <f t="shared" si="30"/>
         <v>-0.3125</v>
       </c>
-      <c r="S84" s="159">
-        <f t="shared" si="29"/>
+      <c r="S86" s="159">
+        <f t="shared" si="30"/>
         <v>-4.8484848484848395E-2</v>
       </c>
-      <c r="T84" s="159">
-        <f t="shared" si="29"/>
+      <c r="T86" s="159">
+        <f t="shared" si="30"/>
         <v>0.178343949044586</v>
       </c>
-      <c r="U84" s="159">
-        <f t="shared" si="29"/>
+      <c r="U86" s="159">
+        <f t="shared" si="30"/>
         <v>0.535135135135135</v>
       </c>
-      <c r="W84" s="163"/>
-    </row>
-    <row r="86" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="15" t="s">
+      <c r="W86" s="163"/>
+    </row>
+    <row r="88" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C86" s="14"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
-      <c r="H86" s="14"/>
-      <c r="I86" s="14"/>
-      <c r="J86" s="14"/>
-      <c r="K86" s="14"/>
-      <c r="L86" s="14"/>
-      <c r="N86" s="14"/>
-      <c r="O86" s="14"/>
-      <c r="P86" s="14"/>
-      <c r="Q86" s="14"/>
-      <c r="R86" s="14"/>
-      <c r="S86" s="14"/>
-      <c r="T86" s="14"/>
-      <c r="U86" s="14"/>
-      <c r="W86" s="14"/>
-    </row>
-    <row r="87" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B87" s="9" t="s">
+      <c r="C88" s="14"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="14"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="14"/>
+      <c r="H88" s="14"/>
+      <c r="I88" s="14"/>
+      <c r="J88" s="14"/>
+      <c r="K88" s="14"/>
+      <c r="L88" s="14"/>
+      <c r="N88" s="14"/>
+      <c r="O88" s="14"/>
+      <c r="P88" s="14"/>
+      <c r="Q88" s="14"/>
+      <c r="R88" s="14"/>
+      <c r="S88" s="14"/>
+      <c r="T88" s="14"/>
+      <c r="U88" s="14"/>
+      <c r="W88" s="14"/>
+    </row>
+    <row r="89" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B89" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C87" s="75">
-        <f t="shared" ref="C87:I87" si="30">C7/C5</f>
+      <c r="C89" s="75">
+        <f t="shared" ref="C89:I89" si="31">C7/C5</f>
         <v>0.39075955648097049</v>
       </c>
-      <c r="D87" s="75">
-        <f t="shared" si="30"/>
+      <c r="D89" s="75">
+        <f t="shared" si="31"/>
         <v>0.38469860491899105</v>
       </c>
-      <c r="E87" s="75">
-        <f t="shared" si="30"/>
+      <c r="E89" s="75">
+        <f t="shared" si="31"/>
         <v>0.38343718820007905</v>
       </c>
-      <c r="F87" s="75">
-        <f t="shared" si="30"/>
+      <c r="F89" s="75">
+        <f t="shared" si="31"/>
         <v>0.37817768109034722</v>
       </c>
-      <c r="G87" s="75">
-        <f t="shared" si="30"/>
+      <c r="G89" s="75">
+        <f t="shared" si="31"/>
         <v>0.38233247727810865</v>
       </c>
-      <c r="H87" s="75">
-        <f t="shared" si="30"/>
+      <c r="H89" s="75">
+        <f t="shared" si="31"/>
         <v>0.41779359625167778</v>
       </c>
-      <c r="I87" s="75">
-        <f t="shared" si="30"/>
+      <c r="I89" s="75">
+        <f t="shared" si="31"/>
         <v>0.43309630561360085</v>
       </c>
-      <c r="J87" s="75">
-        <f t="shared" ref="J87:L87" si="31">J7/J5</f>
+      <c r="J89" s="75">
+        <f t="shared" ref="J89:L89" si="32">J7/J5</f>
         <v>0.44131129577207562</v>
       </c>
-      <c r="K87" s="75">
-        <f t="shared" si="31"/>
+      <c r="K89" s="75">
+        <f t="shared" si="32"/>
         <v>0.46206349815233932</v>
       </c>
-      <c r="L87" s="75">
-        <f t="shared" si="31"/>
+      <c r="L89" s="75">
+        <f t="shared" si="32"/>
         <v>0.46905164107160452</v>
       </c>
-      <c r="N87" s="75">
-        <f t="shared" ref="N87:U87" si="32">N7/N5</f>
+      <c r="N89" s="75">
+        <f t="shared" ref="N89:U89" si="33">N7/N5</f>
         <v>0.46578074554009236</v>
       </c>
-      <c r="O87" s="75">
-        <f t="shared" si="32"/>
+      <c r="O89" s="75">
+        <f t="shared" si="33"/>
         <v>0.46257155181458898</v>
       </c>
-      <c r="P87" s="75">
-        <f t="shared" si="32"/>
+      <c r="P89" s="75">
+        <f t="shared" si="33"/>
         <v>0.4622247972190035</v>
       </c>
-      <c r="Q87" s="75">
-        <f t="shared" si="32"/>
+      <c r="Q89" s="75">
+        <f t="shared" si="33"/>
         <v>0.46882542236524538</v>
       </c>
-      <c r="R87" s="75">
-        <f t="shared" si="32"/>
+      <c r="R89" s="75">
+        <f t="shared" si="33"/>
         <v>0.47050619238876246</v>
       </c>
-      <c r="S87" s="75">
-        <f t="shared" si="32"/>
+      <c r="S89" s="75">
+        <f t="shared" si="33"/>
         <v>0.46490705687183631</v>
       </c>
-      <c r="T87" s="75">
-        <f t="shared" si="32"/>
+      <c r="T89" s="75">
+        <f t="shared" si="33"/>
         <v>0.47177600374758455</v>
       </c>
-      <c r="U87" s="75">
-        <f t="shared" si="32"/>
+      <c r="U89" s="75">
+        <f t="shared" si="33"/>
         <v>0.4815868555051615</v>
       </c>
-      <c r="W87" s="75">
+      <c r="W89" s="75">
         <f>W7/W5</f>
         <v>0.47325288039722968</v>
       </c>
     </row>
-    <row r="88" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B88" s="9" t="s">
+    <row r="90" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B90" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C88" s="75">
-        <f t="shared" ref="C88:I88" si="33">C11/C5</f>
+      <c r="C90" s="75">
+        <f t="shared" ref="C90:I90" si="34">C11/C5</f>
         <v>0.27835410106706115</v>
       </c>
-      <c r="D88" s="75">
-        <f t="shared" si="33"/>
+      <c r="D90" s="75">
+        <f t="shared" si="34"/>
         <v>0.26760428208729942</v>
       </c>
-      <c r="E88" s="75">
-        <f t="shared" si="33"/>
+      <c r="E90" s="75">
+        <f t="shared" si="34"/>
         <v>0.26694026619477024</v>
       </c>
-      <c r="F88" s="75">
-        <f t="shared" si="33"/>
+      <c r="F90" s="75">
+        <f t="shared" si="34"/>
         <v>0.24572017188496928</v>
       </c>
-      <c r="G88" s="75">
-        <f t="shared" si="33"/>
+      <c r="G90" s="75">
+        <f t="shared" si="34"/>
         <v>0.24147314354406862</v>
       </c>
-      <c r="H88" s="75">
-        <f t="shared" si="33"/>
+      <c r="H90" s="75">
+        <f t="shared" si="34"/>
         <v>0.29782377527561593</v>
       </c>
-      <c r="I88" s="75">
-        <f t="shared" si="33"/>
+      <c r="I90" s="75">
+        <f t="shared" si="34"/>
         <v>0.30288744395528594</v>
       </c>
-      <c r="J88" s="75">
-        <f t="shared" ref="J88:L88" si="34">J11/J5</f>
+      <c r="J90" s="75">
+        <f t="shared" ref="J90:L90" si="35">J11/J5</f>
         <v>0.29821412265024722</v>
       </c>
-      <c r="K88" s="75">
-        <f t="shared" si="34"/>
+      <c r="K90" s="75">
+        <f t="shared" si="35"/>
         <v>0.31510222870075566</v>
       </c>
-      <c r="L88" s="75">
-        <f t="shared" si="34"/>
+      <c r="L90" s="75">
+        <f t="shared" si="35"/>
         <v>0.31970799762591884</v>
       </c>
-      <c r="N88" s="75">
-        <f t="shared" ref="N88:U88" si="35">N11/N5</f>
+      <c r="N90" s="75">
+        <f t="shared" ref="N90:U90" si="36">N11/N5</f>
         <v>0.30742785362467356</v>
       </c>
-      <c r="O88" s="75">
-        <f t="shared" si="35"/>
+      <c r="O90" s="75">
+        <f t="shared" si="36"/>
         <v>0.29555708406682446</v>
       </c>
-      <c r="P88" s="75">
-        <f t="shared" si="35"/>
+      <c r="P90" s="75">
+        <f t="shared" si="36"/>
         <v>0.31171389444854103</v>
       </c>
-      <c r="Q88" s="75">
-        <f t="shared" si="35"/>
+      <c r="Q90" s="75">
+        <f t="shared" si="36"/>
         <v>0.34458567980691873</v>
       </c>
-      <c r="R88" s="75">
-        <f t="shared" si="35"/>
+      <c r="R90" s="75">
+        <f t="shared" si="36"/>
         <v>0.31029058610094484</v>
       </c>
-      <c r="S88" s="75">
-        <f t="shared" si="35"/>
+      <c r="S90" s="75">
+        <f t="shared" si="36"/>
         <v>0.29990641881832492</v>
       </c>
-      <c r="T88" s="75">
-        <f t="shared" si="35"/>
+      <c r="T90" s="75">
+        <f t="shared" si="36"/>
         <v>0.31646594968086977</v>
       </c>
-      <c r="U88" s="75">
-        <f t="shared" si="35"/>
+      <c r="U90" s="75">
+        <f t="shared" si="36"/>
         <v>0.35373827875010433</v>
       </c>
-      <c r="W88" s="75">
+      <c r="W90" s="75">
         <f>W11/W5</f>
         <v>0.32383951957797791</v>
       </c>
     </row>
-    <row r="89" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B89" s="82" t="s">
+    <row r="91" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B91" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="C89" s="168">
-        <f t="shared" ref="C89:I89" si="36">C16/C5</f>
+      <c r="C91" s="168">
+        <f t="shared" ref="C91:I91" si="37">C17/C5</f>
         <v>0.211867983064288</v>
       </c>
-      <c r="D89" s="168">
-        <f t="shared" si="36"/>
+      <c r="D91" s="168">
+        <f t="shared" si="37"/>
         <v>0.21092420845075338</v>
       </c>
-      <c r="E89" s="168">
-        <f t="shared" si="36"/>
+      <c r="E91" s="168">
+        <f t="shared" si="37"/>
         <v>0.22414202074587247</v>
       </c>
-      <c r="F89" s="168">
-        <f t="shared" si="36"/>
+      <c r="F91" s="168">
+        <f t="shared" si="37"/>
         <v>0.21238094505984456</v>
       </c>
-      <c r="G89" s="168">
-        <f t="shared" si="36"/>
+      <c r="G91" s="168">
+        <f t="shared" si="37"/>
         <v>0.20913611278072236</v>
       </c>
-      <c r="H89" s="168">
-        <f t="shared" si="36"/>
+      <c r="H91" s="168">
+        <f t="shared" si="37"/>
         <v>0.25881793355694238</v>
       </c>
-      <c r="I89" s="168">
-        <f t="shared" si="36"/>
+      <c r="I91" s="168">
+        <f t="shared" si="37"/>
         <v>0.25309640705199732</v>
       </c>
-      <c r="J89" s="168">
-        <f t="shared" ref="J89:L89" si="37">J16/J5</f>
+      <c r="J91" s="168">
+        <f t="shared" ref="J91:L91" si="38">J17/J5</f>
         <v>0.25306234264320282</v>
       </c>
-      <c r="K89" s="168">
-        <f t="shared" si="37"/>
+      <c r="K91" s="168">
+        <f t="shared" si="38"/>
         <v>0.23971255769943867</v>
       </c>
-      <c r="L89" s="168">
-        <f t="shared" si="37"/>
+      <c r="L91" s="168">
+        <f t="shared" si="38"/>
         <v>0.26915064121818238</v>
       </c>
-      <c r="N89" s="168">
-        <f t="shared" ref="N89:U89" si="38">N16/N5</f>
+      <c r="N91" s="168">
+        <f t="shared" ref="N91:U91" si="39">N17/N5</f>
         <v>0.26044318094167684</v>
       </c>
-      <c r="O89" s="168">
-        <f t="shared" si="38"/>
+      <c r="O91" s="168">
+        <f t="shared" si="39"/>
         <v>0.25004371801298714</v>
       </c>
-      <c r="P89" s="168">
-        <f t="shared" si="38"/>
+      <c r="P91" s="168">
+        <f t="shared" si="39"/>
         <v>0.15523016959865163</v>
       </c>
-      <c r="Q89" s="168">
-        <f t="shared" si="38"/>
+      <c r="Q91" s="168">
+        <f t="shared" si="39"/>
         <v>0.29227674979887369</v>
       </c>
-      <c r="R89" s="168">
-        <f t="shared" si="38"/>
+      <c r="R91" s="168">
+        <f t="shared" si="39"/>
         <v>0.25986010759341016</v>
       </c>
-      <c r="S89" s="168">
-        <f t="shared" si="38"/>
+      <c r="S91" s="168">
+        <f t="shared" si="39"/>
         <v>0.24920243311072354</v>
       </c>
-      <c r="T89" s="168">
-        <f t="shared" si="38"/>
+      <c r="T91" s="168">
+        <f t="shared" si="39"/>
         <v>0.26804988971951671</v>
       </c>
-      <c r="U89" s="168">
-        <f t="shared" si="38"/>
+      <c r="U91" s="168">
+        <f t="shared" si="39"/>
         <v>0.29283647291243498</v>
       </c>
-      <c r="W89" s="168">
-        <f>W16/W5</f>
+      <c r="W91" s="168">
+        <f>W17/W5</f>
         <v>0.27036823631768275</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="W17 C72:H72 W72 I72:L72 D83:L83 O83:U83" formula="1"/>
-    <ignoredError sqref="N54:U54" formulaRange="1"/>
+    <ignoredError sqref="W18 C73:H73 W73 I73:L73 D85:L85 O85:U85" formula="1"/>
+    <ignoredError sqref="N55:U55" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -23303,36 +23411,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="212"/>
-      <c r="F2" s="212"/>
-      <c r="G2" s="213"/>
-      <c r="H2" s="214" t="s">
+      <c r="D2" s="211"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="215" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="212"/>
-      <c r="J2" s="212"/>
-      <c r="K2" s="212"/>
-      <c r="L2" s="212"/>
+      <c r="I2" s="211"/>
+      <c r="J2" s="211"/>
+      <c r="K2" s="211"/>
+      <c r="L2" s="211"/>
       <c r="O2" s="90"/>
-      <c r="S2" s="212" t="s">
+      <c r="S2" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="212"/>
-      <c r="U2" s="212"/>
-      <c r="V2" s="212"/>
-      <c r="W2" s="212"/>
-      <c r="X2" s="212"/>
-      <c r="Y2" s="212"/>
-      <c r="Z2" s="212"/>
-      <c r="AA2" s="212" t="s">
+      <c r="T2" s="211"/>
+      <c r="U2" s="211"/>
+      <c r="V2" s="211"/>
+      <c r="W2" s="211"/>
+      <c r="X2" s="211"/>
+      <c r="Y2" s="211"/>
+      <c r="Z2" s="211"/>
+      <c r="AA2" s="211" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="212"/>
-      <c r="AC2" s="212"/>
+      <c r="AB2" s="211"/>
+      <c r="AC2" s="211"/>
       <c r="AE2" s="117" t="s">
         <v>75</v>
       </c>
@@ -23343,32 +23451,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="211" t="s">
+      <c r="C4" s="216" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="211"/>
-      <c r="E4" s="211"/>
-      <c r="F4" s="211"/>
-      <c r="G4" s="211"/>
-      <c r="H4" s="211"/>
-      <c r="I4" s="211"/>
-      <c r="J4" s="211"/>
-      <c r="K4" s="211"/>
-      <c r="L4" s="211"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
       <c r="O4" s="90"/>
-      <c r="S4" s="219" t="s">
+      <c r="S4" s="212" t="s">
         <v>114</v>
       </c>
-      <c r="T4" s="220"/>
-      <c r="U4" s="220"/>
-      <c r="V4" s="220"/>
-      <c r="W4" s="220"/>
-      <c r="X4" s="220"/>
-      <c r="Y4" s="220"/>
-      <c r="Z4" s="220"/>
-      <c r="AA4" s="220"/>
-      <c r="AB4" s="220"/>
-      <c r="AC4" s="220"/>
+      <c r="T4" s="213"/>
+      <c r="U4" s="213"/>
+      <c r="V4" s="213"/>
+      <c r="W4" s="213"/>
+      <c r="X4" s="213"/>
+      <c r="Y4" s="213"/>
+      <c r="Z4" s="213"/>
+      <c r="AA4" s="213"/>
+      <c r="AB4" s="213"/>
+      <c r="AC4" s="213"/>
       <c r="AE4" s="119" t="s">
         <v>121</v>
       </c>
@@ -24044,33 +24152,33 @@
       <c r="Q12" s="91"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="211" t="s">
+      <c r="C13" s="216" t="s">
         <v>116</v>
       </c>
-      <c r="D13" s="211"/>
-      <c r="E13" s="211"/>
-      <c r="F13" s="211"/>
-      <c r="G13" s="211"/>
-      <c r="H13" s="211"/>
-      <c r="I13" s="211"/>
-      <c r="J13" s="211"/>
-      <c r="K13" s="211"/>
-      <c r="L13" s="211"/>
+      <c r="D13" s="216"/>
+      <c r="E13" s="216"/>
+      <c r="F13" s="216"/>
+      <c r="G13" s="216"/>
+      <c r="H13" s="216"/>
+      <c r="I13" s="216"/>
+      <c r="J13" s="216"/>
+      <c r="K13" s="216"/>
+      <c r="L13" s="216"/>
       <c r="O13" s="90"/>
       <c r="Q13" s="91"/>
-      <c r="S13" s="219" t="s">
+      <c r="S13" s="212" t="s">
         <v>116</v>
       </c>
-      <c r="T13" s="220"/>
-      <c r="U13" s="220"/>
-      <c r="V13" s="220"/>
-      <c r="W13" s="220"/>
-      <c r="X13" s="220"/>
-      <c r="Y13" s="220"/>
-      <c r="Z13" s="220"/>
-      <c r="AA13" s="220"/>
-      <c r="AB13" s="220"/>
-      <c r="AC13" s="220"/>
+      <c r="T13" s="213"/>
+      <c r="U13" s="213"/>
+      <c r="V13" s="213"/>
+      <c r="W13" s="213"/>
+      <c r="X13" s="213"/>
+      <c r="Y13" s="213"/>
+      <c r="Z13" s="213"/>
+      <c r="AA13" s="213"/>
+      <c r="AB13" s="213"/>
+      <c r="AC13" s="213"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
@@ -24652,35 +24760,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="212"/>
-      <c r="F2" s="212"/>
-      <c r="G2" s="213"/>
-      <c r="H2" s="214" t="s">
+      <c r="D2" s="211"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="215" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="212"/>
-      <c r="J2" s="212"/>
-      <c r="K2" s="212"/>
-      <c r="L2" s="212"/>
-      <c r="P2" s="212" t="s">
+      <c r="I2" s="211"/>
+      <c r="J2" s="211"/>
+      <c r="K2" s="211"/>
+      <c r="L2" s="211"/>
+      <c r="P2" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="212"/>
-      <c r="R2" s="212"/>
-      <c r="S2" s="212"/>
-      <c r="T2" s="212"/>
-      <c r="U2" s="212"/>
-      <c r="V2" s="212"/>
-      <c r="W2" s="212"/>
-      <c r="X2" s="212" t="s">
+      <c r="Q2" s="211"/>
+      <c r="R2" s="211"/>
+      <c r="S2" s="211"/>
+      <c r="T2" s="211"/>
+      <c r="U2" s="211"/>
+      <c r="V2" s="211"/>
+      <c r="W2" s="211"/>
+      <c r="X2" s="211" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="212"/>
-      <c r="Z2" s="212"/>
+      <c r="Y2" s="211"/>
+      <c r="Z2" s="211"/>
       <c r="AB2" s="117" t="s">
         <v>75</v>
       </c>
@@ -24689,31 +24797,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="211" t="s">
+      <c r="C4" s="216" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="211"/>
-      <c r="E4" s="211"/>
-      <c r="F4" s="211"/>
-      <c r="G4" s="211"/>
-      <c r="H4" s="211"/>
-      <c r="I4" s="211"/>
-      <c r="J4" s="211"/>
-      <c r="K4" s="211"/>
-      <c r="L4" s="211"/>
-      <c r="P4" s="220" t="s">
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
+      <c r="P4" s="213" t="s">
         <v>114</v>
       </c>
-      <c r="Q4" s="220"/>
-      <c r="R4" s="220"/>
-      <c r="S4" s="220"/>
-      <c r="T4" s="220"/>
-      <c r="U4" s="220"/>
-      <c r="V4" s="220"/>
-      <c r="W4" s="220"/>
-      <c r="X4" s="220"/>
-      <c r="Y4" s="220"/>
-      <c r="Z4" s="220"/>
+      <c r="Q4" s="213"/>
+      <c r="R4" s="213"/>
+      <c r="S4" s="213"/>
+      <c r="T4" s="213"/>
+      <c r="U4" s="213"/>
+      <c r="V4" s="213"/>
+      <c r="W4" s="213"/>
+      <c r="X4" s="213"/>
+      <c r="Y4" s="213"/>
+      <c r="Z4" s="213"/>
       <c r="AB4" s="119" t="s">
         <v>121</v>
       </c>
@@ -24914,32 +25022,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="211" t="s">
+      <c r="C9" s="216" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="211"/>
-      <c r="E9" s="211"/>
-      <c r="F9" s="211"/>
-      <c r="G9" s="211"/>
-      <c r="H9" s="211"/>
-      <c r="I9" s="211"/>
-      <c r="J9" s="211"/>
-      <c r="K9" s="211"/>
-      <c r="L9" s="211"/>
+      <c r="D9" s="216"/>
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="216"/>
+      <c r="H9" s="216"/>
+      <c r="I9" s="216"/>
+      <c r="J9" s="216"/>
+      <c r="K9" s="216"/>
+      <c r="L9" s="216"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="220" t="s">
+      <c r="P9" s="213" t="s">
         <v>128</v>
       </c>
-      <c r="Q9" s="220"/>
-      <c r="R9" s="220"/>
-      <c r="S9" s="220"/>
-      <c r="T9" s="220"/>
-      <c r="U9" s="220"/>
-      <c r="V9" s="220"/>
-      <c r="W9" s="220"/>
-      <c r="X9" s="220"/>
-      <c r="Y9" s="220"/>
-      <c r="Z9" s="220"/>
+      <c r="Q9" s="213"/>
+      <c r="R9" s="213"/>
+      <c r="S9" s="213"/>
+      <c r="T9" s="213"/>
+      <c r="U9" s="213"/>
+      <c r="V9" s="213"/>
+      <c r="W9" s="213"/>
+      <c r="X9" s="213"/>
+      <c r="Y9" s="213"/>
+      <c r="Z9" s="213"/>
       <c r="AB9" s="119" t="str">
         <f>AB4</f>
         <v>Q1-Q2-Q3</v>
@@ -25409,31 +25517,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="211" t="s">
+      <c r="C17" s="216" t="s">
         <v>126</v>
       </c>
-      <c r="D17" s="211"/>
-      <c r="E17" s="211"/>
-      <c r="F17" s="211"/>
-      <c r="G17" s="211"/>
-      <c r="H17" s="211"/>
-      <c r="I17" s="211"/>
-      <c r="J17" s="211"/>
-      <c r="K17" s="211"/>
-      <c r="L17" s="211"/>
-      <c r="P17" s="220" t="s">
+      <c r="D17" s="216"/>
+      <c r="E17" s="216"/>
+      <c r="F17" s="216"/>
+      <c r="G17" s="216"/>
+      <c r="H17" s="216"/>
+      <c r="I17" s="216"/>
+      <c r="J17" s="216"/>
+      <c r="K17" s="216"/>
+      <c r="L17" s="216"/>
+      <c r="P17" s="213" t="s">
         <v>126</v>
       </c>
-      <c r="Q17" s="220"/>
-      <c r="R17" s="220"/>
-      <c r="S17" s="220"/>
-      <c r="T17" s="220"/>
-      <c r="U17" s="220"/>
-      <c r="V17" s="220"/>
-      <c r="W17" s="220"/>
-      <c r="X17" s="220"/>
-      <c r="Y17" s="220"/>
-      <c r="Z17" s="220"/>
+      <c r="Q17" s="213"/>
+      <c r="R17" s="213"/>
+      <c r="S17" s="213"/>
+      <c r="T17" s="213"/>
+      <c r="U17" s="213"/>
+      <c r="V17" s="213"/>
+      <c r="W17" s="213"/>
+      <c r="X17" s="213"/>
+      <c r="Y17" s="213"/>
+      <c r="Z17" s="213"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="7" t="s">
@@ -25823,60 +25931,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="212" t="s">
+      <c r="C3" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="212"/>
-      <c r="G3" s="213"/>
-      <c r="H3" s="214" t="s">
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="215" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="212"/>
-      <c r="J3" s="212"/>
-      <c r="K3" s="212"/>
-      <c r="L3" s="212"/>
-      <c r="P3" s="215"/>
-      <c r="Q3" s="215"/>
-      <c r="R3" s="215"/>
-      <c r="S3" s="215"/>
-      <c r="T3" s="215"/>
-      <c r="U3" s="215"/>
-      <c r="V3" s="215"/>
-      <c r="W3" s="215"/>
-      <c r="X3" s="215"/>
-      <c r="Y3" s="215"/>
-      <c r="Z3" s="215"/>
+      <c r="I3" s="211"/>
+      <c r="J3" s="211"/>
+      <c r="K3" s="211"/>
+      <c r="L3" s="211"/>
+      <c r="P3" s="217"/>
+      <c r="Q3" s="217"/>
+      <c r="R3" s="217"/>
+      <c r="S3" s="217"/>
+      <c r="T3" s="217"/>
+      <c r="U3" s="217"/>
+      <c r="V3" s="217"/>
+      <c r="W3" s="217"/>
+      <c r="X3" s="217"/>
+      <c r="Y3" s="217"/>
+      <c r="Z3" s="217"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="211" t="s">
+      <c r="C5" s="216" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="211"/>
-      <c r="E5" s="211"/>
-      <c r="F5" s="211"/>
-      <c r="G5" s="211"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="211"/>
-      <c r="K5" s="211"/>
-      <c r="L5" s="211"/>
-      <c r="P5" s="215"/>
-      <c r="Q5" s="215"/>
-      <c r="R5" s="215"/>
-      <c r="S5" s="215"/>
-      <c r="T5" s="215"/>
-      <c r="U5" s="215"/>
-      <c r="V5" s="215"/>
-      <c r="W5" s="215"/>
-      <c r="X5" s="215"/>
-      <c r="Y5" s="215"/>
-      <c r="Z5" s="215"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="216"/>
+      <c r="K5" s="216"/>
+      <c r="L5" s="216"/>
+      <c r="P5" s="217"/>
+      <c r="Q5" s="217"/>
+      <c r="R5" s="217"/>
+      <c r="S5" s="217"/>
+      <c r="T5" s="217"/>
+      <c r="U5" s="217"/>
+      <c r="V5" s="217"/>
+      <c r="W5" s="217"/>
+      <c r="X5" s="217"/>
+      <c r="Y5" s="217"/>
+      <c r="Z5" s="217"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -26062,30 +26170,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="211" t="s">
+      <c r="C11" s="216" t="s">
         <v>134</v>
       </c>
-      <c r="D11" s="211"/>
-      <c r="E11" s="211"/>
-      <c r="F11" s="211"/>
-      <c r="G11" s="211"/>
-      <c r="H11" s="211"/>
-      <c r="I11" s="211"/>
-      <c r="J11" s="211"/>
-      <c r="K11" s="211"/>
-      <c r="L11" s="211"/>
+      <c r="D11" s="216"/>
+      <c r="E11" s="216"/>
+      <c r="F11" s="216"/>
+      <c r="G11" s="216"/>
+      <c r="H11" s="216"/>
+      <c r="I11" s="216"/>
+      <c r="J11" s="216"/>
+      <c r="K11" s="216"/>
+      <c r="L11" s="216"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="215"/>
-      <c r="Q11" s="215"/>
-      <c r="R11" s="215"/>
-      <c r="S11" s="215"/>
-      <c r="T11" s="215"/>
-      <c r="U11" s="215"/>
-      <c r="V11" s="215"/>
-      <c r="W11" s="215"/>
-      <c r="X11" s="215"/>
-      <c r="Y11" s="215"/>
-      <c r="Z11" s="215"/>
+      <c r="P11" s="217"/>
+      <c r="Q11" s="217"/>
+      <c r="R11" s="217"/>
+      <c r="S11" s="217"/>
+      <c r="T11" s="217"/>
+      <c r="U11" s="217"/>
+      <c r="V11" s="217"/>
+      <c r="W11" s="217"/>
+      <c r="X11" s="217"/>
+      <c r="Y11" s="217"/>
+      <c r="Z11" s="217"/>
       <c r="AB11" s="123"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -26152,23 +26260,23 @@
         <v>135</v>
       </c>
       <c r="C13" s="127">
-        <f>Statements!H22</f>
+        <f>Statements!H23</f>
         <v>26278</v>
       </c>
       <c r="D13" s="127">
-        <f>Statements!I22</f>
+        <f>Statements!I23</f>
         <v>28184</v>
       </c>
       <c r="E13" s="127">
-        <f>Statements!J22</f>
+        <f>Statements!J23</f>
         <v>29508</v>
       </c>
       <c r="F13" s="127">
-        <f>Statements!K22</f>
+        <f>Statements!K23</f>
         <v>33410</v>
       </c>
       <c r="G13" s="128">
-        <f>Statements!L22</f>
+        <f>Statements!L23</f>
         <v>39777</v>
       </c>
       <c r="H13" s="34">
@@ -26211,23 +26319,23 @@
         <v>242</v>
       </c>
       <c r="C14" s="127">
-        <f>Statements!H24</f>
+        <f>Statements!H25</f>
         <v>6580</v>
       </c>
       <c r="D14" s="127">
-        <f>Statements!I24</f>
+        <f>Statements!I25</f>
         <v>4946</v>
       </c>
       <c r="E14" s="127">
-        <f>Statements!J24</f>
+        <f>Statements!J25</f>
         <v>6331</v>
       </c>
       <c r="F14" s="127">
-        <f>Statements!K24</f>
+        <f>Statements!K25</f>
         <v>7286</v>
       </c>
       <c r="G14" s="128">
-        <f>Statements!L24</f>
+        <f>Statements!L25</f>
         <v>5718</v>
       </c>
       <c r="H14" s="34">
@@ -26270,23 +26378,23 @@
         <v>136</v>
       </c>
       <c r="C15" s="127">
-        <f>Statements!H32</f>
+        <f>Statements!H33</f>
         <v>54763</v>
       </c>
       <c r="D15" s="127">
-        <f>Statements!I32</f>
+        <f>Statements!I33</f>
         <v>64115</v>
       </c>
       <c r="E15" s="127">
-        <f>Statements!J32</f>
+        <f>Statements!J33</f>
         <v>62611</v>
       </c>
       <c r="F15" s="127">
-        <f>Statements!K32</f>
+        <f>Statements!K33</f>
         <v>68960</v>
       </c>
       <c r="G15" s="128">
-        <f>Statements!L32</f>
+        <f>Statements!L33</f>
         <v>69860</v>
       </c>
       <c r="H15" s="20">
@@ -26327,18 +26435,18 @@
       <c r="D16" s="20"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="211" t="s">
+      <c r="C18" s="216" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="211"/>
-      <c r="E18" s="211"/>
-      <c r="F18" s="211"/>
-      <c r="G18" s="211"/>
-      <c r="H18" s="211"/>
-      <c r="I18" s="211"/>
-      <c r="J18" s="211"/>
-      <c r="K18" s="211"/>
-      <c r="L18" s="211"/>
+      <c r="D18" s="216"/>
+      <c r="E18" s="216"/>
+      <c r="F18" s="216"/>
+      <c r="G18" s="216"/>
+      <c r="H18" s="216"/>
+      <c r="I18" s="216"/>
+      <c r="J18" s="216"/>
+      <c r="K18" s="216"/>
+      <c r="L18" s="216"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -26551,23 +26659,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="215"/>
-      <c r="C25" s="215"/>
+      <c r="B25" s="217"/>
+      <c r="C25" s="217"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="122"/>
-      <c r="C26" s="211" t="s">
+      <c r="C26" s="216" t="s">
         <v>302</v>
       </c>
-      <c r="D26" s="211"/>
-      <c r="E26" s="211"/>
-      <c r="F26" s="211"/>
-      <c r="G26" s="211"/>
-      <c r="H26" s="211"/>
-      <c r="I26" s="211"/>
-      <c r="J26" s="211"/>
-      <c r="K26" s="211"/>
-      <c r="L26" s="211"/>
+      <c r="D26" s="216"/>
+      <c r="E26" s="216"/>
+      <c r="F26" s="216"/>
+      <c r="G26" s="216"/>
+      <c r="H26" s="216"/>
+      <c r="I26" s="216"/>
+      <c r="J26" s="216"/>
+      <c r="K26" s="216"/>
+      <c r="L26" s="216"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
@@ -26759,18 +26867,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="122"/>
-      <c r="C33" s="211" t="s">
+      <c r="C33" s="216" t="s">
         <v>305</v>
       </c>
-      <c r="D33" s="211"/>
-      <c r="E33" s="211"/>
-      <c r="F33" s="211"/>
-      <c r="G33" s="211"/>
-      <c r="H33" s="211"/>
-      <c r="I33" s="211"/>
-      <c r="J33" s="211"/>
-      <c r="K33" s="211"/>
-      <c r="L33" s="211"/>
+      <c r="D33" s="216"/>
+      <c r="E33" s="216"/>
+      <c r="F33" s="216"/>
+      <c r="G33" s="216"/>
+      <c r="H33" s="216"/>
+      <c r="I33" s="216"/>
+      <c r="J33" s="216"/>
+      <c r="K33" s="216"/>
+      <c r="L33" s="216"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
@@ -26822,23 +26930,23 @@
         <v>306</v>
       </c>
       <c r="C35" s="127">
-        <f>Statements!H54</f>
+        <f>Statements!H55</f>
         <v>-4911</v>
       </c>
       <c r="D35" s="127">
-        <f>Statements!I54</f>
+        <f>Statements!I55</f>
         <v>1200</v>
       </c>
       <c r="E35" s="127">
-        <f>Statements!J54</f>
+        <f>Statements!J55</f>
         <v>-6577</v>
       </c>
       <c r="F35" s="127">
-        <f>Statements!K54</f>
+        <f>Statements!K55</f>
         <v>3651</v>
       </c>
       <c r="G35" s="128">
-        <f>Statements!L54</f>
+        <f>Statements!L55</f>
         <v>-25000</v>
       </c>
       <c r="H35" s="34">
@@ -26954,18 +27062,18 @@
       <c r="C39" s="131"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="211" t="s">
+      <c r="C40" s="216" t="s">
         <v>308</v>
       </c>
-      <c r="D40" s="211"/>
-      <c r="E40" s="211"/>
-      <c r="F40" s="211"/>
-      <c r="G40" s="211"/>
-      <c r="H40" s="211"/>
-      <c r="I40" s="211"/>
-      <c r="J40" s="211"/>
-      <c r="K40" s="211"/>
-      <c r="L40" s="211"/>
+      <c r="D40" s="216"/>
+      <c r="E40" s="216"/>
+      <c r="F40" s="216"/>
+      <c r="G40" s="216"/>
+      <c r="H40" s="216"/>
+      <c r="I40" s="216"/>
+      <c r="J40" s="216"/>
+      <c r="K40" s="216"/>
+      <c r="L40" s="216"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
@@ -27017,23 +27125,23 @@
         <v>36</v>
       </c>
       <c r="C42" s="127">
-        <f>Statements!H50</f>
+        <f>Statements!H51</f>
         <v>11284</v>
       </c>
       <c r="D42" s="127">
-        <f>Statements!I50</f>
+        <f>Statements!I51</f>
         <v>11104</v>
       </c>
       <c r="E42" s="127">
-        <f>Statements!J50</f>
+        <f>Statements!J51</f>
         <v>11519</v>
       </c>
       <c r="F42" s="127">
-        <f>Statements!K50</f>
+        <f>Statements!K51</f>
         <v>11445</v>
       </c>
       <c r="G42" s="128">
-        <f>Statements!L50</f>
+        <f>Statements!L51</f>
         <v>11698</v>
       </c>
       <c r="H42" s="34">
@@ -27147,23 +27255,23 @@
         <v>40</v>
       </c>
       <c r="C45" s="127">
-        <f>-Statements!H56</f>
+        <f>-Statements!H57</f>
         <v>11085</v>
       </c>
       <c r="D45" s="127">
-        <f>-Statements!I56</f>
+        <f>-Statements!I57</f>
         <v>10708</v>
       </c>
       <c r="E45" s="127">
-        <f>-Statements!J56</f>
+        <f>-Statements!J57</f>
         <v>10959</v>
       </c>
       <c r="F45" s="127">
-        <f>-Statements!K56</f>
+        <f>-Statements!K57</f>
         <v>9447</v>
       </c>
       <c r="G45" s="128">
-        <f>-Statements!L56</f>
+        <f>-Statements!L57</f>
         <v>12715</v>
       </c>
       <c r="H45" s="34">

--- a/AAPL.xlsx
+++ b/AAPL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD86634-215F-6E46-B728-67C9769C9DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F956880-9F09-E143-86D0-0F2E0407F153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="3" activeTab="9" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2116,9 +2116,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2129,6 +2126,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2257,15 +2257,15 @@
       <sheetData sheetId="0">
         <row r="10">
           <cell r="C10">
-            <v>43.9</v>
+            <v>44.16</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>280.25</v>
+            <v>287.46300000000002</v>
           </cell>
           <cell r="F17">
-            <v>1.0647</v>
+            <v>1.0612999999999999</v>
           </cell>
         </row>
       </sheetData>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$17</f>
-        <v>280.25</v>
+        <v>287.46300000000002</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="C11" s="93">
         <f>$C$3/'Statement Q'!$N$19</f>
-        <v>33.922653477462774</v>
+        <v>34.795745714868445</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="C12" s="93">
         <f>$C$3/Statements!W19</f>
-        <v>33.922653477462774</v>
+        <v>34.795745714868445</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="C13" s="98">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$17)</f>
-        <v>9.2106389082096936</v>
+        <v>9.4476998839275037</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="C15" s="20">
         <f>C3*'Statement Q'!N100</f>
-        <v>4116031.75</v>
+        <v>4221969.0810000002</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="C18" s="20">
         <f>C15+C17-C16</f>
-        <v>4054147.75</v>
+        <v>4160085.0810000002</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -3019,60 +3019,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="210" t="s">
+      <c r="C2" s="209" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="210"/>
-      <c r="E2" s="210"/>
-      <c r="F2" s="210"/>
-      <c r="G2" s="211"/>
-      <c r="H2" s="212" t="s">
+      <c r="D2" s="209"/>
+      <c r="E2" s="209"/>
+      <c r="F2" s="209"/>
+      <c r="G2" s="210"/>
+      <c r="H2" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="210"/>
-      <c r="J2" s="210"/>
-      <c r="K2" s="210"/>
-      <c r="L2" s="210"/>
-      <c r="S2" s="208"/>
-      <c r="T2" s="208"/>
-      <c r="U2" s="208"/>
-      <c r="V2" s="208"/>
-      <c r="W2" s="208"/>
-      <c r="X2" s="208"/>
-      <c r="Y2" s="208"/>
-      <c r="Z2" s="208"/>
-      <c r="AA2" s="208"/>
-      <c r="AB2" s="208"/>
-      <c r="AC2" s="208"/>
+      <c r="I2" s="209"/>
+      <c r="J2" s="209"/>
+      <c r="K2" s="209"/>
+      <c r="L2" s="209"/>
+      <c r="S2" s="212"/>
+      <c r="T2" s="212"/>
+      <c r="U2" s="212"/>
+      <c r="V2" s="212"/>
+      <c r="W2" s="212"/>
+      <c r="X2" s="212"/>
+      <c r="Y2" s="212"/>
+      <c r="Z2" s="212"/>
+      <c r="AA2" s="212"/>
+      <c r="AB2" s="212"/>
+      <c r="AC2" s="212"/>
       <c r="AE2" s="122"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="208" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="209"/>
-      <c r="E4" s="209"/>
-      <c r="F4" s="209"/>
-      <c r="G4" s="209"/>
-      <c r="H4" s="209"/>
-      <c r="I4" s="209"/>
-      <c r="J4" s="209"/>
-      <c r="K4" s="209"/>
-      <c r="L4" s="209"/>
-      <c r="S4" s="208"/>
-      <c r="T4" s="208"/>
-      <c r="U4" s="208"/>
-      <c r="V4" s="208"/>
-      <c r="W4" s="208"/>
-      <c r="X4" s="208"/>
-      <c r="Y4" s="208"/>
-      <c r="Z4" s="208"/>
-      <c r="AA4" s="208"/>
-      <c r="AB4" s="208"/>
-      <c r="AC4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
+      <c r="L4" s="208"/>
+      <c r="S4" s="212"/>
+      <c r="T4" s="212"/>
+      <c r="U4" s="212"/>
+      <c r="V4" s="212"/>
+      <c r="W4" s="212"/>
+      <c r="X4" s="212"/>
+      <c r="Y4" s="212"/>
+      <c r="Z4" s="212"/>
+      <c r="AA4" s="212"/>
+      <c r="AB4" s="212"/>
+      <c r="AC4" s="212"/>
       <c r="AE4" s="123"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -3557,18 +3557,18 @@
       <c r="AE12" s="104"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C15" s="209" t="s">
+      <c r="C15" s="208" t="s">
         <v>141</v>
       </c>
-      <c r="D15" s="209"/>
-      <c r="E15" s="209"/>
-      <c r="F15" s="209"/>
-      <c r="G15" s="209"/>
-      <c r="H15" s="209"/>
-      <c r="I15" s="209"/>
-      <c r="J15" s="209"/>
-      <c r="K15" s="209"/>
-      <c r="L15" s="209"/>
+      <c r="D15" s="208"/>
+      <c r="E15" s="208"/>
+      <c r="F15" s="208"/>
+      <c r="G15" s="208"/>
+      <c r="H15" s="208"/>
+      <c r="I15" s="208"/>
+      <c r="J15" s="208"/>
+      <c r="K15" s="208"/>
+      <c r="L15" s="208"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C16" s="62">
@@ -3653,18 +3653,18 @@
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C20" s="209" t="s">
+      <c r="C20" s="208" t="s">
         <v>312</v>
       </c>
-      <c r="D20" s="209"/>
-      <c r="E20" s="209"/>
-      <c r="F20" s="209"/>
-      <c r="G20" s="209"/>
-      <c r="H20" s="209"/>
-      <c r="I20" s="209"/>
-      <c r="J20" s="209"/>
-      <c r="K20" s="209"/>
-      <c r="L20" s="209"/>
+      <c r="D20" s="208"/>
+      <c r="E20" s="208"/>
+      <c r="F20" s="208"/>
+      <c r="G20" s="208"/>
+      <c r="H20" s="208"/>
+      <c r="I20" s="208"/>
+      <c r="J20" s="208"/>
+      <c r="K20" s="208"/>
+      <c r="L20" s="208"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
@@ -3856,18 +3856,18 @@
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="209" t="s">
+      <c r="C27" s="208" t="s">
         <v>144</v>
       </c>
-      <c r="D27" s="209"/>
-      <c r="E27" s="209"/>
-      <c r="F27" s="209"/>
-      <c r="G27" s="209"/>
-      <c r="H27" s="209"/>
-      <c r="I27" s="209"/>
-      <c r="J27" s="209"/>
-      <c r="K27" s="209"/>
-      <c r="L27" s="209"/>
+      <c r="D27" s="208"/>
+      <c r="E27" s="208"/>
+      <c r="F27" s="208"/>
+      <c r="G27" s="208"/>
+      <c r="H27" s="208"/>
+      <c r="I27" s="208"/>
+      <c r="J27" s="208"/>
+      <c r="K27" s="208"/>
+      <c r="L27" s="208"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
@@ -4074,10 +4074,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="210" t="s">
+      <c r="B4" s="209" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="210"/>
+      <c r="C4" s="209"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="C6" s="145">
         <f>Overview!C3</f>
-        <v>280.25</v>
+        <v>287.46300000000002</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="C7" s="147">
         <f>C5*C6</f>
-        <v>4116031.75</v>
+        <v>4221969.0810000002</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="C9" s="170">
         <f>[1]Sheet1!$C$10/1000</f>
-        <v>4.3900000000000002E-2</v>
+        <v>4.4159999999999998E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="C10" s="145">
         <f>[1]Sheet1!$F$17</f>
-        <v>1.0647</v>
+        <v>1.0612999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4159,10 +4159,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="210" t="s">
+      <c r="B15" s="209" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="210"/>
+      <c r="C15" s="209"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="C16" s="148">
         <f>C8/(C8+C7)</f>
-        <v>2.0165719502818875E-2</v>
+        <v>1.9669675575328623E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C17" s="148">
         <f>C7/(C8+C7)</f>
-        <v>0.97983428049718113</v>
+        <v>0.98033032442467138</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="C19" s="148">
         <f>C9+C10*C11</f>
-        <v>9.7134999999999999E-2</v>
+        <v>9.7225000000000006E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="C20" s="148">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>9.5893094164418893E-2</v>
+        <v>9.6011872758891614E-2</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4260,60 +4260,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="210" t="s">
+      <c r="C3" s="209" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="210"/>
-      <c r="E3" s="210"/>
-      <c r="F3" s="210"/>
-      <c r="G3" s="211"/>
-      <c r="H3" s="212" t="s">
+      <c r="D3" s="209"/>
+      <c r="E3" s="209"/>
+      <c r="F3" s="209"/>
+      <c r="G3" s="210"/>
+      <c r="H3" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="210"/>
-      <c r="J3" s="210"/>
-      <c r="K3" s="210"/>
-      <c r="L3" s="210"/>
-      <c r="P3" s="208"/>
-      <c r="Q3" s="208"/>
-      <c r="R3" s="208"/>
-      <c r="S3" s="208"/>
-      <c r="T3" s="208"/>
-      <c r="U3" s="208"/>
-      <c r="V3" s="208"/>
-      <c r="W3" s="208"/>
-      <c r="X3" s="208"/>
-      <c r="Y3" s="208"/>
-      <c r="Z3" s="208"/>
+      <c r="I3" s="209"/>
+      <c r="J3" s="209"/>
+      <c r="K3" s="209"/>
+      <c r="L3" s="209"/>
+      <c r="P3" s="212"/>
+      <c r="Q3" s="212"/>
+      <c r="R3" s="212"/>
+      <c r="S3" s="212"/>
+      <c r="T3" s="212"/>
+      <c r="U3" s="212"/>
+      <c r="V3" s="212"/>
+      <c r="W3" s="212"/>
+      <c r="X3" s="212"/>
+      <c r="Y3" s="212"/>
+      <c r="Z3" s="212"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="209" t="s">
+      <c r="C5" s="208" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="209"/>
-      <c r="E5" s="209"/>
-      <c r="F5" s="209"/>
-      <c r="G5" s="209"/>
-      <c r="H5" s="209"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="209"/>
-      <c r="K5" s="209"/>
-      <c r="L5" s="209"/>
-      <c r="P5" s="208"/>
-      <c r="Q5" s="208"/>
-      <c r="R5" s="208"/>
-      <c r="S5" s="208"/>
-      <c r="T5" s="208"/>
-      <c r="U5" s="208"/>
-      <c r="V5" s="208"/>
-      <c r="W5" s="208"/>
-      <c r="X5" s="208"/>
-      <c r="Y5" s="208"/>
-      <c r="Z5" s="208"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="208"/>
+      <c r="I5" s="208"/>
+      <c r="J5" s="208"/>
+      <c r="K5" s="208"/>
+      <c r="L5" s="208"/>
+      <c r="P5" s="212"/>
+      <c r="Q5" s="212"/>
+      <c r="R5" s="212"/>
+      <c r="S5" s="212"/>
+      <c r="T5" s="212"/>
+      <c r="U5" s="212"/>
+      <c r="V5" s="212"/>
+      <c r="W5" s="212"/>
+      <c r="X5" s="212"/>
+      <c r="Y5" s="212"/>
+      <c r="Z5" s="212"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -4559,10 +4559,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="210" t="s">
+      <c r="B13" s="209" t="s">
         <v>180</v>
       </c>
-      <c r="C13" s="210"/>
+      <c r="C13" s="209"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -4582,10 +4582,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="210" t="s">
+      <c r="B18" s="209" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="210"/>
+      <c r="C18" s="209"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -4699,37 +4699,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="210" t="s">
+      <c r="C2" s="209" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="210"/>
-      <c r="E2" s="210"/>
-      <c r="F2" s="210"/>
-      <c r="G2" s="211"/>
-      <c r="H2" s="212" t="s">
+      <c r="D2" s="209"/>
+      <c r="E2" s="209"/>
+      <c r="F2" s="209"/>
+      <c r="G2" s="210"/>
+      <c r="H2" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="210"/>
-      <c r="J2" s="210"/>
-      <c r="K2" s="210"/>
-      <c r="L2" s="210"/>
+      <c r="I2" s="209"/>
+      <c r="J2" s="209"/>
+      <c r="K2" s="209"/>
+      <c r="L2" s="209"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="208" t="s">
         <v>316</v>
       </c>
-      <c r="D4" s="209"/>
-      <c r="E4" s="209"/>
-      <c r="F4" s="209"/>
-      <c r="G4" s="209"/>
-      <c r="H4" s="209"/>
-      <c r="I4" s="209"/>
-      <c r="J4" s="209"/>
-      <c r="K4" s="209"/>
-      <c r="L4" s="209"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
+      <c r="L4" s="208"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -4918,18 +4918,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="209" t="s">
+      <c r="C10" s="208" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="209"/>
-      <c r="E10" s="209"/>
-      <c r="F10" s="209"/>
-      <c r="G10" s="209"/>
-      <c r="H10" s="209"/>
-      <c r="I10" s="209"/>
-      <c r="J10" s="209"/>
-      <c r="K10" s="209"/>
-      <c r="L10" s="209"/>
+      <c r="D10" s="208"/>
+      <c r="E10" s="208"/>
+      <c r="F10" s="208"/>
+      <c r="G10" s="208"/>
+      <c r="H10" s="208"/>
+      <c r="I10" s="208"/>
+      <c r="J10" s="208"/>
+      <c r="K10" s="208"/>
+      <c r="L10" s="208"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5111,18 +5111,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="209" t="s">
+      <c r="C16" s="208" t="s">
         <v>216</v>
       </c>
-      <c r="D16" s="209"/>
-      <c r="E16" s="209"/>
-      <c r="F16" s="209"/>
-      <c r="G16" s="209"/>
-      <c r="H16" s="209"/>
-      <c r="I16" s="209"/>
-      <c r="J16" s="209"/>
-      <c r="K16" s="209"/>
-      <c r="L16" s="209"/>
+      <c r="D16" s="208"/>
+      <c r="E16" s="208"/>
+      <c r="F16" s="208"/>
+      <c r="G16" s="208"/>
+      <c r="H16" s="208"/>
+      <c r="I16" s="208"/>
+      <c r="J16" s="208"/>
+      <c r="K16" s="208"/>
+      <c r="L16" s="208"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -5256,18 +5256,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="209" t="s">
+      <c r="C21" s="208" t="s">
         <v>317</v>
       </c>
-      <c r="D21" s="209"/>
-      <c r="E21" s="209"/>
-      <c r="F21" s="209"/>
-      <c r="G21" s="209"/>
-      <c r="H21" s="209"/>
-      <c r="I21" s="209"/>
-      <c r="J21" s="209"/>
-      <c r="K21" s="209"/>
-      <c r="L21" s="209"/>
+      <c r="D21" s="208"/>
+      <c r="E21" s="208"/>
+      <c r="F21" s="208"/>
+      <c r="G21" s="208"/>
+      <c r="H21" s="208"/>
+      <c r="I21" s="208"/>
+      <c r="J21" s="208"/>
+      <c r="K21" s="208"/>
+      <c r="L21" s="208"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -5351,18 +5351,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="209" t="s">
+      <c r="C26" s="208" t="s">
         <v>318</v>
       </c>
-      <c r="D26" s="209"/>
-      <c r="E26" s="209"/>
-      <c r="F26" s="209"/>
-      <c r="G26" s="209"/>
-      <c r="H26" s="209"/>
-      <c r="I26" s="209"/>
-      <c r="J26" s="209"/>
-      <c r="K26" s="209"/>
-      <c r="L26" s="209"/>
+      <c r="D26" s="208"/>
+      <c r="E26" s="208"/>
+      <c r="F26" s="208"/>
+      <c r="G26" s="208"/>
+      <c r="H26" s="208"/>
+      <c r="I26" s="208"/>
+      <c r="J26" s="208"/>
+      <c r="K26" s="208"/>
+      <c r="L26" s="208"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -5632,10 +5632,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="210" t="s">
+      <c r="B37" s="209" t="s">
         <v>322</v>
       </c>
-      <c r="C37" s="210"/>
+      <c r="C37" s="209"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -5701,10 +5701,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="210" t="s">
+      <c r="B46" s="209" t="s">
         <v>192</v>
       </c>
-      <c r="C46" s="210"/>
+      <c r="C46" s="209"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -5760,10 +5760,10 @@
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="210" t="s">
+      <c r="B54" s="209" t="s">
         <v>326</v>
       </c>
-      <c r="C54" s="210"/>
+      <c r="C54" s="209"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -5873,10 +5873,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="210" t="s">
+      <c r="B4" s="209" t="s">
         <v>200</v>
       </c>
-      <c r="C4" s="210"/>
+      <c r="C4" s="209"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C10" s="35">
         <f>Overview!C3</f>
-        <v>280.25</v>
+        <v>287.46300000000002</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="C11" s="89">
         <f>(C9-C10)/C10</f>
-        <v>-0.27269616639149274</v>
+        <v>-0.29094561954483139</v>
       </c>
     </row>
   </sheetData>
@@ -5983,60 +5983,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="210" t="s">
+      <c r="C3" s="209" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="210"/>
-      <c r="E3" s="210"/>
-      <c r="F3" s="210"/>
-      <c r="G3" s="211"/>
-      <c r="H3" s="212" t="s">
+      <c r="D3" s="209"/>
+      <c r="E3" s="209"/>
+      <c r="F3" s="209"/>
+      <c r="G3" s="210"/>
+      <c r="H3" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="210"/>
-      <c r="J3" s="210"/>
-      <c r="K3" s="210"/>
-      <c r="L3" s="210"/>
-      <c r="P3" s="208"/>
-      <c r="Q3" s="208"/>
-      <c r="R3" s="208"/>
-      <c r="S3" s="208"/>
-      <c r="T3" s="208"/>
-      <c r="U3" s="208"/>
-      <c r="V3" s="208"/>
-      <c r="W3" s="208"/>
-      <c r="X3" s="208"/>
-      <c r="Y3" s="208"/>
-      <c r="Z3" s="208"/>
+      <c r="I3" s="209"/>
+      <c r="J3" s="209"/>
+      <c r="K3" s="209"/>
+      <c r="L3" s="209"/>
+      <c r="P3" s="212"/>
+      <c r="Q3" s="212"/>
+      <c r="R3" s="212"/>
+      <c r="S3" s="212"/>
+      <c r="T3" s="212"/>
+      <c r="U3" s="212"/>
+      <c r="V3" s="212"/>
+      <c r="W3" s="212"/>
+      <c r="X3" s="212"/>
+      <c r="Y3" s="212"/>
+      <c r="Z3" s="212"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="209" t="s">
+      <c r="C5" s="208" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="209"/>
-      <c r="E5" s="209"/>
-      <c r="F5" s="209"/>
-      <c r="G5" s="209"/>
-      <c r="H5" s="209"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="209"/>
-      <c r="K5" s="209"/>
-      <c r="L5" s="209"/>
-      <c r="P5" s="208"/>
-      <c r="Q5" s="208"/>
-      <c r="R5" s="208"/>
-      <c r="S5" s="208"/>
-      <c r="T5" s="208"/>
-      <c r="U5" s="208"/>
-      <c r="V5" s="208"/>
-      <c r="W5" s="208"/>
-      <c r="X5" s="208"/>
-      <c r="Y5" s="208"/>
-      <c r="Z5" s="208"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="208"/>
+      <c r="I5" s="208"/>
+      <c r="J5" s="208"/>
+      <c r="K5" s="208"/>
+      <c r="L5" s="208"/>
+      <c r="P5" s="212"/>
+      <c r="Q5" s="212"/>
+      <c r="R5" s="212"/>
+      <c r="S5" s="212"/>
+      <c r="T5" s="212"/>
+      <c r="U5" s="212"/>
+      <c r="V5" s="212"/>
+      <c r="W5" s="212"/>
+      <c r="X5" s="212"/>
+      <c r="Y5" s="212"/>
+      <c r="Z5" s="212"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="C15" s="194">
         <f>Overview!C3</f>
-        <v>280.25</v>
+        <v>287.46300000000002</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="C23" s="200">
         <f>C15*C22</f>
-        <v>4116031.75</v>
+        <v>4221969.0810000002</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="C26" s="201">
         <f>C23+C25-C24</f>
-        <v>4054147.75</v>
+        <v>4160085.0810000002</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6452,18 +6452,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="209" t="s">
+      <c r="C39" s="208" t="s">
         <v>338</v>
       </c>
-      <c r="D39" s="209"/>
-      <c r="E39" s="209"/>
-      <c r="F39" s="209"/>
-      <c r="G39" s="209"/>
-      <c r="H39" s="209"/>
-      <c r="I39" s="209"/>
-      <c r="J39" s="209"/>
-      <c r="K39" s="209"/>
-      <c r="L39" s="209"/>
+      <c r="D39" s="208"/>
+      <c r="E39" s="208"/>
+      <c r="F39" s="208"/>
+      <c r="G39" s="208"/>
+      <c r="H39" s="208"/>
+      <c r="I39" s="208"/>
+      <c r="J39" s="208"/>
+      <c r="K39" s="208"/>
+      <c r="L39" s="208"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="62">
@@ -6895,17 +6895,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -13587,7 +13587,7 @@
         <v>18379</v>
       </c>
       <c r="J10" s="20">
-        <f t="shared" ref="C10:J10" si="7">SUM(J8:J9)</f>
+        <f t="shared" ref="J10" si="7">SUM(J8:J9)</f>
         <v>18896</v>
       </c>
       <c r="K10" s="20"/>
@@ -14477,7 +14477,7 @@
         <v>221193</v>
       </c>
       <c r="J32" s="56">
-        <f t="shared" ref="C32:J32" si="10">SUM(J29:J31)</f>
+        <f t="shared" ref="J32" si="10">SUM(J29:J31)</f>
         <v>226968</v>
       </c>
       <c r="K32" s="21"/>
@@ -14820,7 +14820,7 @@
         <v>28</v>
       </c>
       <c r="C42" s="56">
-        <f t="shared" ref="C42:I42" si="11">SUM(C40:C41)</f>
+        <f t="shared" ref="C42:H42" si="11">SUM(C40:C41)</f>
         <v>133280</v>
       </c>
       <c r="D42" s="56">
@@ -15128,7 +15128,7 @@
         <v>42097</v>
       </c>
       <c r="J51" s="20">
-        <f t="shared" ref="C51:J51" si="14">J15</f>
+        <f t="shared" ref="J51" si="14">J15</f>
         <v>29578</v>
       </c>
       <c r="K51" s="20"/>
@@ -16066,7 +16066,7 @@
         <v>42097</v>
       </c>
       <c r="J81" s="20">
-        <f t="shared" ref="C81:J81" si="17">J5-J6-J10+J12+J14</f>
+        <f t="shared" ref="J81" si="17">J5-J6-J10+J12+J14</f>
         <v>29578</v>
       </c>
       <c r="K81" s="20"/>
@@ -16107,7 +16107,7 @@
         <v>0</v>
       </c>
       <c r="J82" s="24">
-        <f t="shared" ref="C82:J82" si="19">J15-J81</f>
+        <f t="shared" ref="J82" si="19">J15-J81</f>
         <v>0</v>
       </c>
       <c r="K82" s="26"/>
@@ -16149,7 +16149,7 @@
         <v>379297</v>
       </c>
       <c r="J83" s="20">
-        <f t="shared" ref="C83:J83" si="21">SUM(J22:J27)+SUM(J29:J31)</f>
+        <f t="shared" ref="J83" si="21">SUM(J22:J27)+SUM(J29:J31)</f>
         <v>371082</v>
       </c>
       <c r="K83" s="20"/>
@@ -16189,7 +16189,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="23">
-        <f t="shared" ref="C84:J84" si="23">J33-J83</f>
+        <f t="shared" ref="J84" si="23">J33-J83</f>
         <v>0</v>
       </c>
       <c r="K84" s="26"/>
@@ -16229,7 +16229,7 @@
         <v>291107</v>
       </c>
       <c r="J85" s="20">
-        <f t="shared" ref="C85:J85" si="25">SUM(J34:J38)+SUM(J40:J41)</f>
+        <f t="shared" ref="J85" si="25">SUM(J34:J38)+SUM(J40:J41)</f>
         <v>264591</v>
       </c>
       <c r="K85" s="20"/>
@@ -16269,7 +16269,7 @@
         <v>0</v>
       </c>
       <c r="J86" s="23">
-        <f t="shared" ref="C86:J86" si="27">J43-J85</f>
+        <f t="shared" ref="J86" si="27">J43-J85</f>
         <v>0</v>
       </c>
       <c r="K86" s="26"/>
@@ -16309,7 +16309,7 @@
         <v>88190</v>
       </c>
       <c r="J87" s="20">
-        <f t="shared" ref="C87:J87" si="29">SUM(J44:J46)</f>
+        <f t="shared" ref="J87" si="29">SUM(J44:J46)</f>
         <v>106491</v>
       </c>
       <c r="K87" s="20"/>
@@ -16349,7 +16349,7 @@
         <v>0</v>
       </c>
       <c r="J88" s="23">
-        <f t="shared" ref="C88:J88" si="31">J47-J87</f>
+        <f t="shared" ref="J88" si="31">J47-J87</f>
         <v>0</v>
       </c>
       <c r="K88" s="26"/>
@@ -16390,7 +16390,7 @@
         <v>0</v>
       </c>
       <c r="J89" s="22">
-        <f t="shared" ref="C89:J89" si="33">J33-(J43+J47)</f>
+        <f t="shared" ref="J89" si="33">J33-(J43+J47)</f>
         <v>0</v>
       </c>
       <c r="K89" s="26"/>
@@ -16432,7 +16432,7 @@
         <v>53925</v>
       </c>
       <c r="J90" s="20">
-        <f t="shared" ref="C90:J90" si="35">SUM(J51:J60)</f>
+        <f t="shared" ref="J90" si="35">SUM(J51:J60)</f>
         <v>28702</v>
       </c>
       <c r="K90" s="20"/>
@@ -16472,7 +16472,7 @@
         <v>0</v>
       </c>
       <c r="J91" s="23">
-        <f t="shared" ref="C91:J91" si="37">J61-J90</f>
+        <f t="shared" ref="J91" si="37">J61-J90</f>
         <v>0</v>
       </c>
       <c r="K91" s="26"/>
@@ -16512,7 +16512,7 @@
         <v>-4886</v>
       </c>
       <c r="J92" s="20">
-        <f t="shared" ref="C92:J92" si="39">SUM(J62:J66)</f>
+        <f t="shared" ref="J92" si="39">SUM(J62:J66)</f>
         <v>-6168</v>
       </c>
       <c r="K92" s="20"/>
@@ -16552,7 +16552,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="23">
-        <f t="shared" ref="C93:J93" si="41">J67-J92</f>
+        <f t="shared" ref="J93" si="41">J67-J92</f>
         <v>0</v>
       </c>
       <c r="K93" s="26"/>
@@ -16592,7 +16592,7 @@
         <v>-39656</v>
       </c>
       <c r="J94" s="20">
-        <f t="shared" ref="C94:J94" si="43">SUM(J68:J74)</f>
+        <f t="shared" ref="J94" si="43">SUM(J68:J74)</f>
         <v>-22279</v>
       </c>
       <c r="K94" s="20"/>
@@ -16604,7 +16604,7 @@
         <v>60</v>
       </c>
       <c r="C95" s="23">
-        <f t="shared" ref="C95:I95" si="44">C75-C94</f>
+        <f t="shared" ref="C95:H95" si="44">C75-C94</f>
         <v>0</v>
       </c>
       <c r="D95" s="23">
@@ -16672,7 +16672,7 @@
         <v>45317</v>
       </c>
       <c r="J96" s="20">
-        <f t="shared" ref="C96:J96" si="47">J61+J67+J75+J77</f>
+        <f t="shared" ref="J96" si="47">J61+J67+J75+J77</f>
         <v>45572</v>
       </c>
       <c r="K96" s="20"/>
@@ -16685,7 +16685,7 @@
         <v>61</v>
       </c>
       <c r="C97" s="22">
-        <f t="shared" ref="C97:I97" si="48">C78-C96</f>
+        <f t="shared" ref="C97:H97" si="48">C78-C96</f>
         <v>0</v>
       </c>
       <c r="D97" s="22">
@@ -16913,7 +16913,7 @@
         <v>111184</v>
       </c>
       <c r="J107" s="34">
-        <f t="shared" ref="C107:J107" si="57">K5</f>
+        <f t="shared" ref="J107" si="57">K5</f>
         <v>0</v>
       </c>
     </row>
@@ -16950,7 +16950,7 @@
         <v>BEAT</v>
       </c>
       <c r="J108" s="64" t="str">
-        <f t="shared" ref="C108:J108" si="65">IF(K5&gt;J106, "BEAT", IF(K5&lt;J105, "MISSED", "MET"))</f>
+        <f t="shared" ref="J108" si="65">IF(K5&gt;J106, "BEAT", IF(K5&lt;J105, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
     </row>
@@ -23495,36 +23495,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="210" t="s">
+      <c r="C2" s="209" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="210"/>
-      <c r="E2" s="210"/>
-      <c r="F2" s="210"/>
-      <c r="G2" s="211"/>
-      <c r="H2" s="212" t="s">
+      <c r="D2" s="209"/>
+      <c r="E2" s="209"/>
+      <c r="F2" s="209"/>
+      <c r="G2" s="210"/>
+      <c r="H2" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="210"/>
-      <c r="J2" s="210"/>
-      <c r="K2" s="210"/>
-      <c r="L2" s="210"/>
+      <c r="I2" s="209"/>
+      <c r="J2" s="209"/>
+      <c r="K2" s="209"/>
+      <c r="L2" s="209"/>
       <c r="O2" s="90"/>
-      <c r="S2" s="210" t="s">
+      <c r="S2" s="209" t="s">
         <v>104</v>
       </c>
-      <c r="T2" s="210"/>
-      <c r="U2" s="210"/>
-      <c r="V2" s="210"/>
-      <c r="W2" s="210"/>
-      <c r="X2" s="210"/>
-      <c r="Y2" s="210"/>
-      <c r="Z2" s="210"/>
-      <c r="AA2" s="210" t="s">
+      <c r="T2" s="209"/>
+      <c r="U2" s="209"/>
+      <c r="V2" s="209"/>
+      <c r="W2" s="209"/>
+      <c r="X2" s="209"/>
+      <c r="Y2" s="209"/>
+      <c r="Z2" s="209"/>
+      <c r="AA2" s="209" t="s">
         <v>105</v>
       </c>
-      <c r="AB2" s="210"/>
-      <c r="AC2" s="210"/>
+      <c r="AB2" s="209"/>
+      <c r="AC2" s="209"/>
       <c r="AE2" s="117" t="s">
         <v>74</v>
       </c>
@@ -23535,18 +23535,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="208" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="209"/>
-      <c r="E4" s="209"/>
-      <c r="F4" s="209"/>
-      <c r="G4" s="209"/>
-      <c r="H4" s="209"/>
-      <c r="I4" s="209"/>
-      <c r="J4" s="209"/>
-      <c r="K4" s="209"/>
-      <c r="L4" s="209"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
+      <c r="L4" s="208"/>
       <c r="O4" s="90"/>
       <c r="S4" s="216" t="s">
         <v>113</v>
@@ -24236,18 +24236,18 @@
       <c r="Q12" s="91"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="209" t="s">
+      <c r="C13" s="208" t="s">
         <v>115</v>
       </c>
-      <c r="D13" s="209"/>
-      <c r="E13" s="209"/>
-      <c r="F13" s="209"/>
-      <c r="G13" s="209"/>
-      <c r="H13" s="209"/>
-      <c r="I13" s="209"/>
-      <c r="J13" s="209"/>
-      <c r="K13" s="209"/>
-      <c r="L13" s="209"/>
+      <c r="D13" s="208"/>
+      <c r="E13" s="208"/>
+      <c r="F13" s="208"/>
+      <c r="G13" s="208"/>
+      <c r="H13" s="208"/>
+      <c r="I13" s="208"/>
+      <c r="J13" s="208"/>
+      <c r="K13" s="208"/>
+      <c r="L13" s="208"/>
       <c r="O13" s="90"/>
       <c r="Q13" s="91"/>
       <c r="S13" s="216" t="s">
@@ -24844,35 +24844,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="210" t="s">
+      <c r="C2" s="209" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="210"/>
-      <c r="E2" s="210"/>
-      <c r="F2" s="210"/>
-      <c r="G2" s="211"/>
-      <c r="H2" s="212" t="s">
+      <c r="D2" s="209"/>
+      <c r="E2" s="209"/>
+      <c r="F2" s="209"/>
+      <c r="G2" s="210"/>
+      <c r="H2" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="210"/>
-      <c r="J2" s="210"/>
-      <c r="K2" s="210"/>
-      <c r="L2" s="210"/>
-      <c r="P2" s="210" t="s">
+      <c r="I2" s="209"/>
+      <c r="J2" s="209"/>
+      <c r="K2" s="209"/>
+      <c r="L2" s="209"/>
+      <c r="P2" s="209" t="s">
         <v>104</v>
       </c>
-      <c r="Q2" s="210"/>
-      <c r="R2" s="210"/>
-      <c r="S2" s="210"/>
-      <c r="T2" s="210"/>
-      <c r="U2" s="210"/>
-      <c r="V2" s="210"/>
-      <c r="W2" s="210"/>
-      <c r="X2" s="210" t="s">
+      <c r="Q2" s="209"/>
+      <c r="R2" s="209"/>
+      <c r="S2" s="209"/>
+      <c r="T2" s="209"/>
+      <c r="U2" s="209"/>
+      <c r="V2" s="209"/>
+      <c r="W2" s="209"/>
+      <c r="X2" s="209" t="s">
         <v>105</v>
       </c>
-      <c r="Y2" s="210"/>
-      <c r="Z2" s="210"/>
+      <c r="Y2" s="209"/>
+      <c r="Z2" s="209"/>
       <c r="AB2" s="117" t="s">
         <v>74</v>
       </c>
@@ -24881,18 +24881,18 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="208" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="209"/>
-      <c r="E4" s="209"/>
-      <c r="F4" s="209"/>
-      <c r="G4" s="209"/>
-      <c r="H4" s="209"/>
-      <c r="I4" s="209"/>
-      <c r="J4" s="209"/>
-      <c r="K4" s="209"/>
-      <c r="L4" s="209"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
+      <c r="L4" s="208"/>
       <c r="P4" s="217" t="s">
         <v>113</v>
       </c>
@@ -25106,18 +25106,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="209" t="s">
+      <c r="C9" s="208" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="209"/>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="209"/>
-      <c r="H9" s="209"/>
-      <c r="I9" s="209"/>
-      <c r="J9" s="209"/>
-      <c r="K9" s="209"/>
-      <c r="L9" s="209"/>
+      <c r="D9" s="208"/>
+      <c r="E9" s="208"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
+      <c r="H9" s="208"/>
+      <c r="I9" s="208"/>
+      <c r="J9" s="208"/>
+      <c r="K9" s="208"/>
+      <c r="L9" s="208"/>
       <c r="N9" s="91"/>
       <c r="P9" s="217" t="s">
         <v>127</v>
@@ -25601,18 +25601,18 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="209" t="s">
+      <c r="C17" s="208" t="s">
         <v>125</v>
       </c>
-      <c r="D17" s="209"/>
-      <c r="E17" s="209"/>
-      <c r="F17" s="209"/>
-      <c r="G17" s="209"/>
-      <c r="H17" s="209"/>
-      <c r="I17" s="209"/>
-      <c r="J17" s="209"/>
-      <c r="K17" s="209"/>
-      <c r="L17" s="209"/>
+      <c r="D17" s="208"/>
+      <c r="E17" s="208"/>
+      <c r="F17" s="208"/>
+      <c r="G17" s="208"/>
+      <c r="H17" s="208"/>
+      <c r="I17" s="208"/>
+      <c r="J17" s="208"/>
+      <c r="K17" s="208"/>
+      <c r="L17" s="208"/>
       <c r="P17" s="217" t="s">
         <v>125</v>
       </c>
@@ -26015,60 +26015,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="210" t="s">
+      <c r="C3" s="209" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="210"/>
-      <c r="E3" s="210"/>
-      <c r="F3" s="210"/>
-      <c r="G3" s="211"/>
-      <c r="H3" s="212" t="s">
+      <c r="D3" s="209"/>
+      <c r="E3" s="209"/>
+      <c r="F3" s="209"/>
+      <c r="G3" s="210"/>
+      <c r="H3" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="210"/>
-      <c r="J3" s="210"/>
-      <c r="K3" s="210"/>
-      <c r="L3" s="210"/>
-      <c r="P3" s="208"/>
-      <c r="Q3" s="208"/>
-      <c r="R3" s="208"/>
-      <c r="S3" s="208"/>
-      <c r="T3" s="208"/>
-      <c r="U3" s="208"/>
-      <c r="V3" s="208"/>
-      <c r="W3" s="208"/>
-      <c r="X3" s="208"/>
-      <c r="Y3" s="208"/>
-      <c r="Z3" s="208"/>
+      <c r="I3" s="209"/>
+      <c r="J3" s="209"/>
+      <c r="K3" s="209"/>
+      <c r="L3" s="209"/>
+      <c r="P3" s="212"/>
+      <c r="Q3" s="212"/>
+      <c r="R3" s="212"/>
+      <c r="S3" s="212"/>
+      <c r="T3" s="212"/>
+      <c r="U3" s="212"/>
+      <c r="V3" s="212"/>
+      <c r="W3" s="212"/>
+      <c r="X3" s="212"/>
+      <c r="Y3" s="212"/>
+      <c r="Z3" s="212"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="209" t="s">
+      <c r="C5" s="208" t="s">
         <v>113</v>
       </c>
-      <c r="D5" s="209"/>
-      <c r="E5" s="209"/>
-      <c r="F5" s="209"/>
-      <c r="G5" s="209"/>
-      <c r="H5" s="209"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="209"/>
-      <c r="K5" s="209"/>
-      <c r="L5" s="209"/>
-      <c r="P5" s="208"/>
-      <c r="Q5" s="208"/>
-      <c r="R5" s="208"/>
-      <c r="S5" s="208"/>
-      <c r="T5" s="208"/>
-      <c r="U5" s="208"/>
-      <c r="V5" s="208"/>
-      <c r="W5" s="208"/>
-      <c r="X5" s="208"/>
-      <c r="Y5" s="208"/>
-      <c r="Z5" s="208"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="208"/>
+      <c r="I5" s="208"/>
+      <c r="J5" s="208"/>
+      <c r="K5" s="208"/>
+      <c r="L5" s="208"/>
+      <c r="P5" s="212"/>
+      <c r="Q5" s="212"/>
+      <c r="R5" s="212"/>
+      <c r="S5" s="212"/>
+      <c r="T5" s="212"/>
+      <c r="U5" s="212"/>
+      <c r="V5" s="212"/>
+      <c r="W5" s="212"/>
+      <c r="X5" s="212"/>
+      <c r="Y5" s="212"/>
+      <c r="Z5" s="212"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -26254,30 +26254,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="209" t="s">
+      <c r="C11" s="208" t="s">
         <v>133</v>
       </c>
-      <c r="D11" s="209"/>
-      <c r="E11" s="209"/>
-      <c r="F11" s="209"/>
-      <c r="G11" s="209"/>
-      <c r="H11" s="209"/>
-      <c r="I11" s="209"/>
-      <c r="J11" s="209"/>
-      <c r="K11" s="209"/>
-      <c r="L11" s="209"/>
+      <c r="D11" s="208"/>
+      <c r="E11" s="208"/>
+      <c r="F11" s="208"/>
+      <c r="G11" s="208"/>
+      <c r="H11" s="208"/>
+      <c r="I11" s="208"/>
+      <c r="J11" s="208"/>
+      <c r="K11" s="208"/>
+      <c r="L11" s="208"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="208"/>
-      <c r="Q11" s="208"/>
-      <c r="R11" s="208"/>
-      <c r="S11" s="208"/>
-      <c r="T11" s="208"/>
-      <c r="U11" s="208"/>
-      <c r="V11" s="208"/>
-      <c r="W11" s="208"/>
-      <c r="X11" s="208"/>
-      <c r="Y11" s="208"/>
-      <c r="Z11" s="208"/>
+      <c r="P11" s="212"/>
+      <c r="Q11" s="212"/>
+      <c r="R11" s="212"/>
+      <c r="S11" s="212"/>
+      <c r="T11" s="212"/>
+      <c r="U11" s="212"/>
+      <c r="V11" s="212"/>
+      <c r="W11" s="212"/>
+      <c r="X11" s="212"/>
+      <c r="Y11" s="212"/>
+      <c r="Z11" s="212"/>
       <c r="AB11" s="123"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -26519,18 +26519,18 @@
       <c r="D16" s="20"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="209" t="s">
+      <c r="C18" s="208" t="s">
         <v>140</v>
       </c>
-      <c r="D18" s="209"/>
-      <c r="E18" s="209"/>
-      <c r="F18" s="209"/>
-      <c r="G18" s="209"/>
-      <c r="H18" s="209"/>
-      <c r="I18" s="209"/>
-      <c r="J18" s="209"/>
-      <c r="K18" s="209"/>
-      <c r="L18" s="209"/>
+      <c r="D18" s="208"/>
+      <c r="E18" s="208"/>
+      <c r="F18" s="208"/>
+      <c r="G18" s="208"/>
+      <c r="H18" s="208"/>
+      <c r="I18" s="208"/>
+      <c r="J18" s="208"/>
+      <c r="K18" s="208"/>
+      <c r="L18" s="208"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -26743,23 +26743,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="208"/>
-      <c r="C25" s="208"/>
+      <c r="B25" s="212"/>
+      <c r="C25" s="212"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="122"/>
-      <c r="C26" s="209" t="s">
+      <c r="C26" s="208" t="s">
         <v>300</v>
       </c>
-      <c r="D26" s="209"/>
-      <c r="E26" s="209"/>
-      <c r="F26" s="209"/>
-      <c r="G26" s="209"/>
-      <c r="H26" s="209"/>
-      <c r="I26" s="209"/>
-      <c r="J26" s="209"/>
-      <c r="K26" s="209"/>
-      <c r="L26" s="209"/>
+      <c r="D26" s="208"/>
+      <c r="E26" s="208"/>
+      <c r="F26" s="208"/>
+      <c r="G26" s="208"/>
+      <c r="H26" s="208"/>
+      <c r="I26" s="208"/>
+      <c r="J26" s="208"/>
+      <c r="K26" s="208"/>
+      <c r="L26" s="208"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
@@ -26951,18 +26951,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="122"/>
-      <c r="C33" s="209" t="s">
+      <c r="C33" s="208" t="s">
         <v>303</v>
       </c>
-      <c r="D33" s="209"/>
-      <c r="E33" s="209"/>
-      <c r="F33" s="209"/>
-      <c r="G33" s="209"/>
-      <c r="H33" s="209"/>
-      <c r="I33" s="209"/>
-      <c r="J33" s="209"/>
-      <c r="K33" s="209"/>
-      <c r="L33" s="209"/>
+      <c r="D33" s="208"/>
+      <c r="E33" s="208"/>
+      <c r="F33" s="208"/>
+      <c r="G33" s="208"/>
+      <c r="H33" s="208"/>
+      <c r="I33" s="208"/>
+      <c r="J33" s="208"/>
+      <c r="K33" s="208"/>
+      <c r="L33" s="208"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
@@ -27146,18 +27146,18 @@
       <c r="C39" s="131"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="209" t="s">
+      <c r="C40" s="208" t="s">
         <v>306</v>
       </c>
-      <c r="D40" s="209"/>
-      <c r="E40" s="209"/>
-      <c r="F40" s="209"/>
-      <c r="G40" s="209"/>
-      <c r="H40" s="209"/>
-      <c r="I40" s="209"/>
-      <c r="J40" s="209"/>
-      <c r="K40" s="209"/>
-      <c r="L40" s="209"/>
+      <c r="D40" s="208"/>
+      <c r="E40" s="208"/>
+      <c r="F40" s="208"/>
+      <c r="G40" s="208"/>
+      <c r="H40" s="208"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="208"/>
+      <c r="L40" s="208"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
@@ -27421,12 +27421,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -27434,6 +27428,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/AAPL.xlsx
+++ b/AAPL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F956880-9F09-E143-86D0-0F2E0407F153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1437D0F9-1C70-754B-8E30-581DA526B4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="15" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2116,21 +2116,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2140,10 +2125,25 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2255,17 +2255,22 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="8">
+          <cell r="C8">
+            <v>218.965</v>
+          </cell>
+        </row>
         <row r="10">
           <cell r="C10">
-            <v>44.16</v>
+            <v>43.92</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>287.46300000000002</v>
+            <v>292.48</v>
           </cell>
           <cell r="F17">
-            <v>1.0612999999999999</v>
+            <v>1.0644</v>
           </cell>
         </row>
       </sheetData>
@@ -2719,7 +2724,7 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$17</f>
-        <v>287.46300000000002</v>
+        <v>292.48</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2745,7 +2750,7 @@
       </c>
       <c r="C11" s="93">
         <f>$C$3/'Statement Q'!$N$19</f>
-        <v>34.795745714868445</v>
+        <v>35.403024760350803</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2754,7 +2759,7 @@
       </c>
       <c r="C12" s="93">
         <f>$C$3/Statements!W19</f>
-        <v>34.795745714868445</v>
+        <v>35.403024760350803</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2763,7 +2768,7 @@
       </c>
       <c r="C13" s="98">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$17)</f>
-        <v>9.4476998839275037</v>
+        <v>9.6125875749265699</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -2772,7 +2777,7 @@
       </c>
       <c r="C15" s="20">
         <f>C3*'Statement Q'!N100</f>
-        <v>4221969.0810000002</v>
+        <v>4295653.7600000007</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -2799,7 +2804,7 @@
       </c>
       <c r="C18" s="20">
         <f>C15+C17-C16</f>
-        <v>4160085.0810000002</v>
+        <v>4233769.7600000007</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -3019,60 +3024,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="209" t="s">
+      <c r="C2" s="211" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="209"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="209"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="211" t="s">
+      <c r="D2" s="211"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="215" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="209"/>
-      <c r="J2" s="209"/>
-      <c r="K2" s="209"/>
-      <c r="L2" s="209"/>
-      <c r="S2" s="212"/>
-      <c r="T2" s="212"/>
-      <c r="U2" s="212"/>
-      <c r="V2" s="212"/>
-      <c r="W2" s="212"/>
-      <c r="X2" s="212"/>
-      <c r="Y2" s="212"/>
-      <c r="Z2" s="212"/>
-      <c r="AA2" s="212"/>
-      <c r="AB2" s="212"/>
-      <c r="AC2" s="212"/>
+      <c r="I2" s="211"/>
+      <c r="J2" s="211"/>
+      <c r="K2" s="211"/>
+      <c r="L2" s="211"/>
+      <c r="S2" s="217"/>
+      <c r="T2" s="217"/>
+      <c r="U2" s="217"/>
+      <c r="V2" s="217"/>
+      <c r="W2" s="217"/>
+      <c r="X2" s="217"/>
+      <c r="Y2" s="217"/>
+      <c r="Z2" s="217"/>
+      <c r="AA2" s="217"/>
+      <c r="AB2" s="217"/>
+      <c r="AC2" s="217"/>
       <c r="AE2" s="122"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="208" t="s">
+      <c r="C4" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="208"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
-      <c r="I4" s="208"/>
-      <c r="J4" s="208"/>
-      <c r="K4" s="208"/>
-      <c r="L4" s="208"/>
-      <c r="S4" s="212"/>
-      <c r="T4" s="212"/>
-      <c r="U4" s="212"/>
-      <c r="V4" s="212"/>
-      <c r="W4" s="212"/>
-      <c r="X4" s="212"/>
-      <c r="Y4" s="212"/>
-      <c r="Z4" s="212"/>
-      <c r="AA4" s="212"/>
-      <c r="AB4" s="212"/>
-      <c r="AC4" s="212"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
+      <c r="S4" s="217"/>
+      <c r="T4" s="217"/>
+      <c r="U4" s="217"/>
+      <c r="V4" s="217"/>
+      <c r="W4" s="217"/>
+      <c r="X4" s="217"/>
+      <c r="Y4" s="217"/>
+      <c r="Z4" s="217"/>
+      <c r="AA4" s="217"/>
+      <c r="AB4" s="217"/>
+      <c r="AC4" s="217"/>
       <c r="AE4" s="123"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -3557,18 +3562,18 @@
       <c r="AE12" s="104"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C15" s="208" t="s">
+      <c r="C15" s="216" t="s">
         <v>141</v>
       </c>
-      <c r="D15" s="208"/>
-      <c r="E15" s="208"/>
-      <c r="F15" s="208"/>
-      <c r="G15" s="208"/>
-      <c r="H15" s="208"/>
-      <c r="I15" s="208"/>
-      <c r="J15" s="208"/>
-      <c r="K15" s="208"/>
-      <c r="L15" s="208"/>
+      <c r="D15" s="216"/>
+      <c r="E15" s="216"/>
+      <c r="F15" s="216"/>
+      <c r="G15" s="216"/>
+      <c r="H15" s="216"/>
+      <c r="I15" s="216"/>
+      <c r="J15" s="216"/>
+      <c r="K15" s="216"/>
+      <c r="L15" s="216"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C16" s="62">
@@ -3653,18 +3658,18 @@
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C20" s="208" t="s">
+      <c r="C20" s="216" t="s">
         <v>312</v>
       </c>
-      <c r="D20" s="208"/>
-      <c r="E20" s="208"/>
-      <c r="F20" s="208"/>
-      <c r="G20" s="208"/>
-      <c r="H20" s="208"/>
-      <c r="I20" s="208"/>
-      <c r="J20" s="208"/>
-      <c r="K20" s="208"/>
-      <c r="L20" s="208"/>
+      <c r="D20" s="216"/>
+      <c r="E20" s="216"/>
+      <c r="F20" s="216"/>
+      <c r="G20" s="216"/>
+      <c r="H20" s="216"/>
+      <c r="I20" s="216"/>
+      <c r="J20" s="216"/>
+      <c r="K20" s="216"/>
+      <c r="L20" s="216"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
@@ -3856,18 +3861,18 @@
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="208" t="s">
+      <c r="C27" s="216" t="s">
         <v>144</v>
       </c>
-      <c r="D27" s="208"/>
-      <c r="E27" s="208"/>
-      <c r="F27" s="208"/>
-      <c r="G27" s="208"/>
-      <c r="H27" s="208"/>
-      <c r="I27" s="208"/>
-      <c r="J27" s="208"/>
-      <c r="K27" s="208"/>
-      <c r="L27" s="208"/>
+      <c r="D27" s="216"/>
+      <c r="E27" s="216"/>
+      <c r="F27" s="216"/>
+      <c r="G27" s="216"/>
+      <c r="H27" s="216"/>
+      <c r="I27" s="216"/>
+      <c r="J27" s="216"/>
+      <c r="K27" s="216"/>
+      <c r="L27" s="216"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
@@ -4074,10 +4079,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="209" t="s">
+      <c r="B4" s="211" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="209"/>
+      <c r="C4" s="211"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -4094,7 +4099,7 @@
       </c>
       <c r="C6" s="145">
         <f>Overview!C3</f>
-        <v>287.46300000000002</v>
+        <v>292.48</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4103,7 +4108,7 @@
       </c>
       <c r="C7" s="147">
         <f>C5*C6</f>
-        <v>4221969.0810000002</v>
+        <v>4295653.7600000007</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4121,7 +4126,7 @@
       </c>
       <c r="C9" s="170">
         <f>[1]Sheet1!$C$10/1000</f>
-        <v>4.4159999999999998E-2</v>
+        <v>4.3920000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4130,7 +4135,7 @@
       </c>
       <c r="C10" s="145">
         <f>[1]Sheet1!$F$17</f>
-        <v>1.0612999999999999</v>
+        <v>1.0644</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4159,10 +4164,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="209" t="s">
+      <c r="B15" s="211" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="209"/>
+      <c r="C15" s="211"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -4170,7 +4175,7 @@
       </c>
       <c r="C16" s="148">
         <f>C8/(C8+C7)</f>
-        <v>1.9669675575328623E-2</v>
+        <v>1.9338800451860084E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4179,7 +4184,7 @@
       </c>
       <c r="C17" s="148">
         <f>C7/(C8+C7)</f>
-        <v>0.98033032442467138</v>
+        <v>0.98066119954813991</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4197,7 +4202,7 @@
       </c>
       <c r="C19" s="148">
         <f>C9+C10*C11</f>
-        <v>9.7225000000000006E-2</v>
+        <v>9.7140000000000004E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4206,7 +4211,7 @@
       </c>
       <c r="C20" s="148">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>9.6011872758891614E-2</v>
+        <v>9.5948923280169934E-2</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4260,60 +4265,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="209" t="s">
+      <c r="C3" s="211" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="209"/>
-      <c r="E3" s="209"/>
-      <c r="F3" s="209"/>
-      <c r="G3" s="210"/>
-      <c r="H3" s="211" t="s">
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="215" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="209"/>
-      <c r="J3" s="209"/>
-      <c r="K3" s="209"/>
-      <c r="L3" s="209"/>
-      <c r="P3" s="212"/>
-      <c r="Q3" s="212"/>
-      <c r="R3" s="212"/>
-      <c r="S3" s="212"/>
-      <c r="T3" s="212"/>
-      <c r="U3" s="212"/>
-      <c r="V3" s="212"/>
-      <c r="W3" s="212"/>
-      <c r="X3" s="212"/>
-      <c r="Y3" s="212"/>
-      <c r="Z3" s="212"/>
+      <c r="I3" s="211"/>
+      <c r="J3" s="211"/>
+      <c r="K3" s="211"/>
+      <c r="L3" s="211"/>
+      <c r="P3" s="217"/>
+      <c r="Q3" s="217"/>
+      <c r="R3" s="217"/>
+      <c r="S3" s="217"/>
+      <c r="T3" s="217"/>
+      <c r="U3" s="217"/>
+      <c r="V3" s="217"/>
+      <c r="W3" s="217"/>
+      <c r="X3" s="217"/>
+      <c r="Y3" s="217"/>
+      <c r="Z3" s="217"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="208" t="s">
+      <c r="C5" s="216" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="208"/>
-      <c r="E5" s="208"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="208"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="208"/>
-      <c r="J5" s="208"/>
-      <c r="K5" s="208"/>
-      <c r="L5" s="208"/>
-      <c r="P5" s="212"/>
-      <c r="Q5" s="212"/>
-      <c r="R5" s="212"/>
-      <c r="S5" s="212"/>
-      <c r="T5" s="212"/>
-      <c r="U5" s="212"/>
-      <c r="V5" s="212"/>
-      <c r="W5" s="212"/>
-      <c r="X5" s="212"/>
-      <c r="Y5" s="212"/>
-      <c r="Z5" s="212"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="216"/>
+      <c r="K5" s="216"/>
+      <c r="L5" s="216"/>
+      <c r="P5" s="217"/>
+      <c r="Q5" s="217"/>
+      <c r="R5" s="217"/>
+      <c r="S5" s="217"/>
+      <c r="T5" s="217"/>
+      <c r="U5" s="217"/>
+      <c r="V5" s="217"/>
+      <c r="W5" s="217"/>
+      <c r="X5" s="217"/>
+      <c r="Y5" s="217"/>
+      <c r="Z5" s="217"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -4559,10 +4564,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="209" t="s">
+      <c r="B13" s="211" t="s">
         <v>180</v>
       </c>
-      <c r="C13" s="209"/>
+      <c r="C13" s="211"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -4582,10 +4587,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="209" t="s">
+      <c r="B18" s="211" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="209"/>
+      <c r="C18" s="211"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -4699,37 +4704,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="209" t="s">
+      <c r="C2" s="211" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="209"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="209"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="211" t="s">
+      <c r="D2" s="211"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="215" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="209"/>
-      <c r="J2" s="209"/>
-      <c r="K2" s="209"/>
-      <c r="L2" s="209"/>
+      <c r="I2" s="211"/>
+      <c r="J2" s="211"/>
+      <c r="K2" s="211"/>
+      <c r="L2" s="211"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="208" t="s">
+      <c r="C4" s="216" t="s">
         <v>316</v>
       </c>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="208"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
-      <c r="I4" s="208"/>
-      <c r="J4" s="208"/>
-      <c r="K4" s="208"/>
-      <c r="L4" s="208"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -4918,18 +4923,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="208" t="s">
+      <c r="C10" s="216" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="208"/>
-      <c r="E10" s="208"/>
-      <c r="F10" s="208"/>
-      <c r="G10" s="208"/>
-      <c r="H10" s="208"/>
-      <c r="I10" s="208"/>
-      <c r="J10" s="208"/>
-      <c r="K10" s="208"/>
-      <c r="L10" s="208"/>
+      <c r="D10" s="216"/>
+      <c r="E10" s="216"/>
+      <c r="F10" s="216"/>
+      <c r="G10" s="216"/>
+      <c r="H10" s="216"/>
+      <c r="I10" s="216"/>
+      <c r="J10" s="216"/>
+      <c r="K10" s="216"/>
+      <c r="L10" s="216"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5111,18 +5116,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="208" t="s">
+      <c r="C16" s="216" t="s">
         <v>216</v>
       </c>
-      <c r="D16" s="208"/>
-      <c r="E16" s="208"/>
-      <c r="F16" s="208"/>
-      <c r="G16" s="208"/>
-      <c r="H16" s="208"/>
-      <c r="I16" s="208"/>
-      <c r="J16" s="208"/>
-      <c r="K16" s="208"/>
-      <c r="L16" s="208"/>
+      <c r="D16" s="216"/>
+      <c r="E16" s="216"/>
+      <c r="F16" s="216"/>
+      <c r="G16" s="216"/>
+      <c r="H16" s="216"/>
+      <c r="I16" s="216"/>
+      <c r="J16" s="216"/>
+      <c r="K16" s="216"/>
+      <c r="L16" s="216"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -5256,18 +5261,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="208" t="s">
+      <c r="C21" s="216" t="s">
         <v>317</v>
       </c>
-      <c r="D21" s="208"/>
-      <c r="E21" s="208"/>
-      <c r="F21" s="208"/>
-      <c r="G21" s="208"/>
-      <c r="H21" s="208"/>
-      <c r="I21" s="208"/>
-      <c r="J21" s="208"/>
-      <c r="K21" s="208"/>
-      <c r="L21" s="208"/>
+      <c r="D21" s="216"/>
+      <c r="E21" s="216"/>
+      <c r="F21" s="216"/>
+      <c r="G21" s="216"/>
+      <c r="H21" s="216"/>
+      <c r="I21" s="216"/>
+      <c r="J21" s="216"/>
+      <c r="K21" s="216"/>
+      <c r="L21" s="216"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -5351,18 +5356,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="208" t="s">
+      <c r="C26" s="216" t="s">
         <v>318</v>
       </c>
-      <c r="D26" s="208"/>
-      <c r="E26" s="208"/>
-      <c r="F26" s="208"/>
-      <c r="G26" s="208"/>
-      <c r="H26" s="208"/>
-      <c r="I26" s="208"/>
-      <c r="J26" s="208"/>
-      <c r="K26" s="208"/>
-      <c r="L26" s="208"/>
+      <c r="D26" s="216"/>
+      <c r="E26" s="216"/>
+      <c r="F26" s="216"/>
+      <c r="G26" s="216"/>
+      <c r="H26" s="216"/>
+      <c r="I26" s="216"/>
+      <c r="J26" s="216"/>
+      <c r="K26" s="216"/>
+      <c r="L26" s="216"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -5632,10 +5637,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="209" t="s">
+      <c r="B37" s="211" t="s">
         <v>322</v>
       </c>
-      <c r="C37" s="209"/>
+      <c r="C37" s="211"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -5701,10 +5706,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="209" t="s">
+      <c r="B46" s="211" t="s">
         <v>192</v>
       </c>
-      <c r="C46" s="209"/>
+      <c r="C46" s="211"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -5760,10 +5765,10 @@
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="209" t="s">
+      <c r="B54" s="211" t="s">
         <v>326</v>
       </c>
-      <c r="C54" s="209"/>
+      <c r="C54" s="211"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -5873,10 +5878,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="209" t="s">
+      <c r="B4" s="211" t="s">
         <v>200</v>
       </c>
-      <c r="C4" s="209"/>
+      <c r="C4" s="211"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -5930,7 +5935,7 @@
       </c>
       <c r="C10" s="35">
         <f>Overview!C3</f>
-        <v>287.46300000000002</v>
+        <v>292.48</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5939,7 +5944,7 @@
       </c>
       <c r="C11" s="89">
         <f>(C9-C10)/C10</f>
-        <v>-0.29094561954483139</v>
+        <v>-0.30310824887587479</v>
       </c>
     </row>
   </sheetData>
@@ -5983,60 +5988,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="209" t="s">
+      <c r="C3" s="211" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="209"/>
-      <c r="E3" s="209"/>
-      <c r="F3" s="209"/>
-      <c r="G3" s="210"/>
-      <c r="H3" s="211" t="s">
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="215" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="209"/>
-      <c r="J3" s="209"/>
-      <c r="K3" s="209"/>
-      <c r="L3" s="209"/>
-      <c r="P3" s="212"/>
-      <c r="Q3" s="212"/>
-      <c r="R3" s="212"/>
-      <c r="S3" s="212"/>
-      <c r="T3" s="212"/>
-      <c r="U3" s="212"/>
-      <c r="V3" s="212"/>
-      <c r="W3" s="212"/>
-      <c r="X3" s="212"/>
-      <c r="Y3" s="212"/>
-      <c r="Z3" s="212"/>
+      <c r="I3" s="211"/>
+      <c r="J3" s="211"/>
+      <c r="K3" s="211"/>
+      <c r="L3" s="211"/>
+      <c r="P3" s="217"/>
+      <c r="Q3" s="217"/>
+      <c r="R3" s="217"/>
+      <c r="S3" s="217"/>
+      <c r="T3" s="217"/>
+      <c r="U3" s="217"/>
+      <c r="V3" s="217"/>
+      <c r="W3" s="217"/>
+      <c r="X3" s="217"/>
+      <c r="Y3" s="217"/>
+      <c r="Z3" s="217"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="208" t="s">
+      <c r="C5" s="216" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="208"/>
-      <c r="E5" s="208"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="208"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="208"/>
-      <c r="J5" s="208"/>
-      <c r="K5" s="208"/>
-      <c r="L5" s="208"/>
-      <c r="P5" s="212"/>
-      <c r="Q5" s="212"/>
-      <c r="R5" s="212"/>
-      <c r="S5" s="212"/>
-      <c r="T5" s="212"/>
-      <c r="U5" s="212"/>
-      <c r="V5" s="212"/>
-      <c r="W5" s="212"/>
-      <c r="X5" s="212"/>
-      <c r="Y5" s="212"/>
-      <c r="Z5" s="212"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="216"/>
+      <c r="K5" s="216"/>
+      <c r="L5" s="216"/>
+      <c r="P5" s="217"/>
+      <c r="Q5" s="217"/>
+      <c r="R5" s="217"/>
+      <c r="S5" s="217"/>
+      <c r="T5" s="217"/>
+      <c r="U5" s="217"/>
+      <c r="V5" s="217"/>
+      <c r="W5" s="217"/>
+      <c r="X5" s="217"/>
+      <c r="Y5" s="217"/>
+      <c r="Z5" s="217"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -6123,23 +6128,23 @@
       </c>
       <c r="H7" s="133">
         <f>G7*(1+$C$17)</f>
-        <v>108002.39264941346</v>
+        <v>109037.5593521235</v>
       </c>
       <c r="I7" s="133">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>135218.99559706566</v>
+        <v>137823.4750210841</v>
       </c>
       <c r="J7" s="133">
         <f t="shared" si="0"/>
-        <v>169294.18248752621</v>
+        <v>174208.87242665031</v>
       </c>
       <c r="K7" s="133">
         <f t="shared" si="0"/>
-        <v>211956.31647438282</v>
+        <v>220200.01474728598</v>
       </c>
       <c r="L7" s="133">
         <f t="shared" si="0"/>
-        <v>265369.30822592729</v>
+        <v>278332.81864056946</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="7"/>
@@ -6171,7 +6176,7 @@
       <c r="K8" s="130"/>
       <c r="L8" s="133">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>4945518.9260286447</v>
+        <v>5187111.620119703</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="7"/>
@@ -6225,23 +6230,23 @@
       <c r="G10" s="150"/>
       <c r="H10" s="133">
         <f>H7/(1+$C$21)^H9</f>
-        <v>100002.21541612357</v>
+        <v>100960.70310381804</v>
       </c>
       <c r="I10" s="133">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>115928.49416758028</v>
+        <v>118161.41548446853</v>
       </c>
       <c r="J10" s="133">
         <f t="shared" si="1"/>
-        <v>134391.18027575049</v>
+        <v>138292.61960404465</v>
       </c>
       <c r="K10" s="133">
         <f t="shared" si="1"/>
-        <v>155794.22009744408</v>
+        <v>161853.58442547446</v>
       </c>
       <c r="L10" s="133">
         <f t="shared" si="1"/>
-        <v>180605.89218703701</v>
+        <v>189428.63954981451</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -6260,7 +6265,7 @@
       <c r="K11" s="130"/>
       <c r="L11" s="133">
         <f>L8/(1+C21)^L9</f>
-        <v>3365837.0816675075</v>
+        <v>3530261.0097919977</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6276,7 +6281,7 @@
       </c>
       <c r="C15" s="194">
         <f>Overview!C3</f>
-        <v>287.46300000000002</v>
+        <v>292.48</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6285,7 +6290,7 @@
       </c>
       <c r="C16" s="194">
         <f>C36</f>
-        <v>280.14183181122377</v>
+        <v>292.83325198880766</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6293,7 +6298,7 @@
         <v>335</v>
       </c>
       <c r="C17" s="196">
-        <v>0.252</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="E17" s="220" t="s">
         <v>336</v>
@@ -6342,7 +6347,7 @@
       </c>
       <c r="C23" s="200">
         <f>C15*C22</f>
-        <v>4221969.0810000002</v>
+        <v>4295653.7600000007</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6369,7 +6374,7 @@
       </c>
       <c r="C26" s="201">
         <f>C23+C25-C24</f>
-        <v>4160085.0810000002</v>
+        <v>4233769.7600000007</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6385,7 +6390,7 @@
       </c>
       <c r="C29" s="200">
         <f>SUM(H10:L10)</f>
-        <v>686722.00214393542</v>
+        <v>708696.96216762019</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -6394,7 +6399,7 @@
       </c>
       <c r="C30" s="200">
         <f>L11</f>
-        <v>3365837.0816675075</v>
+        <v>3530261.0097919977</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -6403,7 +6408,7 @@
       </c>
       <c r="C31" s="203">
         <f>C29+C30</f>
-        <v>4052559.0838114428</v>
+        <v>4238957.9719596179</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -6430,7 +6435,7 @@
       </c>
       <c r="C34" s="203">
         <f>C31+C32-C33</f>
-        <v>4114443.0838114433</v>
+        <v>4300841.9719596179</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -6448,22 +6453,22 @@
       </c>
       <c r="C36" s="206">
         <f>C34/C35</f>
-        <v>280.14183181122377</v>
+        <v>292.83325198880766</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="208" t="s">
+      <c r="C39" s="216" t="s">
         <v>338</v>
       </c>
-      <c r="D39" s="208"/>
-      <c r="E39" s="208"/>
-      <c r="F39" s="208"/>
-      <c r="G39" s="208"/>
-      <c r="H39" s="208"/>
-      <c r="I39" s="208"/>
-      <c r="J39" s="208"/>
-      <c r="K39" s="208"/>
-      <c r="L39" s="208"/>
+      <c r="D39" s="216"/>
+      <c r="E39" s="216"/>
+      <c r="F39" s="216"/>
+      <c r="G39" s="216"/>
+      <c r="H39" s="216"/>
+      <c r="I39" s="216"/>
+      <c r="J39" s="216"/>
+      <c r="K39" s="216"/>
+      <c r="L39" s="216"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="62">
@@ -6533,23 +6538,23 @@
       </c>
       <c r="H41" s="174">
         <f t="shared" si="3"/>
-        <v>108002.39264941346</v>
+        <v>109037.5593521235</v>
       </c>
       <c r="I41" s="174">
         <f t="shared" si="3"/>
-        <v>135218.99559706566</v>
+        <v>137823.4750210841</v>
       </c>
       <c r="J41" s="174">
         <f t="shared" si="3"/>
-        <v>169294.18248752621</v>
+        <v>174208.87242665031</v>
       </c>
       <c r="K41" s="174">
         <f t="shared" si="3"/>
-        <v>211956.31647438282</v>
+        <v>220200.01474728598</v>
       </c>
       <c r="L41" s="174">
         <f t="shared" si="3"/>
-        <v>265369.30822592729</v>
+        <v>278332.81864056946</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
@@ -6578,23 +6583,23 @@
       </c>
       <c r="H42" s="174">
         <f>H41/H43</f>
-        <v>135002.99081176682</v>
+        <v>136296.94919015435</v>
       </c>
       <c r="I42" s="174">
         <f t="shared" ref="I42:L42" si="4">I41/I43</f>
-        <v>169023.74449633207</v>
+        <v>172279.34377635512</v>
       </c>
       <c r="J42" s="174">
         <f t="shared" si="4"/>
-        <v>211617.72810940776</v>
+        <v>217761.09053331288</v>
       </c>
       <c r="K42" s="174">
         <f t="shared" si="4"/>
-        <v>264945.39559297852</v>
+        <v>275250.01843410748</v>
       </c>
       <c r="L42" s="174">
         <f t="shared" si="4"/>
-        <v>331711.63528240909</v>
+        <v>347916.02330071182</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -6663,23 +6668,23 @@
       </c>
       <c r="H44" s="174">
         <f>H41/H45</f>
-        <v>469575.62021484115</v>
+        <v>474076.34500923258</v>
       </c>
       <c r="I44" s="174">
         <f t="shared" ref="I44:L44" si="6">I41/I45</f>
-        <v>587908.67650898115</v>
+        <v>599232.50009166996</v>
       </c>
       <c r="J44" s="174">
         <f t="shared" si="6"/>
-        <v>736061.66298924433</v>
+        <v>757429.88011587085</v>
       </c>
       <c r="K44" s="174">
         <f t="shared" si="6"/>
-        <v>921549.20206253394</v>
+        <v>957391.36846646073</v>
       </c>
       <c r="L44" s="174">
         <f t="shared" si="6"/>
-        <v>1153779.6009822926</v>
+        <v>1210142.6897416064</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
@@ -6745,23 +6750,23 @@
       </c>
       <c r="H46" s="207">
         <f t="shared" si="8"/>
-        <v>0.252</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="I46" s="207">
         <f t="shared" si="8"/>
-        <v>0.252</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="J46" s="207">
         <f t="shared" si="8"/>
-        <v>0.252</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="K46" s="207">
         <f t="shared" si="8"/>
-        <v>0.252</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="L46" s="207">
         <f t="shared" si="8"/>
-        <v>0.252</v>
+        <v>0.26399999999999979</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.2">
@@ -6787,23 +6792,23 @@
       </c>
       <c r="H47" s="207">
         <f t="shared" si="9"/>
-        <v>1.4678623162471371E-2</v>
+        <v>2.4403977378085973E-2</v>
       </c>
       <c r="I47" s="207">
         <f t="shared" si="9"/>
-        <v>0.252</v>
+        <v>0.26400000000000023</v>
       </c>
       <c r="J47" s="207">
         <f t="shared" si="9"/>
-        <v>0.252</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="K47" s="207">
         <f t="shared" si="9"/>
-        <v>0.252</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="L47" s="207">
         <f t="shared" si="9"/>
-        <v>0.252</v>
+        <v>0.26399999999999979</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.2">
@@ -6829,23 +6834,23 @@
       </c>
       <c r="H48" s="207">
         <f t="shared" si="10"/>
-        <v>0.12835085511338429</v>
+        <v>0.13916571953939116</v>
       </c>
       <c r="I48" s="207">
         <f t="shared" si="10"/>
-        <v>0.252</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="J48" s="207">
         <f t="shared" si="10"/>
-        <v>0.25199999999999978</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="K48" s="207">
         <f t="shared" si="10"/>
-        <v>0.252</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="L48" s="207">
         <f t="shared" si="10"/>
-        <v>0.252</v>
+        <v>0.26400000000000001</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
@@ -6878,7 +6883,7 @@
       </c>
       <c r="I49" s="207">
         <f t="shared" si="11"/>
-        <v>0.28749999999999998</v>
+        <v>0.28750000000000003</v>
       </c>
       <c r="J49" s="207">
         <f t="shared" si="11"/>
@@ -6895,17 +6900,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -13290,11 +13295,11 @@
         <v>74</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="213" t="s">
+      <c r="P4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="Q4" s="214"/>
-      <c r="R4" s="215"/>
+      <c r="Q4" s="209"/>
+      <c r="R4" s="210"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -23495,36 +23500,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="209" t="s">
+      <c r="C2" s="211" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="209"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="209"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="211" t="s">
+      <c r="D2" s="211"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="215" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="209"/>
-      <c r="J2" s="209"/>
-      <c r="K2" s="209"/>
-      <c r="L2" s="209"/>
+      <c r="I2" s="211"/>
+      <c r="J2" s="211"/>
+      <c r="K2" s="211"/>
+      <c r="L2" s="211"/>
       <c r="O2" s="90"/>
-      <c r="S2" s="209" t="s">
+      <c r="S2" s="211" t="s">
         <v>104</v>
       </c>
-      <c r="T2" s="209"/>
-      <c r="U2" s="209"/>
-      <c r="V2" s="209"/>
-      <c r="W2" s="209"/>
-      <c r="X2" s="209"/>
-      <c r="Y2" s="209"/>
-      <c r="Z2" s="209"/>
-      <c r="AA2" s="209" t="s">
+      <c r="T2" s="211"/>
+      <c r="U2" s="211"/>
+      <c r="V2" s="211"/>
+      <c r="W2" s="211"/>
+      <c r="X2" s="211"/>
+      <c r="Y2" s="211"/>
+      <c r="Z2" s="211"/>
+      <c r="AA2" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="AB2" s="209"/>
-      <c r="AC2" s="209"/>
+      <c r="AB2" s="211"/>
+      <c r="AC2" s="211"/>
       <c r="AE2" s="117" t="s">
         <v>74</v>
       </c>
@@ -23535,32 +23540,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="208" t="s">
+      <c r="C4" s="216" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="208"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
-      <c r="I4" s="208"/>
-      <c r="J4" s="208"/>
-      <c r="K4" s="208"/>
-      <c r="L4" s="208"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
       <c r="O4" s="90"/>
-      <c r="S4" s="216" t="s">
+      <c r="S4" s="212" t="s">
         <v>113</v>
       </c>
-      <c r="T4" s="217"/>
-      <c r="U4" s="217"/>
-      <c r="V4" s="217"/>
-      <c r="W4" s="217"/>
-      <c r="X4" s="217"/>
-      <c r="Y4" s="217"/>
-      <c r="Z4" s="217"/>
-      <c r="AA4" s="217"/>
-      <c r="AB4" s="217"/>
-      <c r="AC4" s="217"/>
+      <c r="T4" s="213"/>
+      <c r="U4" s="213"/>
+      <c r="V4" s="213"/>
+      <c r="W4" s="213"/>
+      <c r="X4" s="213"/>
+      <c r="Y4" s="213"/>
+      <c r="Z4" s="213"/>
+      <c r="AA4" s="213"/>
+      <c r="AB4" s="213"/>
+      <c r="AC4" s="213"/>
       <c r="AE4" s="119" t="s">
         <v>120</v>
       </c>
@@ -24236,33 +24241,33 @@
       <c r="Q12" s="91"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="208" t="s">
+      <c r="C13" s="216" t="s">
         <v>115</v>
       </c>
-      <c r="D13" s="208"/>
-      <c r="E13" s="208"/>
-      <c r="F13" s="208"/>
-      <c r="G13" s="208"/>
-      <c r="H13" s="208"/>
-      <c r="I13" s="208"/>
-      <c r="J13" s="208"/>
-      <c r="K13" s="208"/>
-      <c r="L13" s="208"/>
+      <c r="D13" s="216"/>
+      <c r="E13" s="216"/>
+      <c r="F13" s="216"/>
+      <c r="G13" s="216"/>
+      <c r="H13" s="216"/>
+      <c r="I13" s="216"/>
+      <c r="J13" s="216"/>
+      <c r="K13" s="216"/>
+      <c r="L13" s="216"/>
       <c r="O13" s="90"/>
       <c r="Q13" s="91"/>
-      <c r="S13" s="216" t="s">
+      <c r="S13" s="212" t="s">
         <v>115</v>
       </c>
-      <c r="T13" s="217"/>
-      <c r="U13" s="217"/>
-      <c r="V13" s="217"/>
-      <c r="W13" s="217"/>
-      <c r="X13" s="217"/>
-      <c r="Y13" s="217"/>
-      <c r="Z13" s="217"/>
-      <c r="AA13" s="217"/>
-      <c r="AB13" s="217"/>
-      <c r="AC13" s="217"/>
+      <c r="T13" s="213"/>
+      <c r="U13" s="213"/>
+      <c r="V13" s="213"/>
+      <c r="W13" s="213"/>
+      <c r="X13" s="213"/>
+      <c r="Y13" s="213"/>
+      <c r="Z13" s="213"/>
+      <c r="AA13" s="213"/>
+      <c r="AB13" s="213"/>
+      <c r="AC13" s="213"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
@@ -24844,35 +24849,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="209" t="s">
+      <c r="C2" s="211" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="209"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="209"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="211" t="s">
+      <c r="D2" s="211"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="215" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="209"/>
-      <c r="J2" s="209"/>
-      <c r="K2" s="209"/>
-      <c r="L2" s="209"/>
-      <c r="P2" s="209" t="s">
+      <c r="I2" s="211"/>
+      <c r="J2" s="211"/>
+      <c r="K2" s="211"/>
+      <c r="L2" s="211"/>
+      <c r="P2" s="211" t="s">
         <v>104</v>
       </c>
-      <c r="Q2" s="209"/>
-      <c r="R2" s="209"/>
-      <c r="S2" s="209"/>
-      <c r="T2" s="209"/>
-      <c r="U2" s="209"/>
-      <c r="V2" s="209"/>
-      <c r="W2" s="209"/>
-      <c r="X2" s="209" t="s">
+      <c r="Q2" s="211"/>
+      <c r="R2" s="211"/>
+      <c r="S2" s="211"/>
+      <c r="T2" s="211"/>
+      <c r="U2" s="211"/>
+      <c r="V2" s="211"/>
+      <c r="W2" s="211"/>
+      <c r="X2" s="211" t="s">
         <v>105</v>
       </c>
-      <c r="Y2" s="209"/>
-      <c r="Z2" s="209"/>
+      <c r="Y2" s="211"/>
+      <c r="Z2" s="211"/>
       <c r="AB2" s="117" t="s">
         <v>74</v>
       </c>
@@ -24881,31 +24886,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="208" t="s">
+      <c r="C4" s="216" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="208"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
-      <c r="I4" s="208"/>
-      <c r="J4" s="208"/>
-      <c r="K4" s="208"/>
-      <c r="L4" s="208"/>
-      <c r="P4" s="217" t="s">
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
+      <c r="P4" s="213" t="s">
         <v>113</v>
       </c>
-      <c r="Q4" s="217"/>
-      <c r="R4" s="217"/>
-      <c r="S4" s="217"/>
-      <c r="T4" s="217"/>
-      <c r="U4" s="217"/>
-      <c r="V4" s="217"/>
-      <c r="W4" s="217"/>
-      <c r="X4" s="217"/>
-      <c r="Y4" s="217"/>
-      <c r="Z4" s="217"/>
+      <c r="Q4" s="213"/>
+      <c r="R4" s="213"/>
+      <c r="S4" s="213"/>
+      <c r="T4" s="213"/>
+      <c r="U4" s="213"/>
+      <c r="V4" s="213"/>
+      <c r="W4" s="213"/>
+      <c r="X4" s="213"/>
+      <c r="Y4" s="213"/>
+      <c r="Z4" s="213"/>
       <c r="AB4" s="119" t="s">
         <v>120</v>
       </c>
@@ -25106,32 +25111,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="208" t="s">
+      <c r="C9" s="216" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="208"/>
-      <c r="E9" s="208"/>
-      <c r="F9" s="208"/>
-      <c r="G9" s="208"/>
-      <c r="H9" s="208"/>
-      <c r="I9" s="208"/>
-      <c r="J9" s="208"/>
-      <c r="K9" s="208"/>
-      <c r="L9" s="208"/>
+      <c r="D9" s="216"/>
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="216"/>
+      <c r="H9" s="216"/>
+      <c r="I9" s="216"/>
+      <c r="J9" s="216"/>
+      <c r="K9" s="216"/>
+      <c r="L9" s="216"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="217" t="s">
+      <c r="P9" s="213" t="s">
         <v>127</v>
       </c>
-      <c r="Q9" s="217"/>
-      <c r="R9" s="217"/>
-      <c r="S9" s="217"/>
-      <c r="T9" s="217"/>
-      <c r="U9" s="217"/>
-      <c r="V9" s="217"/>
-      <c r="W9" s="217"/>
-      <c r="X9" s="217"/>
-      <c r="Y9" s="217"/>
-      <c r="Z9" s="217"/>
+      <c r="Q9" s="213"/>
+      <c r="R9" s="213"/>
+      <c r="S9" s="213"/>
+      <c r="T9" s="213"/>
+      <c r="U9" s="213"/>
+      <c r="V9" s="213"/>
+      <c r="W9" s="213"/>
+      <c r="X9" s="213"/>
+      <c r="Y9" s="213"/>
+      <c r="Z9" s="213"/>
       <c r="AB9" s="119" t="str">
         <f>AB4</f>
         <v>Q1-Q2-Q3</v>
@@ -25601,31 +25606,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="208" t="s">
+      <c r="C17" s="216" t="s">
         <v>125</v>
       </c>
-      <c r="D17" s="208"/>
-      <c r="E17" s="208"/>
-      <c r="F17" s="208"/>
-      <c r="G17" s="208"/>
-      <c r="H17" s="208"/>
-      <c r="I17" s="208"/>
-      <c r="J17" s="208"/>
-      <c r="K17" s="208"/>
-      <c r="L17" s="208"/>
-      <c r="P17" s="217" t="s">
+      <c r="D17" s="216"/>
+      <c r="E17" s="216"/>
+      <c r="F17" s="216"/>
+      <c r="G17" s="216"/>
+      <c r="H17" s="216"/>
+      <c r="I17" s="216"/>
+      <c r="J17" s="216"/>
+      <c r="K17" s="216"/>
+      <c r="L17" s="216"/>
+      <c r="P17" s="213" t="s">
         <v>125</v>
       </c>
-      <c r="Q17" s="217"/>
-      <c r="R17" s="217"/>
-      <c r="S17" s="217"/>
-      <c r="T17" s="217"/>
-      <c r="U17" s="217"/>
-      <c r="V17" s="217"/>
-      <c r="W17" s="217"/>
-      <c r="X17" s="217"/>
-      <c r="Y17" s="217"/>
-      <c r="Z17" s="217"/>
+      <c r="Q17" s="213"/>
+      <c r="R17" s="213"/>
+      <c r="S17" s="213"/>
+      <c r="T17" s="213"/>
+      <c r="U17" s="213"/>
+      <c r="V17" s="213"/>
+      <c r="W17" s="213"/>
+      <c r="X17" s="213"/>
+      <c r="Y17" s="213"/>
+      <c r="Z17" s="213"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="7" t="s">
@@ -26015,60 +26020,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="209" t="s">
+      <c r="C3" s="211" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="209"/>
-      <c r="E3" s="209"/>
-      <c r="F3" s="209"/>
-      <c r="G3" s="210"/>
-      <c r="H3" s="211" t="s">
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="215" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="209"/>
-      <c r="J3" s="209"/>
-      <c r="K3" s="209"/>
-      <c r="L3" s="209"/>
-      <c r="P3" s="212"/>
-      <c r="Q3" s="212"/>
-      <c r="R3" s="212"/>
-      <c r="S3" s="212"/>
-      <c r="T3" s="212"/>
-      <c r="U3" s="212"/>
-      <c r="V3" s="212"/>
-      <c r="W3" s="212"/>
-      <c r="X3" s="212"/>
-      <c r="Y3" s="212"/>
-      <c r="Z3" s="212"/>
+      <c r="I3" s="211"/>
+      <c r="J3" s="211"/>
+      <c r="K3" s="211"/>
+      <c r="L3" s="211"/>
+      <c r="P3" s="217"/>
+      <c r="Q3" s="217"/>
+      <c r="R3" s="217"/>
+      <c r="S3" s="217"/>
+      <c r="T3" s="217"/>
+      <c r="U3" s="217"/>
+      <c r="V3" s="217"/>
+      <c r="W3" s="217"/>
+      <c r="X3" s="217"/>
+      <c r="Y3" s="217"/>
+      <c r="Z3" s="217"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="208" t="s">
+      <c r="C5" s="216" t="s">
         <v>113</v>
       </c>
-      <c r="D5" s="208"/>
-      <c r="E5" s="208"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="208"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="208"/>
-      <c r="J5" s="208"/>
-      <c r="K5" s="208"/>
-      <c r="L5" s="208"/>
-      <c r="P5" s="212"/>
-      <c r="Q5" s="212"/>
-      <c r="R5" s="212"/>
-      <c r="S5" s="212"/>
-      <c r="T5" s="212"/>
-      <c r="U5" s="212"/>
-      <c r="V5" s="212"/>
-      <c r="W5" s="212"/>
-      <c r="X5" s="212"/>
-      <c r="Y5" s="212"/>
-      <c r="Z5" s="212"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="216"/>
+      <c r="K5" s="216"/>
+      <c r="L5" s="216"/>
+      <c r="P5" s="217"/>
+      <c r="Q5" s="217"/>
+      <c r="R5" s="217"/>
+      <c r="S5" s="217"/>
+      <c r="T5" s="217"/>
+      <c r="U5" s="217"/>
+      <c r="V5" s="217"/>
+      <c r="W5" s="217"/>
+      <c r="X5" s="217"/>
+      <c r="Y5" s="217"/>
+      <c r="Z5" s="217"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -26254,30 +26259,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="208" t="s">
+      <c r="C11" s="216" t="s">
         <v>133</v>
       </c>
-      <c r="D11" s="208"/>
-      <c r="E11" s="208"/>
-      <c r="F11" s="208"/>
-      <c r="G11" s="208"/>
-      <c r="H11" s="208"/>
-      <c r="I11" s="208"/>
-      <c r="J11" s="208"/>
-      <c r="K11" s="208"/>
-      <c r="L11" s="208"/>
+      <c r="D11" s="216"/>
+      <c r="E11" s="216"/>
+      <c r="F11" s="216"/>
+      <c r="G11" s="216"/>
+      <c r="H11" s="216"/>
+      <c r="I11" s="216"/>
+      <c r="J11" s="216"/>
+      <c r="K11" s="216"/>
+      <c r="L11" s="216"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="212"/>
-      <c r="Q11" s="212"/>
-      <c r="R11" s="212"/>
-      <c r="S11" s="212"/>
-      <c r="T11" s="212"/>
-      <c r="U11" s="212"/>
-      <c r="V11" s="212"/>
-      <c r="W11" s="212"/>
-      <c r="X11" s="212"/>
-      <c r="Y11" s="212"/>
-      <c r="Z11" s="212"/>
+      <c r="P11" s="217"/>
+      <c r="Q11" s="217"/>
+      <c r="R11" s="217"/>
+      <c r="S11" s="217"/>
+      <c r="T11" s="217"/>
+      <c r="U11" s="217"/>
+      <c r="V11" s="217"/>
+      <c r="W11" s="217"/>
+      <c r="X11" s="217"/>
+      <c r="Y11" s="217"/>
+      <c r="Z11" s="217"/>
       <c r="AB11" s="123"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -26519,18 +26524,18 @@
       <c r="D16" s="20"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="208" t="s">
+      <c r="C18" s="216" t="s">
         <v>140</v>
       </c>
-      <c r="D18" s="208"/>
-      <c r="E18" s="208"/>
-      <c r="F18" s="208"/>
-      <c r="G18" s="208"/>
-      <c r="H18" s="208"/>
-      <c r="I18" s="208"/>
-      <c r="J18" s="208"/>
-      <c r="K18" s="208"/>
-      <c r="L18" s="208"/>
+      <c r="D18" s="216"/>
+      <c r="E18" s="216"/>
+      <c r="F18" s="216"/>
+      <c r="G18" s="216"/>
+      <c r="H18" s="216"/>
+      <c r="I18" s="216"/>
+      <c r="J18" s="216"/>
+      <c r="K18" s="216"/>
+      <c r="L18" s="216"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -26743,23 +26748,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="212"/>
-      <c r="C25" s="212"/>
+      <c r="B25" s="217"/>
+      <c r="C25" s="217"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="122"/>
-      <c r="C26" s="208" t="s">
+      <c r="C26" s="216" t="s">
         <v>300</v>
       </c>
-      <c r="D26" s="208"/>
-      <c r="E26" s="208"/>
-      <c r="F26" s="208"/>
-      <c r="G26" s="208"/>
-      <c r="H26" s="208"/>
-      <c r="I26" s="208"/>
-      <c r="J26" s="208"/>
-      <c r="K26" s="208"/>
-      <c r="L26" s="208"/>
+      <c r="D26" s="216"/>
+      <c r="E26" s="216"/>
+      <c r="F26" s="216"/>
+      <c r="G26" s="216"/>
+      <c r="H26" s="216"/>
+      <c r="I26" s="216"/>
+      <c r="J26" s="216"/>
+      <c r="K26" s="216"/>
+      <c r="L26" s="216"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
@@ -26951,18 +26956,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="122"/>
-      <c r="C33" s="208" t="s">
+      <c r="C33" s="216" t="s">
         <v>303</v>
       </c>
-      <c r="D33" s="208"/>
-      <c r="E33" s="208"/>
-      <c r="F33" s="208"/>
-      <c r="G33" s="208"/>
-      <c r="H33" s="208"/>
-      <c r="I33" s="208"/>
-      <c r="J33" s="208"/>
-      <c r="K33" s="208"/>
-      <c r="L33" s="208"/>
+      <c r="D33" s="216"/>
+      <c r="E33" s="216"/>
+      <c r="F33" s="216"/>
+      <c r="G33" s="216"/>
+      <c r="H33" s="216"/>
+      <c r="I33" s="216"/>
+      <c r="J33" s="216"/>
+      <c r="K33" s="216"/>
+      <c r="L33" s="216"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
@@ -27146,18 +27151,18 @@
       <c r="C39" s="131"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="208" t="s">
+      <c r="C40" s="216" t="s">
         <v>306</v>
       </c>
-      <c r="D40" s="208"/>
-      <c r="E40" s="208"/>
-      <c r="F40" s="208"/>
-      <c r="G40" s="208"/>
-      <c r="H40" s="208"/>
-      <c r="I40" s="208"/>
-      <c r="J40" s="208"/>
-      <c r="K40" s="208"/>
-      <c r="L40" s="208"/>
+      <c r="D40" s="216"/>
+      <c r="E40" s="216"/>
+      <c r="F40" s="216"/>
+      <c r="G40" s="216"/>
+      <c r="H40" s="216"/>
+      <c r="I40" s="216"/>
+      <c r="J40" s="216"/>
+      <c r="K40" s="216"/>
+      <c r="L40" s="216"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
@@ -27421,6 +27426,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -27428,12 +27439,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/AAPL.xlsx
+++ b/AAPL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1437D0F9-1C70-754B-8E30-581DA526B4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039C3B8B-0282-6D44-AB23-005145B99DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="15" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="14" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2116,6 +2116,30 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2125,35 +2149,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2255,22 +2255,17 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="8">
-          <cell r="C8">
-            <v>218.965</v>
-          </cell>
-        </row>
         <row r="10">
           <cell r="C10">
-            <v>43.92</v>
+            <v>43.64</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>292.48</v>
+            <v>293.48</v>
           </cell>
           <cell r="F17">
-            <v>1.0644</v>
+            <v>1.0685</v>
           </cell>
         </row>
       </sheetData>
@@ -2724,7 +2719,7 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$17</f>
-        <v>292.48</v>
+        <v>293.48</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2750,7 +2745,7 @@
       </c>
       <c r="C11" s="93">
         <f>$C$3/'Statement Q'!$N$19</f>
-        <v>35.403024760350803</v>
+        <v>35.524069018967978</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2759,7 +2754,7 @@
       </c>
       <c r="C12" s="93">
         <f>$C$3/Statements!W19</f>
-        <v>35.403024760350803</v>
+        <v>35.524069018967978</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2768,7 +2763,7 @@
       </c>
       <c r="C13" s="98">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$17)</f>
-        <v>9.6125875749265699</v>
+        <v>9.6454533694250877</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -2777,7 +2772,7 @@
       </c>
       <c r="C15" s="20">
         <f>C3*'Statement Q'!N100</f>
-        <v>4295653.7600000007</v>
+        <v>4310340.7600000007</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -2804,7 +2799,7 @@
       </c>
       <c r="C18" s="20">
         <f>C15+C17-C16</f>
-        <v>4233769.7600000007</v>
+        <v>4248456.7600000007</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -3024,60 +3019,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="211" t="s">
+      <c r="C2" s="212" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="211"/>
-      <c r="E2" s="211"/>
-      <c r="F2" s="211"/>
-      <c r="G2" s="214"/>
-      <c r="H2" s="215" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="213"/>
+      <c r="H2" s="214" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="211"/>
-      <c r="J2" s="211"/>
-      <c r="K2" s="211"/>
-      <c r="L2" s="211"/>
-      <c r="S2" s="217"/>
-      <c r="T2" s="217"/>
-      <c r="U2" s="217"/>
-      <c r="V2" s="217"/>
-      <c r="W2" s="217"/>
-      <c r="X2" s="217"/>
-      <c r="Y2" s="217"/>
-      <c r="Z2" s="217"/>
-      <c r="AA2" s="217"/>
-      <c r="AB2" s="217"/>
-      <c r="AC2" s="217"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
+      <c r="S2" s="215"/>
+      <c r="T2" s="215"/>
+      <c r="U2" s="215"/>
+      <c r="V2" s="215"/>
+      <c r="W2" s="215"/>
+      <c r="X2" s="215"/>
+      <c r="Y2" s="215"/>
+      <c r="Z2" s="215"/>
+      <c r="AA2" s="215"/>
+      <c r="AB2" s="215"/>
+      <c r="AC2" s="215"/>
       <c r="AE2" s="122"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="216"/>
-      <c r="E4" s="216"/>
-      <c r="F4" s="216"/>
-      <c r="G4" s="216"/>
-      <c r="H4" s="216"/>
-      <c r="I4" s="216"/>
-      <c r="J4" s="216"/>
-      <c r="K4" s="216"/>
-      <c r="L4" s="216"/>
-      <c r="S4" s="217"/>
-      <c r="T4" s="217"/>
-      <c r="U4" s="217"/>
-      <c r="V4" s="217"/>
-      <c r="W4" s="217"/>
-      <c r="X4" s="217"/>
-      <c r="Y4" s="217"/>
-      <c r="Z4" s="217"/>
-      <c r="AA4" s="217"/>
-      <c r="AB4" s="217"/>
-      <c r="AC4" s="217"/>
+      <c r="D4" s="211"/>
+      <c r="E4" s="211"/>
+      <c r="F4" s="211"/>
+      <c r="G4" s="211"/>
+      <c r="H4" s="211"/>
+      <c r="I4" s="211"/>
+      <c r="J4" s="211"/>
+      <c r="K4" s="211"/>
+      <c r="L4" s="211"/>
+      <c r="S4" s="215"/>
+      <c r="T4" s="215"/>
+      <c r="U4" s="215"/>
+      <c r="V4" s="215"/>
+      <c r="W4" s="215"/>
+      <c r="X4" s="215"/>
+      <c r="Y4" s="215"/>
+      <c r="Z4" s="215"/>
+      <c r="AA4" s="215"/>
+      <c r="AB4" s="215"/>
+      <c r="AC4" s="215"/>
       <c r="AE4" s="123"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -3562,18 +3557,18 @@
       <c r="AE12" s="104"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C15" s="216" t="s">
+      <c r="C15" s="211" t="s">
         <v>141</v>
       </c>
-      <c r="D15" s="216"/>
-      <c r="E15" s="216"/>
-      <c r="F15" s="216"/>
-      <c r="G15" s="216"/>
-      <c r="H15" s="216"/>
-      <c r="I15" s="216"/>
-      <c r="J15" s="216"/>
-      <c r="K15" s="216"/>
-      <c r="L15" s="216"/>
+      <c r="D15" s="211"/>
+      <c r="E15" s="211"/>
+      <c r="F15" s="211"/>
+      <c r="G15" s="211"/>
+      <c r="H15" s="211"/>
+      <c r="I15" s="211"/>
+      <c r="J15" s="211"/>
+      <c r="K15" s="211"/>
+      <c r="L15" s="211"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C16" s="62">
@@ -3658,18 +3653,18 @@
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C20" s="216" t="s">
+      <c r="C20" s="211" t="s">
         <v>312</v>
       </c>
-      <c r="D20" s="216"/>
-      <c r="E20" s="216"/>
-      <c r="F20" s="216"/>
-      <c r="G20" s="216"/>
-      <c r="H20" s="216"/>
-      <c r="I20" s="216"/>
-      <c r="J20" s="216"/>
-      <c r="K20" s="216"/>
-      <c r="L20" s="216"/>
+      <c r="D20" s="211"/>
+      <c r="E20" s="211"/>
+      <c r="F20" s="211"/>
+      <c r="G20" s="211"/>
+      <c r="H20" s="211"/>
+      <c r="I20" s="211"/>
+      <c r="J20" s="211"/>
+      <c r="K20" s="211"/>
+      <c r="L20" s="211"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
@@ -3861,18 +3856,18 @@
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="216" t="s">
+      <c r="C27" s="211" t="s">
         <v>144</v>
       </c>
-      <c r="D27" s="216"/>
-      <c r="E27" s="216"/>
-      <c r="F27" s="216"/>
-      <c r="G27" s="216"/>
-      <c r="H27" s="216"/>
-      <c r="I27" s="216"/>
-      <c r="J27" s="216"/>
-      <c r="K27" s="216"/>
-      <c r="L27" s="216"/>
+      <c r="D27" s="211"/>
+      <c r="E27" s="211"/>
+      <c r="F27" s="211"/>
+      <c r="G27" s="211"/>
+      <c r="H27" s="211"/>
+      <c r="I27" s="211"/>
+      <c r="J27" s="211"/>
+      <c r="K27" s="211"/>
+      <c r="L27" s="211"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
@@ -4079,10 +4074,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="212" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="211"/>
+      <c r="C4" s="212"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -4099,7 +4094,7 @@
       </c>
       <c r="C6" s="145">
         <f>Overview!C3</f>
-        <v>292.48</v>
+        <v>293.48</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4108,7 +4103,7 @@
       </c>
       <c r="C7" s="147">
         <f>C5*C6</f>
-        <v>4295653.7600000007</v>
+        <v>4310340.7600000007</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4126,7 +4121,7 @@
       </c>
       <c r="C9" s="170">
         <f>[1]Sheet1!$C$10/1000</f>
-        <v>4.3920000000000001E-2</v>
+        <v>4.3639999999999998E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4135,7 +4130,7 @@
       </c>
       <c r="C10" s="145">
         <f>[1]Sheet1!$F$17</f>
-        <v>1.0644</v>
+        <v>1.0685</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4164,10 +4159,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="211" t="s">
+      <c r="B15" s="212" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="211"/>
+      <c r="C15" s="212"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -4175,7 +4170,7 @@
       </c>
       <c r="C16" s="148">
         <f>C8/(C8+C7)</f>
-        <v>1.9338800451860084E-2</v>
+        <v>1.9274175738034992E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4184,7 +4179,7 @@
       </c>
       <c r="C17" s="148">
         <f>C7/(C8+C7)</f>
-        <v>0.98066119954813991</v>
+        <v>0.98072582426196497</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4202,7 +4197,7 @@
       </c>
       <c r="C19" s="148">
         <f>C9+C10*C11</f>
-        <v>9.7140000000000004E-2</v>
+        <v>9.7064999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4211,7 +4206,7 @@
       </c>
       <c r="C20" s="148">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>9.5948923280169934E-2</v>
+        <v>9.5879349079474777E-2</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4265,60 +4260,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="211" t="s">
+      <c r="C3" s="212" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="211"/>
-      <c r="E3" s="211"/>
-      <c r="F3" s="211"/>
-      <c r="G3" s="214"/>
-      <c r="H3" s="215" t="s">
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="213"/>
+      <c r="H3" s="214" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="211"/>
-      <c r="J3" s="211"/>
-      <c r="K3" s="211"/>
-      <c r="L3" s="211"/>
-      <c r="P3" s="217"/>
-      <c r="Q3" s="217"/>
-      <c r="R3" s="217"/>
-      <c r="S3" s="217"/>
-      <c r="T3" s="217"/>
-      <c r="U3" s="217"/>
-      <c r="V3" s="217"/>
-      <c r="W3" s="217"/>
-      <c r="X3" s="217"/>
-      <c r="Y3" s="217"/>
-      <c r="Z3" s="217"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212"/>
+      <c r="L3" s="212"/>
+      <c r="P3" s="215"/>
+      <c r="Q3" s="215"/>
+      <c r="R3" s="215"/>
+      <c r="S3" s="215"/>
+      <c r="T3" s="215"/>
+      <c r="U3" s="215"/>
+      <c r="V3" s="215"/>
+      <c r="W3" s="215"/>
+      <c r="X3" s="215"/>
+      <c r="Y3" s="215"/>
+      <c r="Z3" s="215"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="216" t="s">
+      <c r="C5" s="211" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="216"/>
-      <c r="E5" s="216"/>
-      <c r="F5" s="216"/>
-      <c r="G5" s="216"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="216"/>
-      <c r="J5" s="216"/>
-      <c r="K5" s="216"/>
-      <c r="L5" s="216"/>
-      <c r="P5" s="217"/>
-      <c r="Q5" s="217"/>
-      <c r="R5" s="217"/>
-      <c r="S5" s="217"/>
-      <c r="T5" s="217"/>
-      <c r="U5" s="217"/>
-      <c r="V5" s="217"/>
-      <c r="W5" s="217"/>
-      <c r="X5" s="217"/>
-      <c r="Y5" s="217"/>
-      <c r="Z5" s="217"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="211"/>
+      <c r="P5" s="215"/>
+      <c r="Q5" s="215"/>
+      <c r="R5" s="215"/>
+      <c r="S5" s="215"/>
+      <c r="T5" s="215"/>
+      <c r="U5" s="215"/>
+      <c r="V5" s="215"/>
+      <c r="W5" s="215"/>
+      <c r="X5" s="215"/>
+      <c r="Y5" s="215"/>
+      <c r="Z5" s="215"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -4564,10 +4559,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="211" t="s">
+      <c r="B13" s="212" t="s">
         <v>180</v>
       </c>
-      <c r="C13" s="211"/>
+      <c r="C13" s="212"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -4587,10 +4582,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="211" t="s">
+      <c r="B18" s="212" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="211"/>
+      <c r="C18" s="212"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -4704,37 +4699,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="211" t="s">
+      <c r="C2" s="212" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="211"/>
-      <c r="E2" s="211"/>
-      <c r="F2" s="211"/>
-      <c r="G2" s="214"/>
-      <c r="H2" s="215" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="213"/>
+      <c r="H2" s="214" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="211"/>
-      <c r="J2" s="211"/>
-      <c r="K2" s="211"/>
-      <c r="L2" s="211"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="211" t="s">
         <v>316</v>
       </c>
-      <c r="D4" s="216"/>
-      <c r="E4" s="216"/>
-      <c r="F4" s="216"/>
-      <c r="G4" s="216"/>
-      <c r="H4" s="216"/>
-      <c r="I4" s="216"/>
-      <c r="J4" s="216"/>
-      <c r="K4" s="216"/>
-      <c r="L4" s="216"/>
+      <c r="D4" s="211"/>
+      <c r="E4" s="211"/>
+      <c r="F4" s="211"/>
+      <c r="G4" s="211"/>
+      <c r="H4" s="211"/>
+      <c r="I4" s="211"/>
+      <c r="J4" s="211"/>
+      <c r="K4" s="211"/>
+      <c r="L4" s="211"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -4923,18 +4918,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="216" t="s">
+      <c r="C10" s="211" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="216"/>
-      <c r="E10" s="216"/>
-      <c r="F10" s="216"/>
-      <c r="G10" s="216"/>
-      <c r="H10" s="216"/>
-      <c r="I10" s="216"/>
-      <c r="J10" s="216"/>
-      <c r="K10" s="216"/>
-      <c r="L10" s="216"/>
+      <c r="D10" s="211"/>
+      <c r="E10" s="211"/>
+      <c r="F10" s="211"/>
+      <c r="G10" s="211"/>
+      <c r="H10" s="211"/>
+      <c r="I10" s="211"/>
+      <c r="J10" s="211"/>
+      <c r="K10" s="211"/>
+      <c r="L10" s="211"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5116,18 +5111,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="216" t="s">
+      <c r="C16" s="211" t="s">
         <v>216</v>
       </c>
-      <c r="D16" s="216"/>
-      <c r="E16" s="216"/>
-      <c r="F16" s="216"/>
-      <c r="G16" s="216"/>
-      <c r="H16" s="216"/>
-      <c r="I16" s="216"/>
-      <c r="J16" s="216"/>
-      <c r="K16" s="216"/>
-      <c r="L16" s="216"/>
+      <c r="D16" s="211"/>
+      <c r="E16" s="211"/>
+      <c r="F16" s="211"/>
+      <c r="G16" s="211"/>
+      <c r="H16" s="211"/>
+      <c r="I16" s="211"/>
+      <c r="J16" s="211"/>
+      <c r="K16" s="211"/>
+      <c r="L16" s="211"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -5261,18 +5256,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="216" t="s">
+      <c r="C21" s="211" t="s">
         <v>317</v>
       </c>
-      <c r="D21" s="216"/>
-      <c r="E21" s="216"/>
-      <c r="F21" s="216"/>
-      <c r="G21" s="216"/>
-      <c r="H21" s="216"/>
-      <c r="I21" s="216"/>
-      <c r="J21" s="216"/>
-      <c r="K21" s="216"/>
-      <c r="L21" s="216"/>
+      <c r="D21" s="211"/>
+      <c r="E21" s="211"/>
+      <c r="F21" s="211"/>
+      <c r="G21" s="211"/>
+      <c r="H21" s="211"/>
+      <c r="I21" s="211"/>
+      <c r="J21" s="211"/>
+      <c r="K21" s="211"/>
+      <c r="L21" s="211"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -5356,18 +5351,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="216" t="s">
+      <c r="C26" s="211" t="s">
         <v>318</v>
       </c>
-      <c r="D26" s="216"/>
-      <c r="E26" s="216"/>
-      <c r="F26" s="216"/>
-      <c r="G26" s="216"/>
-      <c r="H26" s="216"/>
-      <c r="I26" s="216"/>
-      <c r="J26" s="216"/>
-      <c r="K26" s="216"/>
-      <c r="L26" s="216"/>
+      <c r="D26" s="211"/>
+      <c r="E26" s="211"/>
+      <c r="F26" s="211"/>
+      <c r="G26" s="211"/>
+      <c r="H26" s="211"/>
+      <c r="I26" s="211"/>
+      <c r="J26" s="211"/>
+      <c r="K26" s="211"/>
+      <c r="L26" s="211"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -5637,10 +5632,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="211" t="s">
+      <c r="B37" s="212" t="s">
         <v>322</v>
       </c>
-      <c r="C37" s="211"/>
+      <c r="C37" s="212"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -5706,10 +5701,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="211" t="s">
+      <c r="B46" s="212" t="s">
         <v>192</v>
       </c>
-      <c r="C46" s="211"/>
+      <c r="C46" s="212"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -5765,10 +5760,10 @@
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="211" t="s">
+      <c r="B54" s="212" t="s">
         <v>326</v>
       </c>
-      <c r="C54" s="211"/>
+      <c r="C54" s="212"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -5878,10 +5873,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="212" t="s">
         <v>200</v>
       </c>
-      <c r="C4" s="211"/>
+      <c r="C4" s="212"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -5935,7 +5930,7 @@
       </c>
       <c r="C10" s="35">
         <f>Overview!C3</f>
-        <v>292.48</v>
+        <v>293.48</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5944,7 +5939,7 @@
       </c>
       <c r="C11" s="89">
         <f>(C9-C10)/C10</f>
-        <v>-0.30310824887587479</v>
+        <v>-0.30548282891923079</v>
       </c>
     </row>
   </sheetData>
@@ -5988,60 +5983,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="211" t="s">
+      <c r="C3" s="212" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="211"/>
-      <c r="E3" s="211"/>
-      <c r="F3" s="211"/>
-      <c r="G3" s="214"/>
-      <c r="H3" s="215" t="s">
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="213"/>
+      <c r="H3" s="214" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="211"/>
-      <c r="J3" s="211"/>
-      <c r="K3" s="211"/>
-      <c r="L3" s="211"/>
-      <c r="P3" s="217"/>
-      <c r="Q3" s="217"/>
-      <c r="R3" s="217"/>
-      <c r="S3" s="217"/>
-      <c r="T3" s="217"/>
-      <c r="U3" s="217"/>
-      <c r="V3" s="217"/>
-      <c r="W3" s="217"/>
-      <c r="X3" s="217"/>
-      <c r="Y3" s="217"/>
-      <c r="Z3" s="217"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212"/>
+      <c r="L3" s="212"/>
+      <c r="P3" s="215"/>
+      <c r="Q3" s="215"/>
+      <c r="R3" s="215"/>
+      <c r="S3" s="215"/>
+      <c r="T3" s="215"/>
+      <c r="U3" s="215"/>
+      <c r="V3" s="215"/>
+      <c r="W3" s="215"/>
+      <c r="X3" s="215"/>
+      <c r="Y3" s="215"/>
+      <c r="Z3" s="215"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="216" t="s">
+      <c r="C5" s="211" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="216"/>
-      <c r="E5" s="216"/>
-      <c r="F5" s="216"/>
-      <c r="G5" s="216"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="216"/>
-      <c r="J5" s="216"/>
-      <c r="K5" s="216"/>
-      <c r="L5" s="216"/>
-      <c r="P5" s="217"/>
-      <c r="Q5" s="217"/>
-      <c r="R5" s="217"/>
-      <c r="S5" s="217"/>
-      <c r="T5" s="217"/>
-      <c r="U5" s="217"/>
-      <c r="V5" s="217"/>
-      <c r="W5" s="217"/>
-      <c r="X5" s="217"/>
-      <c r="Y5" s="217"/>
-      <c r="Z5" s="217"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="211"/>
+      <c r="P5" s="215"/>
+      <c r="Q5" s="215"/>
+      <c r="R5" s="215"/>
+      <c r="S5" s="215"/>
+      <c r="T5" s="215"/>
+      <c r="U5" s="215"/>
+      <c r="V5" s="215"/>
+      <c r="W5" s="215"/>
+      <c r="X5" s="215"/>
+      <c r="Y5" s="215"/>
+      <c r="Z5" s="215"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -6270,10 +6265,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="218" t="s">
+      <c r="B14" s="208" t="s">
         <v>332</v>
       </c>
-      <c r="C14" s="219"/>
+      <c r="C14" s="209"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="193" t="s">
@@ -6281,7 +6276,7 @@
       </c>
       <c r="C15" s="194">
         <f>Overview!C3</f>
-        <v>292.48</v>
+        <v>293.48</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6300,20 +6295,20 @@
       <c r="C17" s="196">
         <v>0.26400000000000001</v>
       </c>
-      <c r="E17" s="220" t="s">
+      <c r="E17" s="210" t="s">
         <v>336</v>
       </c>
-      <c r="F17" s="220"/>
-      <c r="G17" s="220"/>
-      <c r="H17" s="220"/>
-      <c r="I17" s="220"/>
+      <c r="F17" s="210"/>
+      <c r="G17" s="210"/>
+      <c r="H17" s="210"/>
+      <c r="I17" s="210"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="218" t="s">
+      <c r="B19" s="208" t="s">
         <v>180</v>
       </c>
-      <c r="C19" s="219"/>
+      <c r="C19" s="209"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="197" t="s">
@@ -6347,7 +6342,7 @@
       </c>
       <c r="C23" s="200">
         <f>C15*C22</f>
-        <v>4295653.7600000007</v>
+        <v>4310340.7600000007</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6374,15 +6369,15 @@
       </c>
       <c r="C26" s="201">
         <f>C23+C25-C24</f>
-        <v>4233769.7600000007</v>
+        <v>4248456.7600000007</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="218" t="s">
+      <c r="B28" s="208" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="219"/>
+      <c r="C28" s="209"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="197" t="s">
@@ -6457,18 +6452,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="216" t="s">
+      <c r="C39" s="211" t="s">
         <v>338</v>
       </c>
-      <c r="D39" s="216"/>
-      <c r="E39" s="216"/>
-      <c r="F39" s="216"/>
-      <c r="G39" s="216"/>
-      <c r="H39" s="216"/>
-      <c r="I39" s="216"/>
-      <c r="J39" s="216"/>
-      <c r="K39" s="216"/>
-      <c r="L39" s="216"/>
+      <c r="D39" s="211"/>
+      <c r="E39" s="211"/>
+      <c r="F39" s="211"/>
+      <c r="G39" s="211"/>
+      <c r="H39" s="211"/>
+      <c r="I39" s="211"/>
+      <c r="J39" s="211"/>
+      <c r="K39" s="211"/>
+      <c r="L39" s="211"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="62">
@@ -6900,17 +6895,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -13295,11 +13290,11 @@
         <v>74</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="208" t="s">
+      <c r="P4" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="Q4" s="209"/>
-      <c r="R4" s="210"/>
+      <c r="Q4" s="217"/>
+      <c r="R4" s="218"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -23500,36 +23495,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="211" t="s">
+      <c r="C2" s="212" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="211"/>
-      <c r="E2" s="211"/>
-      <c r="F2" s="211"/>
-      <c r="G2" s="214"/>
-      <c r="H2" s="215" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="213"/>
+      <c r="H2" s="214" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="211"/>
-      <c r="J2" s="211"/>
-      <c r="K2" s="211"/>
-      <c r="L2" s="211"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
       <c r="O2" s="90"/>
-      <c r="S2" s="211" t="s">
+      <c r="S2" s="212" t="s">
         <v>104</v>
       </c>
-      <c r="T2" s="211"/>
-      <c r="U2" s="211"/>
-      <c r="V2" s="211"/>
-      <c r="W2" s="211"/>
-      <c r="X2" s="211"/>
-      <c r="Y2" s="211"/>
-      <c r="Z2" s="211"/>
-      <c r="AA2" s="211" t="s">
+      <c r="T2" s="212"/>
+      <c r="U2" s="212"/>
+      <c r="V2" s="212"/>
+      <c r="W2" s="212"/>
+      <c r="X2" s="212"/>
+      <c r="Y2" s="212"/>
+      <c r="Z2" s="212"/>
+      <c r="AA2" s="212" t="s">
         <v>105</v>
       </c>
-      <c r="AB2" s="211"/>
-      <c r="AC2" s="211"/>
+      <c r="AB2" s="212"/>
+      <c r="AC2" s="212"/>
       <c r="AE2" s="117" t="s">
         <v>74</v>
       </c>
@@ -23540,32 +23535,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="211" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="216"/>
-      <c r="E4" s="216"/>
-      <c r="F4" s="216"/>
-      <c r="G4" s="216"/>
-      <c r="H4" s="216"/>
-      <c r="I4" s="216"/>
-      <c r="J4" s="216"/>
-      <c r="K4" s="216"/>
-      <c r="L4" s="216"/>
+      <c r="D4" s="211"/>
+      <c r="E4" s="211"/>
+      <c r="F4" s="211"/>
+      <c r="G4" s="211"/>
+      <c r="H4" s="211"/>
+      <c r="I4" s="211"/>
+      <c r="J4" s="211"/>
+      <c r="K4" s="211"/>
+      <c r="L4" s="211"/>
       <c r="O4" s="90"/>
-      <c r="S4" s="212" t="s">
+      <c r="S4" s="219" t="s">
         <v>113</v>
       </c>
-      <c r="T4" s="213"/>
-      <c r="U4" s="213"/>
-      <c r="V4" s="213"/>
-      <c r="W4" s="213"/>
-      <c r="X4" s="213"/>
-      <c r="Y4" s="213"/>
-      <c r="Z4" s="213"/>
-      <c r="AA4" s="213"/>
-      <c r="AB4" s="213"/>
-      <c r="AC4" s="213"/>
+      <c r="T4" s="220"/>
+      <c r="U4" s="220"/>
+      <c r="V4" s="220"/>
+      <c r="W4" s="220"/>
+      <c r="X4" s="220"/>
+      <c r="Y4" s="220"/>
+      <c r="Z4" s="220"/>
+      <c r="AA4" s="220"/>
+      <c r="AB4" s="220"/>
+      <c r="AC4" s="220"/>
       <c r="AE4" s="119" t="s">
         <v>120</v>
       </c>
@@ -24241,33 +24236,33 @@
       <c r="Q12" s="91"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="216" t="s">
+      <c r="C13" s="211" t="s">
         <v>115</v>
       </c>
-      <c r="D13" s="216"/>
-      <c r="E13" s="216"/>
-      <c r="F13" s="216"/>
-      <c r="G13" s="216"/>
-      <c r="H13" s="216"/>
-      <c r="I13" s="216"/>
-      <c r="J13" s="216"/>
-      <c r="K13" s="216"/>
-      <c r="L13" s="216"/>
+      <c r="D13" s="211"/>
+      <c r="E13" s="211"/>
+      <c r="F13" s="211"/>
+      <c r="G13" s="211"/>
+      <c r="H13" s="211"/>
+      <c r="I13" s="211"/>
+      <c r="J13" s="211"/>
+      <c r="K13" s="211"/>
+      <c r="L13" s="211"/>
       <c r="O13" s="90"/>
       <c r="Q13" s="91"/>
-      <c r="S13" s="212" t="s">
+      <c r="S13" s="219" t="s">
         <v>115</v>
       </c>
-      <c r="T13" s="213"/>
-      <c r="U13" s="213"/>
-      <c r="V13" s="213"/>
-      <c r="W13" s="213"/>
-      <c r="X13" s="213"/>
-      <c r="Y13" s="213"/>
-      <c r="Z13" s="213"/>
-      <c r="AA13" s="213"/>
-      <c r="AB13" s="213"/>
-      <c r="AC13" s="213"/>
+      <c r="T13" s="220"/>
+      <c r="U13" s="220"/>
+      <c r="V13" s="220"/>
+      <c r="W13" s="220"/>
+      <c r="X13" s="220"/>
+      <c r="Y13" s="220"/>
+      <c r="Z13" s="220"/>
+      <c r="AA13" s="220"/>
+      <c r="AB13" s="220"/>
+      <c r="AC13" s="220"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
@@ -24849,35 +24844,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="100"/>
-      <c r="C2" s="211" t="s">
+      <c r="C2" s="212" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="211"/>
-      <c r="E2" s="211"/>
-      <c r="F2" s="211"/>
-      <c r="G2" s="214"/>
-      <c r="H2" s="215" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="213"/>
+      <c r="H2" s="214" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="211"/>
-      <c r="J2" s="211"/>
-      <c r="K2" s="211"/>
-      <c r="L2" s="211"/>
-      <c r="P2" s="211" t="s">
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
+      <c r="P2" s="212" t="s">
         <v>104</v>
       </c>
-      <c r="Q2" s="211"/>
-      <c r="R2" s="211"/>
-      <c r="S2" s="211"/>
-      <c r="T2" s="211"/>
-      <c r="U2" s="211"/>
-      <c r="V2" s="211"/>
-      <c r="W2" s="211"/>
-      <c r="X2" s="211" t="s">
+      <c r="Q2" s="212"/>
+      <c r="R2" s="212"/>
+      <c r="S2" s="212"/>
+      <c r="T2" s="212"/>
+      <c r="U2" s="212"/>
+      <c r="V2" s="212"/>
+      <c r="W2" s="212"/>
+      <c r="X2" s="212" t="s">
         <v>105</v>
       </c>
-      <c r="Y2" s="211"/>
-      <c r="Z2" s="211"/>
+      <c r="Y2" s="212"/>
+      <c r="Z2" s="212"/>
       <c r="AB2" s="117" t="s">
         <v>74</v>
       </c>
@@ -24886,31 +24881,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105"/>
       <c r="B4" s="92"/>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="211" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="216"/>
-      <c r="E4" s="216"/>
-      <c r="F4" s="216"/>
-      <c r="G4" s="216"/>
-      <c r="H4" s="216"/>
-      <c r="I4" s="216"/>
-      <c r="J4" s="216"/>
-      <c r="K4" s="216"/>
-      <c r="L4" s="216"/>
-      <c r="P4" s="213" t="s">
+      <c r="D4" s="211"/>
+      <c r="E4" s="211"/>
+      <c r="F4" s="211"/>
+      <c r="G4" s="211"/>
+      <c r="H4" s="211"/>
+      <c r="I4" s="211"/>
+      <c r="J4" s="211"/>
+      <c r="K4" s="211"/>
+      <c r="L4" s="211"/>
+      <c r="P4" s="220" t="s">
         <v>113</v>
       </c>
-      <c r="Q4" s="213"/>
-      <c r="R4" s="213"/>
-      <c r="S4" s="213"/>
-      <c r="T4" s="213"/>
-      <c r="U4" s="213"/>
-      <c r="V4" s="213"/>
-      <c r="W4" s="213"/>
-      <c r="X4" s="213"/>
-      <c r="Y4" s="213"/>
-      <c r="Z4" s="213"/>
+      <c r="Q4" s="220"/>
+      <c r="R4" s="220"/>
+      <c r="S4" s="220"/>
+      <c r="T4" s="220"/>
+      <c r="U4" s="220"/>
+      <c r="V4" s="220"/>
+      <c r="W4" s="220"/>
+      <c r="X4" s="220"/>
+      <c r="Y4" s="220"/>
+      <c r="Z4" s="220"/>
       <c r="AB4" s="119" t="s">
         <v>120</v>
       </c>
@@ -25111,32 +25106,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="216" t="s">
+      <c r="C9" s="211" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="216"/>
-      <c r="E9" s="216"/>
-      <c r="F9" s="216"/>
-      <c r="G9" s="216"/>
-      <c r="H9" s="216"/>
-      <c r="I9" s="216"/>
-      <c r="J9" s="216"/>
-      <c r="K9" s="216"/>
-      <c r="L9" s="216"/>
+      <c r="D9" s="211"/>
+      <c r="E9" s="211"/>
+      <c r="F9" s="211"/>
+      <c r="G9" s="211"/>
+      <c r="H9" s="211"/>
+      <c r="I9" s="211"/>
+      <c r="J9" s="211"/>
+      <c r="K9" s="211"/>
+      <c r="L9" s="211"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="213" t="s">
+      <c r="P9" s="220" t="s">
         <v>127</v>
       </c>
-      <c r="Q9" s="213"/>
-      <c r="R9" s="213"/>
-      <c r="S9" s="213"/>
-      <c r="T9" s="213"/>
-      <c r="U9" s="213"/>
-      <c r="V9" s="213"/>
-      <c r="W9" s="213"/>
-      <c r="X9" s="213"/>
-      <c r="Y9" s="213"/>
-      <c r="Z9" s="213"/>
+      <c r="Q9" s="220"/>
+      <c r="R9" s="220"/>
+      <c r="S9" s="220"/>
+      <c r="T9" s="220"/>
+      <c r="U9" s="220"/>
+      <c r="V9" s="220"/>
+      <c r="W9" s="220"/>
+      <c r="X9" s="220"/>
+      <c r="Y9" s="220"/>
+      <c r="Z9" s="220"/>
       <c r="AB9" s="119" t="str">
         <f>AB4</f>
         <v>Q1-Q2-Q3</v>
@@ -25606,31 +25601,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="216" t="s">
+      <c r="C17" s="211" t="s">
         <v>125</v>
       </c>
-      <c r="D17" s="216"/>
-      <c r="E17" s="216"/>
-      <c r="F17" s="216"/>
-      <c r="G17" s="216"/>
-      <c r="H17" s="216"/>
-      <c r="I17" s="216"/>
-      <c r="J17" s="216"/>
-      <c r="K17" s="216"/>
-      <c r="L17" s="216"/>
-      <c r="P17" s="213" t="s">
+      <c r="D17" s="211"/>
+      <c r="E17" s="211"/>
+      <c r="F17" s="211"/>
+      <c r="G17" s="211"/>
+      <c r="H17" s="211"/>
+      <c r="I17" s="211"/>
+      <c r="J17" s="211"/>
+      <c r="K17" s="211"/>
+      <c r="L17" s="211"/>
+      <c r="P17" s="220" t="s">
         <v>125</v>
       </c>
-      <c r="Q17" s="213"/>
-      <c r="R17" s="213"/>
-      <c r="S17" s="213"/>
-      <c r="T17" s="213"/>
-      <c r="U17" s="213"/>
-      <c r="V17" s="213"/>
-      <c r="W17" s="213"/>
-      <c r="X17" s="213"/>
-      <c r="Y17" s="213"/>
-      <c r="Z17" s="213"/>
+      <c r="Q17" s="220"/>
+      <c r="R17" s="220"/>
+      <c r="S17" s="220"/>
+      <c r="T17" s="220"/>
+      <c r="U17" s="220"/>
+      <c r="V17" s="220"/>
+      <c r="W17" s="220"/>
+      <c r="X17" s="220"/>
+      <c r="Y17" s="220"/>
+      <c r="Z17" s="220"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="7" t="s">
@@ -26020,60 +26015,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="100"/>
-      <c r="C3" s="211" t="s">
+      <c r="C3" s="212" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="211"/>
-      <c r="E3" s="211"/>
-      <c r="F3" s="211"/>
-      <c r="G3" s="214"/>
-      <c r="H3" s="215" t="s">
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="213"/>
+      <c r="H3" s="214" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="211"/>
-      <c r="J3" s="211"/>
-      <c r="K3" s="211"/>
-      <c r="L3" s="211"/>
-      <c r="P3" s="217"/>
-      <c r="Q3" s="217"/>
-      <c r="R3" s="217"/>
-      <c r="S3" s="217"/>
-      <c r="T3" s="217"/>
-      <c r="U3" s="217"/>
-      <c r="V3" s="217"/>
-      <c r="W3" s="217"/>
-      <c r="X3" s="217"/>
-      <c r="Y3" s="217"/>
-      <c r="Z3" s="217"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212"/>
+      <c r="L3" s="212"/>
+      <c r="P3" s="215"/>
+      <c r="Q3" s="215"/>
+      <c r="R3" s="215"/>
+      <c r="S3" s="215"/>
+      <c r="T3" s="215"/>
+      <c r="U3" s="215"/>
+      <c r="V3" s="215"/>
+      <c r="W3" s="215"/>
+      <c r="X3" s="215"/>
+      <c r="Y3" s="215"/>
+      <c r="Z3" s="215"/>
       <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105"/>
       <c r="B5" s="92"/>
-      <c r="C5" s="216" t="s">
+      <c r="C5" s="211" t="s">
         <v>113</v>
       </c>
-      <c r="D5" s="216"/>
-      <c r="E5" s="216"/>
-      <c r="F5" s="216"/>
-      <c r="G5" s="216"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="216"/>
-      <c r="J5" s="216"/>
-      <c r="K5" s="216"/>
-      <c r="L5" s="216"/>
-      <c r="P5" s="217"/>
-      <c r="Q5" s="217"/>
-      <c r="R5" s="217"/>
-      <c r="S5" s="217"/>
-      <c r="T5" s="217"/>
-      <c r="U5" s="217"/>
-      <c r="V5" s="217"/>
-      <c r="W5" s="217"/>
-      <c r="X5" s="217"/>
-      <c r="Y5" s="217"/>
-      <c r="Z5" s="217"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="211"/>
+      <c r="P5" s="215"/>
+      <c r="Q5" s="215"/>
+      <c r="R5" s="215"/>
+      <c r="S5" s="215"/>
+      <c r="T5" s="215"/>
+      <c r="U5" s="215"/>
+      <c r="V5" s="215"/>
+      <c r="W5" s="215"/>
+      <c r="X5" s="215"/>
+      <c r="Y5" s="215"/>
+      <c r="Z5" s="215"/>
       <c r="AB5" s="123"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -26259,30 +26254,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="216" t="s">
+      <c r="C11" s="211" t="s">
         <v>133</v>
       </c>
-      <c r="D11" s="216"/>
-      <c r="E11" s="216"/>
-      <c r="F11" s="216"/>
-      <c r="G11" s="216"/>
-      <c r="H11" s="216"/>
-      <c r="I11" s="216"/>
-      <c r="J11" s="216"/>
-      <c r="K11" s="216"/>
-      <c r="L11" s="216"/>
+      <c r="D11" s="211"/>
+      <c r="E11" s="211"/>
+      <c r="F11" s="211"/>
+      <c r="G11" s="211"/>
+      <c r="H11" s="211"/>
+      <c r="I11" s="211"/>
+      <c r="J11" s="211"/>
+      <c r="K11" s="211"/>
+      <c r="L11" s="211"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="217"/>
-      <c r="Q11" s="217"/>
-      <c r="R11" s="217"/>
-      <c r="S11" s="217"/>
-      <c r="T11" s="217"/>
-      <c r="U11" s="217"/>
-      <c r="V11" s="217"/>
-      <c r="W11" s="217"/>
-      <c r="X11" s="217"/>
-      <c r="Y11" s="217"/>
-      <c r="Z11" s="217"/>
+      <c r="P11" s="215"/>
+      <c r="Q11" s="215"/>
+      <c r="R11" s="215"/>
+      <c r="S11" s="215"/>
+      <c r="T11" s="215"/>
+      <c r="U11" s="215"/>
+      <c r="V11" s="215"/>
+      <c r="W11" s="215"/>
+      <c r="X11" s="215"/>
+      <c r="Y11" s="215"/>
+      <c r="Z11" s="215"/>
       <c r="AB11" s="123"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -26524,18 +26519,18 @@
       <c r="D16" s="20"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="216" t="s">
+      <c r="C18" s="211" t="s">
         <v>140</v>
       </c>
-      <c r="D18" s="216"/>
-      <c r="E18" s="216"/>
-      <c r="F18" s="216"/>
-      <c r="G18" s="216"/>
-      <c r="H18" s="216"/>
-      <c r="I18" s="216"/>
-      <c r="J18" s="216"/>
-      <c r="K18" s="216"/>
-      <c r="L18" s="216"/>
+      <c r="D18" s="211"/>
+      <c r="E18" s="211"/>
+      <c r="F18" s="211"/>
+      <c r="G18" s="211"/>
+      <c r="H18" s="211"/>
+      <c r="I18" s="211"/>
+      <c r="J18" s="211"/>
+      <c r="K18" s="211"/>
+      <c r="L18" s="211"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -26748,23 +26743,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="217"/>
-      <c r="C25" s="217"/>
+      <c r="B25" s="215"/>
+      <c r="C25" s="215"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="122"/>
-      <c r="C26" s="216" t="s">
+      <c r="C26" s="211" t="s">
         <v>300</v>
       </c>
-      <c r="D26" s="216"/>
-      <c r="E26" s="216"/>
-      <c r="F26" s="216"/>
-      <c r="G26" s="216"/>
-      <c r="H26" s="216"/>
-      <c r="I26" s="216"/>
-      <c r="J26" s="216"/>
-      <c r="K26" s="216"/>
-      <c r="L26" s="216"/>
+      <c r="D26" s="211"/>
+      <c r="E26" s="211"/>
+      <c r="F26" s="211"/>
+      <c r="G26" s="211"/>
+      <c r="H26" s="211"/>
+      <c r="I26" s="211"/>
+      <c r="J26" s="211"/>
+      <c r="K26" s="211"/>
+      <c r="L26" s="211"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
@@ -26956,18 +26951,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="122"/>
-      <c r="C33" s="216" t="s">
+      <c r="C33" s="211" t="s">
         <v>303</v>
       </c>
-      <c r="D33" s="216"/>
-      <c r="E33" s="216"/>
-      <c r="F33" s="216"/>
-      <c r="G33" s="216"/>
-      <c r="H33" s="216"/>
-      <c r="I33" s="216"/>
-      <c r="J33" s="216"/>
-      <c r="K33" s="216"/>
-      <c r="L33" s="216"/>
+      <c r="D33" s="211"/>
+      <c r="E33" s="211"/>
+      <c r="F33" s="211"/>
+      <c r="G33" s="211"/>
+      <c r="H33" s="211"/>
+      <c r="I33" s="211"/>
+      <c r="J33" s="211"/>
+      <c r="K33" s="211"/>
+      <c r="L33" s="211"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
@@ -27151,18 +27146,18 @@
       <c r="C39" s="131"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="216" t="s">
+      <c r="C40" s="211" t="s">
         <v>306</v>
       </c>
-      <c r="D40" s="216"/>
-      <c r="E40" s="216"/>
-      <c r="F40" s="216"/>
-      <c r="G40" s="216"/>
-      <c r="H40" s="216"/>
-      <c r="I40" s="216"/>
-      <c r="J40" s="216"/>
-      <c r="K40" s="216"/>
-      <c r="L40" s="216"/>
+      <c r="D40" s="211"/>
+      <c r="E40" s="211"/>
+      <c r="F40" s="211"/>
+      <c r="G40" s="211"/>
+      <c r="H40" s="211"/>
+      <c r="I40" s="211"/>
+      <c r="J40" s="211"/>
+      <c r="K40" s="211"/>
+      <c r="L40" s="211"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
@@ -27426,12 +27421,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -27439,6 +27428,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/AAPL.xlsx
+++ b/AAPL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03DD2411-50DF-9E4A-BF73-208FE750533F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF684A7F-51CC-D14A-9613-4BC650C4DB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -117,7 +117,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -128,28 +128,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -159,21 +138,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2311,9 +2281,12 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="38" fontId="9" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="23" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2323,6 +2296,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2330,12 +2312,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2365,12 +2341,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="23" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15400,7 +15370,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1mou2&amp;q=XNAS%3aAAPL&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -15418,10 +15388,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>317.39999999999998</v>
-    <v>198.96</v>
-    <v>1.0922000000000001</v>
-    <v>1.76</v>
-    <v>5.9059999999999998E-3</v>
+    <v>199.26070000000001</v>
+    <v>1.0964</v>
+    <v>-17.93</v>
+    <v>-6.1177999999999996E-2</v>
+    <v>0</v>
+    <v>0</v>
     <v>USD</v>
     <v>Apple Inc. designs, manufactures and markets smartphones, personal computers, tablets, wearables and accessories, and sells a variety of related services. Its product categories include iPhone, Mac, iPad, Wearables, Home and Accessories. Its services include advertising, AppleCare, cloud services, digital content, and payment services. The Company operates various platforms, including the App Store, that allow customers to discover and download applications and digital content, such as books, music, video, games and podcasts. It also offers digital content through subscription-based services, including Apple Arcade, Apple Fitness+, Apple Music, Apple News+, and Apple TV+. Its wearables include smartwatches, wireless headphones, and spatial computers. Its products include iPhone 16 Pro, iPhone 16, iPhone 15, iPhone 14, iPhone SE, MacBook Air, MacBook Pro, iMac, Mac mini, Mac Studio, Mac Pro, iPad Pro, iPad Air, AirPods, AirPods Pro, AirPods Max, Apple TV, Apple Vision Pro and others.</v>
     <v>166000</v>
@@ -15429,49 +15401,35 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Apple Park Way, CUPERTINO, CA, 95014 US</v>
-    <v>302.42</v>
+    <v>288.8</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46195.614923784378</v>
+    <v>46198.910747233596</v>
     <v>0</v>
-    <v>297.33999999999997</v>
-    <v>4402829907200</v>
+    <v>273.75</v>
+    <v>4041227103999</v>
     <v>APPLE INC.</v>
     <v>APPLE INC.</v>
-    <v>297.85000000000002</v>
-    <v>36.407200000000003</v>
-    <v>298.01</v>
-    <v>299.77</v>
+    <v>287.39999999999998</v>
+    <v>33.417099999999998</v>
+    <v>293.08</v>
+    <v>275.14999999999998</v>
+    <v>275.14999999999998</v>
     <v>14687360000</v>
     <v>AAPL</v>
     <v>APPLE INC. (XNAS:AAPL)</v>
-    <v>10024972</v>
-    <v>50375269</v>
+    <v>106976285</v>
+    <v>51387349</v>
     <v>1977</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -15485,28 +15443,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.12</v>
-    <v>-2.6889999999999996E-3</v>
+    <v>-0.91</v>
+    <v>-2.0253999999999998E-2</v>
     <v>US</v>
-    <v>44.53</v>
+    <v>44.55</v>
     <v>Index</v>
-    <v>6</v>
-    <v>44.2</v>
+    <v>3</v>
+    <v>43.98</v>
     <v>10 Y TSY YLD NDX</v>
     <v>44.53</v>
-    <v>44.63</v>
-    <v>44.51</v>
+    <v>44.93</v>
+    <v>44.02</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -15528,6 +15486,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -15548,6 +15508,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -15557,11 +15518,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -15597,7 +15553,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -15608,13 +15564,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -15708,13 +15667,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -15786,6 +15751,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -15793,6 +15761,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -16277,18 +16248,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="227" t="s">
+      <c r="B2" s="232" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="228"/>
-      <c r="E2" s="227" t="s">
+      <c r="C2" s="233"/>
+      <c r="E2" s="232" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="228"/>
-      <c r="H2" s="227" t="s">
+      <c r="F2" s="233"/>
+      <c r="H2" s="232" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="228"/>
+      <c r="I2" s="233"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="182" t="s">
@@ -16303,7 +16274,7 @@
       </c>
       <c r="F3" s="184">
         <f ca="1">Statement!AC143</f>
-        <v>4418609.8</v>
+        <v>4055710.9999999995</v>
       </c>
       <c r="H3" s="182" t="str">
         <f>'AVG target price'!B5</f>
@@ -16311,7 +16282,7 @@
       </c>
       <c r="I3" s="208">
         <f ca="1">'AVG target price'!C5</f>
-        <v>119.29441062988022</v>
+        <v>119.93072905261404</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16327,7 +16298,7 @@
       </c>
       <c r="F4" s="185">
         <f ca="1">Statement!AC144</f>
-        <v>4356725.8</v>
+        <v>3993826.9999999995</v>
       </c>
       <c r="H4" s="182" t="str">
         <f>'AVG target price'!B6</f>
@@ -16335,7 +16306,7 @@
       </c>
       <c r="I4" s="208">
         <f ca="1">'AVG target price'!C6</f>
-        <v>191.07494748443645</v>
+        <v>191.41111102679096</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16344,7 +16315,7 @@
       </c>
       <c r="C5" s="205" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>299.77</v>
+        <v>275.14999999999998</v>
       </c>
       <c r="E5" s="182" t="s">
         <v>242</v>
@@ -16366,16 +16337,16 @@
       <c r="B6" s="182" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="205" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="205" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>275.14999999999998</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="187">
         <f ca="1">Statement!AC140</f>
-        <v>36.247883917775091</v>
+        <v>33.270858524788387</v>
       </c>
       <c r="H6" s="182" t="str">
         <f>'AVG target price'!B8</f>
@@ -16383,7 +16354,7 @@
       </c>
       <c r="I6" s="208">
         <f ca="1">'AVG target price'!C8</f>
-        <v>122.08758570789347</v>
+        <v>122.30090520877316</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16392,14 +16363,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>1.76</v>
+        <v>-17.93</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>198</v>
       </c>
       <c r="F7" s="188">
         <f ca="1">Statement!AC141</f>
-        <v>9.8521792168207654</v>
+        <v>9.0430233562672502</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -16407,23 +16378,23 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>142.78609402713997</v>
+        <v>143.08254439363199</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="182" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="189">
         <f ca="1">Statement!AC151</f>
-        <v>2.6184932645557435E-2</v>
+        <v>2.8527920258618035E-2</v>
       </c>
       <c r="H8" s="181" t="str">
         <f>'AVG target price'!B11</f>
@@ -16431,7 +16402,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.52368117547739945</v>
+        <v>-0.47998348394100671</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16440,30 +16411,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>5.9059999999999998E-3</v>
+        <v>-6.1177999999999996E-2</v>
       </c>
       <c r="E9" s="182" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="189">
         <f ca="1">Statement!AC152</f>
-        <v>2.7587817326617074E-2</v>
+        <v>3.0056332909322189E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="182" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>0</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="189">
         <f ca="1">Statement!AC154</f>
-        <v>1.76969688520584E-2</v>
+        <v>1.9280466482942203E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -16479,7 +16450,7 @@
       </c>
       <c r="F11" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>3.4693264836374556E-3</v>
+        <v>3.7797564964564788E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -16488,7 +16459,7 @@
       </c>
       <c r="C12" s="206" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>198.96</v>
+        <v>199.26070000000001</v>
       </c>
       <c r="E12" s="182" t="s">
         <v>99</v>
@@ -16504,7 +16475,7 @@
       </c>
       <c r="C13" s="206" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0922000000000001</v>
+        <v>1.0964</v>
       </c>
       <c r="E13" s="182" t="s">
         <v>101</v>
@@ -16520,7 +16491,7 @@
       </c>
       <c r="C14" s="207" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>50375269</v>
+        <v>51387349</v>
       </c>
       <c r="E14" s="183" t="s">
         <v>102</v>
@@ -16536,7 +16507,7 @@
       </c>
       <c r="F15" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.400530999591772E-2</v>
+        <v>1.5258483654284047E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -16549,10 +16520,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="229" t="s">
+      <c r="B17" s="234" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="229"/>
+      <c r="C17" s="234"/>
       <c r="E17" s="181" t="s">
         <v>295</v>
       </c>
@@ -16625,14 +16596,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="229" t="s">
+      <c r="B25" s="234" t="s">
         <v>104</v>
       </c>
-      <c r="C25" s="229"/>
-      <c r="E25" s="227" t="s">
+      <c r="C25" s="234"/>
+      <c r="E25" s="232" t="s">
         <v>342</v>
       </c>
-      <c r="F25" s="228"/>
+      <c r="F25" s="233"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="181" t="s">
@@ -16641,12 +16612,12 @@
       <c r="C26" s="167">
         <v>0.21</v>
       </c>
-      <c r="E26" s="182" t="e" vm="5">
+      <c r="E26" s="182" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="216" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.51</v>
+        <v>44.02</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16661,7 +16632,7 @@
       </c>
       <c r="F27" s="217">
         <f ca="1">F26/1000</f>
-        <v>4.4510000000000001E-2</v>
+        <v>4.4020000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16681,15 +16652,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="226" t="s">
+      <c r="B33" s="235" t="s">
         <v>337</v>
       </c>
-      <c r="C33" s="226"/>
-      <c r="D33" s="226"/>
-      <c r="E33" s="226"/>
-      <c r="F33" s="226"/>
-      <c r="G33" s="226"/>
-      <c r="H33" s="226"/>
+      <c r="C33" s="235"/>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="235"/>
+      <c r="H33" s="235"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -16702,24 +16673,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="226"/>
-      <c r="C39" s="226"/>
-      <c r="D39" s="226"/>
-      <c r="E39" s="226"/>
-      <c r="F39" s="226"/>
-      <c r="G39" s="226"/>
-      <c r="H39" s="226"/>
+      <c r="B39" s="235"/>
+      <c r="C39" s="235"/>
+      <c r="D39" s="235"/>
+      <c r="E39" s="235"/>
+      <c r="F39" s="235"/>
+      <c r="G39" s="235"/>
+      <c r="H39" s="235"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="226" t="s">
+      <c r="B42" s="235" t="s">
         <v>340</v>
       </c>
-      <c r="C42" s="226"/>
-      <c r="D42" s="226"/>
-      <c r="E42" s="226"/>
-      <c r="F42" s="226"/>
-      <c r="G42" s="226"/>
-      <c r="H42" s="226"/>
+      <c r="C42" s="235"/>
+      <c r="D42" s="235"/>
+      <c r="E42" s="235"/>
+      <c r="F42" s="235"/>
+      <c r="G42" s="235"/>
+      <c r="H42" s="235"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -16734,24 +16705,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="226"/>
-      <c r="C49" s="226"/>
-      <c r="D49" s="226"/>
-      <c r="E49" s="226"/>
-      <c r="F49" s="226"/>
-      <c r="G49" s="226"/>
-      <c r="H49" s="226"/>
+      <c r="B49" s="235"/>
+      <c r="C49" s="235"/>
+      <c r="D49" s="235"/>
+      <c r="E49" s="235"/>
+      <c r="F49" s="235"/>
+      <c r="G49" s="235"/>
+      <c r="H49" s="235"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="226" t="s">
+      <c r="B52" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="C52" s="226"/>
-      <c r="D52" s="226"/>
-      <c r="E52" s="226"/>
-      <c r="F52" s="226"/>
-      <c r="G52" s="226"/>
-      <c r="H52" s="226"/>
+      <c r="C52" s="235"/>
+      <c r="D52" s="235"/>
+      <c r="E52" s="235"/>
+      <c r="F52" s="235"/>
+      <c r="G52" s="235"/>
+      <c r="H52" s="235"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -16766,28 +16737,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="226"/>
-      <c r="C59" s="226"/>
-      <c r="D59" s="226"/>
-      <c r="E59" s="226"/>
-      <c r="F59" s="226"/>
-      <c r="G59" s="226"/>
-      <c r="H59" s="226"/>
+      <c r="B59" s="235"/>
+      <c r="C59" s="235"/>
+      <c r="D59" s="235"/>
+      <c r="E59" s="235"/>
+      <c r="F59" s="235"/>
+      <c r="G59" s="235"/>
+      <c r="H59" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -16857,36 +16828,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="226" t="s">
+      <c r="C2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="226"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="226" t="s">
+      <c r="S2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="T2" s="226"/>
-      <c r="U2" s="226"/>
-      <c r="V2" s="226"/>
-      <c r="W2" s="226"/>
-      <c r="X2" s="226"/>
-      <c r="Y2" s="226"/>
-      <c r="Z2" s="226"/>
-      <c r="AA2" s="226" t="s">
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
+      <c r="AA2" s="235" t="s">
         <v>111</v>
       </c>
-      <c r="AB2" s="226"/>
-      <c r="AC2" s="226"/>
+      <c r="AB2" s="235"/>
+      <c r="AC2" s="235"/>
       <c r="AE2" s="85" t="s">
         <v>112</v>
       </c>
@@ -16897,32 +16868,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="235" t="s">
+      <c r="C4" s="241" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="235"/>
-      <c r="E4" s="235"/>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
-      <c r="H4" s="235"/>
-      <c r="I4" s="235"/>
-      <c r="J4" s="235"/>
-      <c r="K4" s="235"/>
-      <c r="L4" s="235"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="236" t="s">
+      <c r="S4" s="242" t="s">
         <v>113</v>
       </c>
-      <c r="T4" s="237"/>
-      <c r="U4" s="237"/>
-      <c r="V4" s="237"/>
-      <c r="W4" s="237"/>
-      <c r="X4" s="237"/>
-      <c r="Y4" s="237"/>
-      <c r="Z4" s="237"/>
-      <c r="AA4" s="237"/>
-      <c r="AB4" s="237"/>
-      <c r="AC4" s="237"/>
+      <c r="T4" s="243"/>
+      <c r="U4" s="243"/>
+      <c r="V4" s="243"/>
+      <c r="W4" s="243"/>
+      <c r="X4" s="243"/>
+      <c r="Y4" s="243"/>
+      <c r="Z4" s="243"/>
+      <c r="AA4" s="243"/>
+      <c r="AB4" s="243"/>
+      <c r="AC4" s="243"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -17243,7 +17214,7 @@
         <v>28023</v>
       </c>
       <c r="H8" s="64">
-        <f t="shared" ref="H8:L10" si="5">G8*(1+H17)</f>
+        <f t="shared" ref="H8:I10" si="5">G8*(1+H17)</f>
         <v>28863.690000000002</v>
       </c>
       <c r="I8" s="64">
@@ -17610,33 +17581,33 @@
       <c r="Q12" s="91"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="235" t="s">
+      <c r="C13" s="241" t="s">
         <v>119</v>
       </c>
-      <c r="D13" s="235"/>
-      <c r="E13" s="235"/>
-      <c r="F13" s="235"/>
-      <c r="G13" s="235"/>
-      <c r="H13" s="235"/>
-      <c r="I13" s="235"/>
-      <c r="J13" s="235"/>
-      <c r="K13" s="235"/>
-      <c r="L13" s="235"/>
+      <c r="D13" s="241"/>
+      <c r="E13" s="241"/>
+      <c r="F13" s="241"/>
+      <c r="G13" s="241"/>
+      <c r="H13" s="241"/>
+      <c r="I13" s="241"/>
+      <c r="J13" s="241"/>
+      <c r="K13" s="241"/>
+      <c r="L13" s="241"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="91"/>
-      <c r="S13" s="236" t="s">
+      <c r="S13" s="242" t="s">
         <v>119</v>
       </c>
-      <c r="T13" s="237"/>
-      <c r="U13" s="237"/>
-      <c r="V13" s="237"/>
-      <c r="W13" s="237"/>
-      <c r="X13" s="237"/>
-      <c r="Y13" s="237"/>
-      <c r="Z13" s="237"/>
-      <c r="AA13" s="237"/>
-      <c r="AB13" s="237"/>
-      <c r="AC13" s="237"/>
+      <c r="T13" s="243"/>
+      <c r="U13" s="243"/>
+      <c r="V13" s="243"/>
+      <c r="W13" s="243"/>
+      <c r="X13" s="243"/>
+      <c r="Y13" s="243"/>
+      <c r="Z13" s="243"/>
+      <c r="AA13" s="243"/>
+      <c r="AB13" s="243"/>
+      <c r="AC13" s="243"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -17777,31 +17748,31 @@
       </c>
       <c r="S15" s="47"/>
       <c r="T15" s="95">
-        <f>T6/S6-1</f>
+        <f t="shared" ref="T15:Z16" si="12">T6/S6-1</f>
         <v>0.17625203583061899</v>
       </c>
       <c r="U15" s="95">
-        <f>U6/T6-1</f>
+        <f t="shared" si="12"/>
         <v>0.49578122971745064</v>
       </c>
       <c r="V15" s="95">
-        <f>V6/U6-1</f>
+        <f t="shared" si="12"/>
         <v>-0.3224999276808701</v>
       </c>
       <c r="W15" s="95">
-        <f>W6/V6-1</f>
+        <f t="shared" si="12"/>
         <v>-4.8226980636621786E-2</v>
       </c>
       <c r="X15" s="95">
-        <f>X6/W6-1</f>
+        <f t="shared" si="12"/>
         <v>9.9659055224081472E-2</v>
       </c>
       <c r="Y15" s="95">
-        <f>Y6/X6-1</f>
+        <f t="shared" si="12"/>
         <v>0.73929627740948489</v>
       </c>
       <c r="Z15" s="96">
-        <f>Z6/Y6-1</f>
+        <f t="shared" si="12"/>
         <v>-0.33159764979066253</v>
       </c>
       <c r="AA15" s="97">
@@ -17817,19 +17788,19 @@
       </c>
       <c r="C16" s="47"/>
       <c r="D16" s="95">
-        <f t="shared" ref="D16:G19" si="12">D7/C7-1</f>
+        <f t="shared" ref="D16:G19" si="13">D7/C7-1</f>
         <v>0.14171639670360903</v>
       </c>
       <c r="E16" s="95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-0.26930831072504169</v>
       </c>
       <c r="F16" s="95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.1357768164322E-2</v>
       </c>
       <c r="G16" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.12419957310565644</v>
       </c>
       <c r="H16" s="97">
@@ -17855,31 +17826,31 @@
       </c>
       <c r="S16" s="47"/>
       <c r="T16" s="95">
-        <f>T7/S7-1</f>
+        <f t="shared" si="12"/>
         <v>0.10486517334855194</v>
       </c>
       <c r="U16" s="95">
-        <f>U7/T7-1</f>
+        <f t="shared" si="12"/>
         <v>0.16051136363636354</v>
       </c>
       <c r="V16" s="95">
-        <f>V7/U7-1</f>
+        <f t="shared" si="12"/>
         <v>-0.11550016690775566</v>
       </c>
       <c r="W16" s="95">
-        <f>W7/V7-1</f>
+        <f t="shared" si="12"/>
         <v>1.2202792804126394E-2</v>
       </c>
       <c r="X16" s="95">
-        <f>X7/W7-1</f>
+        <f t="shared" si="12"/>
         <v>8.4514044245587838E-2</v>
       </c>
       <c r="Y16" s="95">
-        <f>Y7/X7-1</f>
+        <f t="shared" si="12"/>
         <v>-3.8964015585606249E-2</v>
       </c>
       <c r="Z16" s="96">
-        <f>Z7/Y7-1</f>
+        <f t="shared" si="12"/>
         <v>1.5502027188170064E-3</v>
       </c>
       <c r="AA16" s="97">
@@ -17895,19 +17866,19 @@
       </c>
       <c r="C17" s="47"/>
       <c r="D17" s="95">
-        <f t="shared" ref="D17:G17" si="13">D8/C8-1</f>
+        <f t="shared" ref="D17" si="14">D8/C8-1</f>
         <v>-8.0660347749670458E-2</v>
       </c>
       <c r="E17" s="95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-3.3865901952751631E-2</v>
       </c>
       <c r="F17" s="95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-5.674911660777382E-2</v>
       </c>
       <c r="G17" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.9786468869408962E-2</v>
       </c>
       <c r="H17" s="97">
@@ -17937,27 +17908,27 @@
         <v>-2.9600670203853707E-2</v>
       </c>
       <c r="U17" s="95">
-        <f t="shared" ref="U17:Z17" si="14">U8/T8-1</f>
+        <f t="shared" ref="U17:Z17" si="15">U8/T8-1</f>
         <v>0.16374100719424467</v>
       </c>
       <c r="V17" s="95">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-0.20845697329376855</v>
       </c>
       <c r="W17" s="95">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.7960012496095032E-2</v>
       </c>
       <c r="X17" s="95">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.6374411183710782E-2</v>
       </c>
       <c r="Y17" s="95">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.2363348676639816</v>
       </c>
       <c r="Z17" s="96">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-0.19557882489819667</v>
       </c>
       <c r="AA17" s="97">
@@ -17968,24 +17939,24 @@
     </row>
     <row r="18" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="str">
-        <f t="shared" ref="B18:B19" si="15">B9</f>
+        <f t="shared" ref="B18:B19" si="16">B9</f>
         <v>Wearables, Home, Accessories</v>
       </c>
       <c r="C18" s="47"/>
       <c r="D18" s="95">
-        <f t="shared" ref="D18:D19" si="16">D9/C9-1</f>
+        <f t="shared" ref="D18:D19" si="17">D9/C9-1</f>
         <v>7.4908124169208001E-2</v>
       </c>
       <c r="E18" s="95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-3.3849809655439933E-2</v>
       </c>
       <c r="F18" s="95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-7.1276195256619435E-2</v>
       </c>
       <c r="G18" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-3.5643831914606183E-2</v>
       </c>
       <c r="H18" s="97">
@@ -18006,36 +17977,36 @@
       <c r="O18" s="5"/>
       <c r="Q18" s="91"/>
       <c r="R18" s="1" t="str">
-        <f t="shared" ref="R18:R19" si="17">R9</f>
+        <f t="shared" ref="R18:R19" si="18">R9</f>
         <v>Wearables, Home, Accessories</v>
       </c>
       <c r="S18" s="47"/>
       <c r="T18" s="95">
-        <f t="shared" ref="T18:Z18" si="18">T9/S9-1</f>
+        <f t="shared" ref="T18:Z18" si="19">T9/S9-1</f>
         <v>0.1167098925527974</v>
       </c>
       <c r="U18" s="95">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.2991594779915947</v>
       </c>
       <c r="V18" s="95">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.35966629777815617</v>
       </c>
       <c r="W18" s="95">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-1.5687317202871531E-2</v>
       </c>
       <c r="X18" s="95">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.21731496488384661</v>
       </c>
       <c r="Y18" s="95">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.27515810495950288</v>
       </c>
       <c r="Z18" s="96">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.31253806664926476</v>
       </c>
       <c r="AA18" s="97">
@@ -18046,24 +18017,24 @@
     </row>
     <row r="19" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Services</v>
       </c>
       <c r="C19" s="47"/>
       <c r="D19" s="95">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.14181951041286078</v>
       </c>
       <c r="E19" s="95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.7704821513138622E-2</v>
       </c>
       <c r="F19" s="95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.14214964370546324</v>
       </c>
       <c r="G19" s="96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.13506431386413498</v>
       </c>
       <c r="H19" s="97">
@@ -18084,36 +18055,36 @@
       <c r="O19" s="5"/>
       <c r="Q19" s="91"/>
       <c r="R19" s="1" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>Services</v>
       </c>
       <c r="S19" s="47"/>
       <c r="T19" s="95">
-        <f t="shared" ref="T19:Z19" si="19">T10/S10-1</f>
+        <f t="shared" ref="T19:Z19" si="20">T10/S10-1</f>
         <v>3.1346797175071162E-2</v>
       </c>
       <c r="U19" s="95">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5.4781355117731856E-2</v>
       </c>
       <c r="V19" s="95">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.1579347000759244E-2</v>
       </c>
       <c r="W19" s="95">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.9198723963220097E-2</v>
       </c>
       <c r="X19" s="95">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4.8390037559712606E-2</v>
       </c>
       <c r="Y19" s="95">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4.3930434782608607E-2</v>
       </c>
       <c r="Z19" s="96">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.2086096025055744E-2</v>
       </c>
       <c r="AA19" s="97">
@@ -18129,39 +18100,39 @@
       </c>
       <c r="C20" s="47"/>
       <c r="D20" s="103">
-        <f t="shared" ref="D20:L20" si="20">D11/C11-1</f>
+        <f t="shared" ref="D20:L20" si="21">D11/C11-1</f>
         <v>7.7937876041846099E-2</v>
       </c>
       <c r="E20" s="103">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-2.800460530319937E-2</v>
       </c>
       <c r="F20" s="103">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.021994077514111E-2</v>
       </c>
       <c r="G20" s="104">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6.425511782832749E-2</v>
       </c>
       <c r="H20" s="103">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9.3884746528386742E-2</v>
       </c>
       <c r="I20" s="103">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6.2611731569849338E-2</v>
       </c>
       <c r="J20" s="103">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6.5373577062155741E-2</v>
       </c>
       <c r="K20" s="103">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>7.1483879768876379E-2</v>
       </c>
       <c r="L20" s="103">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>7.6127877601726901E-2</v>
       </c>
       <c r="O20" s="5"/>
@@ -18172,35 +18143,35 @@
       </c>
       <c r="S20" s="47"/>
       <c r="T20" s="103">
-        <f t="shared" ref="T20:AA20" si="21">T11/S11-1</f>
+        <f t="shared" ref="T20:AA20" si="22">T11/S11-1</f>
         <v>0.10670692609907095</v>
       </c>
       <c r="U20" s="103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.30938586326767092</v>
       </c>
       <c r="V20" s="103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-0.23283185840707965</v>
       </c>
       <c r="W20" s="103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-1.387388710032611E-2</v>
       </c>
       <c r="X20" s="103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>8.9646518354672633E-2</v>
       </c>
       <c r="Y20" s="103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.40296293404641537</v>
       </c>
       <c r="Z20" s="104">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-0.2265783689028632</v>
       </c>
       <c r="AA20" s="103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-1.6374892070801561E-2</v>
       </c>
       <c r="AB20" s="103"/>
@@ -18257,35 +18228,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="226" t="s">
+      <c r="C2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="226"/>
-      <c r="P2" s="226" t="s">
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
+      <c r="P2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="Q2" s="226"/>
-      <c r="R2" s="226"/>
-      <c r="S2" s="226"/>
-      <c r="T2" s="226"/>
-      <c r="U2" s="226"/>
-      <c r="V2" s="226"/>
-      <c r="W2" s="226"/>
-      <c r="X2" s="226" t="s">
+      <c r="Q2" s="235"/>
+      <c r="R2" s="235"/>
+      <c r="S2" s="235"/>
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235" t="s">
         <v>111</v>
       </c>
-      <c r="Y2" s="226"/>
-      <c r="Z2" s="226"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
       <c r="AB2" s="85" t="s">
         <v>112</v>
       </c>
@@ -18294,31 +18265,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="235" t="s">
+      <c r="C4" s="241" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="235"/>
-      <c r="E4" s="235"/>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
-      <c r="H4" s="235"/>
-      <c r="I4" s="235"/>
-      <c r="J4" s="235"/>
-      <c r="K4" s="235"/>
-      <c r="L4" s="235"/>
-      <c r="P4" s="237" t="s">
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
+      <c r="P4" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="Q4" s="237"/>
-      <c r="R4" s="237"/>
-      <c r="S4" s="237"/>
-      <c r="T4" s="237"/>
-      <c r="U4" s="237"/>
-      <c r="V4" s="237"/>
-      <c r="W4" s="237"/>
-      <c r="X4" s="237"/>
-      <c r="Y4" s="237"/>
-      <c r="Z4" s="237"/>
+      <c r="Q4" s="243"/>
+      <c r="R4" s="243"/>
+      <c r="S4" s="243"/>
+      <c r="T4" s="243"/>
+      <c r="U4" s="243"/>
+      <c r="V4" s="243"/>
+      <c r="W4" s="243"/>
+      <c r="X4" s="243"/>
+      <c r="Y4" s="243"/>
+      <c r="Z4" s="243"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18513,32 +18484,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="235" t="s">
+      <c r="C9" s="241" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="235"/>
-      <c r="E9" s="235"/>
-      <c r="F9" s="235"/>
-      <c r="G9" s="235"/>
-      <c r="H9" s="235"/>
-      <c r="I9" s="235"/>
-      <c r="J9" s="235"/>
-      <c r="K9" s="235"/>
-      <c r="L9" s="235"/>
+      <c r="D9" s="241"/>
+      <c r="E9" s="241"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="241"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="237" t="s">
+      <c r="P9" s="243" t="s">
         <v>123</v>
       </c>
-      <c r="Q9" s="237"/>
-      <c r="R9" s="237"/>
-      <c r="S9" s="237"/>
-      <c r="T9" s="237"/>
-      <c r="U9" s="237"/>
-      <c r="V9" s="237"/>
-      <c r="W9" s="237"/>
-      <c r="X9" s="237"/>
-      <c r="Y9" s="237"/>
-      <c r="Z9" s="237"/>
+      <c r="Q9" s="243"/>
+      <c r="R9" s="243"/>
+      <c r="S9" s="243"/>
+      <c r="T9" s="243"/>
+      <c r="U9" s="243"/>
+      <c r="V9" s="243"/>
+      <c r="W9" s="243"/>
+      <c r="X9" s="243"/>
+      <c r="Y9" s="243"/>
+      <c r="Z9" s="243"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -19014,121 +18985,121 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="235" t="s">
+      <c r="C17" s="241" t="s">
         <v>125</v>
       </c>
-      <c r="D17" s="235"/>
-      <c r="E17" s="235"/>
-      <c r="F17" s="235"/>
-      <c r="G17" s="235"/>
-      <c r="H17" s="235"/>
-      <c r="I17" s="235"/>
-      <c r="J17" s="235"/>
-      <c r="K17" s="235"/>
-      <c r="L17" s="235"/>
-      <c r="P17" s="237" t="s">
+      <c r="D17" s="241"/>
+      <c r="E17" s="241"/>
+      <c r="F17" s="241"/>
+      <c r="G17" s="241"/>
+      <c r="H17" s="241"/>
+      <c r="I17" s="241"/>
+      <c r="J17" s="241"/>
+      <c r="K17" s="241"/>
+      <c r="L17" s="241"/>
+      <c r="P17" s="243" t="s">
         <v>125</v>
       </c>
-      <c r="Q17" s="237"/>
-      <c r="R17" s="237"/>
-      <c r="S17" s="237"/>
-      <c r="T17" s="237"/>
-      <c r="U17" s="237"/>
-      <c r="V17" s="237"/>
-      <c r="W17" s="237"/>
-      <c r="X17" s="237"/>
-      <c r="Y17" s="237"/>
-      <c r="Z17" s="237"/>
+      <c r="Q17" s="243"/>
+      <c r="R17" s="243"/>
+      <c r="S17" s="243"/>
+      <c r="T17" s="243"/>
+      <c r="U17" s="243"/>
+      <c r="V17" s="243"/>
+      <c r="W17" s="243"/>
+      <c r="X17" s="243"/>
+      <c r="Y17" s="243"/>
+      <c r="Z17" s="243"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
         <v>126</v>
       </c>
       <c r="C18" s="12">
-        <f>C5</f>
+        <f t="shared" ref="C18:L18" si="5">C5</f>
         <v>2021</v>
       </c>
       <c r="D18" s="12">
-        <f>D5</f>
+        <f t="shared" si="5"/>
         <v>2022</v>
       </c>
       <c r="E18" s="12">
-        <f>E5</f>
+        <f t="shared" si="5"/>
         <v>2023</v>
       </c>
       <c r="F18" s="12">
-        <f>F5</f>
+        <f t="shared" si="5"/>
         <v>2024</v>
       </c>
       <c r="G18" s="12">
-        <f>G5</f>
+        <f t="shared" si="5"/>
         <v>2025</v>
       </c>
       <c r="H18" s="12">
-        <f>H5</f>
+        <f t="shared" si="5"/>
         <v>2026</v>
       </c>
       <c r="I18" s="12">
-        <f>I5</f>
+        <f t="shared" si="5"/>
         <v>2027</v>
       </c>
       <c r="J18" s="12">
-        <f>J5</f>
+        <f t="shared" si="5"/>
         <v>2028</v>
       </c>
       <c r="K18" s="12">
-        <f>K5</f>
+        <f t="shared" si="5"/>
         <v>2029</v>
       </c>
       <c r="L18" s="12">
-        <f>L5</f>
+        <f t="shared" si="5"/>
         <v>2030</v>
       </c>
       <c r="O18" s="16" t="s">
         <v>126</v>
       </c>
       <c r="P18" s="12" t="str">
-        <f>P5</f>
+        <f t="shared" ref="P18:Z18" si="6">P5</f>
         <v>Q3 2024</v>
       </c>
       <c r="Q18" s="12" t="str">
-        <f>Q5</f>
+        <f t="shared" si="6"/>
         <v>Q4 2024</v>
       </c>
       <c r="R18" s="12" t="str">
-        <f>R5</f>
+        <f t="shared" si="6"/>
         <v>Q1 2025</v>
       </c>
       <c r="S18" s="12" t="str">
-        <f>S5</f>
+        <f t="shared" si="6"/>
         <v>Q2 2025</v>
       </c>
       <c r="T18" s="12" t="str">
-        <f>T5</f>
+        <f t="shared" si="6"/>
         <v>Q3 2025</v>
       </c>
       <c r="U18" s="12" t="str">
-        <f>U5</f>
+        <f t="shared" si="6"/>
         <v>Q4 2025</v>
       </c>
       <c r="V18" s="12" t="str">
-        <f>V5</f>
+        <f t="shared" si="6"/>
         <v>Q1 2026</v>
       </c>
       <c r="W18" s="12" t="str">
-        <f>W5</f>
+        <f t="shared" si="6"/>
         <v>Q2 2026</v>
       </c>
       <c r="X18" s="12" t="str">
-        <f>X5</f>
+        <f t="shared" si="6"/>
         <v>FQ1</v>
       </c>
       <c r="Y18" s="12" t="str">
-        <f>Y5</f>
+        <f t="shared" si="6"/>
         <v>FQ2</v>
       </c>
       <c r="Z18" s="12" t="str">
-        <f>Z5</f>
+        <f t="shared" si="6"/>
         <v>FQ3</v>
       </c>
     </row>
@@ -19138,23 +19109,23 @@
         <v>COGS</v>
       </c>
       <c r="C19" s="103">
-        <f>C11/C$6</f>
+        <f t="shared" ref="C19:G21" si="7">C11/C$6</f>
         <v>0.58220640374832222</v>
       </c>
       <c r="D19" s="103">
-        <f>D11/D$6</f>
+        <f t="shared" si="7"/>
         <v>0.56690369438639909</v>
       </c>
       <c r="E19" s="103">
-        <f>E11/E$6</f>
+        <f t="shared" si="7"/>
         <v>0.55868870422792438</v>
       </c>
       <c r="F19" s="103">
-        <f>F11/F$6</f>
+        <f t="shared" si="7"/>
         <v>0.53793650184766073</v>
       </c>
       <c r="G19" s="104">
-        <f>G11/G$6</f>
+        <f t="shared" si="7"/>
         <v>0.53094835892839554</v>
       </c>
       <c r="H19" s="97">
@@ -19177,35 +19148,35 @@
         <v>COGS</v>
       </c>
       <c r="P19" s="103">
-        <f>P11/P$6</f>
+        <f t="shared" ref="P19:W21" si="8">P11/P$6</f>
         <v>0.53742844818541102</v>
       </c>
       <c r="Q19" s="103">
-        <f>Q11/Q$6</f>
+        <f t="shared" si="8"/>
         <v>0.53777520278099655</v>
       </c>
       <c r="R19" s="103">
-        <f>R11/R$6</f>
+        <f t="shared" si="8"/>
         <v>0.53117457763475462</v>
       </c>
       <c r="S19" s="103">
-        <f>S11/S$6</f>
+        <f t="shared" si="8"/>
         <v>0.52949380761123754</v>
       </c>
       <c r="T19" s="103">
-        <f>T11/T$6</f>
+        <f t="shared" si="8"/>
         <v>0.53509294312816369</v>
       </c>
       <c r="U19" s="103">
-        <f>U11/U$6</f>
+        <f t="shared" si="8"/>
         <v>0.52822399625241545</v>
       </c>
       <c r="V19" s="103">
-        <f>V11/V$6</f>
+        <f t="shared" si="8"/>
         <v>0.51841314449483844</v>
       </c>
       <c r="W19" s="104">
-        <f>W11/W$6</f>
+        <f t="shared" si="8"/>
         <v>0.5072942149949633</v>
       </c>
       <c r="X19" s="97">
@@ -19220,23 +19191,23 @@
         <v>R&amp;D</v>
       </c>
       <c r="C20" s="95">
-        <f>C12/C$6</f>
+        <f t="shared" si="7"/>
         <v>5.9904269074427925E-2</v>
       </c>
       <c r="D20" s="95">
-        <f>D12/D$6</f>
+        <f t="shared" si="7"/>
         <v>6.657148363798665E-2</v>
       </c>
       <c r="E20" s="95">
-        <f>E12/E$6</f>
+        <f t="shared" si="7"/>
         <v>7.8048971392045086E-2</v>
       </c>
       <c r="F20" s="95">
-        <f>F12/F$6</f>
+        <f t="shared" si="7"/>
         <v>8.0222997941360744E-2</v>
       </c>
       <c r="G20" s="96">
-        <f>G12/G$6</f>
+        <f t="shared" si="7"/>
         <v>8.3020753987038676E-2</v>
       </c>
       <c r="H20" s="97">
@@ -19259,35 +19230,35 @@
         <v>R&amp;D</v>
       </c>
       <c r="P20" s="95">
-        <f>P12/P$6</f>
+        <f t="shared" si="8"/>
         <v>9.3335043193396833E-2</v>
       </c>
       <c r="Q20" s="95">
-        <f>Q12/Q$6</f>
+        <f t="shared" si="8"/>
         <v>8.1797113662698831E-2</v>
       </c>
       <c r="R20" s="95">
-        <f>R12/R$6</f>
+        <f t="shared" si="8"/>
         <v>6.6516492357200321E-2</v>
       </c>
       <c r="S20" s="95">
-        <f>S12/S$6</f>
+        <f t="shared" si="8"/>
         <v>8.9661175138162102E-2</v>
       </c>
       <c r="T20" s="95">
-        <f>T12/T$6</f>
+        <f t="shared" si="8"/>
         <v>9.4283040537666424E-2</v>
       </c>
       <c r="U20" s="95">
-        <f>U12/U$6</f>
+        <f t="shared" si="8"/>
         <v>8.6526262369956863E-2</v>
       </c>
       <c r="V20" s="95">
-        <f>V12/V$6</f>
+        <f t="shared" si="8"/>
         <v>7.5732491165586127E-2</v>
       </c>
       <c r="W20" s="96">
-        <f>W12/W$6</f>
+        <f t="shared" si="8"/>
         <v>0.10270362642106778</v>
       </c>
       <c r="X20" s="97">
@@ -19302,23 +19273,23 @@
         <v>SG&amp;A</v>
       </c>
       <c r="C21" s="95">
-        <f>C13/C$6</f>
+        <f t="shared" si="7"/>
         <v>6.006555190163388E-2</v>
       </c>
       <c r="D21" s="95">
-        <f>D13/D$6</f>
+        <f t="shared" si="7"/>
         <v>6.3637378020328261E-2</v>
       </c>
       <c r="E21" s="95">
-        <f>E13/E$6</f>
+        <f t="shared" si="7"/>
         <v>6.5048201729783317E-2</v>
       </c>
       <c r="F21" s="95">
-        <f>F13/F$6</f>
+        <f t="shared" si="7"/>
         <v>6.6738271510222866E-2</v>
       </c>
       <c r="G21" s="96">
-        <f>G13/G$6</f>
+        <f t="shared" si="7"/>
         <v>6.6322889458647019E-2</v>
       </c>
       <c r="H21" s="97">
@@ -19341,35 +19312,35 @@
         <v>SG&amp;A</v>
       </c>
       <c r="P21" s="95">
-        <f>P13/P$6</f>
+        <f t="shared" si="8"/>
         <v>7.3679424554367726E-2</v>
       </c>
       <c r="Q21" s="95">
-        <f>Q13/Q$6</f>
+        <f t="shared" si="8"/>
         <v>6.8713789107763615E-2</v>
       </c>
       <c r="R21" s="95">
-        <f>R13/R$6</f>
+        <f t="shared" si="8"/>
         <v>5.7723250201126307E-2</v>
       </c>
       <c r="S21" s="95">
-        <f>S13/S$6</f>
+        <f t="shared" si="8"/>
         <v>7.0554431149655511E-2</v>
       </c>
       <c r="T21" s="95">
-        <f>T13/T$6</f>
+        <f t="shared" si="8"/>
         <v>7.0717597515844999E-2</v>
       </c>
       <c r="U21" s="95">
-        <f>U13/U$6</f>
+        <f t="shared" si="8"/>
         <v>6.8783791696757954E-2</v>
       </c>
       <c r="V21" s="95">
-        <f>V13/V$6</f>
+        <f t="shared" si="8"/>
         <v>5.2116085589471048E-2</v>
       </c>
       <c r="W21" s="96">
-        <f>W13/W$6</f>
+        <f t="shared" si="8"/>
         <v>6.7248884731616054E-2</v>
       </c>
       <c r="X21" s="97">
@@ -19380,7 +19351,7 @@
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="str">
-        <f t="shared" ref="B22" si="5">B14</f>
+        <f t="shared" ref="B22" si="9">B14</f>
         <v>OpEx</v>
       </c>
       <c r="C22" s="103">
@@ -19388,79 +19359,79 @@
         <v>0.11996982097606181</v>
       </c>
       <c r="D22" s="103">
-        <f t="shared" ref="D22:L22" si="6">D14/D$6</f>
+        <f t="shared" ref="D22:L22" si="10">D14/D$6</f>
         <v>0.13020886165831491</v>
       </c>
       <c r="E22" s="103">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.1430971731218284</v>
       </c>
       <c r="F22" s="103">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.14696126945158361</v>
       </c>
       <c r="G22" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.14934364344568568</v>
       </c>
       <c r="H22" s="103">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.156</v>
       </c>
       <c r="I22" s="103">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.15899999999999997</v>
       </c>
       <c r="J22" s="103">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.16400000000000001</v>
       </c>
       <c r="K22" s="103">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.17</v>
       </c>
       <c r="L22" s="103">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.16800000000000004</v>
       </c>
       <c r="O22" s="16" t="str">
-        <f t="shared" ref="O22" si="7">O14</f>
+        <f t="shared" ref="O22" si="11">O14</f>
         <v>OpEx</v>
       </c>
       <c r="P22" s="103">
-        <f t="shared" ref="P22:V22" si="8">P14/P$6</f>
+        <f t="shared" ref="P22:V22" si="12">P14/P$6</f>
         <v>0.16701446774776454</v>
       </c>
       <c r="Q22" s="103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.15051090277046245</v>
       </c>
       <c r="R22" s="103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.12423974255832664</v>
       </c>
       <c r="S22" s="103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.16021560628781761</v>
       </c>
       <c r="T22" s="103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.16500063805351142</v>
       </c>
       <c r="U22" s="103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.1553100540667148</v>
       </c>
       <c r="V22" s="103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.12784857675505718</v>
       </c>
       <c r="W22" s="104">
-        <f t="shared" ref="W22:X22" si="9">W14/W$6</f>
+        <f t="shared" ref="W22:X22" si="13">W14/W$6</f>
         <v>0.16995251115268384</v>
       </c>
       <c r="X22" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.16</v>
       </c>
       <c r="Y22" s="16"/>
@@ -19516,60 +19487,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="226" t="s">
+      <c r="C3" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="226"/>
-      <c r="E3" s="226"/>
-      <c r="F3" s="226"/>
-      <c r="G3" s="238"/>
-      <c r="H3" s="239" t="s">
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="226"/>
-      <c r="J3" s="226"/>
-      <c r="K3" s="226"/>
-      <c r="L3" s="226"/>
-      <c r="P3" s="240"/>
-      <c r="Q3" s="240"/>
-      <c r="R3" s="240"/>
-      <c r="S3" s="240"/>
-      <c r="T3" s="240"/>
-      <c r="U3" s="240"/>
-      <c r="V3" s="240"/>
-      <c r="W3" s="240"/>
-      <c r="X3" s="240"/>
-      <c r="Y3" s="240"/>
-      <c r="Z3" s="240"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
+      <c r="P3" s="246"/>
+      <c r="Q3" s="246"/>
+      <c r="R3" s="246"/>
+      <c r="S3" s="246"/>
+      <c r="T3" s="246"/>
+      <c r="U3" s="246"/>
+      <c r="V3" s="246"/>
+      <c r="W3" s="246"/>
+      <c r="X3" s="246"/>
+      <c r="Y3" s="246"/>
+      <c r="Z3" s="246"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="235" t="s">
+      <c r="C5" s="241" t="s">
         <v>113</v>
       </c>
-      <c r="D5" s="235"/>
-      <c r="E5" s="235"/>
-      <c r="F5" s="235"/>
-      <c r="G5" s="235"/>
-      <c r="H5" s="235"/>
-      <c r="I5" s="235"/>
-      <c r="J5" s="235"/>
-      <c r="K5" s="235"/>
-      <c r="L5" s="235"/>
-      <c r="P5" s="240"/>
-      <c r="Q5" s="240"/>
-      <c r="R5" s="240"/>
-      <c r="S5" s="240"/>
-      <c r="T5" s="240"/>
-      <c r="U5" s="240"/>
-      <c r="V5" s="240"/>
-      <c r="W5" s="240"/>
-      <c r="X5" s="240"/>
-      <c r="Y5" s="240"/>
-      <c r="Z5" s="240"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
+      <c r="P5" s="246"/>
+      <c r="Q5" s="246"/>
+      <c r="R5" s="246"/>
+      <c r="S5" s="246"/>
+      <c r="T5" s="246"/>
+      <c r="U5" s="246"/>
+      <c r="V5" s="246"/>
+      <c r="W5" s="246"/>
+      <c r="X5" s="246"/>
+      <c r="Y5" s="246"/>
+      <c r="Z5" s="246"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19755,30 +19726,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="235" t="s">
+      <c r="C11" s="241" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="235"/>
-      <c r="E11" s="235"/>
-      <c r="F11" s="235"/>
-      <c r="G11" s="235"/>
-      <c r="H11" s="235"/>
-      <c r="I11" s="235"/>
-      <c r="J11" s="235"/>
-      <c r="K11" s="235"/>
-      <c r="L11" s="235"/>
+      <c r="D11" s="241"/>
+      <c r="E11" s="241"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="241"/>
+      <c r="K11" s="241"/>
+      <c r="L11" s="241"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="240"/>
-      <c r="Q11" s="240"/>
-      <c r="R11" s="240"/>
-      <c r="S11" s="240"/>
-      <c r="T11" s="240"/>
-      <c r="U11" s="240"/>
-      <c r="V11" s="240"/>
-      <c r="W11" s="240"/>
-      <c r="X11" s="240"/>
-      <c r="Y11" s="240"/>
-      <c r="Z11" s="240"/>
+      <c r="P11" s="246"/>
+      <c r="Q11" s="246"/>
+      <c r="R11" s="246"/>
+      <c r="S11" s="246"/>
+      <c r="T11" s="246"/>
+      <c r="U11" s="246"/>
+      <c r="V11" s="246"/>
+      <c r="W11" s="246"/>
+      <c r="X11" s="246"/>
+      <c r="Y11" s="246"/>
+      <c r="Z11" s="246"/>
       <c r="AB11" s="110"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -20020,18 +19991,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="235" t="s">
+      <c r="C18" s="241" t="s">
         <v>134</v>
       </c>
-      <c r="D18" s="235"/>
-      <c r="E18" s="235"/>
-      <c r="F18" s="235"/>
-      <c r="G18" s="235"/>
-      <c r="H18" s="235"/>
-      <c r="I18" s="235"/>
-      <c r="J18" s="235"/>
-      <c r="K18" s="235"/>
-      <c r="L18" s="235"/>
+      <c r="D18" s="241"/>
+      <c r="E18" s="241"/>
+      <c r="F18" s="241"/>
+      <c r="G18" s="241"/>
+      <c r="H18" s="241"/>
+      <c r="I18" s="241"/>
+      <c r="J18" s="241"/>
+      <c r="K18" s="241"/>
+      <c r="L18" s="241"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20244,23 +20215,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="240"/>
-      <c r="C25" s="240"/>
+      <c r="B25" s="246"/>
+      <c r="C25" s="246"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="235" t="s">
+      <c r="C26" s="241" t="s">
         <v>140</v>
       </c>
-      <c r="D26" s="235"/>
-      <c r="E26" s="235"/>
-      <c r="F26" s="235"/>
-      <c r="G26" s="235"/>
-      <c r="H26" s="235"/>
-      <c r="I26" s="235"/>
-      <c r="J26" s="235"/>
-      <c r="K26" s="235"/>
-      <c r="L26" s="235"/>
+      <c r="D26" s="241"/>
+      <c r="E26" s="241"/>
+      <c r="F26" s="241"/>
+      <c r="G26" s="241"/>
+      <c r="H26" s="241"/>
+      <c r="I26" s="241"/>
+      <c r="J26" s="241"/>
+      <c r="K26" s="241"/>
+      <c r="L26" s="241"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20452,18 +20423,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="235" t="s">
+      <c r="C33" s="241" t="s">
         <v>144</v>
       </c>
-      <c r="D33" s="235"/>
-      <c r="E33" s="235"/>
-      <c r="F33" s="235"/>
-      <c r="G33" s="235"/>
-      <c r="H33" s="235"/>
-      <c r="I33" s="235"/>
-      <c r="J33" s="235"/>
-      <c r="K33" s="235"/>
-      <c r="L33" s="235"/>
+      <c r="D33" s="241"/>
+      <c r="E33" s="241"/>
+      <c r="F33" s="241"/>
+      <c r="G33" s="241"/>
+      <c r="H33" s="241"/>
+      <c r="I33" s="241"/>
+      <c r="J33" s="241"/>
+      <c r="K33" s="241"/>
+      <c r="L33" s="241"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20647,18 +20618,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="235" t="s">
+      <c r="C40" s="241" t="s">
         <v>147</v>
       </c>
-      <c r="D40" s="235"/>
-      <c r="E40" s="235"/>
-      <c r="F40" s="235"/>
-      <c r="G40" s="235"/>
-      <c r="H40" s="235"/>
-      <c r="I40" s="235"/>
-      <c r="J40" s="235"/>
-      <c r="K40" s="235"/>
-      <c r="L40" s="235"/>
+      <c r="D40" s="241"/>
+      <c r="E40" s="241"/>
+      <c r="F40" s="241"/>
+      <c r="G40" s="241"/>
+      <c r="H40" s="241"/>
+      <c r="I40" s="241"/>
+      <c r="J40" s="241"/>
+      <c r="K40" s="241"/>
+      <c r="L40" s="241"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20922,6 +20893,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20929,12 +20906,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20972,60 +20943,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="226" t="s">
+      <c r="C2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="226"/>
-      <c r="S2" s="240"/>
-      <c r="T2" s="240"/>
-      <c r="U2" s="240"/>
-      <c r="V2" s="240"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="240"/>
-      <c r="Y2" s="240"/>
-      <c r="Z2" s="240"/>
-      <c r="AA2" s="240"/>
-      <c r="AB2" s="240"/>
-      <c r="AC2" s="240"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
+      <c r="S2" s="246"/>
+      <c r="T2" s="246"/>
+      <c r="U2" s="246"/>
+      <c r="V2" s="246"/>
+      <c r="W2" s="246"/>
+      <c r="X2" s="246"/>
+      <c r="Y2" s="246"/>
+      <c r="Z2" s="246"/>
+      <c r="AA2" s="246"/>
+      <c r="AB2" s="246"/>
+      <c r="AC2" s="246"/>
       <c r="AE2" s="109"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="235" t="s">
+      <c r="C4" s="241" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="235"/>
-      <c r="E4" s="235"/>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
-      <c r="H4" s="235"/>
-      <c r="I4" s="235"/>
-      <c r="J4" s="235"/>
-      <c r="K4" s="235"/>
-      <c r="L4" s="235"/>
-      <c r="S4" s="240"/>
-      <c r="T4" s="240"/>
-      <c r="U4" s="240"/>
-      <c r="V4" s="240"/>
-      <c r="W4" s="240"/>
-      <c r="X4" s="240"/>
-      <c r="Y4" s="240"/>
-      <c r="Z4" s="240"/>
-      <c r="AA4" s="240"/>
-      <c r="AB4" s="240"/>
-      <c r="AC4" s="240"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="246"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="246"/>
+      <c r="Y4" s="246"/>
+      <c r="Z4" s="246"/>
+      <c r="AA4" s="246"/>
+      <c r="AB4" s="246"/>
+      <c r="AC4" s="246"/>
       <c r="AE4" s="110"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -21388,18 +21359,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="235" t="s">
+      <c r="C13" s="241" t="s">
         <v>155</v>
       </c>
-      <c r="D13" s="235"/>
-      <c r="E13" s="235"/>
-      <c r="F13" s="235"/>
-      <c r="G13" s="235"/>
-      <c r="H13" s="235"/>
-      <c r="I13" s="235"/>
-      <c r="J13" s="235"/>
-      <c r="K13" s="235"/>
-      <c r="L13" s="235"/>
+      <c r="D13" s="241"/>
+      <c r="E13" s="241"/>
+      <c r="F13" s="241"/>
+      <c r="G13" s="241"/>
+      <c r="H13" s="241"/>
+      <c r="I13" s="241"/>
+      <c r="J13" s="241"/>
+      <c r="K13" s="241"/>
+      <c r="L13" s="241"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21492,18 +21463,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="235" t="s">
+      <c r="C18" s="241" t="s">
         <v>156</v>
       </c>
-      <c r="D18" s="235"/>
-      <c r="E18" s="235"/>
-      <c r="F18" s="235"/>
-      <c r="G18" s="235"/>
-      <c r="H18" s="235"/>
-      <c r="I18" s="235"/>
-      <c r="J18" s="235"/>
-      <c r="K18" s="235"/>
-      <c r="L18" s="235"/>
+      <c r="D18" s="241"/>
+      <c r="E18" s="241"/>
+      <c r="F18" s="241"/>
+      <c r="G18" s="241"/>
+      <c r="H18" s="241"/>
+      <c r="I18" s="241"/>
+      <c r="J18" s="241"/>
+      <c r="K18" s="241"/>
+      <c r="L18" s="241"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21695,18 +21666,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="235" t="s">
+      <c r="C25" s="241" t="s">
         <v>261</v>
       </c>
-      <c r="D25" s="235"/>
-      <c r="E25" s="235"/>
-      <c r="F25" s="235"/>
-      <c r="G25" s="235"/>
-      <c r="H25" s="235"/>
-      <c r="I25" s="235"/>
-      <c r="J25" s="235"/>
-      <c r="K25" s="235"/>
-      <c r="L25" s="235"/>
+      <c r="D25" s="241"/>
+      <c r="E25" s="241"/>
+      <c r="F25" s="241"/>
+      <c r="G25" s="241"/>
+      <c r="H25" s="241"/>
+      <c r="I25" s="241"/>
+      <c r="J25" s="241"/>
+      <c r="K25" s="241"/>
+      <c r="L25" s="241"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21844,18 +21815,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="235" t="s">
+      <c r="C31" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="235"/>
-      <c r="E31" s="235"/>
-      <c r="F31" s="235"/>
-      <c r="G31" s="235"/>
-      <c r="H31" s="235"/>
-      <c r="I31" s="235"/>
-      <c r="J31" s="235"/>
-      <c r="K31" s="235"/>
-      <c r="L31" s="235"/>
+      <c r="D31" s="241"/>
+      <c r="E31" s="241"/>
+      <c r="F31" s="241"/>
+      <c r="G31" s="241"/>
+      <c r="H31" s="241"/>
+      <c r="I31" s="241"/>
+      <c r="J31" s="241"/>
+      <c r="K31" s="241"/>
+      <c r="L31" s="241"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21994,16 +21965,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22066,10 +22037,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="226" t="s">
+      <c r="B4" s="235" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="226"/>
+      <c r="C4" s="235"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22086,7 +22057,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>299.77</v>
+        <v>275.14999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22095,7 +22066,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>4418609.8</v>
+        <v>4055710.9999999995</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22113,7 +22084,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.4510000000000001E-2</v>
+        <v>4.4020000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22122,7 +22093,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.0922000000000001</v>
+        <v>1.0964</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22154,10 +22125,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="226" t="s">
+      <c r="B15" s="235" t="s">
         <v>170</v>
       </c>
-      <c r="C15" s="226"/>
+      <c r="C15" s="235"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22165,7 +22136,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.8810785143265833E-2</v>
+        <v>2.0459508716744335E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22174,7 +22145,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.98118921485673416</v>
+        <v>0.97954049128325571</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22192,7 +22163,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.3658999999999992E-2</v>
+        <v>9.3357999999999997E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22201,7 +22172,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.2588214866504731E-2</v>
+        <v>9.2199521237931792E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22246,60 +22217,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="226" t="s">
+      <c r="C3" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="226"/>
-      <c r="E3" s="226"/>
-      <c r="F3" s="226"/>
-      <c r="G3" s="238"/>
-      <c r="H3" s="239" t="s">
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="226"/>
-      <c r="J3" s="226"/>
-      <c r="K3" s="226"/>
-      <c r="L3" s="226"/>
-      <c r="P3" s="240"/>
-      <c r="Q3" s="240"/>
-      <c r="R3" s="240"/>
-      <c r="S3" s="240"/>
-      <c r="T3" s="240"/>
-      <c r="U3" s="240"/>
-      <c r="V3" s="240"/>
-      <c r="W3" s="240"/>
-      <c r="X3" s="240"/>
-      <c r="Y3" s="240"/>
-      <c r="Z3" s="240"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
+      <c r="P3" s="246"/>
+      <c r="Q3" s="246"/>
+      <c r="R3" s="246"/>
+      <c r="S3" s="246"/>
+      <c r="T3" s="246"/>
+      <c r="U3" s="246"/>
+      <c r="V3" s="246"/>
+      <c r="W3" s="246"/>
+      <c r="X3" s="246"/>
+      <c r="Y3" s="246"/>
+      <c r="Z3" s="246"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="235" t="s">
+      <c r="C5" s="241" t="s">
         <v>177</v>
       </c>
-      <c r="D5" s="235"/>
-      <c r="E5" s="235"/>
-      <c r="F5" s="235"/>
-      <c r="G5" s="235"/>
-      <c r="H5" s="235"/>
-      <c r="I5" s="235"/>
-      <c r="J5" s="235"/>
-      <c r="K5" s="235"/>
-      <c r="L5" s="235"/>
-      <c r="P5" s="240"/>
-      <c r="Q5" s="240"/>
-      <c r="R5" s="240"/>
-      <c r="S5" s="240"/>
-      <c r="T5" s="240"/>
-      <c r="U5" s="240"/>
-      <c r="V5" s="240"/>
-      <c r="W5" s="240"/>
-      <c r="X5" s="240"/>
-      <c r="Y5" s="240"/>
-      <c r="Z5" s="240"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
+      <c r="P5" s="246"/>
+      <c r="Q5" s="246"/>
+      <c r="R5" s="246"/>
+      <c r="S5" s="246"/>
+      <c r="T5" s="246"/>
+      <c r="U5" s="246"/>
+      <c r="V5" s="246"/>
+      <c r="W5" s="246"/>
+      <c r="X5" s="246"/>
+      <c r="Y5" s="246"/>
+      <c r="Z5" s="246"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22452,7 +22423,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>1931657.3988720458</v>
+        <v>1942056.6772973558</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22506,23 +22477,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>96424.225627615611</v>
+        <v>96458.541227844995</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>93215.345344565896</v>
+        <v>93281.704388500948</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>90427.692784731567</v>
+        <v>90524.271782232376</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>87512.909039601291</v>
+        <v>87637.552466566398</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>88290.400666717484</v>
+        <v>88447.617138865826</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22541,14 +22512,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>1240645.0392212027</v>
+        <v>1249545.2592315206</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="226" t="s">
+      <c r="B13" s="235" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="226"/>
+      <c r="C13" s="235"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22564,14 +22535,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.2588214866504731E-2</v>
+        <v>9.2199521237931792E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="226" t="s">
+      <c r="B18" s="235" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="226"/>
+      <c r="C18" s="235"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22579,7 +22550,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>455870.57346323185</v>
+        <v>456349.68700401054</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -22588,7 +22559,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>1240645.0392212027</v>
+        <v>1249545.2592315206</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -22597,7 +22568,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>1696515.6126844345</v>
+        <v>1705894.946235531</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -22624,7 +22595,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>1758399.6126844345</v>
+        <v>1767778.946235531</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -22642,7 +22613,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>119.29441062988022</v>
+        <v>119.93072905261404</v>
       </c>
     </row>
   </sheetData>
@@ -22685,37 +22656,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="226" t="s">
+      <c r="C2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="226"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="235" t="s">
+      <c r="C4" s="241" t="s">
         <v>191</v>
       </c>
-      <c r="D4" s="235"/>
-      <c r="E4" s="235"/>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
-      <c r="H4" s="235"/>
-      <c r="I4" s="235"/>
-      <c r="J4" s="235"/>
-      <c r="K4" s="235"/>
-      <c r="L4" s="235"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22904,18 +22875,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="235" t="s">
+      <c r="C10" s="241" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="235"/>
-      <c r="E10" s="235"/>
-      <c r="F10" s="235"/>
-      <c r="G10" s="235"/>
-      <c r="H10" s="235"/>
-      <c r="I10" s="235"/>
-      <c r="J10" s="235"/>
-      <c r="K10" s="235"/>
-      <c r="L10" s="235"/>
+      <c r="D10" s="241"/>
+      <c r="E10" s="241"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
+      <c r="H10" s="241"/>
+      <c r="I10" s="241"/>
+      <c r="J10" s="241"/>
+      <c r="K10" s="241"/>
+      <c r="L10" s="241"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23109,18 +23080,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="235" t="s">
+      <c r="C16" s="241" t="s">
         <v>193</v>
       </c>
-      <c r="D16" s="235"/>
-      <c r="E16" s="235"/>
-      <c r="F16" s="235"/>
-      <c r="G16" s="235"/>
-      <c r="H16" s="235"/>
-      <c r="I16" s="235"/>
-      <c r="J16" s="235"/>
-      <c r="K16" s="235"/>
-      <c r="L16" s="235"/>
+      <c r="D16" s="241"/>
+      <c r="E16" s="241"/>
+      <c r="F16" s="241"/>
+      <c r="G16" s="241"/>
+      <c r="H16" s="241"/>
+      <c r="I16" s="241"/>
+      <c r="J16" s="241"/>
+      <c r="K16" s="241"/>
+      <c r="L16" s="241"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -23217,23 +23188,23 @@
         <v>195</v>
       </c>
       <c r="C19" s="137"/>
-      <c r="D19" s="248">
+      <c r="D19" s="230">
         <f>D18/C18-1</f>
         <v>-3.1959679810257935E-2</v>
       </c>
-      <c r="E19" s="248">
+      <c r="E19" s="230">
         <f t="shared" ref="E19:G19" si="6">E18/D18-1</f>
         <v>-3.1422271223814802E-2</v>
       </c>
-      <c r="F19" s="248">
+      <c r="F19" s="230">
         <f t="shared" si="6"/>
         <v>-2.5611838360842354E-2</v>
       </c>
-      <c r="G19" s="249">
+      <c r="G19" s="231">
         <f t="shared" si="6"/>
         <v>-2.6155244029075764E-2</v>
       </c>
-      <c r="H19" s="247">
+      <c r="H19" s="229">
         <v>-2.5000000000000001E-2</v>
       </c>
       <c r="I19" s="165">
@@ -23254,18 +23225,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="235" t="s">
+      <c r="C21" s="241" t="s">
         <v>196</v>
       </c>
-      <c r="D21" s="235"/>
-      <c r="E21" s="235"/>
-      <c r="F21" s="235"/>
-      <c r="G21" s="235"/>
-      <c r="H21" s="235"/>
-      <c r="I21" s="235"/>
-      <c r="J21" s="235"/>
-      <c r="K21" s="235"/>
-      <c r="L21" s="235"/>
+      <c r="D21" s="241"/>
+      <c r="E21" s="241"/>
+      <c r="F21" s="241"/>
+      <c r="G21" s="241"/>
+      <c r="H21" s="241"/>
+      <c r="I21" s="241"/>
+      <c r="J21" s="241"/>
+      <c r="K21" s="241"/>
+      <c r="L21" s="241"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -23349,18 +23320,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="235" t="s">
+      <c r="C26" s="241" t="s">
         <v>197</v>
       </c>
-      <c r="D26" s="235"/>
-      <c r="E26" s="235"/>
-      <c r="F26" s="235"/>
-      <c r="G26" s="235"/>
-      <c r="H26" s="235"/>
-      <c r="I26" s="235"/>
-      <c r="J26" s="235"/>
-      <c r="K26" s="235"/>
-      <c r="L26" s="235"/>
+      <c r="D26" s="241"/>
+      <c r="E26" s="241"/>
+      <c r="F26" s="241"/>
+      <c r="G26" s="241"/>
+      <c r="H26" s="241"/>
+      <c r="I26" s="241"/>
+      <c r="J26" s="241"/>
+      <c r="K26" s="241"/>
+      <c r="L26" s="241"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -23630,10 +23601,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="226" t="s">
+      <c r="B37" s="235" t="s">
         <v>202</v>
       </c>
-      <c r="C37" s="226"/>
+      <c r="C37" s="235"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -23651,7 +23622,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.2588214866504731E-2</v>
+        <v>9.2199521237931792E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -23686,7 +23657,7 @@
       </c>
       <c r="C43" s="24">
         <f ca="1">C42/(1+C39)^5-G30+G31</f>
-        <v>2816444.7259205934</v>
+        <v>2821399.7765348987</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -23704,14 +23675,14 @@
       </c>
       <c r="C45" s="142">
         <f ca="1">C43/C44</f>
-        <v>191.07494748443645</v>
+        <v>191.41111102679096</v>
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="226" t="s">
+      <c r="B47" s="235" t="s">
         <v>207</v>
       </c>
-      <c r="C47" s="226"/>
+      <c r="C47" s="235"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
@@ -23767,10 +23738,10 @@
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="226" t="s">
+      <c r="B55" s="235" t="s">
         <v>321</v>
       </c>
-      <c r="C55" s="226"/>
+      <c r="C55" s="235"/>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
@@ -23787,7 +23758,7 @@
       </c>
       <c r="C57" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.2588214866504731E-2</v>
+        <v>9.2199521237931792E-2</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
@@ -23813,7 +23784,7 @@
       </c>
       <c r="C60" s="24">
         <f ca="1">C59/(1+C57)^5-G30+G31</f>
-        <v>1799571.0133343497</v>
+        <v>1802715.3427773165</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
@@ -23831,7 +23802,7 @@
       </c>
       <c r="C62" s="142">
         <f ca="1">C60/C61</f>
-        <v>122.08758570789347</v>
+        <v>122.30090520877316</v>
       </c>
     </row>
   </sheetData>
@@ -23883,10 +23854,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="226" t="s">
+      <c r="B4" s="235" t="s">
         <v>212</v>
       </c>
-      <c r="C4" s="226"/>
+      <c r="C4" s="235"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23895,7 +23866,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>119.29441062988022</v>
+        <v>119.93072905261404</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23904,7 +23875,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C45</f>
-        <v>191.07494748443645</v>
+        <v>191.41111102679096</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23922,7 +23893,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C62</f>
-        <v>122.08758570789347</v>
+        <v>122.30090520877316</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23931,7 +23902,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>142.78609402713997</v>
+        <v>143.08254439363199</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23940,7 +23911,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>299.77</v>
+        <v>275.14999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23949,7 +23920,7 @@
       </c>
       <c r="C11" s="151">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.52368117547739945</v>
+        <v>-0.47998348394100671</v>
       </c>
     </row>
   </sheetData>
@@ -24014,60 +23985,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="226" t="s">
+      <c r="C3" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="226"/>
-      <c r="E3" s="226"/>
-      <c r="F3" s="226"/>
-      <c r="G3" s="238"/>
-      <c r="H3" s="239" t="s">
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="226"/>
-      <c r="J3" s="226"/>
-      <c r="K3" s="226"/>
-      <c r="L3" s="226"/>
-      <c r="P3" s="240"/>
-      <c r="Q3" s="240"/>
-      <c r="R3" s="240"/>
-      <c r="S3" s="240"/>
-      <c r="T3" s="240"/>
-      <c r="U3" s="240"/>
-      <c r="V3" s="240"/>
-      <c r="W3" s="240"/>
-      <c r="X3" s="240"/>
-      <c r="Y3" s="240"/>
-      <c r="Z3" s="240"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
+      <c r="P3" s="246"/>
+      <c r="Q3" s="246"/>
+      <c r="R3" s="246"/>
+      <c r="S3" s="246"/>
+      <c r="T3" s="246"/>
+      <c r="U3" s="246"/>
+      <c r="V3" s="246"/>
+      <c r="W3" s="246"/>
+      <c r="X3" s="246"/>
+      <c r="Y3" s="246"/>
+      <c r="Z3" s="246"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="235" t="s">
+      <c r="C5" s="241" t="s">
         <v>177</v>
       </c>
-      <c r="D5" s="235"/>
-      <c r="E5" s="235"/>
-      <c r="F5" s="235"/>
-      <c r="G5" s="235"/>
-      <c r="H5" s="235"/>
-      <c r="I5" s="235"/>
-      <c r="J5" s="235"/>
-      <c r="K5" s="235"/>
-      <c r="L5" s="235"/>
-      <c r="P5" s="240"/>
-      <c r="Q5" s="240"/>
-      <c r="R5" s="240"/>
-      <c r="S5" s="240"/>
-      <c r="T5" s="240"/>
-      <c r="U5" s="240"/>
-      <c r="V5" s="240"/>
-      <c r="W5" s="240"/>
-      <c r="X5" s="240"/>
-      <c r="Y5" s="240"/>
-      <c r="Z5" s="240"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
+      <c r="P5" s="246"/>
+      <c r="Q5" s="246"/>
+      <c r="R5" s="246"/>
+      <c r="S5" s="246"/>
+      <c r="T5" s="246"/>
+      <c r="U5" s="246"/>
+      <c r="V5" s="246"/>
+      <c r="W5" s="246"/>
+      <c r="X5" s="246"/>
+      <c r="Y5" s="246"/>
+      <c r="Z5" s="246"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -24202,7 +24173,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>5264783.2863974785</v>
+        <v>5293126.7945558801</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -24256,23 +24227,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>145045.14317194922</v>
+        <v>145096.76205834324</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>164614.60510554042</v>
+        <v>164731.79254685889</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>186824.37495979239</v>
+        <v>187023.90798210766</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>212030.68255541057</v>
+        <v>212332.67492642748</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>240637.82016981865</v>
+        <v>241066.31781924461</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -24291,15 +24262,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>3381410.8395504341</v>
+        <v>3405668.6243848167</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="241" t="s">
+      <c r="B14" s="247" t="s">
         <v>220</v>
       </c>
-      <c r="C14" s="242"/>
+      <c r="C14" s="248"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="152" t="s">
@@ -24307,7 +24278,7 @@
       </c>
       <c r="C15" s="153">
         <f ca="1">Overview!C5</f>
-        <v>299.77</v>
+        <v>275.14999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24316,7 +24287,7 @@
       </c>
       <c r="C16" s="153">
         <f ca="1">C36</f>
-        <v>299.07043409225474</v>
+        <v>300.79690064123361</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24326,20 +24297,20 @@
       <c r="C17" s="155">
         <v>0.24</v>
       </c>
-      <c r="E17" s="243" t="s">
+      <c r="E17" s="249" t="s">
         <v>223</v>
       </c>
-      <c r="F17" s="243"/>
-      <c r="G17" s="243"/>
-      <c r="H17" s="243"/>
-      <c r="I17" s="243"/>
+      <c r="F17" s="249"/>
+      <c r="G17" s="249"/>
+      <c r="H17" s="249"/>
+      <c r="I17" s="249"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="241" t="s">
+      <c r="B19" s="247" t="s">
         <v>181</v>
       </c>
-      <c r="C19" s="242"/>
+      <c r="C19" s="248"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="156" t="s">
@@ -24355,7 +24326,7 @@
       </c>
       <c r="C21" s="219">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.2588214866504731E-2</v>
+        <v>9.2199521237931792E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24373,7 +24344,7 @@
       </c>
       <c r="C23" s="158">
         <f ca="1">C15*C22</f>
-        <v>4402721.9899999993</v>
+        <v>4041128.05</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24400,15 +24371,15 @@
       </c>
       <c r="C26" s="159">
         <f ca="1">C23+C25-C24</f>
-        <v>4340837.9899999993</v>
+        <v>3979244.05</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="241" t="s">
+      <c r="B28" s="247" t="s">
         <v>183</v>
       </c>
-      <c r="C28" s="242"/>
+      <c r="C28" s="248"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="156" t="s">
@@ -24416,7 +24387,7 @@
       </c>
       <c r="C29" s="158">
         <f ca="1">SUM(H10:L10)</f>
-        <v>949152.62596251117</v>
+        <v>950251.45533298189</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24425,7 +24396,7 @@
       </c>
       <c r="C30" s="158">
         <f ca="1">L11</f>
-        <v>3381410.8395504341</v>
+        <v>3405668.6243848167</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24434,7 +24405,7 @@
       </c>
       <c r="C31" s="161">
         <f ca="1">C29+C30</f>
-        <v>4330563.4655129453</v>
+        <v>4355920.0797177982</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24461,7 +24432,7 @@
       </c>
       <c r="C34" s="161">
         <f ca="1">C31+C32-C33</f>
-        <v>4392447.4655129453</v>
+        <v>4417804.0797177982</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -24479,22 +24450,22 @@
       </c>
       <c r="C36" s="164">
         <f ca="1">C34/C35</f>
-        <v>299.07043409225474</v>
+        <v>300.79690064123361</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="235" t="s">
+      <c r="C39" s="241" t="s">
         <v>226</v>
       </c>
-      <c r="D39" s="235"/>
-      <c r="E39" s="235"/>
-      <c r="F39" s="235"/>
-      <c r="G39" s="235"/>
-      <c r="H39" s="235"/>
-      <c r="I39" s="235"/>
-      <c r="J39" s="235"/>
-      <c r="K39" s="235"/>
-      <c r="L39" s="235"/>
+      <c r="D39" s="241"/>
+      <c r="E39" s="241"/>
+      <c r="F39" s="241"/>
+      <c r="G39" s="241"/>
+      <c r="H39" s="241"/>
+      <c r="I39" s="241"/>
+      <c r="J39" s="241"/>
+      <c r="K39" s="241"/>
+      <c r="L39" s="241"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -24926,17 +24897,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29502,28 +29473,28 @@
       <c r="Q80" s="44">
         <v>1.02</v>
       </c>
-      <c r="T80" s="244">
+      <c r="T80" s="226">
         <v>0.25</v>
       </c>
-      <c r="U80" s="244">
+      <c r="U80" s="226">
         <v>0.25</v>
       </c>
-      <c r="V80" s="244">
+      <c r="V80" s="226">
         <v>0.25</v>
       </c>
-      <c r="W80" s="244">
+      <c r="W80" s="226">
         <v>0.25</v>
       </c>
-      <c r="X80" s="244">
+      <c r="X80" s="226">
         <v>0.26</v>
       </c>
-      <c r="Y80" s="244">
+      <c r="Y80" s="226">
         <v>0.26</v>
       </c>
-      <c r="Z80" s="244">
+      <c r="Z80" s="226">
         <v>0.26</v>
       </c>
-      <c r="AA80" s="244">
+      <c r="AA80" s="226">
         <v>0.26</v>
       </c>
       <c r="AC80" s="72">
@@ -31334,7 +31305,7 @@
       <c r="AA114" s="68"/>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>299.77</v>
+        <v>275.14999999999998</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -31381,7 +31352,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>299.77</v>
+        <v>275.14999999999998</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32295,7 +32266,7 @@
       <c r="AA140" s="49"/>
       <c r="AC140" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>36.247883917775091</v>
+        <v>33.270858524788387</v>
       </c>
     </row>
     <row r="141" spans="2:29" x14ac:dyDescent="0.2">
@@ -32332,7 +32303,7 @@
       <c r="AA141" s="49"/>
       <c r="AC141" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>9.8521792168207654</v>
+        <v>9.0430233562672502</v>
       </c>
     </row>
     <row r="142" spans="2:29" x14ac:dyDescent="0.2">
@@ -32369,7 +32340,7 @@
       <c r="AA142" s="49"/>
       <c r="AC142" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>41.343606408053262</v>
+        <v>37.948071198505033</v>
       </c>
     </row>
     <row r="143" spans="2:29" x14ac:dyDescent="0.2">
@@ -32406,7 +32377,7 @@
       <c r="AA143" s="49"/>
       <c r="AC143" s="143">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>4418609.8</v>
+        <v>4055710.9999999995</v>
       </c>
     </row>
     <row r="144" spans="2:29" x14ac:dyDescent="0.2">
@@ -32443,7 +32414,7 @@
       <c r="AA144" s="49"/>
       <c r="AC144" s="143">
         <f ca="1">AC143+AC106-AC105+AC47+AC44</f>
-        <v>4356725.8</v>
+        <v>3993826.9999999995</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
@@ -32480,7 +32451,7 @@
       <c r="AA145" s="49"/>
       <c r="AC145" s="180">
         <f ca="1">AC144/AC5</f>
-        <v>9.6506877959959407</v>
+        <v>8.8468219616251904</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
@@ -32517,7 +32488,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="180">
         <f ca="1">AC144/AC11</f>
-        <v>29.563982193993187</v>
+        <v>27.101414166089867</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32652,7 +32623,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f t="shared" ref="AC149:AC150" ca="1" si="89">AC143/AC147</f>
-        <v>38.189901556598471</v>
+        <v>35.053378968202516</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32689,7 +32660,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f t="shared" ca="1" si="89"/>
-        <v>37.694571317704373</v>
+        <v>34.554755932097741</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32726,7 +32697,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="74">
         <f t="shared" ref="AC151" ca="1" si="92">AC147/AC143</f>
-        <v>2.6184932645557435E-2</v>
+        <v>2.8527920258618035E-2</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32763,7 +32734,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>2.7587817326617074E-2</v>
+        <v>3.0056332909322189E-2</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32800,7 +32771,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="151">
         <f ca="1">AC81/AC115</f>
-        <v>3.4693264836374556E-3</v>
+        <v>3.7797564964564788E-3</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32837,7 +32808,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="151">
         <f ca="1">-AC62/AC143</f>
-        <v>1.76969688520584E-2</v>
+        <v>1.9280466482942203E-2</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32874,7 +32845,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="151">
         <f ca="1">-(AC62+AC63)/AC143</f>
-        <v>2.1216175277572597E-2</v>
+        <v>2.3114566101973245E-2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33377,7 +33348,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="151">
         <f ca="1">(AC105-AC106)/AC143</f>
-        <v>1.400530999591772E-2</v>
+        <v>1.5258483654284047E-2</v>
       </c>
     </row>
     <row r="167" spans="1:31" x14ac:dyDescent="0.2">
@@ -35374,15 +35345,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="226" t="s">
+      <c r="B4" s="235" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="226"/>
-      <c r="E4" s="226" t="s">
+      <c r="C4" s="235"/>
+      <c r="E4" s="235" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="226"/>
-      <c r="G4" s="226"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35390,7 +35361,7 @@
       </c>
       <c r="C5" s="169">
         <f ca="1">Overview!C5</f>
-        <v>299.77</v>
+        <v>275.14999999999998</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -35406,7 +35377,7 @@
       </c>
       <c r="C6" s="170">
         <f ca="1">Statement!AC143</f>
-        <v>4418609.8</v>
+        <v>4055710.9999999995</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -35426,7 +35397,7 @@
       </c>
       <c r="C7" s="170">
         <f ca="1">Statement!AC144</f>
-        <v>4356725.8</v>
+        <v>3993826.9999999995</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -35446,7 +35417,7 @@
       </c>
       <c r="C8" s="171">
         <f ca="1">Statement!AC140</f>
-        <v>36.247883917775091</v>
+        <v>33.270858524788387</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -35466,7 +35437,7 @@
       </c>
       <c r="C9" s="171">
         <f ca="1">Statement!AC141</f>
-        <v>9.8521792168207654</v>
+        <v>9.0430233562672502</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -35486,7 +35457,7 @@
       </c>
       <c r="C10" s="171">
         <f ca="1">Statement!AC142</f>
-        <v>41.343606408053262</v>
+        <v>37.948071198505033</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35506,7 +35477,7 @@
       </c>
       <c r="C11" s="171">
         <f ca="1">Statement!AC145</f>
-        <v>9.6506877959959407</v>
+        <v>8.8468219616251904</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35515,18 +35486,18 @@
       </c>
       <c r="C12" s="171">
         <f ca="1">Statement!AC146</f>
-        <v>29.563982193993187</v>
+        <v>27.101414166089867</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="226" t="s">
+      <c r="B15" s="235" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="226"/>
-      <c r="E15" s="226" t="s">
+      <c r="C15" s="235"/>
+      <c r="E15" s="235" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="226"/>
+      <c r="F15" s="235"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35577,14 +35548,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="226" t="s">
+      <c r="B21" s="235" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="226"/>
-      <c r="E21" s="226" t="s">
+      <c r="C21" s="235"/>
+      <c r="E21" s="235" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="226"/>
+      <c r="F21" s="235"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35653,14 +35624,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="226" t="s">
+      <c r="B29" s="235" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="226"/>
-      <c r="E29" s="226" t="s">
+      <c r="C29" s="235"/>
+      <c r="E29" s="235" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="226"/>
+      <c r="F29" s="235"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35736,14 +35707,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="226" t="s">
+      <c r="B37" s="235" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="226"/>
-      <c r="E37" s="226" t="s">
+      <c r="C37" s="235"/>
+      <c r="E37" s="235" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="226"/>
+      <c r="F37" s="235"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35751,7 +35722,7 @@
       </c>
       <c r="C38" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>2.7587817326617074E-2</v>
+        <v>3.0056332909322189E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -35767,7 +35738,7 @@
       </c>
       <c r="C39" s="212">
         <f ca="1">Statement!AC151</f>
-        <v>2.6184932645557435E-2</v>
+        <v>2.8527920258618035E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -35783,7 +35754,7 @@
       </c>
       <c r="C40" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>3.4693264836374556E-3</v>
+        <v>3.7797564964564788E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -35799,7 +35770,7 @@
       </c>
       <c r="C41" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>1.76969688520584E-2</v>
+        <v>1.9280466482942203E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35808,18 +35779,18 @@
       </c>
       <c r="C42" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>2.1216175277572597E-2</v>
+        <v>2.3114566101973245E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="226" t="s">
+      <c r="B45" s="235" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="226"/>
-      <c r="E45" s="226" t="s">
+      <c r="C45" s="235"/>
+      <c r="E45" s="235" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="226"/>
+      <c r="F45" s="235"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35852,18 +35823,18 @@
       </c>
       <c r="F48" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.400530999591772E-2</v>
+        <v>1.5258483654284047E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="226" t="s">
+      <c r="B51" s="235" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="226"/>
-      <c r="E51" s="226" t="s">
+      <c r="C51" s="235"/>
+      <c r="E51" s="235" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="226"/>
+      <c r="F51" s="235"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36031,7 +36002,7 @@
       </c>
       <c r="I6" s="169">
         <f ca="1">Statement!AC114</f>
-        <v>299.77</v>
+        <v>275.14999999999998</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36060,7 +36031,7 @@
       </c>
       <c r="I7" s="170">
         <f ca="1">Statement!AC143</f>
-        <v>4418609.8</v>
+        <v>4055710.9999999995</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36089,7 +36060,7 @@
       </c>
       <c r="I8" s="170">
         <f ca="1">Statement!AC144</f>
-        <v>4356725.8</v>
+        <v>3993826.9999999995</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36118,7 +36089,7 @@
       </c>
       <c r="I9" s="171">
         <f ca="1">Statement!AC140</f>
-        <v>36.247883917775091</v>
+        <v>33.270858524788387</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36147,7 +36118,7 @@
       </c>
       <c r="I10" s="171">
         <f ca="1">Statement!AC141</f>
-        <v>9.8521792168207654</v>
+        <v>9.0430233562672502</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36176,7 +36147,7 @@
       </c>
       <c r="I11" s="171">
         <f ca="1">Statement!AC142</f>
-        <v>41.343606408053262</v>
+        <v>37.948071198505033</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36205,7 +36176,7 @@
       </c>
       <c r="I12" s="171">
         <f ca="1">Statement!AC145</f>
-        <v>9.6506877959959407</v>
+        <v>8.8468219616251904</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36234,7 +36205,7 @@
       </c>
       <c r="I13" s="171">
         <f ca="1">Statement!AC146</f>
-        <v>29.563982193993187</v>
+        <v>27.101414166089867</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37007,7 +36978,7 @@
       </c>
       <c r="I51" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>2.7587817326617074E-2</v>
+        <v>3.0056332909322189E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37036,7 +37007,7 @@
       </c>
       <c r="I52" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>2.6184932645557435E-2</v>
+        <v>2.8527920258618035E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37065,7 +37036,7 @@
       </c>
       <c r="I53" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>3.4693264836374556E-3</v>
+        <v>3.7797564964564788E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -37094,7 +37065,7 @@
       </c>
       <c r="I54" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>1.76969688520584E-2</v>
+        <v>1.9280466482942203E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37123,7 +37094,7 @@
       </c>
       <c r="I55" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>2.1216175277572597E-2</v>
+        <v>2.3114566101973245E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37359,7 +37330,7 @@
       </c>
       <c r="I68" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>1.400530999591772E-2</v>
+        <v>1.5258483654284047E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38051,14 +38022,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="230" t="s">
+      <c r="C3" s="238" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="231"/>
-      <c r="F3" s="232" t="s">
+      <c r="D3" s="239"/>
+      <c r="F3" s="240" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="231"/>
+      <c r="G3" s="239"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38125,19 +38096,19 @@
       <c r="B7" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="233">
+      <c r="C7" s="236">
         <f>Statement!AA88</f>
         <v>-0.22657836890286318</v>
       </c>
-      <c r="D7" s="234"/>
-      <c r="F7" s="233">
+      <c r="D7" s="237"/>
+      <c r="F7" s="236">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.16595182415922985</v>
       </c>
-      <c r="G7" s="234"/>
+      <c r="G7" s="237"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="204" t="s">
@@ -38164,19 +38135,19 @@
       <c r="B9" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="233">
+      <c r="C9" s="236">
         <f>Statement!AA89</f>
         <v>-0.24316672257631666</v>
       </c>
-      <c r="D9" s="234"/>
-      <c r="F9" s="233">
+      <c r="D9" s="237"/>
+      <c r="F9" s="236">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.11706805038421929</v>
       </c>
-      <c r="G9" s="234"/>
+      <c r="G9" s="237"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="204" t="s">
@@ -38203,19 +38174,19 @@
       <c r="B11" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="233">
+      <c r="C11" s="236">
         <f>Statement!AA90</f>
         <v>-0.2087215264838006</v>
       </c>
-      <c r="D11" s="234"/>
-      <c r="F11" s="233">
+      <c r="D11" s="237"/>
+      <c r="F11" s="236">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.22096418302984375</v>
       </c>
-      <c r="G11" s="234"/>
+      <c r="G11" s="237"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="204" t="s">
@@ -38242,19 +38213,19 @@
       <c r="B13" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="233">
+      <c r="C13" s="236">
         <f>Statement!AA93</f>
         <v>2.8129930899396048E-2</v>
       </c>
-      <c r="D13" s="234"/>
-      <c r="F13" s="233">
+      <c r="D13" s="237"/>
+      <c r="F13" s="236">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.23681110092944102</v>
       </c>
-      <c r="G13" s="234"/>
+      <c r="G13" s="237"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="204" t="s">
@@ -38281,19 +38252,19 @@
       <c r="B15" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="233">
+      <c r="C15" s="236">
         <f>Statement!AA94</f>
         <v>-0.29432470699284197</v>
       </c>
-      <c r="D15" s="234"/>
-      <c r="F15" s="233">
+      <c r="D15" s="237"/>
+      <c r="F15" s="236">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.21278177701172732</v>
       </c>
-      <c r="G15" s="234"/>
+      <c r="G15" s="237"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="204" t="s">
@@ -38320,19 +38291,19 @@
       <c r="B17" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="233">
+      <c r="C17" s="236">
         <f>Statement!AA96</f>
         <v>-0.29738461173005204</v>
       </c>
-      <c r="D17" s="234"/>
-      <c r="F17" s="233">
+      <c r="D17" s="237"/>
+      <c r="F17" s="236">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.19362389023405974</v>
       </c>
-      <c r="G17" s="234"/>
+      <c r="G17" s="237"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="204" t="s">
@@ -38359,22 +38330,22 @@
       <c r="B19" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="233">
+      <c r="C19" s="236">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-5.6718433490884537E-3</v>
       </c>
-      <c r="D19" s="234"/>
-      <c r="F19" s="233">
+      <c r="D19" s="237"/>
+      <c r="F19" s="236">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-2.1918172157279491E-2</v>
       </c>
-      <c r="G19" s="234"/>
+      <c r="G19" s="237"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="204" t="s">
@@ -38401,22 +38372,22 @@
       <c r="B21" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="233">
+      <c r="C21" s="236">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.29225352112676062</v>
       </c>
-      <c r="D21" s="234"/>
-      <c r="F21" s="233">
+      <c r="D21" s="237"/>
+      <c r="F21" s="236">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.21818181818181812</v>
       </c>
-      <c r="G21" s="234"/>
+      <c r="G21" s="237"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38464,22 +38435,22 @@
       <c r="B25" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="233">
+      <c r="C25" s="236">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.22956141399989749</v>
       </c>
-      <c r="D25" s="234"/>
-      <c r="F25" s="233">
+      <c r="D25" s="237"/>
+      <c r="F25" s="236">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.11851668113605358</v>
       </c>
-      <c r="G25" s="234"/>
+      <c r="G25" s="237"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -38506,22 +38477,22 @@
       <c r="B27" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="233">
+      <c r="C27" s="236">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-0.26453625543962672</v>
       </c>
-      <c r="D27" s="234"/>
-      <c r="F27" s="233">
+      <c r="D27" s="237"/>
+      <c r="F27" s="236">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.14725607262615523</v>
       </c>
-      <c r="G27" s="234"/>
+      <c r="G27" s="237"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -38548,22 +38519,22 @@
       <c r="B29" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="233">
+      <c r="C29" s="236">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-0.19701480843061975</v>
       </c>
-      <c r="D29" s="234"/>
-      <c r="F29" s="233">
+      <c r="D29" s="237"/>
+      <c r="F29" s="236">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.28090238720159982</v>
       </c>
-      <c r="G29" s="234"/>
+      <c r="G29" s="237"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -38590,22 +38561,22 @@
       <c r="B31" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C31" s="233">
+      <c r="C31" s="236">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-0.10751088919579305</v>
       </c>
-      <c r="D31" s="234"/>
-      <c r="F31" s="233">
+      <c r="D31" s="237"/>
+      <c r="F31" s="236">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.15113729788983282</v>
       </c>
-      <c r="G31" s="234"/>
+      <c r="G31" s="237"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -38632,32 +38603,32 @@
       <c r="B33" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C33" s="233">
+      <c r="C33" s="236">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-0.2474056992258277</v>
       </c>
-      <c r="D33" s="234"/>
-      <c r="F33" s="233">
+      <c r="D33" s="237"/>
+      <c r="F33" s="236">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.25349794238683127</v>
       </c>
-      <c r="G33" s="234"/>
+      <c r="G33" s="237"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B35" s="245" t="s">
+      <c r="B35" s="227" t="s">
         <v>385</v>
       </c>
       <c r="C35" s="197">
         <f>Statement!Z183</f>
         <v>85269</v>
       </c>
-      <c r="D35" s="246">
+      <c r="D35" s="228">
         <f>Statement!AA183</f>
         <v>56994</v>
       </c>
@@ -38665,7 +38636,7 @@
         <f>Statement!W183</f>
         <v>46841</v>
       </c>
-      <c r="G35" s="246">
+      <c r="G35" s="228">
         <f>Statement!AA183</f>
         <v>56994</v>
       </c>
@@ -38674,32 +38645,32 @@
       <c r="B36" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C36" s="233">
+      <c r="C36" s="236">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>-0.33159764979066247</v>
       </c>
-      <c r="D36" s="234"/>
-      <c r="F36" s="233">
+      <c r="D36" s="237"/>
+      <c r="F36" s="236">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>0.21675455263551163</v>
       </c>
-      <c r="G36" s="234"/>
+      <c r="G36" s="237"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B37" s="245" t="s">
+      <c r="B37" s="227" t="s">
         <v>386</v>
       </c>
       <c r="C37" s="197">
         <f>Statement!Z184</f>
         <v>8386</v>
       </c>
-      <c r="D37" s="246">
+      <c r="D37" s="228">
         <f>Statement!AA184</f>
         <v>8399</v>
       </c>
@@ -38707,7 +38678,7 @@
         <f>Statement!W184</f>
         <v>7949</v>
       </c>
-      <c r="G37" s="246">
+      <c r="G37" s="228">
         <f>Statement!AA184</f>
         <v>8399</v>
       </c>
@@ -38716,32 +38687,32 @@
       <c r="B38" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C38" s="233">
+      <c r="C38" s="236">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>1.550202718817076E-3</v>
       </c>
-      <c r="D38" s="234"/>
-      <c r="F38" s="233">
+      <c r="D38" s="237"/>
+      <c r="F38" s="236">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>5.661089445213234E-2</v>
       </c>
-      <c r="G38" s="234"/>
+      <c r="G38" s="237"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B39" s="245" t="s">
+      <c r="B39" s="227" t="s">
         <v>387</v>
       </c>
       <c r="C39" s="197">
         <f>Statement!Z185</f>
         <v>8595</v>
       </c>
-      <c r="D39" s="246">
+      <c r="D39" s="228">
         <f>Statement!AA185</f>
         <v>6914</v>
       </c>
@@ -38749,7 +38720,7 @@
         <f>Statement!W185</f>
         <v>6402</v>
       </c>
-      <c r="G39" s="246">
+      <c r="G39" s="228">
         <f>Statement!AA185</f>
         <v>6914</v>
       </c>
@@ -38758,32 +38729,32 @@
       <c r="B40" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C40" s="233">
+      <c r="C40" s="236">
         <f>IF(C39=0,
 IF(D39=0,0,IF(D39&gt;0,1,-1)),
 (D39-C39)/ABS(C39)
 )</f>
         <v>-0.19557882489819661</v>
       </c>
-      <c r="D40" s="234"/>
-      <c r="F40" s="233">
+      <c r="D40" s="237"/>
+      <c r="F40" s="236">
         <f>IF(F39=0,
 IF(G39=0,0,IF(G39&gt;0,1,-1)),
 (G39-F39)/ABS(F39)
 )</f>
         <v>7.9975007810059354E-2</v>
       </c>
-      <c r="G40" s="234"/>
+      <c r="G40" s="237"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B41" s="245" t="s">
+      <c r="B41" s="227" t="s">
         <v>388</v>
       </c>
       <c r="C41" s="197">
         <f>Statement!Z186</f>
         <v>11493</v>
       </c>
-      <c r="D41" s="246">
+      <c r="D41" s="228">
         <f>Statement!AA186</f>
         <v>7901</v>
       </c>
@@ -38791,7 +38762,7 @@
         <f>Statement!W186</f>
         <v>7522</v>
       </c>
-      <c r="G41" s="246">
+      <c r="G41" s="228">
         <f>Statement!AA186</f>
         <v>7901</v>
       </c>
@@ -38800,32 +38771,32 @@
       <c r="B42" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C42" s="233">
+      <c r="C42" s="236">
         <f>IF(C41=0,
 IF(D41=0,0,IF(D41&gt;0,1,-1)),
 (D41-C41)/ABS(C41)
 )</f>
         <v>-0.31253806664926476</v>
       </c>
-      <c r="D42" s="234"/>
-      <c r="F42" s="233">
+      <c r="D42" s="237"/>
+      <c r="F42" s="236">
         <f>IF(F41=0,
 IF(G41=0,0,IF(G41&gt;0,1,-1)),
 (G41-F41)/ABS(F41)
 )</f>
         <v>5.0385535761765486E-2</v>
       </c>
-      <c r="G42" s="234"/>
+      <c r="G42" s="237"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B43" s="245" t="s">
+      <c r="B43" s="227" t="s">
         <v>365</v>
       </c>
       <c r="C43" s="197">
         <f>Statement!Z187</f>
         <v>30013</v>
       </c>
-      <c r="D43" s="246">
+      <c r="D43" s="228">
         <f>Statement!AA187</f>
         <v>30976</v>
       </c>
@@ -38833,7 +38804,7 @@
         <f>Statement!W187</f>
         <v>26645</v>
       </c>
-      <c r="G43" s="246">
+      <c r="G43" s="228">
         <f>Statement!AA187</f>
         <v>30976</v>
       </c>
@@ -38842,25 +38813,55 @@
       <c r="B44" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C44" s="233">
+      <c r="C44" s="236">
         <f>IF(C43=0,
 IF(D43=0,0,IF(D43&gt;0,1,-1)),
 (D43-C43)/ABS(C43)
 )</f>
         <v>3.2086096025055806E-2</v>
       </c>
-      <c r="D44" s="234"/>
-      <c r="F44" s="233">
+      <c r="D44" s="237"/>
+      <c r="F44" s="236">
         <f>IF(F43=0,
 IF(G43=0,0,IF(G43&gt;0,1,-1)),
 (G43-F43)/ABS(F43)
 )</f>
         <v>0.16254456746106211</v>
       </c>
-      <c r="G44" s="234"/>
+      <c r="G44" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F36:G36"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="F44:G44"/>
     <mergeCell ref="C38:D38"/>
@@ -38869,36 +38870,6 @@
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="F42:G42"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/AAPL.xlsx
+++ b/AAPL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF684A7F-51CC-D14A-9613-4BC650C4DB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8570968-7C2F-7742-AA71-196745752CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2287,6 +2287,9 @@
     <xf numFmtId="10" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="23" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2296,15 +2299,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2312,6 +2306,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15389,11 +15389,11 @@
     <v>Powered by Refinitiv</v>
     <v>317.39999999999998</v>
     <v>199.26070000000001</v>
-    <v>1.0964</v>
-    <v>-17.93</v>
-    <v>-6.1177999999999996E-2</v>
-    <v>0</v>
-    <v>0</v>
+    <v>1.1047</v>
+    <v>7.62</v>
+    <v>2.7046000000000001E-2</v>
+    <v>-0.3</v>
+    <v>-1.0369999999999999E-3</v>
     <v>USD</v>
     <v>Apple Inc. designs, manufactures and markets smartphones, personal computers, tablets, wearables and accessories, and sells a variety of related services. Its product categories include iPhone, Mac, iPad, Wearables, Home and Accessories. Its services include advertising, AppleCare, cloud services, digital content, and payment services. The Company operates various platforms, including the App Store, that allow customers to discover and download applications and digital content, such as books, music, video, games and podcasts. It also offers digital content through subscription-based services, including Apple Arcade, Apple Fitness+, Apple Music, Apple News+, and Apple TV+. Its wearables include smartwatches, wireless headphones, and spatial computers. Its products include iPhone 16 Pro, iPhone 16, iPhone 15, iPhone 14, iPhone SE, MacBook Air, MacBook Pro, iMac, Mac mini, Mac Studio, Mac Pro, iPad Pro, iPad Air, AirPods, AirPods Pro, AirPods Max, Apple TV, Apple Vision Pro and others.</v>
     <v>166000</v>
@@ -15401,25 +15401,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Apple Park Way, CUPERTINO, CA, 95014 US</v>
-    <v>288.8</v>
+    <v>289.94</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46198.910747233596</v>
+    <v>46203.952167812502</v>
     <v>0</v>
-    <v>273.75</v>
-    <v>4041227103999</v>
+    <v>280.69499999999999</v>
+    <v>4249934489600</v>
     <v>APPLE INC.</v>
     <v>APPLE INC.</v>
-    <v>287.39999999999998</v>
-    <v>33.417099999999998</v>
-    <v>293.08</v>
-    <v>275.14999999999998</v>
-    <v>275.14999999999998</v>
+    <v>281.17</v>
+    <v>35.142899999999997</v>
+    <v>281.74</v>
+    <v>289.36</v>
+    <v>289.06</v>
     <v>14687360000</v>
     <v>AAPL</v>
     <v>APPLE INC. (XNAS:AAPL)</v>
-    <v>106976285</v>
-    <v>51387349</v>
+    <v>65048942</v>
+    <v>63868052</v>
     <v>1977</v>
   </rv>
   <rv s="2">
@@ -15443,17 +15443,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.91</v>
-    <v>-2.0253999999999998E-2</v>
+    <v>0.02</v>
+    <v>4.5750000000000001E-4</v>
     <v>US</v>
-    <v>44.55</v>
+    <v>43.9</v>
     <v>Index</v>
     <v>3</v>
-    <v>43.98</v>
+    <v>43.67</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.53</v>
-    <v>44.93</v>
-    <v>44.02</v>
+    <v>43.78</v>
+    <v>43.72</v>
+    <v>43.74</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -16248,18 +16248,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="232" t="s">
+      <c r="B2" s="233" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="233"/>
-      <c r="E2" s="232" t="s">
+      <c r="C2" s="234"/>
+      <c r="E2" s="233" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="233"/>
-      <c r="H2" s="232" t="s">
+      <c r="F2" s="234"/>
+      <c r="H2" s="233" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="233"/>
+      <c r="I2" s="234"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="182" t="s">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="F3" s="184">
         <f ca="1">Statement!AC143</f>
-        <v>4055710.9999999995</v>
+        <v>4265166.4000000004</v>
       </c>
       <c r="H3" s="182" t="str">
         <f>'AVG target price'!B5</f>
@@ -16282,7 +16282,7 @@
       </c>
       <c r="I3" s="208">
         <f ca="1">'AVG target price'!C5</f>
-        <v>119.93072905261404</v>
+        <v>119.68851520308499</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="F4" s="185">
         <f ca="1">Statement!AC144</f>
-        <v>3993826.9999999995</v>
+        <v>4203282.4000000004</v>
       </c>
       <c r="H4" s="182" t="str">
         <f>'AVG target price'!B6</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="I4" s="208">
         <f ca="1">'AVG target price'!C6</f>
-        <v>191.41111102679096</v>
+        <v>191.28349310124528</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16315,7 +16315,7 @@
       </c>
       <c r="C5" s="205" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>275.14999999999998</v>
+        <v>289.36</v>
       </c>
       <c r="E5" s="182" t="s">
         <v>242</v>
@@ -16339,14 +16339,14 @@
       </c>
       <c r="C6" s="205" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>275.14999999999998</v>
+        <v>289.06</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="187">
         <f ca="1">Statement!AC140</f>
-        <v>33.270858524788387</v>
+        <v>34.989117291414757</v>
       </c>
       <c r="H6" s="182" t="str">
         <f>'AVG target price'!B8</f>
@@ -16354,7 +16354,7 @@
       </c>
       <c r="I6" s="208">
         <f ca="1">'AVG target price'!C8</f>
-        <v>122.30090520877316</v>
+        <v>122.21992262514725</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16363,14 +16363,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-17.93</v>
+        <v>7.62</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>198</v>
       </c>
       <c r="F7" s="188">
         <f ca="1">Statement!AC141</f>
-        <v>9.0430233562672502</v>
+        <v>9.5100462960911933</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -16378,7 +16378,7 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>143.08254439363199</v>
+        <v>142.9698408039568</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -16387,14 +16387,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="189">
         <f ca="1">Statement!AC151</f>
-        <v>2.8527920258618035E-2</v>
+        <v>2.7126960392447993E-2</v>
       </c>
       <c r="H8" s="181" t="str">
         <f>'AVG target price'!B11</f>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.47998348394100671</v>
+        <v>-0.50591014375187726</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16411,14 +16411,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-6.1177999999999996E-2</v>
+        <v>2.7046000000000001E-2</v>
       </c>
       <c r="E9" s="182" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="189">
         <f ca="1">Statement!AC152</f>
-        <v>3.0056332909322189E-2</v>
+        <v>2.8580315178324576E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -16427,14 +16427,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>0</v>
+        <v>-1.0369999999999999E-3</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="189">
         <f ca="1">Statement!AC154</f>
-        <v>1.9280466482942203E-2</v>
+        <v>1.8333634064077779E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="F11" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>3.7797564964564788E-3</v>
+        <v>3.5941387890517005E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -16475,7 +16475,7 @@
       </c>
       <c r="C13" s="206" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0964</v>
+        <v>1.1047</v>
       </c>
       <c r="E13" s="182" t="s">
         <v>101</v>
@@ -16491,7 +16491,7 @@
       </c>
       <c r="C14" s="207" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>51387349</v>
+        <v>63868052</v>
       </c>
       <c r="E14" s="183" t="s">
         <v>102</v>
@@ -16507,7 +16507,7 @@
       </c>
       <c r="F15" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.5258483654284047E-2</v>
+        <v>1.4509164284891674E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -16520,10 +16520,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="234" t="s">
+      <c r="B17" s="235" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="234"/>
+      <c r="C17" s="235"/>
       <c r="E17" s="181" t="s">
         <v>295</v>
       </c>
@@ -16596,14 +16596,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="234" t="s">
+      <c r="B25" s="235" t="s">
         <v>104</v>
       </c>
-      <c r="C25" s="234"/>
-      <c r="E25" s="232" t="s">
+      <c r="C25" s="235"/>
+      <c r="E25" s="233" t="s">
         <v>342</v>
       </c>
-      <c r="F25" s="233"/>
+      <c r="F25" s="234"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="181" t="s">
@@ -16617,7 +16617,7 @@
       </c>
       <c r="F26" s="216" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.02</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="F27" s="217">
         <f ca="1">F26/1000</f>
-        <v>4.4020000000000004E-2</v>
+        <v>4.3740000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16652,15 +16652,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="235" t="s">
+      <c r="B33" s="232" t="s">
         <v>337</v>
       </c>
-      <c r="C33" s="235"/>
-      <c r="D33" s="235"/>
-      <c r="E33" s="235"/>
-      <c r="F33" s="235"/>
-      <c r="G33" s="235"/>
-      <c r="H33" s="235"/>
+      <c r="C33" s="232"/>
+      <c r="D33" s="232"/>
+      <c r="E33" s="232"/>
+      <c r="F33" s="232"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="232"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -16673,24 +16673,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="235"/>
-      <c r="C39" s="235"/>
-      <c r="D39" s="235"/>
-      <c r="E39" s="235"/>
-      <c r="F39" s="235"/>
-      <c r="G39" s="235"/>
-      <c r="H39" s="235"/>
+      <c r="B39" s="232"/>
+      <c r="C39" s="232"/>
+      <c r="D39" s="232"/>
+      <c r="E39" s="232"/>
+      <c r="F39" s="232"/>
+      <c r="G39" s="232"/>
+      <c r="H39" s="232"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="235" t="s">
+      <c r="B42" s="232" t="s">
         <v>340</v>
       </c>
-      <c r="C42" s="235"/>
-      <c r="D42" s="235"/>
-      <c r="E42" s="235"/>
-      <c r="F42" s="235"/>
-      <c r="G42" s="235"/>
-      <c r="H42" s="235"/>
+      <c r="C42" s="232"/>
+      <c r="D42" s="232"/>
+      <c r="E42" s="232"/>
+      <c r="F42" s="232"/>
+      <c r="G42" s="232"/>
+      <c r="H42" s="232"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -16705,24 +16705,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="235"/>
-      <c r="C49" s="235"/>
-      <c r="D49" s="235"/>
-      <c r="E49" s="235"/>
-      <c r="F49" s="235"/>
-      <c r="G49" s="235"/>
-      <c r="H49" s="235"/>
+      <c r="B49" s="232"/>
+      <c r="C49" s="232"/>
+      <c r="D49" s="232"/>
+      <c r="E49" s="232"/>
+      <c r="F49" s="232"/>
+      <c r="G49" s="232"/>
+      <c r="H49" s="232"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="235" t="s">
+      <c r="B52" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="C52" s="235"/>
-      <c r="D52" s="235"/>
-      <c r="E52" s="235"/>
-      <c r="F52" s="235"/>
-      <c r="G52" s="235"/>
-      <c r="H52" s="235"/>
+      <c r="C52" s="232"/>
+      <c r="D52" s="232"/>
+      <c r="E52" s="232"/>
+      <c r="F52" s="232"/>
+      <c r="G52" s="232"/>
+      <c r="H52" s="232"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -16737,28 +16737,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="235"/>
-      <c r="C59" s="235"/>
-      <c r="D59" s="235"/>
-      <c r="E59" s="235"/>
-      <c r="F59" s="235"/>
-      <c r="G59" s="235"/>
-      <c r="H59" s="235"/>
+      <c r="B59" s="232"/>
+      <c r="C59" s="232"/>
+      <c r="D59" s="232"/>
+      <c r="E59" s="232"/>
+      <c r="F59" s="232"/>
+      <c r="G59" s="232"/>
+      <c r="H59" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -16828,36 +16828,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="235" t="s">
+      <c r="S2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235"/>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
-      <c r="AA2" s="235" t="s">
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
+      <c r="AA2" s="232" t="s">
         <v>111</v>
       </c>
-      <c r="AB2" s="235"/>
-      <c r="AC2" s="235"/>
+      <c r="AB2" s="232"/>
+      <c r="AC2" s="232"/>
       <c r="AE2" s="85" t="s">
         <v>112</v>
       </c>
@@ -18228,35 +18228,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
-      <c r="P2" s="235" t="s">
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
+      <c r="P2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="Q2" s="235"/>
-      <c r="R2" s="235"/>
-      <c r="S2" s="235"/>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235" t="s">
+      <c r="Q2" s="232"/>
+      <c r="R2" s="232"/>
+      <c r="S2" s="232"/>
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232" t="s">
         <v>111</v>
       </c>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
       <c r="AB2" s="85" t="s">
         <v>112</v>
       </c>
@@ -19487,20 +19487,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -20893,12 +20893,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20906,6 +20900,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20943,20 +20943,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="S2" s="246"/>
       <c r="T2" s="246"/>
       <c r="U2" s="246"/>
@@ -21965,16 +21965,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22037,10 +22037,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="232"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22057,7 +22057,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>275.14999999999998</v>
+        <v>289.36</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22066,7 +22066,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>4055710.9999999995</v>
+        <v>4265166.4000000004</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.4020000000000004E-2</v>
+        <v>4.3740000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22093,7 +22093,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.0964</v>
+        <v>1.1047</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22125,10 +22125,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="232" t="s">
         <v>170</v>
       </c>
-      <c r="C15" s="235"/>
+      <c r="C15" s="232"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>2.0459508716744335E-2</v>
+        <v>1.9474341966511516E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22145,7 +22145,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.97954049128325571</v>
+        <v>0.98052565803348846</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22163,7 +22163,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.3357999999999997E-2</v>
+        <v>9.3451499999999993E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22172,7 +22172,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.2199521237931792E-2</v>
+        <v>9.2346983483856337E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22217,20 +22217,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>1942056.6772973558</v>
+        <v>1938098.253247638</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22477,23 +22477,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>96458.541227844995</v>
+        <v>96445.519730698827</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>93281.704388500948</v>
+        <v>93256.520813370589</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>90524.271782232376</v>
+        <v>90487.615543884356</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>87637.552466566398</v>
+        <v>87590.239245136399</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>88447.617138865826</v>
+        <v>88387.932974733514</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22512,14 +22512,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>1249545.2592315206</v>
+        <v>1246156.8857856491</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="235" t="s">
+      <c r="B13" s="232" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="235"/>
+      <c r="C13" s="232"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22535,14 +22535,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.2199521237931792E-2</v>
+        <v>9.2346983483856337E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="235" t="s">
+      <c r="B18" s="232" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="235"/>
+      <c r="C18" s="232"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22550,7 +22550,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>456349.68700401054</v>
+        <v>456167.82830782369</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -22559,7 +22559,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>1249545.2592315206</v>
+        <v>1246156.8857856491</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>1705894.946235531</v>
+        <v>1702324.7140934728</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -22595,7 +22595,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>1767778.946235531</v>
+        <v>1764208.7140934728</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -22613,7 +22613,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>119.93072905261404</v>
+        <v>119.68851520308499</v>
       </c>
     </row>
   </sheetData>
@@ -22656,20 +22656,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -23601,10 +23601,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="232" t="s">
         <v>202</v>
       </c>
-      <c r="C37" s="235"/>
+      <c r="C37" s="232"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.2199521237931792E-2</v>
+        <v>9.2346983483856337E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -23657,7 +23657,7 @@
       </c>
       <c r="C43" s="24">
         <f ca="1">C42/(1+C39)^5-G30+G31</f>
-        <v>2821399.7765348987</v>
+        <v>2819518.6883123554</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -23675,14 +23675,14 @@
       </c>
       <c r="C45" s="142">
         <f ca="1">C43/C44</f>
-        <v>191.41111102679096</v>
+        <v>191.28349310124528</v>
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="235" t="s">
+      <c r="B47" s="232" t="s">
         <v>207</v>
       </c>
-      <c r="C47" s="235"/>
+      <c r="C47" s="232"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
@@ -23738,10 +23738,10 @@
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="235" t="s">
+      <c r="B55" s="232" t="s">
         <v>321</v>
       </c>
-      <c r="C55" s="235"/>
+      <c r="C55" s="232"/>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C57" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.2199521237931792E-2</v>
+        <v>9.2346983483856337E-2</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
@@ -23784,7 +23784,7 @@
       </c>
       <c r="C60" s="24">
         <f ca="1">C59/(1+C57)^5-G30+G31</f>
-        <v>1802715.3427773165</v>
+        <v>1801521.6594946703</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C62" s="142">
         <f ca="1">C60/C61</f>
-        <v>122.30090520877316</v>
+        <v>122.21992262514725</v>
       </c>
     </row>
   </sheetData>
@@ -23854,10 +23854,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>212</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="232"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23866,7 +23866,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>119.93072905261404</v>
+        <v>119.68851520308499</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23875,7 +23875,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C45</f>
-        <v>191.41111102679096</v>
+        <v>191.28349310124528</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C62</f>
-        <v>122.30090520877316</v>
+        <v>122.21992262514725</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>143.08254439363199</v>
+        <v>142.9698408039568</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23911,7 +23911,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>275.14999999999998</v>
+        <v>289.36</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="C11" s="151">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.47998348394100671</v>
+        <v>-0.50591014375187726</v>
       </c>
     </row>
   </sheetData>
@@ -23985,20 +23985,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -24173,7 +24173,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>5293126.7945558801</v>
+        <v>5282338.0052034836</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -24227,23 +24227,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>145096.76205834324</v>
+        <v>145077.1746060657</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>164731.79254685889</v>
+        <v>164687.31935137906</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>187023.90798210766</v>
+        <v>186948.17588492756</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>212332.67492642748</v>
+        <v>212218.04207118601</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>241066.31781924461</v>
+        <v>240903.64705269467</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -24262,7 +24262,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>3405668.6243848167</v>
+        <v>3396433.5230172998</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24278,7 +24278,7 @@
       </c>
       <c r="C15" s="153">
         <f ca="1">Overview!C5</f>
-        <v>275.14999999999998</v>
+        <v>289.36</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24287,7 +24287,7 @@
       </c>
       <c r="C16" s="153">
         <f ca="1">C36</f>
-        <v>300.79690064123361</v>
+        <v>300.13970735913074</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="C21" s="219">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.2199521237931792E-2</v>
+        <v>9.2346983483856337E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24344,7 +24344,7 @@
       </c>
       <c r="C23" s="158">
         <f ca="1">C15*C22</f>
-        <v>4041128.05</v>
+        <v>4249830.32</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24371,7 +24371,7 @@
       </c>
       <c r="C26" s="159">
         <f ca="1">C23+C25-C24</f>
-        <v>3979244.05</v>
+        <v>4187946.3200000003</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24387,7 +24387,7 @@
       </c>
       <c r="C29" s="158">
         <f ca="1">SUM(H10:L10)</f>
-        <v>950251.45533298189</v>
+        <v>949834.35896625312</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24396,7 +24396,7 @@
       </c>
       <c r="C30" s="158">
         <f ca="1">L11</f>
-        <v>3405668.6243848167</v>
+        <v>3396433.5230172998</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24405,7 +24405,7 @@
       </c>
       <c r="C31" s="161">
         <f ca="1">C29+C30</f>
-        <v>4355920.0797177982</v>
+        <v>4346267.8819835531</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24432,7 +24432,7 @@
       </c>
       <c r="C34" s="161">
         <f ca="1">C31+C32-C33</f>
-        <v>4417804.0797177982</v>
+        <v>4408151.8819835531</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -24450,7 +24450,7 @@
       </c>
       <c r="C36" s="164">
         <f ca="1">C34/C35</f>
-        <v>300.79690064123361</v>
+        <v>300.13970735913074</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -24897,17 +24897,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31305,7 +31305,7 @@
       <c r="AA114" s="68"/>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>275.14999999999998</v>
+        <v>289.36</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -31352,7 +31352,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>275.14999999999998</v>
+        <v>289.36</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32266,7 +32266,7 @@
       <c r="AA140" s="49"/>
       <c r="AC140" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>33.270858524788387</v>
+        <v>34.989117291414757</v>
       </c>
     </row>
     <row r="141" spans="2:29" x14ac:dyDescent="0.2">
@@ -32303,7 +32303,7 @@
       <c r="AA141" s="49"/>
       <c r="AC141" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>9.0430233562672502</v>
+        <v>9.5100462960911933</v>
       </c>
     </row>
     <row r="142" spans="2:29" x14ac:dyDescent="0.2">
@@ -32340,7 +32340,7 @@
       <c r="AA142" s="49"/>
       <c r="AC142" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>37.948071198505033</v>
+        <v>39.907882544064755</v>
       </c>
     </row>
     <row r="143" spans="2:29" x14ac:dyDescent="0.2">
@@ -32377,7 +32377,7 @@
       <c r="AA143" s="49"/>
       <c r="AC143" s="143">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>4055710.9999999995</v>
+        <v>4265166.4000000004</v>
       </c>
     </row>
     <row r="144" spans="2:29" x14ac:dyDescent="0.2">
@@ -32414,7 +32414,7 @@
       <c r="AA144" s="49"/>
       <c r="AC144" s="143">
         <f ca="1">AC143+AC106-AC105+AC47+AC44</f>
-        <v>3993826.9999999995</v>
+        <v>4203282.4000000004</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
@@ -32451,7 +32451,7 @@
       <c r="AA145" s="49"/>
       <c r="AC145" s="180">
         <f ca="1">AC144/AC5</f>
-        <v>8.8468219616251904</v>
+        <v>9.3107916410081479</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
@@ -32488,7 +32488,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="180">
         <f ca="1">AC144/AC11</f>
-        <v>27.101414166089867</v>
+        <v>28.522742016475988</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32623,7 +32623,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f t="shared" ref="AC149:AC150" ca="1" si="89">AC143/AC147</f>
-        <v>35.053378968202516</v>
+        <v>36.863695214388812</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32660,7 +32660,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f t="shared" ca="1" si="89"/>
-        <v>34.554755932097741</v>
+        <v>36.366972692027488</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32697,7 +32697,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="74">
         <f t="shared" ref="AC151" ca="1" si="92">AC147/AC143</f>
-        <v>2.8527920258618035E-2</v>
+        <v>2.7126960392447993E-2</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32734,7 +32734,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.0056332909322189E-2</v>
+        <v>2.8580315178324576E-2</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32771,7 +32771,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="151">
         <f ca="1">AC81/AC115</f>
-        <v>3.7797564964564788E-3</v>
+        <v>3.5941387890517005E-3</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32808,7 +32808,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="151">
         <f ca="1">-AC62/AC143</f>
-        <v>1.9280466482942203E-2</v>
+        <v>1.8333634064077779E-2</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32845,7 +32845,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="151">
         <f ca="1">-(AC62+AC63)/AC143</f>
-        <v>2.3114566101973245E-2</v>
+        <v>2.1979447273147417E-2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33348,7 +33348,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="151">
         <f ca="1">(AC105-AC106)/AC143</f>
-        <v>1.5258483654284047E-2</v>
+        <v>1.4509164284891674E-2</v>
       </c>
     </row>
     <row r="167" spans="1:31" x14ac:dyDescent="0.2">
@@ -35345,15 +35345,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="235"/>
-      <c r="E4" s="235" t="s">
+      <c r="C4" s="232"/>
+      <c r="E4" s="232" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
+      <c r="F4" s="232"/>
+      <c r="G4" s="232"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35361,7 +35361,7 @@
       </c>
       <c r="C5" s="169">
         <f ca="1">Overview!C5</f>
-        <v>275.14999999999998</v>
+        <v>289.36</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -35377,7 +35377,7 @@
       </c>
       <c r="C6" s="170">
         <f ca="1">Statement!AC143</f>
-        <v>4055710.9999999995</v>
+        <v>4265166.4000000004</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -35397,7 +35397,7 @@
       </c>
       <c r="C7" s="170">
         <f ca="1">Statement!AC144</f>
-        <v>3993826.9999999995</v>
+        <v>4203282.4000000004</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -35417,7 +35417,7 @@
       </c>
       <c r="C8" s="171">
         <f ca="1">Statement!AC140</f>
-        <v>33.270858524788387</v>
+        <v>34.989117291414757</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -35437,7 +35437,7 @@
       </c>
       <c r="C9" s="171">
         <f ca="1">Statement!AC141</f>
-        <v>9.0430233562672502</v>
+        <v>9.5100462960911933</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -35457,7 +35457,7 @@
       </c>
       <c r="C10" s="171">
         <f ca="1">Statement!AC142</f>
-        <v>37.948071198505033</v>
+        <v>39.907882544064755</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="C11" s="171">
         <f ca="1">Statement!AC145</f>
-        <v>8.8468219616251904</v>
+        <v>9.3107916410081479</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35486,18 +35486,18 @@
       </c>
       <c r="C12" s="171">
         <f ca="1">Statement!AC146</f>
-        <v>27.101414166089867</v>
+        <v>28.522742016475988</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="235"/>
-      <c r="E15" s="235" t="s">
+      <c r="C15" s="232"/>
+      <c r="E15" s="232" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="235"/>
+      <c r="F15" s="232"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35548,14 +35548,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="235" t="s">
+      <c r="B21" s="232" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="235"/>
-      <c r="E21" s="235" t="s">
+      <c r="C21" s="232"/>
+      <c r="E21" s="232" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="235"/>
+      <c r="F21" s="232"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35624,14 +35624,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="235" t="s">
+      <c r="B29" s="232" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="235"/>
-      <c r="E29" s="235" t="s">
+      <c r="C29" s="232"/>
+      <c r="E29" s="232" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="235"/>
+      <c r="F29" s="232"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35707,14 +35707,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="232" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="235"/>
-      <c r="E37" s="235" t="s">
+      <c r="C37" s="232"/>
+      <c r="E37" s="232" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="235"/>
+      <c r="F37" s="232"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35722,7 +35722,7 @@
       </c>
       <c r="C38" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>3.0056332909322189E-2</v>
+        <v>2.8580315178324576E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -35738,7 +35738,7 @@
       </c>
       <c r="C39" s="212">
         <f ca="1">Statement!AC151</f>
-        <v>2.8527920258618035E-2</v>
+        <v>2.7126960392447993E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -35754,7 +35754,7 @@
       </c>
       <c r="C40" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>3.7797564964564788E-3</v>
+        <v>3.5941387890517005E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -35770,7 +35770,7 @@
       </c>
       <c r="C41" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>1.9280466482942203E-2</v>
+        <v>1.8333634064077779E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35779,18 +35779,18 @@
       </c>
       <c r="C42" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>2.3114566101973245E-2</v>
+        <v>2.1979447273147417E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="235" t="s">
+      <c r="B45" s="232" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="235"/>
-      <c r="E45" s="235" t="s">
+      <c r="C45" s="232"/>
+      <c r="E45" s="232" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="235"/>
+      <c r="F45" s="232"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35823,18 +35823,18 @@
       </c>
       <c r="F48" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.5258483654284047E-2</v>
+        <v>1.4509164284891674E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="235" t="s">
+      <c r="B51" s="232" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="235"/>
-      <c r="E51" s="235" t="s">
+      <c r="C51" s="232"/>
+      <c r="E51" s="232" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="235"/>
+      <c r="F51" s="232"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36002,7 +36002,7 @@
       </c>
       <c r="I6" s="169">
         <f ca="1">Statement!AC114</f>
-        <v>275.14999999999998</v>
+        <v>289.36</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36031,7 +36031,7 @@
       </c>
       <c r="I7" s="170">
         <f ca="1">Statement!AC143</f>
-        <v>4055710.9999999995</v>
+        <v>4265166.4000000004</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36060,7 +36060,7 @@
       </c>
       <c r="I8" s="170">
         <f ca="1">Statement!AC144</f>
-        <v>3993826.9999999995</v>
+        <v>4203282.4000000004</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36089,7 +36089,7 @@
       </c>
       <c r="I9" s="171">
         <f ca="1">Statement!AC140</f>
-        <v>33.270858524788387</v>
+        <v>34.989117291414757</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36118,7 +36118,7 @@
       </c>
       <c r="I10" s="171">
         <f ca="1">Statement!AC141</f>
-        <v>9.0430233562672502</v>
+        <v>9.5100462960911933</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36147,7 +36147,7 @@
       </c>
       <c r="I11" s="171">
         <f ca="1">Statement!AC142</f>
-        <v>37.948071198505033</v>
+        <v>39.907882544064755</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36176,7 +36176,7 @@
       </c>
       <c r="I12" s="171">
         <f ca="1">Statement!AC145</f>
-        <v>8.8468219616251904</v>
+        <v>9.3107916410081479</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36205,7 +36205,7 @@
       </c>
       <c r="I13" s="171">
         <f ca="1">Statement!AC146</f>
-        <v>27.101414166089867</v>
+        <v>28.522742016475988</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36978,7 +36978,7 @@
       </c>
       <c r="I51" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>3.0056332909322189E-2</v>
+        <v>2.8580315178324576E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37007,7 +37007,7 @@
       </c>
       <c r="I52" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>2.8527920258618035E-2</v>
+        <v>2.7126960392447993E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37036,7 +37036,7 @@
       </c>
       <c r="I53" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>3.7797564964564788E-3</v>
+        <v>3.5941387890517005E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -37065,7 +37065,7 @@
       </c>
       <c r="I54" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>1.9280466482942203E-2</v>
+        <v>1.8333634064077779E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37094,7 +37094,7 @@
       </c>
       <c r="I55" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>2.3114566101973245E-2</v>
+        <v>2.1979447273147417E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37330,7 +37330,7 @@
       </c>
       <c r="I68" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>1.5258483654284047E-2</v>
+        <v>1.4509164284891674E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38022,14 +38022,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="236" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="239"/>
-      <c r="F3" s="240" t="s">
+      <c r="D3" s="237"/>
+      <c r="F3" s="238" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="239"/>
+      <c r="G3" s="237"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38096,19 +38096,19 @@
       <c r="B7" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="236">
+      <c r="C7" s="239">
         <f>Statement!AA88</f>
         <v>-0.22657836890286318</v>
       </c>
-      <c r="D7" s="237"/>
-      <c r="F7" s="236">
+      <c r="D7" s="240"/>
+      <c r="F7" s="239">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.16595182415922985</v>
       </c>
-      <c r="G7" s="237"/>
+      <c r="G7" s="240"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="204" t="s">
@@ -38135,19 +38135,19 @@
       <c r="B9" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="236">
+      <c r="C9" s="239">
         <f>Statement!AA89</f>
         <v>-0.24316672257631666</v>
       </c>
-      <c r="D9" s="237"/>
-      <c r="F9" s="236">
+      <c r="D9" s="240"/>
+      <c r="F9" s="239">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.11706805038421929</v>
       </c>
-      <c r="G9" s="237"/>
+      <c r="G9" s="240"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="204" t="s">
@@ -38174,19 +38174,19 @@
       <c r="B11" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="236">
+      <c r="C11" s="239">
         <f>Statement!AA90</f>
         <v>-0.2087215264838006</v>
       </c>
-      <c r="D11" s="237"/>
-      <c r="F11" s="236">
+      <c r="D11" s="240"/>
+      <c r="F11" s="239">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.22096418302984375</v>
       </c>
-      <c r="G11" s="237"/>
+      <c r="G11" s="240"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="204" t="s">
@@ -38213,19 +38213,19 @@
       <c r="B13" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="236">
+      <c r="C13" s="239">
         <f>Statement!AA93</f>
         <v>2.8129930899396048E-2</v>
       </c>
-      <c r="D13" s="237"/>
-      <c r="F13" s="236">
+      <c r="D13" s="240"/>
+      <c r="F13" s="239">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.23681110092944102</v>
       </c>
-      <c r="G13" s="237"/>
+      <c r="G13" s="240"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="204" t="s">
@@ -38252,19 +38252,19 @@
       <c r="B15" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="236">
+      <c r="C15" s="239">
         <f>Statement!AA94</f>
         <v>-0.29432470699284197</v>
       </c>
-      <c r="D15" s="237"/>
-      <c r="F15" s="236">
+      <c r="D15" s="240"/>
+      <c r="F15" s="239">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.21278177701172732</v>
       </c>
-      <c r="G15" s="237"/>
+      <c r="G15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="204" t="s">
@@ -38291,19 +38291,19 @@
       <c r="B17" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="236">
+      <c r="C17" s="239">
         <f>Statement!AA96</f>
         <v>-0.29738461173005204</v>
       </c>
-      <c r="D17" s="237"/>
-      <c r="F17" s="236">
+      <c r="D17" s="240"/>
+      <c r="F17" s="239">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.19362389023405974</v>
       </c>
-      <c r="G17" s="237"/>
+      <c r="G17" s="240"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="204" t="s">
@@ -38330,22 +38330,22 @@
       <c r="B19" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="236">
+      <c r="C19" s="239">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-5.6718433490884537E-3</v>
       </c>
-      <c r="D19" s="237"/>
-      <c r="F19" s="236">
+      <c r="D19" s="240"/>
+      <c r="F19" s="239">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-2.1918172157279491E-2</v>
       </c>
-      <c r="G19" s="237"/>
+      <c r="G19" s="240"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="204" t="s">
@@ -38372,22 +38372,22 @@
       <c r="B21" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="236">
+      <c r="C21" s="239">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.29225352112676062</v>
       </c>
-      <c r="D21" s="237"/>
-      <c r="F21" s="236">
+      <c r="D21" s="240"/>
+      <c r="F21" s="239">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.21818181818181812</v>
       </c>
-      <c r="G21" s="237"/>
+      <c r="G21" s="240"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38435,22 +38435,22 @@
       <c r="B25" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="236">
+      <c r="C25" s="239">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.22956141399989749</v>
       </c>
-      <c r="D25" s="237"/>
-      <c r="F25" s="236">
+      <c r="D25" s="240"/>
+      <c r="F25" s="239">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.11851668113605358</v>
       </c>
-      <c r="G25" s="237"/>
+      <c r="G25" s="240"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -38477,22 +38477,22 @@
       <c r="B27" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="236">
+      <c r="C27" s="239">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-0.26453625543962672</v>
       </c>
-      <c r="D27" s="237"/>
-      <c r="F27" s="236">
+      <c r="D27" s="240"/>
+      <c r="F27" s="239">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.14725607262615523</v>
       </c>
-      <c r="G27" s="237"/>
+      <c r="G27" s="240"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -38519,22 +38519,22 @@
       <c r="B29" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="236">
+      <c r="C29" s="239">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-0.19701480843061975</v>
       </c>
-      <c r="D29" s="237"/>
-      <c r="F29" s="236">
+      <c r="D29" s="240"/>
+      <c r="F29" s="239">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.28090238720159982</v>
       </c>
-      <c r="G29" s="237"/>
+      <c r="G29" s="240"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -38561,22 +38561,22 @@
       <c r="B31" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C31" s="236">
+      <c r="C31" s="239">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-0.10751088919579305</v>
       </c>
-      <c r="D31" s="237"/>
-      <c r="F31" s="236">
+      <c r="D31" s="240"/>
+      <c r="F31" s="239">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.15113729788983282</v>
       </c>
-      <c r="G31" s="237"/>
+      <c r="G31" s="240"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -38603,22 +38603,22 @@
       <c r="B33" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C33" s="236">
+      <c r="C33" s="239">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-0.2474056992258277</v>
       </c>
-      <c r="D33" s="237"/>
-      <c r="F33" s="236">
+      <c r="D33" s="240"/>
+      <c r="F33" s="239">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.25349794238683127</v>
       </c>
-      <c r="G33" s="237"/>
+      <c r="G33" s="240"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="227" t="s">
@@ -38645,22 +38645,22 @@
       <c r="B36" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C36" s="236">
+      <c r="C36" s="239">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>-0.33159764979066247</v>
       </c>
-      <c r="D36" s="237"/>
-      <c r="F36" s="236">
+      <c r="D36" s="240"/>
+      <c r="F36" s="239">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>0.21675455263551163</v>
       </c>
-      <c r="G36" s="237"/>
+      <c r="G36" s="240"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="227" t="s">
@@ -38687,22 +38687,22 @@
       <c r="B38" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C38" s="236">
+      <c r="C38" s="239">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>1.550202718817076E-3</v>
       </c>
-      <c r="D38" s="237"/>
-      <c r="F38" s="236">
+      <c r="D38" s="240"/>
+      <c r="F38" s="239">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>5.661089445213234E-2</v>
       </c>
-      <c r="G38" s="237"/>
+      <c r="G38" s="240"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B39" s="227" t="s">
@@ -38729,22 +38729,22 @@
       <c r="B40" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C40" s="236">
+      <c r="C40" s="239">
         <f>IF(C39=0,
 IF(D39=0,0,IF(D39&gt;0,1,-1)),
 (D39-C39)/ABS(C39)
 )</f>
         <v>-0.19557882489819661</v>
       </c>
-      <c r="D40" s="237"/>
-      <c r="F40" s="236">
+      <c r="D40" s="240"/>
+      <c r="F40" s="239">
         <f>IF(F39=0,
 IF(G39=0,0,IF(G39&gt;0,1,-1)),
 (G39-F39)/ABS(F39)
 )</f>
         <v>7.9975007810059354E-2</v>
       </c>
-      <c r="G40" s="237"/>
+      <c r="G40" s="240"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B41" s="227" t="s">
@@ -38771,22 +38771,22 @@
       <c r="B42" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C42" s="236">
+      <c r="C42" s="239">
         <f>IF(C41=0,
 IF(D41=0,0,IF(D41&gt;0,1,-1)),
 (D41-C41)/ABS(C41)
 )</f>
         <v>-0.31253806664926476</v>
       </c>
-      <c r="D42" s="237"/>
-      <c r="F42" s="236">
+      <c r="D42" s="240"/>
+      <c r="F42" s="239">
         <f>IF(F41=0,
 IF(G41=0,0,IF(G41&gt;0,1,-1)),
 (G41-F41)/ABS(F41)
 )</f>
         <v>5.0385535761765486E-2</v>
       </c>
-      <c r="G42" s="237"/>
+      <c r="G42" s="240"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B43" s="227" t="s">
@@ -38813,55 +38813,25 @@
       <c r="B44" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C44" s="236">
+      <c r="C44" s="239">
         <f>IF(C43=0,
 IF(D43=0,0,IF(D43&gt;0,1,-1)),
 (D43-C43)/ABS(C43)
 )</f>
         <v>3.2086096025055806E-2</v>
       </c>
-      <c r="D44" s="237"/>
-      <c r="F44" s="236">
+      <c r="D44" s="240"/>
+      <c r="F44" s="239">
         <f>IF(F43=0,
 IF(G43=0,0,IF(G43&gt;0,1,-1)),
 (G43-F43)/ABS(F43)
 )</f>
         <v>0.16254456746106211</v>
       </c>
-      <c r="G44" s="237"/>
+      <c r="G44" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F36:G36"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="F44:G44"/>
     <mergeCell ref="C38:D38"/>
@@ -38870,6 +38840,36 @@
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="F42:G42"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/AAPL.xlsx
+++ b/AAPL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8570968-7C2F-7742-AA71-196745752CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46326320-F300-6946-897C-CE5AA581779D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="3" activeTab="12" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2287,9 +2287,6 @@
     <xf numFmtId="10" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="23" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2299,6 +2296,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2306,12 +2312,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15388,12 +15388,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>317.39999999999998</v>
-    <v>199.26070000000001</v>
-    <v>1.1047</v>
-    <v>7.62</v>
-    <v>2.7046000000000001E-2</v>
-    <v>-0.3</v>
-    <v>-1.0369999999999999E-3</v>
+    <v>201.5</v>
+    <v>1.0868</v>
+    <v>14.25</v>
+    <v>4.8406999999999999E-2</v>
+    <v>-0.1893</v>
+    <v>-6.1339999999999995E-4</v>
     <v>USD</v>
     <v>Apple Inc. designs, manufactures and markets smartphones, personal computers, tablets, wearables and accessories, and sells a variety of related services. Its product categories include iPhone, Mac, iPad, Wearables, Home and Accessories. Its services include advertising, AppleCare, cloud services, digital content, and payment services. The Company operates various platforms, including the App Store, that allow customers to discover and download applications and digital content, such as books, music, video, games and podcasts. It also offers digital content through subscription-based services, including Apple Arcade, Apple Fitness+, Apple Music, Apple News+, and Apple TV+. Its wearables include smartwatches, wireless headphones, and spatial computers. Its products include iPhone 16 Pro, iPhone 16, iPhone 15, iPhone 14, iPhone SE, MacBook Air, MacBook Pro, iMac, Mac mini, Mac Studio, Mac Pro, iPad Pro, iPad Air, AirPods, AirPods Pro, AirPods Max, Apple TV, Apple Vision Pro and others.</v>
     <v>166000</v>
@@ -15401,25 +15401,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Apple Park Way, CUPERTINO, CA, 95014 US</v>
-    <v>289.94</v>
+    <v>309.42</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46203.952167812502</v>
+    <v>46205.999965821095</v>
     <v>0</v>
-    <v>280.69499999999999</v>
-    <v>4249934489600</v>
+    <v>293.68</v>
+    <v>4532959916800</v>
     <v>APPLE INC.</v>
     <v>APPLE INC.</v>
-    <v>281.17</v>
-    <v>35.142899999999997</v>
-    <v>281.74</v>
-    <v>289.36</v>
-    <v>289.06</v>
+    <v>294.12</v>
+    <v>35.752499999999998</v>
+    <v>294.38</v>
+    <v>308.63</v>
+    <v>308.44069999999999</v>
     <v>14687360000</v>
     <v>AAPL</v>
     <v>APPLE INC. (XNAS:AAPL)</v>
-    <v>65048942</v>
-    <v>63868052</v>
+    <v>75400626</v>
+    <v>64811799</v>
     <v>1977</v>
   </rv>
   <rv s="2">
@@ -15443,17 +15443,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.02</v>
-    <v>4.5750000000000001E-4</v>
+    <v>0.1</v>
+    <v>2.235E-3</v>
     <v>US</v>
-    <v>43.9</v>
+    <v>45.05</v>
     <v>Index</v>
     <v>3</v>
-    <v>43.67</v>
+    <v>44.53</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>43.78</v>
-    <v>43.72</v>
-    <v>43.74</v>
+    <v>45.03</v>
+    <v>44.75</v>
+    <v>44.85</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -15675,9 +15675,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -16248,18 +16248,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="233" t="s">
+      <c r="B2" s="232" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="234"/>
-      <c r="E2" s="233" t="s">
+      <c r="C2" s="233"/>
+      <c r="E2" s="232" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="234"/>
-      <c r="H2" s="233" t="s">
+      <c r="F2" s="233"/>
+      <c r="H2" s="232" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="234"/>
+      <c r="I2" s="233"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="182" t="s">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="F3" s="184">
         <f ca="1">Statement!AC143</f>
-        <v>4265166.4000000004</v>
+        <v>4549206.2</v>
       </c>
       <c r="H3" s="182" t="str">
         <f>'AVG target price'!B5</f>
@@ -16282,7 +16282,7 @@
       </c>
       <c r="I3" s="208">
         <f ca="1">'AVG target price'!C5</f>
-        <v>119.68851520308499</v>
+        <v>119.09057177167055</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="F4" s="185">
         <f ca="1">Statement!AC144</f>
-        <v>4203282.4000000004</v>
+        <v>4487322.2</v>
       </c>
       <c r="H4" s="182" t="str">
         <f>'AVG target price'!B6</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="I4" s="208">
         <f ca="1">'AVG target price'!C6</f>
-        <v>191.28349310124528</v>
+        <v>190.96664389474685</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16315,7 +16315,7 @@
       </c>
       <c r="C5" s="205" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>289.36</v>
+        <v>308.63</v>
       </c>
       <c r="E5" s="182" t="s">
         <v>242</v>
@@ -16339,14 +16339,14 @@
       </c>
       <c r="C6" s="205" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>289.06</v>
+        <v>308.44069999999999</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="187">
         <f ca="1">Statement!AC140</f>
-        <v>34.989117291414757</v>
+        <v>37.319226118500609</v>
       </c>
       <c r="H6" s="182" t="str">
         <f>'AVG target price'!B8</f>
@@ -16354,7 +16354,7 @@
       </c>
       <c r="I6" s="208">
         <f ca="1">'AVG target price'!C8</f>
-        <v>122.21992262514725</v>
+        <v>122.01885943396663</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16363,14 +16363,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>7.62</v>
+        <v>14.25</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>198</v>
       </c>
       <c r="F7" s="188">
         <f ca="1">Statement!AC141</f>
-        <v>9.5100462960911933</v>
+        <v>10.143370156077635</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -16378,7 +16378,7 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>142.9698408039568</v>
+        <v>142.69087684668344</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -16387,14 +16387,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.3</v>
+        <v>-0.1893</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="189">
         <f ca="1">Statement!AC151</f>
-        <v>2.7126960392447993E-2</v>
+        <v>2.5433228328933518E-2</v>
       </c>
       <c r="H8" s="181" t="str">
         <f>'AVG target price'!B11</f>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.50591014375187726</v>
+        <v>-0.53766362036521587</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16411,14 +16411,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.7046000000000001E-2</v>
+        <v>4.8406999999999999E-2</v>
       </c>
       <c r="E9" s="182" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="189">
         <f ca="1">Statement!AC152</f>
-        <v>2.8580315178324576E-2</v>
+        <v>2.6795839678579528E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -16427,14 +16427,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.0369999999999999E-3</v>
+        <v>-6.1339999999999995E-4</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="189">
         <f ca="1">Statement!AC154</f>
-        <v>1.8333634064077779E-2</v>
+        <v>1.7188932873607708E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="F11" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>3.5941387890517005E-3</v>
+        <v>3.3697307455529276E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="C12" s="206" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>199.26070000000001</v>
+        <v>201.5</v>
       </c>
       <c r="E12" s="182" t="s">
         <v>99</v>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="C13" s="206" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.1047</v>
+        <v>1.0868</v>
       </c>
       <c r="E13" s="182" t="s">
         <v>101</v>
@@ -16491,7 +16491,7 @@
       </c>
       <c r="C14" s="207" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>63868052</v>
+        <v>64811799</v>
       </c>
       <c r="E14" s="183" t="s">
         <v>102</v>
@@ -16507,7 +16507,7 @@
       </c>
       <c r="F15" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.4509164284891674E-2</v>
+        <v>1.3603252365214836E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -16520,10 +16520,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="235" t="s">
+      <c r="B17" s="234" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="235"/>
+      <c r="C17" s="234"/>
       <c r="E17" s="181" t="s">
         <v>295</v>
       </c>
@@ -16596,14 +16596,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="235" t="s">
+      <c r="B25" s="234" t="s">
         <v>104</v>
       </c>
-      <c r="C25" s="235"/>
-      <c r="E25" s="233" t="s">
+      <c r="C25" s="234"/>
+      <c r="E25" s="232" t="s">
         <v>342</v>
       </c>
-      <c r="F25" s="234"/>
+      <c r="F25" s="233"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="181" t="s">
@@ -16617,7 +16617,7 @@
       </c>
       <c r="F26" s="216" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>43.74</v>
+        <v>44.85</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="F27" s="217">
         <f ca="1">F26/1000</f>
-        <v>4.3740000000000001E-2</v>
+        <v>4.4850000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16652,15 +16652,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="232" t="s">
+      <c r="B33" s="235" t="s">
         <v>337</v>
       </c>
-      <c r="C33" s="232"/>
-      <c r="D33" s="232"/>
-      <c r="E33" s="232"/>
-      <c r="F33" s="232"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="232"/>
+      <c r="C33" s="235"/>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="235"/>
+      <c r="H33" s="235"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -16673,24 +16673,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="232"/>
-      <c r="C39" s="232"/>
-      <c r="D39" s="232"/>
-      <c r="E39" s="232"/>
-      <c r="F39" s="232"/>
-      <c r="G39" s="232"/>
-      <c r="H39" s="232"/>
+      <c r="B39" s="235"/>
+      <c r="C39" s="235"/>
+      <c r="D39" s="235"/>
+      <c r="E39" s="235"/>
+      <c r="F39" s="235"/>
+      <c r="G39" s="235"/>
+      <c r="H39" s="235"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="232" t="s">
+      <c r="B42" s="235" t="s">
         <v>340</v>
       </c>
-      <c r="C42" s="232"/>
-      <c r="D42" s="232"/>
-      <c r="E42" s="232"/>
-      <c r="F42" s="232"/>
-      <c r="G42" s="232"/>
-      <c r="H42" s="232"/>
+      <c r="C42" s="235"/>
+      <c r="D42" s="235"/>
+      <c r="E42" s="235"/>
+      <c r="F42" s="235"/>
+      <c r="G42" s="235"/>
+      <c r="H42" s="235"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -16705,24 +16705,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="232"/>
-      <c r="C49" s="232"/>
-      <c r="D49" s="232"/>
-      <c r="E49" s="232"/>
-      <c r="F49" s="232"/>
-      <c r="G49" s="232"/>
-      <c r="H49" s="232"/>
+      <c r="B49" s="235"/>
+      <c r="C49" s="235"/>
+      <c r="D49" s="235"/>
+      <c r="E49" s="235"/>
+      <c r="F49" s="235"/>
+      <c r="G49" s="235"/>
+      <c r="H49" s="235"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="232" t="s">
+      <c r="B52" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="C52" s="232"/>
-      <c r="D52" s="232"/>
-      <c r="E52" s="232"/>
-      <c r="F52" s="232"/>
-      <c r="G52" s="232"/>
-      <c r="H52" s="232"/>
+      <c r="C52" s="235"/>
+      <c r="D52" s="235"/>
+      <c r="E52" s="235"/>
+      <c r="F52" s="235"/>
+      <c r="G52" s="235"/>
+      <c r="H52" s="235"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -16737,28 +16737,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="232"/>
-      <c r="C59" s="232"/>
-      <c r="D59" s="232"/>
-      <c r="E59" s="232"/>
-      <c r="F59" s="232"/>
-      <c r="G59" s="232"/>
-      <c r="H59" s="232"/>
+      <c r="B59" s="235"/>
+      <c r="C59" s="235"/>
+      <c r="D59" s="235"/>
+      <c r="E59" s="235"/>
+      <c r="F59" s="235"/>
+      <c r="G59" s="235"/>
+      <c r="H59" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -16828,36 +16828,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="232" t="s">
+      <c r="S2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="232" t="s">
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
+      <c r="AA2" s="235" t="s">
         <v>111</v>
       </c>
-      <c r="AB2" s="232"/>
-      <c r="AC2" s="232"/>
+      <c r="AB2" s="235"/>
+      <c r="AC2" s="235"/>
       <c r="AE2" s="85" t="s">
         <v>112</v>
       </c>
@@ -18228,35 +18228,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="P2" s="232" t="s">
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
+      <c r="P2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="Q2" s="232"/>
-      <c r="R2" s="232"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232" t="s">
+      <c r="Q2" s="235"/>
+      <c r="R2" s="235"/>
+      <c r="S2" s="235"/>
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235" t="s">
         <v>111</v>
       </c>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
       <c r="AB2" s="85" t="s">
         <v>112</v>
       </c>
@@ -19487,20 +19487,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -20811,23 +20811,23 @@
         <v>58</v>
       </c>
       <c r="C45" s="114">
-        <f>-Statement!M59</f>
+        <f>-Statement!M108</f>
         <v>11085</v>
       </c>
       <c r="D45" s="114">
-        <f>-Statement!N59</f>
+        <f>-Statement!N108</f>
         <v>10708</v>
       </c>
       <c r="E45" s="114">
-        <f>-Statement!O59</f>
+        <f>-Statement!O108</f>
         <v>10959</v>
       </c>
       <c r="F45" s="114">
-        <f>-Statement!P59</f>
+        <f>-Statement!P108</f>
         <v>9447</v>
       </c>
       <c r="G45" s="115">
-        <f>-Statement!Q59</f>
+        <f>-Statement!Q108</f>
         <v>12715</v>
       </c>
       <c r="H45" s="25">
@@ -20893,6 +20893,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20900,12 +20906,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20943,20 +20943,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="S2" s="246"/>
       <c r="T2" s="246"/>
       <c r="U2" s="246"/>
@@ -21965,16 +21965,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22037,10 +22037,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="235"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22057,7 +22057,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>289.36</v>
+        <v>308.63</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22066,7 +22066,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>4265166.4000000004</v>
+        <v>4549206.2</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.3740000000000001E-2</v>
+        <v>4.4850000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22093,7 +22093,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.1047</v>
+        <v>1.0868</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22125,10 +22125,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="235" t="s">
         <v>170</v>
       </c>
-      <c r="C15" s="232"/>
+      <c r="C15" s="235"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.9474341966511516E-2</v>
+        <v>1.8280646015858892E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22145,7 +22145,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.98052565803348846</v>
+        <v>0.98171935398414112</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22163,7 +22163,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.3451499999999993E-2</v>
+        <v>9.3756000000000006E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22172,7 +22172,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.2346983483856337E-2</v>
+        <v>9.2713619283529725E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22217,20 +22217,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>1938098.253247638</v>
+        <v>1928325.9958641303</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22477,23 +22477,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>96445.519730698827</v>
+        <v>96413.15957738203</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>93256.520813370589</v>
+        <v>93193.951001053298</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>90487.615543884356</v>
+        <v>90396.562769008087</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>87590.239245136399</v>
+        <v>87472.742554731027</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>88387.932974733514</v>
+        <v>88239.749402833404</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22512,14 +22512,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>1246156.8857856491</v>
+        <v>1237794.8626094162</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="232" t="s">
+      <c r="B13" s="235" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="232"/>
+      <c r="C13" s="235"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22535,14 +22535,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.2346983483856337E-2</v>
+        <v>9.2713619283529725E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="232" t="s">
+      <c r="B18" s="235" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="232"/>
+      <c r="C18" s="235"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22550,7 +22550,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>456167.82830782369</v>
+        <v>455716.16530500783</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -22559,7 +22559,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>1246156.8857856491</v>
+        <v>1237794.8626094162</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>1702324.7140934728</v>
+        <v>1693511.027914424</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -22595,7 +22595,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>1764208.7140934728</v>
+        <v>1755395.027914424</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -22613,7 +22613,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>119.68851520308499</v>
+        <v>119.09057177167055</v>
       </c>
     </row>
   </sheetData>
@@ -22656,20 +22656,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -23601,10 +23601,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="235" t="s">
         <v>202</v>
       </c>
-      <c r="C37" s="232"/>
+      <c r="C37" s="235"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.2346983483856337E-2</v>
+        <v>9.2713619283529725E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -23657,7 +23657,7 @@
       </c>
       <c r="C43" s="24">
         <f ca="1">C42/(1+C39)^5-G30+G31</f>
-        <v>2819518.6883123554</v>
+        <v>2814848.3310085684</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -23675,14 +23675,14 @@
       </c>
       <c r="C45" s="142">
         <f ca="1">C43/C44</f>
-        <v>191.28349310124528</v>
+        <v>190.96664389474685</v>
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="232" t="s">
+      <c r="B47" s="235" t="s">
         <v>207</v>
       </c>
-      <c r="C47" s="232"/>
+      <c r="C47" s="235"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
@@ -23738,10 +23738,10 @@
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="232" t="s">
+      <c r="B55" s="235" t="s">
         <v>321</v>
       </c>
-      <c r="C55" s="232"/>
+      <c r="C55" s="235"/>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C57" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.2346983483856337E-2</v>
+        <v>9.2713619283529725E-2</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
@@ -23784,7 +23784,7 @@
       </c>
       <c r="C60" s="24">
         <f ca="1">C59/(1+C57)^5-G30+G31</f>
-        <v>1801521.6594946703</v>
+        <v>1798557.9880566681</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C62" s="142">
         <f ca="1">C60/C61</f>
-        <v>122.21992262514725</v>
+        <v>122.01885943396663</v>
       </c>
     </row>
   </sheetData>
@@ -23854,10 +23854,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>212</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="235"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23866,7 +23866,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>119.68851520308499</v>
+        <v>119.09057177167055</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23875,7 +23875,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C45</f>
-        <v>191.28349310124528</v>
+        <v>190.96664389474685</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C62</f>
-        <v>122.21992262514725</v>
+        <v>122.01885943396663</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>142.9698408039568</v>
+        <v>142.69087684668344</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23911,7 +23911,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>289.36</v>
+        <v>308.63</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="C11" s="151">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.50591014375187726</v>
+        <v>-0.53766362036521587</v>
       </c>
     </row>
   </sheetData>
@@ -23985,20 +23985,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -24173,7 +24173,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>5282338.0052034836</v>
+        <v>5255703.4594641058</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -24227,23 +24227,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>145077.1746060657</v>
+        <v>145028.49718044625</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>164687.31935137906</v>
+        <v>164576.82354290391</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>186948.17588492756</v>
+        <v>186760.06008510161</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>212218.04207118601</v>
+        <v>211933.36517336537</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>240903.64705269467</v>
+        <v>240499.76881159769</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -24262,7 +24262,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>3396433.5230172998</v>
+        <v>3373642.6078765481</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24278,7 +24278,7 @@
       </c>
       <c r="C15" s="153">
         <f ca="1">Overview!C5</f>
-        <v>289.36</v>
+        <v>308.63</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24287,7 +24287,7 @@
       </c>
       <c r="C16" s="153">
         <f ca="1">C36</f>
-        <v>300.13970735913074</v>
+        <v>298.51740468917842</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="C21" s="219">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.2346983483856337E-2</v>
+        <v>9.2713619283529725E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24344,7 +24344,7 @@
       </c>
       <c r="C23" s="158">
         <f ca="1">C15*C22</f>
-        <v>4249830.32</v>
+        <v>4532848.8099999996</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24371,7 +24371,7 @@
       </c>
       <c r="C26" s="159">
         <f ca="1">C23+C25-C24</f>
-        <v>4187946.3200000003</v>
+        <v>4470964.8099999996</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24387,7 +24387,7 @@
       </c>
       <c r="C29" s="158">
         <f ca="1">SUM(H10:L10)</f>
-        <v>949834.35896625312</v>
+        <v>948798.51479341486</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24396,7 +24396,7 @@
       </c>
       <c r="C30" s="158">
         <f ca="1">L11</f>
-        <v>3396433.5230172998</v>
+        <v>3373642.6078765481</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24405,7 +24405,7 @@
       </c>
       <c r="C31" s="161">
         <f ca="1">C29+C30</f>
-        <v>4346267.8819835531</v>
+        <v>4322441.1226699632</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24432,7 +24432,7 @@
       </c>
       <c r="C34" s="161">
         <f ca="1">C31+C32-C33</f>
-        <v>4408151.8819835531</v>
+        <v>4384325.1226699632</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -24450,7 +24450,7 @@
       </c>
       <c r="C36" s="164">
         <f ca="1">C34/C35</f>
-        <v>300.13970735913074</v>
+        <v>298.51740468917842</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -24897,17 +24897,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31305,7 +31305,7 @@
       <c r="AA114" s="68"/>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>289.36</v>
+        <v>308.63</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -31352,7 +31352,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>289.36</v>
+        <v>308.63</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32266,7 +32266,7 @@
       <c r="AA140" s="49"/>
       <c r="AC140" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>34.989117291414757</v>
+        <v>37.319226118500609</v>
       </c>
     </row>
     <row r="141" spans="2:29" x14ac:dyDescent="0.2">
@@ -32303,7 +32303,7 @@
       <c r="AA141" s="49"/>
       <c r="AC141" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>9.5100462960911933</v>
+        <v>10.143370156077635</v>
       </c>
     </row>
     <row r="142" spans="2:29" x14ac:dyDescent="0.2">
@@ -32340,7 +32340,7 @@
       <c r="AA142" s="49"/>
       <c r="AC142" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>39.907882544064755</v>
+        <v>42.565557746664034</v>
       </c>
     </row>
     <row r="143" spans="2:29" x14ac:dyDescent="0.2">
@@ -32377,7 +32377,7 @@
       <c r="AA143" s="49"/>
       <c r="AC143" s="143">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>4265166.4000000004</v>
+        <v>4549206.2</v>
       </c>
     </row>
     <row r="144" spans="2:29" x14ac:dyDescent="0.2">
@@ -32414,7 +32414,7 @@
       <c r="AA144" s="49"/>
       <c r="AC144" s="143">
         <f ca="1">AC143+AC106-AC105+AC47+AC44</f>
-        <v>4203282.4000000004</v>
+        <v>4487322.2</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
@@ -32451,7 +32451,7 @@
       <c r="AA145" s="49"/>
       <c r="AC145" s="180">
         <f ca="1">AC144/AC5</f>
-        <v>9.3107916410081479</v>
+        <v>9.9399750134015008</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
@@ -32488,7 +32488,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="180">
         <f ca="1">AC144/AC11</f>
-        <v>28.522742016475988</v>
+        <v>30.450186610208597</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32623,7 +32623,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f t="shared" ref="AC149:AC150" ca="1" si="89">AC143/AC147</f>
-        <v>36.863695214388812</v>
+        <v>39.318642016922929</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32660,7 +32660,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f t="shared" ca="1" si="89"/>
-        <v>36.366972692027488</v>
+        <v>38.824496757041281</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32697,7 +32697,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="74">
         <f t="shared" ref="AC151" ca="1" si="92">AC147/AC143</f>
-        <v>2.7126960392447993E-2</v>
+        <v>2.5433228328933518E-2</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32734,7 +32734,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>2.8580315178324576E-2</v>
+        <v>2.6795839678579528E-2</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32771,7 +32771,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="151">
         <f ca="1">AC81/AC115</f>
-        <v>3.5941387890517005E-3</v>
+        <v>3.3697307455529276E-3</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32808,7 +32808,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="151">
         <f ca="1">-AC62/AC143</f>
-        <v>1.8333634064077779E-2</v>
+        <v>1.7188932873607708E-2</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32845,7 +32845,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="151">
         <f ca="1">-(AC62+AC63)/AC143</f>
-        <v>2.1979447273147417E-2</v>
+        <v>2.0607111631915035E-2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33348,7 +33348,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="151">
         <f ca="1">(AC105-AC106)/AC143</f>
-        <v>1.4509164284891674E-2</v>
+        <v>1.3603252365214836E-2</v>
       </c>
     </row>
     <row r="167" spans="1:31" x14ac:dyDescent="0.2">
@@ -35345,15 +35345,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="E4" s="232" t="s">
+      <c r="C4" s="235"/>
+      <c r="E4" s="235" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35361,7 +35361,7 @@
       </c>
       <c r="C5" s="169">
         <f ca="1">Overview!C5</f>
-        <v>289.36</v>
+        <v>308.63</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -35377,7 +35377,7 @@
       </c>
       <c r="C6" s="170">
         <f ca="1">Statement!AC143</f>
-        <v>4265166.4000000004</v>
+        <v>4549206.2</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -35397,7 +35397,7 @@
       </c>
       <c r="C7" s="170">
         <f ca="1">Statement!AC144</f>
-        <v>4203282.4000000004</v>
+        <v>4487322.2</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -35417,7 +35417,7 @@
       </c>
       <c r="C8" s="171">
         <f ca="1">Statement!AC140</f>
-        <v>34.989117291414757</v>
+        <v>37.319226118500609</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -35437,7 +35437,7 @@
       </c>
       <c r="C9" s="171">
         <f ca="1">Statement!AC141</f>
-        <v>9.5100462960911933</v>
+        <v>10.143370156077635</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -35457,7 +35457,7 @@
       </c>
       <c r="C10" s="171">
         <f ca="1">Statement!AC142</f>
-        <v>39.907882544064755</v>
+        <v>42.565557746664034</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="C11" s="171">
         <f ca="1">Statement!AC145</f>
-        <v>9.3107916410081479</v>
+        <v>9.9399750134015008</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35486,18 +35486,18 @@
       </c>
       <c r="C12" s="171">
         <f ca="1">Statement!AC146</f>
-        <v>28.522742016475988</v>
+        <v>30.450186610208597</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="235" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="232"/>
-      <c r="E15" s="232" t="s">
+      <c r="C15" s="235"/>
+      <c r="E15" s="235" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="232"/>
+      <c r="F15" s="235"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35548,14 +35548,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="232" t="s">
+      <c r="B21" s="235" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="232"/>
-      <c r="E21" s="232" t="s">
+      <c r="C21" s="235"/>
+      <c r="E21" s="235" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="232"/>
+      <c r="F21" s="235"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35624,14 +35624,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="232" t="s">
+      <c r="B29" s="235" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="232"/>
-      <c r="E29" s="232" t="s">
+      <c r="C29" s="235"/>
+      <c r="E29" s="235" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="232"/>
+      <c r="F29" s="235"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35707,14 +35707,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="235" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="232"/>
-      <c r="E37" s="232" t="s">
+      <c r="C37" s="235"/>
+      <c r="E37" s="235" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="232"/>
+      <c r="F37" s="235"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35722,7 +35722,7 @@
       </c>
       <c r="C38" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>2.8580315178324576E-2</v>
+        <v>2.6795839678579528E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -35738,7 +35738,7 @@
       </c>
       <c r="C39" s="212">
         <f ca="1">Statement!AC151</f>
-        <v>2.7126960392447993E-2</v>
+        <v>2.5433228328933518E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -35754,7 +35754,7 @@
       </c>
       <c r="C40" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>3.5941387890517005E-3</v>
+        <v>3.3697307455529276E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -35770,7 +35770,7 @@
       </c>
       <c r="C41" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>1.8333634064077779E-2</v>
+        <v>1.7188932873607708E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35779,18 +35779,18 @@
       </c>
       <c r="C42" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>2.1979447273147417E-2</v>
+        <v>2.0607111631915035E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="232" t="s">
+      <c r="B45" s="235" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="232"/>
-      <c r="E45" s="232" t="s">
+      <c r="C45" s="235"/>
+      <c r="E45" s="235" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="232"/>
+      <c r="F45" s="235"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35823,18 +35823,18 @@
       </c>
       <c r="F48" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.4509164284891674E-2</v>
+        <v>1.3603252365214836E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="232" t="s">
+      <c r="B51" s="235" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="232"/>
-      <c r="E51" s="232" t="s">
+      <c r="C51" s="235"/>
+      <c r="E51" s="235" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="232"/>
+      <c r="F51" s="235"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36002,7 +36002,7 @@
       </c>
       <c r="I6" s="169">
         <f ca="1">Statement!AC114</f>
-        <v>289.36</v>
+        <v>308.63</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36031,7 +36031,7 @@
       </c>
       <c r="I7" s="170">
         <f ca="1">Statement!AC143</f>
-        <v>4265166.4000000004</v>
+        <v>4549206.2</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36060,7 +36060,7 @@
       </c>
       <c r="I8" s="170">
         <f ca="1">Statement!AC144</f>
-        <v>4203282.4000000004</v>
+        <v>4487322.2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36089,7 +36089,7 @@
       </c>
       <c r="I9" s="171">
         <f ca="1">Statement!AC140</f>
-        <v>34.989117291414757</v>
+        <v>37.319226118500609</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36118,7 +36118,7 @@
       </c>
       <c r="I10" s="171">
         <f ca="1">Statement!AC141</f>
-        <v>9.5100462960911933</v>
+        <v>10.143370156077635</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36147,7 +36147,7 @@
       </c>
       <c r="I11" s="171">
         <f ca="1">Statement!AC142</f>
-        <v>39.907882544064755</v>
+        <v>42.565557746664034</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36176,7 +36176,7 @@
       </c>
       <c r="I12" s="171">
         <f ca="1">Statement!AC145</f>
-        <v>9.3107916410081479</v>
+        <v>9.9399750134015008</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36205,7 +36205,7 @@
       </c>
       <c r="I13" s="171">
         <f ca="1">Statement!AC146</f>
-        <v>28.522742016475988</v>
+        <v>30.450186610208597</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36978,7 +36978,7 @@
       </c>
       <c r="I51" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>2.8580315178324576E-2</v>
+        <v>2.6795839678579528E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37007,7 +37007,7 @@
       </c>
       <c r="I52" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>2.7126960392447993E-2</v>
+        <v>2.5433228328933518E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37036,7 +37036,7 @@
       </c>
       <c r="I53" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>3.5941387890517005E-3</v>
+        <v>3.3697307455529276E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -37065,7 +37065,7 @@
       </c>
       <c r="I54" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>1.8333634064077779E-2</v>
+        <v>1.7188932873607708E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37094,7 +37094,7 @@
       </c>
       <c r="I55" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>2.1979447273147417E-2</v>
+        <v>2.0607111631915035E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37330,7 +37330,7 @@
       </c>
       <c r="I68" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>1.4509164284891674E-2</v>
+        <v>1.3603252365214836E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38022,14 +38022,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="236" t="s">
+      <c r="C3" s="238" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="F3" s="238" t="s">
+      <c r="D3" s="239"/>
+      <c r="F3" s="240" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="237"/>
+      <c r="G3" s="239"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38096,19 +38096,19 @@
       <c r="B7" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="239">
+      <c r="C7" s="236">
         <f>Statement!AA88</f>
         <v>-0.22657836890286318</v>
       </c>
-      <c r="D7" s="240"/>
-      <c r="F7" s="239">
+      <c r="D7" s="237"/>
+      <c r="F7" s="236">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.16595182415922985</v>
       </c>
-      <c r="G7" s="240"/>
+      <c r="G7" s="237"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="204" t="s">
@@ -38135,19 +38135,19 @@
       <c r="B9" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="239">
+      <c r="C9" s="236">
         <f>Statement!AA89</f>
         <v>-0.24316672257631666</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="F9" s="239">
+      <c r="D9" s="237"/>
+      <c r="F9" s="236">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.11706805038421929</v>
       </c>
-      <c r="G9" s="240"/>
+      <c r="G9" s="237"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="204" t="s">
@@ -38174,19 +38174,19 @@
       <c r="B11" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="239">
+      <c r="C11" s="236">
         <f>Statement!AA90</f>
         <v>-0.2087215264838006</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="F11" s="239">
+      <c r="D11" s="237"/>
+      <c r="F11" s="236">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.22096418302984375</v>
       </c>
-      <c r="G11" s="240"/>
+      <c r="G11" s="237"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="204" t="s">
@@ -38213,19 +38213,19 @@
       <c r="B13" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="239">
+      <c r="C13" s="236">
         <f>Statement!AA93</f>
         <v>2.8129930899396048E-2</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="F13" s="239">
+      <c r="D13" s="237"/>
+      <c r="F13" s="236">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.23681110092944102</v>
       </c>
-      <c r="G13" s="240"/>
+      <c r="G13" s="237"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="204" t="s">
@@ -38252,19 +38252,19 @@
       <c r="B15" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="239">
+      <c r="C15" s="236">
         <f>Statement!AA94</f>
         <v>-0.29432470699284197</v>
       </c>
-      <c r="D15" s="240"/>
-      <c r="F15" s="239">
+      <c r="D15" s="237"/>
+      <c r="F15" s="236">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.21278177701172732</v>
       </c>
-      <c r="G15" s="240"/>
+      <c r="G15" s="237"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="204" t="s">
@@ -38291,19 +38291,19 @@
       <c r="B17" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="239">
+      <c r="C17" s="236">
         <f>Statement!AA96</f>
         <v>-0.29738461173005204</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="F17" s="239">
+      <c r="D17" s="237"/>
+      <c r="F17" s="236">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.19362389023405974</v>
       </c>
-      <c r="G17" s="240"/>
+      <c r="G17" s="237"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="204" t="s">
@@ -38330,22 +38330,22 @@
       <c r="B19" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="239">
+      <c r="C19" s="236">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-5.6718433490884537E-3</v>
       </c>
-      <c r="D19" s="240"/>
-      <c r="F19" s="239">
+      <c r="D19" s="237"/>
+      <c r="F19" s="236">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-2.1918172157279491E-2</v>
       </c>
-      <c r="G19" s="240"/>
+      <c r="G19" s="237"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="204" t="s">
@@ -38372,22 +38372,22 @@
       <c r="B21" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="239">
+      <c r="C21" s="236">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.29225352112676062</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="F21" s="239">
+      <c r="D21" s="237"/>
+      <c r="F21" s="236">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.21818181818181812</v>
       </c>
-      <c r="G21" s="240"/>
+      <c r="G21" s="237"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38435,22 +38435,22 @@
       <c r="B25" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="239">
+      <c r="C25" s="236">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.22956141399989749</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="F25" s="239">
+      <c r="D25" s="237"/>
+      <c r="F25" s="236">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.11851668113605358</v>
       </c>
-      <c r="G25" s="240"/>
+      <c r="G25" s="237"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -38477,22 +38477,22 @@
       <c r="B27" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="239">
+      <c r="C27" s="236">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-0.26453625543962672</v>
       </c>
-      <c r="D27" s="240"/>
-      <c r="F27" s="239">
+      <c r="D27" s="237"/>
+      <c r="F27" s="236">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.14725607262615523</v>
       </c>
-      <c r="G27" s="240"/>
+      <c r="G27" s="237"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -38519,22 +38519,22 @@
       <c r="B29" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="239">
+      <c r="C29" s="236">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-0.19701480843061975</v>
       </c>
-      <c r="D29" s="240"/>
-      <c r="F29" s="239">
+      <c r="D29" s="237"/>
+      <c r="F29" s="236">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.28090238720159982</v>
       </c>
-      <c r="G29" s="240"/>
+      <c r="G29" s="237"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -38561,22 +38561,22 @@
       <c r="B31" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C31" s="239">
+      <c r="C31" s="236">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-0.10751088919579305</v>
       </c>
-      <c r="D31" s="240"/>
-      <c r="F31" s="239">
+      <c r="D31" s="237"/>
+      <c r="F31" s="236">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.15113729788983282</v>
       </c>
-      <c r="G31" s="240"/>
+      <c r="G31" s="237"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -38603,22 +38603,22 @@
       <c r="B33" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C33" s="239">
+      <c r="C33" s="236">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-0.2474056992258277</v>
       </c>
-      <c r="D33" s="240"/>
-      <c r="F33" s="239">
+      <c r="D33" s="237"/>
+      <c r="F33" s="236">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.25349794238683127</v>
       </c>
-      <c r="G33" s="240"/>
+      <c r="G33" s="237"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="227" t="s">
@@ -38645,22 +38645,22 @@
       <c r="B36" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C36" s="239">
+      <c r="C36" s="236">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>-0.33159764979066247</v>
       </c>
-      <c r="D36" s="240"/>
-      <c r="F36" s="239">
+      <c r="D36" s="237"/>
+      <c r="F36" s="236">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>0.21675455263551163</v>
       </c>
-      <c r="G36" s="240"/>
+      <c r="G36" s="237"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="227" t="s">
@@ -38687,22 +38687,22 @@
       <c r="B38" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C38" s="239">
+      <c r="C38" s="236">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>1.550202718817076E-3</v>
       </c>
-      <c r="D38" s="240"/>
-      <c r="F38" s="239">
+      <c r="D38" s="237"/>
+      <c r="F38" s="236">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>5.661089445213234E-2</v>
       </c>
-      <c r="G38" s="240"/>
+      <c r="G38" s="237"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B39" s="227" t="s">
@@ -38729,22 +38729,22 @@
       <c r="B40" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C40" s="239">
+      <c r="C40" s="236">
         <f>IF(C39=0,
 IF(D39=0,0,IF(D39&gt;0,1,-1)),
 (D39-C39)/ABS(C39)
 )</f>
         <v>-0.19557882489819661</v>
       </c>
-      <c r="D40" s="240"/>
-      <c r="F40" s="239">
+      <c r="D40" s="237"/>
+      <c r="F40" s="236">
         <f>IF(F39=0,
 IF(G39=0,0,IF(G39&gt;0,1,-1)),
 (G39-F39)/ABS(F39)
 )</f>
         <v>7.9975007810059354E-2</v>
       </c>
-      <c r="G40" s="240"/>
+      <c r="G40" s="237"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B41" s="227" t="s">
@@ -38771,22 +38771,22 @@
       <c r="B42" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C42" s="239">
+      <c r="C42" s="236">
         <f>IF(C41=0,
 IF(D41=0,0,IF(D41&gt;0,1,-1)),
 (D41-C41)/ABS(C41)
 )</f>
         <v>-0.31253806664926476</v>
       </c>
-      <c r="D42" s="240"/>
-      <c r="F42" s="239">
+      <c r="D42" s="237"/>
+      <c r="F42" s="236">
         <f>IF(F41=0,
 IF(G41=0,0,IF(G41&gt;0,1,-1)),
 (G41-F41)/ABS(F41)
 )</f>
         <v>5.0385535761765486E-2</v>
       </c>
-      <c r="G42" s="240"/>
+      <c r="G42" s="237"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B43" s="227" t="s">
@@ -38813,25 +38813,55 @@
       <c r="B44" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C44" s="239">
+      <c r="C44" s="236">
         <f>IF(C43=0,
 IF(D43=0,0,IF(D43&gt;0,1,-1)),
 (D43-C43)/ABS(C43)
 )</f>
         <v>3.2086096025055806E-2</v>
       </c>
-      <c r="D44" s="240"/>
-      <c r="F44" s="239">
+      <c r="D44" s="237"/>
+      <c r="F44" s="236">
         <f>IF(F43=0,
 IF(G43=0,0,IF(G43&gt;0,1,-1)),
 (G43-F43)/ABS(F43)
 )</f>
         <v>0.16254456746106211</v>
       </c>
-      <c r="G44" s="240"/>
+      <c r="G44" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F36:G36"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="F44:G44"/>
     <mergeCell ref="C38:D38"/>
@@ -38840,36 +38870,6 @@
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="F42:G42"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/AAPL.xlsx
+++ b/AAPL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46326320-F300-6946-897C-CE5AA581779D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4BF1AB-0D5E-6C4A-8414-8E4E638DF49B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="3" activeTab="12" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -117,7 +117,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -128,7 +128,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -138,19 +159,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="406">
   <si>
     <t>Ticker</t>
   </si>
@@ -2287,6 +2317,9 @@
     <xf numFmtId="10" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="23" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2294,9 +2327,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15370,7 +15400,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1mou2&amp;q=XNAS%3aAAPL&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -15389,11 +15419,9 @@
     <v>Powered by Refinitiv</v>
     <v>317.39999999999998</v>
     <v>201.5</v>
-    <v>1.0868</v>
-    <v>14.25</v>
-    <v>4.8406999999999999E-2</v>
-    <v>-0.1893</v>
-    <v>-6.1339999999999995E-4</v>
+    <v>1.0903</v>
+    <v>-0.4</v>
+    <v>-1.2790000000000002E-3</v>
     <v>USD</v>
     <v>Apple Inc. designs, manufactures and markets smartphones, personal computers, tablets, wearables and accessories, and sells a variety of related services. Its product categories include iPhone, Mac, iPad, Wearables, Home and Accessories. Its services include advertising, AppleCare, cloud services, digital content, and payment services. The Company operates various platforms, including the App Store, that allow customers to discover and download applications and digital content, such as books, music, video, games and podcasts. It also offers digital content through subscription-based services, including Apple Arcade, Apple Fitness+, Apple Music, Apple News+, and Apple TV+. Its wearables include smartwatches, wireless headphones, and spatial computers. Its products include iPhone 16 Pro, iPhone 16, iPhone 15, iPhone 14, iPhone SE, MacBook Air, MacBook Pro, iMac, Mac mini, Mac Studio, Mac Pro, iPad Pro, iPad Air, AirPods, AirPods Pro, AirPods Max, Apple TV, Apple Vision Pro and others.</v>
     <v>166000</v>
@@ -15401,35 +15429,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Apple Park Way, CUPERTINO, CA, 95014 US</v>
-    <v>309.42</v>
+    <v>315.48</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46205.999965821095</v>
+    <v>46210.767967233594</v>
     <v>0</v>
-    <v>293.68</v>
-    <v>4532959916800</v>
+    <v>310.14999999999998</v>
+    <v>4586275033600</v>
     <v>APPLE INC.</v>
     <v>APPLE INC.</v>
-    <v>294.12</v>
-    <v>35.752499999999998</v>
-    <v>294.38</v>
-    <v>308.63</v>
-    <v>308.44069999999999</v>
+    <v>315</v>
+    <v>37.924199999999999</v>
+    <v>312.66000000000003</v>
+    <v>312.26</v>
     <v>14687360000</v>
     <v>AAPL</v>
     <v>APPLE INC. (XNAS:AAPL)</v>
-    <v>75400626</v>
-    <v>64811799</v>
+    <v>25322976</v>
+    <v>66025371</v>
     <v>1977</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -15443,28 +15485,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.1</v>
-    <v>2.235E-3</v>
+    <v>-0.06</v>
+    <v>-1.338E-3</v>
     <v>US</v>
-    <v>45.05</v>
+    <v>44.91</v>
     <v>Index</v>
-    <v>3</v>
-    <v>44.53</v>
+    <v>6</v>
+    <v>44.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.03</v>
-    <v>44.75</v>
+    <v>44.57</v>
     <v>44.85</v>
+    <v>44.79</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -15486,8 +15528,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -15508,7 +15548,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -15518,6 +15557,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -15553,7 +15597,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -15564,16 +15608,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -15667,19 +15708,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -15751,9 +15786,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -15761,9 +15793,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -16248,18 +16277,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="232" t="s">
+      <c r="B2" s="233" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="233"/>
-      <c r="E2" s="232" t="s">
+      <c r="C2" s="234"/>
+      <c r="E2" s="233" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="233"/>
-      <c r="H2" s="232" t="s">
+      <c r="F2" s="234"/>
+      <c r="H2" s="233" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="233"/>
+      <c r="I2" s="234"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="182" t="s">
@@ -16274,7 +16303,7 @@
       </c>
       <c r="F3" s="184">
         <f ca="1">Statement!AC143</f>
-        <v>4549206.2</v>
+        <v>4602712.3999999994</v>
       </c>
       <c r="H3" s="182" t="str">
         <f>'AVG target price'!B5</f>
@@ -16282,7 +16311,7 @@
       </c>
       <c r="I3" s="208">
         <f ca="1">'AVG target price'!C5</f>
-        <v>119.09057177167055</v>
+        <v>118.91617564595006</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16298,7 +16327,7 @@
       </c>
       <c r="F4" s="185">
         <f ca="1">Statement!AC144</f>
-        <v>4487322.2</v>
+        <v>4540828.3999999994</v>
       </c>
       <c r="H4" s="182" t="str">
         <f>'AVG target price'!B6</f>
@@ -16306,7 +16335,7 @@
       </c>
       <c r="I4" s="208">
         <f ca="1">'AVG target price'!C6</f>
-        <v>190.96664389474685</v>
+        <v>195.0721164457571</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16315,7 +16344,7 @@
       </c>
       <c r="C5" s="205" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>308.63</v>
+        <v>312.26</v>
       </c>
       <c r="E5" s="182" t="s">
         <v>242</v>
@@ -16337,16 +16366,16 @@
       <c r="B6" s="182" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="205" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>308.44069999999999</v>
+      <c r="C6" s="205" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="187">
         <f ca="1">Statement!AC140</f>
-        <v>37.319226118500609</v>
+        <v>37.758162031438935</v>
       </c>
       <c r="H6" s="182" t="str">
         <f>'AVG target price'!B8</f>
@@ -16354,7 +16383,7 @@
       </c>
       <c r="I6" s="208">
         <f ca="1">'AVG target price'!C8</f>
-        <v>122.01885943396663</v>
+        <v>126.15828009353453</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16363,14 +16392,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>14.25</v>
+        <v>-0.4</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>198</v>
       </c>
       <c r="F7" s="188">
         <f ca="1">Statement!AC141</f>
-        <v>10.143370156077635</v>
+        <v>10.262672990107257</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -16378,23 +16407,23 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>142.69087684668344</v>
+        <v>144.70850111789787</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="182" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.1893</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="189">
         <f ca="1">Statement!AC151</f>
-        <v>2.5433228328933518E-2</v>
+        <v>2.5137568882209544E-2</v>
       </c>
       <c r="H8" s="181" t="str">
         <f>'AVG target price'!B11</f>
@@ -16402,7 +16431,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.53766362036521587</v>
+        <v>-0.53657688747230559</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16411,30 +16440,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>4.8406999999999999E-2</v>
+        <v>-1.2790000000000002E-3</v>
       </c>
       <c r="E9" s="182" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="189">
         <f ca="1">Statement!AC152</f>
-        <v>2.6795839678579528E-2</v>
+        <v>2.648433997309934E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="182" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-6.1339999999999995E-4</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="189">
         <f ca="1">Statement!AC154</f>
-        <v>1.7188932873607708E-2</v>
+        <v>1.6989112767506396E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -16450,7 +16479,7 @@
       </c>
       <c r="F11" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>3.3697307455529276E-3</v>
+        <v>3.3305578684429643E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -16475,7 +16504,7 @@
       </c>
       <c r="C13" s="206" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0868</v>
+        <v>1.0903</v>
       </c>
       <c r="E13" s="182" t="s">
         <v>101</v>
@@ -16491,7 +16520,7 @@
       </c>
       <c r="C14" s="207" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>64811799</v>
+        <v>66025371</v>
       </c>
       <c r="E14" s="183" t="s">
         <v>102</v>
@@ -16507,7 +16536,7 @@
       </c>
       <c r="F15" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.3603252365214836E-2</v>
+        <v>1.344511553665617E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -16520,10 +16549,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="234" t="s">
+      <c r="B17" s="235" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="234"/>
+      <c r="C17" s="235"/>
       <c r="E17" s="181" t="s">
         <v>295</v>
       </c>
@@ -16596,14 +16625,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="234" t="s">
+      <c r="B25" s="235" t="s">
         <v>104</v>
       </c>
-      <c r="C25" s="234"/>
-      <c r="E25" s="232" t="s">
+      <c r="C25" s="235"/>
+      <c r="E25" s="233" t="s">
         <v>342</v>
       </c>
-      <c r="F25" s="233"/>
+      <c r="F25" s="234"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="181" t="s">
@@ -16612,12 +16641,12 @@
       <c r="C26" s="167">
         <v>0.21</v>
       </c>
-      <c r="E26" s="182" t="e" vm="2">
+      <c r="E26" s="182" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="216" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.85</v>
+        <v>44.79</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16632,7 +16661,7 @@
       </c>
       <c r="F27" s="217">
         <f ca="1">F26/1000</f>
-        <v>4.4850000000000001E-2</v>
+        <v>4.4789999999999996E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16652,15 +16681,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="235" t="s">
+      <c r="B33" s="232" t="s">
         <v>337</v>
       </c>
-      <c r="C33" s="235"/>
-      <c r="D33" s="235"/>
-      <c r="E33" s="235"/>
-      <c r="F33" s="235"/>
-      <c r="G33" s="235"/>
-      <c r="H33" s="235"/>
+      <c r="C33" s="232"/>
+      <c r="D33" s="232"/>
+      <c r="E33" s="232"/>
+      <c r="F33" s="232"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="232"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -16673,24 +16702,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="235"/>
-      <c r="C39" s="235"/>
-      <c r="D39" s="235"/>
-      <c r="E39" s="235"/>
-      <c r="F39" s="235"/>
-      <c r="G39" s="235"/>
-      <c r="H39" s="235"/>
+      <c r="B39" s="232"/>
+      <c r="C39" s="232"/>
+      <c r="D39" s="232"/>
+      <c r="E39" s="232"/>
+      <c r="F39" s="232"/>
+      <c r="G39" s="232"/>
+      <c r="H39" s="232"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="235" t="s">
+      <c r="B42" s="232" t="s">
         <v>340</v>
       </c>
-      <c r="C42" s="235"/>
-      <c r="D42" s="235"/>
-      <c r="E42" s="235"/>
-      <c r="F42" s="235"/>
-      <c r="G42" s="235"/>
-      <c r="H42" s="235"/>
+      <c r="C42" s="232"/>
+      <c r="D42" s="232"/>
+      <c r="E42" s="232"/>
+      <c r="F42" s="232"/>
+      <c r="G42" s="232"/>
+      <c r="H42" s="232"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -16705,24 +16734,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="235"/>
-      <c r="C49" s="235"/>
-      <c r="D49" s="235"/>
-      <c r="E49" s="235"/>
-      <c r="F49" s="235"/>
-      <c r="G49" s="235"/>
-      <c r="H49" s="235"/>
+      <c r="B49" s="232"/>
+      <c r="C49" s="232"/>
+      <c r="D49" s="232"/>
+      <c r="E49" s="232"/>
+      <c r="F49" s="232"/>
+      <c r="G49" s="232"/>
+      <c r="H49" s="232"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="235" t="s">
+      <c r="B52" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="C52" s="235"/>
-      <c r="D52" s="235"/>
-      <c r="E52" s="235"/>
-      <c r="F52" s="235"/>
-      <c r="G52" s="235"/>
-      <c r="H52" s="235"/>
+      <c r="C52" s="232"/>
+      <c r="D52" s="232"/>
+      <c r="E52" s="232"/>
+      <c r="F52" s="232"/>
+      <c r="G52" s="232"/>
+      <c r="H52" s="232"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -16737,13 +16766,13 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="235"/>
-      <c r="C59" s="235"/>
-      <c r="D59" s="235"/>
-      <c r="E59" s="235"/>
-      <c r="F59" s="235"/>
-      <c r="G59" s="235"/>
-      <c r="H59" s="235"/>
+      <c r="B59" s="232"/>
+      <c r="C59" s="232"/>
+      <c r="D59" s="232"/>
+      <c r="E59" s="232"/>
+      <c r="F59" s="232"/>
+      <c r="G59" s="232"/>
+      <c r="H59" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -16828,36 +16857,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="235" t="s">
+      <c r="S2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235"/>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
-      <c r="AA2" s="235" t="s">
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
+      <c r="AA2" s="232" t="s">
         <v>111</v>
       </c>
-      <c r="AB2" s="235"/>
-      <c r="AC2" s="235"/>
+      <c r="AB2" s="232"/>
+      <c r="AC2" s="232"/>
       <c r="AE2" s="85" t="s">
         <v>112</v>
       </c>
@@ -18228,35 +18257,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
-      <c r="P2" s="235" t="s">
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
+      <c r="P2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="Q2" s="235"/>
-      <c r="R2" s="235"/>
-      <c r="S2" s="235"/>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235" t="s">
+      <c r="Q2" s="232"/>
+      <c r="R2" s="232"/>
+      <c r="S2" s="232"/>
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232" t="s">
         <v>111</v>
       </c>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
       <c r="AB2" s="85" t="s">
         <v>112</v>
       </c>
@@ -19487,20 +19516,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -20943,20 +20972,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="S2" s="246"/>
       <c r="T2" s="246"/>
       <c r="U2" s="246"/>
@@ -22037,10 +22066,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="232"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22057,7 +22086,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>308.63</v>
+        <v>312.26</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22066,7 +22095,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>4549206.2</v>
+        <v>4602712.3999999994</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22084,7 +22113,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.4850000000000001E-2</v>
+        <v>4.4789999999999996E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22093,7 +22122,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.0868</v>
+        <v>1.0903</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22125,10 +22154,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="232" t="s">
         <v>170</v>
       </c>
-      <c r="C15" s="235"/>
+      <c r="C15" s="232"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22136,7 +22165,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.8280646015858892E-2</v>
+        <v>1.8071975320172701E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22145,7 +22174,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.98171935398414112</v>
+        <v>0.98192802467982732</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22163,7 +22192,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.3756000000000006E-2</v>
+        <v>9.3853500000000006E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22172,7 +22201,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.2713619283529725E-2</v>
+        <v>9.282125587767473E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22217,20 +22246,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -22423,7 +22452,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>1928325.9958641303</v>
+        <v>1925475.7505601391</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22477,23 +22506,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>96413.15957738203</v>
+        <v>96403.663436936506</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>93193.951001053298</v>
+        <v>93175.593771222775</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>90396.562769008087</v>
+        <v>90369.85477873635</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>87472.742554731027</v>
+        <v>87438.285402272217</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>88239.749402833404</v>
+        <v>88196.302428934941</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22512,14 +22541,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>1237794.8626094162</v>
+        <v>1235356.7292032014</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="235" t="s">
+      <c r="B13" s="232" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="235"/>
+      <c r="C13" s="232"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22535,14 +22564,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.2713619283529725E-2</v>
+        <v>9.282125587767473E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="235" t="s">
+      <c r="B18" s="232" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="235"/>
+      <c r="C18" s="232"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22550,7 +22579,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>455716.16530500783</v>
+        <v>455583.69981810276</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -22559,7 +22588,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>1237794.8626094162</v>
+        <v>1235356.7292032014</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -22568,7 +22597,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>1693511.027914424</v>
+        <v>1690940.429021304</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -22595,7 +22624,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>1755395.027914424</v>
+        <v>1752824.429021304</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -22613,7 +22642,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>119.09057177167055</v>
+        <v>118.91617564595006</v>
       </c>
     </row>
   </sheetData>
@@ -22634,7 +22663,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -22656,20 +22685,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -23601,10 +23630,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="232" t="s">
         <v>202</v>
       </c>
-      <c r="C37" s="235"/>
+      <c r="C37" s="232"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -23622,7 +23651,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.2713619283529725E-2</v>
+        <v>9.282125587767473E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -23635,182 +23664,227 @@
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C41" s="24">
+        <f>(C38*C40)</f>
+        <v>4332575.051406119</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B42" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C42" s="24">
+        <f ca="1">C41/(1+C39)^5-G30+G31</f>
+        <v>2813478.9964104597</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B43" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C43" s="88">
+        <f>Statement!AC105</f>
+        <v>146595</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C44" s="88">
+        <f>Statement!AC106</f>
+        <v>84711</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="64">
+        <f ca="1">C42+C43-C44</f>
+        <v>2875362.9964104597</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" s="88">
+        <f>Statement!AC77</f>
+        <v>14740</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="141" t="s">
+        <v>206</v>
+      </c>
+      <c r="C47" s="142">
+        <f ca="1">C45/C46</f>
+        <v>195.0721164457571</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="232" t="s">
+        <v>207</v>
+      </c>
+      <c r="C49" s="232"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C50" s="64">
+        <f>L6</f>
+        <v>594236.0514889753</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B51" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C51" s="135">
+        <f>Overview!C29</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="C52" s="105">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C41" s="24">
+      <c r="C53" s="24">
         <f>L18</f>
         <v>13302.3529680093</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C54" s="24">
+        <f>(C50*C52)/C53</f>
+        <v>223.35749657148918</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="141" t="s">
+        <v>206</v>
+      </c>
+      <c r="C55" s="142">
+        <f>C54/(1+C51)^5</f>
+        <v>138.68743228634972</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="232" t="s">
+        <v>321</v>
+      </c>
+      <c r="C57" s="232"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C58" s="64">
+        <f>L8</f>
+        <v>137466.23756646831</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B59" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C59" s="135">
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>9.282125587767473E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="39" t="s">
+        <v>350</v>
+      </c>
+      <c r="C60" s="105">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C42" s="24">
-        <f>(C38*C40)</f>
-        <v>4332575.051406119</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B43" s="1" t="s">
+      <c r="C61" s="24">
+        <f>(C58*C60)</f>
+        <v>2749324.7513293661</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C43" s="24">
-        <f ca="1">C42/(1+C39)^5-G30+G31</f>
-        <v>2814848.3310085684</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="1" t="s">
+      <c r="C62" s="24">
+        <f ca="1">C61/(1+C59)^5-G30+G31</f>
+        <v>1797689.0485786989</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" s="88">
+        <f>Statement!AC105</f>
+        <v>146595</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B64" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C64" s="88">
+        <f>Statement!AC106</f>
+        <v>84711</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C65" s="64">
+        <f ca="1">C62+C63-C64</f>
+        <v>1859573.0485786989</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C44" s="88">
+      <c r="C66" s="88">
         <f>Statement!AC77</f>
         <v>14740</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B45" s="141" t="s">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="141" t="s">
         <v>206</v>
       </c>
-      <c r="C45" s="142">
-        <f ca="1">C43/C44</f>
-        <v>190.96664389474685</v>
-      </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="235" t="s">
-        <v>207</v>
-      </c>
-      <c r="C47" s="235"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="C48" s="64">
-        <f>L6</f>
-        <v>594236.0514889753</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C49" s="135">
-        <f>Overview!C29</f>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B50" s="39" t="s">
-        <v>209</v>
-      </c>
-      <c r="C50" s="105">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C51" s="24">
-        <f>L18</f>
-        <v>13302.3529680093</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C52" s="24">
-        <f>(C48*C50)/C51</f>
-        <v>223.35749657148918</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="141" t="s">
-        <v>206</v>
-      </c>
-      <c r="C53" s="142">
-        <f>C52/(1+C49)^5</f>
-        <v>138.68743228634972</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="235" t="s">
-        <v>321</v>
-      </c>
-      <c r="C55" s="235"/>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C56" s="64">
-        <f>L8</f>
-        <v>137466.23756646831</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C57" s="135">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.2713619283529725E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B58" s="39" t="s">
-        <v>350</v>
-      </c>
-      <c r="C58" s="105">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C59" s="24">
-        <f>(C56*C58)</f>
-        <v>2749324.7513293661</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="C60" s="24">
-        <f ca="1">C59/(1+C57)^5-G30+G31</f>
-        <v>1798557.9880566681</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C61" s="88">
-        <f>Statement!AC77</f>
-        <v>14740</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="141" t="s">
-        <v>206</v>
-      </c>
-      <c r="C62" s="142">
-        <f ca="1">C60/C61</f>
-        <v>122.01885943396663</v>
+      <c r="C67" s="142">
+        <f ca="1">C65/C66</f>
+        <v>126.15828009353453</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
@@ -23854,10 +23928,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>212</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="232"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23866,7 +23940,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>119.09057177167055</v>
+        <v>118.91617564595006</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23874,8 +23948,8 @@
         <v>214</v>
       </c>
       <c r="C6" s="133">
-        <f ca="1">Multiples!C45</f>
-        <v>190.96664389474685</v>
+        <f ca="1">Multiples!C47</f>
+        <v>195.0721164457571</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23883,7 +23957,7 @@
         <v>215</v>
       </c>
       <c r="C7" s="133">
-        <f>Multiples!C53</f>
+        <f>Multiples!C55</f>
         <v>138.68743228634972</v>
       </c>
     </row>
@@ -23892,8 +23966,8 @@
         <v>322</v>
       </c>
       <c r="C8" s="133">
-        <f ca="1">Multiples!C62</f>
-        <v>122.01885943396663</v>
+        <f ca="1">Multiples!C67</f>
+        <v>126.15828009353453</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23902,7 +23976,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>142.69087684668344</v>
+        <v>144.70850111789787</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23911,7 +23985,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>308.63</v>
+        <v>312.26</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23920,7 +23994,7 @@
       </c>
       <c r="C11" s="151">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.53766362036521587</v>
+        <v>-0.53657688747230559</v>
       </c>
     </row>
   </sheetData>
@@ -23985,20 +24059,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -24173,7 +24247,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>5255703.4594641058</v>
+        <v>5247935.0405677995</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -24227,23 +24301,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>145028.49718044625</v>
+        <v>145014.21270948954</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>164576.82354290391</v>
+        <v>164544.405402648</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>186760.06008510161</v>
+        <v>186704.88115224056</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>211933.36517336537</v>
+        <v>211849.88064936845</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>240499.76881159769</v>
+        <v>240381.35293611235</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -24262,7 +24336,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>3373642.6078765481</v>
+        <v>3366997.4108480564</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24278,7 +24352,7 @@
       </c>
       <c r="C15" s="153">
         <f ca="1">Overview!C5</f>
-        <v>308.63</v>
+        <v>312.26</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24287,7 +24361,7 @@
       </c>
       <c r="C16" s="153">
         <f ca="1">C36</f>
-        <v>298.51740468917842</v>
+        <v>298.04426660978521</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24326,7 +24400,7 @@
       </c>
       <c r="C21" s="219">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.2713619283529725E-2</v>
+        <v>9.282125587767473E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24344,7 +24418,7 @@
       </c>
       <c r="C23" s="158">
         <f ca="1">C15*C22</f>
-        <v>4532848.8099999996</v>
+        <v>4586162.62</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24371,7 +24445,7 @@
       </c>
       <c r="C26" s="159">
         <f ca="1">C23+C25-C24</f>
-        <v>4470964.8099999996</v>
+        <v>4524278.62</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24387,7 +24461,7 @@
       </c>
       <c r="C29" s="158">
         <f ca="1">SUM(H10:L10)</f>
-        <v>948798.51479341486</v>
+        <v>948494.73284985893</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24396,7 +24470,7 @@
       </c>
       <c r="C30" s="158">
         <f ca="1">L11</f>
-        <v>3373642.6078765481</v>
+        <v>3366997.4108480564</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24405,7 +24479,7 @@
       </c>
       <c r="C31" s="161">
         <f ca="1">C29+C30</f>
-        <v>4322441.1226699632</v>
+        <v>4315492.1436979156</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24432,7 +24506,7 @@
       </c>
       <c r="C34" s="161">
         <f ca="1">C31+C32-C33</f>
-        <v>4384325.1226699632</v>
+        <v>4377376.1436979156</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -24450,7 +24524,7 @@
       </c>
       <c r="C36" s="164">
         <f ca="1">C34/C35</f>
-        <v>298.51740468917842</v>
+        <v>298.04426660978521</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -31305,7 +31379,7 @@
       <c r="AA114" s="68"/>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>308.63</v>
+        <v>312.26</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -31352,7 +31426,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>308.63</v>
+        <v>312.26</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32266,7 +32340,7 @@
       <c r="AA140" s="49"/>
       <c r="AC140" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>37.319226118500609</v>
+        <v>37.758162031438935</v>
       </c>
     </row>
     <row r="141" spans="2:29" x14ac:dyDescent="0.2">
@@ -32303,7 +32377,7 @@
       <c r="AA141" s="49"/>
       <c r="AC141" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>10.143370156077635</v>
+        <v>10.262672990107257</v>
       </c>
     </row>
     <row r="142" spans="2:29" x14ac:dyDescent="0.2">
@@ -32340,7 +32414,7 @@
       <c r="AA142" s="49"/>
       <c r="AC142" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>42.565557746664034</v>
+        <v>43.066199209322853</v>
       </c>
     </row>
     <row r="143" spans="2:29" x14ac:dyDescent="0.2">
@@ -32377,7 +32451,7 @@
       <c r="AA143" s="49"/>
       <c r="AC143" s="143">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>4549206.2</v>
+        <v>4602712.3999999994</v>
       </c>
     </row>
     <row r="144" spans="2:29" x14ac:dyDescent="0.2">
@@ -32414,7 +32488,7 @@
       <c r="AA144" s="49"/>
       <c r="AC144" s="143">
         <f ca="1">AC143+AC106-AC105+AC47+AC44</f>
-        <v>4487322.2</v>
+        <v>4540828.3999999994</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
@@ -32451,7 +32525,7 @@
       <c r="AA145" s="49"/>
       <c r="AC145" s="180">
         <f ca="1">AC144/AC5</f>
-        <v>9.9399750134015008</v>
+        <v>10.05849788012635</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
@@ -32488,7 +32562,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="180">
         <f ca="1">AC144/AC11</f>
-        <v>30.450186610208597</v>
+        <v>30.813270360870209</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32623,7 +32697,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f t="shared" ref="AC149:AC150" ca="1" si="89">AC143/AC147</f>
-        <v>39.318642016922929</v>
+        <v>39.781094372563757</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32660,7 +32734,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f t="shared" ca="1" si="89"/>
-        <v>38.824496757041281</v>
+        <v>39.28743460634071</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32697,7 +32771,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="74">
         <f t="shared" ref="AC151" ca="1" si="92">AC147/AC143</f>
-        <v>2.5433228328933518E-2</v>
+        <v>2.5137568882209544E-2</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32734,7 +32808,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>2.6795839678579528E-2</v>
+        <v>2.648433997309934E-2</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32771,7 +32845,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="151">
         <f ca="1">AC81/AC115</f>
-        <v>3.3697307455529276E-3</v>
+        <v>3.3305578684429643E-3</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32808,7 +32882,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="151">
         <f ca="1">-AC62/AC143</f>
-        <v>1.7188932873607708E-2</v>
+        <v>1.6989112767506396E-2</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32845,7 +32919,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="151">
         <f ca="1">-(AC62+AC63)/AC143</f>
-        <v>2.0607111631915035E-2</v>
+        <v>2.0367555444046431E-2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33348,7 +33422,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="151">
         <f ca="1">(AC105-AC106)/AC143</f>
-        <v>1.3603252365214836E-2</v>
+        <v>1.344511553665617E-2</v>
       </c>
     </row>
     <row r="167" spans="1:31" x14ac:dyDescent="0.2">
@@ -35345,15 +35419,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="235"/>
-      <c r="E4" s="235" t="s">
+      <c r="C4" s="232"/>
+      <c r="E4" s="232" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
+      <c r="F4" s="232"/>
+      <c r="G4" s="232"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35361,7 +35435,7 @@
       </c>
       <c r="C5" s="169">
         <f ca="1">Overview!C5</f>
-        <v>308.63</v>
+        <v>312.26</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -35377,7 +35451,7 @@
       </c>
       <c r="C6" s="170">
         <f ca="1">Statement!AC143</f>
-        <v>4549206.2</v>
+        <v>4602712.3999999994</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -35397,7 +35471,7 @@
       </c>
       <c r="C7" s="170">
         <f ca="1">Statement!AC144</f>
-        <v>4487322.2</v>
+        <v>4540828.3999999994</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -35417,7 +35491,7 @@
       </c>
       <c r="C8" s="171">
         <f ca="1">Statement!AC140</f>
-        <v>37.319226118500609</v>
+        <v>37.758162031438935</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -35437,7 +35511,7 @@
       </c>
       <c r="C9" s="171">
         <f ca="1">Statement!AC141</f>
-        <v>10.143370156077635</v>
+        <v>10.262672990107257</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -35457,7 +35531,7 @@
       </c>
       <c r="C10" s="171">
         <f ca="1">Statement!AC142</f>
-        <v>42.565557746664034</v>
+        <v>43.066199209322853</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35477,7 +35551,7 @@
       </c>
       <c r="C11" s="171">
         <f ca="1">Statement!AC145</f>
-        <v>9.9399750134015008</v>
+        <v>10.05849788012635</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35486,18 +35560,18 @@
       </c>
       <c r="C12" s="171">
         <f ca="1">Statement!AC146</f>
-        <v>30.450186610208597</v>
+        <v>30.813270360870209</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="235"/>
-      <c r="E15" s="235" t="s">
+      <c r="C15" s="232"/>
+      <c r="E15" s="232" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="235"/>
+      <c r="F15" s="232"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35548,14 +35622,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="235" t="s">
+      <c r="B21" s="232" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="235"/>
-      <c r="E21" s="235" t="s">
+      <c r="C21" s="232"/>
+      <c r="E21" s="232" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="235"/>
+      <c r="F21" s="232"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35624,14 +35698,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="235" t="s">
+      <c r="B29" s="232" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="235"/>
-      <c r="E29" s="235" t="s">
+      <c r="C29" s="232"/>
+      <c r="E29" s="232" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="235"/>
+      <c r="F29" s="232"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35707,14 +35781,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="232" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="235"/>
-      <c r="E37" s="235" t="s">
+      <c r="C37" s="232"/>
+      <c r="E37" s="232" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="235"/>
+      <c r="F37" s="232"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35722,7 +35796,7 @@
       </c>
       <c r="C38" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>2.6795839678579528E-2</v>
+        <v>2.648433997309934E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -35738,7 +35812,7 @@
       </c>
       <c r="C39" s="212">
         <f ca="1">Statement!AC151</f>
-        <v>2.5433228328933518E-2</v>
+        <v>2.5137568882209544E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -35754,7 +35828,7 @@
       </c>
       <c r="C40" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>3.3697307455529276E-3</v>
+        <v>3.3305578684429643E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -35770,7 +35844,7 @@
       </c>
       <c r="C41" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>1.7188932873607708E-2</v>
+        <v>1.6989112767506396E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35779,18 +35853,18 @@
       </c>
       <c r="C42" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>2.0607111631915035E-2</v>
+        <v>2.0367555444046431E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="235" t="s">
+      <c r="B45" s="232" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="235"/>
-      <c r="E45" s="235" t="s">
+      <c r="C45" s="232"/>
+      <c r="E45" s="232" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="235"/>
+      <c r="F45" s="232"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35823,18 +35897,18 @@
       </c>
       <c r="F48" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.3603252365214836E-2</v>
+        <v>1.344511553665617E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="235" t="s">
+      <c r="B51" s="232" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="235"/>
-      <c r="E51" s="235" t="s">
+      <c r="C51" s="232"/>
+      <c r="E51" s="232" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="235"/>
+      <c r="F51" s="232"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36002,7 +36076,7 @@
       </c>
       <c r="I6" s="169">
         <f ca="1">Statement!AC114</f>
-        <v>308.63</v>
+        <v>312.26</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36031,7 +36105,7 @@
       </c>
       <c r="I7" s="170">
         <f ca="1">Statement!AC143</f>
-        <v>4549206.2</v>
+        <v>4602712.3999999994</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36060,7 +36134,7 @@
       </c>
       <c r="I8" s="170">
         <f ca="1">Statement!AC144</f>
-        <v>4487322.2</v>
+        <v>4540828.3999999994</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36089,7 +36163,7 @@
       </c>
       <c r="I9" s="171">
         <f ca="1">Statement!AC140</f>
-        <v>37.319226118500609</v>
+        <v>37.758162031438935</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36118,7 +36192,7 @@
       </c>
       <c r="I10" s="171">
         <f ca="1">Statement!AC141</f>
-        <v>10.143370156077635</v>
+        <v>10.262672990107257</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36147,7 +36221,7 @@
       </c>
       <c r="I11" s="171">
         <f ca="1">Statement!AC142</f>
-        <v>42.565557746664034</v>
+        <v>43.066199209322853</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36176,7 +36250,7 @@
       </c>
       <c r="I12" s="171">
         <f ca="1">Statement!AC145</f>
-        <v>9.9399750134015008</v>
+        <v>10.05849788012635</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36205,7 +36279,7 @@
       </c>
       <c r="I13" s="171">
         <f ca="1">Statement!AC146</f>
-        <v>30.450186610208597</v>
+        <v>30.813270360870209</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36978,7 +37052,7 @@
       </c>
       <c r="I51" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>2.6795839678579528E-2</v>
+        <v>2.648433997309934E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37007,7 +37081,7 @@
       </c>
       <c r="I52" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>2.5433228328933518E-2</v>
+        <v>2.5137568882209544E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37036,7 +37110,7 @@
       </c>
       <c r="I53" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>3.3697307455529276E-3</v>
+        <v>3.3305578684429643E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -37065,7 +37139,7 @@
       </c>
       <c r="I54" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>1.7188932873607708E-2</v>
+        <v>1.6989112767506396E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37094,7 +37168,7 @@
       </c>
       <c r="I55" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>2.0607111631915035E-2</v>
+        <v>2.0367555444046431E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37330,7 +37404,7 @@
       </c>
       <c r="I68" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>1.3603252365214836E-2</v>
+        <v>1.344511553665617E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/AAPL.xlsx
+++ b/AAPL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4BF1AB-0D5E-6C4A-8414-8E4E638DF49B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD5252E-72F5-7649-9C41-6EE97B78816D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -117,7 +117,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -128,28 +128,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -159,21 +138,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2317,9 +2287,6 @@
     <xf numFmtId="10" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="23" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2327,6 +2294,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15400,7 +15370,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1mou2&amp;q=XNAS%3aAAPL&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -15419,9 +15389,11 @@
     <v>Powered by Refinitiv</v>
     <v>317.39999999999998</v>
     <v>201.5</v>
-    <v>1.0903</v>
-    <v>-0.4</v>
-    <v>-1.2790000000000002E-3</v>
+    <v>1.0904</v>
+    <v>-0.9</v>
+    <v>-2.846E-3</v>
+    <v>-0.21809999999999999</v>
+    <v>-6.9169999999999995E-4</v>
     <v>USD</v>
     <v>Apple Inc. designs, manufactures and markets smartphones, personal computers, tablets, wearables and accessories, and sells a variety of related services. Its product categories include iPhone, Mac, iPad, Wearables, Home and Accessories. Its services include advertising, AppleCare, cloud services, digital content, and payment services. The Company operates various platforms, including the App Store, that allow customers to discover and download applications and digital content, such as books, music, video, games and podcasts. It also offers digital content through subscription-based services, including Apple Arcade, Apple Fitness+, Apple Music, Apple News+, and Apple TV+. Its wearables include smartwatches, wireless headphones, and spatial computers. Its products include iPhone 16 Pro, iPhone 16, iPhone 15, iPhone 14, iPhone SE, MacBook Air, MacBook Pro, iMac, Mac mini, Mac Studio, Mac Pro, iPad Pro, iPad Air, AirPods, AirPods Pro, AirPods Max, Apple TV, Apple Vision Pro and others.</v>
     <v>166000</v>
@@ -15429,49 +15401,35 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Apple Park Way, CUPERTINO, CA, 95014 US</v>
-    <v>315.48</v>
+    <v>316.91000000000003</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46210.767967233594</v>
+    <v>46213.888557071092</v>
     <v>0</v>
-    <v>310.14999999999998</v>
-    <v>4586275033600</v>
+    <v>312.17</v>
+    <v>4631218355200</v>
     <v>APPLE INC.</v>
     <v>APPLE INC.</v>
-    <v>315</v>
-    <v>37.924199999999999</v>
-    <v>312.66000000000003</v>
-    <v>312.26</v>
+    <v>314.72000000000003</v>
+    <v>38.2958</v>
+    <v>316.22000000000003</v>
+    <v>315.32</v>
+    <v>315.1019</v>
     <v>14687360000</v>
     <v>AAPL</v>
     <v>APPLE INC. (XNAS:AAPL)</v>
-    <v>25322976</v>
-    <v>66025371</v>
+    <v>32478188</v>
+    <v>64766433</v>
     <v>1977</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -15485,28 +15443,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.06</v>
-    <v>-1.338E-3</v>
+    <v>-0.3</v>
+    <v>-6.5659999999999998E-3</v>
     <v>US</v>
-    <v>44.91</v>
+    <v>45.81</v>
     <v>Index</v>
-    <v>6</v>
-    <v>44.57</v>
+    <v>3</v>
+    <v>45.29</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.57</v>
-    <v>44.85</v>
-    <v>44.79</v>
+    <v>45.77</v>
+    <v>45.69</v>
+    <v>45.39</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -15528,6 +15486,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -15548,6 +15508,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -15557,11 +15518,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -15597,7 +15553,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -15608,13 +15564,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -15708,13 +15667,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -15786,6 +15751,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -15793,6 +15761,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -16277,18 +16248,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="233" t="s">
+      <c r="B2" s="232" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="234"/>
-      <c r="E2" s="233" t="s">
+      <c r="C2" s="233"/>
+      <c r="E2" s="232" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="234"/>
-      <c r="H2" s="233" t="s">
+      <c r="F2" s="233"/>
+      <c r="H2" s="232" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="234"/>
+      <c r="I2" s="233"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="182" t="s">
@@ -16303,7 +16274,7 @@
       </c>
       <c r="F3" s="184">
         <f ca="1">Statement!AC143</f>
-        <v>4602712.3999999994</v>
+        <v>4647816.8</v>
       </c>
       <c r="H3" s="182" t="str">
         <f>'AVG target price'!B5</f>
@@ -16311,7 +16282,7 @@
       </c>
       <c r="I3" s="208">
         <f ca="1">'AVG target price'!C5</f>
-        <v>118.91617564595006</v>
+        <v>117.94784406159961</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16327,7 +16298,7 @@
       </c>
       <c r="F4" s="185">
         <f ca="1">Statement!AC144</f>
-        <v>4540828.3999999994</v>
+        <v>4585932.7999999998</v>
       </c>
       <c r="H4" s="182" t="str">
         <f>'AVG target price'!B6</f>
@@ -16335,7 +16306,7 @@
       </c>
       <c r="I4" s="208">
         <f ca="1">'AVG target price'!C6</f>
-        <v>195.0721164457571</v>
+        <v>194.55224664880012</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16344,7 +16315,7 @@
       </c>
       <c r="C5" s="205" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>312.26</v>
+        <v>315.32</v>
       </c>
       <c r="E5" s="182" t="s">
         <v>242</v>
@@ -16366,16 +16337,16 @@
       <c r="B6" s="182" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="205" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="205" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>315.1019</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="187">
         <f ca="1">Statement!AC140</f>
-        <v>37.758162031438935</v>
+        <v>38.128174123337367</v>
       </c>
       <c r="H6" s="182" t="str">
         <f>'AVG target price'!B8</f>
@@ -16383,7 +16354,7 @@
       </c>
       <c r="I6" s="208">
         <f ca="1">'AVG target price'!C8</f>
-        <v>126.15828009353453</v>
+        <v>125.82838600438804</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16392,14 +16363,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>198</v>
       </c>
       <c r="F7" s="188">
         <f ca="1">Statement!AC141</f>
-        <v>10.262672990107257</v>
+        <v>10.363242321272722</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -16407,23 +16378,23 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>144.70850111789787</v>
+        <v>144.25397725028435</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="182" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-0.21809999999999999</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="189">
         <f ca="1">Statement!AC151</f>
-        <v>2.5137568882209544E-2</v>
+        <v>2.4893623173787745E-2</v>
       </c>
       <c r="H8" s="181" t="str">
         <f>'AVG target price'!B11</f>
@@ -16431,7 +16402,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.53657688747230559</v>
+        <v>-0.5425156119171497</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16440,30 +16411,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.2790000000000002E-3</v>
+        <v>-2.846E-3</v>
       </c>
       <c r="E9" s="182" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="189">
         <f ca="1">Statement!AC152</f>
-        <v>2.648433997309934E-2</v>
+        <v>2.6227324622605606E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="182" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-6.9169999999999995E-4</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="189">
         <f ca="1">Statement!AC154</f>
-        <v>1.6989112767506396E-2</v>
+        <v>1.6824243158637408E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -16479,7 +16450,7 @@
       </c>
       <c r="F11" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>3.3305578684429643E-3</v>
+        <v>3.2982367119117088E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -16504,7 +16475,7 @@
       </c>
       <c r="C13" s="206" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0903</v>
+        <v>1.0904</v>
       </c>
       <c r="E13" s="182" t="s">
         <v>101</v>
@@ -16520,7 +16491,7 @@
       </c>
       <c r="C14" s="207" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>66025371</v>
+        <v>64766433</v>
       </c>
       <c r="E14" s="183" t="s">
         <v>102</v>
@@ -16536,7 +16507,7 @@
       </c>
       <c r="F15" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.344511553665617E-2</v>
+        <v>1.3314638391082885E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -16549,10 +16520,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="235" t="s">
+      <c r="B17" s="234" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="235"/>
+      <c r="C17" s="234"/>
       <c r="E17" s="181" t="s">
         <v>295</v>
       </c>
@@ -16625,14 +16596,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="235" t="s">
+      <c r="B25" s="234" t="s">
         <v>104</v>
       </c>
-      <c r="C25" s="235"/>
-      <c r="E25" s="233" t="s">
+      <c r="C25" s="234"/>
+      <c r="E25" s="232" t="s">
         <v>342</v>
       </c>
-      <c r="F25" s="234"/>
+      <c r="F25" s="233"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="181" t="s">
@@ -16641,12 +16612,12 @@
       <c r="C26" s="167">
         <v>0.21</v>
       </c>
-      <c r="E26" s="182" t="e" vm="5">
+      <c r="E26" s="182" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="216" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.79</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16661,7 +16632,7 @@
       </c>
       <c r="F27" s="217">
         <f ca="1">F26/1000</f>
-        <v>4.4789999999999996E-2</v>
+        <v>4.539E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16681,15 +16652,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="232" t="s">
+      <c r="B33" s="235" t="s">
         <v>337</v>
       </c>
-      <c r="C33" s="232"/>
-      <c r="D33" s="232"/>
-      <c r="E33" s="232"/>
-      <c r="F33" s="232"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="232"/>
+      <c r="C33" s="235"/>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="235"/>
+      <c r="H33" s="235"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -16702,24 +16673,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="232"/>
-      <c r="C39" s="232"/>
-      <c r="D39" s="232"/>
-      <c r="E39" s="232"/>
-      <c r="F39" s="232"/>
-      <c r="G39" s="232"/>
-      <c r="H39" s="232"/>
+      <c r="B39" s="235"/>
+      <c r="C39" s="235"/>
+      <c r="D39" s="235"/>
+      <c r="E39" s="235"/>
+      <c r="F39" s="235"/>
+      <c r="G39" s="235"/>
+      <c r="H39" s="235"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="232" t="s">
+      <c r="B42" s="235" t="s">
         <v>340</v>
       </c>
-      <c r="C42" s="232"/>
-      <c r="D42" s="232"/>
-      <c r="E42" s="232"/>
-      <c r="F42" s="232"/>
-      <c r="G42" s="232"/>
-      <c r="H42" s="232"/>
+      <c r="C42" s="235"/>
+      <c r="D42" s="235"/>
+      <c r="E42" s="235"/>
+      <c r="F42" s="235"/>
+      <c r="G42" s="235"/>
+      <c r="H42" s="235"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -16734,24 +16705,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="232"/>
-      <c r="C49" s="232"/>
-      <c r="D49" s="232"/>
-      <c r="E49" s="232"/>
-      <c r="F49" s="232"/>
-      <c r="G49" s="232"/>
-      <c r="H49" s="232"/>
+      <c r="B49" s="235"/>
+      <c r="C49" s="235"/>
+      <c r="D49" s="235"/>
+      <c r="E49" s="235"/>
+      <c r="F49" s="235"/>
+      <c r="G49" s="235"/>
+      <c r="H49" s="235"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="232" t="s">
+      <c r="B52" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="C52" s="232"/>
-      <c r="D52" s="232"/>
-      <c r="E52" s="232"/>
-      <c r="F52" s="232"/>
-      <c r="G52" s="232"/>
-      <c r="H52" s="232"/>
+      <c r="C52" s="235"/>
+      <c r="D52" s="235"/>
+      <c r="E52" s="235"/>
+      <c r="F52" s="235"/>
+      <c r="G52" s="235"/>
+      <c r="H52" s="235"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -16766,13 +16737,13 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="232"/>
-      <c r="C59" s="232"/>
-      <c r="D59" s="232"/>
-      <c r="E59" s="232"/>
-      <c r="F59" s="232"/>
-      <c r="G59" s="232"/>
-      <c r="H59" s="232"/>
+      <c r="B59" s="235"/>
+      <c r="C59" s="235"/>
+      <c r="D59" s="235"/>
+      <c r="E59" s="235"/>
+      <c r="F59" s="235"/>
+      <c r="G59" s="235"/>
+      <c r="H59" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -16857,36 +16828,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="232" t="s">
+      <c r="S2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="232" t="s">
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
+      <c r="AA2" s="235" t="s">
         <v>111</v>
       </c>
-      <c r="AB2" s="232"/>
-      <c r="AC2" s="232"/>
+      <c r="AB2" s="235"/>
+      <c r="AC2" s="235"/>
       <c r="AE2" s="85" t="s">
         <v>112</v>
       </c>
@@ -18257,35 +18228,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="P2" s="232" t="s">
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
+      <c r="P2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="Q2" s="232"/>
-      <c r="R2" s="232"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232" t="s">
+      <c r="Q2" s="235"/>
+      <c r="R2" s="235"/>
+      <c r="S2" s="235"/>
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235" t="s">
         <v>111</v>
       </c>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
       <c r="AB2" s="85" t="s">
         <v>112</v>
       </c>
@@ -19516,20 +19487,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -20972,20 +20943,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="S2" s="246"/>
       <c r="T2" s="246"/>
       <c r="U2" s="246"/>
@@ -22066,10 +22037,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="235"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22086,7 +22057,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>312.26</v>
+        <v>315.32</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22095,7 +22066,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>4602712.3999999994</v>
+        <v>4647816.8</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22113,7 +22084,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.4789999999999996E-2</v>
+        <v>4.539E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22122,7 +22093,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.0903</v>
+        <v>1.0904</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22154,10 +22125,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="235" t="s">
         <v>170</v>
       </c>
-      <c r="C15" s="232"/>
+      <c r="C15" s="235"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22165,7 +22136,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.8071975320172701E-2</v>
+        <v>1.7899736373445076E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22174,7 +22145,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.98192802467982732</v>
+        <v>0.98210026362655489</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22192,7 +22163,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.3853500000000006E-2</v>
+        <v>9.4458E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22201,7 +22172,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.282125587767473E-2</v>
+        <v>9.3424773517315624E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22246,20 +22217,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -22452,7 +22423,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>1925475.7505601391</v>
+        <v>1909649.2314645126</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22506,23 +22477,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>96403.663436936506</v>
+        <v>96350.45327303739</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>93175.593771222775</v>
+        <v>93072.765306374349</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>90369.85477873635</v>
+        <v>90220.297978009301</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>87438.285402272217</v>
+        <v>87245.398338495695</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>88196.302428934941</v>
+        <v>87953.170485233975</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22541,14 +22512,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>1235356.7292032014</v>
+        <v>1221825.1360868276</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="232" t="s">
+      <c r="B13" s="235" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="232"/>
+      <c r="C13" s="235"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22564,14 +22535,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.282125587767473E-2</v>
+        <v>9.3424773517315624E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="232" t="s">
+      <c r="B18" s="235" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="232"/>
+      <c r="C18" s="235"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22579,7 +22550,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>455583.69981810276</v>
+        <v>454842.08538115071</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -22588,7 +22559,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>1235356.7292032014</v>
+        <v>1221825.1360868276</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -22597,7 +22568,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>1690940.429021304</v>
+        <v>1676667.2214679783</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -22624,7 +22595,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>1752824.429021304</v>
+        <v>1738551.2214679783</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -22642,7 +22613,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>118.91617564595006</v>
+        <v>117.94784406159961</v>
       </c>
     </row>
   </sheetData>
@@ -22685,20 +22656,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -23630,10 +23601,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="235" t="s">
         <v>202</v>
       </c>
-      <c r="C37" s="232"/>
+      <c r="C37" s="235"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -23651,7 +23622,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.282125587767473E-2</v>
+        <v>9.3424773517315624E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -23677,7 +23648,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>2813478.9964104597</v>
+        <v>2805816.1156033138</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -23704,7 +23675,7 @@
       </c>
       <c r="C45" s="64">
         <f ca="1">C42+C43-C44</f>
-        <v>2875362.9964104597</v>
+        <v>2867700.1156033138</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23722,14 +23693,14 @@
       </c>
       <c r="C47" s="142">
         <f ca="1">C45/C46</f>
-        <v>195.0721164457571</v>
+        <v>194.55224664880012</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="232" t="s">
+      <c r="B49" s="235" t="s">
         <v>207</v>
       </c>
-      <c r="C49" s="232"/>
+      <c r="C49" s="235"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -23785,10 +23756,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="232" t="s">
+      <c r="B57" s="235" t="s">
         <v>321</v>
       </c>
-      <c r="C57" s="232"/>
+      <c r="C57" s="235"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -23805,7 +23776,7 @@
       </c>
       <c r="C59" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.282125587767473E-2</v>
+        <v>9.3424773517315624E-2</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -23831,7 +23802,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>1797689.0485786989</v>
+        <v>1792826.4097046796</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -23858,7 +23829,7 @@
       </c>
       <c r="C65" s="64">
         <f ca="1">C62+C63-C64</f>
-        <v>1859573.0485786989</v>
+        <v>1854710.4097046796</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23876,7 +23847,7 @@
       </c>
       <c r="C67" s="142">
         <f ca="1">C65/C66</f>
-        <v>126.15828009353453</v>
+        <v>125.82838600438804</v>
       </c>
     </row>
   </sheetData>
@@ -23928,10 +23899,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>212</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="235"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23940,7 +23911,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>118.91617564595006</v>
+        <v>117.94784406159961</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23949,7 +23920,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C47</f>
-        <v>195.0721164457571</v>
+        <v>194.55224664880012</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23967,7 +23938,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C67</f>
-        <v>126.15828009353453</v>
+        <v>125.82838600438804</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23976,7 +23947,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>144.70850111789787</v>
+        <v>144.25397725028435</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23985,7 +23956,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>312.26</v>
+        <v>315.32</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23994,7 +23965,7 @@
       </c>
       <c r="C11" s="151">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.53657688747230559</v>
+        <v>-0.5425156119171497</v>
       </c>
     </row>
   </sheetData>
@@ -24059,20 +24030,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -24247,7 +24218,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>5247935.0405677995</v>
+        <v>5204799.4445427703</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -24301,23 +24272,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>145014.21270948954</v>
+        <v>144934.17187130061</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>164544.405402648</v>
+        <v>164362.81440953349</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>186704.88115224056</v>
+        <v>186395.89554223133</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>211849.88064936845</v>
+        <v>211382.54415881552</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>240381.35293611235</v>
+        <v>239718.69039857667</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -24336,7 +24307,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>3366997.4108480564</v>
+        <v>3330116.6962249489</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24352,7 +24323,7 @@
       </c>
       <c r="C15" s="153">
         <f ca="1">Overview!C5</f>
-        <v>312.26</v>
+        <v>315.32</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24361,7 +24332,7 @@
       </c>
       <c r="C16" s="153">
         <f ca="1">C36</f>
-        <v>298.04426660978521</v>
+        <v>295.41736315145408</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24400,7 +24371,7 @@
       </c>
       <c r="C21" s="219">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.282125587767473E-2</v>
+        <v>9.3424773517315624E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24418,7 +24389,7 @@
       </c>
       <c r="C23" s="158">
         <f ca="1">C15*C22</f>
-        <v>4586162.62</v>
+        <v>4631104.84</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -24445,7 +24416,7 @@
       </c>
       <c r="C26" s="159">
         <f ca="1">C23+C25-C24</f>
-        <v>4524278.62</v>
+        <v>4569220.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24461,7 +24432,7 @@
       </c>
       <c r="C29" s="158">
         <f ca="1">SUM(H10:L10)</f>
-        <v>948494.73284985893</v>
+        <v>946794.11638045753</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24470,7 +24441,7 @@
       </c>
       <c r="C30" s="158">
         <f ca="1">L11</f>
-        <v>3366997.4108480564</v>
+        <v>3330116.6962249489</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24479,7 +24450,7 @@
       </c>
       <c r="C31" s="161">
         <f ca="1">C29+C30</f>
-        <v>4315492.1436979156</v>
+        <v>4276910.8126054062</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24506,7 +24477,7 @@
       </c>
       <c r="C34" s="161">
         <f ca="1">C31+C32-C33</f>
-        <v>4377376.1436979156</v>
+        <v>4338794.8126054062</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -24524,7 +24495,7 @@
       </c>
       <c r="C36" s="164">
         <f ca="1">C34/C35</f>
-        <v>298.04426660978521</v>
+        <v>295.41736315145408</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -31379,7 +31350,7 @@
       <c r="AA114" s="68"/>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>312.26</v>
+        <v>315.32</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -31426,7 +31397,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>312.26</v>
+        <v>315.32</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32340,7 +32311,7 @@
       <c r="AA140" s="49"/>
       <c r="AC140" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>37.758162031438935</v>
+        <v>38.128174123337367</v>
       </c>
     </row>
     <row r="141" spans="2:29" x14ac:dyDescent="0.2">
@@ -32377,7 +32348,7 @@
       <c r="AA141" s="49"/>
       <c r="AC141" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>10.262672990107257</v>
+        <v>10.363242321272722</v>
       </c>
     </row>
     <row r="142" spans="2:29" x14ac:dyDescent="0.2">
@@ -32414,7 +32385,7 @@
       <c r="AA142" s="49"/>
       <c r="AC142" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>43.066199209322853</v>
+        <v>43.488227549745986</v>
       </c>
     </row>
     <row r="143" spans="2:29" x14ac:dyDescent="0.2">
@@ -32451,7 +32422,7 @@
       <c r="AA143" s="49"/>
       <c r="AC143" s="143">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>4602712.3999999994</v>
+        <v>4647816.8</v>
       </c>
     </row>
     <row r="144" spans="2:29" x14ac:dyDescent="0.2">
@@ -32488,7 +32459,7 @@
       <c r="AA144" s="49"/>
       <c r="AC144" s="143">
         <f ca="1">AC143+AC106-AC105+AC47+AC44</f>
-        <v>4540828.3999999994</v>
+        <v>4585932.7999999998</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
@@ -32525,7 +32496,7 @@
       <c r="AA145" s="49"/>
       <c r="AC145" s="180">
         <f ca="1">AC144/AC5</f>
-        <v>10.05849788012635</v>
+        <v>10.158409718191926</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
@@ -32562,7 +32533,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="180">
         <f ca="1">AC144/AC11</f>
-        <v>30.813270360870209</v>
+        <v>31.119340960601495</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -32697,7 +32668,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f t="shared" ref="AC149:AC150" ca="1" si="89">AC143/AC147</f>
-        <v>39.781094372563757</v>
+        <v>40.170930242608101</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -32734,7 +32705,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f t="shared" ca="1" si="89"/>
-        <v>39.28743460634071</v>
+        <v>39.677679735502217</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32771,7 +32742,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="74">
         <f t="shared" ref="AC151" ca="1" si="92">AC147/AC143</f>
-        <v>2.5137568882209544E-2</v>
+        <v>2.4893623173787745E-2</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32808,7 +32779,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>2.648433997309934E-2</v>
+        <v>2.6227324622605606E-2</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32845,7 +32816,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="151">
         <f ca="1">AC81/AC115</f>
-        <v>3.3305578684429643E-3</v>
+        <v>3.2982367119117088E-3</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32882,7 +32853,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="151">
         <f ca="1">-AC62/AC143</f>
-        <v>1.6989112767506396E-2</v>
+        <v>1.6824243158637408E-2</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32919,7 +32890,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="151">
         <f ca="1">-(AC62+AC63)/AC143</f>
-        <v>2.0367555444046431E-2</v>
+        <v>2.0169899984009698E-2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33422,7 +33393,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="151">
         <f ca="1">(AC105-AC106)/AC143</f>
-        <v>1.344511553665617E-2</v>
+        <v>1.3314638391082885E-2</v>
       </c>
     </row>
     <row r="167" spans="1:31" x14ac:dyDescent="0.2">
@@ -35419,15 +35390,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="E4" s="232" t="s">
+      <c r="C4" s="235"/>
+      <c r="E4" s="235" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35435,7 +35406,7 @@
       </c>
       <c r="C5" s="169">
         <f ca="1">Overview!C5</f>
-        <v>312.26</v>
+        <v>315.32</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -35451,7 +35422,7 @@
       </c>
       <c r="C6" s="170">
         <f ca="1">Statement!AC143</f>
-        <v>4602712.3999999994</v>
+        <v>4647816.8</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -35471,7 +35442,7 @@
       </c>
       <c r="C7" s="170">
         <f ca="1">Statement!AC144</f>
-        <v>4540828.3999999994</v>
+        <v>4585932.7999999998</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -35491,7 +35462,7 @@
       </c>
       <c r="C8" s="171">
         <f ca="1">Statement!AC140</f>
-        <v>37.758162031438935</v>
+        <v>38.128174123337367</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -35511,7 +35482,7 @@
       </c>
       <c r="C9" s="171">
         <f ca="1">Statement!AC141</f>
-        <v>10.262672990107257</v>
+        <v>10.363242321272722</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -35531,7 +35502,7 @@
       </c>
       <c r="C10" s="171">
         <f ca="1">Statement!AC142</f>
-        <v>43.066199209322853</v>
+        <v>43.488227549745986</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35551,7 +35522,7 @@
       </c>
       <c r="C11" s="171">
         <f ca="1">Statement!AC145</f>
-        <v>10.05849788012635</v>
+        <v>10.158409718191926</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35560,18 +35531,18 @@
       </c>
       <c r="C12" s="171">
         <f ca="1">Statement!AC146</f>
-        <v>30.813270360870209</v>
+        <v>31.119340960601495</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="235" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="232"/>
-      <c r="E15" s="232" t="s">
+      <c r="C15" s="235"/>
+      <c r="E15" s="235" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="232"/>
+      <c r="F15" s="235"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35622,14 +35593,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="232" t="s">
+      <c r="B21" s="235" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="232"/>
-      <c r="E21" s="232" t="s">
+      <c r="C21" s="235"/>
+      <c r="E21" s="235" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="232"/>
+      <c r="F21" s="235"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35698,14 +35669,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="232" t="s">
+      <c r="B29" s="235" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="232"/>
-      <c r="E29" s="232" t="s">
+      <c r="C29" s="235"/>
+      <c r="E29" s="235" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="232"/>
+      <c r="F29" s="235"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35781,14 +35752,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="235" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="232"/>
-      <c r="E37" s="232" t="s">
+      <c r="C37" s="235"/>
+      <c r="E37" s="235" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="232"/>
+      <c r="F37" s="235"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35796,7 +35767,7 @@
       </c>
       <c r="C38" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>2.648433997309934E-2</v>
+        <v>2.6227324622605606E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -35812,7 +35783,7 @@
       </c>
       <c r="C39" s="212">
         <f ca="1">Statement!AC151</f>
-        <v>2.5137568882209544E-2</v>
+        <v>2.4893623173787745E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -35828,7 +35799,7 @@
       </c>
       <c r="C40" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>3.3305578684429643E-3</v>
+        <v>3.2982367119117088E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -35844,7 +35815,7 @@
       </c>
       <c r="C41" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>1.6989112767506396E-2</v>
+        <v>1.6824243158637408E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35853,18 +35824,18 @@
       </c>
       <c r="C42" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>2.0367555444046431E-2</v>
+        <v>2.0169899984009698E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="232" t="s">
+      <c r="B45" s="235" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="232"/>
-      <c r="E45" s="232" t="s">
+      <c r="C45" s="235"/>
+      <c r="E45" s="235" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="232"/>
+      <c r="F45" s="235"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35897,18 +35868,18 @@
       </c>
       <c r="F48" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.344511553665617E-2</v>
+        <v>1.3314638391082885E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="232" t="s">
+      <c r="B51" s="235" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="232"/>
-      <c r="E51" s="232" t="s">
+      <c r="C51" s="235"/>
+      <c r="E51" s="235" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="232"/>
+      <c r="F51" s="235"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36076,7 +36047,7 @@
       </c>
       <c r="I6" s="169">
         <f ca="1">Statement!AC114</f>
-        <v>312.26</v>
+        <v>315.32</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36105,7 +36076,7 @@
       </c>
       <c r="I7" s="170">
         <f ca="1">Statement!AC143</f>
-        <v>4602712.3999999994</v>
+        <v>4647816.8</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36134,7 +36105,7 @@
       </c>
       <c r="I8" s="170">
         <f ca="1">Statement!AC144</f>
-        <v>4540828.3999999994</v>
+        <v>4585932.7999999998</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36163,7 +36134,7 @@
       </c>
       <c r="I9" s="171">
         <f ca="1">Statement!AC140</f>
-        <v>37.758162031438935</v>
+        <v>38.128174123337367</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36192,7 +36163,7 @@
       </c>
       <c r="I10" s="171">
         <f ca="1">Statement!AC141</f>
-        <v>10.262672990107257</v>
+        <v>10.363242321272722</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36221,7 +36192,7 @@
       </c>
       <c r="I11" s="171">
         <f ca="1">Statement!AC142</f>
-        <v>43.066199209322853</v>
+        <v>43.488227549745986</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36250,7 +36221,7 @@
       </c>
       <c r="I12" s="171">
         <f ca="1">Statement!AC145</f>
-        <v>10.05849788012635</v>
+        <v>10.158409718191926</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36279,7 +36250,7 @@
       </c>
       <c r="I13" s="171">
         <f ca="1">Statement!AC146</f>
-        <v>30.813270360870209</v>
+        <v>31.119340960601495</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37052,7 +37023,7 @@
       </c>
       <c r="I51" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>2.648433997309934E-2</v>
+        <v>2.6227324622605606E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37081,7 +37052,7 @@
       </c>
       <c r="I52" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>2.5137568882209544E-2</v>
+        <v>2.4893623173787745E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37110,7 +37081,7 @@
       </c>
       <c r="I53" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>3.3305578684429643E-3</v>
+        <v>3.2982367119117088E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -37139,7 +37110,7 @@
       </c>
       <c r="I54" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>1.6989112767506396E-2</v>
+        <v>1.6824243158637408E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37168,7 +37139,7 @@
       </c>
       <c r="I55" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>2.0367555444046431E-2</v>
+        <v>2.0169899984009698E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37404,7 +37375,7 @@
       </c>
       <c r="I68" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>1.344511553665617E-2</v>
+        <v>1.3314638391082885E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/AAPL.xlsx
+++ b/AAPL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD5252E-72F5-7649-9C41-6EE97B78816D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B3157A-2698-C74D-BA44-79D191A8B7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -32,10 +32,12 @@
     <sheet name="DCF" sheetId="11" r:id="rId17"/>
     <sheet name="Multiples" sheetId="12" r:id="rId18"/>
     <sheet name="AVG target price" sheetId="13" r:id="rId19"/>
-    <sheet name="Reverse DCF" sheetId="14" r:id="rId20"/>
+    <sheet name="DDM" sheetId="21" r:id="rId20"/>
+    <sheet name="Reverse DCF" sheetId="14" r:id="rId21"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId21"/>
+    <externalReference r:id="rId22"/>
+    <externalReference r:id="rId23"/>
   </externalReferences>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -150,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="417">
   <si>
     <t>Ticker</t>
   </si>
@@ -1368,6 +1370,39 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>Manual Cost of Equity</t>
+  </si>
+  <si>
+    <t>DDM price</t>
+  </si>
+  <si>
+    <t>Dividend discount model</t>
+  </si>
+  <si>
+    <t>Dividend per share</t>
+  </si>
+  <si>
+    <t>Ratios</t>
+  </si>
+  <si>
+    <t>Payout</t>
+  </si>
+  <si>
+    <t>DDM valuation</t>
+  </si>
+  <si>
+    <t>Latest dividend</t>
+  </si>
+  <si>
+    <t>Year 1 growth rate</t>
+  </si>
+  <si>
+    <t>Year 1 dividend</t>
+  </si>
+  <si>
+    <t>Perpetual dividend growth</t>
   </si>
 </sst>
 </file>
@@ -1980,7 +2015,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="250">
+  <cellXfs count="255">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2287,6 +2322,9 @@
     <xf numFmtId="10" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="23" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2296,15 +2334,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2312,6 +2341,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2341,6 +2376,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15260,6 +15300,95 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Overview"/>
+      <sheetName val="Financials -&gt;"/>
+      <sheetName val="Statement"/>
+      <sheetName val="Analysis -&gt;"/>
+      <sheetName val="Basic"/>
+      <sheetName val="Yearly Analysis"/>
+      <sheetName val="Quarter analysis"/>
+      <sheetName val="Graphs Year"/>
+      <sheetName val="Graphs Quarter"/>
+      <sheetName val="Forecast -&gt;"/>
+      <sheetName val="Revenue"/>
+      <sheetName val="COGS &amp; OpEx"/>
+      <sheetName val="WC &amp; Investments"/>
+      <sheetName val="FCF &amp; Other"/>
+      <sheetName val="Valuation -&gt;"/>
+      <sheetName val="WACC"/>
+      <sheetName val="DCF"/>
+      <sheetName val="Multiples"/>
+      <sheetName val="AVG target price"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Reverse DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10">
+        <row r="5">
+          <cell r="C5">
+            <v>2021</v>
+          </cell>
+          <cell r="D5">
+            <v>2022</v>
+          </cell>
+          <cell r="E5">
+            <v>2023</v>
+          </cell>
+          <cell r="F5">
+            <v>2024</v>
+          </cell>
+          <cell r="G5">
+            <v>2025</v>
+          </cell>
+          <cell r="H5">
+            <v>2026</v>
+          </cell>
+          <cell r="I5">
+            <v>2027</v>
+          </cell>
+          <cell r="J5">
+            <v>2028</v>
+          </cell>
+          <cell r="K5">
+            <v>2029</v>
+          </cell>
+          <cell r="L5">
+            <v>2030</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="adi dumitras" id="{A0F62302-F8D3-B346-B5DF-839B413AE710}" userId="b24535bb88af1c42" providerId="Windows Live"/>
@@ -15389,11 +15518,11 @@
     <v>Powered by Refinitiv</v>
     <v>317.39999999999998</v>
     <v>201.5</v>
-    <v>1.0904</v>
+    <v>1.0931999999999999</v>
     <v>-0.9</v>
     <v>-2.846E-3</v>
-    <v>-0.21809999999999999</v>
-    <v>-6.9169999999999995E-4</v>
+    <v>-0.35</v>
+    <v>-1.1100000000000001E-3</v>
     <v>USD</v>
     <v>Apple Inc. designs, manufactures and markets smartphones, personal computers, tablets, wearables and accessories, and sells a variety of related services. Its product categories include iPhone, Mac, iPad, Wearables, Home and Accessories. Its services include advertising, AppleCare, cloud services, digital content, and payment services. The Company operates various platforms, including the App Store, that allow customers to discover and download applications and digital content, such as books, music, video, games and podcasts. It also offers digital content through subscription-based services, including Apple Arcade, Apple Fitness+, Apple Music, Apple News+, and Apple TV+. Its wearables include smartwatches, wireless headphones, and spatial computers. Its products include iPhone 16 Pro, iPhone 16, iPhone 15, iPhone 14, iPhone SE, MacBook Air, MacBook Pro, iMac, Mac mini, Mac Studio, Mac Pro, iPad Pro, iPad Air, AirPods, AirPods Pro, AirPods Max, Apple TV, Apple Vision Pro and others.</v>
     <v>166000</v>
@@ -15404,21 +15533,21 @@
     <v>316.91000000000003</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46213.888557071092</v>
+    <v>46213.99998719844</v>
     <v>0</v>
     <v>312.17</v>
     <v>4631218355200</v>
     <v>APPLE INC.</v>
     <v>APPLE INC.</v>
     <v>314.72000000000003</v>
-    <v>38.2958</v>
+    <v>38.405000000000001</v>
     <v>316.22000000000003</v>
     <v>315.32</v>
-    <v>315.1019</v>
+    <v>314.97000000000003</v>
     <v>14687360000</v>
     <v>AAPL</v>
     <v>APPLE INC. (XNAS:AAPL)</v>
-    <v>32478188</v>
+    <v>34132321</v>
     <v>64766433</v>
     <v>1977</v>
   </rv>
@@ -15443,17 +15572,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.3</v>
-    <v>-6.5659999999999998E-3</v>
+    <v>0.3</v>
+    <v>6.6090000000000003E-3</v>
     <v>US</v>
-    <v>45.81</v>
+    <v>45.71</v>
     <v>Index</v>
     <v>3</v>
-    <v>45.29</v>
+    <v>45.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.77</v>
+    <v>45.41</v>
+    <v>45.39</v>
     <v>45.69</v>
-    <v>45.39</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -15675,9 +15804,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -16248,18 +16377,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="232" t="s">
+      <c r="B2" s="233" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="233"/>
-      <c r="E2" s="232" t="s">
+      <c r="C2" s="234"/>
+      <c r="E2" s="233" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="233"/>
-      <c r="H2" s="232" t="s">
+      <c r="F2" s="234"/>
+      <c r="H2" s="233" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="233"/>
+      <c r="I2" s="234"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="182" t="s">
@@ -16282,7 +16411,7 @@
       </c>
       <c r="I3" s="208">
         <f ca="1">'AVG target price'!C5</f>
-        <v>117.94784406159961</v>
+        <v>117.28589507926682</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16306,7 +16435,7 @@
       </c>
       <c r="I4" s="208">
         <f ca="1">'AVG target price'!C6</f>
-        <v>194.55224664880012</v>
+        <v>194.19286803829158</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16339,7 +16468,7 @@
       </c>
       <c r="C6" s="205" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>315.1019</v>
+        <v>314.97000000000003</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>236</v>
@@ -16354,7 +16483,7 @@
       </c>
       <c r="I6" s="208">
         <f ca="1">'AVG target price'!C8</f>
-        <v>125.82838600438804</v>
+        <v>125.60033490377322</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16378,7 +16507,7 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>144.25397725028435</v>
+        <v>143.94163257692031</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -16387,7 +16516,7 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.21809999999999999</v>
+        <v>-0.35</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>264</v>
@@ -16402,7 +16531,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.5425156119171497</v>
+        <v>-0.54350617602143758</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16427,7 +16556,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-6.9169999999999995E-4</v>
+        <v>-1.1100000000000001E-3</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>292</v>
@@ -16436,6 +16565,13 @@
         <f ca="1">Statement!AC154</f>
         <v>1.6824243158637408E-2</v>
       </c>
+      <c r="H10" s="181" t="s">
+        <v>407</v>
+      </c>
+      <c r="I10" s="209">
+        <f>DDM!C26</f>
+        <v>13.26</v>
+      </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="182" t="s">
@@ -16475,7 +16611,7 @@
       </c>
       <c r="C13" s="206" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0904</v>
+        <v>1.0931999999999999</v>
       </c>
       <c r="E13" s="182" t="s">
         <v>101</v>
@@ -16520,10 +16656,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="234" t="s">
+      <c r="B17" s="235" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="234"/>
+      <c r="C17" s="235"/>
       <c r="E17" s="181" t="s">
         <v>295</v>
       </c>
@@ -16596,14 +16732,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="234" t="s">
+      <c r="B25" s="235" t="s">
         <v>104</v>
       </c>
-      <c r="C25" s="234"/>
-      <c r="E25" s="232" t="s">
+      <c r="C25" s="235"/>
+      <c r="E25" s="233" t="s">
         <v>342</v>
       </c>
-      <c r="F25" s="233"/>
+      <c r="F25" s="234"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="181" t="s">
@@ -16617,7 +16753,7 @@
       </c>
       <c r="F26" s="216" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.39</v>
+        <v>45.69</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16632,7 +16768,7 @@
       </c>
       <c r="F27" s="217">
         <f ca="1">F26/1000</f>
-        <v>4.539E-2</v>
+        <v>4.5689999999999995E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16645,22 +16781,22 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="181" t="s">
-        <v>348</v>
+        <v>406</v>
       </c>
       <c r="C29" s="218">
         <v>0.1</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="235" t="s">
+      <c r="B33" s="232" t="s">
         <v>337</v>
       </c>
-      <c r="C33" s="235"/>
-      <c r="D33" s="235"/>
-      <c r="E33" s="235"/>
-      <c r="F33" s="235"/>
-      <c r="G33" s="235"/>
-      <c r="H33" s="235"/>
+      <c r="C33" s="232"/>
+      <c r="D33" s="232"/>
+      <c r="E33" s="232"/>
+      <c r="F33" s="232"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="232"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -16673,24 +16809,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="235"/>
-      <c r="C39" s="235"/>
-      <c r="D39" s="235"/>
-      <c r="E39" s="235"/>
-      <c r="F39" s="235"/>
-      <c r="G39" s="235"/>
-      <c r="H39" s="235"/>
+      <c r="B39" s="232"/>
+      <c r="C39" s="232"/>
+      <c r="D39" s="232"/>
+      <c r="E39" s="232"/>
+      <c r="F39" s="232"/>
+      <c r="G39" s="232"/>
+      <c r="H39" s="232"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="235" t="s">
+      <c r="B42" s="232" t="s">
         <v>340</v>
       </c>
-      <c r="C42" s="235"/>
-      <c r="D42" s="235"/>
-      <c r="E42" s="235"/>
-      <c r="F42" s="235"/>
-      <c r="G42" s="235"/>
-      <c r="H42" s="235"/>
+      <c r="C42" s="232"/>
+      <c r="D42" s="232"/>
+      <c r="E42" s="232"/>
+      <c r="F42" s="232"/>
+      <c r="G42" s="232"/>
+      <c r="H42" s="232"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -16705,24 +16841,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="235"/>
-      <c r="C49" s="235"/>
-      <c r="D49" s="235"/>
-      <c r="E49" s="235"/>
-      <c r="F49" s="235"/>
-      <c r="G49" s="235"/>
-      <c r="H49" s="235"/>
+      <c r="B49" s="232"/>
+      <c r="C49" s="232"/>
+      <c r="D49" s="232"/>
+      <c r="E49" s="232"/>
+      <c r="F49" s="232"/>
+      <c r="G49" s="232"/>
+      <c r="H49" s="232"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="235" t="s">
+      <c r="B52" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="C52" s="235"/>
-      <c r="D52" s="235"/>
-      <c r="E52" s="235"/>
-      <c r="F52" s="235"/>
-      <c r="G52" s="235"/>
-      <c r="H52" s="235"/>
+      <c r="C52" s="232"/>
+      <c r="D52" s="232"/>
+      <c r="E52" s="232"/>
+      <c r="F52" s="232"/>
+      <c r="G52" s="232"/>
+      <c r="H52" s="232"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -16737,28 +16873,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="235"/>
-      <c r="C59" s="235"/>
-      <c r="D59" s="235"/>
-      <c r="E59" s="235"/>
-      <c r="F59" s="235"/>
-      <c r="G59" s="235"/>
-      <c r="H59" s="235"/>
+      <c r="B59" s="232"/>
+      <c r="C59" s="232"/>
+      <c r="D59" s="232"/>
+      <c r="E59" s="232"/>
+      <c r="F59" s="232"/>
+      <c r="G59" s="232"/>
+      <c r="H59" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -16828,36 +16964,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="235" t="s">
+      <c r="S2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235"/>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
-      <c r="AA2" s="235" t="s">
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
+      <c r="AA2" s="232" t="s">
         <v>111</v>
       </c>
-      <c r="AB2" s="235"/>
-      <c r="AC2" s="235"/>
+      <c r="AB2" s="232"/>
+      <c r="AC2" s="232"/>
       <c r="AE2" s="85" t="s">
         <v>112</v>
       </c>
@@ -18228,35 +18364,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
-      <c r="P2" s="235" t="s">
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
+      <c r="P2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="Q2" s="235"/>
-      <c r="R2" s="235"/>
-      <c r="S2" s="235"/>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235" t="s">
+      <c r="Q2" s="232"/>
+      <c r="R2" s="232"/>
+      <c r="S2" s="232"/>
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232" t="s">
         <v>111</v>
       </c>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
       <c r="AB2" s="85" t="s">
         <v>112</v>
       </c>
@@ -19487,20 +19623,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -20893,12 +21029,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -20906,6 +21036,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20943,20 +21079,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="S2" s="246"/>
       <c r="T2" s="246"/>
       <c r="U2" s="246"/>
@@ -21965,16 +22101,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22037,10 +22173,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="232"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22084,7 +22220,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.539E-2</v>
+        <v>4.5689999999999995E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22093,7 +22229,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.0904</v>
+        <v>1.0931999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22125,10 +22261,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="232" t="s">
         <v>170</v>
       </c>
-      <c r="C15" s="235"/>
+      <c r="C15" s="232"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22163,7 +22299,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.4458E-2</v>
+        <v>9.4883999999999996E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22172,7 +22308,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.3424773517315624E-2</v>
+        <v>9.3843148229620532E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22217,20 +22353,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -22423,7 +22559,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>1909649.2314645126</v>
+        <v>1898829.6907627422</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22477,23 +22613,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>96350.45327303739</v>
+        <v>96313.601012058483</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>93072.765306374349</v>
+        <v>93001.581709908671</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>90220.297978009301</v>
+        <v>90116.814797603191</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>87245.398338495695</v>
+        <v>87111.995913326784</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>87953.170485233975</v>
+        <v>87785.096824080858</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22512,14 +22648,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>1221825.1360868276</v>
+        <v>1212581.0032114149</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="235" t="s">
+      <c r="B13" s="232" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="235"/>
+      <c r="C13" s="232"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22535,14 +22671,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.3424773517315624E-2</v>
+        <v>9.3843148229620532E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="235" t="s">
+      <c r="B18" s="232" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="235"/>
+      <c r="C18" s="232"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22550,7 +22686,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>454842.08538115071</v>
+        <v>454329.090256978</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -22559,7 +22695,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>1221825.1360868276</v>
+        <v>1212581.0032114149</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -22568,7 +22704,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>1676667.2214679783</v>
+        <v>1666910.093468393</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -22595,7 +22731,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>1738551.2214679783</v>
+        <v>1728794.093468393</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -22613,7 +22749,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>117.94784406159961</v>
+        <v>117.28589507926682</v>
       </c>
     </row>
   </sheetData>
@@ -22656,20 +22792,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -23601,10 +23737,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="232" t="s">
         <v>202</v>
       </c>
-      <c r="C37" s="235"/>
+      <c r="C37" s="232"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -23622,7 +23758,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.3424773517315624E-2</v>
+        <v>9.3843148229620532E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -23648,7 +23784,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>2805816.1156033138</v>
+        <v>2800518.8748844177</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -23675,7 +23811,7 @@
       </c>
       <c r="C45" s="64">
         <f ca="1">C42+C43-C44</f>
-        <v>2867700.1156033138</v>
+        <v>2862402.8748844177</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23693,14 +23829,14 @@
       </c>
       <c r="C47" s="142">
         <f ca="1">C45/C46</f>
-        <v>194.55224664880012</v>
+        <v>194.19286803829158</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="235" t="s">
+      <c r="B49" s="232" t="s">
         <v>207</v>
       </c>
-      <c r="C49" s="235"/>
+      <c r="C49" s="232"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -23716,7 +23852,7 @@
         <v>348</v>
       </c>
       <c r="C51" s="135">
-        <f>Overview!C29</f>
+        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
         <v>0.1</v>
       </c>
     </row>
@@ -23756,10 +23892,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="235" t="s">
+      <c r="B57" s="232" t="s">
         <v>321</v>
       </c>
-      <c r="C57" s="235"/>
+      <c r="C57" s="232"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -23776,7 +23912,7 @@
       </c>
       <c r="C59" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.3424773517315624E-2</v>
+        <v>9.3843148229620532E-2</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -23802,7 +23938,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>1792826.4097046796</v>
+        <v>1789464.9364816172</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -23829,7 +23965,7 @@
       </c>
       <c r="C65" s="64">
         <f ca="1">C62+C63-C64</f>
-        <v>1854710.4097046796</v>
+        <v>1851348.9364816172</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23847,7 +23983,7 @@
       </c>
       <c r="C67" s="142">
         <f ca="1">C65/C66</f>
-        <v>125.82838600438804</v>
+        <v>125.60033490377322</v>
       </c>
     </row>
   </sheetData>
@@ -23899,10 +24035,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>212</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="232"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23911,7 +24047,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>117.94784406159961</v>
+        <v>117.28589507926682</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -23920,7 +24056,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C47</f>
-        <v>194.55224664880012</v>
+        <v>194.19286803829158</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -23938,7 +24074,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C67</f>
-        <v>125.82838600438804</v>
+        <v>125.60033490377322</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -23947,7 +24083,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>144.25397725028435</v>
+        <v>143.94163257692031</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23965,7 +24101,7 @@
       </c>
       <c r="C11" s="151">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.5425156119171497</v>
+        <v>-0.54350617602143758</v>
       </c>
     </row>
   </sheetData>
@@ -23998,6 +24134,477 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{272A8DA5-299F-1343-8F22-D98E787B4AC7}">
+  <dimension ref="A1:N26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2" style="83" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="1"/>
+    <col min="4" max="4" width="10.83203125" style="1" customWidth="1"/>
+    <col min="5" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="10.83203125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="10.83203125" style="1"/>
+    <col min="13" max="14" width="9.5" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="83" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4"/>
+      <c r="B1" s="82" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="4"/>
+      <c r="C2" s="232" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
+        <v>111</v>
+      </c>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
+    </row>
+    <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="86"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="241" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B5" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="12">
+        <f>[2]Revenue!C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D5" s="12">
+        <f>[2]Revenue!D5</f>
+        <v>2022</v>
+      </c>
+      <c r="E5" s="12">
+        <f>[2]Revenue!E5</f>
+        <v>2023</v>
+      </c>
+      <c r="F5" s="12">
+        <f>[2]Revenue!F5</f>
+        <v>2024</v>
+      </c>
+      <c r="G5" s="12">
+        <f>[2]Revenue!G5</f>
+        <v>2025</v>
+      </c>
+      <c r="H5" s="12">
+        <f>[2]Revenue!H5</f>
+        <v>2026</v>
+      </c>
+      <c r="I5" s="12">
+        <f>[2]Revenue!I5</f>
+        <v>2027</v>
+      </c>
+      <c r="J5" s="12">
+        <f>[2]Revenue!J5</f>
+        <v>2028</v>
+      </c>
+      <c r="K5" s="12">
+        <f>[2]Revenue!K5</f>
+        <v>2029</v>
+      </c>
+      <c r="L5" s="12">
+        <f>[2]Revenue!L5</f>
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B6" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="C6" s="250">
+        <f>Statement!M25</f>
+        <v>5.61</v>
+      </c>
+      <c r="D6" s="250">
+        <f>Statement!N25</f>
+        <v>6.11</v>
+      </c>
+      <c r="E6" s="250">
+        <f>Statement!O25</f>
+        <v>6.13</v>
+      </c>
+      <c r="F6" s="250">
+        <f>Statement!P25</f>
+        <v>6.08</v>
+      </c>
+      <c r="G6" s="251">
+        <f>Statement!Q25</f>
+        <v>7.46</v>
+      </c>
+      <c r="H6" s="137"/>
+      <c r="I6" s="137"/>
+      <c r="J6" s="137"/>
+      <c r="K6" s="137"/>
+      <c r="L6" s="137"/>
+      <c r="N6" s="91"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B7" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="C7" s="250">
+        <f>Statement!M81</f>
+        <v>0.85</v>
+      </c>
+      <c r="D7" s="250">
+        <f>Statement!N81</f>
+        <v>0.9</v>
+      </c>
+      <c r="E7" s="250">
+        <f>Statement!O81</f>
+        <v>0.94</v>
+      </c>
+      <c r="F7" s="250">
+        <f>Statement!P81</f>
+        <v>0.98</v>
+      </c>
+      <c r="G7" s="251">
+        <f>Statement!Q81</f>
+        <v>1.02</v>
+      </c>
+      <c r="H7" s="137"/>
+      <c r="I7" s="137"/>
+      <c r="J7" s="137"/>
+      <c r="K7" s="137"/>
+      <c r="L7" s="137"/>
+      <c r="N7" s="91"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="91"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C9" s="241" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" s="241"/>
+      <c r="E9" s="241"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="241"/>
+      <c r="N9" s="91"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="12">
+        <f t="shared" ref="C10:L10" si="0">C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D10" s="12">
+        <f t="shared" si="0"/>
+        <v>2022</v>
+      </c>
+      <c r="E10" s="12">
+        <f t="shared" si="0"/>
+        <v>2023</v>
+      </c>
+      <c r="F10" s="12">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
+      <c r="G10" s="12">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="H10" s="12">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="I10" s="12">
+        <f t="shared" si="0"/>
+        <v>2027</v>
+      </c>
+      <c r="J10" s="12">
+        <f t="shared" si="0"/>
+        <v>2028</v>
+      </c>
+      <c r="K10" s="12">
+        <f t="shared" si="0"/>
+        <v>2029</v>
+      </c>
+      <c r="L10" s="12">
+        <f t="shared" si="0"/>
+        <v>2030</v>
+      </c>
+      <c r="N10" s="91"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C11" s="137"/>
+      <c r="D11" s="95">
+        <f>(D6-C6)/C6</f>
+        <v>8.9126559714795009E-2</v>
+      </c>
+      <c r="E11" s="95">
+        <f>(E6-D6)/D6</f>
+        <v>3.2733224222585224E-3</v>
+      </c>
+      <c r="F11" s="95">
+        <f>(F6-E6)/E6</f>
+        <v>-8.1566068515497268E-3</v>
+      </c>
+      <c r="G11" s="96">
+        <f>(G6-F6)/F6</f>
+        <v>0.2269736842105263</v>
+      </c>
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="137"/>
+      <c r="K11" s="137"/>
+      <c r="L11" s="137"/>
+      <c r="N11" s="91"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="137"/>
+      <c r="D12" s="95">
+        <f>IF(C7=0,
+IF(D7=0,0,IF(D7&gt;0,1,-1)),
+(D7-C7)/ABS(C7)
+)</f>
+        <v>5.8823529411764761E-2</v>
+      </c>
+      <c r="E12" s="95">
+        <f>IF(D7=0,
+IF(E7=0,0,IF(E7&gt;0,1,-1)),
+(E7-D7)/ABS(D7)
+)</f>
+        <v>4.4444444444444363E-2</v>
+      </c>
+      <c r="F12" s="95">
+        <f>IF(E7=0,
+IF(F7=0,0,IF(F7&gt;0,1,-1)),
+(F7-E7)/ABS(E7)
+)</f>
+        <v>4.2553191489361743E-2</v>
+      </c>
+      <c r="G12" s="96">
+        <f>IF(F7=0,
+IF(G7=0,0,IF(G7&gt;0,1,-1)),
+(G7-F7)/ABS(F7)
+)</f>
+        <v>4.0816326530612283E-2</v>
+      </c>
+      <c r="H12" s="137"/>
+      <c r="I12" s="137"/>
+      <c r="J12" s="137"/>
+      <c r="K12" s="137"/>
+      <c r="L12" s="137"/>
+      <c r="N12" s="91"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="91"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C14" s="241" t="s">
+        <v>410</v>
+      </c>
+      <c r="D14" s="241"/>
+      <c r="E14" s="241"/>
+      <c r="F14" s="241"/>
+      <c r="G14" s="241"/>
+      <c r="H14" s="241"/>
+      <c r="I14" s="241"/>
+      <c r="J14" s="241"/>
+      <c r="K14" s="241"/>
+      <c r="L14" s="241"/>
+      <c r="N14" s="91"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B15" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="C15" s="12">
+        <f>C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D15" s="12">
+        <f t="shared" ref="D15:L15" si="1">D5</f>
+        <v>2022</v>
+      </c>
+      <c r="E15" s="12">
+        <f t="shared" si="1"/>
+        <v>2023</v>
+      </c>
+      <c r="F15" s="12">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="G15" s="12">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="H15" s="12">
+        <f t="shared" si="1"/>
+        <v>2026</v>
+      </c>
+      <c r="I15" s="12">
+        <f t="shared" si="1"/>
+        <v>2027</v>
+      </c>
+      <c r="J15" s="12">
+        <f t="shared" si="1"/>
+        <v>2028</v>
+      </c>
+      <c r="K15" s="12">
+        <f t="shared" si="1"/>
+        <v>2029</v>
+      </c>
+      <c r="L15" s="12">
+        <f t="shared" si="1"/>
+        <v>2030</v>
+      </c>
+      <c r="N15" s="91"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C16" s="95">
+        <f>C7/C6</f>
+        <v>0.15151515151515149</v>
+      </c>
+      <c r="D16" s="95">
+        <f t="shared" ref="D16:G16" si="2">D7/D6</f>
+        <v>0.14729950900163666</v>
+      </c>
+      <c r="E16" s="95">
+        <f t="shared" si="2"/>
+        <v>0.15334420880913541</v>
+      </c>
+      <c r="F16" s="95">
+        <f t="shared" si="2"/>
+        <v>0.16118421052631579</v>
+      </c>
+      <c r="G16" s="96">
+        <f t="shared" si="2"/>
+        <v>0.13672922252010725</v>
+      </c>
+      <c r="H16" s="137"/>
+      <c r="I16" s="137"/>
+      <c r="J16" s="137"/>
+      <c r="K16" s="137"/>
+      <c r="L16" s="137"/>
+      <c r="N16" s="91"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="91"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="91"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N19" s="91"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B20" s="232" t="s">
+        <v>412</v>
+      </c>
+      <c r="C20" s="232"/>
+      <c r="N20" s="91"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C21" s="252">
+        <f>G7</f>
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C22" s="253">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B23" s="39" t="s">
+        <v>415</v>
+      </c>
+      <c r="C23" s="254">
+        <f>C21*(1+C22)</f>
+        <v>1.0608</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C24" s="135">
+        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B25" s="39" t="s">
+        <v>416</v>
+      </c>
+      <c r="C25" s="253">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B26" s="141" t="s">
+        <v>206</v>
+      </c>
+      <c r="C26" s="142">
+        <f>C23/(C24-C25)</f>
+        <v>13.26</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="B20:C20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0116CE1A-CCEC-514B-9208-A0DCC7740441}">
   <dimension ref="A1:AB49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -24030,20 +24637,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -24218,7 +24825,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>5204799.4445427703</v>
+        <v>5175310.5004440695</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -24272,23 +24879,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>144934.17187130061</v>
+        <v>144878.73723923485</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>164362.81440953349</v>
+        <v>164237.1069996765</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>186395.89554223133</v>
+        <v>186182.09841988026</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>211382.54415881552</v>
+        <v>211059.33004590889</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>239718.69039857667</v>
+        <v>239260.60119360726</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -24307,7 +24914,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>3330116.6962249489</v>
+        <v>3304921.567788545</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24332,7 +24939,7 @@
       </c>
       <c r="C16" s="153">
         <f ca="1">C36</f>
-        <v>295.41736315145408</v>
+        <v>293.62180443159616</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24371,7 +24978,7 @@
       </c>
       <c r="C21" s="219">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.3424773517315624E-2</v>
+        <v>9.3843148229620532E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24432,7 +25039,7 @@
       </c>
       <c r="C29" s="158">
         <f ca="1">SUM(H10:L10)</f>
-        <v>946794.11638045753</v>
+        <v>945617.87389830779</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -24441,7 +25048,7 @@
       </c>
       <c r="C30" s="158">
         <f ca="1">L11</f>
-        <v>3330116.6962249489</v>
+        <v>3304921.567788545</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -24450,7 +25057,7 @@
       </c>
       <c r="C31" s="161">
         <f ca="1">C29+C30</f>
-        <v>4276910.8126054062</v>
+        <v>4250539.4416868528</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -24477,7 +25084,7 @@
       </c>
       <c r="C34" s="161">
         <f ca="1">C31+C32-C33</f>
-        <v>4338794.8126054062</v>
+        <v>4312423.4416868528</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -24495,7 +25102,7 @@
       </c>
       <c r="C36" s="164">
         <f ca="1">C34/C35</f>
-        <v>295.41736315145408</v>
+        <v>293.62180443159616</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -24942,17 +25549,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -35390,15 +35997,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="235"/>
-      <c r="E4" s="235" t="s">
+      <c r="C4" s="232"/>
+      <c r="E4" s="232" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
+      <c r="F4" s="232"/>
+      <c r="G4" s="232"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35535,14 +36142,14 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="235"/>
-      <c r="E15" s="235" t="s">
+      <c r="C15" s="232"/>
+      <c r="E15" s="232" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="235"/>
+      <c r="F15" s="232"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35593,14 +36200,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="235" t="s">
+      <c r="B21" s="232" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="235"/>
-      <c r="E21" s="235" t="s">
+      <c r="C21" s="232"/>
+      <c r="E21" s="232" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="235"/>
+      <c r="F21" s="232"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35669,14 +36276,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="235" t="s">
+      <c r="B29" s="232" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="235"/>
-      <c r="E29" s="235" t="s">
+      <c r="C29" s="232"/>
+      <c r="E29" s="232" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="235"/>
+      <c r="F29" s="232"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35752,14 +36359,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="232" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="235"/>
-      <c r="E37" s="235" t="s">
+      <c r="C37" s="232"/>
+      <c r="E37" s="232" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="235"/>
+      <c r="F37" s="232"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35828,14 +36435,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="235" t="s">
+      <c r="B45" s="232" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="235"/>
-      <c r="E45" s="235" t="s">
+      <c r="C45" s="232"/>
+      <c r="E45" s="232" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="235"/>
+      <c r="F45" s="232"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35872,14 +36479,14 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="235" t="s">
+      <c r="B51" s="232" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="235"/>
-      <c r="E51" s="235" t="s">
+      <c r="C51" s="232"/>
+      <c r="E51" s="232" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="235"/>
+      <c r="F51" s="232"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -38067,14 +38674,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="236" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="239"/>
-      <c r="F3" s="240" t="s">
+      <c r="D3" s="237"/>
+      <c r="F3" s="238" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="239"/>
+      <c r="G3" s="237"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38141,19 +38748,19 @@
       <c r="B7" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="236">
+      <c r="C7" s="239">
         <f>Statement!AA88</f>
         <v>-0.22657836890286318</v>
       </c>
-      <c r="D7" s="237"/>
-      <c r="F7" s="236">
+      <c r="D7" s="240"/>
+      <c r="F7" s="239">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.16595182415922985</v>
       </c>
-      <c r="G7" s="237"/>
+      <c r="G7" s="240"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="204" t="s">
@@ -38180,19 +38787,19 @@
       <c r="B9" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="236">
+      <c r="C9" s="239">
         <f>Statement!AA89</f>
         <v>-0.24316672257631666</v>
       </c>
-      <c r="D9" s="237"/>
-      <c r="F9" s="236">
+      <c r="D9" s="240"/>
+      <c r="F9" s="239">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.11706805038421929</v>
       </c>
-      <c r="G9" s="237"/>
+      <c r="G9" s="240"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="204" t="s">
@@ -38219,19 +38826,19 @@
       <c r="B11" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="236">
+      <c r="C11" s="239">
         <f>Statement!AA90</f>
         <v>-0.2087215264838006</v>
       </c>
-      <c r="D11" s="237"/>
-      <c r="F11" s="236">
+      <c r="D11" s="240"/>
+      <c r="F11" s="239">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.22096418302984375</v>
       </c>
-      <c r="G11" s="237"/>
+      <c r="G11" s="240"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="204" t="s">
@@ -38258,19 +38865,19 @@
       <c r="B13" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="236">
+      <c r="C13" s="239">
         <f>Statement!AA93</f>
         <v>2.8129930899396048E-2</v>
       </c>
-      <c r="D13" s="237"/>
-      <c r="F13" s="236">
+      <c r="D13" s="240"/>
+      <c r="F13" s="239">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.23681110092944102</v>
       </c>
-      <c r="G13" s="237"/>
+      <c r="G13" s="240"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="204" t="s">
@@ -38297,19 +38904,19 @@
       <c r="B15" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="236">
+      <c r="C15" s="239">
         <f>Statement!AA94</f>
         <v>-0.29432470699284197</v>
       </c>
-      <c r="D15" s="237"/>
-      <c r="F15" s="236">
+      <c r="D15" s="240"/>
+      <c r="F15" s="239">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.21278177701172732</v>
       </c>
-      <c r="G15" s="237"/>
+      <c r="G15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="204" t="s">
@@ -38336,19 +38943,19 @@
       <c r="B17" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="236">
+      <c r="C17" s="239">
         <f>Statement!AA96</f>
         <v>-0.29738461173005204</v>
       </c>
-      <c r="D17" s="237"/>
-      <c r="F17" s="236">
+      <c r="D17" s="240"/>
+      <c r="F17" s="239">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.19362389023405974</v>
       </c>
-      <c r="G17" s="237"/>
+      <c r="G17" s="240"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="204" t="s">
@@ -38375,22 +38982,22 @@
       <c r="B19" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="236">
+      <c r="C19" s="239">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-5.6718433490884537E-3</v>
       </c>
-      <c r="D19" s="237"/>
-      <c r="F19" s="236">
+      <c r="D19" s="240"/>
+      <c r="F19" s="239">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-2.1918172157279491E-2</v>
       </c>
-      <c r="G19" s="237"/>
+      <c r="G19" s="240"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="204" t="s">
@@ -38417,22 +39024,22 @@
       <c r="B21" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="236">
+      <c r="C21" s="239">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.29225352112676062</v>
       </c>
-      <c r="D21" s="237"/>
-      <c r="F21" s="236">
+      <c r="D21" s="240"/>
+      <c r="F21" s="239">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.21818181818181812</v>
       </c>
-      <c r="G21" s="237"/>
+      <c r="G21" s="240"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38480,22 +39087,22 @@
       <c r="B25" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="236">
+      <c r="C25" s="239">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.22956141399989749</v>
       </c>
-      <c r="D25" s="237"/>
-      <c r="F25" s="236">
+      <c r="D25" s="240"/>
+      <c r="F25" s="239">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.11851668113605358</v>
       </c>
-      <c r="G25" s="237"/>
+      <c r="G25" s="240"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -38522,22 +39129,22 @@
       <c r="B27" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="236">
+      <c r="C27" s="239">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-0.26453625543962672</v>
       </c>
-      <c r="D27" s="237"/>
-      <c r="F27" s="236">
+      <c r="D27" s="240"/>
+      <c r="F27" s="239">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.14725607262615523</v>
       </c>
-      <c r="G27" s="237"/>
+      <c r="G27" s="240"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -38564,22 +39171,22 @@
       <c r="B29" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="236">
+      <c r="C29" s="239">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-0.19701480843061975</v>
       </c>
-      <c r="D29" s="237"/>
-      <c r="F29" s="236">
+      <c r="D29" s="240"/>
+      <c r="F29" s="239">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.28090238720159982</v>
       </c>
-      <c r="G29" s="237"/>
+      <c r="G29" s="240"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -38606,22 +39213,22 @@
       <c r="B31" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C31" s="236">
+      <c r="C31" s="239">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-0.10751088919579305</v>
       </c>
-      <c r="D31" s="237"/>
-      <c r="F31" s="236">
+      <c r="D31" s="240"/>
+      <c r="F31" s="239">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.15113729788983282</v>
       </c>
-      <c r="G31" s="237"/>
+      <c r="G31" s="240"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -38648,22 +39255,22 @@
       <c r="B33" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C33" s="236">
+      <c r="C33" s="239">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-0.2474056992258277</v>
       </c>
-      <c r="D33" s="237"/>
-      <c r="F33" s="236">
+      <c r="D33" s="240"/>
+      <c r="F33" s="239">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.25349794238683127</v>
       </c>
-      <c r="G33" s="237"/>
+      <c r="G33" s="240"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="227" t="s">
@@ -38690,22 +39297,22 @@
       <c r="B36" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C36" s="236">
+      <c r="C36" s="239">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>-0.33159764979066247</v>
       </c>
-      <c r="D36" s="237"/>
-      <c r="F36" s="236">
+      <c r="D36" s="240"/>
+      <c r="F36" s="239">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>0.21675455263551163</v>
       </c>
-      <c r="G36" s="237"/>
+      <c r="G36" s="240"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="227" t="s">
@@ -38732,22 +39339,22 @@
       <c r="B38" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C38" s="236">
+      <c r="C38" s="239">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>1.550202718817076E-3</v>
       </c>
-      <c r="D38" s="237"/>
-      <c r="F38" s="236">
+      <c r="D38" s="240"/>
+      <c r="F38" s="239">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>5.661089445213234E-2</v>
       </c>
-      <c r="G38" s="237"/>
+      <c r="G38" s="240"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B39" s="227" t="s">
@@ -38774,22 +39381,22 @@
       <c r="B40" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C40" s="236">
+      <c r="C40" s="239">
         <f>IF(C39=0,
 IF(D39=0,0,IF(D39&gt;0,1,-1)),
 (D39-C39)/ABS(C39)
 )</f>
         <v>-0.19557882489819661</v>
       </c>
-      <c r="D40" s="237"/>
-      <c r="F40" s="236">
+      <c r="D40" s="240"/>
+      <c r="F40" s="239">
         <f>IF(F39=0,
 IF(G39=0,0,IF(G39&gt;0,1,-1)),
 (G39-F39)/ABS(F39)
 )</f>
         <v>7.9975007810059354E-2</v>
       </c>
-      <c r="G40" s="237"/>
+      <c r="G40" s="240"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B41" s="227" t="s">
@@ -38816,22 +39423,22 @@
       <c r="B42" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C42" s="236">
+      <c r="C42" s="239">
         <f>IF(C41=0,
 IF(D41=0,0,IF(D41&gt;0,1,-1)),
 (D41-C41)/ABS(C41)
 )</f>
         <v>-0.31253806664926476</v>
       </c>
-      <c r="D42" s="237"/>
-      <c r="F42" s="236">
+      <c r="D42" s="240"/>
+      <c r="F42" s="239">
         <f>IF(F41=0,
 IF(G41=0,0,IF(G41&gt;0,1,-1)),
 (G41-F41)/ABS(F41)
 )</f>
         <v>5.0385535761765486E-2</v>
       </c>
-      <c r="G42" s="237"/>
+      <c r="G42" s="240"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B43" s="227" t="s">
@@ -38858,55 +39465,25 @@
       <c r="B44" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C44" s="236">
+      <c r="C44" s="239">
         <f>IF(C43=0,
 IF(D43=0,0,IF(D43&gt;0,1,-1)),
 (D43-C43)/ABS(C43)
 )</f>
         <v>3.2086096025055806E-2</v>
       </c>
-      <c r="D44" s="237"/>
-      <c r="F44" s="236">
+      <c r="D44" s="240"/>
+      <c r="F44" s="239">
         <f>IF(F43=0,
 IF(G43=0,0,IF(G43&gt;0,1,-1)),
 (G43-F43)/ABS(F43)
 )</f>
         <v>0.16254456746106211</v>
       </c>
-      <c r="G44" s="237"/>
+      <c r="G44" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F36:G36"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="F44:G44"/>
     <mergeCell ref="C38:D38"/>
@@ -38915,6 +39492,36 @@
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="F42:G42"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/AAPL.xlsx
+++ b/AAPL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B3157A-2698-C74D-BA44-79D191A8B7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD271FD9-6301-4141-837F-61D5CC4F4947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2322,9 +2322,11 @@
     <xf numFmtId="10" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="23" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2334,6 +2336,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2341,12 +2352,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2376,11 +2381,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15516,13 +15516,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>317.39999999999998</v>
+    <v>344.56990000000002</v>
     <v>201.5</v>
-    <v>1.0931999999999999</v>
-    <v>-0.9</v>
-    <v>-2.846E-3</v>
-    <v>-0.35</v>
-    <v>-1.1100000000000001E-3</v>
+    <v>1.0406</v>
+    <v>-24.52</v>
+    <v>-7.3539000000000007E-2</v>
+    <v>-2.23</v>
+    <v>-7.2189999999999997E-3</v>
     <v>USD</v>
     <v>Apple Inc. designs, manufactures and markets smartphones, personal computers, tablets, wearables and accessories, and sells a variety of related services. Its product categories include iPhone, Mac, iPad, Wearables, Home and Accessories. Its services include advertising, AppleCare, cloud services, digital content, and payment services. The Company operates various platforms, including the App Store, that allow customers to discover and download applications and digital content, such as books, music, video, games and podcasts. It also offers digital content through subscription-based services, including Apple Arcade, Apple Fitness+, Apple Music, Apple News+, and Apple TV+. Its wearables include smartwatches, wireless headphones, and spatial computers. Its products include iPhone 16 Pro, iPhone 16, iPhone 15, iPhone 14, iPhone SE, MacBook Air, MacBook Pro, iMac, Mac mini, Mac Studio, Mac Pro, iPad Pro, iPad Air, AirPods, AirPods Pro, AirPods Max, Apple TV, Apple Vision Pro and others.</v>
     <v>166000</v>
@@ -15530,25 +15530,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Apple Park Way, CUPERTINO, CA, 95014 US</v>
-    <v>316.91000000000003</v>
+    <v>310.69</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46213.99998719844</v>
+    <v>46234.920069594533</v>
     <v>0</v>
-    <v>312.17</v>
-    <v>4631218355200</v>
+    <v>300</v>
+    <v>4537072377600</v>
     <v>APPLE INC.</v>
     <v>APPLE INC.</v>
-    <v>314.72000000000003</v>
-    <v>38.405000000000001</v>
-    <v>316.22000000000003</v>
-    <v>315.32</v>
-    <v>314.97000000000003</v>
+    <v>304.81</v>
+    <v>35.545299999999997</v>
+    <v>333.43</v>
+    <v>308.91000000000003</v>
+    <v>306.68</v>
     <v>14687360000</v>
     <v>AAPL</v>
     <v>APPLE INC. (XNAS:AAPL)</v>
-    <v>34132321</v>
-    <v>64766433</v>
+    <v>132261193</v>
+    <v>62679055</v>
     <v>1977</v>
   </rv>
   <rv s="2">
@@ -15570,19 +15570,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>46.87</v>
+    <v>47.14</v>
     <v>39.47</v>
-    <v>0.3</v>
-    <v>6.6090000000000003E-3</v>
+    <v>0.41</v>
+    <v>8.8710000000000004E-3</v>
     <v>US</v>
-    <v>45.71</v>
+    <v>46.86</v>
     <v>Index</v>
     <v>3</v>
-    <v>45.39</v>
+    <v>46.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.41</v>
-    <v>45.39</v>
-    <v>45.69</v>
+    <v>46.69</v>
+    <v>46.22</v>
+    <v>46.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -15804,9 +15804,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -16377,18 +16377,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="233" t="s">
+      <c r="B2" s="237" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="234"/>
-      <c r="E2" s="233" t="s">
+      <c r="C2" s="238"/>
+      <c r="E2" s="237" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="234"/>
-      <c r="H2" s="233" t="s">
+      <c r="F2" s="238"/>
+      <c r="H2" s="237" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="234"/>
+      <c r="I2" s="238"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="182" t="s">
@@ -16403,7 +16403,7 @@
       </c>
       <c r="F3" s="184">
         <f ca="1">Statement!AC143</f>
-        <v>4647816.8</v>
+        <v>4553333.4000000004</v>
       </c>
       <c r="H3" s="182" t="str">
         <f>'AVG target price'!B5</f>
@@ -16411,7 +16411,7 @@
       </c>
       <c r="I3" s="208">
         <f ca="1">'AVG target price'!C5</f>
-        <v>117.28589507926682</v>
+        <v>119.56729975955574</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="F4" s="185">
         <f ca="1">Statement!AC144</f>
-        <v>4585932.7999999998</v>
+        <v>4491449.4000000004</v>
       </c>
       <c r="H4" s="182" t="str">
         <f>'AVG target price'!B6</f>
@@ -16435,7 +16435,7 @@
       </c>
       <c r="I4" s="208">
         <f ca="1">'AVG target price'!C6</f>
-        <v>194.19286803829158</v>
+        <v>195.41784104778867</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16444,7 +16444,7 @@
       </c>
       <c r="C5" s="205" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>315.32</v>
+        <v>308.91000000000003</v>
       </c>
       <c r="E5" s="182" t="s">
         <v>242</v>
@@ -16468,14 +16468,14 @@
       </c>
       <c r="C6" s="205" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>314.97000000000003</v>
+        <v>306.68</v>
       </c>
       <c r="E6" s="182" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="187">
         <f ca="1">Statement!AC140</f>
-        <v>38.128174123337367</v>
+        <v>37.353083434099162</v>
       </c>
       <c r="H6" s="182" t="str">
         <f>'AVG target price'!B8</f>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="I6" s="208">
         <f ca="1">'AVG target price'!C8</f>
-        <v>125.60033490377322</v>
+        <v>126.37766676179324</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16492,14 +16492,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.9</v>
+        <v>-24.52</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>198</v>
       </c>
       <c r="F7" s="188">
         <f ca="1">Statement!AC141</f>
-        <v>10.363242321272722</v>
+        <v>10.152572578537221</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -16507,7 +16507,7 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>143.94163257692031</v>
+        <v>145.01255996387184</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -16516,14 +16516,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.35</v>
+        <v>-2.23</v>
       </c>
       <c r="E8" s="182" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="189">
         <f ca="1">Statement!AC151</f>
-        <v>2.4893623173787745E-2</v>
+        <v>2.5410175323423493E-2</v>
       </c>
       <c r="H8" s="181" t="str">
         <f>'AVG target price'!B11</f>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.54350617602143758</v>
+        <v>-0.53056696136780346</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16540,14 +16540,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-2.846E-3</v>
+        <v>-7.3539000000000007E-2</v>
       </c>
       <c r="E9" s="182" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="189">
         <f ca="1">Statement!AC152</f>
-        <v>2.6227324622605606E-2</v>
+        <v>2.6771551584603925E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -16556,14 +16556,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.1100000000000001E-3</v>
+        <v>-7.2189999999999997E-3</v>
       </c>
       <c r="E10" s="182" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="189">
         <f ca="1">Statement!AC154</f>
-        <v>1.6824243158637408E-2</v>
+        <v>1.7173352603611233E-2</v>
       </c>
       <c r="H10" s="181" t="s">
         <v>407</v>
@@ -16579,14 +16579,14 @@
       </c>
       <c r="C11" s="206" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>317.39999999999998</v>
+        <v>344.56990000000002</v>
       </c>
       <c r="E11" s="183" t="s">
         <v>288</v>
       </c>
       <c r="F11" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>3.2982367119117088E-3</v>
+        <v>3.3666763782331422E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="C13" s="206" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.0931999999999999</v>
+        <v>1.0406</v>
       </c>
       <c r="E13" s="182" t="s">
         <v>101</v>
@@ -16627,7 +16627,7 @@
       </c>
       <c r="C14" s="207" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>64766433</v>
+        <v>62679055</v>
       </c>
       <c r="E14" s="183" t="s">
         <v>102</v>
@@ -16643,7 +16643,7 @@
       </c>
       <c r="F15" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.3314638391082885E-2</v>
+        <v>1.3590922202182689E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -16656,10 +16656,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="235" t="s">
+      <c r="B17" s="239" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="235"/>
+      <c r="C17" s="239"/>
       <c r="E17" s="181" t="s">
         <v>295</v>
       </c>
@@ -16732,14 +16732,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="235" t="s">
+      <c r="B25" s="239" t="s">
         <v>104</v>
       </c>
-      <c r="C25" s="235"/>
-      <c r="E25" s="233" t="s">
+      <c r="C25" s="239"/>
+      <c r="E25" s="237" t="s">
         <v>342</v>
       </c>
-      <c r="F25" s="234"/>
+      <c r="F25" s="238"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="181" t="s">
@@ -16753,7 +16753,7 @@
       </c>
       <c r="F26" s="216" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.69</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16768,7 +16768,7 @@
       </c>
       <c r="F27" s="217">
         <f ca="1">F26/1000</f>
-        <v>4.5689999999999995E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16788,15 +16788,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="232" t="s">
+      <c r="B33" s="240" t="s">
         <v>337</v>
       </c>
-      <c r="C33" s="232"/>
-      <c r="D33" s="232"/>
-      <c r="E33" s="232"/>
-      <c r="F33" s="232"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="232"/>
+      <c r="C33" s="240"/>
+      <c r="D33" s="240"/>
+      <c r="E33" s="240"/>
+      <c r="F33" s="240"/>
+      <c r="G33" s="240"/>
+      <c r="H33" s="240"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -16809,24 +16809,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="232"/>
-      <c r="C39" s="232"/>
-      <c r="D39" s="232"/>
-      <c r="E39" s="232"/>
-      <c r="F39" s="232"/>
-      <c r="G39" s="232"/>
-      <c r="H39" s="232"/>
+      <c r="B39" s="240"/>
+      <c r="C39" s="240"/>
+      <c r="D39" s="240"/>
+      <c r="E39" s="240"/>
+      <c r="F39" s="240"/>
+      <c r="G39" s="240"/>
+      <c r="H39" s="240"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="232" t="s">
+      <c r="B42" s="240" t="s">
         <v>340</v>
       </c>
-      <c r="C42" s="232"/>
-      <c r="D42" s="232"/>
-      <c r="E42" s="232"/>
-      <c r="F42" s="232"/>
-      <c r="G42" s="232"/>
-      <c r="H42" s="232"/>
+      <c r="C42" s="240"/>
+      <c r="D42" s="240"/>
+      <c r="E42" s="240"/>
+      <c r="F42" s="240"/>
+      <c r="G42" s="240"/>
+      <c r="H42" s="240"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -16841,24 +16841,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="232"/>
-      <c r="C49" s="232"/>
-      <c r="D49" s="232"/>
-      <c r="E49" s="232"/>
-      <c r="F49" s="232"/>
-      <c r="G49" s="232"/>
-      <c r="H49" s="232"/>
+      <c r="B49" s="240"/>
+      <c r="C49" s="240"/>
+      <c r="D49" s="240"/>
+      <c r="E49" s="240"/>
+      <c r="F49" s="240"/>
+      <c r="G49" s="240"/>
+      <c r="H49" s="240"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="232" t="s">
+      <c r="B52" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="C52" s="232"/>
-      <c r="D52" s="232"/>
-      <c r="E52" s="232"/>
-      <c r="F52" s="232"/>
-      <c r="G52" s="232"/>
-      <c r="H52" s="232"/>
+      <c r="C52" s="240"/>
+      <c r="D52" s="240"/>
+      <c r="E52" s="240"/>
+      <c r="F52" s="240"/>
+      <c r="G52" s="240"/>
+      <c r="H52" s="240"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -16873,28 +16873,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="232"/>
-      <c r="C59" s="232"/>
-      <c r="D59" s="232"/>
-      <c r="E59" s="232"/>
-      <c r="F59" s="232"/>
-      <c r="G59" s="232"/>
-      <c r="H59" s="232"/>
+      <c r="B59" s="240"/>
+      <c r="C59" s="240"/>
+      <c r="D59" s="240"/>
+      <c r="E59" s="240"/>
+      <c r="F59" s="240"/>
+      <c r="G59" s="240"/>
+      <c r="H59" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -16964,36 +16964,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="240" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="232" t="s">
+      <c r="S2" s="240" t="s">
         <v>110</v>
       </c>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="232" t="s">
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
+      <c r="AA2" s="240" t="s">
         <v>111</v>
       </c>
-      <c r="AB2" s="232"/>
-      <c r="AC2" s="232"/>
+      <c r="AB2" s="240"/>
+      <c r="AC2" s="240"/>
       <c r="AE2" s="85" t="s">
         <v>112</v>
       </c>
@@ -17004,32 +17004,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="246" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="242" t="s">
+      <c r="S4" s="247" t="s">
         <v>113</v>
       </c>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="243"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="243"/>
-      <c r="Y4" s="243"/>
-      <c r="Z4" s="243"/>
-      <c r="AA4" s="243"/>
-      <c r="AB4" s="243"/>
-      <c r="AC4" s="243"/>
+      <c r="T4" s="248"/>
+      <c r="U4" s="248"/>
+      <c r="V4" s="248"/>
+      <c r="W4" s="248"/>
+      <c r="X4" s="248"/>
+      <c r="Y4" s="248"/>
+      <c r="Z4" s="248"/>
+      <c r="AA4" s="248"/>
+      <c r="AB4" s="248"/>
+      <c r="AC4" s="248"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -17717,33 +17717,33 @@
       <c r="Q12" s="91"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="241" t="s">
+      <c r="C13" s="246" t="s">
         <v>119</v>
       </c>
-      <c r="D13" s="241"/>
-      <c r="E13" s="241"/>
-      <c r="F13" s="241"/>
-      <c r="G13" s="241"/>
-      <c r="H13" s="241"/>
-      <c r="I13" s="241"/>
-      <c r="J13" s="241"/>
-      <c r="K13" s="241"/>
-      <c r="L13" s="241"/>
+      <c r="D13" s="246"/>
+      <c r="E13" s="246"/>
+      <c r="F13" s="246"/>
+      <c r="G13" s="246"/>
+      <c r="H13" s="246"/>
+      <c r="I13" s="246"/>
+      <c r="J13" s="246"/>
+      <c r="K13" s="246"/>
+      <c r="L13" s="246"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="91"/>
-      <c r="S13" s="242" t="s">
+      <c r="S13" s="247" t="s">
         <v>119</v>
       </c>
-      <c r="T13" s="243"/>
-      <c r="U13" s="243"/>
-      <c r="V13" s="243"/>
-      <c r="W13" s="243"/>
-      <c r="X13" s="243"/>
-      <c r="Y13" s="243"/>
-      <c r="Z13" s="243"/>
-      <c r="AA13" s="243"/>
-      <c r="AB13" s="243"/>
-      <c r="AC13" s="243"/>
+      <c r="T13" s="248"/>
+      <c r="U13" s="248"/>
+      <c r="V13" s="248"/>
+      <c r="W13" s="248"/>
+      <c r="X13" s="248"/>
+      <c r="Y13" s="248"/>
+      <c r="Z13" s="248"/>
+      <c r="AA13" s="248"/>
+      <c r="AB13" s="248"/>
+      <c r="AC13" s="248"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -18364,35 +18364,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="240" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="P2" s="232" t="s">
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
+      <c r="P2" s="240" t="s">
         <v>110</v>
       </c>
-      <c r="Q2" s="232"/>
-      <c r="R2" s="232"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232" t="s">
+      <c r="Q2" s="240"/>
+      <c r="R2" s="240"/>
+      <c r="S2" s="240"/>
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240" t="s">
         <v>111</v>
       </c>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
       <c r="AB2" s="85" t="s">
         <v>112</v>
       </c>
@@ -18401,31 +18401,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="246" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
-      <c r="P4" s="243" t="s">
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
+      <c r="P4" s="248" t="s">
         <v>113</v>
       </c>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="243"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="243"/>
-      <c r="Y4" s="243"/>
-      <c r="Z4" s="243"/>
+      <c r="Q4" s="248"/>
+      <c r="R4" s="248"/>
+      <c r="S4" s="248"/>
+      <c r="T4" s="248"/>
+      <c r="U4" s="248"/>
+      <c r="V4" s="248"/>
+      <c r="W4" s="248"/>
+      <c r="X4" s="248"/>
+      <c r="Y4" s="248"/>
+      <c r="Z4" s="248"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18620,32 +18620,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="241" t="s">
+      <c r="C9" s="246" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="241"/>
-      <c r="E9" s="241"/>
-      <c r="F9" s="241"/>
-      <c r="G9" s="241"/>
-      <c r="H9" s="241"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="241"/>
-      <c r="K9" s="241"/>
-      <c r="L9" s="241"/>
+      <c r="D9" s="246"/>
+      <c r="E9" s="246"/>
+      <c r="F9" s="246"/>
+      <c r="G9" s="246"/>
+      <c r="H9" s="246"/>
+      <c r="I9" s="246"/>
+      <c r="J9" s="246"/>
+      <c r="K9" s="246"/>
+      <c r="L9" s="246"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="243" t="s">
+      <c r="P9" s="248" t="s">
         <v>123</v>
       </c>
-      <c r="Q9" s="243"/>
-      <c r="R9" s="243"/>
-      <c r="S9" s="243"/>
-      <c r="T9" s="243"/>
-      <c r="U9" s="243"/>
-      <c r="V9" s="243"/>
-      <c r="W9" s="243"/>
-      <c r="X9" s="243"/>
-      <c r="Y9" s="243"/>
-      <c r="Z9" s="243"/>
+      <c r="Q9" s="248"/>
+      <c r="R9" s="248"/>
+      <c r="S9" s="248"/>
+      <c r="T9" s="248"/>
+      <c r="U9" s="248"/>
+      <c r="V9" s="248"/>
+      <c r="W9" s="248"/>
+      <c r="X9" s="248"/>
+      <c r="Y9" s="248"/>
+      <c r="Z9" s="248"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -19121,31 +19121,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="241" t="s">
+      <c r="C17" s="246" t="s">
         <v>125</v>
       </c>
-      <c r="D17" s="241"/>
-      <c r="E17" s="241"/>
-      <c r="F17" s="241"/>
-      <c r="G17" s="241"/>
-      <c r="H17" s="241"/>
-      <c r="I17" s="241"/>
-      <c r="J17" s="241"/>
-      <c r="K17" s="241"/>
-      <c r="L17" s="241"/>
-      <c r="P17" s="243" t="s">
+      <c r="D17" s="246"/>
+      <c r="E17" s="246"/>
+      <c r="F17" s="246"/>
+      <c r="G17" s="246"/>
+      <c r="H17" s="246"/>
+      <c r="I17" s="246"/>
+      <c r="J17" s="246"/>
+      <c r="K17" s="246"/>
+      <c r="L17" s="246"/>
+      <c r="P17" s="248" t="s">
         <v>125</v>
       </c>
-      <c r="Q17" s="243"/>
-      <c r="R17" s="243"/>
-      <c r="S17" s="243"/>
-      <c r="T17" s="243"/>
-      <c r="U17" s="243"/>
-      <c r="V17" s="243"/>
-      <c r="W17" s="243"/>
-      <c r="X17" s="243"/>
-      <c r="Y17" s="243"/>
-      <c r="Z17" s="243"/>
+      <c r="Q17" s="248"/>
+      <c r="R17" s="248"/>
+      <c r="S17" s="248"/>
+      <c r="T17" s="248"/>
+      <c r="U17" s="248"/>
+      <c r="V17" s="248"/>
+      <c r="W17" s="248"/>
+      <c r="X17" s="248"/>
+      <c r="Y17" s="248"/>
+      <c r="Z17" s="248"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -19623,60 +19623,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="240" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="250" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
-      <c r="P3" s="246"/>
-      <c r="Q3" s="246"/>
-      <c r="R3" s="246"/>
-      <c r="S3" s="246"/>
-      <c r="T3" s="246"/>
-      <c r="U3" s="246"/>
-      <c r="V3" s="246"/>
-      <c r="W3" s="246"/>
-      <c r="X3" s="246"/>
-      <c r="Y3" s="246"/>
-      <c r="Z3" s="246"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
+      <c r="P3" s="251"/>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="251"/>
+      <c r="T3" s="251"/>
+      <c r="U3" s="251"/>
+      <c r="V3" s="251"/>
+      <c r="W3" s="251"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="251"/>
+      <c r="Z3" s="251"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="241" t="s">
+      <c r="C5" s="246" t="s">
         <v>113</v>
       </c>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="241"/>
-      <c r="L5" s="241"/>
-      <c r="P5" s="246"/>
-      <c r="Q5" s="246"/>
-      <c r="R5" s="246"/>
-      <c r="S5" s="246"/>
-      <c r="T5" s="246"/>
-      <c r="U5" s="246"/>
-      <c r="V5" s="246"/>
-      <c r="W5" s="246"/>
-      <c r="X5" s="246"/>
-      <c r="Y5" s="246"/>
-      <c r="Z5" s="246"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
+      <c r="P5" s="251"/>
+      <c r="Q5" s="251"/>
+      <c r="R5" s="251"/>
+      <c r="S5" s="251"/>
+      <c r="T5" s="251"/>
+      <c r="U5" s="251"/>
+      <c r="V5" s="251"/>
+      <c r="W5" s="251"/>
+      <c r="X5" s="251"/>
+      <c r="Y5" s="251"/>
+      <c r="Z5" s="251"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19862,30 +19862,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="241" t="s">
+      <c r="C11" s="246" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="241"/>
-      <c r="E11" s="241"/>
-      <c r="F11" s="241"/>
-      <c r="G11" s="241"/>
-      <c r="H11" s="241"/>
-      <c r="I11" s="241"/>
-      <c r="J11" s="241"/>
-      <c r="K11" s="241"/>
-      <c r="L11" s="241"/>
+      <c r="D11" s="246"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="246"/>
+      <c r="G11" s="246"/>
+      <c r="H11" s="246"/>
+      <c r="I11" s="246"/>
+      <c r="J11" s="246"/>
+      <c r="K11" s="246"/>
+      <c r="L11" s="246"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="246"/>
-      <c r="Q11" s="246"/>
-      <c r="R11" s="246"/>
-      <c r="S11" s="246"/>
-      <c r="T11" s="246"/>
-      <c r="U11" s="246"/>
-      <c r="V11" s="246"/>
-      <c r="W11" s="246"/>
-      <c r="X11" s="246"/>
-      <c r="Y11" s="246"/>
-      <c r="Z11" s="246"/>
+      <c r="P11" s="251"/>
+      <c r="Q11" s="251"/>
+      <c r="R11" s="251"/>
+      <c r="S11" s="251"/>
+      <c r="T11" s="251"/>
+      <c r="U11" s="251"/>
+      <c r="V11" s="251"/>
+      <c r="W11" s="251"/>
+      <c r="X11" s="251"/>
+      <c r="Y11" s="251"/>
+      <c r="Z11" s="251"/>
       <c r="AB11" s="110"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -20127,18 +20127,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="241" t="s">
+      <c r="C18" s="246" t="s">
         <v>134</v>
       </c>
-      <c r="D18" s="241"/>
-      <c r="E18" s="241"/>
-      <c r="F18" s="241"/>
-      <c r="G18" s="241"/>
-      <c r="H18" s="241"/>
-      <c r="I18" s="241"/>
-      <c r="J18" s="241"/>
-      <c r="K18" s="241"/>
-      <c r="L18" s="241"/>
+      <c r="D18" s="246"/>
+      <c r="E18" s="246"/>
+      <c r="F18" s="246"/>
+      <c r="G18" s="246"/>
+      <c r="H18" s="246"/>
+      <c r="I18" s="246"/>
+      <c r="J18" s="246"/>
+      <c r="K18" s="246"/>
+      <c r="L18" s="246"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20351,23 +20351,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="246"/>
-      <c r="C25" s="246"/>
+      <c r="B25" s="251"/>
+      <c r="C25" s="251"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="241" t="s">
+      <c r="C26" s="246" t="s">
         <v>140</v>
       </c>
-      <c r="D26" s="241"/>
-      <c r="E26" s="241"/>
-      <c r="F26" s="241"/>
-      <c r="G26" s="241"/>
-      <c r="H26" s="241"/>
-      <c r="I26" s="241"/>
-      <c r="J26" s="241"/>
-      <c r="K26" s="241"/>
-      <c r="L26" s="241"/>
+      <c r="D26" s="246"/>
+      <c r="E26" s="246"/>
+      <c r="F26" s="246"/>
+      <c r="G26" s="246"/>
+      <c r="H26" s="246"/>
+      <c r="I26" s="246"/>
+      <c r="J26" s="246"/>
+      <c r="K26" s="246"/>
+      <c r="L26" s="246"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -20559,18 +20559,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="241" t="s">
+      <c r="C33" s="246" t="s">
         <v>144</v>
       </c>
-      <c r="D33" s="241"/>
-      <c r="E33" s="241"/>
-      <c r="F33" s="241"/>
-      <c r="G33" s="241"/>
-      <c r="H33" s="241"/>
-      <c r="I33" s="241"/>
-      <c r="J33" s="241"/>
-      <c r="K33" s="241"/>
-      <c r="L33" s="241"/>
+      <c r="D33" s="246"/>
+      <c r="E33" s="246"/>
+      <c r="F33" s="246"/>
+      <c r="G33" s="246"/>
+      <c r="H33" s="246"/>
+      <c r="I33" s="246"/>
+      <c r="J33" s="246"/>
+      <c r="K33" s="246"/>
+      <c r="L33" s="246"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -20754,18 +20754,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="241" t="s">
+      <c r="C40" s="246" t="s">
         <v>147</v>
       </c>
-      <c r="D40" s="241"/>
-      <c r="E40" s="241"/>
-      <c r="F40" s="241"/>
-      <c r="G40" s="241"/>
-      <c r="H40" s="241"/>
-      <c r="I40" s="241"/>
-      <c r="J40" s="241"/>
-      <c r="K40" s="241"/>
-      <c r="L40" s="241"/>
+      <c r="D40" s="246"/>
+      <c r="E40" s="246"/>
+      <c r="F40" s="246"/>
+      <c r="G40" s="246"/>
+      <c r="H40" s="246"/>
+      <c r="I40" s="246"/>
+      <c r="J40" s="246"/>
+      <c r="K40" s="246"/>
+      <c r="L40" s="246"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -21029,6 +21029,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -21036,12 +21042,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21079,60 +21079,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="240" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="S2" s="246"/>
-      <c r="T2" s="246"/>
-      <c r="U2" s="246"/>
-      <c r="V2" s="246"/>
-      <c r="W2" s="246"/>
-      <c r="X2" s="246"/>
-      <c r="Y2" s="246"/>
-      <c r="Z2" s="246"/>
-      <c r="AA2" s="246"/>
-      <c r="AB2" s="246"/>
-      <c r="AC2" s="246"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
+      <c r="S2" s="251"/>
+      <c r="T2" s="251"/>
+      <c r="U2" s="251"/>
+      <c r="V2" s="251"/>
+      <c r="W2" s="251"/>
+      <c r="X2" s="251"/>
+      <c r="Y2" s="251"/>
+      <c r="Z2" s="251"/>
+      <c r="AA2" s="251"/>
+      <c r="AB2" s="251"/>
+      <c r="AC2" s="251"/>
       <c r="AE2" s="109"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="246" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
-      <c r="S4" s="246"/>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
-      <c r="AA4" s="246"/>
-      <c r="AB4" s="246"/>
-      <c r="AC4" s="246"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
+      <c r="S4" s="251"/>
+      <c r="T4" s="251"/>
+      <c r="U4" s="251"/>
+      <c r="V4" s="251"/>
+      <c r="W4" s="251"/>
+      <c r="X4" s="251"/>
+      <c r="Y4" s="251"/>
+      <c r="Z4" s="251"/>
+      <c r="AA4" s="251"/>
+      <c r="AB4" s="251"/>
+      <c r="AC4" s="251"/>
       <c r="AE4" s="110"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -21495,18 +21495,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="241" t="s">
+      <c r="C13" s="246" t="s">
         <v>155</v>
       </c>
-      <c r="D13" s="241"/>
-      <c r="E13" s="241"/>
-      <c r="F13" s="241"/>
-      <c r="G13" s="241"/>
-      <c r="H13" s="241"/>
-      <c r="I13" s="241"/>
-      <c r="J13" s="241"/>
-      <c r="K13" s="241"/>
-      <c r="L13" s="241"/>
+      <c r="D13" s="246"/>
+      <c r="E13" s="246"/>
+      <c r="F13" s="246"/>
+      <c r="G13" s="246"/>
+      <c r="H13" s="246"/>
+      <c r="I13" s="246"/>
+      <c r="J13" s="246"/>
+      <c r="K13" s="246"/>
+      <c r="L13" s="246"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -21599,18 +21599,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="241" t="s">
+      <c r="C18" s="246" t="s">
         <v>156</v>
       </c>
-      <c r="D18" s="241"/>
-      <c r="E18" s="241"/>
-      <c r="F18" s="241"/>
-      <c r="G18" s="241"/>
-      <c r="H18" s="241"/>
-      <c r="I18" s="241"/>
-      <c r="J18" s="241"/>
-      <c r="K18" s="241"/>
-      <c r="L18" s="241"/>
+      <c r="D18" s="246"/>
+      <c r="E18" s="246"/>
+      <c r="F18" s="246"/>
+      <c r="G18" s="246"/>
+      <c r="H18" s="246"/>
+      <c r="I18" s="246"/>
+      <c r="J18" s="246"/>
+      <c r="K18" s="246"/>
+      <c r="L18" s="246"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21802,18 +21802,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="241" t="s">
+      <c r="C25" s="246" t="s">
         <v>261</v>
       </c>
-      <c r="D25" s="241"/>
-      <c r="E25" s="241"/>
-      <c r="F25" s="241"/>
-      <c r="G25" s="241"/>
-      <c r="H25" s="241"/>
-      <c r="I25" s="241"/>
-      <c r="J25" s="241"/>
-      <c r="K25" s="241"/>
-      <c r="L25" s="241"/>
+      <c r="D25" s="246"/>
+      <c r="E25" s="246"/>
+      <c r="F25" s="246"/>
+      <c r="G25" s="246"/>
+      <c r="H25" s="246"/>
+      <c r="I25" s="246"/>
+      <c r="J25" s="246"/>
+      <c r="K25" s="246"/>
+      <c r="L25" s="246"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -21951,18 +21951,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="241" t="s">
+      <c r="C31" s="246" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="241"/>
-      <c r="E31" s="241"/>
-      <c r="F31" s="241"/>
-      <c r="G31" s="241"/>
-      <c r="H31" s="241"/>
-      <c r="I31" s="241"/>
-      <c r="J31" s="241"/>
-      <c r="K31" s="241"/>
-      <c r="L31" s="241"/>
+      <c r="D31" s="246"/>
+      <c r="E31" s="246"/>
+      <c r="F31" s="246"/>
+      <c r="G31" s="246"/>
+      <c r="H31" s="246"/>
+      <c r="I31" s="246"/>
+      <c r="J31" s="246"/>
+      <c r="K31" s="246"/>
+      <c r="L31" s="246"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -22101,16 +22101,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22173,10 +22173,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="240" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="240"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -22193,7 +22193,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>315.32</v>
+        <v>308.91000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22202,7 +22202,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>4647816.8</v>
+        <v>4553333.4000000004</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22220,7 +22220,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.5689999999999995E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22229,7 +22229,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.0931999999999999</v>
+        <v>1.0406</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22261,10 +22261,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="240" t="s">
         <v>170</v>
       </c>
-      <c r="C15" s="232"/>
+      <c r="C15" s="240"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.7899736373445076E-2</v>
+        <v>1.8264378840357802E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.98210026362655489</v>
+        <v>0.98173562115964219</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22299,7 +22299,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>9.4883999999999996E-2</v>
+        <v>9.3456999999999998E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -22308,7 +22308,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>9.3843148229620532E-2</v>
+        <v>9.2421007903417229E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22353,60 +22353,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="240" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="250" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
-      <c r="P3" s="246"/>
-      <c r="Q3" s="246"/>
-      <c r="R3" s="246"/>
-      <c r="S3" s="246"/>
-      <c r="T3" s="246"/>
-      <c r="U3" s="246"/>
-      <c r="V3" s="246"/>
-      <c r="W3" s="246"/>
-      <c r="X3" s="246"/>
-      <c r="Y3" s="246"/>
-      <c r="Z3" s="246"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
+      <c r="P3" s="251"/>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="251"/>
+      <c r="T3" s="251"/>
+      <c r="U3" s="251"/>
+      <c r="V3" s="251"/>
+      <c r="W3" s="251"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="251"/>
+      <c r="Z3" s="251"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="241" t="s">
+      <c r="C5" s="246" t="s">
         <v>177</v>
       </c>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="241"/>
-      <c r="L5" s="241"/>
-      <c r="P5" s="246"/>
-      <c r="Q5" s="246"/>
-      <c r="R5" s="246"/>
-      <c r="S5" s="246"/>
-      <c r="T5" s="246"/>
-      <c r="U5" s="246"/>
-      <c r="V5" s="246"/>
-      <c r="W5" s="246"/>
-      <c r="X5" s="246"/>
-      <c r="Y5" s="246"/>
-      <c r="Z5" s="246"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
+      <c r="P5" s="251"/>
+      <c r="Q5" s="251"/>
+      <c r="R5" s="251"/>
+      <c r="S5" s="251"/>
+      <c r="T5" s="251"/>
+      <c r="U5" s="251"/>
+      <c r="V5" s="251"/>
+      <c r="W5" s="251"/>
+      <c r="X5" s="251"/>
+      <c r="Y5" s="251"/>
+      <c r="Z5" s="251"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22559,7 +22559,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>1898829.6907627422</v>
+        <v>1936117.2452169301</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22613,23 +22613,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>96313.601012058483</v>
+        <v>96438.984408176038</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>93001.581709908671</v>
+        <v>93243.882781174441</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>90116.814797603191</v>
+        <v>90469.221977782698</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>87111.995913326784</v>
+        <v>87566.500567210896</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>87785.096824080858</v>
+        <v>88357.99040344161</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22648,14 +22648,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>1212581.0032114149</v>
+        <v>1244461.4183180658</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="232" t="s">
+      <c r="B13" s="240" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="232"/>
+      <c r="C13" s="240"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -22671,14 +22671,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.3843148229620532E-2</v>
+        <v>9.2421007903417229E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="232" t="s">
+      <c r="B18" s="240" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="232"/>
+      <c r="C18" s="240"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -22686,7 +22686,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>454329.090256978</v>
+        <v>456076.5801377857</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -22695,7 +22695,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>1212581.0032114149</v>
+        <v>1244461.4183180658</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -22704,7 +22704,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>1666910.093468393</v>
+        <v>1700537.9984558516</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -22731,7 +22731,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>1728794.093468393</v>
+        <v>1762421.9984558516</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -22749,7 +22749,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>117.28589507926682</v>
+        <v>119.56729975955574</v>
       </c>
     </row>
   </sheetData>
@@ -22792,37 +22792,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="240" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="246" t="s">
         <v>191</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23011,18 +23011,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="241" t="s">
+      <c r="C10" s="246" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="241"/>
-      <c r="E10" s="241"/>
-      <c r="F10" s="241"/>
-      <c r="G10" s="241"/>
-      <c r="H10" s="241"/>
-      <c r="I10" s="241"/>
-      <c r="J10" s="241"/>
-      <c r="K10" s="241"/>
-      <c r="L10" s="241"/>
+      <c r="D10" s="246"/>
+      <c r="E10" s="246"/>
+      <c r="F10" s="246"/>
+      <c r="G10" s="246"/>
+      <c r="H10" s="246"/>
+      <c r="I10" s="246"/>
+      <c r="J10" s="246"/>
+      <c r="K10" s="246"/>
+      <c r="L10" s="246"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23216,18 +23216,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="241" t="s">
+      <c r="C16" s="246" t="s">
         <v>193</v>
       </c>
-      <c r="D16" s="241"/>
-      <c r="E16" s="241"/>
-      <c r="F16" s="241"/>
-      <c r="G16" s="241"/>
-      <c r="H16" s="241"/>
-      <c r="I16" s="241"/>
-      <c r="J16" s="241"/>
-      <c r="K16" s="241"/>
-      <c r="L16" s="241"/>
+      <c r="D16" s="246"/>
+      <c r="E16" s="246"/>
+      <c r="F16" s="246"/>
+      <c r="G16" s="246"/>
+      <c r="H16" s="246"/>
+      <c r="I16" s="246"/>
+      <c r="J16" s="246"/>
+      <c r="K16" s="246"/>
+      <c r="L16" s="246"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -23361,18 +23361,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="241" t="s">
+      <c r="C21" s="246" t="s">
         <v>196</v>
       </c>
-      <c r="D21" s="241"/>
-      <c r="E21" s="241"/>
-      <c r="F21" s="241"/>
-      <c r="G21" s="241"/>
-      <c r="H21" s="241"/>
-      <c r="I21" s="241"/>
-      <c r="J21" s="241"/>
-      <c r="K21" s="241"/>
-      <c r="L21" s="241"/>
+      <c r="D21" s="246"/>
+      <c r="E21" s="246"/>
+      <c r="F21" s="246"/>
+      <c r="G21" s="246"/>
+      <c r="H21" s="246"/>
+      <c r="I21" s="246"/>
+      <c r="J21" s="246"/>
+      <c r="K21" s="246"/>
+      <c r="L21" s="246"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -23456,18 +23456,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="241" t="s">
+      <c r="C26" s="246" t="s">
         <v>197</v>
       </c>
-      <c r="D26" s="241"/>
-      <c r="E26" s="241"/>
-      <c r="F26" s="241"/>
-      <c r="G26" s="241"/>
-      <c r="H26" s="241"/>
-      <c r="I26" s="241"/>
-      <c r="J26" s="241"/>
-      <c r="K26" s="241"/>
-      <c r="L26" s="241"/>
+      <c r="D26" s="246"/>
+      <c r="E26" s="246"/>
+      <c r="F26" s="246"/>
+      <c r="G26" s="246"/>
+      <c r="H26" s="246"/>
+      <c r="I26" s="246"/>
+      <c r="J26" s="246"/>
+      <c r="K26" s="246"/>
+      <c r="L26" s="246"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -23737,10 +23737,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="240" t="s">
         <v>202</v>
       </c>
-      <c r="C37" s="232"/>
+      <c r="C37" s="240"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.3843148229620532E-2</v>
+        <v>9.2421007903417229E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -23784,7 +23784,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>2800518.8748844177</v>
+        <v>2818574.9770444049</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -23811,7 +23811,7 @@
       </c>
       <c r="C45" s="64">
         <f ca="1">C42+C43-C44</f>
-        <v>2862402.8748844177</v>
+        <v>2880458.9770444049</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -23829,14 +23829,14 @@
       </c>
       <c r="C47" s="142">
         <f ca="1">C45/C46</f>
-        <v>194.19286803829158</v>
+        <v>195.41784104778867</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="232" t="s">
+      <c r="B49" s="240" t="s">
         <v>207</v>
       </c>
-      <c r="C49" s="232"/>
+      <c r="C49" s="240"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -23892,10 +23892,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="232" t="s">
+      <c r="B57" s="240" t="s">
         <v>321</v>
       </c>
-      <c r="C57" s="232"/>
+      <c r="C57" s="240"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="C59" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.3843148229620532E-2</v>
+        <v>9.2421007903417229E-2</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -23938,7 +23938,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>1789464.9364816172</v>
+        <v>1800922.8080688324</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -23965,7 +23965,7 @@
       </c>
       <c r="C65" s="64">
         <f ca="1">C62+C63-C64</f>
-        <v>1851348.9364816172</v>
+        <v>1862806.8080688324</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -23983,7 +23983,7 @@
       </c>
       <c r="C67" s="142">
         <f ca="1">C65/C66</f>
-        <v>125.60033490377322</v>
+        <v>126.37766676179324</v>
       </c>
     </row>
   </sheetData>
@@ -24035,10 +24035,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="240" t="s">
         <v>212</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="240"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -24047,7 +24047,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>117.28589507926682</v>
+        <v>119.56729975955574</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -24056,7 +24056,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C47</f>
-        <v>194.19286803829158</v>
+        <v>195.41784104778867</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -24074,7 +24074,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C67</f>
-        <v>125.60033490377322</v>
+        <v>126.37766676179324</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -24083,7 +24083,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>143.94163257692031</v>
+        <v>145.01255996387184</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24092,7 +24092,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>315.32</v>
+        <v>308.91000000000003</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -24101,7 +24101,7 @@
       </c>
       <c r="C11" s="151">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.54350617602143758</v>
+        <v>-0.53056696136780346</v>
       </c>
     </row>
   </sheetData>
@@ -24157,37 +24157,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="240" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="246" t="s">
         <v>191</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24238,23 +24238,23 @@
       <c r="B6" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="C6" s="250">
+      <c r="C6" s="232">
         <f>Statement!M25</f>
         <v>5.61</v>
       </c>
-      <c r="D6" s="250">
+      <c r="D6" s="232">
         <f>Statement!N25</f>
         <v>6.11</v>
       </c>
-      <c r="E6" s="250">
+      <c r="E6" s="232">
         <f>Statement!O25</f>
         <v>6.13</v>
       </c>
-      <c r="F6" s="250">
+      <c r="F6" s="232">
         <f>Statement!P25</f>
         <v>6.08</v>
       </c>
-      <c r="G6" s="251">
+      <c r="G6" s="233">
         <f>Statement!Q25</f>
         <v>7.46</v>
       </c>
@@ -24269,23 +24269,23 @@
       <c r="B7" s="16" t="s">
         <v>409</v>
       </c>
-      <c r="C7" s="250">
+      <c r="C7" s="232">
         <f>Statement!M81</f>
         <v>0.85</v>
       </c>
-      <c r="D7" s="250">
+      <c r="D7" s="232">
         <f>Statement!N81</f>
         <v>0.9</v>
       </c>
-      <c r="E7" s="250">
+      <c r="E7" s="232">
         <f>Statement!O81</f>
         <v>0.94</v>
       </c>
-      <c r="F7" s="250">
+      <c r="F7" s="232">
         <f>Statement!P81</f>
         <v>0.98</v>
       </c>
-      <c r="G7" s="251">
+      <c r="G7" s="233">
         <f>Statement!Q81</f>
         <v>1.02</v>
       </c>
@@ -24300,18 +24300,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="241" t="s">
+      <c r="C9" s="246" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="241"/>
-      <c r="E9" s="241"/>
-      <c r="F9" s="241"/>
-      <c r="G9" s="241"/>
-      <c r="H9" s="241"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="241"/>
-      <c r="K9" s="241"/>
-      <c r="L9" s="241"/>
+      <c r="D9" s="246"/>
+      <c r="E9" s="246"/>
+      <c r="F9" s="246"/>
+      <c r="G9" s="246"/>
+      <c r="H9" s="246"/>
+      <c r="I9" s="246"/>
+      <c r="J9" s="246"/>
+      <c r="K9" s="246"/>
+      <c r="L9" s="246"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -24432,18 +24432,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="241" t="s">
+      <c r="C14" s="246" t="s">
         <v>410</v>
       </c>
-      <c r="D14" s="241"/>
-      <c r="E14" s="241"/>
-      <c r="F14" s="241"/>
-      <c r="G14" s="241"/>
-      <c r="H14" s="241"/>
-      <c r="I14" s="241"/>
-      <c r="J14" s="241"/>
-      <c r="K14" s="241"/>
-      <c r="L14" s="241"/>
+      <c r="D14" s="246"/>
+      <c r="E14" s="246"/>
+      <c r="F14" s="246"/>
+      <c r="G14" s="246"/>
+      <c r="H14" s="246"/>
+      <c r="I14" s="246"/>
+      <c r="J14" s="246"/>
+      <c r="K14" s="246"/>
+      <c r="L14" s="246"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -24533,17 +24533,17 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="232" t="s">
+      <c r="B20" s="240" t="s">
         <v>412</v>
       </c>
-      <c r="C20" s="232"/>
+      <c r="C20" s="240"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="C21" s="252">
+      <c r="C21" s="234">
         <f>G7</f>
         <v>1.02</v>
       </c>
@@ -24552,7 +24552,7 @@
       <c r="B22" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C22" s="253">
+      <c r="C22" s="235">
         <v>0.04</v>
       </c>
     </row>
@@ -24560,7 +24560,7 @@
       <c r="B23" s="39" t="s">
         <v>415</v>
       </c>
-      <c r="C23" s="254">
+      <c r="C23" s="236">
         <f>C21*(1+C22)</f>
         <v>1.0608</v>
       </c>
@@ -24578,7 +24578,7 @@
       <c r="B25" s="39" t="s">
         <v>416</v>
       </c>
-      <c r="C25" s="253">
+      <c r="C25" s="235">
         <v>0.02</v>
       </c>
     </row>
@@ -24593,12 +24593,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C9:L9"/>
     <mergeCell ref="C14:L14"/>
-    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24637,60 +24637,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="240" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="250" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
-      <c r="P3" s="246"/>
-      <c r="Q3" s="246"/>
-      <c r="R3" s="246"/>
-      <c r="S3" s="246"/>
-      <c r="T3" s="246"/>
-      <c r="U3" s="246"/>
-      <c r="V3" s="246"/>
-      <c r="W3" s="246"/>
-      <c r="X3" s="246"/>
-      <c r="Y3" s="246"/>
-      <c r="Z3" s="246"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
+      <c r="P3" s="251"/>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="251"/>
+      <c r="T3" s="251"/>
+      <c r="U3" s="251"/>
+      <c r="V3" s="251"/>
+      <c r="W3" s="251"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="251"/>
+      <c r="Z3" s="251"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="241" t="s">
+      <c r="C5" s="246" t="s">
         <v>177</v>
       </c>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="241"/>
-      <c r="L5" s="241"/>
-      <c r="P5" s="246"/>
-      <c r="Q5" s="246"/>
-      <c r="R5" s="246"/>
-      <c r="S5" s="246"/>
-      <c r="T5" s="246"/>
-      <c r="U5" s="246"/>
-      <c r="V5" s="246"/>
-      <c r="W5" s="246"/>
-      <c r="X5" s="246"/>
-      <c r="Y5" s="246"/>
-      <c r="Z5" s="246"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
+      <c r="P5" s="251"/>
+      <c r="Q5" s="251"/>
+      <c r="R5" s="251"/>
+      <c r="S5" s="251"/>
+      <c r="T5" s="251"/>
+      <c r="U5" s="251"/>
+      <c r="V5" s="251"/>
+      <c r="W5" s="251"/>
+      <c r="X5" s="251"/>
+      <c r="Y5" s="251"/>
+      <c r="Z5" s="251"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -24825,7 +24825,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>5175310.5004440695</v>
+        <v>5276938.7154658828</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -24879,23 +24879,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>144878.73723923485</v>
+        <v>145067.34391481749</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>164237.1069996765</v>
+        <v>164665.00108745386</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>186182.09841988026</v>
+        <v>186910.17462243373</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>211059.33004590889</v>
+        <v>212160.52680699533</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>239260.60119360726</v>
+        <v>240822.03778337943</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -24914,15 +24914,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>3304921.567788545</v>
+        <v>3391812.48163016</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="247" t="s">
+      <c r="B14" s="252" t="s">
         <v>220</v>
       </c>
-      <c r="C14" s="248"/>
+      <c r="C14" s="253"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="152" t="s">
@@ -24930,7 +24930,7 @@
       </c>
       <c r="C15" s="153">
         <f ca="1">Overview!C5</f>
-        <v>315.32</v>
+        <v>308.91000000000003</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -24939,7 +24939,7 @@
       </c>
       <c r="C16" s="153">
         <f ca="1">C36</f>
-        <v>293.62180443159616</v>
+        <v>299.81082357494654</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24949,20 +24949,20 @@
       <c r="C17" s="155">
         <v>0.24</v>
       </c>
-      <c r="E17" s="249" t="s">
+      <c r="E17" s="254" t="s">
         <v>223</v>
       </c>
-      <c r="F17" s="249"/>
-      <c r="G17" s="249"/>
-      <c r="H17" s="249"/>
-      <c r="I17" s="249"/>
+      <c r="F17" s="254"/>
+      <c r="G17" s="254"/>
+      <c r="H17" s="254"/>
+      <c r="I17" s="254"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="247" t="s">
+      <c r="B19" s="252" t="s">
         <v>181</v>
       </c>
-      <c r="C19" s="248"/>
+      <c r="C19" s="253"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="156" t="s">
@@ -24978,7 +24978,7 @@
       </c>
       <c r="C21" s="219">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>9.3843148229620532E-2</v>
+        <v>9.2421007903417229E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -24996,7 +24996,7 @@
       </c>
       <c r="C23" s="158">
         <f ca="1">C15*C22</f>
-        <v>4631104.84</v>
+        <v>4536961.17</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -25023,15 +25023,15 @@
       </c>
       <c r="C26" s="159">
         <f ca="1">C23+C25-C24</f>
-        <v>4569220.84</v>
+        <v>4475077.17</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="247" t="s">
+      <c r="B28" s="252" t="s">
         <v>183</v>
       </c>
-      <c r="C28" s="248"/>
+      <c r="C28" s="253"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="156" t="s">
@@ -25039,7 +25039,7 @@
       </c>
       <c r="C29" s="158">
         <f ca="1">SUM(H10:L10)</f>
-        <v>945617.87389830779</v>
+        <v>949625.0842150799</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -25048,7 +25048,7 @@
       </c>
       <c r="C30" s="158">
         <f ca="1">L11</f>
-        <v>3304921.567788545</v>
+        <v>3391812.48163016</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -25057,7 +25057,7 @@
       </c>
       <c r="C31" s="161">
         <f ca="1">C29+C30</f>
-        <v>4250539.4416868528</v>
+        <v>4341437.5658452399</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C34" s="161">
         <f ca="1">C31+C32-C33</f>
-        <v>4312423.4416868528</v>
+        <v>4403321.5658452399</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -25102,22 +25102,22 @@
       </c>
       <c r="C36" s="164">
         <f ca="1">C34/C35</f>
-        <v>293.62180443159616</v>
+        <v>299.81082357494654</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="241" t="s">
+      <c r="C39" s="246" t="s">
         <v>226</v>
       </c>
-      <c r="D39" s="241"/>
-      <c r="E39" s="241"/>
-      <c r="F39" s="241"/>
-      <c r="G39" s="241"/>
-      <c r="H39" s="241"/>
-      <c r="I39" s="241"/>
-      <c r="J39" s="241"/>
-      <c r="K39" s="241"/>
-      <c r="L39" s="241"/>
+      <c r="D39" s="246"/>
+      <c r="E39" s="246"/>
+      <c r="F39" s="246"/>
+      <c r="G39" s="246"/>
+      <c r="H39" s="246"/>
+      <c r="I39" s="246"/>
+      <c r="J39" s="246"/>
+      <c r="K39" s="246"/>
+      <c r="L39" s="246"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -25549,17 +25549,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -31947,17 +31947,33 @@
       <c r="Q114" s="26">
         <v>255.46</v>
       </c>
-      <c r="T114" s="68"/>
-      <c r="U114" s="68"/>
-      <c r="V114" s="68"/>
-      <c r="W114" s="68"/>
-      <c r="X114" s="68"/>
-      <c r="Y114" s="68"/>
-      <c r="Z114" s="68"/>
-      <c r="AA114" s="68"/>
+      <c r="T114" s="26">
+        <v>208.81</v>
+      </c>
+      <c r="U114" s="26">
+        <v>227.79</v>
+      </c>
+      <c r="V114" s="26">
+        <v>255.59</v>
+      </c>
+      <c r="W114" s="26">
+        <v>217.73</v>
+      </c>
+      <c r="X114" s="26">
+        <v>201.08</v>
+      </c>
+      <c r="Y114" s="26">
+        <v>255.46</v>
+      </c>
+      <c r="Z114" s="26">
+        <v>272.89</v>
+      </c>
+      <c r="AA114" s="26">
+        <v>248.8</v>
+      </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>315.32</v>
+        <v>308.91000000000003</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -31994,17 +32010,41 @@
         <f>Q114/Q84</f>
         <v>255.46</v>
       </c>
-      <c r="T115" s="68"/>
-      <c r="U115" s="68"/>
-      <c r="V115" s="68"/>
-      <c r="W115" s="68"/>
-      <c r="X115" s="68"/>
-      <c r="Y115" s="68"/>
-      <c r="Z115" s="68"/>
-      <c r="AA115" s="68"/>
+      <c r="T115" s="65">
+        <f t="shared" ref="T115:AA115" si="67">T114/T84</f>
+        <v>208.81</v>
+      </c>
+      <c r="U115" s="65">
+        <f t="shared" si="67"/>
+        <v>227.79</v>
+      </c>
+      <c r="V115" s="65">
+        <f t="shared" si="67"/>
+        <v>255.59</v>
+      </c>
+      <c r="W115" s="65">
+        <f t="shared" si="67"/>
+        <v>217.73</v>
+      </c>
+      <c r="X115" s="65">
+        <f t="shared" si="67"/>
+        <v>201.08</v>
+      </c>
+      <c r="Y115" s="65">
+        <f t="shared" si="67"/>
+        <v>255.46</v>
+      </c>
+      <c r="Z115" s="65">
+        <f t="shared" si="67"/>
+        <v>272.89</v>
+      </c>
+      <c r="AA115" s="65">
+        <f t="shared" si="67"/>
+        <v>248.8</v>
+      </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>315.32</v>
+        <v>308.91000000000003</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -32118,19 +32158,19 @@
         <v>99</v>
       </c>
       <c r="M121" s="76">
-        <f t="shared" ref="M121:P121" si="67">M119*M120</f>
+        <f t="shared" ref="M121:P121" si="68">M119*M120</f>
         <v>0.26974205275183616</v>
       </c>
       <c r="N121" s="76">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.28292440929256846</v>
       </c>
       <c r="O121" s="76">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.2750983456377647</v>
       </c>
       <c r="P121" s="76">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.25682503150857577</v>
       </c>
       <c r="Q121" s="76">
@@ -32192,19 +32232,19 @@
         <v>101</v>
       </c>
       <c r="M123" s="76">
-        <f t="shared" ref="M123:P123" si="68">M121*M122</f>
+        <f t="shared" ref="M123:P123" si="69">M121*M122</f>
         <v>1.5007132667617686</v>
       </c>
       <c r="N123" s="76">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>1.9695887275023678</v>
       </c>
       <c r="O123" s="76">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>1.5607601454639075</v>
       </c>
       <c r="P123" s="76">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>1.6459350307287091</v>
       </c>
       <c r="Q123" s="76">
@@ -32340,55 +32380,55 @@
         <v>136</v>
       </c>
       <c r="M131" s="118">
-        <f t="shared" ref="M131:Q132" si="69">M29/M5*365</f>
+        <f t="shared" ref="M131:Q132" si="70">M29/M5*365</f>
         <v>26.219311841713207</v>
       </c>
       <c r="N131" s="118">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>26.087825363656648</v>
       </c>
       <c r="O131" s="118">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>28.100290906244702</v>
       </c>
       <c r="P131" s="118">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>31.185571624023428</v>
       </c>
       <c r="Q131" s="118">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>34.886990852098108</v>
       </c>
       <c r="T131" s="118">
-        <f t="shared" ref="T131:AA131" si="70">T29/T5*90</f>
+        <f t="shared" ref="T131:AA131" si="71">T29/T5*90</f>
         <v>23.917250545017893</v>
       </c>
       <c r="U131" s="118">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>31.674918360897504</v>
       </c>
       <c r="V131" s="118">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>21.46025744167337</v>
       </c>
       <c r="W131" s="118">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>24.667204983273734</v>
       </c>
       <c r="X131" s="118">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>26.374260921349272</v>
       </c>
       <c r="Y131" s="118">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>34.937735443952143</v>
       </c>
       <c r="Z131" s="118">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>24.992974206294001</v>
       </c>
       <c r="AA131" s="118">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>24.558479637357895</v>
       </c>
       <c r="AC131" s="118">
@@ -32401,55 +32441,55 @@
         <v>137</v>
       </c>
       <c r="M132" s="118">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>11.27659274770989</v>
       </c>
       <c r="N132" s="118">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>8.0756980666171607</v>
       </c>
       <c r="O132" s="118">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>10.791292490321617</v>
       </c>
       <c r="P132" s="118">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>12.642570548414087</v>
       </c>
       <c r="Q132" s="118">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>9.4454652425778427</v>
       </c>
       <c r="T132" s="118">
-        <f t="shared" ref="T132:AA132" si="71">T30/T6*365</f>
+        <f t="shared" ref="T132:AA132" si="72">T30/T6*365</f>
         <v>48.812880973556915</v>
       </c>
       <c r="U132" s="118">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>52.092809151632679</v>
       </c>
       <c r="V132" s="118">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>38.205452480121167</v>
       </c>
       <c r="W132" s="118">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>45.317773112572283</v>
       </c>
       <c r="X132" s="118">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>42.979152589530585</v>
       </c>
       <c r="Y132" s="118">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>38.560184757505773</v>
       </c>
       <c r="Z132" s="118">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>28.773901375377392</v>
       </c>
       <c r="AA132" s="118">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>43.661773309930325</v>
       </c>
       <c r="AC132" s="118">
@@ -32482,35 +32522,35 @@
         <v>115.40052498189718</v>
       </c>
       <c r="T133" s="118">
-        <f t="shared" ref="T133:AA133" si="72">T37/T6*90</f>
+        <f t="shared" ref="T133:AA133" si="73">T37/T6*90</f>
         <v>92.879672010238835</v>
       </c>
       <c r="U133" s="118">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>121.57254510195688</v>
       </c>
       <c r="V133" s="118">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>84.390761075350255</v>
       </c>
       <c r="W133" s="118">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>96.477461776122951</v>
       </c>
       <c r="X133" s="118">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>90.10016296355181</v>
       </c>
       <c r="Y133" s="118">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>116.16443418013857</v>
       </c>
       <c r="Z133" s="118">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>85.244280442804424</v>
       </c>
       <c r="AA133" s="118">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>91.509494175841695</v>
       </c>
       <c r="AC133" s="118">
@@ -32527,55 +32567,55 @@
         <v>-56.355166632892498</v>
       </c>
       <c r="N134" s="118">
-        <f t="shared" ref="N134:Q134" si="73">N131+N132-N133</f>
+        <f t="shared" ref="N134:Q134" si="74">N131+N132-N133</f>
         <v>-70.521753872831582</v>
       </c>
       <c r="O134" s="118">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>-67.829884635581323</v>
       </c>
       <c r="P134" s="118">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>-75.830335046699929</v>
       </c>
       <c r="Q134" s="118">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>-71.06806888722123</v>
       </c>
       <c r="T134" s="118">
-        <f t="shared" ref="T134" si="74">T131+T132-T133</f>
+        <f t="shared" ref="T134" si="75">T131+T132-T133</f>
         <v>-20.149540491664027</v>
       </c>
       <c r="U134" s="118">
-        <f t="shared" ref="U134" si="75">U131+U132-U133</f>
+        <f t="shared" ref="U134" si="76">U131+U132-U133</f>
         <v>-37.80481758942669</v>
       </c>
       <c r="V134" s="118">
-        <f t="shared" ref="V134" si="76">V131+V132-V133</f>
+        <f t="shared" ref="V134" si="77">V131+V132-V133</f>
         <v>-24.725051153555718</v>
       </c>
       <c r="W134" s="118">
-        <f t="shared" ref="W134" si="77">W131+W132-W133</f>
+        <f t="shared" ref="W134" si="78">W131+W132-W133</f>
         <v>-26.492483680276933</v>
       </c>
       <c r="X134" s="118">
-        <f t="shared" ref="X134" si="78">X131+X132-X133</f>
+        <f t="shared" ref="X134" si="79">X131+X132-X133</f>
         <v>-20.746749452671949</v>
       </c>
       <c r="Y134" s="118">
-        <f t="shared" ref="Y134" si="79">Y131+Y132-Y133</f>
+        <f t="shared" ref="Y134" si="80">Y131+Y132-Y133</f>
         <v>-42.666513978680655</v>
       </c>
       <c r="Z134" s="118">
-        <f t="shared" ref="Z134:AA134" si="80">Z131+Z132-Z133</f>
+        <f t="shared" ref="Z134:AA134" si="81">Z131+Z132-Z133</f>
         <v>-31.477404861133031</v>
       </c>
       <c r="AA134" s="118">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>-23.289241228553479</v>
       </c>
       <c r="AC134" s="118">
-        <f t="shared" ref="AC134" si="81">AC131+AC132-AC133</f>
+        <f t="shared" ref="AC134" si="82">AC131+AC132-AC133</f>
         <v>-53.941016242707917</v>
       </c>
     </row>
@@ -32604,35 +32644,35 @@
         <v>1.3380304612588665</v>
       </c>
       <c r="T135" s="118">
-        <f t="shared" ref="T135:AA135" si="82">T106/T48</f>
+        <f t="shared" ref="T135:AA135" si="83">T106/T48</f>
         <v>1.5186184565569347</v>
       </c>
       <c r="U135" s="118">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.8723266022827041</v>
       </c>
       <c r="V135" s="118">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.4499985020521886</v>
       </c>
       <c r="W135" s="118">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.4699383196598599</v>
       </c>
       <c r="X135" s="118">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.5448579674920249</v>
       </c>
       <c r="Y135" s="118">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.3380304612588665</v>
       </c>
       <c r="Z135" s="118">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.0262954983558226</v>
       </c>
       <c r="AA135" s="118">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.7954756740006198</v>
       </c>
       <c r="AC135" s="118">
@@ -32665,35 +32705,35 @@
         <v>-0.45790894172215968</v>
       </c>
       <c r="T136" s="176">
-        <f t="shared" ref="T136:AA136" si="83">(T106-T105)/T48</f>
+        <f t="shared" ref="T136:AA136" si="84">(T106-T105)/T48</f>
         <v>-0.77557414403070102</v>
       </c>
       <c r="U136" s="176">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-0.87833187006145741</v>
       </c>
       <c r="V136" s="176">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-0.66762036010665393</v>
       </c>
       <c r="W136" s="176">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-0.520031139589197</v>
       </c>
       <c r="X136" s="176">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-0.47528482454807841</v>
       </c>
       <c r="Y136" s="176">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-0.45790894172215968</v>
       </c>
       <c r="Z136" s="176">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-0.61555731942397096</v>
       </c>
       <c r="AA136" s="176">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-0.58111953122799109</v>
       </c>
       <c r="AC136" s="176">
@@ -32726,35 +32766,35 @@
         <v>1.0396423374851327</v>
       </c>
       <c r="T137" s="118">
-        <f t="shared" ref="T137:AA137" si="84">(T105+T29)/T39</f>
+        <f t="shared" ref="T137:AA137" si="85">(T105+T29)/T39</f>
         <v>1.3358961891448369</v>
       </c>
       <c r="U137" s="118">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>1.0774865073245952</v>
       </c>
       <c r="V137" s="118">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>1.1845461157482768</v>
       </c>
       <c r="W137" s="118">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>1.1002068187949174</v>
       </c>
       <c r="X137" s="118">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>1.1376346371882087</v>
       </c>
       <c r="Y137" s="118">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>1.0413398564353142</v>
       </c>
       <c r="Z137" s="118">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>1.1376449648019611</v>
       </c>
       <c r="AA137" s="118">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>1.3141167994890115</v>
       </c>
       <c r="AC137" s="118">
@@ -32787,35 +32827,35 @@
         <v>0.89329292221866674</v>
       </c>
       <c r="T138" s="118">
-        <f t="shared" ref="T138:AA138" si="85">T31/T39</f>
+        <f t="shared" ref="T138:AA138" si="86">T31/T39</f>
         <v>0.95297969975080532</v>
       </c>
       <c r="U138" s="118">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.86731257653408322</v>
       </c>
       <c r="V138" s="118">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.92293838534270767</v>
       </c>
       <c r="W138" s="118">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.82087002234196349</v>
       </c>
       <c r="X138" s="118">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.86799178004535149</v>
       </c>
       <c r="Y138" s="118">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.8947514831187523</v>
       </c>
       <c r="Z138" s="118">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.97374466486416578</v>
       </c>
       <c r="AA138" s="118">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>1.07035746912159</v>
       </c>
       <c r="AC138" s="118">
@@ -32848,35 +32888,35 @@
         <v>N/A</v>
       </c>
       <c r="T139" s="178" t="str">
-        <f t="shared" ref="T139:AA139" si="86">IF(T12&gt;=0,"N/A",IF(T11&lt;=0,"N/A",T11/-T12))</f>
+        <f t="shared" ref="T139:AA139" si="87">IF(T12&gt;=0,"N/A",IF(T11&lt;=0,"N/A",T11/-T12))</f>
         <v>N/A</v>
       </c>
       <c r="U139" s="178" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>N/A</v>
       </c>
       <c r="V139" s="178" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>N/A</v>
       </c>
       <c r="W139" s="178" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>N/A</v>
       </c>
       <c r="X139" s="178" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>N/A</v>
       </c>
       <c r="Y139" s="178" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>N/A</v>
       </c>
       <c r="Z139" s="178" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>N/A</v>
       </c>
       <c r="AA139" s="178" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>N/A</v>
       </c>
       <c r="AC139" s="178" t="str">
@@ -32918,7 +32958,7 @@
       <c r="AA140" s="49"/>
       <c r="AC140" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>38.128174123337367</v>
+        <v>37.353083434099162</v>
       </c>
     </row>
     <row r="141" spans="2:29" x14ac:dyDescent="0.2">
@@ -32955,7 +32995,7 @@
       <c r="AA141" s="49"/>
       <c r="AC141" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>10.363242321272722</v>
+        <v>10.152572578537221</v>
       </c>
     </row>
     <row r="142" spans="2:29" x14ac:dyDescent="0.2">
@@ -32982,17 +33022,41 @@
         <f>Q115/(Statement!Q48/Statement!Q74)</f>
         <v>51.193861093404578</v>
       </c>
-      <c r="T142" s="49"/>
-      <c r="U142" s="49"/>
-      <c r="V142" s="49"/>
-      <c r="W142" s="49"/>
-      <c r="X142" s="49"/>
-      <c r="Y142" s="49"/>
-      <c r="Z142" s="49"/>
-      <c r="AA142" s="49"/>
+      <c r="T142" s="72">
+        <f>T115/(Statement!T48/Statement!T74)</f>
+        <v>47.591701744918154</v>
+      </c>
+      <c r="U142" s="72">
+        <f>U115/(Statement!U48/Statement!U74)</f>
+        <v>60.461345741878837</v>
+      </c>
+      <c r="V142" s="72">
+        <f>V115/(Statement!V48/Statement!V74)</f>
+        <v>57.513301476976537</v>
+      </c>
+      <c r="W142" s="72">
+        <f>W115/(Statement!W48/Statement!W74)</f>
+        <v>48.685778789149047</v>
+      </c>
+      <c r="X142" s="72">
+        <f>X115/(Statement!X48/Statement!X74)</f>
+        <v>45.329290596992251</v>
+      </c>
+      <c r="Y142" s="72">
+        <f>Y115/(Statement!Y48/Statement!Y74)</f>
+        <v>51.193861093404578</v>
+      </c>
+      <c r="Z142" s="72">
+        <f>Z115/(Statement!Z48/Statement!Z74)</f>
+        <v>45.428031409456857</v>
+      </c>
+      <c r="AA142" s="72">
+        <f>AA115/(Statement!AA48/Statement!AA74)</f>
+        <v>34.313938267083607</v>
+      </c>
       <c r="AC142" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>43.488227549745986</v>
+        <v>42.604174718990343</v>
       </c>
     </row>
     <row r="143" spans="2:29" x14ac:dyDescent="0.2">
@@ -33019,17 +33083,41 @@
         <f>Statement!Q115*Statement!Q77</f>
         <v>3788982.72</v>
       </c>
-      <c r="T143" s="49"/>
-      <c r="U143" s="49"/>
-      <c r="V143" s="49"/>
-      <c r="W143" s="49"/>
-      <c r="X143" s="49"/>
-      <c r="Y143" s="49"/>
-      <c r="Z143" s="49"/>
-      <c r="AA143" s="49"/>
+      <c r="T143" s="143">
+        <f>Statement!T115*Statement!T77</f>
+        <v>3187484.65</v>
+      </c>
+      <c r="U143" s="143">
+        <f>Statement!U115*Statement!U77</f>
+        <v>3457852.1999999997</v>
+      </c>
+      <c r="V143" s="143">
+        <f>Statement!V115*Statement!V77</f>
+        <v>3857108.69</v>
+      </c>
+      <c r="W143" s="143">
+        <f>Statement!W115*Statement!W77</f>
+        <v>3265514.54</v>
+      </c>
+      <c r="X143" s="143">
+        <f>Statement!X115*Statement!X77</f>
+        <v>2993075.8000000003</v>
+      </c>
+      <c r="Y143" s="143">
+        <f>Statement!Y115*Statement!Y77</f>
+        <v>3788982.72</v>
+      </c>
+      <c r="Z143" s="143">
+        <f>Statement!Z115*Statement!Z77</f>
+        <v>4023217.27</v>
+      </c>
+      <c r="AA143" s="143">
+        <f>Statement!AA115*Statement!AA77</f>
+        <v>3667312</v>
+      </c>
       <c r="AC143" s="143">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>4647816.8</v>
+        <v>4553333.4000000004</v>
       </c>
     </row>
     <row r="144" spans="2:29" x14ac:dyDescent="0.2">
@@ -33056,17 +33144,41 @@
         <f>Q143+Q106-Q105+Q47+Q44</f>
         <v>3755219.72</v>
       </c>
-      <c r="T144" s="49"/>
-      <c r="U144" s="49"/>
-      <c r="V144" s="49"/>
-      <c r="W144" s="49"/>
-      <c r="X144" s="49"/>
-      <c r="Y144" s="49"/>
-      <c r="Z144" s="49"/>
-      <c r="AA144" s="49"/>
+      <c r="T144" s="143">
+        <f t="shared" ref="T144:AA144" si="88">T143+T106-T105+T47+T44</f>
+        <v>3135747.65</v>
+      </c>
+      <c r="U144" s="143">
+        <f t="shared" si="88"/>
+        <v>3407831.1999999997</v>
+      </c>
+      <c r="V144" s="143">
+        <f t="shared" si="88"/>
+        <v>3812539.69</v>
+      </c>
+      <c r="W144" s="143">
+        <f t="shared" si="88"/>
+        <v>3230778.54</v>
+      </c>
+      <c r="X144" s="143">
+        <f t="shared" si="88"/>
+        <v>2961787.8000000003</v>
+      </c>
+      <c r="Y144" s="143">
+        <f t="shared" si="88"/>
+        <v>3755219.72</v>
+      </c>
+      <c r="Z144" s="143">
+        <f t="shared" si="88"/>
+        <v>3968931.27</v>
+      </c>
+      <c r="AA144" s="143">
+        <f t="shared" si="88"/>
+        <v>3605428</v>
+      </c>
       <c r="AC144" s="143">
         <f ca="1">AC143+AC106-AC105+AC47+AC44</f>
-        <v>4585932.7999999998</v>
+        <v>4491449.4000000004</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
@@ -33103,7 +33215,7 @@
       <c r="AA145" s="49"/>
       <c r="AC145" s="180">
         <f ca="1">AC144/AC5</f>
-        <v>10.158409718191926</v>
+        <v>9.9491172730937762</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
@@ -33140,7 +33252,7 @@
       <c r="AA146" s="49"/>
       <c r="AC146" s="180">
         <f ca="1">AC144/AC11</f>
-        <v>31.119340960601495</v>
+        <v>30.478193070314727</v>
       </c>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
@@ -33168,35 +33280,35 @@
         <v>85904</v>
       </c>
       <c r="T147" s="64">
-        <f t="shared" ref="T147:AA147" si="87">T58-T53+T108+T64</f>
+        <f t="shared" ref="T147:AA147" si="89">T58-T53+T108+T64</f>
         <v>0</v>
       </c>
       <c r="U147" s="64">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="V147" s="64">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>23709</v>
       </c>
       <c r="W147" s="64">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>17655</v>
       </c>
       <c r="X147" s="64">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>21237</v>
       </c>
       <c r="Y147" s="64">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>23303</v>
       </c>
       <c r="Z147" s="64">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>47958</v>
       </c>
       <c r="AA147" s="64">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>23203</v>
       </c>
       <c r="AC147" s="64">
@@ -33250,19 +33362,19 @@
         <v>28.624929744729386</v>
       </c>
       <c r="N149" s="72">
-        <f t="shared" ref="N149:Q149" si="88">N143/N147</f>
+        <f t="shared" ref="N149:Q149" si="90">N143/N147</f>
         <v>23.529981348566967</v>
       </c>
       <c r="O149" s="72">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>30.134549582539918</v>
       </c>
       <c r="P149" s="72">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>35.604281345565745</v>
       </c>
       <c r="Q149" s="72">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>44.107174520394864</v>
       </c>
       <c r="T149" s="49"/>
@@ -33274,8 +33386,8 @@
       <c r="Z149" s="49"/>
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
-        <f t="shared" ref="AC149:AC150" ca="1" si="89">AC143/AC147</f>
-        <v>40.170930242608101</v>
+        <f t="shared" ref="AC149:AC150" ca="1" si="91">AC143/AC147</f>
+        <v>39.354313273005424</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -33287,19 +33399,19 @@
         <v>26.393507738520981</v>
       </c>
       <c r="N150" s="72">
-        <f t="shared" ref="N150:Q150" si="90">N144/N148</f>
+        <f t="shared" ref="N150:Q150" si="92">N144/N148</f>
         <v>23.215714092962134</v>
       </c>
       <c r="O150" s="72">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>28.684289253562675</v>
       </c>
       <c r="P150" s="72">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>34.359785546217651</v>
       </c>
       <c r="Q150" s="72">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>43.5317678998247</v>
       </c>
       <c r="T150" s="49"/>
@@ -33311,8 +33423,8 @@
       <c r="Z150" s="49"/>
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
-        <f t="shared" ca="1" si="89"/>
-        <v>39.677679735502217</v>
+        <f t="shared" ca="1" si="91"/>
+        <v>38.860205461670439</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -33324,19 +33436,19 @@
         <v>3.4934583557681108E-2</v>
       </c>
       <c r="N151" s="74">
-        <f t="shared" ref="N151:Q151" si="91">N147/N143</f>
+        <f t="shared" ref="N151:Q151" si="93">N147/N143</f>
         <v>4.2498971214055062E-2</v>
       </c>
       <c r="O151" s="74">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>3.3184501306746064E-2</v>
       </c>
       <c r="P151" s="74">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>2.8086509886107915E-2</v>
       </c>
       <c r="Q151" s="74">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>2.2672048501714993E-2</v>
       </c>
       <c r="T151" s="49"/>
@@ -33348,8 +33460,8 @@
       <c r="Z151" s="49"/>
       <c r="AA151" s="49"/>
       <c r="AC151" s="74">
-        <f t="shared" ref="AC151" ca="1" si="92">AC147/AC143</f>
-        <v>2.4893623173787745E-2</v>
+        <f t="shared" ref="AC151" ca="1" si="94">AC147/AC143</f>
+        <v>2.5410175323423493E-2</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -33386,7 +33498,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>2.6227324622605606E-2</v>
+        <v>2.6771551584603925E-2</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -33423,7 +33535,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="151">
         <f ca="1">AC81/AC115</f>
-        <v>3.2982367119117088E-3</v>
+        <v>3.3666763782331422E-3</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -33460,7 +33572,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="151">
         <f ca="1">-AC62/AC143</f>
-        <v>1.6824243158637408E-2</v>
+        <v>1.7173352603611233E-2</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -33497,7 +33609,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="151">
         <f ca="1">-(AC62+AC63)/AC143</f>
-        <v>2.0169899984009698E-2</v>
+        <v>2.0588433080696439E-2</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -33747,35 +33859,35 @@
         <v>8.9618299945858144</v>
       </c>
       <c r="T162" s="72">
-        <f t="shared" ref="T162:AA162" si="93">T105/T74</f>
+        <f t="shared" ref="T162:AA162" si="95">T105/T74</f>
         <v>10.065837937384899</v>
       </c>
       <c r="U162" s="72">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>10.363191320455147</v>
       </c>
       <c r="V162" s="72">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>9.4107309279723079</v>
       </c>
       <c r="W162" s="72">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>8.8994376004284952</v>
       </c>
       <c r="X162" s="72">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>8.9613207547169811</v>
       </c>
       <c r="Y162" s="72">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>8.9618299945858144</v>
       </c>
       <c r="Z162" s="72">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>9.8627477692255301</v>
       </c>
       <c r="AA162" s="72">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>9.981275958330496</v>
       </c>
       <c r="AC162" s="72">
@@ -33808,35 +33920,35 @@
         <v>0.11538185536678566</v>
       </c>
       <c r="T163" s="151" t="e">
-        <f t="shared" ref="T163:AA163" si="94">T53/T58</f>
+        <f t="shared" ref="T163:AA163" si="96">T53/T58</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U163" s="151" t="e">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V163" s="151">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>0.1097711708702188</v>
       </c>
       <c r="W163" s="151">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>0.13468603874415497</v>
       </c>
       <c r="X163" s="151">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>0.11368285068360426</v>
       </c>
       <c r="Y163" s="151">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>0.10707077502691066</v>
       </c>
       <c r="Z163" s="151">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>6.6648122392211406E-2</v>
       </c>
       <c r="AA163" s="151">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>0.12291826353564211</v>
       </c>
       <c r="AC163" s="151">
@@ -33869,35 +33981,35 @@
         <v>3.0908710811440764E-2</v>
       </c>
       <c r="T164" s="151">
-        <f t="shared" ref="T164:AA164" si="95">T53/T5</f>
+        <f t="shared" ref="T164:AA164" si="97">T53/T5</f>
         <v>0</v>
       </c>
       <c r="U164" s="151">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="V164" s="151">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>2.6436041834271923E-2</v>
       </c>
       <c r="W164" s="151">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>3.3830052748036368E-2</v>
       </c>
       <c r="X164" s="151">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>3.3689225403037135E-2</v>
       </c>
       <c r="Y164" s="151">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>3.106396268030371E-2</v>
       </c>
       <c r="Z164" s="151">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>2.5000695623139207E-2</v>
       </c>
       <c r="AA164" s="151">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>3.1731184343070942E-2</v>
       </c>
       <c r="AC164" s="151">
@@ -33930,35 +34042,35 @@
         <v>2.2849891716296695</v>
       </c>
       <c r="T165" s="72">
-        <f t="shared" ref="T165:AA165" si="96">(T105-T106)/T74</f>
+        <f t="shared" ref="T165:AA165" si="98">(T105-T106)/T74</f>
         <v>3.402854511970534</v>
       </c>
       <c r="U165" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>3.3091426303254829</v>
       </c>
       <c r="V165" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2.966915191053122</v>
       </c>
       <c r="W165" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2.3256561328334224</v>
       </c>
       <c r="X165" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2.1083557951482481</v>
       </c>
       <c r="Y165" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2.2849891716296695</v>
       </c>
       <c r="Z165" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>3.6977045160411417</v>
       </c>
       <c r="AA165" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>4.2135221624565942</v>
       </c>
       <c r="AC165" s="72">
@@ -34000,7 +34112,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="151">
         <f ca="1">(AC105-AC106)/AC143</f>
-        <v>1.3314638391082885E-2</v>
+        <v>1.3590922202182689E-2</v>
       </c>
     </row>
     <row r="167" spans="1:31" x14ac:dyDescent="0.2">
@@ -34028,35 +34140,35 @@
         <v>3.0553079216937677E-2</v>
       </c>
       <c r="T167" s="151">
-        <f t="shared" ref="T167:AA167" si="97">-T108/T5</f>
+        <f t="shared" ref="T167:AA167" si="99">-T108/T5</f>
         <v>0</v>
       </c>
       <c r="U167" s="151">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="V167" s="151">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>2.3652453740949316E-2</v>
       </c>
       <c r="W167" s="151">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>3.2204616239683723E-2</v>
       </c>
       <c r="X167" s="151">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>3.6815687609000808E-2</v>
       </c>
       <c r="Y167" s="151">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>3.1639763433724356E-2</v>
       </c>
       <c r="Z167" s="151">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>1.6507137093408276E-2</v>
       </c>
       <c r="AA167" s="151">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>1.7727370844725861E-2</v>
       </c>
       <c r="AC167" s="151">
@@ -34089,35 +34201,35 @@
         <v>0.11405428679069267</v>
       </c>
       <c r="T168" s="151" t="e">
-        <f t="shared" ref="T168:AA168" si="98">-(T108/T58)</f>
+        <f t="shared" ref="T168:AA168" si="100">-(T108/T58)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U168" s="151" t="e">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V168" s="151">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>9.8212794387840321E-2</v>
       </c>
       <c r="W168" s="151">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0.12821476285905142</v>
       </c>
       <c r="X168" s="151">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0.12423296372052967</v>
       </c>
       <c r="Y168" s="151">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0.10905543595263724</v>
       </c>
       <c r="Z168" s="151">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>4.4005563282336575E-2</v>
       </c>
       <c r="AA168" s="151">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>6.8671172740575576E-2</v>
       </c>
       <c r="AC168" s="151">
@@ -34150,35 +34262,35 @@
         <v>1.0869379381090785</v>
       </c>
       <c r="T169" s="151" t="e">
-        <f t="shared" ref="T169:AA169" si="99">-T108/T52</f>
+        <f t="shared" ref="T169:AA169" si="101">-T108/T52</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U169" s="151" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V169" s="151">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>0.95454545454545459</v>
       </c>
       <c r="W169" s="151">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>1.1540774145058248</v>
       </c>
       <c r="X169" s="151">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>1.223321554770318</v>
       </c>
       <c r="Y169" s="151">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>1.0367764630636394</v>
       </c>
       <c r="Z169" s="151">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>0.73833229620410701</v>
       </c>
       <c r="AA169" s="151">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>0.57313172433847048</v>
       </c>
       <c r="AC169" s="151">
@@ -34460,7 +34572,7 @@
         <v>28055</v>
       </c>
       <c r="AC178" s="62">
-        <f t="shared" ref="AC178:AC187" si="100">SUM(X178:AA178)</f>
+        <f t="shared" ref="AC178:AC187" si="102">SUM(X178:AA178)</f>
         <v>118918</v>
       </c>
     </row>
@@ -34518,7 +34630,7 @@
         <v>20497</v>
       </c>
       <c r="AC179" s="62">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>75885</v>
       </c>
     </row>
@@ -34576,7 +34688,7 @@
         <v>8401</v>
       </c>
       <c r="AC180" s="62">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>30232</v>
       </c>
     </row>
@@ -34634,7 +34746,7 @@
         <v>9138</v>
       </c>
       <c r="AC181" s="62">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>37395</v>
       </c>
     </row>
@@ -34710,7 +34822,7 @@
         <v>56994</v>
       </c>
       <c r="AC183" s="62">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>235870</v>
       </c>
     </row>
@@ -34768,7 +34880,7 @@
         <v>8399</v>
       </c>
       <c r="AC184" s="62">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>33557</v>
       </c>
     </row>
@@ -34826,7 +34938,7 @@
         <v>6914</v>
       </c>
       <c r="AC185" s="62">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>29042</v>
       </c>
     </row>
@@ -34884,7 +34996,7 @@
         <v>7901</v>
       </c>
       <c r="AC186" s="62">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>35811</v>
       </c>
     </row>
@@ -34942,7 +35054,7 @@
         <v>30976</v>
       </c>
       <c r="AC187" s="62">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>117162</v>
       </c>
     </row>
@@ -35006,61 +35118,61 @@
       <c r="K191" s="81"/>
       <c r="L191" s="81"/>
       <c r="M191" s="81">
-        <f t="shared" ref="M191:Q193" si="101">IF(L177=0,
+        <f t="shared" ref="M191:Q193" si="103">IF(L177=0,
 IF(M177=0,0,IF(M177&gt;0,1,-1)),
 (M177-L177)/ABS(L177)
 )</f>
         <v>1</v>
       </c>
       <c r="N191" s="81">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.10666249200944516</v>
       </c>
       <c r="O191" s="81">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>-4.1837107592922231E-2</v>
       </c>
       <c r="P191" s="81">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>2.7589812992125984E-2</v>
       </c>
       <c r="Q191" s="81">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>6.7694333862132958E-2</v>
       </c>
       <c r="T191" s="81">
-        <f t="shared" ref="T191:AA193" si="102">IF(S177=0,
+        <f t="shared" ref="T191:AA193" si="104">IF(S177=0,
 IF(T177=0,0,IF(T177&gt;0,1,-1)),
 (T177-S177)/ABS(S177)
 )</f>
         <v>1</v>
       </c>
       <c r="U191" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>0.10579117787568343</v>
       </c>
       <c r="V191" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>0.26363287250384027</v>
       </c>
       <c r="W191" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-0.2342539127792129</v>
       </c>
       <c r="X191" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>2.1902517673322585E-2</v>
       </c>
       <c r="Y191" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>7.2673430749065487E-2</v>
       </c>
       <c r="Z191" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>0.32442523533671253</v>
       </c>
       <c r="AA191" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-0.22956141399989749</v>
       </c>
       <c r="AC191" s="49"/>
@@ -35070,55 +35182,55 @@
         <v>381</v>
       </c>
       <c r="M192" s="81">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>1</v>
       </c>
       <c r="N192" s="81">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>6.5067687863213416E-2</v>
       </c>
       <c r="O192" s="81">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>-8.6629239470972889E-3</v>
       </c>
       <c r="P192" s="81">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>7.459647485524E-2</v>
       </c>
       <c r="Q192" s="81">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>9.5768198326227696E-2</v>
       </c>
       <c r="T192" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>1</v>
       </c>
       <c r="U192" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>0.13891427526960337</v>
       </c>
       <c r="V192" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>0.35857005296100142</v>
       </c>
       <c r="W192" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-0.27781223236171404</v>
       </c>
       <c r="X192" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-1.7992966385867344E-2</v>
       </c>
       <c r="Y192" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>0.19526109769301242</v>
       </c>
       <c r="Z192" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>0.32899000104518694</v>
       </c>
       <c r="AA192" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-0.26453625543962672</v>
       </c>
       <c r="AC192" s="49"/>
@@ -35128,85 +35240,85 @@
         <v>382</v>
       </c>
       <c r="M193" s="81">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>1</v>
       </c>
       <c r="N193" s="81">
-        <f t="shared" ref="N193:N195" si="103">IF(M179=0,
+        <f t="shared" ref="N193:N195" si="105">IF(M179=0,
 IF(N179=0,0,IF(N179&gt;0,1,-1)),
 (N179-M179)/ABS(M179)
 )</f>
         <v>8.5334815551589976E-2</v>
       </c>
       <c r="O193" s="81">
-        <f t="shared" ref="O193:O195" si="104">IF(N179=0,
+        <f t="shared" ref="O193:O195" si="106">IF(N179=0,
 IF(O179=0,0,IF(O179&gt;0,1,-1)),
 (O179-N179)/ABS(N179)
 )</f>
         <v>-2.211590296495957E-2</v>
       </c>
       <c r="P193" s="81">
-        <f t="shared" ref="P193:P195" si="105">IF(O179=0,
+        <f t="shared" ref="P193:P195" si="107">IF(O179=0,
 IF(P179=0,0,IF(P179&gt;0,1,-1)),
 (P179-O179)/ABS(O179)
 )</f>
         <v>-7.7275045135682688E-2</v>
       </c>
       <c r="Q193" s="81">
-        <f t="shared" ref="Q193:Q195" si="106">IF(P179=0,
+        <f t="shared" ref="Q193:Q195" si="108">IF(P179=0,
 IF(Q179=0,0,IF(Q179&gt;0,1,-1)),
 (Q179-P179)/ABS(P179)
 )</f>
         <v>-3.8460389532799615E-2</v>
       </c>
       <c r="T193" s="81">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>1</v>
       </c>
       <c r="U193" s="81">
-        <f t="shared" ref="U193:U195" si="107">IF(T179=0,
+        <f t="shared" ref="U193:U195" si="109">IF(T179=0,
 IF(U179=0,0,IF(U179&gt;0,1,-1)),
 (U179-T179)/ABS(T179)
 )</f>
         <v>2.0708853883758826E-2</v>
       </c>
       <c r="V193" s="81">
-        <f t="shared" ref="V193:V195" si="108">IF(U179=0,
+        <f t="shared" ref="V193:V195" si="110">IF(U179=0,
 IF(V179=0,0,IF(V179&gt;0,1,-1)),
 (V179-U179)/ABS(U179)
 )</f>
         <v>0.23149072041508681</v>
       </c>
       <c r="W193" s="81">
-        <f t="shared" ref="W193:W195" si="109">IF(V179=0,
+        <f t="shared" ref="W193:W195" si="111">IF(V179=0,
 IF(W179=0,0,IF(W179&gt;0,1,-1)),
 (W179-V179)/ABS(V179)
 )</f>
         <v>-0.13563441905687895</v>
       </c>
       <c r="X193" s="81">
-        <f t="shared" ref="X193:X195" si="110">IF(W179=0,
+        <f t="shared" ref="X193:X195" si="112">IF(W179=0,
 IF(X179=0,0,IF(X179&gt;0,1,-1)),
 (X179-W179)/ABS(W179)
 )</f>
         <v>-3.95575553055868E-2</v>
       </c>
       <c r="Y193" s="81">
-        <f t="shared" ref="Y193:Y195" si="111">IF(X179=0,
+        <f t="shared" ref="Y193:Y195" si="113">IF(X179=0,
 IF(Y179=0,0,IF(Y179&gt;0,1,-1)),
 (Y179-X179)/ABS(X179)
 )</f>
         <v>-5.699785282061292E-2</v>
       </c>
       <c r="Z193" s="81">
-        <f t="shared" ref="Z193:Z195" si="112">IF(Y179=0,
+        <f t="shared" ref="Z193:Z195" si="114">IF(Y179=0,
 IF(Z179=0,0,IF(Z179&gt;0,1,-1)),
 (Z179-Y179)/ABS(Y179)
 )</f>
         <v>0.76126405851100531</v>
       </c>
       <c r="AA193" s="81">
-        <f t="shared" ref="AA193:AA195" si="113">IF(Z179=0,
+        <f t="shared" ref="AA193:AA195" si="115">IF(Z179=0,
 IF(AA179=0,0,IF(AA179&gt;0,1,-1)),
 (AA179-Z179)/ABS(Z179)
 )</f>
@@ -35219,61 +35331,61 @@
         <v>383</v>
       </c>
       <c r="M194" s="81">
-        <f t="shared" ref="M194:M195" si="114">IF(L180=0,
+        <f t="shared" ref="M194:M195" si="116">IF(L180=0,
 IF(M180=0,0,IF(M180&gt;0,1,-1)),
 (M180-L180)/ABS(L180)
 )</f>
         <v>1</v>
       </c>
       <c r="N194" s="81">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>-8.7950284390141145E-2</v>
       </c>
       <c r="O194" s="81">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>-6.6212418678061366E-2</v>
       </c>
       <c r="P194" s="81">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>3.2774044605680834E-2</v>
       </c>
       <c r="Q194" s="81">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>0.14573686731598276</v>
       </c>
       <c r="T194" s="81">
-        <f t="shared" ref="T194:T195" si="115">IF(S180=0,
+        <f t="shared" ref="T194:T195" si="117">IF(S180=0,
 IF(T180=0,0,IF(T180&gt;0,1,-1)),
 (T180-S180)/ABS(S180)
 )</f>
         <v>1</v>
       </c>
       <c r="U194" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.16264469295664116</v>
       </c>
       <c r="V194" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.51653729328383391</v>
       </c>
       <c r="W194" s="81">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>-0.1879381328585735</v>
       </c>
       <c r="X194" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>-0.20772814469717732</v>
       </c>
       <c r="Y194" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.14769975786924938</v>
       </c>
       <c r="Z194" s="81">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>0.41847498493068114</v>
       </c>
       <c r="AA194" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>-0.10751088919579305</v>
       </c>
       <c r="AC194" s="49"/>
@@ -35283,55 +35395,55 @@
         <v>384</v>
       </c>
       <c r="M195" s="81">
+        <f t="shared" si="116"/>
+        <v>1</v>
+      </c>
+      <c r="N195" s="81">
+        <f t="shared" si="105"/>
+        <v>0.114546972226438</v>
+      </c>
+      <c r="O195" s="81">
+        <f t="shared" si="106"/>
+        <v>8.1702127659574464E-3</v>
+      </c>
+      <c r="P195" s="81">
+        <f t="shared" si="107"/>
+        <v>3.5218639203106535E-2</v>
+      </c>
+      <c r="Q195" s="81">
+        <f t="shared" si="108"/>
+        <v>9.9093221997521033E-2</v>
+      </c>
+      <c r="T195" s="81">
+        <f t="shared" si="117"/>
+        <v>1</v>
+      </c>
+      <c r="U195" s="81">
+        <f t="shared" si="109"/>
+        <v>0.15539906103286386</v>
+      </c>
+      <c r="V195" s="81">
+        <f t="shared" si="110"/>
+        <v>0.39387782744141947</v>
+      </c>
+      <c r="W195" s="81">
+        <f t="shared" si="111"/>
+        <v>-0.29161403167816541</v>
+      </c>
+      <c r="X195" s="81">
+        <f t="shared" si="112"/>
+        <v>5.2537722908093276E-2</v>
+      </c>
+      <c r="Y195" s="81">
+        <f t="shared" si="113"/>
+        <v>0.10022155610582562</v>
+      </c>
+      <c r="Z195" s="81">
         <f t="shared" si="114"/>
-        <v>1</v>
-      </c>
-      <c r="N195" s="81">
-        <f t="shared" si="103"/>
-        <v>0.114546972226438</v>
-      </c>
-      <c r="O195" s="81">
-        <f t="shared" si="104"/>
-        <v>8.1702127659574464E-3</v>
-      </c>
-      <c r="P195" s="81">
-        <f t="shared" si="105"/>
-        <v>3.5218639203106535E-2</v>
-      </c>
-      <c r="Q195" s="81">
-        <f t="shared" si="106"/>
-        <v>9.9093221997521033E-2</v>
-      </c>
-      <c r="T195" s="81">
+        <v>0.43828476664297561</v>
+      </c>
+      <c r="AA195" s="81">
         <f t="shared" si="115"/>
-        <v>1</v>
-      </c>
-      <c r="U195" s="81">
-        <f t="shared" si="107"/>
-        <v>0.15539906103286386</v>
-      </c>
-      <c r="V195" s="81">
-        <f t="shared" si="108"/>
-        <v>0.39387782744141947</v>
-      </c>
-      <c r="W195" s="81">
-        <f t="shared" si="109"/>
-        <v>-0.29161403167816541</v>
-      </c>
-      <c r="X195" s="81">
-        <f t="shared" si="110"/>
-        <v>5.2537722908093276E-2</v>
-      </c>
-      <c r="Y195" s="81">
-        <f t="shared" si="111"/>
-        <v>0.10022155610582562</v>
-      </c>
-      <c r="Z195" s="81">
-        <f t="shared" si="112"/>
-        <v>0.43828476664297561</v>
-      </c>
-      <c r="AA195" s="81">
-        <f t="shared" si="113"/>
         <v>-0.2474056992258277</v>
       </c>
       <c r="AC195" s="49"/>
@@ -35357,91 +35469,91 @@
         <v>385</v>
       </c>
       <c r="M197" s="81">
-        <f t="shared" ref="M197:M201" si="116">IF(L183=0,
+        <f t="shared" ref="M197:M201" si="118">IF(L183=0,
 IF(M183=0,0,IF(M183&gt;0,1,-1)),
 (M183-L183)/ABS(L183)
 )</f>
         <v>1</v>
       </c>
       <c r="N197" s="81">
-        <f t="shared" ref="N197:N201" si="117">IF(M183=0,
+        <f t="shared" ref="N197:N201" si="119">IF(M183=0,
 IF(N183=0,0,IF(N183&gt;0,1,-1)),
 (N183-M183)/ABS(M183)
 )</f>
         <v>7.0405734139696724E-2</v>
       </c>
       <c r="O197" s="81">
-        <f t="shared" ref="O197:O201" si="118">IF(N183=0,
+        <f t="shared" ref="O197:O201" si="120">IF(N183=0,
 IF(O183=0,0,IF(O183&gt;0,1,-1)),
 (O183-N183)/ABS(N183)
 )</f>
         <v>-2.3874757286278098E-2</v>
       </c>
       <c r="P197" s="81">
-        <f t="shared" ref="P197:P201" si="119">IF(O183=0,
+        <f t="shared" ref="P197:P201" si="121">IF(O183=0,
 IF(P183=0,0,IF(P183&gt;0,1,-1)),
 (P183-O183)/ABS(O183)
 )</f>
         <v>2.9912804175827464E-3</v>
       </c>
       <c r="Q197" s="81">
-        <f t="shared" ref="Q197:Q201" si="120">IF(P183=0,
+        <f t="shared" ref="Q197:Q201" si="122">IF(P183=0,
 IF(Q183=0,0,IF(Q183&gt;0,1,-1)),
 (Q183-P183)/ABS(P183)
 )</f>
         <v>4.1767942619406209E-2</v>
       </c>
       <c r="T197" s="81">
-        <f t="shared" ref="T197:T201" si="121">IF(S183=0,
+        <f t="shared" ref="T197:T201" si="123">IF(S183=0,
 IF(T183=0,0,IF(T183&gt;0,1,-1)),
 (T183-S183)/ABS(S183)
 )</f>
         <v>1</v>
       </c>
       <c r="U197" s="81">
-        <f t="shared" ref="U197:U201" si="122">IF(T183=0,
+        <f t="shared" ref="U197:U201" si="124">IF(T183=0,
 IF(U183=0,0,IF(U183&gt;0,1,-1)),
 (U183-T183)/ABS(T183)
 )</f>
         <v>0.17625203583061888</v>
       </c>
       <c r="V197" s="81">
-        <f t="shared" ref="V197:V201" si="123">IF(U183=0,
+        <f t="shared" ref="V197:V201" si="125">IF(U183=0,
 IF(V183=0,0,IF(V183&gt;0,1,-1)),
 (V183-U183)/ABS(U183)
 )</f>
         <v>0.49578122971745059</v>
       </c>
       <c r="W197" s="81">
-        <f t="shared" ref="W197:W201" si="124">IF(V183=0,
+        <f t="shared" ref="W197:W201" si="126">IF(V183=0,
 IF(W183=0,0,IF(W183&gt;0,1,-1)),
 (W183-V183)/ABS(V183)
 )</f>
         <v>-0.32249992768087016</v>
       </c>
       <c r="X197" s="81">
-        <f t="shared" ref="X197:X201" si="125">IF(W183=0,
+        <f t="shared" ref="X197:X201" si="127">IF(W183=0,
 IF(X183=0,0,IF(X183&gt;0,1,-1)),
 (X183-W183)/ABS(W183)
 )</f>
         <v>-4.8226980636621765E-2</v>
       </c>
       <c r="Y197" s="81">
-        <f t="shared" ref="Y197:Y201" si="126">IF(X183=0,
+        <f t="shared" ref="Y197:Y201" si="128">IF(X183=0,
 IF(Y183=0,0,IF(Y183&gt;0,1,-1)),
 (Y183-X183)/ABS(X183)
 )</f>
         <v>9.9659055224081472E-2</v>
       </c>
       <c r="Z197" s="81">
-        <f t="shared" ref="Z197:Z201" si="127">IF(Y183=0,
+        <f t="shared" ref="Z197:Z201" si="129">IF(Y183=0,
 IF(Z183=0,0,IF(Z183&gt;0,1,-1)),
 (Z183-Y183)/ABS(Y183)
 )</f>
         <v>0.739296277409485</v>
       </c>
       <c r="AA197" s="81">
-        <f t="shared" ref="AA197:AA201" si="128">IF(Z183=0,
+        <f t="shared" ref="AA197:AA201" si="130">IF(Z183=0,
 IF(AA183=0,0,IF(AA183&gt;0,1,-1)),
 (AA183-Z183)/ABS(Z183)
 )</f>
@@ -35454,55 +35566,55 @@
         <v>386</v>
       </c>
       <c r="M198" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>1</v>
       </c>
       <c r="N198" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.14171639670360897</v>
       </c>
       <c r="O198" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>-0.26930831072504169</v>
       </c>
       <c r="P198" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>2.1357768164321968E-2</v>
       </c>
       <c r="Q198" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>0.12419957310565635</v>
       </c>
       <c r="T198" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1</v>
       </c>
       <c r="U198" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>0.10486517334855186</v>
       </c>
       <c r="V198" s="81">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.16051136363636365</v>
       </c>
       <c r="W198" s="81">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>-0.11550016690775565</v>
       </c>
       <c r="X198" s="81">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>1.2202792804126306E-2</v>
       </c>
       <c r="Y198" s="81">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>8.4514044245587866E-2</v>
       </c>
       <c r="Z198" s="81">
-        <f t="shared" si="127"/>
+        <f t="shared" si="129"/>
         <v>-3.8964015585606235E-2</v>
       </c>
       <c r="AA198" s="81">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>1.550202718817076E-3</v>
       </c>
       <c r="AC198" s="49"/>
@@ -35512,55 +35624,55 @@
         <v>387</v>
       </c>
       <c r="M199" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>1</v>
       </c>
       <c r="N199" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>-8.0660347749670458E-2</v>
       </c>
       <c r="O199" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>-3.3865901952751604E-2</v>
       </c>
       <c r="P199" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>-5.6749116607773854E-2</v>
       </c>
       <c r="Q199" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>4.9786468869408858E-2</v>
       </c>
       <c r="T199" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1</v>
       </c>
       <c r="U199" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>-2.9600670203853673E-2</v>
       </c>
       <c r="V199" s="81">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.16374100719424461</v>
       </c>
       <c r="W199" s="81">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>-0.20845697329376855</v>
       </c>
       <c r="X199" s="81">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>2.796001249609497E-2</v>
       </c>
       <c r="Y199" s="81">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>5.6374411183710685E-2</v>
       </c>
       <c r="Z199" s="81">
-        <f t="shared" si="127"/>
+        <f t="shared" si="129"/>
         <v>0.2363348676639816</v>
       </c>
       <c r="AA199" s="81">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>-0.19557882489819661</v>
       </c>
       <c r="AC199" s="49"/>
@@ -35570,55 +35682,55 @@
         <v>388</v>
       </c>
       <c r="M200" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>1</v>
       </c>
       <c r="N200" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>7.4908124169207918E-2</v>
       </c>
       <c r="O200" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>-3.3849809655439975E-2</v>
       </c>
       <c r="P200" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>-7.1276195256619407E-2</v>
       </c>
       <c r="Q200" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-3.5643831914606135E-2</v>
       </c>
       <c r="T200" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1</v>
       </c>
       <c r="U200" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>0.11670989255279733</v>
       </c>
       <c r="V200" s="81">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.29915947799159476</v>
       </c>
       <c r="W200" s="81">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>-0.35966629777815612</v>
       </c>
       <c r="X200" s="81">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>-1.5687317202871576E-2</v>
       </c>
       <c r="Y200" s="81">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>0.21731496488384658</v>
       </c>
       <c r="Z200" s="81">
-        <f t="shared" si="127"/>
+        <f t="shared" si="129"/>
         <v>0.27515810495950294</v>
       </c>
       <c r="AA200" s="81">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>-0.31253806664926476</v>
       </c>
       <c r="AC200" s="49"/>
@@ -35628,55 +35740,55 @@
         <v>365</v>
       </c>
       <c r="M201" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>1</v>
       </c>
       <c r="N201" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.14181951041286078</v>
       </c>
       <c r="O201" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>7.7704821513138525E-2</v>
       </c>
       <c r="P201" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>0.14214964370546318</v>
       </c>
       <c r="Q201" s="81">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>0.135064313864135</v>
       </c>
       <c r="T201" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1</v>
       </c>
       <c r="U201" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>3.1346797175071245E-2</v>
       </c>
       <c r="V201" s="81">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>5.4781355117731863E-2</v>
       </c>
       <c r="W201" s="81">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>1.1579347000759301E-2</v>
       </c>
       <c r="X201" s="81">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>2.9198723963220118E-2</v>
       </c>
       <c r="Y201" s="81">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>4.8390037559712648E-2</v>
       </c>
       <c r="Z201" s="81">
-        <f t="shared" si="127"/>
+        <f t="shared" si="129"/>
         <v>4.3930434782608697E-2</v>
       </c>
       <c r="AA201" s="81">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>3.2086096025055806E-2</v>
       </c>
       <c r="AC201" s="49"/>
@@ -35816,15 +35928,15 @@
         <v>102.38905526817317</v>
       </c>
       <c r="O209" s="143">
-        <f t="shared" ref="O209:Q209" si="129">100*(1+((O115-$M115)/ABS($M115)))</f>
+        <f t="shared" ref="O209:Q209" si="131">100*(1+((O115-$M115)/ABS($M115)))</f>
         <v>116.53280696977947</v>
       </c>
       <c r="P209" s="143">
-        <f t="shared" si="129"/>
+        <f t="shared" si="131"/>
         <v>155.04356112169887</v>
       </c>
       <c r="Q209" s="143">
-        <f t="shared" si="129"/>
+        <f t="shared" si="131"/>
         <v>173.87693983120067</v>
       </c>
       <c r="T209" s="49"/>
@@ -35882,15 +35994,15 @@
         <v>108.9126559714795</v>
       </c>
       <c r="O211" s="143">
-        <f t="shared" ref="O211:Q211" si="130">100*(1+((O25-$M25)/ABS($M25)))</f>
+        <f t="shared" ref="O211:Q211" si="132">100*(1+((O25-$M25)/ABS($M25)))</f>
         <v>109.26916221033866</v>
       </c>
       <c r="P211" s="143">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>108.37789661319073</v>
       </c>
       <c r="Q211" s="143">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>132.97682709447415</v>
       </c>
       <c r="T211" s="49"/>
@@ -35997,15 +36109,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="240" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="E4" s="232" t="s">
+      <c r="C4" s="240"/>
+      <c r="E4" s="240" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="240"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -36013,7 +36125,7 @@
       </c>
       <c r="C5" s="169">
         <f ca="1">Overview!C5</f>
-        <v>315.32</v>
+        <v>308.91000000000003</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -36029,7 +36141,7 @@
       </c>
       <c r="C6" s="170">
         <f ca="1">Statement!AC143</f>
-        <v>4647816.8</v>
+        <v>4553333.4000000004</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -36049,7 +36161,7 @@
       </c>
       <c r="C7" s="170">
         <f ca="1">Statement!AC144</f>
-        <v>4585932.7999999998</v>
+        <v>4491449.4000000004</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -36069,7 +36181,7 @@
       </c>
       <c r="C8" s="171">
         <f ca="1">Statement!AC140</f>
-        <v>38.128174123337367</v>
+        <v>37.353083434099162</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -36089,7 +36201,7 @@
       </c>
       <c r="C9" s="171">
         <f ca="1">Statement!AC141</f>
-        <v>10.363242321272722</v>
+        <v>10.152572578537221</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -36109,7 +36221,7 @@
       </c>
       <c r="C10" s="171">
         <f ca="1">Statement!AC142</f>
-        <v>43.488227549745986</v>
+        <v>42.604174718990343</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -36129,7 +36241,7 @@
       </c>
       <c r="C11" s="171">
         <f ca="1">Statement!AC145</f>
-        <v>10.158409718191926</v>
+        <v>9.9491172730937762</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -36138,18 +36250,18 @@
       </c>
       <c r="C12" s="171">
         <f ca="1">Statement!AC146</f>
-        <v>31.119340960601495</v>
+        <v>30.478193070314727</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="240" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="232"/>
-      <c r="E15" s="232" t="s">
+      <c r="C15" s="240"/>
+      <c r="E15" s="240" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="232"/>
+      <c r="F15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -36200,14 +36312,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="232" t="s">
+      <c r="B21" s="240" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="232"/>
-      <c r="E21" s="232" t="s">
+      <c r="C21" s="240"/>
+      <c r="E21" s="240" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="232"/>
+      <c r="F21" s="240"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -36276,14 +36388,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="232" t="s">
+      <c r="B29" s="240" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="232"/>
-      <c r="E29" s="232" t="s">
+      <c r="C29" s="240"/>
+      <c r="E29" s="240" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="232"/>
+      <c r="F29" s="240"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36359,14 +36471,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="240" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="232"/>
-      <c r="E37" s="232" t="s">
+      <c r="C37" s="240"/>
+      <c r="E37" s="240" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="232"/>
+      <c r="F37" s="240"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -36374,7 +36486,7 @@
       </c>
       <c r="C38" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>2.6227324622605606E-2</v>
+        <v>2.6771551584603925E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -36390,7 +36502,7 @@
       </c>
       <c r="C39" s="212">
         <f ca="1">Statement!AC151</f>
-        <v>2.4893623173787745E-2</v>
+        <v>2.5410175323423493E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -36406,7 +36518,7 @@
       </c>
       <c r="C40" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>3.2982367119117088E-3</v>
+        <v>3.3666763782331422E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -36422,7 +36534,7 @@
       </c>
       <c r="C41" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>1.6824243158637408E-2</v>
+        <v>1.7173352603611233E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -36431,18 +36543,18 @@
       </c>
       <c r="C42" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>2.0169899984009698E-2</v>
+        <v>2.0588433080696439E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="232" t="s">
+      <c r="B45" s="240" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="232"/>
-      <c r="E45" s="232" t="s">
+      <c r="C45" s="240"/>
+      <c r="E45" s="240" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="232"/>
+      <c r="F45" s="240"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -36475,18 +36587,18 @@
       </c>
       <c r="F48" s="172">
         <f ca="1">Statement!AC166</f>
-        <v>1.3314638391082885E-2</v>
+        <v>1.3590922202182689E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="232" t="s">
+      <c r="B51" s="240" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="232"/>
-      <c r="E51" s="232" t="s">
+      <c r="C51" s="240"/>
+      <c r="E51" s="240" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="232"/>
+      <c r="F51" s="240"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36654,7 +36766,7 @@
       </c>
       <c r="I6" s="169">
         <f ca="1">Statement!AC114</f>
-        <v>315.32</v>
+        <v>308.91000000000003</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -36683,7 +36795,7 @@
       </c>
       <c r="I7" s="170">
         <f ca="1">Statement!AC143</f>
-        <v>4647816.8</v>
+        <v>4553333.4000000004</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -36712,7 +36824,7 @@
       </c>
       <c r="I8" s="170">
         <f ca="1">Statement!AC144</f>
-        <v>4585932.7999999998</v>
+        <v>4491449.4000000004</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36741,7 +36853,7 @@
       </c>
       <c r="I9" s="171">
         <f ca="1">Statement!AC140</f>
-        <v>38.128174123337367</v>
+        <v>37.353083434099162</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36770,7 +36882,7 @@
       </c>
       <c r="I10" s="171">
         <f ca="1">Statement!AC141</f>
-        <v>10.363242321272722</v>
+        <v>10.152572578537221</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36799,7 +36911,7 @@
       </c>
       <c r="I11" s="171">
         <f ca="1">Statement!AC142</f>
-        <v>43.488227549745986</v>
+        <v>42.604174718990343</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36828,7 +36940,7 @@
       </c>
       <c r="I12" s="171">
         <f ca="1">Statement!AC145</f>
-        <v>10.158409718191926</v>
+        <v>9.9491172730937762</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36857,7 +36969,7 @@
       </c>
       <c r="I13" s="171">
         <f ca="1">Statement!AC146</f>
-        <v>31.119340960601495</v>
+        <v>30.478193070314727</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37630,7 +37742,7 @@
       </c>
       <c r="I51" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>2.6227324622605606E-2</v>
+        <v>2.6771551584603925E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -37659,7 +37771,7 @@
       </c>
       <c r="I52" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>2.4893623173787745E-2</v>
+        <v>2.5410175323423493E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37688,7 +37800,7 @@
       </c>
       <c r="I53" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>3.2982367119117088E-3</v>
+        <v>3.3666763782331422E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -37717,7 +37829,7 @@
       </c>
       <c r="I54" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>1.6824243158637408E-2</v>
+        <v>1.7173352603611233E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -37746,7 +37858,7 @@
       </c>
       <c r="I55" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>2.0169899984009698E-2</v>
+        <v>2.0588433080696439E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37982,7 +38094,7 @@
       </c>
       <c r="I68" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>1.3314638391082885E-2</v>
+        <v>1.3590922202182689E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -38674,14 +38786,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="236" t="s">
+      <c r="C3" s="243" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="F3" s="238" t="s">
+      <c r="D3" s="244"/>
+      <c r="F3" s="245" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="237"/>
+      <c r="G3" s="244"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -38748,19 +38860,19 @@
       <c r="B7" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="239">
+      <c r="C7" s="241">
         <f>Statement!AA88</f>
         <v>-0.22657836890286318</v>
       </c>
-      <c r="D7" s="240"/>
-      <c r="F7" s="239">
+      <c r="D7" s="242"/>
+      <c r="F7" s="241">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.16595182415922985</v>
       </c>
-      <c r="G7" s="240"/>
+      <c r="G7" s="242"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="204" t="s">
@@ -38787,19 +38899,19 @@
       <c r="B9" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="239">
+      <c r="C9" s="241">
         <f>Statement!AA89</f>
         <v>-0.24316672257631666</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="F9" s="239">
+      <c r="D9" s="242"/>
+      <c r="F9" s="241">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.11706805038421929</v>
       </c>
-      <c r="G9" s="240"/>
+      <c r="G9" s="242"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="204" t="s">
@@ -38826,19 +38938,19 @@
       <c r="B11" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="239">
+      <c r="C11" s="241">
         <f>Statement!AA90</f>
         <v>-0.2087215264838006</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="F11" s="239">
+      <c r="D11" s="242"/>
+      <c r="F11" s="241">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.22096418302984375</v>
       </c>
-      <c r="G11" s="240"/>
+      <c r="G11" s="242"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="204" t="s">
@@ -38865,19 +38977,19 @@
       <c r="B13" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="239">
+      <c r="C13" s="241">
         <f>Statement!AA93</f>
         <v>2.8129930899396048E-2</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="F13" s="239">
+      <c r="D13" s="242"/>
+      <c r="F13" s="241">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.23681110092944102</v>
       </c>
-      <c r="G13" s="240"/>
+      <c r="G13" s="242"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="204" t="s">
@@ -38904,19 +39016,19 @@
       <c r="B15" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="239">
+      <c r="C15" s="241">
         <f>Statement!AA94</f>
         <v>-0.29432470699284197</v>
       </c>
-      <c r="D15" s="240"/>
-      <c r="F15" s="239">
+      <c r="D15" s="242"/>
+      <c r="F15" s="241">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.21278177701172732</v>
       </c>
-      <c r="G15" s="240"/>
+      <c r="G15" s="242"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="204" t="s">
@@ -38943,19 +39055,19 @@
       <c r="B17" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="239">
+      <c r="C17" s="241">
         <f>Statement!AA96</f>
         <v>-0.29738461173005204</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="F17" s="239">
+      <c r="D17" s="242"/>
+      <c r="F17" s="241">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.19362389023405974</v>
       </c>
-      <c r="G17" s="240"/>
+      <c r="G17" s="242"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="204" t="s">
@@ -38982,22 +39094,22 @@
       <c r="B19" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="239">
+      <c r="C19" s="241">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-5.6718433490884537E-3</v>
       </c>
-      <c r="D19" s="240"/>
-      <c r="F19" s="239">
+      <c r="D19" s="242"/>
+      <c r="F19" s="241">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-2.1918172157279491E-2</v>
       </c>
-      <c r="G19" s="240"/>
+      <c r="G19" s="242"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="204" t="s">
@@ -39024,22 +39136,22 @@
       <c r="B21" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="239">
+      <c r="C21" s="241">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.29225352112676062</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="F21" s="239">
+      <c r="D21" s="242"/>
+      <c r="F21" s="241">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.21818181818181812</v>
       </c>
-      <c r="G21" s="240"/>
+      <c r="G21" s="242"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -39087,22 +39199,22 @@
       <c r="B25" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="239">
+      <c r="C25" s="241">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.22956141399989749</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="F25" s="239">
+      <c r="D25" s="242"/>
+      <c r="F25" s="241">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.11851668113605358</v>
       </c>
-      <c r="G25" s="240"/>
+      <c r="G25" s="242"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -39129,22 +39241,22 @@
       <c r="B27" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="239">
+      <c r="C27" s="241">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-0.26453625543962672</v>
       </c>
-      <c r="D27" s="240"/>
-      <c r="F27" s="239">
+      <c r="D27" s="242"/>
+      <c r="F27" s="241">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.14725607262615523</v>
       </c>
-      <c r="G27" s="240"/>
+      <c r="G27" s="242"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -39171,22 +39283,22 @@
       <c r="B29" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="239">
+      <c r="C29" s="241">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-0.19701480843061975</v>
       </c>
-      <c r="D29" s="240"/>
-      <c r="F29" s="239">
+      <c r="D29" s="242"/>
+      <c r="F29" s="241">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.28090238720159982</v>
       </c>
-      <c r="G29" s="240"/>
+      <c r="G29" s="242"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -39213,22 +39325,22 @@
       <c r="B31" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C31" s="239">
+      <c r="C31" s="241">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-0.10751088919579305</v>
       </c>
-      <c r="D31" s="240"/>
-      <c r="F31" s="239">
+      <c r="D31" s="242"/>
+      <c r="F31" s="241">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.15113729788983282</v>
       </c>
-      <c r="G31" s="240"/>
+      <c r="G31" s="242"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -39255,22 +39367,22 @@
       <c r="B33" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C33" s="239">
+      <c r="C33" s="241">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-0.2474056992258277</v>
       </c>
-      <c r="D33" s="240"/>
-      <c r="F33" s="239">
+      <c r="D33" s="242"/>
+      <c r="F33" s="241">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.25349794238683127</v>
       </c>
-      <c r="G33" s="240"/>
+      <c r="G33" s="242"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="227" t="s">
@@ -39297,22 +39409,22 @@
       <c r="B36" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C36" s="239">
+      <c r="C36" s="241">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>-0.33159764979066247</v>
       </c>
-      <c r="D36" s="240"/>
-      <c r="F36" s="239">
+      <c r="D36" s="242"/>
+      <c r="F36" s="241">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>0.21675455263551163</v>
       </c>
-      <c r="G36" s="240"/>
+      <c r="G36" s="242"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="227" t="s">
@@ -39339,22 +39451,22 @@
       <c r="B38" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C38" s="239">
+      <c r="C38" s="241">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>1.550202718817076E-3</v>
       </c>
-      <c r="D38" s="240"/>
-      <c r="F38" s="239">
+      <c r="D38" s="242"/>
+      <c r="F38" s="241">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>5.661089445213234E-2</v>
       </c>
-      <c r="G38" s="240"/>
+      <c r="G38" s="242"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B39" s="227" t="s">
@@ -39381,22 +39493,22 @@
       <c r="B40" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C40" s="239">
+      <c r="C40" s="241">
         <f>IF(C39=0,
 IF(D39=0,0,IF(D39&gt;0,1,-1)),
 (D39-C39)/ABS(C39)
 )</f>
         <v>-0.19557882489819661</v>
       </c>
-      <c r="D40" s="240"/>
-      <c r="F40" s="239">
+      <c r="D40" s="242"/>
+      <c r="F40" s="241">
         <f>IF(F39=0,
 IF(G39=0,0,IF(G39&gt;0,1,-1)),
 (G39-F39)/ABS(F39)
 )</f>
         <v>7.9975007810059354E-2</v>
       </c>
-      <c r="G40" s="240"/>
+      <c r="G40" s="242"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B41" s="227" t="s">
@@ -39423,22 +39535,22 @@
       <c r="B42" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C42" s="239">
+      <c r="C42" s="241">
         <f>IF(C41=0,
 IF(D41=0,0,IF(D41&gt;0,1,-1)),
 (D41-C41)/ABS(C41)
 )</f>
         <v>-0.31253806664926476</v>
       </c>
-      <c r="D42" s="240"/>
-      <c r="F42" s="239">
+      <c r="D42" s="242"/>
+      <c r="F42" s="241">
         <f>IF(F41=0,
 IF(G41=0,0,IF(G41&gt;0,1,-1)),
 (G41-F41)/ABS(F41)
 )</f>
         <v>5.0385535761765486E-2</v>
       </c>
-      <c r="G42" s="240"/>
+      <c r="G42" s="242"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B43" s="227" t="s">
@@ -39465,25 +39577,55 @@
       <c r="B44" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C44" s="239">
+      <c r="C44" s="241">
         <f>IF(C43=0,
 IF(D43=0,0,IF(D43&gt;0,1,-1)),
 (D43-C43)/ABS(C43)
 )</f>
         <v>3.2086096025055806E-2</v>
       </c>
-      <c r="D44" s="240"/>
-      <c r="F44" s="239">
+      <c r="D44" s="242"/>
+      <c r="F44" s="241">
         <f>IF(F43=0,
 IF(G43=0,0,IF(G43&gt;0,1,-1)),
 (G43-F43)/ABS(F43)
 )</f>
         <v>0.16254456746106211</v>
       </c>
-      <c r="G44" s="240"/>
+      <c r="G44" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F36:G36"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="F44:G44"/>
     <mergeCell ref="C38:D38"/>
@@ -39492,36 +39634,6 @@
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="F42:G42"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
